--- a/data/BFF.MI.xlsx
+++ b/data/BFF.MI.xlsx
@@ -55411,6 +55411,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2394">
+      <c r="A2394" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2394" t="n">
+        <v>3685067</v>
+      </c>
+      <c r="C2394" t="n">
+        <v>3.22199988365173</v>
+      </c>
+      <c r="D2394" t="n">
+        <v>2.99200010299683</v>
+      </c>
+      <c r="E2394" t="n">
+        <v>3.14000010490417</v>
+      </c>
+      <c r="F2394" t="n">
+        <v>3.01399993896484</v>
+      </c>
+      <c r="G2394" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BFF.MI.xlsx
+++ b/data/BFF.MI.xlsx
@@ -55434,6 +55434,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2395">
+      <c r="A2395" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2395" t="n">
+        <v>2580885</v>
+      </c>
+      <c r="C2395" t="n">
+        <v>3.04999995231628</v>
+      </c>
+      <c r="D2395" t="n">
+        <v>2.91400003433228</v>
+      </c>
+      <c r="E2395" t="n">
+        <v>3.04999995231628</v>
+      </c>
+      <c r="F2395" t="n">
+        <v>3.01999998092651</v>
+      </c>
+      <c r="G2395" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BFF.MI.xlsx
+++ b/data/BFF.MI.xlsx
@@ -55457,6 +55457,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2396">
+      <c r="A2396" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2396" t="n">
+        <v>1205357</v>
+      </c>
+      <c r="C2396" t="n">
+        <v>3.05999994277954</v>
+      </c>
+      <c r="D2396" t="n">
+        <v>2.99200010299683</v>
+      </c>
+      <c r="E2396" t="n">
+        <v>3.03800010681152</v>
+      </c>
+      <c r="F2396" t="n">
+        <v>3.04200005531311</v>
+      </c>
+      <c r="G2396" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BFF.MI.xlsx
+++ b/data/BFF.MI.xlsx
@@ -55480,6 +55480,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2397">
+      <c r="A2397" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2397" t="n">
+        <v>1926641</v>
+      </c>
+      <c r="C2397" t="n">
+        <v>3.05999994277954</v>
+      </c>
+      <c r="D2397" t="n">
+        <v>2.99000000953674</v>
+      </c>
+      <c r="E2397" t="n">
+        <v>3.00999999046326</v>
+      </c>
+      <c r="F2397" t="n">
+        <v>3.05999994277954</v>
+      </c>
+      <c r="G2397" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BFF.MI.xlsx
+++ b/data/BFF.MI.xlsx
@@ -55321,22 +55321,22 @@
     </row>
     <row r="2390">
       <c r="A2390" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2390" t="n">
-        <v>1851327</v>
+        <v>2160774</v>
       </c>
       <c r="C2390" t="n">
-        <v>2.96799993515015</v>
+        <v>3.02800011634827</v>
       </c>
       <c r="D2390" t="n">
-        <v>2.91199994087219</v>
+        <v>2.96000003814697</v>
       </c>
       <c r="E2390" t="n">
-        <v>2.94799995422363</v>
+        <v>3.02800011634827</v>
       </c>
       <c r="F2390" t="n">
-        <v>2.93400001525879</v>
+        <v>2.97399997711182</v>
       </c>
       <c r="G2390" t="s">
         <v>7</v>
@@ -55344,22 +55344,22 @@
     </row>
     <row r="2391">
       <c r="A2391" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2391" t="n">
-        <v>2810695</v>
+        <v>1851327</v>
       </c>
       <c r="C2391" t="n">
-        <v>3.05999994277954</v>
+        <v>2.96799993515015</v>
       </c>
       <c r="D2391" t="n">
+        <v>2.91199994087219</v>
+      </c>
+      <c r="E2391" t="n">
+        <v>2.94799995422363</v>
+      </c>
+      <c r="F2391" t="n">
         <v>2.93400001525879</v>
-      </c>
-      <c r="E2391" t="n">
-        <v>2.94000005722046</v>
-      </c>
-      <c r="F2391" t="n">
-        <v>3.01600003242493</v>
       </c>
       <c r="G2391" t="s">
         <v>7</v>
@@ -55367,22 +55367,22 @@
     </row>
     <row r="2392">
       <c r="A2392" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2392" t="n">
-        <v>1503728</v>
+        <v>2810695</v>
       </c>
       <c r="C2392" t="n">
-        <v>3.04200005531311</v>
+        <v>3.05999994277954</v>
       </c>
       <c r="D2392" t="n">
-        <v>2.94199991226196</v>
+        <v>2.93400001525879</v>
       </c>
       <c r="E2392" t="n">
-        <v>3.03800010681152</v>
+        <v>2.94000005722046</v>
       </c>
       <c r="F2392" t="n">
-        <v>2.97000002861023</v>
+        <v>3.01600003242493</v>
       </c>
       <c r="G2392" t="s">
         <v>7</v>
@@ -55390,22 +55390,22 @@
     </row>
     <row r="2393">
       <c r="A2393" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2393" t="n">
-        <v>2871742</v>
+        <v>1503728</v>
       </c>
       <c r="C2393" t="n">
-        <v>3.16799998283386</v>
+        <v>3.04200005531311</v>
       </c>
       <c r="D2393" t="n">
-        <v>2.96000003814697</v>
+        <v>2.94199991226196</v>
       </c>
       <c r="E2393" t="n">
-        <v>3.00600004196167</v>
+        <v>3.03800010681152</v>
       </c>
       <c r="F2393" t="n">
-        <v>3.14400005340576</v>
+        <v>2.97000002861023</v>
       </c>
       <c r="G2393" t="s">
         <v>7</v>
@@ -55413,22 +55413,22 @@
     </row>
     <row r="2394">
       <c r="A2394" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2394" t="n">
-        <v>3685067</v>
+        <v>2871742</v>
       </c>
       <c r="C2394" t="n">
-        <v>3.22199988365173</v>
+        <v>3.16799998283386</v>
       </c>
       <c r="D2394" t="n">
-        <v>2.99200010299683</v>
+        <v>2.96000003814697</v>
       </c>
       <c r="E2394" t="n">
-        <v>3.14000010490417</v>
+        <v>3.00600004196167</v>
       </c>
       <c r="F2394" t="n">
-        <v>3.01399993896484</v>
+        <v>3.14400005340576</v>
       </c>
       <c r="G2394" t="s">
         <v>7</v>
@@ -55436,22 +55436,22 @@
     </row>
     <row r="2395">
       <c r="A2395" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2395" t="n">
-        <v>2580885</v>
+        <v>3685067</v>
       </c>
       <c r="C2395" t="n">
-        <v>3.04999995231628</v>
+        <v>3.22199988365173</v>
       </c>
       <c r="D2395" t="n">
-        <v>2.91400003433228</v>
+        <v>2.99200010299683</v>
       </c>
       <c r="E2395" t="n">
-        <v>3.04999995231628</v>
+        <v>3.14000010490417</v>
       </c>
       <c r="F2395" t="n">
-        <v>3.01999998092651</v>
+        <v>3.01399993896484</v>
       </c>
       <c r="G2395" t="s">
         <v>7</v>
@@ -55459,22 +55459,22 @@
     </row>
     <row r="2396">
       <c r="A2396" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2396" t="n">
-        <v>1205357</v>
+        <v>2580885</v>
       </c>
       <c r="C2396" t="n">
-        <v>3.05999994277954</v>
+        <v>3.04999995231628</v>
       </c>
       <c r="D2396" t="n">
-        <v>2.99200010299683</v>
+        <v>2.91400003433228</v>
       </c>
       <c r="E2396" t="n">
-        <v>3.03800010681152</v>
+        <v>3.04999995231628</v>
       </c>
       <c r="F2396" t="n">
-        <v>3.04200005531311</v>
+        <v>3.01999998092651</v>
       </c>
       <c r="G2396" t="s">
         <v>7</v>
@@ -55482,24 +55482,47 @@
     </row>
     <row r="2397">
       <c r="A2397" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2397" t="n">
-        <v>1926641</v>
+        <v>1205357</v>
       </c>
       <c r="C2397" t="n">
         <v>3.05999994277954</v>
       </c>
       <c r="D2397" t="n">
-        <v>2.99000000953674</v>
+        <v>2.99200010299683</v>
       </c>
       <c r="E2397" t="n">
+        <v>3.03800010681152</v>
+      </c>
+      <c r="F2397" t="n">
+        <v>3.04200005531311</v>
+      </c>
+      <c r="G2397" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2398">
+      <c r="A2398" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2398" t="n">
+        <v>2982908</v>
+      </c>
+      <c r="C2398" t="n">
+        <v>3.10800004005432</v>
+      </c>
+      <c r="D2398" t="n">
+        <v>2.99399995803833</v>
+      </c>
+      <c r="E2398" t="n">
+        <v>3.05999994277954</v>
+      </c>
+      <c r="F2398" t="n">
         <v>3.00999999046326</v>
       </c>
-      <c r="F2397" t="n">
-        <v>3.05999994277954</v>
-      </c>
-      <c r="G2397" t="s">
+      <c r="G2398" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/BFF.MI.xlsx
+++ b/data/BFF.MI.xlsx
@@ -421,7 +421,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G2" t="n">
-        <v>2.25471162796021</v>
+        <v>2.25471186637878</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>4.25</v>
       </c>
       <c r="G4" t="n">
-        <v>2.31461930274963</v>
+        <v>2.31461954116821</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>4.29400014877319</v>
       </c>
       <c r="G5" t="n">
-        <v>2.33858275413513</v>
+        <v>2.33858251571655</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>4.2979998588562</v>
       </c>
       <c r="G14" t="n">
-        <v>2.34076118469238</v>
+        <v>2.3407609462738</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G15" t="n">
-        <v>2.36363506317139</v>
+        <v>2.36363482475281</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>4.44600009918213</v>
       </c>
       <c r="G17" t="n">
-        <v>2.42136430740356</v>
+        <v>2.42136454582214</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>4.48600006103516</v>
       </c>
       <c r="G20" t="n">
-        <v>2.44314932823181</v>
+        <v>2.44314908981323</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G21" t="n">
-        <v>2.54335856437683</v>
+        <v>2.54335832595825</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G22" t="n">
-        <v>2.55969667434692</v>
+        <v>2.55969643592834</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>4.83599996566772</v>
       </c>
       <c r="G23" t="n">
-        <v>2.63376474380493</v>
+        <v>2.63376450538635</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>4.85400009155273</v>
       </c>
       <c r="G24" t="n">
-        <v>2.64356756210327</v>
+        <v>2.64356803894043</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G25" t="n">
-        <v>2.55969667434692</v>
+        <v>2.55969643592834</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>4.73799991607666</v>
       </c>
       <c r="G27" t="n">
-        <v>2.58039236068726</v>
+        <v>2.58039212226868</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>4.64200019836426</v>
       </c>
       <c r="G28" t="n">
-        <v>2.5281093120575</v>
+        <v>2.52810907363892</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>4.73199987411499</v>
       </c>
       <c r="G29" t="n">
-        <v>2.57712459564209</v>
+        <v>2.57712435722351</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>4.74200010299683</v>
       </c>
       <c r="G30" t="n">
-        <v>2.58257102966309</v>
+        <v>2.58257079124451</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>4.83799982070923</v>
       </c>
       <c r="G31" t="n">
-        <v>2.63485407829285</v>
+        <v>2.63485360145569</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>4.77600002288818</v>
       </c>
       <c r="G32" t="n">
-        <v>2.60108780860901</v>
+        <v>2.60108804702759</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G34" t="n">
-        <v>2.66317367553711</v>
+        <v>2.66317391395569</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G35" t="n">
-        <v>2.6849582195282</v>
+        <v>2.68495869636536</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>4.89799976348877</v>
       </c>
       <c r="G36" t="n">
-        <v>2.66753053665161</v>
+        <v>2.66753101348877</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G37" t="n">
-        <v>2.6849582195282</v>
+        <v>2.68495869636536</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>4.94799995422363</v>
       </c>
       <c r="G38" t="n">
-        <v>2.6947615146637</v>
+        <v>2.69476175308228</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>4.92199993133545</v>
       </c>
       <c r="G39" t="n">
-        <v>2.6806013584137</v>
+        <v>2.68060159683228</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>4.86800003051758</v>
       </c>
       <c r="G40" t="n">
-        <v>2.65119242668152</v>
+        <v>2.6511926651001</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G41" t="n">
-        <v>2.64138913154602</v>
+        <v>2.6413893699646</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G42" t="n">
-        <v>2.65772795677185</v>
+        <v>2.65772771835327</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G43" t="n">
-        <v>2.66862058639526</v>
+        <v>2.66862010955811</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>4.87599992752075</v>
       </c>
       <c r="G44" t="n">
-        <v>2.65554928779602</v>
+        <v>2.6555495262146</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>4.84600019454956</v>
       </c>
       <c r="G45" t="n">
-        <v>2.63921141624451</v>
+        <v>2.63921070098877</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>4.89599990844727</v>
       </c>
       <c r="G46" t="n">
-        <v>2.66644167900085</v>
+        <v>2.66644191741943</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>5.07499980926514</v>
       </c>
       <c r="G48" t="n">
-        <v>2.76392793655396</v>
+        <v>2.76392817497253</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G49" t="n">
-        <v>2.72852826118469</v>
+        <v>2.72852802276611</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G50" t="n">
-        <v>2.77754354476929</v>
+        <v>2.77754378318787</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G51" t="n">
-        <v>2.81022024154663</v>
+        <v>2.81022047996521</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G53" t="n">
-        <v>2.80749726295471</v>
+        <v>2.80749750137329</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>5</v>
       </c>
       <c r="G54" t="n">
-        <v>2.72308206558228</v>
+        <v>2.7230818271637</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G55" t="n">
-        <v>2.76120519638062</v>
+        <v>2.76120495796204</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G57" t="n">
-        <v>2.84289717674255</v>
+        <v>2.84289765357971</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G58" t="n">
-        <v>2.81022024154663</v>
+        <v>2.81022047996521</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>5</v>
       </c>
       <c r="G59" t="n">
-        <v>2.72308206558228</v>
+        <v>2.7230818271637</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G61" t="n">
-        <v>2.79932832717896</v>
+        <v>2.79932808876038</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G62" t="n">
-        <v>2.78298997879028</v>
+        <v>2.7829897403717</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G63" t="n">
-        <v>2.79932832717896</v>
+        <v>2.79932808876038</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>5.16499996185303</v>
       </c>
       <c r="G64" t="n">
-        <v>2.81294322013855</v>
+        <v>2.81294345855713</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G65" t="n">
-        <v>2.79388189315796</v>
+        <v>2.79388236999512</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>5.07499980926514</v>
       </c>
       <c r="G66" t="n">
-        <v>2.76392793655396</v>
+        <v>2.76392817497253</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G69" t="n">
-        <v>2.78843522071838</v>
+        <v>2.78843593597412</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>5.07499980926514</v>
       </c>
       <c r="G71" t="n">
-        <v>2.76392793655396</v>
+        <v>2.76392817497253</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G72" t="n">
-        <v>2.78026652336121</v>
+        <v>2.78026628494263</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G73" t="n">
-        <v>2.78026652336121</v>
+        <v>2.78026628494263</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G74" t="n">
-        <v>2.78843522071838</v>
+        <v>2.78843593597412</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>5.17500019073486</v>
       </c>
       <c r="G77" t="n">
-        <v>2.81838989257812</v>
+        <v>2.81838941574097</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G78" t="n">
-        <v>2.78843522071838</v>
+        <v>2.78843593597412</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G79" t="n">
-        <v>2.82655882835388</v>
+        <v>2.82655906677246</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G84" t="n">
-        <v>2.79932832717896</v>
+        <v>2.79932808876038</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G85" t="n">
-        <v>2.80749726295471</v>
+        <v>2.80749750137329</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G87" t="n">
-        <v>2.79388189315796</v>
+        <v>2.79388236999512</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>5.13500022888184</v>
       </c>
       <c r="G88" t="n">
-        <v>2.79660534858704</v>
+        <v>2.79660511016846</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>5.08500003814697</v>
       </c>
       <c r="G89" t="n">
-        <v>2.76937389373779</v>
+        <v>2.76937413215637</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G93" t="n">
-        <v>2.80749726295471</v>
+        <v>2.80749750137329</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G94" t="n">
-        <v>2.80749726295471</v>
+        <v>2.80749750137329</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G95" t="n">
-        <v>2.79932832717896</v>
+        <v>2.79932808876038</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>5.16499996185303</v>
       </c>
       <c r="G96" t="n">
-        <v>2.81294322013855</v>
+        <v>2.81294345855713</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G98" t="n">
-        <v>2.79932832717896</v>
+        <v>2.79932808876038</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>5.11499977111816</v>
       </c>
       <c r="G99" t="n">
-        <v>2.78571248054504</v>
+        <v>2.78571224212646</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>4.9520001411438</v>
       </c>
       <c r="G100" t="n">
-        <v>2.69694042205811</v>
+        <v>2.69693994522095</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>4.99200010299683</v>
       </c>
       <c r="G102" t="n">
-        <v>2.71872496604919</v>
+        <v>2.71872520446777</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G103" t="n">
-        <v>2.73942017555237</v>
+        <v>2.73942065238953</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G104" t="n">
-        <v>2.81022024154663</v>
+        <v>2.81022047996521</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G105" t="n">
-        <v>2.77754354476929</v>
+        <v>2.77754378318787</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G106" t="n">
-        <v>2.78026652336121</v>
+        <v>2.78026628494263</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>5.08500003814697</v>
       </c>
       <c r="G107" t="n">
-        <v>2.76937389373779</v>
+        <v>2.76937413215637</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G108" t="n">
-        <v>2.76665091514587</v>
+        <v>2.76665115356445</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G109" t="n">
-        <v>2.78843522071838</v>
+        <v>2.78843593597412</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>5.16499996185303</v>
       </c>
       <c r="G110" t="n">
-        <v>2.81294322013855</v>
+        <v>2.81294345855713</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G112" t="n">
-        <v>2.88102030754089</v>
+        <v>2.88102078437805</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G113" t="n">
-        <v>2.86468195915222</v>
+        <v>2.86468243598938</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>5.50500011444092</v>
       </c>
       <c r="G114" t="n">
-        <v>2.99811339378357</v>
+        <v>2.99811315536499</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>5.49499988555908</v>
       </c>
       <c r="G115" t="n">
-        <v>2.99266695976257</v>
+        <v>2.99266648292542</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G116" t="n">
-        <v>3.02806711196899</v>
+        <v>3.02806687355042</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G117" t="n">
-        <v>3.03895902633667</v>
+        <v>3.03895926475525</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>5.67500019073486</v>
       </c>
       <c r="G120" t="n">
-        <v>3.09069800376892</v>
+        <v>3.09069752693176</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G121" t="n">
-        <v>3.2404670715332</v>
+        <v>3.24046730995178</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G122" t="n">
-        <v>3.21323609352112</v>
+        <v>3.21323680877686</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G124" t="n">
-        <v>3.19689798355103</v>
+        <v>3.19689774513245</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G125" t="n">
-        <v>3.1260974407196</v>
+        <v>3.12609791755676</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G126" t="n">
-        <v>3.07708263397217</v>
+        <v>3.07708215713501</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G127" t="n">
-        <v>3.14243650436401</v>
+        <v>3.14243602752686</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G128" t="n">
-        <v>3.10431289672852</v>
+        <v>3.10431265830994</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>5.72499990463257</v>
       </c>
       <c r="G129" t="n">
-        <v>3.11792874336243</v>
+        <v>3.11792850494385</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G130" t="n">
-        <v>3.15877509117126</v>
+        <v>3.15877461433411</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>6.125</v>
       </c>
       <c r="G134" t="n">
-        <v>3.33577489852905</v>
+        <v>3.33577513694763</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>6.11499977111816</v>
       </c>
       <c r="G136" t="n">
-        <v>3.33032846450806</v>
+        <v>3.33032917976379</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>6</v>
       </c>
       <c r="G138" t="n">
-        <v>3.26769781112671</v>
+        <v>3.26769804954529</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>6.11499977111816</v>
       </c>
       <c r="G139" t="n">
-        <v>3.33032846450806</v>
+        <v>3.33032917976379</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G140" t="n">
-        <v>3.33305191993713</v>
+        <v>3.33305215835571</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G142" t="n">
-        <v>3.34939050674438</v>
+        <v>3.34939026832581</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G143" t="n">
-        <v>3.39295983314514</v>
+        <v>3.39295959472656</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G144" t="n">
-        <v>3.38751339912415</v>
+        <v>3.3875138759613</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>6.25</v>
       </c>
       <c r="G145" t="n">
-        <v>3.40385270118713</v>
+        <v>3.40385222434998</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G146" t="n">
-        <v>3.38206744194031</v>
+        <v>3.38206791877747</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>6.11499977111816</v>
       </c>
       <c r="G147" t="n">
-        <v>3.33032846450806</v>
+        <v>3.33032917976379</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>6.00500011444092</v>
       </c>
       <c r="G149" t="n">
-        <v>3.27042150497437</v>
+        <v>3.27042174339294</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>6.09499979019165</v>
       </c>
       <c r="G150" t="n">
-        <v>3.31943678855896</v>
+        <v>3.31943655014038</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G151" t="n">
-        <v>3.28403663635254</v>
+        <v>3.28403735160828</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G153" t="n">
-        <v>3.2459135055542</v>
+        <v>3.24591374397278</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>5.92999982833862</v>
       </c>
       <c r="G154" t="n">
-        <v>3.22957444190979</v>
+        <v>3.22957491874695</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G155" t="n">
-        <v>3.21323609352112</v>
+        <v>3.21323680877686</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G156" t="n">
-        <v>3.27314424514771</v>
+        <v>3.27314400672913</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>6</v>
       </c>
       <c r="G157" t="n">
-        <v>3.26769781112671</v>
+        <v>3.26769804954529</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>6.125</v>
       </c>
       <c r="G159" t="n">
-        <v>3.33577489852905</v>
+        <v>3.33577513694763</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G161" t="n">
-        <v>3.38206744194031</v>
+        <v>3.38206791877747</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>6.40999984741211</v>
       </c>
       <c r="G162" t="n">
-        <v>3.49099063873291</v>
+        <v>3.49099087715149</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G163" t="n">
-        <v>3.512775182724</v>
+        <v>3.51277494430542</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G164" t="n">
-        <v>3.47465229034424</v>
+        <v>3.47465181350708</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G165" t="n">
-        <v>3.45831346511841</v>
+        <v>3.45831418037415</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>6.41499996185303</v>
       </c>
       <c r="G166" t="n">
-        <v>3.49371433258057</v>
+        <v>3.49371385574341</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>6.36499977111816</v>
       </c>
       <c r="G168" t="n">
-        <v>3.46648263931274</v>
+        <v>3.46648335456848</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>6.40999984741211</v>
       </c>
       <c r="G171" t="n">
-        <v>3.49099063873291</v>
+        <v>3.49099087715149</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G172" t="n">
-        <v>3.583575963974</v>
+        <v>3.58357548713684</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G173" t="n">
-        <v>3.56179094314575</v>
+        <v>3.56179070472717</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>6.58500003814697</v>
       </c>
       <c r="G174" t="n">
-        <v>3.58629822731018</v>
+        <v>3.58629894256592</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>6.53000020980835</v>
       </c>
       <c r="G176" t="n">
-        <v>3.55634450912476</v>
+        <v>3.55634474754333</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G177" t="n">
-        <v>3.52366781234741</v>
+        <v>3.52366757392883</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>6.53499984741211</v>
       </c>
       <c r="G178" t="n">
-        <v>3.55906796455383</v>
+        <v>3.55906772613525</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>6.5149998664856</v>
       </c>
       <c r="G179" t="n">
-        <v>3.54817533493042</v>
+        <v>3.54817581176758</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G182" t="n">
-        <v>3.47465229034424</v>
+        <v>3.47465181350708</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>6.25</v>
       </c>
       <c r="G183" t="n">
-        <v>3.40385270118713</v>
+        <v>3.40385222434998</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G184" t="n">
-        <v>3.44742155075073</v>
+        <v>3.44742178916931</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>6.38500022888184</v>
       </c>
       <c r="G185" t="n">
-        <v>3.47737550735474</v>
+        <v>3.47737526893616</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G186" t="n">
-        <v>3.48554491996765</v>
+        <v>3.48554539680481</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>6.41499996185303</v>
       </c>
       <c r="G187" t="n">
-        <v>3.49371433258057</v>
+        <v>3.49371385574341</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>6.53499984741211</v>
       </c>
       <c r="G188" t="n">
-        <v>3.55906796455383</v>
+        <v>3.55906772613525</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>6.5</v>
       </c>
       <c r="G189" t="n">
-        <v>3.5400059223175</v>
+        <v>3.54000616073608</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>6.5</v>
       </c>
       <c r="G191" t="n">
-        <v>3.5400059223175</v>
+        <v>3.54000616073608</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>6.43499994277954</v>
       </c>
       <c r="G192" t="n">
-        <v>3.50460648536682</v>
+        <v>3.5046067237854</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G193" t="n">
-        <v>3.56179094314575</v>
+        <v>3.56179070472717</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G194" t="n">
-        <v>3.47465229034424</v>
+        <v>3.47465181350708</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>6.46500015258789</v>
       </c>
       <c r="G195" t="n">
-        <v>3.52094507217407</v>
+        <v>3.52094459533691</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G196" t="n">
-        <v>3.52911376953125</v>
+        <v>3.52911400794983</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>6.5</v>
       </c>
       <c r="G197" t="n">
-        <v>3.5400059223175</v>
+        <v>3.54000616073608</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G202" t="n">
-        <v>3.58902192115784</v>
+        <v>3.58902168273926</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>6.53000020980835</v>
       </c>
       <c r="G204" t="n">
-        <v>3.55634450912476</v>
+        <v>3.55634474754333</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>6.59499979019165</v>
       </c>
       <c r="G205" t="n">
-        <v>3.59174489974976</v>
+        <v>3.59174466133118</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G206" t="n">
-        <v>3.59991431236267</v>
+        <v>3.59991383552551</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>6.41499996185303</v>
       </c>
       <c r="G209" t="n">
-        <v>3.49371433258057</v>
+        <v>3.49371385574341</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G211" t="n">
-        <v>3.28403663635254</v>
+        <v>3.28403735160828</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G214" t="n">
-        <v>3.12065148353577</v>
+        <v>3.12065172195435</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>5.92999982833862</v>
       </c>
       <c r="G215" t="n">
-        <v>3.22957444190979</v>
+        <v>3.22957491874695</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G216" t="n">
-        <v>3.16966724395752</v>
+        <v>3.1696674823761</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>5.81500005722046</v>
       </c>
       <c r="G217" t="n">
-        <v>3.1669442653656</v>
+        <v>3.16694474220276</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>5.93499994277954</v>
       </c>
       <c r="G218" t="n">
-        <v>3.23229813575745</v>
+        <v>3.23229837417603</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>6</v>
       </c>
       <c r="G219" t="n">
-        <v>3.26769781112671</v>
+        <v>3.26769804954529</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G220" t="n">
-        <v>3.38206744194031</v>
+        <v>3.38206791877747</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>6.14499998092651</v>
       </c>
       <c r="G221" t="n">
-        <v>3.34666800498962</v>
+        <v>3.34666752815247</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G223" t="n">
-        <v>3.21323609352112</v>
+        <v>3.21323680877686</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G224" t="n">
-        <v>3.18055939674377</v>
+        <v>3.1805591583252</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G225" t="n">
-        <v>3.16966724395752</v>
+        <v>3.1696674823761</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G226" t="n">
-        <v>3.16966724395752</v>
+        <v>3.1696674823761</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>5.81500005722046</v>
       </c>
       <c r="G227" t="n">
-        <v>3.1669442653656</v>
+        <v>3.16694474220276</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G228" t="n">
-        <v>3.18600559234619</v>
+        <v>3.18600583076477</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G229" t="n">
-        <v>3.18600559234619</v>
+        <v>3.18600583076477</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>5.78499984741211</v>
       </c>
       <c r="G231" t="n">
-        <v>3.15060567855835</v>
+        <v>3.15060520172119</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G232" t="n">
-        <v>3.15877509117126</v>
+        <v>3.15877461433411</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>5.88500022888184</v>
       </c>
       <c r="G234" t="n">
-        <v>3.20506763458252</v>
+        <v>3.20506691932678</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>5.95499992370605</v>
       </c>
       <c r="G235" t="n">
-        <v>3.24319052696228</v>
+        <v>3.2431902885437</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>5.95499992370605</v>
       </c>
       <c r="G237" t="n">
-        <v>3.24319052696228</v>
+        <v>3.2431902885437</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G238" t="n">
-        <v>3.2404670715332</v>
+        <v>3.24046730995178</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>5.88500022888184</v>
       </c>
       <c r="G239" t="n">
-        <v>3.20506763458252</v>
+        <v>3.20506691932678</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>5.88500022888184</v>
       </c>
       <c r="G241" t="n">
-        <v>3.20506763458252</v>
+        <v>3.20506691932678</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G246" t="n">
-        <v>3.09342098236084</v>
+        <v>3.09342050552368</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G247" t="n">
-        <v>3.16422080993652</v>
+        <v>3.1642210483551</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G248" t="n">
-        <v>3.18600559234619</v>
+        <v>3.18600583076477</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G249" t="n">
-        <v>3.23502159118652</v>
+        <v>3.23502087593079</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G250" t="n">
-        <v>3.21323609352112</v>
+        <v>3.21323680877686</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G251" t="n">
-        <v>3.18600559234619</v>
+        <v>3.18600583076477</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G255" t="n">
-        <v>3.26296758651733</v>
+        <v>3.26296734809875</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G258" t="n">
-        <v>3.24513745307922</v>
+        <v>3.24513721466064</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G259" t="n">
-        <v>3.21542000770569</v>
+        <v>3.21541953086853</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G260" t="n">
-        <v>3.1559853553772</v>
+        <v>3.15598487854004</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G261" t="n">
-        <v>3.20947599411011</v>
+        <v>3.20947623252869</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>5.41499996185303</v>
       </c>
       <c r="G262" t="n">
-        <v>3.21839118003845</v>
+        <v>3.21839165687561</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>5.35500001907349</v>
       </c>
       <c r="G263" t="n">
-        <v>3.18273091316223</v>
+        <v>3.18273067474365</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>5.36499977111816</v>
       </c>
       <c r="G264" t="n">
-        <v>3.18867421150208</v>
+        <v>3.1886739730835</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>5.25500011444092</v>
       </c>
       <c r="G265" t="n">
-        <v>3.12329602241516</v>
+        <v>3.12329626083374</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G266" t="n">
-        <v>3.06386137008667</v>
+        <v>3.06386160850525</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G267" t="n">
-        <v>3.13815474510193</v>
+        <v>3.13815498352051</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>5.25</v>
       </c>
       <c r="G270" t="n">
-        <v>3.12032437324524</v>
+        <v>3.12032413482666</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G271" t="n">
-        <v>3.13815474510193</v>
+        <v>3.13815498352051</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>5.25500011444092</v>
       </c>
       <c r="G272" t="n">
-        <v>3.12329602241516</v>
+        <v>3.12329626083374</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G274" t="n">
-        <v>3.09655070304871</v>
+        <v>3.09654974937439</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G275" t="n">
-        <v>3.07277607917786</v>
+        <v>3.07277679443359</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>5.22499990463257</v>
       </c>
       <c r="G278" t="n">
-        <v>3.10546588897705</v>
+        <v>3.10546565055847</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G279" t="n">
-        <v>3.01928544044495</v>
+        <v>3.01928496360779</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G281" t="n">
-        <v>3.04305911064148</v>
+        <v>3.0430588722229</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>5.07499980926514</v>
       </c>
       <c r="G283" t="n">
-        <v>3.01631307601929</v>
+        <v>3.01631379127502</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G284" t="n">
-        <v>3.03414392471313</v>
+        <v>3.03414344787598</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G285" t="n">
-        <v>2.98362445831299</v>
+        <v>2.98362421989441</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G286" t="n">
-        <v>3.03117203712463</v>
+        <v>3.03117227554321</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G287" t="n">
-        <v>3.06386137008667</v>
+        <v>3.06386160850525</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>4.89200019836426</v>
       </c>
       <c r="G289" t="n">
-        <v>2.90754795074463</v>
+        <v>2.90754818916321</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>5.07499980926514</v>
       </c>
       <c r="G290" t="n">
-        <v>3.01631307601929</v>
+        <v>3.01631379127502</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>5.07499980926514</v>
       </c>
       <c r="G291" t="n">
-        <v>3.01631307601929</v>
+        <v>3.01631379127502</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G293" t="n">
-        <v>3.09060668945312</v>
+        <v>3.09060645103455</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G294" t="n">
-        <v>3.06683254241943</v>
+        <v>3.06683325767517</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>5.11499977111816</v>
       </c>
       <c r="G295" t="n">
-        <v>3.0400869846344</v>
+        <v>3.04008650779724</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G299" t="n">
-        <v>3.11438059806824</v>
+        <v>3.11438083648682</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G300" t="n">
-        <v>3.09060668945312</v>
+        <v>3.09060645103455</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>5.29500007629395</v>
       </c>
       <c r="G301" t="n">
-        <v>3.14706969261169</v>
+        <v>3.14706993103027</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G303" t="n">
-        <v>3.1559853553772</v>
+        <v>3.15598487854004</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G304" t="n">
-        <v>3.20353221893311</v>
+        <v>3.20353269577026</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G305" t="n">
-        <v>3.14409804344177</v>
+        <v>3.14409852027893</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G308" t="n">
-        <v>3.01928544044495</v>
+        <v>3.01928496360779</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>4.95599985122681</v>
       </c>
       <c r="G310" t="n">
-        <v>2.94558572769165</v>
+        <v>2.94558620452881</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G312" t="n">
-        <v>2.98362445831299</v>
+        <v>2.98362421989441</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>5</v>
       </c>
       <c r="G313" t="n">
-        <v>2.97173762321472</v>
+        <v>2.97173714637756</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>4.93200016021729</v>
       </c>
       <c r="G315" t="n">
-        <v>2.93132162094116</v>
+        <v>2.93132185935974</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>4.96199989318848</v>
       </c>
       <c r="G316" t="n">
-        <v>2.94915199279785</v>
+        <v>2.94915223121643</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G317" t="n">
-        <v>2.98956823348999</v>
+        <v>2.98956775665283</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G319" t="n">
-        <v>3.07277607917786</v>
+        <v>3.07277679443359</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G320" t="n">
-        <v>3.04305911064148</v>
+        <v>3.0430588722229</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G321" t="n">
-        <v>3.02522873878479</v>
+        <v>3.02522826194763</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G323" t="n">
-        <v>3.06683254241943</v>
+        <v>3.06683325767517</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G324" t="n">
-        <v>3.13815474510193</v>
+        <v>3.13815498352051</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>5.2350001335144</v>
       </c>
       <c r="G326" t="n">
-        <v>3.11140942573547</v>
+        <v>3.11140918731689</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G328" t="n">
-        <v>3.08466339111328</v>
+        <v>3.0846631526947</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G330" t="n">
-        <v>3.09060668945312</v>
+        <v>3.09060645103455</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>5.29500007629395</v>
       </c>
       <c r="G332" t="n">
-        <v>3.14706969261169</v>
+        <v>3.14706993103027</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G333" t="n">
-        <v>3.18570256233215</v>
+        <v>3.18570280075073</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G336" t="n">
-        <v>3.15004205703735</v>
+        <v>3.15004181861877</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>5.28499984741211</v>
       </c>
       <c r="G337" t="n">
-        <v>3.14112615585327</v>
+        <v>3.14112639427185</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>5.17500019073486</v>
       </c>
       <c r="G338" t="n">
-        <v>3.07574868202209</v>
+        <v>3.07574820518494</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G339" t="n">
-        <v>3.18570256233215</v>
+        <v>3.18570280075073</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G340" t="n">
-        <v>3.20947599411011</v>
+        <v>3.20947623252869</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>5.35500001907349</v>
       </c>
       <c r="G342" t="n">
-        <v>3.18273091316223</v>
+        <v>3.18273067474365</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G343" t="n">
-        <v>3.16787219047546</v>
+        <v>3.16787195205688</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G345" t="n">
-        <v>3.10249400138855</v>
+        <v>3.10249376296997</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G348" t="n">
-        <v>3.08466339111328</v>
+        <v>3.0846631526947</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G349" t="n">
-        <v>3.06683254241943</v>
+        <v>3.06683325767517</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>5.21500015258789</v>
       </c>
       <c r="G352" t="n">
-        <v>3.09952187538147</v>
+        <v>3.09952211380005</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>5.17500019073486</v>
       </c>
       <c r="G353" t="n">
-        <v>3.07574868202209</v>
+        <v>3.07574820518494</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>5.16499996185303</v>
       </c>
       <c r="G354" t="n">
-        <v>3.06980443000793</v>
+        <v>3.06980466842651</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G355" t="n">
-        <v>3.07277607917786</v>
+        <v>3.07277679443359</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>5.125</v>
       </c>
       <c r="G358" t="n">
-        <v>3.04603028297424</v>
+        <v>3.04603099822998</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G359" t="n">
-        <v>3.07277607917786</v>
+        <v>3.07277679443359</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G362" t="n">
-        <v>3.06683254241943</v>
+        <v>3.06683325767517</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>5.125</v>
       </c>
       <c r="G367" t="n">
-        <v>3.04603028297424</v>
+        <v>3.04603099822998</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G369" t="n">
-        <v>3.09060668945312</v>
+        <v>3.09060645103455</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G370" t="n">
-        <v>3.11438059806824</v>
+        <v>3.11438083648682</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G371" t="n">
-        <v>3.1559853553772</v>
+        <v>3.15598487854004</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G372" t="n">
-        <v>3.09655070304871</v>
+        <v>3.09654974937439</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G373" t="n">
-        <v>3.07277607917786</v>
+        <v>3.07277679443359</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G374" t="n">
-        <v>3.09655070304871</v>
+        <v>3.09654974937439</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>5.25500011444092</v>
       </c>
       <c r="G375" t="n">
-        <v>3.12329602241516</v>
+        <v>3.12329626083374</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G376" t="n">
-        <v>3.06683254241943</v>
+        <v>3.06683325767517</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>5.09499979019165</v>
       </c>
       <c r="G377" t="n">
-        <v>3.02819991111755</v>
+        <v>3.02820014953613</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>5.09499979019165</v>
       </c>
       <c r="G378" t="n">
-        <v>3.02819991111755</v>
+        <v>3.02820014953613</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G380" t="n">
-        <v>3.04305911064148</v>
+        <v>3.0430588722229</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>4.98799991607666</v>
       </c>
       <c r="G381" t="n">
-        <v>2.96460485458374</v>
+        <v>2.9646053314209</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G382" t="n">
-        <v>2.81720685958862</v>
+        <v>2.81720733642578</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G383" t="n">
-        <v>2.79937672615051</v>
+        <v>2.79937648773193</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>4.71799993515015</v>
       </c>
       <c r="G385" t="n">
-        <v>2.80413126945496</v>
+        <v>2.80413150787354</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>4.68400001525879</v>
       </c>
       <c r="G387" t="n">
-        <v>2.78392362594604</v>
+        <v>2.78392338752747</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G388" t="n">
-        <v>2.85881161689758</v>
+        <v>2.858811378479</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>4.71400022506714</v>
       </c>
       <c r="G389" t="n">
-        <v>2.80175399780273</v>
+        <v>2.80175423622131</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G390" t="n">
-        <v>2.80532002449036</v>
+        <v>2.8053195476532</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>4.59600019454956</v>
       </c>
       <c r="G391" t="n">
-        <v>2.73162126541138</v>
+        <v>2.7316210269928</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>4.58199977874756</v>
       </c>
       <c r="G392" t="n">
-        <v>2.72330021858215</v>
+        <v>2.723299741745</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>4.43400001525879</v>
       </c>
       <c r="G393" t="n">
-        <v>2.63533639907837</v>
+        <v>2.63533663749695</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G395" t="n">
-        <v>2.57946825027466</v>
+        <v>2.57946801185608</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G397" t="n">
-        <v>2.63295912742615</v>
+        <v>2.63295888900757</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>4.49599981307983</v>
       </c>
       <c r="G398" t="n">
-        <v>2.67218637466431</v>
+        <v>2.67218589782715</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G399" t="n">
-        <v>2.70428133010864</v>
+        <v>2.70428109169006</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G400" t="n">
-        <v>2.70428133010864</v>
+        <v>2.70428109169006</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G402" t="n">
-        <v>2.71022415161133</v>
+        <v>2.71022439002991</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G403" t="n">
-        <v>2.68645024299622</v>
+        <v>2.68645071983337</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>4.73600006103516</v>
       </c>
       <c r="G404" t="n">
-        <v>2.8148295879364</v>
+        <v>2.81482934951782</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>4.61399984359741</v>
       </c>
       <c r="G405" t="n">
-        <v>2.74231886863708</v>
+        <v>2.74231910705566</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>4.61199998855591</v>
       </c>
       <c r="G406" t="n">
-        <v>2.74113059043884</v>
+        <v>2.74113011360168</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G407" t="n">
-        <v>2.73994183540344</v>
+        <v>2.73994207382202</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>4.57600021362305</v>
       </c>
       <c r="G409" t="n">
-        <v>2.71973466873169</v>
+        <v>2.71973395347595</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>4.57600021362305</v>
       </c>
       <c r="G410" t="n">
-        <v>2.71973466873169</v>
+        <v>2.71973395347595</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G412" t="n">
-        <v>2.71022415161133</v>
+        <v>2.71022439002991</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>4.48799991607666</v>
       </c>
       <c r="G413" t="n">
-        <v>2.66743135452271</v>
+        <v>2.66743111610413</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G414" t="n">
-        <v>2.70428133010864</v>
+        <v>2.70428109169006</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>4.56599998474121</v>
       </c>
       <c r="G416" t="n">
-        <v>2.71379065513611</v>
+        <v>2.71379041671753</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G417" t="n">
-        <v>2.79343318939209</v>
+        <v>2.79343271255493</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>4.67199993133545</v>
       </c>
       <c r="G418" t="n">
-        <v>2.77679133415222</v>
+        <v>2.7767915725708</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G419" t="n">
-        <v>2.72805500030518</v>
+        <v>2.7280547618866</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>4.59800004959106</v>
       </c>
       <c r="G420" t="n">
-        <v>2.73281002044678</v>
+        <v>2.73280954360962</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G421" t="n">
-        <v>2.74588489532471</v>
+        <v>2.74588537216187</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>4.60400009155273</v>
       </c>
       <c r="G422" t="n">
-        <v>2.73637580871582</v>
+        <v>2.7363760471344</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>4.59800004959106</v>
       </c>
       <c r="G424" t="n">
-        <v>2.73281002044678</v>
+        <v>2.73280954360962</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>4.53599977493286</v>
       </c>
       <c r="G425" t="n">
-        <v>2.69596004486084</v>
+        <v>2.69596028327942</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>4.46199989318848</v>
       </c>
       <c r="G428" t="n">
-        <v>2.65197849273682</v>
+        <v>2.65197825431824</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>4.61800003051758</v>
       </c>
       <c r="G430" t="n">
-        <v>2.74469661712646</v>
+        <v>2.74469637870789</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>4.53399991989136</v>
       </c>
       <c r="G431" t="n">
-        <v>2.69477105140686</v>
+        <v>2.69477128982544</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>4.48199987411499</v>
       </c>
       <c r="G433" t="n">
-        <v>2.66386556625366</v>
+        <v>2.66386461257935</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G434" t="n">
-        <v>2.69239377975464</v>
+        <v>2.69239401817322</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>4.49599981307983</v>
       </c>
       <c r="G436" t="n">
-        <v>2.67218637466431</v>
+        <v>2.67218589782715</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>4.45599985122681</v>
       </c>
       <c r="G437" t="n">
-        <v>2.64841222763062</v>
+        <v>2.64841246604919</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>4.57800006866455</v>
       </c>
       <c r="G439" t="n">
-        <v>2.72092270851135</v>
+        <v>2.72092294692993</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>4.72800016403198</v>
       </c>
       <c r="G440" t="n">
-        <v>2.81007480621338</v>
+        <v>2.81007504463196</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G441" t="n">
-        <v>2.86475515365601</v>
+        <v>2.86475491523743</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G443" t="n">
-        <v>2.95390677452087</v>
+        <v>2.95390701293945</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>4.85599994659424</v>
       </c>
       <c r="G444" t="n">
-        <v>2.88615131378174</v>
+        <v>2.88615155220032</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>4.78399991989136</v>
       </c>
       <c r="G445" t="n">
-        <v>2.84335803985596</v>
+        <v>2.84335827827454</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>4.78399991989136</v>
       </c>
       <c r="G446" t="n">
-        <v>2.84335803985596</v>
+        <v>2.84335827827454</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>4.73199987411499</v>
       </c>
       <c r="G447" t="n">
-        <v>2.81245183944702</v>
+        <v>2.8124520778656</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>4.81199979782104</v>
       </c>
       <c r="G449" t="n">
-        <v>2.85999989509583</v>
+        <v>2.8600001335144</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>4.84600019454956</v>
       </c>
       <c r="G452" t="n">
-        <v>2.88020825386047</v>
+        <v>2.88020801544189</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>4.86199998855591</v>
       </c>
       <c r="G454" t="n">
-        <v>2.88971710205078</v>
+        <v>2.88971757888794</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>4.92399978637695</v>
       </c>
       <c r="G456" t="n">
-        <v>2.92656683921814</v>
+        <v>2.92656707763672</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>4.92600011825562</v>
       </c>
       <c r="G457" t="n">
-        <v>2.92775583267212</v>
+        <v>2.92775559425354</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G458" t="n">
-        <v>3.0014545917511</v>
+        <v>3.00145506858826</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G460" t="n">
-        <v>3.04305911064148</v>
+        <v>3.0430588722229</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G464" t="n">
-        <v>3.04305911064148</v>
+        <v>3.0430588722229</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>5.11499977111816</v>
       </c>
       <c r="G466" t="n">
-        <v>3.0400869846344</v>
+        <v>3.04008650779724</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>5.25</v>
       </c>
       <c r="G468" t="n">
-        <v>3.12032437324524</v>
+        <v>3.12032413482666</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G469" t="n">
-        <v>3.16787219047546</v>
+        <v>3.16787195205688</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>5.25</v>
       </c>
       <c r="G470" t="n">
-        <v>3.12032437324524</v>
+        <v>3.12032413482666</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G472" t="n">
-        <v>3.21542000770569</v>
+        <v>3.21541953086853</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G473" t="n">
-        <v>3.16787219047546</v>
+        <v>3.16787195205688</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G474" t="n">
-        <v>3.16787219047546</v>
+        <v>3.16787195205688</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G475" t="n">
-        <v>3.15004205703735</v>
+        <v>3.15004181861877</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G476" t="n">
-        <v>3.13518309593201</v>
+        <v>3.13518285751343</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G477" t="n">
-        <v>3.15004205703735</v>
+        <v>3.15004181861877</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G478" t="n">
-        <v>3.09060668945312</v>
+        <v>3.09060645103455</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>5.24499988555908</v>
       </c>
       <c r="G480" t="n">
-        <v>3.11735200881958</v>
+        <v>3.11735248565674</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G481" t="n">
-        <v>3.14409804344177</v>
+        <v>3.14409852027893</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G482" t="n">
-        <v>3.15004205703735</v>
+        <v>3.15004181861877</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>5.30499982833862</v>
       </c>
       <c r="G483" t="n">
-        <v>3.15301275253296</v>
+        <v>3.15301299095154</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G486" t="n">
-        <v>3.16787219047546</v>
+        <v>3.16787195205688</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G487" t="n">
-        <v>3.18570256233215</v>
+        <v>3.18570280075073</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>5.35500001907349</v>
       </c>
       <c r="G489" t="n">
-        <v>3.18273091316223</v>
+        <v>3.18273067474365</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G490" t="n">
-        <v>3.22730684280396</v>
+        <v>3.22730660438538</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>5.49499988555908</v>
       </c>
       <c r="G491" t="n">
-        <v>3.26593923568726</v>
+        <v>3.2659387588501</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>5.57499980926514</v>
       </c>
       <c r="G492" t="n">
-        <v>3.3134868144989</v>
+        <v>3.31348705291748</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G494" t="n">
-        <v>3.29862880706787</v>
+        <v>3.29862856864929</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G495" t="n">
-        <v>3.29862880706787</v>
+        <v>3.29862856864929</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G496" t="n">
-        <v>3.29268550872803</v>
+        <v>3.29268527030945</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>5.54500007629395</v>
       </c>
       <c r="G498" t="n">
-        <v>3.29565691947937</v>
+        <v>3.29565620422363</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>5.625</v>
       </c>
       <c r="G499" t="n">
-        <v>3.34320425987244</v>
+        <v>3.34320497512817</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>5.60500001907349</v>
       </c>
       <c r="G500" t="n">
-        <v>3.33131742477417</v>
+        <v>3.33131766319275</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>5.42500019073486</v>
       </c>
       <c r="G501" t="n">
-        <v>3.22433495521545</v>
+        <v>3.22433519363403</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>4.99499988555908</v>
       </c>
       <c r="G502" t="n">
-        <v>3.29626536369324</v>
+        <v>3.2962658405304</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>4.96500015258789</v>
       </c>
       <c r="G503" t="n">
-        <v>3.27646851539612</v>
+        <v>3.27646827697754</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G506" t="n">
-        <v>3.3853542804718</v>
+        <v>3.38535380363464</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G507" t="n">
-        <v>3.33256101608276</v>
+        <v>3.33256077766418</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G508" t="n">
-        <v>3.32596182823181</v>
+        <v>3.32596158981323</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G509" t="n">
-        <v>3.31936264038086</v>
+        <v>3.31936311721802</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G512" t="n">
-        <v>3.40515112876892</v>
+        <v>3.40515160560608</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G513" t="n">
-        <v>3.39195322990417</v>
+        <v>3.39195275306702</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G515" t="n">
-        <v>3.41175031661987</v>
+        <v>3.41175055503845</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G519" t="n">
-        <v>3.50413846969604</v>
+        <v>3.50413870811462</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G520" t="n">
-        <v>3.51073789596558</v>
+        <v>3.510737657547</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>5.25</v>
       </c>
       <c r="G522" t="n">
-        <v>3.46454334259033</v>
+        <v>3.46454405784607</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G523" t="n">
-        <v>3.43154764175415</v>
+        <v>3.43154740333557</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G524" t="n">
-        <v>3.39855194091797</v>
+        <v>3.39855217933655</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G525" t="n">
-        <v>3.3853542804718</v>
+        <v>3.38535380363464</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G526" t="n">
-        <v>3.35895752906799</v>
+        <v>3.35895776748657</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G527" t="n">
-        <v>3.33256101608276</v>
+        <v>3.33256077766418</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G529" t="n">
-        <v>3.27976751327515</v>
+        <v>3.27976775169373</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>5</v>
       </c>
       <c r="G530" t="n">
-        <v>3.29956483840942</v>
+        <v>3.29956555366516</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>4.9850001335144</v>
       </c>
       <c r="G532" t="n">
-        <v>3.28966641426086</v>
+        <v>3.28966665267944</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>4.9850001335144</v>
       </c>
       <c r="G533" t="n">
-        <v>3.28966641426086</v>
+        <v>3.28966665267944</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G534" t="n">
-        <v>3.27316856384277</v>
+        <v>3.27316880226135</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G535" t="n">
-        <v>3.30616426467896</v>
+        <v>3.30616450309753</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G536" t="n">
-        <v>3.2665696144104</v>
+        <v>3.26656937599182</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G537" t="n">
-        <v>3.14778542518616</v>
+        <v>3.147784948349</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G539" t="n">
-        <v>3.22037577629089</v>
+        <v>3.22037553787231</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G540" t="n">
-        <v>3.20387816429138</v>
+        <v>3.20387768745422</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>4.81500005722046</v>
       </c>
       <c r="G541" t="n">
-        <v>3.17748117446899</v>
+        <v>3.17748141288757</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G542" t="n">
-        <v>3.20387816429138</v>
+        <v>3.20387768745422</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>4.77500009536743</v>
       </c>
       <c r="G543" t="n">
-        <v>3.15108442306519</v>
+        <v>3.15108489990234</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>4.74499988555908</v>
       </c>
       <c r="G544" t="n">
-        <v>3.13128733634949</v>
+        <v>3.13128709793091</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>4.9850001335144</v>
       </c>
       <c r="G546" t="n">
-        <v>3.28966641426086</v>
+        <v>3.28966665267944</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G547" t="n">
-        <v>3.31936264038086</v>
+        <v>3.31936311721802</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G548" t="n">
-        <v>3.2665696144104</v>
+        <v>3.26656937599182</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G549" t="n">
-        <v>3.28636693954468</v>
+        <v>3.2863667011261</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>4.96500015258789</v>
       </c>
       <c r="G552" t="n">
-        <v>3.27646851539612</v>
+        <v>3.27646827697754</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>4.93499994277954</v>
       </c>
       <c r="G553" t="n">
-        <v>3.25667095184326</v>
+        <v>3.25667071342468</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G554" t="n">
-        <v>3.24017286300659</v>
+        <v>3.24017333984375</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G557" t="n">
-        <v>3.31936264038086</v>
+        <v>3.31936311721802</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G560" t="n">
-        <v>3.22037577629089</v>
+        <v>3.22037553787231</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G562" t="n">
-        <v>3.21377635002136</v>
+        <v>3.21377682685852</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G563" t="n">
-        <v>3.2335741519928</v>
+        <v>3.23357367515564</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G564" t="n">
-        <v>3.25997042655945</v>
+        <v>3.25997090339661</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>5</v>
       </c>
       <c r="G566" t="n">
-        <v>3.29956483840942</v>
+        <v>3.29956555366516</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G567" t="n">
-        <v>3.33256101608276</v>
+        <v>3.33256077766418</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G568" t="n">
-        <v>3.33915996551514</v>
+        <v>3.33915972709656</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G569" t="n">
-        <v>3.35235857963562</v>
+        <v>3.35235810279846</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G570" t="n">
-        <v>3.33256101608276</v>
+        <v>3.33256077766418</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G571" t="n">
-        <v>3.35895752906799</v>
+        <v>3.35895776748657</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G574" t="n">
-        <v>3.32596182823181</v>
+        <v>3.32596158981323</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>4.99499988555908</v>
       </c>
       <c r="G575" t="n">
-        <v>3.29626536369324</v>
+        <v>3.2962658405304</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G576" t="n">
-        <v>3.31936264038086</v>
+        <v>3.31936311721802</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>4.99499988555908</v>
       </c>
       <c r="G577" t="n">
-        <v>3.29626536369324</v>
+        <v>3.2962658405304</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>4.92500019073486</v>
       </c>
       <c r="G578" t="n">
-        <v>3.25007200241089</v>
+        <v>3.25007176399231</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G579" t="n">
-        <v>3.24677228927612</v>
+        <v>3.24677205085754</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G580" t="n">
-        <v>3.2335741519928</v>
+        <v>3.23357367515564</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G581" t="n">
-        <v>3.22037577629089</v>
+        <v>3.22037553787231</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G582" t="n">
-        <v>3.24677228927612</v>
+        <v>3.24677205085754</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>4.92500019073486</v>
       </c>
       <c r="G584" t="n">
-        <v>3.25007200241089</v>
+        <v>3.25007176399231</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G586" t="n">
-        <v>3.2335741519928</v>
+        <v>3.23357367515564</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>4.96500015258789</v>
       </c>
       <c r="G587" t="n">
-        <v>3.27646851539612</v>
+        <v>3.27646827697754</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G589" t="n">
-        <v>3.20387816429138</v>
+        <v>3.20387768745422</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G590" t="n">
-        <v>3.27316856384277</v>
+        <v>3.27316880226135</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>4.96500015258789</v>
       </c>
       <c r="G591" t="n">
-        <v>3.27646851539612</v>
+        <v>3.27646827697754</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G595" t="n">
-        <v>3.00920343399048</v>
+        <v>3.00920367240906</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G597" t="n">
-        <v>3.03559994697571</v>
+        <v>3.03560018539429</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>4.7350001335144</v>
       </c>
       <c r="G598" t="n">
-        <v>3.12468838691711</v>
+        <v>3.12468814849854</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G600" t="n">
-        <v>2.98940587043762</v>
+        <v>2.98940658569336</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G601" t="n">
-        <v>3.03559994697571</v>
+        <v>3.03560018539429</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G603" t="n">
-        <v>3.00260472297668</v>
+        <v>3.00260424613953</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G606" t="n">
-        <v>3.03230023384094</v>
+        <v>3.03230047225952</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G608" t="n">
-        <v>3.05539751052856</v>
+        <v>3.05539727210999</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G612" t="n">
-        <v>3.08179402351379</v>
+        <v>3.08179378509521</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>4.75</v>
       </c>
       <c r="G613" t="n">
-        <v>3.13458704948425</v>
+        <v>3.13458681106567</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G614" t="n">
-        <v>3.17418169975281</v>
+        <v>3.17418146133423</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G615" t="n">
-        <v>3.17418169975281</v>
+        <v>3.17418146133423</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G619" t="n">
-        <v>3.15438461303711</v>
+        <v>3.15438485145569</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G620" t="n">
-        <v>3.18078112602234</v>
+        <v>3.18078088760376</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>4.875</v>
       </c>
       <c r="G621" t="n">
-        <v>3.21707582473755</v>
+        <v>3.21707606315613</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>4.81500005722046</v>
       </c>
       <c r="G622" t="n">
-        <v>3.17748117446899</v>
+        <v>3.17748141288757</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G623" t="n">
-        <v>3.16758251190186</v>
+        <v>3.16758275032043</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>4.77500009536743</v>
       </c>
       <c r="G624" t="n">
-        <v>3.15108442306519</v>
+        <v>3.15108489990234</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>4.74499988555908</v>
       </c>
       <c r="G625" t="n">
-        <v>3.13128733634949</v>
+        <v>3.13128709793091</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G627" t="n">
-        <v>3.17418169975281</v>
+        <v>3.17418146133423</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>4.75500011444092</v>
       </c>
       <c r="G629" t="n">
-        <v>3.13788628578186</v>
+        <v>3.1378870010376</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G630" t="n">
-        <v>3.10159087181091</v>
+        <v>3.10159111022949</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G631" t="n">
-        <v>3.10819029808044</v>
+        <v>3.10819053649902</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>4.75</v>
       </c>
       <c r="G632" t="n">
-        <v>3.13458704948425</v>
+        <v>3.13458681106567</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G633" t="n">
-        <v>3.16758251190186</v>
+        <v>3.16758275032043</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>4.80499982833862</v>
       </c>
       <c r="G634" t="n">
-        <v>3.17088222503662</v>
+        <v>3.17088198661804</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G635" t="n">
-        <v>3.20057845115662</v>
+        <v>3.2005786895752</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G638" t="n">
-        <v>3.31936264038086</v>
+        <v>3.31936311721802</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G639" t="n">
-        <v>3.35895752906799</v>
+        <v>3.35895776748657</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G640" t="n">
-        <v>3.33915996551514</v>
+        <v>3.33915972709656</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>5.25</v>
       </c>
       <c r="G641" t="n">
-        <v>3.46454334259033</v>
+        <v>3.46454405784607</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G642" t="n">
-        <v>3.51073789596558</v>
+        <v>3.510737657547</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G643" t="n">
-        <v>3.48434114456177</v>
+        <v>3.48434090614319</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G644" t="n">
-        <v>3.55033206939697</v>
+        <v>3.55033230781555</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G645" t="n">
-        <v>3.5437331199646</v>
+        <v>3.54373288154602</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G646" t="n">
-        <v>3.53053426742554</v>
+        <v>3.53053450584412</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G650" t="n">
-        <v>3.58332800865173</v>
+        <v>3.58332753181458</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G651" t="n">
-        <v>3.58332800865173</v>
+        <v>3.58332753181458</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G652" t="n">
-        <v>3.60972452163696</v>
+        <v>3.60972476005554</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G653" t="n">
-        <v>3.60972452163696</v>
+        <v>3.60972476005554</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G654" t="n">
-        <v>3.60972452163696</v>
+        <v>3.60972476005554</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>5.5</v>
       </c>
       <c r="G656" t="n">
-        <v>3.62952160835266</v>
+        <v>3.62952208518982</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G657" t="n">
-        <v>3.53053426742554</v>
+        <v>3.53053450584412</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G658" t="n">
-        <v>3.48434114456177</v>
+        <v>3.48434090614319</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G659" t="n">
-        <v>3.53053426742554</v>
+        <v>3.53053450584412</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G660" t="n">
-        <v>3.53053426742554</v>
+        <v>3.53053450584412</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G661" t="n">
-        <v>3.52393555641174</v>
+        <v>3.52393579483032</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G665" t="n">
-        <v>3.44474625587463</v>
+        <v>3.44474577903748</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G667" t="n">
-        <v>3.53053426742554</v>
+        <v>3.53053450584412</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G670" t="n">
-        <v>3.57672882080078</v>
+        <v>3.5767285823822</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G671" t="n">
-        <v>3.60972452163696</v>
+        <v>3.60972476005554</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G672" t="n">
-        <v>3.60312533378601</v>
+        <v>3.60312485694885</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G673" t="n">
-        <v>3.5437331199646</v>
+        <v>3.54373288154602</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G674" t="n">
-        <v>3.53053426742554</v>
+        <v>3.53053450584412</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G675" t="n">
-        <v>3.53713417053223</v>
+        <v>3.53713393211365</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G676" t="n">
-        <v>3.55033206939697</v>
+        <v>3.55033230781555</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G679" t="n">
-        <v>3.49753880500793</v>
+        <v>3.49753904342651</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G680" t="n">
-        <v>3.5437331199646</v>
+        <v>3.54373288154602</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G681" t="n">
-        <v>3.53053426742554</v>
+        <v>3.53053450584412</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G682" t="n">
-        <v>3.51073789596558</v>
+        <v>3.510737657547</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G684" t="n">
-        <v>3.50413846969604</v>
+        <v>3.50413870811462</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G685" t="n">
-        <v>3.55033206939697</v>
+        <v>3.55033230781555</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G686" t="n">
-        <v>3.53053426742554</v>
+        <v>3.53053450584412</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G688" t="n">
-        <v>3.49753880500793</v>
+        <v>3.49753904342651</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G689" t="n">
-        <v>3.47774171829224</v>
+        <v>3.47774147987366</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G690" t="n">
-        <v>3.52393555641174</v>
+        <v>3.52393579483032</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G691" t="n">
-        <v>3.5437331199646</v>
+        <v>3.54373288154602</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G692" t="n">
-        <v>3.50413846969604</v>
+        <v>3.50413870811462</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G693" t="n">
-        <v>3.49753880500793</v>
+        <v>3.49753904342651</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G694" t="n">
-        <v>3.53053426742554</v>
+        <v>3.53053450584412</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G695" t="n">
-        <v>3.53713417053223</v>
+        <v>3.53713393211365</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G697" t="n">
-        <v>3.53053426742554</v>
+        <v>3.53053450584412</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G701" t="n">
-        <v>3.53713417053223</v>
+        <v>3.53713393211365</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G702" t="n">
-        <v>3.58992719650269</v>
+        <v>3.58992695808411</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>5.5</v>
       </c>
       <c r="G703" t="n">
-        <v>3.62952160835266</v>
+        <v>3.62952208518982</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G704" t="n">
-        <v>3.70871090888977</v>
+        <v>3.70871138572693</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G705" t="n">
-        <v>3.72850847244263</v>
+        <v>3.72850894927979</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>5.75</v>
       </c>
       <c r="G707" t="n">
-        <v>3.79450011253357</v>
+        <v>3.79449987411499</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>5.75</v>
       </c>
       <c r="G708" t="n">
-        <v>3.79450011253357</v>
+        <v>3.79449987411499</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G711" t="n">
-        <v>3.66251802444458</v>
+        <v>3.66251707077026</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G712" t="n">
-        <v>3.66251802444458</v>
+        <v>3.66251707077026</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G714" t="n">
-        <v>3.70871090888977</v>
+        <v>3.70871138572693</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G715" t="n">
-        <v>3.77470254898071</v>
+        <v>3.77470278739929</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G718" t="n">
-        <v>3.78790044784546</v>
+        <v>3.78790092468262</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G719" t="n">
-        <v>3.78130221366882</v>
+        <v>3.78130173683167</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G720" t="n">
-        <v>3.82749605178833</v>
+        <v>3.82749581336975</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G721" t="n">
-        <v>3.82749605178833</v>
+        <v>3.82749581336975</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G722" t="n">
-        <v>3.87368941307068</v>
+        <v>3.87368965148926</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G723" t="n">
-        <v>3.93308162689209</v>
+        <v>3.93308186531067</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G724" t="n">
-        <v>3.93308162689209</v>
+        <v>3.93308186531067</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G725" t="n">
-        <v>4.03866767883301</v>
+        <v>4.03866815567017</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G726" t="n">
-        <v>4.04526710510254</v>
+        <v>4.04526662826538</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G727" t="n">
-        <v>3.99247407913208</v>
+        <v>3.9924738407135</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G729" t="n">
-        <v>3.72190952301025</v>
+        <v>3.72190928459167</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G730" t="n">
-        <v>3.84729290008545</v>
+        <v>3.84729313850403</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G731" t="n">
-        <v>3.75490522384644</v>
+        <v>3.75490546226501</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G732" t="n">
-        <v>3.64931893348694</v>
+        <v>3.6493194103241</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G733" t="n">
-        <v>3.48434114456177</v>
+        <v>3.48434090614319</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G735" t="n">
-        <v>3.51073789596558</v>
+        <v>3.510737657547</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G736" t="n">
-        <v>3.47774171829224</v>
+        <v>3.47774147987366</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>4.58500003814697</v>
       </c>
       <c r="G739" t="n">
-        <v>3.02570128440857</v>
+        <v>3.02570080757141</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G742" t="n">
-        <v>2.90361738204956</v>
+        <v>2.90361762046814</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G743" t="n">
-        <v>2.76503539085388</v>
+        <v>2.76503562927246</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>4.14499998092651</v>
       </c>
       <c r="G744" t="n">
-        <v>2.73533964157104</v>
+        <v>2.73533940315247</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>4.07499980926514</v>
       </c>
       <c r="G745" t="n">
-        <v>2.68914532661438</v>
+        <v>2.68914556503296</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>4.56500005722046</v>
       </c>
       <c r="G748" t="n">
-        <v>3.01250314712524</v>
+        <v>3.01250290870667</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>4.75</v>
       </c>
       <c r="G749" t="n">
-        <v>3.13458704948425</v>
+        <v>3.13458681106567</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>4.69500017166138</v>
       </c>
       <c r="G751" t="n">
-        <v>3.09829163551331</v>
+        <v>3.09829187393188</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G752" t="n">
-        <v>3.16758251190186</v>
+        <v>3.16758275032043</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>4.43499994277954</v>
       </c>
       <c r="G753" t="n">
-        <v>2.92671418190002</v>
+        <v>2.92671465873718</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G754" t="n">
-        <v>3.12138891220093</v>
+        <v>3.12138867378235</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G755" t="n">
-        <v>3.11808943748474</v>
+        <v>3.11808896064758</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G756" t="n">
-        <v>3.04879856109619</v>
+        <v>3.04879832267761</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G758" t="n">
-        <v>3.10159087181091</v>
+        <v>3.10159111022949</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>5</v>
       </c>
       <c r="G759" t="n">
-        <v>3.29956483840942</v>
+        <v>3.29956555366516</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G760" t="n">
-        <v>3.33915996551514</v>
+        <v>3.33915972709656</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G762" t="n">
-        <v>3.25997042655945</v>
+        <v>3.25997090339661</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>4.86499977111816</v>
       </c>
       <c r="G763" t="n">
-        <v>3.21047687530518</v>
+        <v>3.2104766368866</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G764" t="n">
-        <v>3.10819029808044</v>
+        <v>3.10819053649902</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G766" t="n">
-        <v>3.08179402351379</v>
+        <v>3.08179378509521</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G767" t="n">
-        <v>3.11808943748474</v>
+        <v>3.11808896064758</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G768" t="n">
-        <v>3.11478996276855</v>
+        <v>3.1147894859314</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G769" t="n">
-        <v>3.11808943748474</v>
+        <v>3.11808896064758</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G770" t="n">
-        <v>3.10159087181091</v>
+        <v>3.10159111022949</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G772" t="n">
-        <v>3.24017286300659</v>
+        <v>3.24017333984375</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G773" t="n">
-        <v>3.24017286300659</v>
+        <v>3.24017333984375</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>4.71500015258789</v>
       </c>
       <c r="G774" t="n">
-        <v>3.11149001121521</v>
+        <v>3.11149048805237</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G775" t="n">
-        <v>3.00260472297668</v>
+        <v>3.00260424613953</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G778" t="n">
-        <v>2.98280668258667</v>
+        <v>2.98280692100525</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>4.82499980926514</v>
       </c>
       <c r="G779" t="n">
-        <v>3.18408060073853</v>
+        <v>3.18408012390137</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G780" t="n">
-        <v>3.17418169975281</v>
+        <v>3.17418146133423</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>4.75</v>
       </c>
       <c r="G781" t="n">
-        <v>3.13458704948425</v>
+        <v>3.13458681106567</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>4.84499979019165</v>
       </c>
       <c r="G783" t="n">
-        <v>3.19727826118469</v>
+        <v>3.19727873802185</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G785" t="n">
-        <v>3.37875461578369</v>
+        <v>3.37875485420227</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G787" t="n">
-        <v>3.2665696144104</v>
+        <v>3.26656937599182</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>4.92500019073486</v>
       </c>
       <c r="G788" t="n">
-        <v>3.25007200241089</v>
+        <v>3.25007176399231</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G789" t="n">
-        <v>3.30616426467896</v>
+        <v>3.30616450309753</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G790" t="n">
-        <v>3.33256101608276</v>
+        <v>3.33256077766418</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G791" t="n">
-        <v>3.41175031661987</v>
+        <v>3.41175055503845</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G792" t="n">
-        <v>3.44474625587463</v>
+        <v>3.44474577903748</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G793" t="n">
-        <v>3.41175031661987</v>
+        <v>3.41175055503845</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G794" t="n">
-        <v>3.52393555641174</v>
+        <v>3.52393579483032</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G795" t="n">
-        <v>3.52393555641174</v>
+        <v>3.52393579483032</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G796" t="n">
-        <v>3.35235857963562</v>
+        <v>3.35235810279846</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G798" t="n">
-        <v>3.37875461578369</v>
+        <v>3.37875485420227</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G799" t="n">
-        <v>3.40515112876892</v>
+        <v>3.40515160560608</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G800" t="n">
-        <v>3.37875461578369</v>
+        <v>3.37875485420227</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>5</v>
       </c>
       <c r="G801" t="n">
-        <v>3.29956483840942</v>
+        <v>3.29956555366516</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>5</v>
       </c>
       <c r="G802" t="n">
-        <v>3.29956483840942</v>
+        <v>3.29956555366516</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G804" t="n">
-        <v>3.11808943748474</v>
+        <v>3.11808896064758</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G805" t="n">
-        <v>3.10159087181091</v>
+        <v>3.10159111022949</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G806" t="n">
-        <v>3.16758251190186</v>
+        <v>3.16758275032043</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G807" t="n">
-        <v>3.18078112602234</v>
+        <v>3.18078088760376</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>4.7649998664856</v>
       </c>
       <c r="G810" t="n">
-        <v>3.14448571205139</v>
+        <v>3.14448547363281</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G811" t="n">
-        <v>3.21377635002136</v>
+        <v>3.21377682685852</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G812" t="n">
-        <v>3.14118599891663</v>
+        <v>3.14118623733521</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>4.7649998664856</v>
       </c>
       <c r="G813" t="n">
-        <v>3.14448571205139</v>
+        <v>3.14448547363281</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G814" t="n">
-        <v>3.2665696144104</v>
+        <v>3.26656937599182</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>4.99499988555908</v>
       </c>
       <c r="G815" t="n">
-        <v>3.29626536369324</v>
+        <v>3.2962658405304</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G816" t="n">
-        <v>3.33915996551514</v>
+        <v>3.33915972709656</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G817" t="n">
-        <v>3.33915996551514</v>
+        <v>3.33915972709656</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G818" t="n">
-        <v>3.41175031661987</v>
+        <v>3.41175055503845</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G819" t="n">
-        <v>3.42494821548462</v>
+        <v>3.4249484539032</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G820" t="n">
-        <v>3.39855194091797</v>
+        <v>3.39855217933655</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G822" t="n">
-        <v>3.3853542804718</v>
+        <v>3.38535380363464</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G823" t="n">
-        <v>3.39195322990417</v>
+        <v>3.39195275306702</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G824" t="n">
-        <v>3.39855194091797</v>
+        <v>3.39855217933655</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G825" t="n">
-        <v>3.31936264038086</v>
+        <v>3.31936311721802</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>4.92500019073486</v>
       </c>
       <c r="G826" t="n">
-        <v>3.25007200241089</v>
+        <v>3.25007176399231</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G827" t="n">
-        <v>3.27976751327515</v>
+        <v>3.27976775169373</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G828" t="n">
-        <v>3.32596182823181</v>
+        <v>3.32596158981323</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G829" t="n">
-        <v>3.30616426467896</v>
+        <v>3.30616450309753</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>4.99499988555908</v>
       </c>
       <c r="G830" t="n">
-        <v>3.29626536369324</v>
+        <v>3.2962658405304</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>5</v>
       </c>
       <c r="G831" t="n">
-        <v>3.29956483840942</v>
+        <v>3.29956555366516</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G832" t="n">
-        <v>3.33915996551514</v>
+        <v>3.33915972709656</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>5</v>
       </c>
       <c r="G833" t="n">
-        <v>3.29956483840942</v>
+        <v>3.29956555366516</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>4.91499996185303</v>
       </c>
       <c r="G834" t="n">
-        <v>3.24347257614136</v>
+        <v>3.24347233772278</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G838" t="n">
-        <v>3.18078112602234</v>
+        <v>3.18078088760376</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>4.81500005722046</v>
       </c>
       <c r="G839" t="n">
-        <v>3.17748117446899</v>
+        <v>3.17748141288757</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>4.80499982833862</v>
       </c>
       <c r="G840" t="n">
-        <v>3.17088222503662</v>
+        <v>3.17088198661804</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>4.86499977111816</v>
       </c>
       <c r="G841" t="n">
-        <v>3.21047687530518</v>
+        <v>3.2104766368866</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G842" t="n">
-        <v>3.2335741519928</v>
+        <v>3.23357367515564</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G843" t="n">
-        <v>3.16758251190186</v>
+        <v>3.16758275032043</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G844" t="n">
-        <v>3.1609833240509</v>
+        <v>3.16098356246948</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G845" t="n">
-        <v>3.16758251190186</v>
+        <v>3.16758275032043</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G846" t="n">
-        <v>3.14778542518616</v>
+        <v>3.147784948349</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>4.75500011444092</v>
       </c>
       <c r="G847" t="n">
-        <v>3.13788628578186</v>
+        <v>3.1378870010376</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G848" t="n">
-        <v>3.14778542518616</v>
+        <v>3.147784948349</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>4.75</v>
       </c>
       <c r="G849" t="n">
-        <v>3.13458704948425</v>
+        <v>3.13458681106567</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>4.68499994277954</v>
       </c>
       <c r="G850" t="n">
-        <v>3.09169268608093</v>
+        <v>3.09169292449951</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>4.61499977111816</v>
       </c>
       <c r="G851" t="n">
-        <v>3.04549813270569</v>
+        <v>3.04549860954285</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>4.64499998092651</v>
       </c>
       <c r="G854" t="n">
-        <v>3.0652961730957</v>
+        <v>3.06529593467712</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G856" t="n">
-        <v>3.05539751052856</v>
+        <v>3.05539727210999</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G857" t="n">
-        <v>3.05539751052856</v>
+        <v>3.05539727210999</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G859" t="n">
-        <v>3.1279878616333</v>
+        <v>3.12798738479614</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G861" t="n">
-        <v>3.03230023384094</v>
+        <v>3.03230047225952</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G862" t="n">
-        <v>3.07519459724426</v>
+        <v>3.07519483566284</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>4.58500003814697</v>
       </c>
       <c r="G865" t="n">
-        <v>3.02570128440857</v>
+        <v>3.02570080757141</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>4.5149998664856</v>
       </c>
       <c r="G866" t="n">
-        <v>2.9795069694519</v>
+        <v>2.97950744628906</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G869" t="n">
-        <v>3.05539751052856</v>
+        <v>3.05539727210999</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G871" t="n">
-        <v>3.05539751052856</v>
+        <v>3.05539727210999</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>4.7649998664856</v>
       </c>
       <c r="G873" t="n">
-        <v>3.14448571205139</v>
+        <v>3.14448547363281</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G874" t="n">
-        <v>3.18078112602234</v>
+        <v>3.18078088760376</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G875" t="n">
-        <v>3.14118599891663</v>
+        <v>3.14118623733521</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>4.75500011444092</v>
       </c>
       <c r="G876" t="n">
-        <v>3.13788628578186</v>
+        <v>3.1378870010376</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>4.7649998664856</v>
       </c>
       <c r="G877" t="n">
-        <v>3.14448571205139</v>
+        <v>3.14448547363281</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>4.7649998664856</v>
       </c>
       <c r="G878" t="n">
-        <v>3.14448571205139</v>
+        <v>3.14448547363281</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G879" t="n">
-        <v>3.1609833240509</v>
+        <v>3.16098356246948</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G880" t="n">
-        <v>3.15438461303711</v>
+        <v>3.15438485145569</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>4.74499988555908</v>
       </c>
       <c r="G881" t="n">
-        <v>3.13128733634949</v>
+        <v>3.13128709793091</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>4.80499982833862</v>
       </c>
       <c r="G882" t="n">
-        <v>3.17088222503662</v>
+        <v>3.17088198661804</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G883" t="n">
-        <v>3.1609833240509</v>
+        <v>3.16098356246948</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G886" t="n">
-        <v>3.33256101608276</v>
+        <v>3.33256077766418</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>4.93499994277954</v>
       </c>
       <c r="G887" t="n">
-        <v>3.25667095184326</v>
+        <v>3.25667071342468</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>4.84499979019165</v>
       </c>
       <c r="G888" t="n">
-        <v>3.19727826118469</v>
+        <v>3.19727873802185</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G889" t="n">
-        <v>3.17418169975281</v>
+        <v>3.17418146133423</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>4.81500005722046</v>
       </c>
       <c r="G890" t="n">
-        <v>3.17748117446899</v>
+        <v>3.17748141288757</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G892" t="n">
-        <v>3.08179402351379</v>
+        <v>3.08179378509521</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G895" t="n">
-        <v>2.91681575775146</v>
+        <v>2.91681551933289</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G896" t="n">
-        <v>2.90361738204956</v>
+        <v>2.90361762046814</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G899" t="n">
-        <v>2.81122994422913</v>
+        <v>2.81122970581055</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>4.16499996185303</v>
       </c>
       <c r="G900" t="n">
-        <v>2.74853801727295</v>
+        <v>2.74853777885437</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G901" t="n">
-        <v>2.75843644142151</v>
+        <v>2.75843620300293</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>3.97499990463257</v>
       </c>
       <c r="G902" t="n">
-        <v>2.62315440177917</v>
+        <v>2.6231541633606</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G903" t="n">
-        <v>2.61985492706299</v>
+        <v>2.61985468864441</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>3.95499992370605</v>
       </c>
       <c r="G904" t="n">
-        <v>2.60995578765869</v>
+        <v>2.60995626449585</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G906" t="n">
-        <v>2.57366108894348</v>
+        <v>2.5736608505249</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G908" t="n">
-        <v>2.75183701515198</v>
+        <v>2.75183749198914</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>4.31500005722046</v>
       </c>
       <c r="G910" t="n">
-        <v>2.84752511978149</v>
+        <v>2.84752464294434</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G911" t="n">
-        <v>2.96300959587097</v>
+        <v>2.96300911903381</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G912" t="n">
-        <v>3.00260472297668</v>
+        <v>3.00260424613953</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>4.36499977111816</v>
       </c>
       <c r="G914" t="n">
-        <v>2.88052010536194</v>
+        <v>2.88052034378052</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>4.5</v>
       </c>
       <c r="G915" t="n">
-        <v>2.96960830688477</v>
+        <v>2.96960854530334</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G917" t="n">
-        <v>3.05539751052856</v>
+        <v>3.05539727210999</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G918" t="n">
-        <v>3.00260472297668</v>
+        <v>3.00260424613953</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G919" t="n">
-        <v>3.03230023384094</v>
+        <v>3.03230047225952</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>4.64499998092651</v>
       </c>
       <c r="G920" t="n">
-        <v>3.0652961730957</v>
+        <v>3.06529593467712</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>4.61499977111816</v>
       </c>
       <c r="G921" t="n">
-        <v>3.04549813270569</v>
+        <v>3.04549860954285</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G922" t="n">
-        <v>3.14778542518616</v>
+        <v>3.147784948349</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>4.7649998664856</v>
       </c>
       <c r="G923" t="n">
-        <v>3.14448571205139</v>
+        <v>3.14448547363281</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G924" t="n">
-        <v>3.12138891220093</v>
+        <v>3.12138867378235</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G925" t="n">
-        <v>3.03559994697571</v>
+        <v>3.03560018539429</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G928" t="n">
-        <v>2.97290849685669</v>
+        <v>2.97290825843811</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G931" t="n">
-        <v>3.00920343399048</v>
+        <v>3.00920367240906</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G933" t="n">
-        <v>2.94981122016907</v>
+        <v>2.94981145858765</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>4.64499998092651</v>
       </c>
       <c r="G935" t="n">
-        <v>3.0652961730957</v>
+        <v>3.06529593467712</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>4.5</v>
       </c>
       <c r="G940" t="n">
-        <v>2.96960830688477</v>
+        <v>2.96960854530334</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G941" t="n">
-        <v>2.98940587043762</v>
+        <v>2.98940658569336</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G942" t="n">
-        <v>3.03559994697571</v>
+        <v>3.03560018539429</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G943" t="n">
-        <v>3.10819029808044</v>
+        <v>3.10819053649902</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G944" t="n">
-        <v>3.20057845115662</v>
+        <v>3.2005786895752</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G945" t="n">
-        <v>3.25997042655945</v>
+        <v>3.25997090339661</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G946" t="n">
-        <v>3.1609833240509</v>
+        <v>3.16098356246948</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>4.68499994277954</v>
       </c>
       <c r="G947" t="n">
-        <v>3.09169268608093</v>
+        <v>3.09169292449951</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G948" t="n">
-        <v>3.14118599891663</v>
+        <v>3.14118623733521</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>4.7350001335144</v>
       </c>
       <c r="G949" t="n">
-        <v>3.12468838691711</v>
+        <v>3.12468814849854</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>4.69500017166138</v>
       </c>
       <c r="G950" t="n">
-        <v>3.09829163551331</v>
+        <v>3.09829187393188</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G951" t="n">
-        <v>3.20387816429138</v>
+        <v>3.20387768745422</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>4.70499992370605</v>
       </c>
       <c r="G953" t="n">
-        <v>3.10489082336426</v>
+        <v>3.10489058494568</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G954" t="n">
-        <v>3.11808943748474</v>
+        <v>3.11808896064758</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G955" t="n">
-        <v>3.08179402351379</v>
+        <v>3.08179378509521</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>4.70499992370605</v>
       </c>
       <c r="G958" t="n">
-        <v>3.10489082336426</v>
+        <v>3.10489058494568</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G960" t="n">
-        <v>3.00260472297668</v>
+        <v>3.00260424613953</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G961" t="n">
-        <v>2.94981122016907</v>
+        <v>2.94981145858765</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G966" t="n">
-        <v>3.03559994697571</v>
+        <v>3.03560018539429</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G967" t="n">
-        <v>3.03559994697571</v>
+        <v>3.03560018539429</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G968" t="n">
-        <v>3.11478996276855</v>
+        <v>3.1147894859314</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G969" t="n">
-        <v>3.20057845115662</v>
+        <v>3.2005786895752</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G971" t="n">
-        <v>3.2335741519928</v>
+        <v>3.23357367515564</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G973" t="n">
-        <v>3.43154764175415</v>
+        <v>3.43154740333557</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G974" t="n">
-        <v>3.69551348686218</v>
+        <v>3.69551301002502</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G977" t="n">
-        <v>3.71531057357788</v>
+        <v>3.7153103351593</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G978" t="n">
-        <v>3.60312533378601</v>
+        <v>3.60312485694885</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G979" t="n">
-        <v>3.70211219787598</v>
+        <v>3.70211243629456</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G980" t="n">
-        <v>3.66251802444458</v>
+        <v>3.66251707077026</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G981" t="n">
-        <v>3.64271974563599</v>
+        <v>3.64271998405457</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G983" t="n">
-        <v>3.62292194366455</v>
+        <v>3.62292218208313</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G984" t="n">
-        <v>3.62292194366455</v>
+        <v>3.62292218208313</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G985" t="n">
-        <v>3.58992719650269</v>
+        <v>3.58992695808411</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G986" t="n">
-        <v>3.68231415748596</v>
+        <v>3.6823148727417</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G987" t="n">
-        <v>3.66911673545837</v>
+        <v>3.66911649703979</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G988" t="n">
-        <v>3.66911673545837</v>
+        <v>3.66911649703979</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G989" t="n">
-        <v>3.64271974563599</v>
+        <v>3.64271998405457</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G990" t="n">
-        <v>3.66911673545837</v>
+        <v>3.66911649703979</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G991" t="n">
-        <v>3.66251802444458</v>
+        <v>3.66251707077026</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G992" t="n">
-        <v>3.82089638710022</v>
+        <v>3.82089614868164</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G994" t="n">
-        <v>4.05186605453491</v>
+        <v>4.05186557769775</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G996" t="n">
-        <v>4.29603433609009</v>
+        <v>4.29603385925293</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G998" t="n">
-        <v>4.21024560928345</v>
+        <v>4.21024513244629</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G1002" t="n">
-        <v>4.29603433609009</v>
+        <v>4.29603385925293</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G1004" t="n">
-        <v>4.27623653411865</v>
+        <v>4.27623605728149</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>6.5</v>
       </c>
       <c r="G1005" t="n">
-        <v>4.28943490982056</v>
+        <v>4.2894344329834</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G1008" t="n">
-        <v>4.14882135391235</v>
+        <v>4.14882183074951</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>6.28499984741211</v>
       </c>
       <c r="G1009" t="n">
-        <v>4.15874719619751</v>
+        <v>4.15874671936035</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G1011" t="n">
-        <v>4.40026521682739</v>
+        <v>4.40026569366455</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G1014" t="n">
-        <v>4.3605637550354</v>
+        <v>4.36056423187256</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G1017" t="n">
-        <v>4.52598714828491</v>
+        <v>4.52598762512207</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>6.83500003814697</v>
       </c>
       <c r="G1019" t="n">
-        <v>4.52267932891846</v>
+        <v>4.5226788520813</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G1022" t="n">
-        <v>4.6847939491272</v>
+        <v>4.68479347229004</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>7.17500019073486</v>
       </c>
       <c r="G1023" t="n">
-        <v>4.74765491485596</v>
+        <v>4.7476544380188</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G1028" t="n">
-        <v>4.92962074279785</v>
+        <v>4.92962026596069</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G1029" t="n">
-        <v>4.92962074279785</v>
+        <v>4.92962026596069</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1033" t="n">
-        <v>5.16121387481689</v>
+        <v>5.16121435165405</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>7.66499996185303</v>
       </c>
       <c r="G1034" t="n">
-        <v>5.07188510894775</v>
+        <v>5.07188415527344</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>7.61499977111816</v>
       </c>
       <c r="G1037" t="n">
-        <v>5.03880023956299</v>
+        <v>5.03879976272583</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G1039" t="n">
-        <v>5.05534267425537</v>
+        <v>5.05534219741821</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>7.66499996185303</v>
       </c>
       <c r="G1040" t="n">
-        <v>5.07188510894775</v>
+        <v>5.07188415527344</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G1042" t="n">
-        <v>5.10827779769897</v>
+        <v>5.10827827453613</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1043" t="n">
-        <v>5.06857681274414</v>
+        <v>5.06857633590698</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>7.71500015258789</v>
       </c>
       <c r="G1044" t="n">
-        <v>5.1049690246582</v>
+        <v>5.10496950149536</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G1046" t="n">
-        <v>5.05534267425537</v>
+        <v>5.05534219741821</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>7.93499994277954</v>
       </c>
       <c r="G1052" t="n">
-        <v>5.25054264068604</v>
+        <v>5.25054216384888</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1053" t="n">
-        <v>5.16121387481689</v>
+        <v>5.16121435165405</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G1054" t="n">
-        <v>5.17444705963135</v>
+        <v>5.17444801330566</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G1055" t="n">
-        <v>5.17444705963135</v>
+        <v>5.17444801330566</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>8.09000015258789</v>
       </c>
       <c r="G1056" t="n">
-        <v>5.35310506820679</v>
+        <v>5.35310459136963</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>8.13000011444092</v>
       </c>
       <c r="G1057" t="n">
-        <v>5.37957286834717</v>
+        <v>5.37957239151001</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1058" t="n">
-        <v>5.4655933380127</v>
+        <v>5.46559286117554</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G1059" t="n">
-        <v>5.30678606033325</v>
+        <v>5.30678653717041</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G1060" t="n">
-        <v>5.38618946075439</v>
+        <v>5.38618993759155</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G1061" t="n">
-        <v>5.51852798461914</v>
+        <v>5.5185284614563</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G1062" t="n">
-        <v>5.60454845428467</v>
+        <v>5.60454893112183</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>8.46500015258789</v>
       </c>
       <c r="G1064" t="n">
-        <v>5.60124015808105</v>
+        <v>5.6012396812439</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G1069" t="n">
-        <v>5.54499578475952</v>
+        <v>5.54499626159668</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G1075" t="n">
-        <v>5.57808113098145</v>
+        <v>5.5780816078186</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1077" t="n">
-        <v>5.50529479980469</v>
+        <v>5.50529336929321</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G1078" t="n">
-        <v>5.65086698532104</v>
+        <v>5.65086650848389</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1079" t="n">
-        <v>5.55822992324829</v>
+        <v>5.55822896957397</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G1080" t="n">
-        <v>5.57808113098145</v>
+        <v>5.5780816078186</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1081" t="n">
-        <v>5.65748453140259</v>
+        <v>5.65748357772827</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>7.95499992370605</v>
       </c>
       <c r="G1084" t="n">
-        <v>5.26377630233765</v>
+        <v>5.26377582550049</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1090" t="n">
-        <v>5.82290744781494</v>
+        <v>5.8229079246521</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>8.875</v>
       </c>
       <c r="G1091" t="n">
-        <v>5.87253427505493</v>
+        <v>5.87253379821777</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1092" t="n">
-        <v>5.88907670974731</v>
+        <v>5.88907718658447</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>8.8100004196167</v>
       </c>
       <c r="G1093" t="n">
-        <v>5.82952451705933</v>
+        <v>5.82952499389648</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G1096" t="n">
-        <v>5.83614158630371</v>
+        <v>5.83614063262939</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>7.78499984741211</v>
       </c>
       <c r="G1101" t="n">
-        <v>5.15128803253174</v>
+        <v>5.15128755569458</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>7.7649998664856</v>
       </c>
       <c r="G1103" t="n">
-        <v>5.13805437088013</v>
+        <v>5.13805389404297</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G1106" t="n">
-        <v>5.05534267425537</v>
+        <v>5.05534219741821</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>7.71500015258789</v>
       </c>
       <c r="G1107" t="n">
-        <v>5.1049690246582</v>
+        <v>5.10496950149536</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>7.96500015258789</v>
       </c>
       <c r="G1110" t="n">
-        <v>5.27039289474487</v>
+        <v>5.27039337158203</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>7.85500001907349</v>
       </c>
       <c r="G1113" t="n">
-        <v>5.19760704040527</v>
+        <v>5.19760656356812</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G1115" t="n">
-        <v>5.12151193618774</v>
+        <v>5.12151145935059</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>7.7649998664856</v>
       </c>
       <c r="G1116" t="n">
-        <v>5.13805437088013</v>
+        <v>5.13805389404297</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G1118" t="n">
-        <v>5.18768119812012</v>
+        <v>5.18768167495728</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>8.01500034332275</v>
       </c>
       <c r="G1119" t="n">
-        <v>5.30347776412964</v>
+        <v>5.30347728729248</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>7.91499996185303</v>
       </c>
       <c r="G1120" t="n">
-        <v>5.23730802536011</v>
+        <v>5.23730850219727</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>8.09500026702881</v>
       </c>
       <c r="G1125" t="n">
-        <v>5.35641288757324</v>
+        <v>5.3564133644104</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G1127" t="n">
-        <v>5.34648752212524</v>
+        <v>5.3464879989624</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G1128" t="n">
-        <v>5.34648752212524</v>
+        <v>5.3464879989624</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>7.95499992370605</v>
       </c>
       <c r="G1129" t="n">
-        <v>5.26377630233765</v>
+        <v>5.26377582550049</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>8.15499973297119</v>
       </c>
       <c r="G1131" t="n">
-        <v>5.39611482620239</v>
+        <v>5.39611434936523</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1134" t="n">
-        <v>5.49206018447876</v>
+        <v>5.49206066131592</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>8.19499969482422</v>
       </c>
       <c r="G1136" t="n">
-        <v>5.42258214950562</v>
+        <v>5.42258262634277</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>8.39500045776367</v>
       </c>
       <c r="G1137" t="n">
-        <v>5.55492210388184</v>
+        <v>5.55492162704468</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>8.57499980926514</v>
       </c>
       <c r="G1138" t="n">
-        <v>5.67402601242065</v>
+        <v>5.67402648925781</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1139" t="n">
-        <v>5.45235919952393</v>
+        <v>5.45235824584961</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G1140" t="n">
-        <v>5.44574213027954</v>
+        <v>5.44574117660522</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G1142" t="n">
-        <v>5.38618946075439</v>
+        <v>5.38618993759155</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>8.17500019073486</v>
       </c>
       <c r="G1143" t="n">
-        <v>5.40934896469116</v>
+        <v>5.409348487854</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G1152" t="n">
-        <v>5.78798198699951</v>
+        <v>5.78798246383667</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G1153" t="n">
-        <v>5.81027221679688</v>
+        <v>5.81027317047119</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>7.86999988555908</v>
       </c>
       <c r="G1154" t="n">
-        <v>5.84742259979248</v>
+        <v>5.84742212295532</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>7.96500015258789</v>
       </c>
       <c r="G1155" t="n">
-        <v>5.91800832748413</v>
+        <v>5.91800785064697</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G1157" t="n">
-        <v>5.74340200424194</v>
+        <v>5.74340295791626</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>7.66499996185303</v>
       </c>
       <c r="G1160" t="n">
-        <v>5.69510746002197</v>
+        <v>5.69510698318481</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>7.42500019073486</v>
       </c>
       <c r="G1161" t="n">
-        <v>5.51678657531738</v>
+        <v>5.51678705215454</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1162" t="n">
-        <v>5.49821186065674</v>
+        <v>5.4982123374939</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G1167" t="n">
-        <v>5.49078178405762</v>
+        <v>5.49078130722046</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>7.42500019073486</v>
       </c>
       <c r="G1168" t="n">
-        <v>5.51678657531738</v>
+        <v>5.51678705215454</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>7.40999984741211</v>
       </c>
       <c r="G1169" t="n">
-        <v>5.50564098358154</v>
+        <v>5.5056414604187</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G1170" t="n">
-        <v>5.41648149490356</v>
+        <v>5.41648101806641</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>7.03499984741211</v>
       </c>
       <c r="G1172" t="n">
-        <v>5.22701644897461</v>
+        <v>5.22701597213745</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G1173" t="n">
-        <v>5.16386079788208</v>
+        <v>5.16386127471924</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>6.82499980926514</v>
       </c>
       <c r="G1176" t="n">
-        <v>5.07098531723022</v>
+        <v>5.07098579406738</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G1178" t="n">
-        <v>4.926100730896</v>
+        <v>4.92610120773315</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1179" t="n">
-        <v>4.7997899055481</v>
+        <v>4.79979038238525</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1181" t="n">
-        <v>5.05241107940674</v>
+        <v>5.05241060256958</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>6.70499992370605</v>
       </c>
       <c r="G1187" t="n">
-        <v>4.98182582855225</v>
+        <v>4.98182535171509</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>6.61499977111816</v>
       </c>
       <c r="G1188" t="n">
-        <v>4.91495561599731</v>
+        <v>4.91495513916016</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>6.61499977111816</v>
       </c>
       <c r="G1189" t="n">
-        <v>4.91495561599731</v>
+        <v>4.91495513916016</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>6.66499996185303</v>
       </c>
       <c r="G1190" t="n">
-        <v>4.95210552215576</v>
+        <v>4.95210599899292</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G1192" t="n">
-        <v>5.08956050872803</v>
+        <v>5.08956098556519</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G1193" t="n">
-        <v>5.10442113876343</v>
+        <v>5.10442066192627</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>6.7350001335144</v>
       </c>
       <c r="G1194" t="n">
-        <v>5.00411558151245</v>
+        <v>5.00411605834961</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>6.93499994277954</v>
       </c>
       <c r="G1196" t="n">
-        <v>5.1527156829834</v>
+        <v>5.15271615982056</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>6.93499994277954</v>
       </c>
       <c r="G1197" t="n">
-        <v>5.1527156829834</v>
+        <v>5.15271615982056</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>7.11499977111816</v>
       </c>
       <c r="G1199" t="n">
-        <v>5.28645658493042</v>
+        <v>5.2864556312561</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1200" t="n">
-        <v>5.27531099319458</v>
+        <v>5.27531147003174</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1202" t="n">
-        <v>5.34961175918579</v>
+        <v>5.34961128234863</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>7.21500015258789</v>
       </c>
       <c r="G1206" t="n">
-        <v>5.36075639724731</v>
+        <v>5.36075687408447</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>7.21500015258789</v>
       </c>
       <c r="G1208" t="n">
-        <v>5.36075639724731</v>
+        <v>5.36075687408447</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1209" t="n">
-        <v>5.27531099319458</v>
+        <v>5.27531147003174</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G1211" t="n">
-        <v>5.24559164047241</v>
+        <v>5.2455906867981</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>7.10500001907349</v>
       </c>
       <c r="G1212" t="n">
-        <v>5.27902698516846</v>
+        <v>5.27902603149414</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>6.94500017166138</v>
       </c>
       <c r="G1213" t="n">
-        <v>5.16014575958252</v>
+        <v>5.16014623641968</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G1218" t="n">
-        <v>4.926100730896</v>
+        <v>4.92610120773315</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>6.82499980926514</v>
       </c>
       <c r="G1220" t="n">
-        <v>5.07098531723022</v>
+        <v>5.07098579406738</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G1222" t="n">
-        <v>5.0375509262085</v>
+        <v>5.03755140304565</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G1226" t="n">
-        <v>5.0375509262085</v>
+        <v>5.03755140304565</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1230" t="n">
-        <v>5.6096625328064</v>
+        <v>5.60966157913208</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G1234" t="n">
-        <v>5.54279232025146</v>
+        <v>5.54279184341431</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G1239" t="n">
-        <v>5.25302219390869</v>
+        <v>5.25302171707153</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>6.53000020980835</v>
       </c>
       <c r="G1240" t="n">
-        <v>4.85180044174194</v>
+        <v>4.8518009185791</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G1242" t="n">
-        <v>4.79235982894897</v>
+        <v>4.79236030578613</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G1243" t="n">
-        <v>4.72548961639404</v>
+        <v>4.7254900932312</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>6.4850001335144</v>
       </c>
       <c r="G1244" t="n">
-        <v>4.81836557388306</v>
+        <v>4.81836605072021</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G1246" t="n">
-        <v>4.36884927749634</v>
+        <v>4.3688497543335</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1247" t="n">
-        <v>4.30940961837769</v>
+        <v>4.30940914154053</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>6.25</v>
       </c>
       <c r="G1249" t="n">
-        <v>4.64376020431519</v>
+        <v>4.64375972747803</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G1251" t="n">
-        <v>4.53231000900269</v>
+        <v>4.53230953216553</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>6.4850001335144</v>
       </c>
       <c r="G1255" t="n">
-        <v>4.81836557388306</v>
+        <v>4.81836605072021</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G1256" t="n">
-        <v>4.85923004150391</v>
+        <v>4.85923051834106</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1257" t="n">
-        <v>4.7997899055481</v>
+        <v>4.79979038238525</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>6.67000007629395</v>
       </c>
       <c r="G1260" t="n">
-        <v>4.95582103729248</v>
+        <v>4.95582056045532</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>6.82499980926514</v>
       </c>
       <c r="G1263" t="n">
-        <v>5.07098531723022</v>
+        <v>5.07098579406738</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>6.82499980926514</v>
       </c>
       <c r="G1264" t="n">
-        <v>5.07098531723022</v>
+        <v>5.07098579406738</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>6.7350001335144</v>
       </c>
       <c r="G1265" t="n">
-        <v>5.00411558151245</v>
+        <v>5.00411605834961</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G1266" t="n">
-        <v>5.08213090896606</v>
+        <v>5.08213138580322</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>6.96500015258789</v>
       </c>
       <c r="G1267" t="n">
-        <v>5.17500591278076</v>
+        <v>5.17500638961792</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>7.00500011444092</v>
       </c>
       <c r="G1268" t="n">
-        <v>5.20472574234009</v>
+        <v>5.20472621917725</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G1271" t="n">
-        <v>5.16386079788208</v>
+        <v>5.16386127471924</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G1272" t="n">
-        <v>5.15643072128296</v>
+        <v>5.15643167495728</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>6.86499977111816</v>
       </c>
       <c r="G1273" t="n">
-        <v>5.10070562362671</v>
+        <v>5.10070610046387</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G1274" t="n">
-        <v>5.11185121536255</v>
+        <v>5.11185073852539</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G1277" t="n">
-        <v>5.03365564346313</v>
+        <v>5.03365612030029</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G1278" t="n">
-        <v>5.00894069671631</v>
+        <v>5.00894021987915</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G1281" t="n">
-        <v>4.79474306106567</v>
+        <v>4.79474258422852</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>5.95499992370605</v>
       </c>
       <c r="G1282" t="n">
-        <v>4.90596103668213</v>
+        <v>4.90596055984497</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G1283" t="n">
-        <v>4.9183177947998</v>
+        <v>4.91831827163696</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G1284" t="n">
-        <v>4.90184116363525</v>
+        <v>4.90184164047241</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>6.22499990463257</v>
       </c>
       <c r="G1286" t="n">
-        <v>5.12839698791504</v>
+        <v>5.1283974647522</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>6.39499998092651</v>
       </c>
       <c r="G1288" t="n">
-        <v>5.26845026016235</v>
+        <v>5.2684497833252</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G1289" t="n">
-        <v>5.23961544036865</v>
+        <v>5.23961591720581</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G1290" t="n">
-        <v>5.06660938262939</v>
+        <v>5.06660890579224</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>6.30499982833862</v>
       </c>
       <c r="G1291" t="n">
-        <v>5.19430446624756</v>
+        <v>5.1943039894104</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>6.40999984741211</v>
       </c>
       <c r="G1292" t="n">
-        <v>5.28080749511719</v>
+        <v>5.28080701828003</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>6.59499979019165</v>
       </c>
       <c r="G1293" t="n">
-        <v>5.43321752548218</v>
+        <v>5.43321704864502</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G1295" t="n">
-        <v>5.61858129501343</v>
+        <v>5.61858177185059</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>7.34499979019165</v>
       </c>
       <c r="G1300" t="n">
-        <v>6.05109691619873</v>
+        <v>6.05109643936157</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G1303" t="n">
-        <v>6.08817005157471</v>
+        <v>6.08816909790039</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>7.33500003814697</v>
       </c>
       <c r="G1304" t="n">
-        <v>6.04285860061646</v>
+        <v>6.0428581237793</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>7.21500015258789</v>
       </c>
       <c r="G1309" t="n">
-        <v>5.94399785995483</v>
+        <v>5.94399833679199</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G1313" t="n">
-        <v>5.83277940750122</v>
+        <v>5.83277893066406</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>6.95499992370605</v>
       </c>
       <c r="G1314" t="n">
-        <v>5.72979927062988</v>
+        <v>5.72979974746704</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>6.86499977111816</v>
       </c>
       <c r="G1317" t="n">
-        <v>5.65565347671509</v>
+        <v>5.6556544303894</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>6.57499980926514</v>
       </c>
       <c r="G1319" t="n">
-        <v>5.41674041748047</v>
+        <v>5.41674089431763</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>6.48999977111816</v>
       </c>
       <c r="G1322" t="n">
-        <v>5.34671401977539</v>
+        <v>5.34671449661255</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>6.5149998664856</v>
       </c>
       <c r="G1323" t="n">
-        <v>5.36731004714966</v>
+        <v>5.36731052398682</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>6.63500022888184</v>
       </c>
       <c r="G1327" t="n">
-        <v>5.4661717414856</v>
+        <v>5.46617126464844</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>6.41499996185303</v>
       </c>
       <c r="G1328" t="n">
-        <v>5.28492641448975</v>
+        <v>5.2849268913269</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G1329" t="n">
-        <v>5.25609254837036</v>
+        <v>5.2560920715332</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>6.39499998092651</v>
       </c>
       <c r="G1330" t="n">
-        <v>5.26845026016235</v>
+        <v>5.2684497833252</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>6.43499994277954</v>
       </c>
       <c r="G1333" t="n">
-        <v>5.30140352249146</v>
+        <v>5.3014030456543</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>6.55499982833862</v>
       </c>
       <c r="G1336" t="n">
-        <v>5.40026378631592</v>
+        <v>5.40026426315308</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>6.16499996185303</v>
       </c>
       <c r="G1338" t="n">
-        <v>5.07896709442139</v>
+        <v>5.07896661758423</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G1339" t="n">
-        <v>5.04189395904541</v>
+        <v>5.04189348220825</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G1344" t="n">
-        <v>5.40438318252563</v>
+        <v>5.40438365936279</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>6.53000020980835</v>
       </c>
       <c r="G1345" t="n">
-        <v>5.37966823577881</v>
+        <v>5.37966871261597</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>6.63500022888184</v>
       </c>
       <c r="G1346" t="n">
-        <v>5.4661717414856</v>
+        <v>5.46617126464844</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G1348" t="n">
-        <v>5.63505792617798</v>
+        <v>5.63505840301514</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>6.85500001907349</v>
       </c>
       <c r="G1349" t="n">
-        <v>5.64741611480713</v>
+        <v>5.64741563796997</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>6.86499977111816</v>
       </c>
       <c r="G1350" t="n">
-        <v>5.65565347671509</v>
+        <v>5.6556544303894</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G1351" t="n">
-        <v>5.54443597793579</v>
+        <v>5.54443550109863</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>6.9850001335144</v>
       </c>
       <c r="G1355" t="n">
-        <v>5.75451517105103</v>
+        <v>5.75451469421387</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>6.86499977111816</v>
       </c>
       <c r="G1356" t="n">
-        <v>5.65565347671509</v>
+        <v>5.6556544303894</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G1357" t="n">
-        <v>5.68448877334595</v>
+        <v>5.68448829650879</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1360" t="n">
-        <v>5.84925651550293</v>
+        <v>5.84925603866577</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>6.95499992370605</v>
       </c>
       <c r="G1361" t="n">
-        <v>5.72979927062988</v>
+        <v>5.72979974746704</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>6.9850001335144</v>
       </c>
       <c r="G1362" t="n">
-        <v>5.75451517105103</v>
+        <v>5.75451469421387</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G1363" t="n">
-        <v>5.67624950408936</v>
+        <v>5.67624998092651</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1364" t="n">
-        <v>5.48472023010254</v>
+        <v>5.4847207069397</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>6.41499996185303</v>
       </c>
       <c r="G1366" t="n">
-        <v>5.58483791351318</v>
+        <v>5.58483839035034</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G1367" t="n">
-        <v>5.54566144943237</v>
+        <v>5.54566192626953</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>6.34499979019165</v>
       </c>
       <c r="G1368" t="n">
-        <v>5.52389669418335</v>
+        <v>5.52389717102051</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>6.31500005722046</v>
       </c>
       <c r="G1369" t="n">
-        <v>5.49777889251709</v>
+        <v>5.49777936935425</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>6.31500005722046</v>
       </c>
       <c r="G1371" t="n">
-        <v>5.49777889251709</v>
+        <v>5.49777936935425</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1373" t="n">
-        <v>5.48472023010254</v>
+        <v>5.4847207069397</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G1377" t="n">
-        <v>5.43248510360718</v>
+        <v>5.43248462677002</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G1383" t="n">
-        <v>5.94613361358643</v>
+        <v>5.94613313674927</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>7.00500011444092</v>
       </c>
       <c r="G1387" t="n">
-        <v>6.09848642349243</v>
+        <v>6.09848690032959</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G1394" t="n">
-        <v>5.98095703125</v>
+        <v>5.98095655441284</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G1398" t="n">
-        <v>5.98966264724731</v>
+        <v>5.98966312408447</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G1406" t="n">
-        <v>6.00707483291626</v>
+        <v>6.0070743560791</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>7.125</v>
       </c>
       <c r="G1409" t="n">
-        <v>6.20295810699463</v>
+        <v>6.20295763015747</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G1416" t="n">
-        <v>6.30307483673096</v>
+        <v>6.30307531356812</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>7.19500017166138</v>
       </c>
       <c r="G1417" t="n">
-        <v>6.26389932632446</v>
+        <v>6.2638988494873</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37263,7 +37263,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1419" t="n">
-        <v>6.44236993789673</v>
+        <v>6.44237041473389</v>
       </c>
       <c r="H1419" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>6.90999984741211</v>
       </c>
       <c r="G1423" t="n">
-        <v>6.01578044891357</v>
+        <v>6.01578092575073</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G1429" t="n">
-        <v>6.43366432189941</v>
+        <v>6.43366384506226</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>7.2649998664856</v>
       </c>
       <c r="G1430" t="n">
-        <v>6.32484006881714</v>
+        <v>6.32483959197998</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G1431" t="n">
-        <v>6.37272310256958</v>
+        <v>6.37272262573242</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1432" t="n">
-        <v>6.44236993789673</v>
+        <v>6.44237041473389</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>7.43499994277954</v>
       </c>
       <c r="G1439" t="n">
-        <v>6.47284078598022</v>
+        <v>6.47284030914307</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G1442" t="n">
-        <v>6.28566360473633</v>
+        <v>6.28566312789917</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>7.32499980926514</v>
       </c>
       <c r="G1443" t="n">
-        <v>6.3770751953125</v>
+        <v>6.37707567214966</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>7.40500020980835</v>
       </c>
       <c r="G1454" t="n">
-        <v>6.44672298431396</v>
+        <v>6.44672250747681</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>7.43499994277954</v>
       </c>
       <c r="G1456" t="n">
-        <v>6.47284078598022</v>
+        <v>6.47284030914307</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>8.42500019073486</v>
       </c>
       <c r="G1468" t="n">
-        <v>7.33472490310669</v>
+        <v>7.33472537994385</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>8.44499969482422</v>
       </c>
       <c r="G1469" t="n">
-        <v>7.35213708877563</v>
+        <v>7.35213756561279</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>8.50500011444092</v>
       </c>
       <c r="G1471" t="n">
-        <v>7.40437269210815</v>
+        <v>7.404372215271</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38641,7 +38641,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G1472" t="n">
-        <v>7.45225477218628</v>
+        <v>7.45225524902344</v>
       </c>
       <c r="H1472" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G1473" t="n">
-        <v>7.53931379318237</v>
+        <v>7.53931427001953</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1475" t="n">
-        <v>7.17366552352905</v>
+        <v>7.17366600036621</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>8.61499977111816</v>
       </c>
       <c r="G1478" t="n">
-        <v>7.50013780593872</v>
+        <v>7.50013732910156</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>8.48499965667725</v>
       </c>
       <c r="G1479" t="n">
-        <v>7.38696002960205</v>
+        <v>7.38696050643921</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38875,7 +38875,7 @@
         <v>8.6899995803833</v>
       </c>
       <c r="G1481" t="n">
-        <v>7.56543159484863</v>
+        <v>7.56543111801147</v>
       </c>
       <c r="H1481" t="s">
         <v>8</v>
@@ -38927,7 +38927,7 @@
         <v>8.76500034332275</v>
       </c>
       <c r="G1483" t="n">
-        <v>7.63072538375854</v>
+        <v>7.63072633743286</v>
       </c>
       <c r="H1483" t="s">
         <v>8</v>
@@ -38979,7 +38979,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G1485" t="n">
-        <v>7.53931379318237</v>
+        <v>7.53931427001953</v>
       </c>
       <c r="H1485" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>8.89000034332275</v>
       </c>
       <c r="G1486" t="n">
-        <v>7.73954916000366</v>
+        <v>7.73955011367798</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>9.41499996185303</v>
       </c>
       <c r="G1488" t="n">
-        <v>8.19660949707031</v>
+        <v>8.19661045074463</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G1491" t="n">
-        <v>8.4621410369873</v>
+        <v>8.46214008331299</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39161,7 +39161,7 @@
         <v>9.71500015258789</v>
       </c>
       <c r="G1492" t="n">
-        <v>8.45778751373291</v>
+        <v>8.45778656005859</v>
       </c>
       <c r="H1492" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>9.36499977111816</v>
       </c>
       <c r="G1500" t="n">
-        <v>8.15307998657227</v>
+        <v>8.15308094024658</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>9.4350004196167</v>
       </c>
       <c r="G1506" t="n">
-        <v>8.21402263641357</v>
+        <v>8.21402168273926</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39551,7 +39551,7 @@
         <v>9.34500026702881</v>
       </c>
       <c r="G1507" t="n">
-        <v>8.13566970825195</v>
+        <v>8.13566875457764</v>
       </c>
       <c r="H1507" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G1508" t="n">
-        <v>7.90496253967285</v>
+        <v>7.90496158599854</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39629,7 +39629,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G1510" t="n">
-        <v>7.85272741317749</v>
+        <v>7.85272645950317</v>
       </c>
       <c r="H1510" t="s">
         <v>8</v>
@@ -39655,7 +39655,7 @@
         <v>9.05500030517578</v>
       </c>
       <c r="G1511" t="n">
-        <v>7.88319778442383</v>
+        <v>7.88319683074951</v>
       </c>
       <c r="H1511" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>9.19499969482422</v>
       </c>
       <c r="G1515" t="n">
-        <v>8.0050802230835</v>
+        <v>8.00507926940918</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G1521" t="n">
-        <v>8.0007266998291</v>
+        <v>8.00072765350342</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>9.15499973297119</v>
       </c>
       <c r="G1523" t="n">
-        <v>7.97025680541992</v>
+        <v>7.97025585174561</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>9.32999992370605</v>
       </c>
       <c r="G1528" t="n">
-        <v>8.12260913848877</v>
+        <v>8.12261009216309</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>9.41499996185303</v>
       </c>
       <c r="G1533" t="n">
-        <v>8.19660949707031</v>
+        <v>8.19661045074463</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>8.69499969482422</v>
       </c>
       <c r="G1536" t="n">
-        <v>7.93662929534912</v>
+        <v>7.93662881851196</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G1540" t="n">
-        <v>7.95944929122925</v>
+        <v>7.95944976806641</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>8.57499980926514</v>
       </c>
       <c r="G1543" t="n">
-        <v>7.82709503173828</v>
+        <v>7.8270959854126</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>8.61499977111816</v>
       </c>
       <c r="G1545" t="n">
-        <v>7.86360740661621</v>
+        <v>7.86360692977905</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40565,7 +40565,7 @@
         <v>8.69499969482422</v>
       </c>
       <c r="G1546" t="n">
-        <v>7.93662929534912</v>
+        <v>7.93662881851196</v>
       </c>
       <c r="H1546" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>8.54500007629395</v>
       </c>
       <c r="G1547" t="n">
-        <v>7.79971265792847</v>
+        <v>7.79971218109131</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>8.625</v>
       </c>
       <c r="G1549" t="n">
-        <v>7.87273454666138</v>
+        <v>7.87273502349854</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40669,7 +40669,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G1550" t="n">
-        <v>7.84078788757324</v>
+        <v>7.84078741073608</v>
       </c>
       <c r="H1550" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G1556" t="n">
-        <v>8.38845539093018</v>
+        <v>8.38845634460449</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40851,7 +40851,7 @@
         <v>9.15499973297119</v>
       </c>
       <c r="G1557" t="n">
-        <v>8.3565092086792</v>
+        <v>8.35650825500488</v>
       </c>
       <c r="H1557" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G1567" t="n">
-        <v>8.87223052978516</v>
+        <v>8.87222957611084</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41501,7 +41501,7 @@
         <v>9.78999996185303</v>
       </c>
       <c r="G1582" t="n">
-        <v>8.93612384796143</v>
+        <v>8.93612480163574</v>
       </c>
       <c r="H1582" t="s">
         <v>8</v>
@@ -41553,7 +41553,7 @@
         <v>10.0299997329712</v>
       </c>
       <c r="G1584" t="n">
-        <v>9.15519142150879</v>
+        <v>9.15519237518311</v>
       </c>
       <c r="H1584" t="s">
         <v>8</v>
@@ -41579,7 +41579,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G1585" t="n">
-        <v>9.03653049468994</v>
+        <v>9.03652954101562</v>
       </c>
       <c r="H1585" t="s">
         <v>8</v>
@@ -41631,7 +41631,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G1587" t="n">
-        <v>9.01827430725098</v>
+        <v>9.01827526092529</v>
       </c>
       <c r="H1587" t="s">
         <v>8</v>
@@ -41917,7 +41917,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G1598" t="n">
-        <v>9.29210948944092</v>
+        <v>9.2921085357666</v>
       </c>
       <c r="H1598" t="s">
         <v>8</v>
@@ -42021,7 +42021,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G1602" t="n">
-        <v>9.01827430725098</v>
+        <v>9.01827526092529</v>
       </c>
       <c r="H1602" t="s">
         <v>8</v>
@@ -42125,7 +42125,7 @@
         <v>10.1700000762939</v>
       </c>
       <c r="G1606" t="n">
-        <v>9.28298091888428</v>
+        <v>9.28298187255859</v>
       </c>
       <c r="H1606" t="s">
         <v>8</v>
@@ -42229,7 +42229,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1610" t="n">
-        <v>8.83571815490723</v>
+        <v>8.83571910858154</v>
       </c>
       <c r="H1610" t="s">
         <v>8</v>
@@ -42281,7 +42281,7 @@
         <v>9.5649995803833</v>
       </c>
       <c r="G1612" t="n">
-        <v>8.73074817657471</v>
+        <v>8.73074913024902</v>
       </c>
       <c r="H1612" t="s">
         <v>8</v>
@@ -42307,7 +42307,7 @@
         <v>9.6850004196167</v>
       </c>
       <c r="G1613" t="n">
-        <v>8.84028339385986</v>
+        <v>8.84028244018555</v>
       </c>
       <c r="H1613" t="s">
         <v>8</v>
@@ -42463,7 +42463,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G1619" t="n">
-        <v>8.80833435058594</v>
+        <v>8.80833530426025</v>
       </c>
       <c r="H1619" t="s">
         <v>8</v>
@@ -42541,7 +42541,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G1622" t="n">
-        <v>8.80833435058594</v>
+        <v>8.80833530426025</v>
       </c>
       <c r="H1622" t="s">
         <v>8</v>
@@ -42827,7 +42827,7 @@
         <v>9.6850004196167</v>
       </c>
       <c r="G1633" t="n">
-        <v>8.84028339385986</v>
+        <v>8.84028244018555</v>
       </c>
       <c r="H1633" t="s">
         <v>8</v>
@@ -62772,6 +62772,32 @@
         <v>2.99000000953674</v>
       </c>
       <c r="H2400" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2401">
+      <c r="A2401" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B2401" t="n">
+        <v>1558730</v>
+      </c>
+      <c r="C2401" t="n">
+        <v>3.04200005531311</v>
+      </c>
+      <c r="D2401" t="n">
+        <v>2.94799995422363</v>
+      </c>
+      <c r="E2401" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2401" t="n">
+        <v>2.94799995422363</v>
+      </c>
+      <c r="G2401" t="n">
+        <v>2.94799995422363</v>
+      </c>
+      <c r="H2401" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/BFF.MI.xlsx
+++ b/data/BFF.MI.xlsx
@@ -447,7 +447,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G3" t="n">
-        <v>2.36908102035522</v>
+        <v>2.3690812587738</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>4.25</v>
       </c>
       <c r="G4" t="n">
-        <v>2.31461954116821</v>
+        <v>2.31461977958679</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>4.06599998474121</v>
       </c>
       <c r="G7" t="n">
-        <v>2.21441006660461</v>
+        <v>2.21440982818604</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G8" t="n">
-        <v>2.2220344543457</v>
+        <v>2.22203469276428</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G13" t="n">
-        <v>2.3418505191803</v>
+        <v>2.34185028076172</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G15" t="n">
-        <v>2.36363482475281</v>
+        <v>2.36363530158997</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>4.36199998855591</v>
       </c>
       <c r="G16" t="n">
-        <v>2.37561678886414</v>
+        <v>2.37561655044556</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>4.4520001411438</v>
       </c>
       <c r="G19" t="n">
-        <v>2.42463183403015</v>
+        <v>2.42463207244873</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G22" t="n">
-        <v>2.55969643592834</v>
+        <v>2.5596969127655</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>4.83599996566772</v>
       </c>
       <c r="G23" t="n">
-        <v>2.63376450538635</v>
+        <v>2.63376474380493</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>4.85400009155273</v>
       </c>
       <c r="G24" t="n">
-        <v>2.64356803894043</v>
+        <v>2.64356756210327</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G25" t="n">
-        <v>2.55969643592834</v>
+        <v>2.5596969127655</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>4.73799991607666</v>
       </c>
       <c r="G27" t="n">
-        <v>2.58039212226868</v>
+        <v>2.58039236068726</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>4.73199987411499</v>
       </c>
       <c r="G29" t="n">
-        <v>2.57712435722351</v>
+        <v>2.57712483406067</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>4.74200010299683</v>
       </c>
       <c r="G30" t="n">
-        <v>2.58257079124451</v>
+        <v>2.58257055282593</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>4.77600002288818</v>
       </c>
       <c r="G32" t="n">
-        <v>2.60108804702759</v>
+        <v>2.60108757019043</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G34" t="n">
-        <v>2.66317391395569</v>
+        <v>2.66317415237427</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G35" t="n">
-        <v>2.68495869636536</v>
+        <v>2.68495845794678</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>4.89799976348877</v>
       </c>
       <c r="G36" t="n">
-        <v>2.66753101348877</v>
+        <v>2.66753053665161</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G37" t="n">
-        <v>2.68495869636536</v>
+        <v>2.68495845794678</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>4.94799995422363</v>
       </c>
       <c r="G38" t="n">
-        <v>2.69476175308228</v>
+        <v>2.69476222991943</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G41" t="n">
-        <v>2.6413893699646</v>
+        <v>2.64138913154602</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G42" t="n">
-        <v>2.65772771835327</v>
+        <v>2.65772795677185</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G43" t="n">
-        <v>2.66862010955811</v>
+        <v>2.66862034797668</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>4.87599992752075</v>
       </c>
       <c r="G44" t="n">
-        <v>2.6555495262146</v>
+        <v>2.65554928779602</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>4.84600019454956</v>
       </c>
       <c r="G45" t="n">
-        <v>2.63921070098877</v>
+        <v>2.63921117782593</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>5.06500005722046</v>
       </c>
       <c r="G47" t="n">
-        <v>2.75848174095154</v>
+        <v>2.75848197937012</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>5.07499980926514</v>
       </c>
       <c r="G48" t="n">
-        <v>2.76392817497253</v>
+        <v>2.76392793655396</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G49" t="n">
-        <v>2.72852802276611</v>
+        <v>2.72852778434753</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G50" t="n">
-        <v>2.77754378318787</v>
+        <v>2.77754306793213</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G51" t="n">
-        <v>2.81022047996521</v>
+        <v>2.81022024154663</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G53" t="n">
-        <v>2.80749750137329</v>
+        <v>2.80749726295471</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>5</v>
       </c>
       <c r="G54" t="n">
-        <v>2.7230818271637</v>
+        <v>2.72308158874512</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G56" t="n">
-        <v>2.81566643714905</v>
+        <v>2.81566667556763</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G57" t="n">
-        <v>2.84289765357971</v>
+        <v>2.84289717674255</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G58" t="n">
-        <v>2.81022047996521</v>
+        <v>2.81022024154663</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>5</v>
       </c>
       <c r="G59" t="n">
-        <v>2.7230818271637</v>
+        <v>2.72308158874512</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>5.09499979019165</v>
       </c>
       <c r="G60" t="n">
-        <v>2.77481985092163</v>
+        <v>2.77482008934021</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G61" t="n">
-        <v>2.79932808876038</v>
+        <v>2.7993278503418</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G63" t="n">
-        <v>2.79932808876038</v>
+        <v>2.7993278503418</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G65" t="n">
-        <v>2.79388236999512</v>
+        <v>2.79388213157654</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>5.07499980926514</v>
       </c>
       <c r="G66" t="n">
-        <v>2.76392817497253</v>
+        <v>2.76392793655396</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>5.125</v>
       </c>
       <c r="G67" t="n">
-        <v>2.79115867614746</v>
+        <v>2.79115891456604</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G68" t="n">
-        <v>2.81566643714905</v>
+        <v>2.81566667556763</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G69" t="n">
-        <v>2.78843593597412</v>
+        <v>2.78843545913696</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G70" t="n">
-        <v>2.80477404594421</v>
+        <v>2.80477452278137</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>5.07499980926514</v>
       </c>
       <c r="G71" t="n">
-        <v>2.76392817497253</v>
+        <v>2.76392793655396</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G72" t="n">
-        <v>2.78026628494263</v>
+        <v>2.78026676177979</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G73" t="n">
-        <v>2.78026628494263</v>
+        <v>2.78026676177979</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G74" t="n">
-        <v>2.78843593597412</v>
+        <v>2.78843545913696</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G75" t="n">
-        <v>2.80477404594421</v>
+        <v>2.80477452278137</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>5.125</v>
       </c>
       <c r="G76" t="n">
-        <v>2.79115867614746</v>
+        <v>2.79115891456604</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>5.17500019073486</v>
       </c>
       <c r="G77" t="n">
-        <v>2.81838941574097</v>
+        <v>2.81838989257812</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G78" t="n">
-        <v>2.78843593597412</v>
+        <v>2.78843545913696</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G79" t="n">
-        <v>2.82655906677246</v>
+        <v>2.82655930519104</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G81" t="n">
-        <v>2.80477404594421</v>
+        <v>2.80477452278137</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G82" t="n">
-        <v>2.80477404594421</v>
+        <v>2.80477452278137</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G83" t="n">
-        <v>2.80477404594421</v>
+        <v>2.80477452278137</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G84" t="n">
-        <v>2.79932808876038</v>
+        <v>2.7993278503418</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G85" t="n">
-        <v>2.80749750137329</v>
+        <v>2.80749726295471</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G86" t="n">
-        <v>2.80477404594421</v>
+        <v>2.80477452278137</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G87" t="n">
-        <v>2.79388236999512</v>
+        <v>2.79388213157654</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>5.13500022888184</v>
       </c>
       <c r="G88" t="n">
-        <v>2.79660511016846</v>
+        <v>2.79660487174988</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>5.08500003814697</v>
       </c>
       <c r="G89" t="n">
-        <v>2.76937413215637</v>
+        <v>2.76937460899353</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G90" t="n">
-        <v>2.81566643714905</v>
+        <v>2.81566667556763</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G92" t="n">
-        <v>2.81566643714905</v>
+        <v>2.81566667556763</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G93" t="n">
-        <v>2.80749750137329</v>
+        <v>2.80749726295471</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G94" t="n">
-        <v>2.80749750137329</v>
+        <v>2.80749726295471</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G95" t="n">
-        <v>2.79932808876038</v>
+        <v>2.7993278503418</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G97" t="n">
-        <v>2.81566643714905</v>
+        <v>2.81566667556763</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G98" t="n">
-        <v>2.79932808876038</v>
+        <v>2.7993278503418</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>4.9520001411438</v>
       </c>
       <c r="G100" t="n">
-        <v>2.69693994522095</v>
+        <v>2.69694018363953</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>4.99200010299683</v>
       </c>
       <c r="G102" t="n">
-        <v>2.71872520446777</v>
+        <v>2.71872496604919</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G103" t="n">
-        <v>2.73942065238953</v>
+        <v>2.73942017555237</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G104" t="n">
-        <v>2.81022047996521</v>
+        <v>2.81022024154663</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G105" t="n">
-        <v>2.77754378318787</v>
+        <v>2.77754306793213</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G106" t="n">
-        <v>2.78026628494263</v>
+        <v>2.78026676177979</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>5.08500003814697</v>
       </c>
       <c r="G107" t="n">
-        <v>2.76937413215637</v>
+        <v>2.76937460899353</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G108" t="n">
-        <v>2.76665115356445</v>
+        <v>2.76665091514587</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G109" t="n">
-        <v>2.78843593597412</v>
+        <v>2.78843545913696</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G113" t="n">
-        <v>2.86468243598938</v>
+        <v>2.86468195915222</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>5.50500011444092</v>
       </c>
       <c r="G114" t="n">
-        <v>2.99811315536499</v>
+        <v>2.99811291694641</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>5.49499988555908</v>
       </c>
       <c r="G115" t="n">
-        <v>2.99266648292542</v>
+        <v>2.99266719818115</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G116" t="n">
-        <v>3.02806687355042</v>
+        <v>3.02806711196899</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G117" t="n">
-        <v>3.03895926475525</v>
+        <v>3.03895950317383</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G119" t="n">
-        <v>3.08797454833984</v>
+        <v>3.08797478675842</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>5.67500019073486</v>
       </c>
       <c r="G120" t="n">
-        <v>3.09069752693176</v>
+        <v>3.09069776535034</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G121" t="n">
-        <v>3.24046730995178</v>
+        <v>3.24046683311462</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G122" t="n">
-        <v>3.21323680877686</v>
+        <v>3.21323609352112</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>5.75</v>
       </c>
       <c r="G123" t="n">
-        <v>3.1315438747406</v>
+        <v>3.13154411315918</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G124" t="n">
-        <v>3.19689774513245</v>
+        <v>3.19689798355103</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G126" t="n">
-        <v>3.07708215713501</v>
+        <v>3.07708263397217</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G128" t="n">
-        <v>3.10431265830994</v>
+        <v>3.10431337356567</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>5.72499990463257</v>
       </c>
       <c r="G129" t="n">
-        <v>3.11792850494385</v>
+        <v>3.11792826652527</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G130" t="n">
-        <v>3.15877461433411</v>
+        <v>3.15877509117126</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G131" t="n">
-        <v>3.20234417915344</v>
+        <v>3.20234441757202</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G133" t="n">
-        <v>3.32216000556946</v>
+        <v>3.32215976715088</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>6.125</v>
       </c>
       <c r="G134" t="n">
-        <v>3.33577513694763</v>
+        <v>3.33577537536621</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G135" t="n">
-        <v>3.30582118034363</v>
+        <v>3.30582141876221</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>6.11499977111816</v>
       </c>
       <c r="G136" t="n">
-        <v>3.33032917976379</v>
+        <v>3.33032870292664</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>6.04500007629395</v>
       </c>
       <c r="G137" t="n">
-        <v>3.2922055721283</v>
+        <v>3.29220628738403</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>6</v>
       </c>
       <c r="G138" t="n">
-        <v>3.26769804954529</v>
+        <v>3.26769828796387</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>6.11499977111816</v>
       </c>
       <c r="G139" t="n">
-        <v>3.33032917976379</v>
+        <v>3.33032870292664</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G141" t="n">
-        <v>3.32216000556946</v>
+        <v>3.32215976715088</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G142" t="n">
-        <v>3.34939026832581</v>
+        <v>3.34939074516296</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G143" t="n">
-        <v>3.39295959472656</v>
+        <v>3.39296007156372</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G144" t="n">
-        <v>3.3875138759613</v>
+        <v>3.38751339912415</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>6.25</v>
       </c>
       <c r="G145" t="n">
-        <v>3.40385222434998</v>
+        <v>3.40385246276855</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G146" t="n">
-        <v>3.38206791877747</v>
+        <v>3.38206768035889</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>6.11499977111816</v>
       </c>
       <c r="G147" t="n">
-        <v>3.33032917976379</v>
+        <v>3.33032870292664</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>6.00500011444092</v>
       </c>
       <c r="G149" t="n">
-        <v>3.27042174339294</v>
+        <v>3.27042150497437</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G151" t="n">
-        <v>3.28403735160828</v>
+        <v>3.28403687477112</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G152" t="n">
-        <v>3.25680589675903</v>
+        <v>3.25680565834045</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G153" t="n">
-        <v>3.24591374397278</v>
+        <v>3.2459135055542</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>5.92999982833862</v>
       </c>
       <c r="G154" t="n">
-        <v>3.22957491874695</v>
+        <v>3.22957468032837</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G155" t="n">
-        <v>3.21323680877686</v>
+        <v>3.21323609352112</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G156" t="n">
-        <v>3.27314400672913</v>
+        <v>3.27314472198486</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>6</v>
       </c>
       <c r="G157" t="n">
-        <v>3.26769804954529</v>
+        <v>3.26769828796387</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G158" t="n">
-        <v>3.32760643959045</v>
+        <v>3.3276059627533</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>6.125</v>
       </c>
       <c r="G159" t="n">
-        <v>3.33577513694763</v>
+        <v>3.33577537536621</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G161" t="n">
-        <v>3.38206791877747</v>
+        <v>3.38206768035889</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>6.40999984741211</v>
       </c>
       <c r="G162" t="n">
-        <v>3.49099087715149</v>
+        <v>3.49099063873291</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G163" t="n">
-        <v>3.51277494430542</v>
+        <v>3.512775182724</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G164" t="n">
-        <v>3.47465181350708</v>
+        <v>3.47465229034424</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G165" t="n">
-        <v>3.45831418037415</v>
+        <v>3.45831370353699</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>6.41499996185303</v>
       </c>
       <c r="G166" t="n">
-        <v>3.49371385574341</v>
+        <v>3.49371337890625</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>6.36499977111816</v>
       </c>
       <c r="G168" t="n">
-        <v>3.46648335456848</v>
+        <v>3.46648287773132</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G169" t="n">
-        <v>3.50732946395874</v>
+        <v>3.50732922554016</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G170" t="n">
-        <v>3.50732946395874</v>
+        <v>3.50732922554016</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>6.40999984741211</v>
       </c>
       <c r="G171" t="n">
-        <v>3.49099087715149</v>
+        <v>3.49099063873291</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>6.58500003814697</v>
       </c>
       <c r="G174" t="n">
-        <v>3.58629894256592</v>
+        <v>3.58629870414734</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G175" t="n">
-        <v>3.59446787834167</v>
+        <v>3.59446740150452</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>6.53000020980835</v>
       </c>
       <c r="G176" t="n">
-        <v>3.55634474754333</v>
+        <v>3.55634498596191</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G177" t="n">
-        <v>3.52366757392883</v>
+        <v>3.52366781234741</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>6.53499984741211</v>
       </c>
       <c r="G178" t="n">
-        <v>3.55906772613525</v>
+        <v>3.55906748771667</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>6.5149998664856</v>
       </c>
       <c r="G179" t="n">
-        <v>3.54817581176758</v>
+        <v>3.548175573349</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>6.375</v>
       </c>
       <c r="G181" t="n">
-        <v>3.47192931175232</v>
+        <v>3.47192859649658</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G182" t="n">
-        <v>3.47465181350708</v>
+        <v>3.47465229034424</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>6.25</v>
       </c>
       <c r="G183" t="n">
-        <v>3.40385222434998</v>
+        <v>3.40385246276855</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G184" t="n">
-        <v>3.44742178916931</v>
+        <v>3.44742155075073</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>6.38500022888184</v>
       </c>
       <c r="G185" t="n">
-        <v>3.47737526893616</v>
+        <v>3.47737574577332</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G186" t="n">
-        <v>3.48554539680481</v>
+        <v>3.48554491996765</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>6.41499996185303</v>
       </c>
       <c r="G187" t="n">
-        <v>3.49371385574341</v>
+        <v>3.49371337890625</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>6.53499984741211</v>
       </c>
       <c r="G188" t="n">
-        <v>3.55906772613525</v>
+        <v>3.55906748771667</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>6.5</v>
       </c>
       <c r="G189" t="n">
-        <v>3.54000616073608</v>
+        <v>3.54000639915466</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>6.5</v>
       </c>
       <c r="G191" t="n">
-        <v>3.54000616073608</v>
+        <v>3.54000639915466</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>6.43499994277954</v>
       </c>
       <c r="G192" t="n">
-        <v>3.5046067237854</v>
+        <v>3.50460648536682</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G194" t="n">
-        <v>3.47465181350708</v>
+        <v>3.47465229034424</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>6.46500015258789</v>
       </c>
       <c r="G195" t="n">
-        <v>3.52094459533691</v>
+        <v>3.52094483375549</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G196" t="n">
-        <v>3.52911400794983</v>
+        <v>3.52911424636841</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>6.5</v>
       </c>
       <c r="G197" t="n">
-        <v>3.54000616073608</v>
+        <v>3.54000639915466</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G202" t="n">
-        <v>3.58902168273926</v>
+        <v>3.58902192115784</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G203" t="n">
-        <v>3.59446787834167</v>
+        <v>3.59446740150452</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>6.53000020980835</v>
       </c>
       <c r="G204" t="n">
-        <v>3.55634474754333</v>
+        <v>3.55634498596191</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>6.59499979019165</v>
       </c>
       <c r="G205" t="n">
-        <v>3.59174466133118</v>
+        <v>3.59174513816833</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G206" t="n">
-        <v>3.59991383552551</v>
+        <v>3.59991455078125</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>6.41499996185303</v>
       </c>
       <c r="G209" t="n">
-        <v>3.49371385574341</v>
+        <v>3.49371337890625</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G211" t="n">
-        <v>3.28403735160828</v>
+        <v>3.28403687477112</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>5.91499996185303</v>
       </c>
       <c r="G212" t="n">
-        <v>3.22140574455261</v>
+        <v>3.22140550613403</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G213" t="n">
-        <v>3.27859044075012</v>
+        <v>3.27858996391296</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G214" t="n">
-        <v>3.12065172195435</v>
+        <v>3.12065148353577</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>5.92999982833862</v>
       </c>
       <c r="G215" t="n">
-        <v>3.22957491874695</v>
+        <v>3.22957468032837</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>5.81500005722046</v>
       </c>
       <c r="G217" t="n">
-        <v>3.16694474220276</v>
+        <v>3.16694402694702</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>5.93499994277954</v>
       </c>
       <c r="G218" t="n">
-        <v>3.23229837417603</v>
+        <v>3.23229765892029</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>6</v>
       </c>
       <c r="G219" t="n">
-        <v>3.26769804954529</v>
+        <v>3.26769828796387</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G220" t="n">
-        <v>3.38206791877747</v>
+        <v>3.38206768035889</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>6.14499998092651</v>
       </c>
       <c r="G221" t="n">
-        <v>3.34666752815247</v>
+        <v>3.34666800498962</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G223" t="n">
-        <v>3.21323680877686</v>
+        <v>3.21323609352112</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G224" t="n">
-        <v>3.1805591583252</v>
+        <v>3.18055987358093</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>5.81500005722046</v>
       </c>
       <c r="G227" t="n">
-        <v>3.16694474220276</v>
+        <v>3.16694402694702</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G228" t="n">
-        <v>3.18600583076477</v>
+        <v>3.18600535392761</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G229" t="n">
-        <v>3.18600583076477</v>
+        <v>3.18600535392761</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G230" t="n">
-        <v>3.17511320114136</v>
+        <v>3.17511343955994</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>5.78499984741211</v>
       </c>
       <c r="G231" t="n">
-        <v>3.15060520172119</v>
+        <v>3.15060544013977</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G232" t="n">
-        <v>3.15877461433411</v>
+        <v>3.15877509117126</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>5.88500022888184</v>
       </c>
       <c r="G234" t="n">
-        <v>3.20506691932678</v>
+        <v>3.20506739616394</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>5.95499992370605</v>
       </c>
       <c r="G235" t="n">
-        <v>3.2431902885437</v>
+        <v>3.24319005012512</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>6.04500007629395</v>
       </c>
       <c r="G236" t="n">
-        <v>3.2922055721283</v>
+        <v>3.29220628738403</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>5.95499992370605</v>
       </c>
       <c r="G237" t="n">
-        <v>3.2431902885437</v>
+        <v>3.24319005012512</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G238" t="n">
-        <v>3.24046730995178</v>
+        <v>3.24046683311462</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>5.88500022888184</v>
       </c>
       <c r="G239" t="n">
-        <v>3.20506691932678</v>
+        <v>3.20506739616394</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>5.91499996185303</v>
       </c>
       <c r="G240" t="n">
-        <v>3.22140574455261</v>
+        <v>3.22140550613403</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>5.88500022888184</v>
       </c>
       <c r="G241" t="n">
-        <v>3.20506691932678</v>
+        <v>3.20506739616394</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>5.75</v>
       </c>
       <c r="G242" t="n">
-        <v>3.1315438747406</v>
+        <v>3.13154411315918</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G245" t="n">
-        <v>3.08797454833984</v>
+        <v>3.08797478675842</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G246" t="n">
-        <v>3.09342050552368</v>
+        <v>3.09342074394226</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G247" t="n">
-        <v>3.1642210483551</v>
+        <v>3.16422080993652</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G248" t="n">
-        <v>3.18600583076477</v>
+        <v>3.18600535392761</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G249" t="n">
-        <v>3.23502087593079</v>
+        <v>3.23502135276794</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G250" t="n">
-        <v>3.21323680877686</v>
+        <v>3.21323609352112</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G251" t="n">
-        <v>3.18600583076477</v>
+        <v>3.18600535392761</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G253" t="n">
-        <v>3.20234417915344</v>
+        <v>3.20234441757202</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>5.5</v>
       </c>
       <c r="G254" t="n">
-        <v>3.26891112327576</v>
+        <v>3.26891088485718</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>5.5</v>
       </c>
       <c r="G257" t="n">
-        <v>3.26891112327576</v>
+        <v>3.26891088485718</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G258" t="n">
-        <v>3.24513721466064</v>
+        <v>3.24513697624207</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G259" t="n">
-        <v>3.21541953086853</v>
+        <v>3.21542000770569</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G260" t="n">
-        <v>3.15598487854004</v>
+        <v>3.15598511695862</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G261" t="n">
-        <v>3.20947623252869</v>
+        <v>3.20947647094727</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>5.41499996185303</v>
       </c>
       <c r="G262" t="n">
-        <v>3.21839165687561</v>
+        <v>3.21839141845703</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G266" t="n">
-        <v>3.06386160850525</v>
+        <v>3.06386137008667</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G267" t="n">
-        <v>3.13815498352051</v>
+        <v>3.13815450668335</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G268" t="n">
-        <v>3.06088948249817</v>
+        <v>3.06088972091675</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G271" t="n">
-        <v>3.13815498352051</v>
+        <v>3.13815450668335</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G273" t="n">
-        <v>3.07872009277344</v>
+        <v>3.07871985435486</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G274" t="n">
-        <v>3.09654974937439</v>
+        <v>3.09655046463013</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>5.02500009536743</v>
       </c>
       <c r="G276" t="n">
-        <v>2.98659610748291</v>
+        <v>2.98659586906433</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>5.22499990463257</v>
       </c>
       <c r="G278" t="n">
-        <v>3.10546565055847</v>
+        <v>3.10546541213989</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G279" t="n">
-        <v>3.01928496360779</v>
+        <v>3.01928520202637</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G281" t="n">
-        <v>3.0430588722229</v>
+        <v>3.04305911064148</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>5.07499980926514</v>
       </c>
       <c r="G283" t="n">
-        <v>3.01631379127502</v>
+        <v>3.01631331443787</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G284" t="n">
-        <v>3.03414344787598</v>
+        <v>3.03414392471313</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G286" t="n">
-        <v>3.03117227554321</v>
+        <v>3.03117203712463</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G287" t="n">
-        <v>3.06386160850525</v>
+        <v>3.06386137008667</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>4.89200019836426</v>
       </c>
       <c r="G289" t="n">
-        <v>2.90754818916321</v>
+        <v>2.90754795074463</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>5.07499980926514</v>
       </c>
       <c r="G290" t="n">
-        <v>3.01631379127502</v>
+        <v>3.01631331443787</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>5.07499980926514</v>
       </c>
       <c r="G291" t="n">
-        <v>3.01631379127502</v>
+        <v>3.01631331443787</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G293" t="n">
-        <v>3.09060645103455</v>
+        <v>3.09060716629028</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G294" t="n">
-        <v>3.06683325767517</v>
+        <v>3.06683301925659</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>5.11499977111816</v>
       </c>
       <c r="G295" t="n">
-        <v>3.04008650779724</v>
+        <v>3.0400869846344</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>5.19500017166138</v>
       </c>
       <c r="G296" t="n">
-        <v>3.08763527870178</v>
+        <v>3.08763551712036</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G297" t="n">
-        <v>3.03711557388306</v>
+        <v>3.03711581230164</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G298" t="n">
-        <v>3.06088948249817</v>
+        <v>3.06088972091675</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G299" t="n">
-        <v>3.11438083648682</v>
+        <v>3.11438035964966</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G300" t="n">
-        <v>3.09060645103455</v>
+        <v>3.09060716629028</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>5.29500007629395</v>
       </c>
       <c r="G301" t="n">
-        <v>3.14706993103027</v>
+        <v>3.14706945419312</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G302" t="n">
-        <v>3.13221096992493</v>
+        <v>3.13221144676208</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G303" t="n">
-        <v>3.15598487854004</v>
+        <v>3.15598511695862</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G304" t="n">
-        <v>3.20353269577026</v>
+        <v>3.20353293418884</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G305" t="n">
-        <v>3.14409852027893</v>
+        <v>3.14409828186035</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>5.34499979019165</v>
       </c>
       <c r="G306" t="n">
-        <v>3.17678713798523</v>
+        <v>3.17678737640381</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G308" t="n">
-        <v>3.01928496360779</v>
+        <v>3.01928520202637</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G309" t="n">
-        <v>3.01334166526794</v>
+        <v>3.01334190368652</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>4.95599985122681</v>
       </c>
       <c r="G310" t="n">
-        <v>2.94558620452881</v>
+        <v>2.94558596611023</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>5</v>
       </c>
       <c r="G313" t="n">
-        <v>2.97173714637756</v>
+        <v>2.97173738479614</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>5.02500009536743</v>
       </c>
       <c r="G314" t="n">
-        <v>2.98659610748291</v>
+        <v>2.98659586906433</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>4.93200016021729</v>
       </c>
       <c r="G315" t="n">
-        <v>2.93132185935974</v>
+        <v>2.93132162094116</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>4.96199989318848</v>
       </c>
       <c r="G316" t="n">
-        <v>2.94915223121643</v>
+        <v>2.94915199279785</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G317" t="n">
-        <v>2.98956775665283</v>
+        <v>2.98956799507141</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G320" t="n">
-        <v>3.0430588722229</v>
+        <v>3.04305911064148</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G321" t="n">
-        <v>3.02522826194763</v>
+        <v>3.02522897720337</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G323" t="n">
-        <v>3.06683325767517</v>
+        <v>3.06683301925659</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G324" t="n">
-        <v>3.13815498352051</v>
+        <v>3.13815450668335</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G325" t="n">
-        <v>3.12626791000366</v>
+        <v>3.12626767158508</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G327" t="n">
-        <v>3.12626791000366</v>
+        <v>3.12626767158508</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G328" t="n">
-        <v>3.0846631526947</v>
+        <v>3.08466339111328</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G330" t="n">
-        <v>3.09060645103455</v>
+        <v>3.09060716629028</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>5.29500007629395</v>
       </c>
       <c r="G332" t="n">
-        <v>3.14706993103027</v>
+        <v>3.14706945419312</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>5.34499979019165</v>
       </c>
       <c r="G334" t="n">
-        <v>3.17678713798523</v>
+        <v>3.17678737640381</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>5.33500003814697</v>
       </c>
       <c r="G335" t="n">
-        <v>3.17084360122681</v>
+        <v>3.17084383964539</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G336" t="n">
-        <v>3.15004181861877</v>
+        <v>3.15004205703735</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>5.17500019073486</v>
       </c>
       <c r="G338" t="n">
-        <v>3.07574820518494</v>
+        <v>3.07574844360352</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G340" t="n">
-        <v>3.20947623252869</v>
+        <v>3.20947647094727</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>5.44500017166138</v>
       </c>
       <c r="G341" t="n">
-        <v>3.23622226715088</v>
+        <v>3.2362220287323</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G344" t="n">
-        <v>3.16192889213562</v>
+        <v>3.16192841529846</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G345" t="n">
-        <v>3.10249376296997</v>
+        <v>3.10249423980713</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G348" t="n">
-        <v>3.0846631526947</v>
+        <v>3.08466339111328</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G349" t="n">
-        <v>3.06683325767517</v>
+        <v>3.06683301925659</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G351" t="n">
-        <v>3.06088948249817</v>
+        <v>3.06088972091675</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>5.17500019073486</v>
       </c>
       <c r="G353" t="n">
-        <v>3.07574820518494</v>
+        <v>3.07574844360352</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>5.16499996185303</v>
       </c>
       <c r="G354" t="n">
-        <v>3.06980466842651</v>
+        <v>3.06980490684509</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G356" t="n">
-        <v>3.06088948249817</v>
+        <v>3.06088972091675</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>5.125</v>
       </c>
       <c r="G358" t="n">
-        <v>3.04603099822998</v>
+        <v>3.0460307598114</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G362" t="n">
-        <v>3.06683325767517</v>
+        <v>3.06683301925659</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>5.125</v>
       </c>
       <c r="G367" t="n">
-        <v>3.04603099822998</v>
+        <v>3.0460307598114</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G368" t="n">
-        <v>3.06088948249817</v>
+        <v>3.06088972091675</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G369" t="n">
-        <v>3.09060645103455</v>
+        <v>3.09060716629028</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G370" t="n">
-        <v>3.11438083648682</v>
+        <v>3.11438035964966</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G371" t="n">
-        <v>3.15598487854004</v>
+        <v>3.15598511695862</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G372" t="n">
-        <v>3.09654974937439</v>
+        <v>3.09655046463013</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G374" t="n">
-        <v>3.09654974937439</v>
+        <v>3.09655046463013</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G376" t="n">
-        <v>3.06683325767517</v>
+        <v>3.06683301925659</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G380" t="n">
-        <v>3.0430588722229</v>
+        <v>3.04305911064148</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>4.98799991607666</v>
       </c>
       <c r="G381" t="n">
-        <v>2.9646053314209</v>
+        <v>2.96460485458374</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G382" t="n">
-        <v>2.81720733642578</v>
+        <v>2.81720662117004</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G384" t="n">
-        <v>2.7696590423584</v>
+        <v>2.76965928077698</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>4.71799993515015</v>
       </c>
       <c r="G385" t="n">
-        <v>2.80413150787354</v>
+        <v>2.80413126945496</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G386" t="n">
-        <v>2.78748965263367</v>
+        <v>2.78748989105225</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>4.68400001525879</v>
       </c>
       <c r="G387" t="n">
-        <v>2.78392338752747</v>
+        <v>2.78392314910889</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G388" t="n">
-        <v>2.858811378479</v>
+        <v>2.85881114006042</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>4.71400022506714</v>
       </c>
       <c r="G389" t="n">
-        <v>2.80175423622131</v>
+        <v>2.80175399780273</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G390" t="n">
-        <v>2.8053195476532</v>
+        <v>2.80532002449036</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>4.59600019454956</v>
       </c>
       <c r="G391" t="n">
-        <v>2.7316210269928</v>
+        <v>2.73162078857422</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>4.43400001525879</v>
       </c>
       <c r="G393" t="n">
-        <v>2.63533663749695</v>
+        <v>2.63533687591553</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G395" t="n">
-        <v>2.57946801185608</v>
+        <v>2.57946825027466</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G397" t="n">
-        <v>2.63295888900757</v>
+        <v>2.63295912742615</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>4.49599981307983</v>
       </c>
       <c r="G398" t="n">
-        <v>2.67218589782715</v>
+        <v>2.67218613624573</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G399" t="n">
-        <v>2.70428109169006</v>
+        <v>2.70428085327148</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G400" t="n">
-        <v>2.70428109169006</v>
+        <v>2.70428085327148</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G403" t="n">
-        <v>2.68645071983337</v>
+        <v>2.68645048141479</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>4.73600006103516</v>
       </c>
       <c r="G404" t="n">
-        <v>2.81482934951782</v>
+        <v>2.81482982635498</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>4.61399984359741</v>
       </c>
       <c r="G405" t="n">
-        <v>2.74231910705566</v>
+        <v>2.74231934547424</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>4.61199998855591</v>
       </c>
       <c r="G406" t="n">
-        <v>2.74113011360168</v>
+        <v>2.74113059043884</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G407" t="n">
-        <v>2.73994207382202</v>
+        <v>2.73994183540344</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>4.57600021362305</v>
       </c>
       <c r="G409" t="n">
-        <v>2.71973395347595</v>
+        <v>2.71973419189453</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>4.57600021362305</v>
       </c>
       <c r="G410" t="n">
-        <v>2.71973395347595</v>
+        <v>2.71973419189453</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G414" t="n">
-        <v>2.70428109169006</v>
+        <v>2.70428085327148</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>4.56599998474121</v>
       </c>
       <c r="G416" t="n">
-        <v>2.71379041671753</v>
+        <v>2.71379017829895</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>4.67199993133545</v>
       </c>
       <c r="G418" t="n">
-        <v>2.7767915725708</v>
+        <v>2.77679109573364</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G419" t="n">
-        <v>2.7280547618866</v>
+        <v>2.72805500030518</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G421" t="n">
-        <v>2.74588537216187</v>
+        <v>2.74588513374329</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>4.53599977493286</v>
       </c>
       <c r="G425" t="n">
-        <v>2.69596028327942</v>
+        <v>2.69595980644226</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>4.50799989700317</v>
       </c>
       <c r="G427" t="n">
-        <v>2.67931818962097</v>
+        <v>2.67931842803955</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>4.46199989318848</v>
       </c>
       <c r="G428" t="n">
-        <v>2.65197825431824</v>
+        <v>2.65197849273682</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>4.57399988174438</v>
       </c>
       <c r="G429" t="n">
-        <v>2.71854543685913</v>
+        <v>2.71854519844055</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>4.61800003051758</v>
       </c>
       <c r="G430" t="n">
-        <v>2.74469637870789</v>
+        <v>2.74469685554504</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>4.48199987411499</v>
       </c>
       <c r="G433" t="n">
-        <v>2.66386461257935</v>
+        <v>2.66386532783508</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>4.50400018692017</v>
       </c>
       <c r="G435" t="n">
-        <v>2.67694115638733</v>
+        <v>2.67694091796875</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>4.49599981307983</v>
       </c>
       <c r="G436" t="n">
-        <v>2.67218589782715</v>
+        <v>2.67218613624573</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>4.45599985122681</v>
       </c>
       <c r="G437" t="n">
-        <v>2.64841246604919</v>
+        <v>2.64841198921204</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>4.57800006866455</v>
       </c>
       <c r="G439" t="n">
-        <v>2.72092294692993</v>
+        <v>2.72092270851135</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>4.72800016403198</v>
       </c>
       <c r="G440" t="n">
-        <v>2.81007504463196</v>
+        <v>2.8100745677948</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>4.90199995040894</v>
       </c>
       <c r="G442" t="n">
-        <v>2.91349124908447</v>
+        <v>2.91349172592163</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G443" t="n">
-        <v>2.95390701293945</v>
+        <v>2.95390677452087</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>4.85599994659424</v>
       </c>
       <c r="G444" t="n">
-        <v>2.88615155220032</v>
+        <v>2.88615131378174</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>4.78399991989136</v>
       </c>
       <c r="G445" t="n">
-        <v>2.84335827827454</v>
+        <v>2.84335875511169</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>4.78399991989136</v>
       </c>
       <c r="G446" t="n">
-        <v>2.84335827827454</v>
+        <v>2.84335875511169</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>4.73199987411499</v>
       </c>
       <c r="G447" t="n">
-        <v>2.8124520778656</v>
+        <v>2.81245183944702</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>4.76800012588501</v>
       </c>
       <c r="G448" t="n">
-        <v>2.83384871482849</v>
+        <v>2.83384895324707</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>4.81199979782104</v>
       </c>
       <c r="G449" t="n">
-        <v>2.8600001335144</v>
+        <v>2.86000037193298</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>4.77400016784668</v>
       </c>
       <c r="G450" t="n">
-        <v>2.83741521835327</v>
+        <v>2.83741474151611</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>4.87799978256226</v>
       </c>
       <c r="G455" t="n">
-        <v>2.89922690391541</v>
+        <v>2.89922666549683</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>4.92399978637695</v>
       </c>
       <c r="G456" t="n">
-        <v>2.92656707763672</v>
+        <v>2.92656683921814</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>4.92600011825562</v>
       </c>
       <c r="G457" t="n">
-        <v>2.92775559425354</v>
+        <v>2.92775583267212</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G458" t="n">
-        <v>3.00145506858826</v>
+        <v>3.00145483016968</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G459" t="n">
-        <v>3.03711557388306</v>
+        <v>3.03711581230164</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G460" t="n">
-        <v>3.0430588722229</v>
+        <v>3.04305911064148</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>5.02500009536743</v>
       </c>
       <c r="G461" t="n">
-        <v>2.98659610748291</v>
+        <v>2.98659586906433</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G462" t="n">
-        <v>3.01334166526794</v>
+        <v>3.01334190368652</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G464" t="n">
-        <v>3.0430588722229</v>
+        <v>3.04305911064148</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>4.98600006103516</v>
       </c>
       <c r="G465" t="n">
-        <v>2.9634165763855</v>
+        <v>2.96341681480408</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>5.11499977111816</v>
       </c>
       <c r="G466" t="n">
-        <v>3.04008650779724</v>
+        <v>3.0400869846344</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G471" t="n">
-        <v>3.16192889213562</v>
+        <v>3.16192841529846</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G472" t="n">
-        <v>3.21541953086853</v>
+        <v>3.21542000770569</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G475" t="n">
-        <v>3.15004181861877</v>
+        <v>3.15004205703735</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G476" t="n">
-        <v>3.13518285751343</v>
+        <v>3.13518309593201</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G477" t="n">
-        <v>3.15004181861877</v>
+        <v>3.15004205703735</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G478" t="n">
-        <v>3.09060645103455</v>
+        <v>3.09060716629028</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G479" t="n">
-        <v>3.07872009277344</v>
+        <v>3.07871985435486</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G481" t="n">
-        <v>3.14409852027893</v>
+        <v>3.14409828186035</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G482" t="n">
-        <v>3.15004181861877</v>
+        <v>3.15004205703735</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>5.30499982833862</v>
       </c>
       <c r="G483" t="n">
-        <v>3.15301299095154</v>
+        <v>3.1530134677887</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>5.34499979019165</v>
       </c>
       <c r="G485" t="n">
-        <v>3.17678713798523</v>
+        <v>3.17678737640381</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G488" t="n">
-        <v>3.191645860672</v>
+        <v>3.19164538383484</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G490" t="n">
-        <v>3.22730660438538</v>
+        <v>3.22730684280396</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>5.49499988555908</v>
       </c>
       <c r="G491" t="n">
-        <v>3.2659387588501</v>
+        <v>3.26593923568726</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G494" t="n">
-        <v>3.29862856864929</v>
+        <v>3.29862809181213</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G495" t="n">
-        <v>3.29862856864929</v>
+        <v>3.29862809181213</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>5.5</v>
       </c>
       <c r="G497" t="n">
-        <v>3.26891112327576</v>
+        <v>3.26891088485718</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>5.54500007629395</v>
       </c>
       <c r="G498" t="n">
-        <v>3.29565620422363</v>
+        <v>3.29565644264221</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>5.625</v>
       </c>
       <c r="G499" t="n">
-        <v>3.34320497512817</v>
+        <v>3.34320449829102</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>5.60500001907349</v>
       </c>
       <c r="G500" t="n">
-        <v>3.33131766319275</v>
+        <v>3.33131742477417</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>5.42500019073486</v>
       </c>
       <c r="G501" t="n">
-        <v>3.22433519363403</v>
+        <v>3.22433495521545</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>4.96500015258789</v>
       </c>
       <c r="G503" t="n">
-        <v>3.27646827697754</v>
+        <v>3.27646851539612</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G504" t="n">
-        <v>3.28306722640991</v>
+        <v>3.28306746482849</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G506" t="n">
-        <v>3.38535380363464</v>
+        <v>3.3853542804718</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G507" t="n">
-        <v>3.33256077766418</v>
+        <v>3.33256101608276</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G508" t="n">
-        <v>3.32596158981323</v>
+        <v>3.32596182823181</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G509" t="n">
-        <v>3.31936311721802</v>
+        <v>3.31936287879944</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G510" t="n">
-        <v>3.34575915336609</v>
+        <v>3.34575939178467</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G512" t="n">
-        <v>3.40515160560608</v>
+        <v>3.4051513671875</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G513" t="n">
-        <v>3.39195275306702</v>
+        <v>3.3919529914856</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G515" t="n">
-        <v>3.41175055503845</v>
+        <v>3.41175079345703</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G518" t="n">
-        <v>3.49093985557556</v>
+        <v>3.49094009399414</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G519" t="n">
-        <v>3.50413870811462</v>
+        <v>3.50413823127747</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G520" t="n">
-        <v>3.510737657547</v>
+        <v>3.51073718070984</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>5.25</v>
       </c>
       <c r="G522" t="n">
-        <v>3.46454405784607</v>
+        <v>3.46454334259033</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G523" t="n">
-        <v>3.43154740333557</v>
+        <v>3.43154811859131</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G524" t="n">
-        <v>3.39855217933655</v>
+        <v>3.39855241775513</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G525" t="n">
-        <v>3.38535380363464</v>
+        <v>3.3853542804718</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G527" t="n">
-        <v>3.33256077766418</v>
+        <v>3.33256101608276</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>5</v>
       </c>
       <c r="G530" t="n">
-        <v>3.29956555366516</v>
+        <v>3.29956531524658</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G531" t="n">
-        <v>3.28306722640991</v>
+        <v>3.28306746482849</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>4.9850001335144</v>
       </c>
       <c r="G532" t="n">
-        <v>3.28966665267944</v>
+        <v>3.28966689109802</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>4.9850001335144</v>
       </c>
       <c r="G533" t="n">
-        <v>3.28966665267944</v>
+        <v>3.28966689109802</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G537" t="n">
-        <v>3.147784948349</v>
+        <v>3.14778470993042</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G539" t="n">
-        <v>3.22037553787231</v>
+        <v>3.22037529945374</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G540" t="n">
-        <v>3.20387768745422</v>
+        <v>3.2038779258728</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>4.81500005722046</v>
       </c>
       <c r="G541" t="n">
-        <v>3.17748141288757</v>
+        <v>3.17748117446899</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G542" t="n">
-        <v>3.20387768745422</v>
+        <v>3.2038779258728</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>4.9850001335144</v>
       </c>
       <c r="G546" t="n">
-        <v>3.28966665267944</v>
+        <v>3.28966689109802</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G547" t="n">
-        <v>3.31936311721802</v>
+        <v>3.31936287879944</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G549" t="n">
-        <v>3.2863667011261</v>
+        <v>3.28636693954468</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G550" t="n">
-        <v>3.28306722640991</v>
+        <v>3.28306746482849</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>4.96500015258789</v>
       </c>
       <c r="G552" t="n">
-        <v>3.27646827697754</v>
+        <v>3.27646851539612</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G554" t="n">
-        <v>3.24017333984375</v>
+        <v>3.24017310142517</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G557" t="n">
-        <v>3.31936311721802</v>
+        <v>3.31936287879944</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G558" t="n">
-        <v>3.28306722640991</v>
+        <v>3.28306746482849</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G559" t="n">
-        <v>3.28306722640991</v>
+        <v>3.28306746482849</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G560" t="n">
-        <v>3.22037553787231</v>
+        <v>3.22037529945374</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G561" t="n">
-        <v>3.20717740058899</v>
+        <v>3.20717716217041</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G562" t="n">
-        <v>3.21377682685852</v>
+        <v>3.21377635002136</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G564" t="n">
-        <v>3.25997090339661</v>
+        <v>3.25997042655945</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>5</v>
       </c>
       <c r="G566" t="n">
-        <v>3.29956555366516</v>
+        <v>3.29956531524658</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G567" t="n">
-        <v>3.33256077766418</v>
+        <v>3.33256101608276</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G568" t="n">
-        <v>3.33915972709656</v>
+        <v>3.33915996551514</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G569" t="n">
-        <v>3.35235810279846</v>
+        <v>3.35235834121704</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G570" t="n">
-        <v>3.33256077766418</v>
+        <v>3.33256101608276</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G573" t="n">
-        <v>3.34575915336609</v>
+        <v>3.34575939178467</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G574" t="n">
-        <v>3.32596158981323</v>
+        <v>3.32596182823181</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G576" t="n">
-        <v>3.31936311721802</v>
+        <v>3.31936287879944</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>4.92500019073486</v>
       </c>
       <c r="G578" t="n">
-        <v>3.25007176399231</v>
+        <v>3.25007200241089</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G581" t="n">
-        <v>3.22037553787231</v>
+        <v>3.22037529945374</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G583" t="n">
-        <v>3.28306722640991</v>
+        <v>3.28306746482849</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>4.92500019073486</v>
       </c>
       <c r="G584" t="n">
-        <v>3.25007176399231</v>
+        <v>3.25007200241089</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G585" t="n">
-        <v>3.22697448730469</v>
+        <v>3.22697472572327</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>4.96500015258789</v>
       </c>
       <c r="G587" t="n">
-        <v>3.27646827697754</v>
+        <v>3.27646851539612</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G588" t="n">
-        <v>3.23027420043945</v>
+        <v>3.23027443885803</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G589" t="n">
-        <v>3.20387768745422</v>
+        <v>3.2038779258728</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>4.96500015258789</v>
       </c>
       <c r="G591" t="n">
-        <v>3.27646827697754</v>
+        <v>3.27646851539612</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G592" t="n">
-        <v>3.20717740058899</v>
+        <v>3.20717716217041</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G593" t="n">
-        <v>2.98610663414001</v>
+        <v>2.98610687255859</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G595" t="n">
-        <v>3.00920367240906</v>
+        <v>3.00920343399048</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G596" t="n">
-        <v>2.94321227073669</v>
+        <v>2.94321179389954</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>4.7350001335144</v>
       </c>
       <c r="G598" t="n">
-        <v>3.12468814849854</v>
+        <v>3.12468838691711</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G599" t="n">
-        <v>2.99930477142334</v>
+        <v>2.99930500984192</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G600" t="n">
-        <v>2.98940658569336</v>
+        <v>2.9894061088562</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G602" t="n">
-        <v>2.99930477142334</v>
+        <v>2.99930500984192</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G604" t="n">
-        <v>3.02240180969238</v>
+        <v>3.0224015712738</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G606" t="n">
-        <v>3.03230047225952</v>
+        <v>3.03230023384094</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G608" t="n">
-        <v>3.05539727210999</v>
+        <v>3.05539751052856</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G611" t="n">
-        <v>3.08839297294617</v>
+        <v>3.08839249610901</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>4.75</v>
       </c>
       <c r="G613" t="n">
-        <v>3.13458681106567</v>
+        <v>3.13458752632141</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G616" t="n">
-        <v>3.15768361091614</v>
+        <v>3.1576840877533</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G617" t="n">
-        <v>3.20717740058899</v>
+        <v>3.20717716217041</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G618" t="n">
-        <v>3.18737983703613</v>
+        <v>3.18737959861755</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G619" t="n">
-        <v>3.15438485145569</v>
+        <v>3.15438437461853</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>4.875</v>
       </c>
       <c r="G621" t="n">
-        <v>3.21707606315613</v>
+        <v>3.21707630157471</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>4.81500005722046</v>
       </c>
       <c r="G622" t="n">
-        <v>3.17748141288757</v>
+        <v>3.17748117446899</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G623" t="n">
-        <v>3.16758275032043</v>
+        <v>3.16758298873901</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G626" t="n">
-        <v>3.15768361091614</v>
+        <v>3.1576840877533</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G628" t="n">
-        <v>3.15768361091614</v>
+        <v>3.1576840877533</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>4.75500011444092</v>
       </c>
       <c r="G629" t="n">
-        <v>3.1378870010376</v>
+        <v>3.13788652420044</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G630" t="n">
-        <v>3.10159111022949</v>
+        <v>3.10159087181091</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G631" t="n">
-        <v>3.10819053649902</v>
+        <v>3.10819029808044</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>4.75</v>
       </c>
       <c r="G632" t="n">
-        <v>3.13458681106567</v>
+        <v>3.13458752632141</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G633" t="n">
-        <v>3.16758275032043</v>
+        <v>3.16758298873901</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>4.80499982833862</v>
       </c>
       <c r="G634" t="n">
-        <v>3.17088198661804</v>
+        <v>3.17088222503662</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G635" t="n">
-        <v>3.2005786895752</v>
+        <v>3.20057797431946</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>4.88500022888184</v>
       </c>
       <c r="G636" t="n">
-        <v>3.22367525100708</v>
+        <v>3.22367548942566</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G637" t="n">
-        <v>3.28306722640991</v>
+        <v>3.28306746482849</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G638" t="n">
-        <v>3.31936311721802</v>
+        <v>3.31936287879944</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G640" t="n">
-        <v>3.33915972709656</v>
+        <v>3.33915996551514</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>5.25</v>
       </c>
       <c r="G641" t="n">
-        <v>3.46454405784607</v>
+        <v>3.46454334259033</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G642" t="n">
-        <v>3.510737657547</v>
+        <v>3.51073718070984</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G643" t="n">
-        <v>3.48434090614319</v>
+        <v>3.48434066772461</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G644" t="n">
-        <v>3.55033230781555</v>
+        <v>3.55033254623413</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G645" t="n">
-        <v>3.54373288154602</v>
+        <v>3.54373240470886</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G646" t="n">
-        <v>3.53053450584412</v>
+        <v>3.5305347442627</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G648" t="n">
-        <v>3.59652590751648</v>
+        <v>3.59652614593506</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G649" t="n">
-        <v>3.61632299423218</v>
+        <v>3.61632394790649</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G650" t="n">
-        <v>3.58332753181458</v>
+        <v>3.58332777023315</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G651" t="n">
-        <v>3.58332753181458</v>
+        <v>3.58332777023315</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>5.5</v>
       </c>
       <c r="G656" t="n">
-        <v>3.62952208518982</v>
+        <v>3.62952136993408</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G657" t="n">
-        <v>3.53053450584412</v>
+        <v>3.5305347442627</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G658" t="n">
-        <v>3.48434090614319</v>
+        <v>3.48434066772461</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G659" t="n">
-        <v>3.53053450584412</v>
+        <v>3.5305347442627</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G660" t="n">
-        <v>3.53053450584412</v>
+        <v>3.5305347442627</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G663" t="n">
-        <v>3.51733660697937</v>
+        <v>3.51733636856079</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G665" t="n">
-        <v>3.44474577903748</v>
+        <v>3.44474649429321</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G667" t="n">
-        <v>3.53053450584412</v>
+        <v>3.5305347442627</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G673" t="n">
-        <v>3.54373288154602</v>
+        <v>3.54373240470886</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G674" t="n">
-        <v>3.53053450584412</v>
+        <v>3.5305347442627</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G675" t="n">
-        <v>3.53713393211365</v>
+        <v>3.53713440895081</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G676" t="n">
-        <v>3.55033230781555</v>
+        <v>3.55033254623413</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G678" t="n">
-        <v>3.51733660697937</v>
+        <v>3.51733636856079</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G679" t="n">
-        <v>3.49753904342651</v>
+        <v>3.49753952026367</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G680" t="n">
-        <v>3.54373288154602</v>
+        <v>3.54373240470886</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G681" t="n">
-        <v>3.53053450584412</v>
+        <v>3.5305347442627</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G682" t="n">
-        <v>3.510737657547</v>
+        <v>3.51073718070984</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G683" t="n">
-        <v>3.49093985557556</v>
+        <v>3.49094009399414</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G684" t="n">
-        <v>3.50413870811462</v>
+        <v>3.50413823127747</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G685" t="n">
-        <v>3.55033230781555</v>
+        <v>3.55033254623413</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G686" t="n">
-        <v>3.53053450584412</v>
+        <v>3.5305347442627</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G687" t="n">
-        <v>3.51733660697937</v>
+        <v>3.51733636856079</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G688" t="n">
-        <v>3.49753904342651</v>
+        <v>3.49753952026367</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G689" t="n">
-        <v>3.47774147987366</v>
+        <v>3.47774195671082</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G691" t="n">
-        <v>3.54373288154602</v>
+        <v>3.54373240470886</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G692" t="n">
-        <v>3.50413870811462</v>
+        <v>3.50413823127747</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G693" t="n">
-        <v>3.49753904342651</v>
+        <v>3.49753952026367</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G694" t="n">
-        <v>3.53053450584412</v>
+        <v>3.5305347442627</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G695" t="n">
-        <v>3.53713393211365</v>
+        <v>3.53713440895081</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G697" t="n">
-        <v>3.53053450584412</v>
+        <v>3.5305347442627</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G698" t="n">
-        <v>3.51733660697937</v>
+        <v>3.51733636856079</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G701" t="n">
-        <v>3.53713393211365</v>
+        <v>3.53713440895081</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G702" t="n">
-        <v>3.58992695808411</v>
+        <v>3.58992671966553</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>5.5</v>
       </c>
       <c r="G703" t="n">
-        <v>3.62952208518982</v>
+        <v>3.62952136993408</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G704" t="n">
-        <v>3.70871138572693</v>
+        <v>3.70871090888977</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G705" t="n">
-        <v>3.72850894927979</v>
+        <v>3.72850871086121</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G706" t="n">
-        <v>3.74170684814453</v>
+        <v>3.74170708656311</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>5.75</v>
       </c>
       <c r="G707" t="n">
-        <v>3.79449987411499</v>
+        <v>3.79450011253357</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>5.75</v>
       </c>
       <c r="G708" t="n">
-        <v>3.79449987411499</v>
+        <v>3.79450011253357</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G709" t="n">
-        <v>3.80769824981689</v>
+        <v>3.80769777297974</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G710" t="n">
-        <v>3.74830603599548</v>
+        <v>3.74830532073975</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G713" t="n">
-        <v>3.68891429901123</v>
+        <v>3.68891382217407</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G714" t="n">
-        <v>3.70871138572693</v>
+        <v>3.70871090888977</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G715" t="n">
-        <v>3.77470278739929</v>
+        <v>3.77470254898071</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G716" t="n">
-        <v>3.74830603599548</v>
+        <v>3.74830532073975</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G717" t="n">
-        <v>3.74830603599548</v>
+        <v>3.74830532073975</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G719" t="n">
-        <v>3.78130173683167</v>
+        <v>3.78130149841309</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G720" t="n">
-        <v>3.82749581336975</v>
+        <v>3.82749533653259</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G721" t="n">
-        <v>3.82749581336975</v>
+        <v>3.82749533653259</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G722" t="n">
-        <v>3.87368965148926</v>
+        <v>3.87368941307068</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G723" t="n">
-        <v>3.93308186531067</v>
+        <v>3.93308162689209</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G724" t="n">
-        <v>3.93308186531067</v>
+        <v>3.93308162689209</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G725" t="n">
-        <v>4.03866815567017</v>
+        <v>4.03866767883301</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G726" t="n">
-        <v>4.04526662826538</v>
+        <v>4.0452675819397</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G728" t="n">
-        <v>3.76150417327881</v>
+        <v>3.76150393486023</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G729" t="n">
-        <v>3.72190928459167</v>
+        <v>3.72190952301025</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G731" t="n">
-        <v>3.75490546226501</v>
+        <v>3.75490570068359</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G732" t="n">
-        <v>3.6493194103241</v>
+        <v>3.64931893348694</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G733" t="n">
-        <v>3.48434090614319</v>
+        <v>3.48434066772461</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G735" t="n">
-        <v>3.510737657547</v>
+        <v>3.51073718070984</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G736" t="n">
-        <v>3.47774147987366</v>
+        <v>3.47774195671082</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G737" t="n">
-        <v>3.28306722640991</v>
+        <v>3.28306746482849</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>4.58500003814697</v>
       </c>
       <c r="G739" t="n">
-        <v>3.02570080757141</v>
+        <v>3.02570128440857</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>4.17500019073486</v>
       </c>
       <c r="G741" t="n">
-        <v>2.7551372051239</v>
+        <v>2.75513696670532</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G742" t="n">
-        <v>2.90361762046814</v>
+        <v>2.90361738204956</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>4.07499980926514</v>
       </c>
       <c r="G745" t="n">
-        <v>2.68914556503296</v>
+        <v>2.68914532661438</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>4.27500009536743</v>
       </c>
       <c r="G746" t="n">
-        <v>2.82112836837769</v>
+        <v>2.82112812995911</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>4.56500005722046</v>
       </c>
       <c r="G748" t="n">
-        <v>3.01250290870667</v>
+        <v>3.01250314712524</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>4.75</v>
       </c>
       <c r="G749" t="n">
-        <v>3.13458681106567</v>
+        <v>3.13458752632141</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G752" t="n">
-        <v>3.16758275032043</v>
+        <v>3.16758298873901</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>4.43499994277954</v>
       </c>
       <c r="G753" t="n">
-        <v>2.92671465873718</v>
+        <v>2.9267144203186</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G756" t="n">
-        <v>3.04879832267761</v>
+        <v>3.04879808425903</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G758" t="n">
-        <v>3.10159111022949</v>
+        <v>3.10159087181091</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>5</v>
       </c>
       <c r="G759" t="n">
-        <v>3.29956555366516</v>
+        <v>3.29956531524658</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G760" t="n">
-        <v>3.33915972709656</v>
+        <v>3.33915996551514</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G762" t="n">
-        <v>3.25997090339661</v>
+        <v>3.25997042655945</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G764" t="n">
-        <v>3.10819053649902</v>
+        <v>3.10819029808044</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G765" t="n">
-        <v>3.08839297294617</v>
+        <v>3.08839249610901</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G770" t="n">
-        <v>3.10159111022949</v>
+        <v>3.10159087181091</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G771" t="n">
-        <v>3.15768361091614</v>
+        <v>3.1576840877533</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G772" t="n">
-        <v>3.24017333984375</v>
+        <v>3.24017310142517</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G773" t="n">
-        <v>3.24017333984375</v>
+        <v>3.24017310142517</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G777" t="n">
-        <v>3.06199645996094</v>
+        <v>3.06199622154236</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>4.75</v>
       </c>
       <c r="G781" t="n">
-        <v>3.13458681106567</v>
+        <v>3.13458752632141</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>4.84499979019165</v>
       </c>
       <c r="G783" t="n">
-        <v>3.19727873802185</v>
+        <v>3.19727826118469</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G784" t="n">
-        <v>3.22697448730469</v>
+        <v>3.22697472572327</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>4.92500019073486</v>
       </c>
       <c r="G788" t="n">
-        <v>3.25007176399231</v>
+        <v>3.25007200241089</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G790" t="n">
-        <v>3.33256077766418</v>
+        <v>3.33256101608276</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G791" t="n">
-        <v>3.41175055503845</v>
+        <v>3.41175079345703</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G792" t="n">
-        <v>3.44474577903748</v>
+        <v>3.44474649429321</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G793" t="n">
-        <v>3.41175055503845</v>
+        <v>3.41175079345703</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G796" t="n">
-        <v>3.35235810279846</v>
+        <v>3.35235834121704</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G799" t="n">
-        <v>3.40515160560608</v>
+        <v>3.4051513671875</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>5</v>
       </c>
       <c r="G801" t="n">
-        <v>3.29956555366516</v>
+        <v>3.29956531524658</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>5</v>
       </c>
       <c r="G802" t="n">
-        <v>3.29956555366516</v>
+        <v>3.29956531524658</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>4.79500007629395</v>
       </c>
       <c r="G803" t="n">
-        <v>3.16428303718567</v>
+        <v>3.16428279876709</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G805" t="n">
-        <v>3.10159111022949</v>
+        <v>3.10159087181091</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G806" t="n">
-        <v>3.16758275032043</v>
+        <v>3.16758298873901</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>4.7649998664856</v>
       </c>
       <c r="G810" t="n">
-        <v>3.14448547363281</v>
+        <v>3.14448595046997</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G811" t="n">
-        <v>3.21377682685852</v>
+        <v>3.21377635002136</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>4.7649998664856</v>
       </c>
       <c r="G813" t="n">
-        <v>3.14448547363281</v>
+        <v>3.14448595046997</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G816" t="n">
-        <v>3.33915972709656</v>
+        <v>3.33915996551514</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G817" t="n">
-        <v>3.33915972709656</v>
+        <v>3.33915996551514</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G818" t="n">
-        <v>3.41175055503845</v>
+        <v>3.41175079345703</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G819" t="n">
-        <v>3.4249484539032</v>
+        <v>3.42494869232178</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G820" t="n">
-        <v>3.39855217933655</v>
+        <v>3.39855241775513</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G822" t="n">
-        <v>3.38535380363464</v>
+        <v>3.3853542804718</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G823" t="n">
-        <v>3.39195275306702</v>
+        <v>3.3919529914856</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G824" t="n">
-        <v>3.39855217933655</v>
+        <v>3.39855241775513</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G825" t="n">
-        <v>3.31936311721802</v>
+        <v>3.31936287879944</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>4.92500019073486</v>
       </c>
       <c r="G826" t="n">
-        <v>3.25007176399231</v>
+        <v>3.25007200241089</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G828" t="n">
-        <v>3.32596158981323</v>
+        <v>3.32596182823181</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>5</v>
       </c>
       <c r="G831" t="n">
-        <v>3.29956555366516</v>
+        <v>3.29956531524658</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G832" t="n">
-        <v>3.33915972709656</v>
+        <v>3.33915996551514</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>5</v>
       </c>
       <c r="G833" t="n">
-        <v>3.29956555366516</v>
+        <v>3.29956531524658</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G835" t="n">
-        <v>3.22697448730469</v>
+        <v>3.22697472572327</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>4.88500022888184</v>
       </c>
       <c r="G836" t="n">
-        <v>3.22367525100708</v>
+        <v>3.22367548942566</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>4.81500005722046</v>
       </c>
       <c r="G839" t="n">
-        <v>3.17748141288757</v>
+        <v>3.17748117446899</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>4.80499982833862</v>
       </c>
       <c r="G840" t="n">
-        <v>3.17088198661804</v>
+        <v>3.17088222503662</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G843" t="n">
-        <v>3.16758275032043</v>
+        <v>3.16758298873901</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G844" t="n">
-        <v>3.16098356246948</v>
+        <v>3.16098308563232</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G845" t="n">
-        <v>3.16758275032043</v>
+        <v>3.16758298873901</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G846" t="n">
-        <v>3.147784948349</v>
+        <v>3.14778470993042</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>4.75500011444092</v>
       </c>
       <c r="G847" t="n">
-        <v>3.1378870010376</v>
+        <v>3.13788652420044</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G848" t="n">
-        <v>3.147784948349</v>
+        <v>3.14778470993042</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>4.75</v>
       </c>
       <c r="G849" t="n">
-        <v>3.13458681106567</v>
+        <v>3.13458752632141</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>4.68499994277954</v>
       </c>
       <c r="G850" t="n">
-        <v>3.09169292449951</v>
+        <v>3.09169268608093</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G853" t="n">
-        <v>3.02240180969238</v>
+        <v>3.0224015712738</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>4.64499998092651</v>
       </c>
       <c r="G854" t="n">
-        <v>3.06529593467712</v>
+        <v>3.06529641151428</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G855" t="n">
-        <v>3.06199645996094</v>
+        <v>3.06199622154236</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G856" t="n">
-        <v>3.05539727210999</v>
+        <v>3.05539751052856</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G857" t="n">
-        <v>3.05539727210999</v>
+        <v>3.05539751052856</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G861" t="n">
-        <v>3.03230047225952</v>
+        <v>3.03230023384094</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G863" t="n">
-        <v>3.00590372085571</v>
+        <v>3.00590395927429</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G864" t="n">
-        <v>2.98610663414001</v>
+        <v>2.98610687255859</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>4.58500003814697</v>
       </c>
       <c r="G865" t="n">
-        <v>3.02570080757141</v>
+        <v>3.02570128440857</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G869" t="n">
-        <v>3.05539727210999</v>
+        <v>3.05539751052856</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G870" t="n">
-        <v>3.06199645996094</v>
+        <v>3.06199622154236</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G871" t="n">
-        <v>3.05539727210999</v>
+        <v>3.05539751052856</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>4.7649998664856</v>
       </c>
       <c r="G873" t="n">
-        <v>3.14448547363281</v>
+        <v>3.14448595046997</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>4.75500011444092</v>
       </c>
       <c r="G876" t="n">
-        <v>3.1378870010376</v>
+        <v>3.13788652420044</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>4.7649998664856</v>
       </c>
       <c r="G877" t="n">
-        <v>3.14448547363281</v>
+        <v>3.14448595046997</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>4.7649998664856</v>
       </c>
       <c r="G878" t="n">
-        <v>3.14448547363281</v>
+        <v>3.14448595046997</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G879" t="n">
-        <v>3.16098356246948</v>
+        <v>3.16098308563232</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G880" t="n">
-        <v>3.15438485145569</v>
+        <v>3.15438437461853</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>4.80499982833862</v>
       </c>
       <c r="G882" t="n">
-        <v>3.17088198661804</v>
+        <v>3.17088222503662</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G883" t="n">
-        <v>3.16098356246948</v>
+        <v>3.16098308563232</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G884" t="n">
-        <v>3.20717740058899</v>
+        <v>3.20717716217041</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G885" t="n">
-        <v>3.22697448730469</v>
+        <v>3.22697472572327</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G886" t="n">
-        <v>3.33256077766418</v>
+        <v>3.33256101608276</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>4.84499979019165</v>
       </c>
       <c r="G888" t="n">
-        <v>3.19727873802185</v>
+        <v>3.19727826118469</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>4.81500005722046</v>
       </c>
       <c r="G890" t="n">
-        <v>3.17748141288757</v>
+        <v>3.17748117446899</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G891" t="n">
-        <v>3.08839297294617</v>
+        <v>3.08839249610901</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G893" t="n">
-        <v>2.94321227073669</v>
+        <v>2.94321179389954</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G894" t="n">
-        <v>2.94321227073669</v>
+        <v>2.94321179389954</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G895" t="n">
-        <v>2.91681551933289</v>
+        <v>2.91681575775146</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G896" t="n">
-        <v>2.90361762046814</v>
+        <v>2.90361738204956</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G897" t="n">
-        <v>2.8706214427948</v>
+        <v>2.87062168121338</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G898" t="n">
-        <v>2.84422516822815</v>
+        <v>2.84422492980957</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G899" t="n">
-        <v>2.81122970581055</v>
+        <v>2.81122994422913</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>4.16499996185303</v>
       </c>
       <c r="G900" t="n">
-        <v>2.74853777885437</v>
+        <v>2.74853754043579</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G901" t="n">
-        <v>2.75843620300293</v>
+        <v>2.75843644142151</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G903" t="n">
-        <v>2.61985468864441</v>
+        <v>2.61985492706299</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>3.95499992370605</v>
       </c>
       <c r="G904" t="n">
-        <v>2.60995626449585</v>
+        <v>2.60995578765869</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G906" t="n">
-        <v>2.5736608505249</v>
+        <v>2.57366108894348</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>4.02500009536743</v>
       </c>
       <c r="G907" t="n">
-        <v>2.65615010261536</v>
+        <v>2.65614986419678</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G909" t="n">
-        <v>2.78483319282532</v>
+        <v>2.78483295440674</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>4.31500005722046</v>
       </c>
       <c r="G910" t="n">
-        <v>2.84752464294434</v>
+        <v>2.84752488136292</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G911" t="n">
-        <v>2.96300911903381</v>
+        <v>2.96300935745239</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>4.36499977111816</v>
       </c>
       <c r="G914" t="n">
-        <v>2.88052034378052</v>
+        <v>2.8805205821991</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>4.5</v>
       </c>
       <c r="G915" t="n">
-        <v>2.96960854530334</v>
+        <v>2.96960878372192</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G916" t="n">
-        <v>3.00590372085571</v>
+        <v>3.00590395927429</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G917" t="n">
-        <v>3.05539727210999</v>
+        <v>3.05539751052856</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G919" t="n">
-        <v>3.03230047225952</v>
+        <v>3.03230023384094</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>4.64499998092651</v>
       </c>
       <c r="G920" t="n">
-        <v>3.06529593467712</v>
+        <v>3.06529641151428</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G922" t="n">
-        <v>3.147784948349</v>
+        <v>3.14778470993042</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>4.7649998664856</v>
       </c>
       <c r="G923" t="n">
-        <v>3.14448547363281</v>
+        <v>3.14448595046997</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G927" t="n">
-        <v>2.98610663414001</v>
+        <v>2.98610687255859</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G929" t="n">
-        <v>3.00590372085571</v>
+        <v>3.00590395927429</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>4.53499984741211</v>
       </c>
       <c r="G930" t="n">
-        <v>2.99270582199097</v>
+        <v>2.99270534515381</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G931" t="n">
-        <v>3.00920367240906</v>
+        <v>3.00920343399048</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G933" t="n">
-        <v>2.94981145858765</v>
+        <v>2.94981122016907</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>4.64499998092651</v>
       </c>
       <c r="G935" t="n">
-        <v>3.06529593467712</v>
+        <v>3.06529641151428</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G937" t="n">
-        <v>3.00590372085571</v>
+        <v>3.00590395927429</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G938" t="n">
-        <v>3.06199645996094</v>
+        <v>3.06199622154236</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>4.5</v>
       </c>
       <c r="G940" t="n">
-        <v>2.96960854530334</v>
+        <v>2.96960878372192</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G941" t="n">
-        <v>2.98940658569336</v>
+        <v>2.9894061088562</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G943" t="n">
-        <v>3.10819053649902</v>
+        <v>3.10819029808044</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G944" t="n">
-        <v>3.2005786895752</v>
+        <v>3.20057797431946</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G945" t="n">
-        <v>3.25997090339661</v>
+        <v>3.25997042655945</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G946" t="n">
-        <v>3.16098356246948</v>
+        <v>3.16098308563232</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>4.68499994277954</v>
       </c>
       <c r="G947" t="n">
-        <v>3.09169292449951</v>
+        <v>3.09169268608093</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>4.7350001335144</v>
       </c>
       <c r="G949" t="n">
-        <v>3.12468814849854</v>
+        <v>3.12468838691711</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G951" t="n">
-        <v>3.20387768745422</v>
+        <v>3.2038779258728</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G952" t="n">
-        <v>3.08839297294617</v>
+        <v>3.08839249610901</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>4.70499992370605</v>
       </c>
       <c r="G953" t="n">
-        <v>3.10489058494568</v>
+        <v>3.10489106178284</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G956" t="n">
-        <v>3.08839297294617</v>
+        <v>3.08839249610901</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G957" t="n">
-        <v>3.08839297294617</v>
+        <v>3.08839249610901</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>4.70499992370605</v>
       </c>
       <c r="G958" t="n">
-        <v>3.10489058494568</v>
+        <v>3.10489106178284</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G961" t="n">
-        <v>2.94981145858765</v>
+        <v>2.94981122016907</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G963" t="n">
-        <v>3.02240180969238</v>
+        <v>3.0224015712738</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G964" t="n">
-        <v>2.98610663414001</v>
+        <v>2.98610687255859</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G965" t="n">
-        <v>2.99930477142334</v>
+        <v>2.99930500984192</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G969" t="n">
-        <v>3.2005786895752</v>
+        <v>3.20057797431946</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G970" t="n">
-        <v>3.23027420043945</v>
+        <v>3.23027443885803</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G973" t="n">
-        <v>3.43154740333557</v>
+        <v>3.43154811859131</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G975" t="n">
-        <v>3.74830603599548</v>
+        <v>3.74830532073975</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G976" t="n">
-        <v>3.76150417327881</v>
+        <v>3.76150393486023</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G977" t="n">
-        <v>3.7153103351593</v>
+        <v>3.71531057357788</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G982" t="n">
-        <v>3.59652590751648</v>
+        <v>3.59652614593506</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G983" t="n">
-        <v>3.62292218208313</v>
+        <v>3.62292242050171</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G984" t="n">
-        <v>3.62292218208313</v>
+        <v>3.62292242050171</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G985" t="n">
-        <v>3.58992695808411</v>
+        <v>3.58992671966553</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G986" t="n">
-        <v>3.6823148727417</v>
+        <v>3.68231439590454</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G987" t="n">
-        <v>3.66911649703979</v>
+        <v>3.66911673545837</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G988" t="n">
-        <v>3.66911649703979</v>
+        <v>3.66911673545837</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G990" t="n">
-        <v>3.66911649703979</v>
+        <v>3.66911673545837</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G992" t="n">
-        <v>3.82089614868164</v>
+        <v>3.82089638710022</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G993" t="n">
-        <v>4.09146070480347</v>
+        <v>4.09146022796631</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G994" t="n">
-        <v>4.05186557769775</v>
+        <v>4.05186605453491</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G996" t="n">
-        <v>4.29603385925293</v>
+        <v>4.29603433609009</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>6.40999984741211</v>
       </c>
       <c r="G999" t="n">
-        <v>4.23004245758057</v>
+        <v>4.23004293441772</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>6.3899998664856</v>
       </c>
       <c r="G1001" t="n">
-        <v>4.21684408187866</v>
+        <v>4.21684455871582</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G1002" t="n">
-        <v>4.29603385925293</v>
+        <v>4.29603433609009</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G1003" t="n">
-        <v>4.26963758468628</v>
+        <v>4.26963710784912</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G1004" t="n">
-        <v>4.27623605728149</v>
+        <v>4.27623701095581</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>6.5</v>
       </c>
       <c r="G1005" t="n">
-        <v>4.2894344329834</v>
+        <v>4.28943538665771</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G1011" t="n">
-        <v>4.40026569366455</v>
+        <v>4.40026521682739</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G1012" t="n">
-        <v>4.31424522399902</v>
+        <v>4.31424474716187</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>6.77500009536743</v>
       </c>
       <c r="G1015" t="n">
-        <v>4.48297739028931</v>
+        <v>4.48297691345215</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G1016" t="n">
-        <v>4.51937007904053</v>
+        <v>4.51937055587769</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G1017" t="n">
-        <v>4.52598762512207</v>
+        <v>4.52598714828491</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>6.75</v>
       </c>
       <c r="G1020" t="n">
-        <v>4.46643447875977</v>
+        <v>4.46643495559692</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G1021" t="n">
-        <v>4.51937007904053</v>
+        <v>4.51937055587769</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>7.17500019073486</v>
       </c>
       <c r="G1023" t="n">
-        <v>4.7476544380188</v>
+        <v>4.74765491485596</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G1027" t="n">
-        <v>4.85683441162109</v>
+        <v>4.85683393478394</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G1030" t="n">
-        <v>4.87668514251709</v>
+        <v>4.87668466567993</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>7.55499982833862</v>
       </c>
       <c r="G1032" t="n">
-        <v>4.99909830093384</v>
+        <v>4.99909782409668</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1033" t="n">
-        <v>5.16121435165405</v>
+        <v>5.16121387481689</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>7.66499996185303</v>
       </c>
       <c r="G1034" t="n">
-        <v>5.07188415527344</v>
+        <v>5.0718846321106</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1035" t="n">
-        <v>4.87006807327271</v>
+        <v>4.87006855010986</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>7.30999994277954</v>
       </c>
       <c r="G1036" t="n">
-        <v>4.8369836807251</v>
+        <v>4.83698320388794</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>7.61499977111816</v>
       </c>
       <c r="G1037" t="n">
-        <v>5.03879976272583</v>
+        <v>5.03880023956299</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G1039" t="n">
-        <v>5.05534219741821</v>
+        <v>5.05534267425537</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>7.66499996185303</v>
       </c>
       <c r="G1040" t="n">
-        <v>5.07188415527344</v>
+        <v>5.0718846321106</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G1041" t="n">
-        <v>5.0619592666626</v>
+        <v>5.06195974349976</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G1042" t="n">
-        <v>5.10827827453613</v>
+        <v>5.10827779769897</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1043" t="n">
-        <v>5.06857633590698</v>
+        <v>5.06857585906982</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>7.71500015258789</v>
       </c>
       <c r="G1044" t="n">
-        <v>5.10496950149536</v>
+        <v>5.1049690246582</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G1046" t="n">
-        <v>5.05534219741821</v>
+        <v>5.05534267425537</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G1047" t="n">
-        <v>5.0619592666626</v>
+        <v>5.06195974349976</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>7.69500017166138</v>
       </c>
       <c r="G1048" t="n">
-        <v>5.09173583984375</v>
+        <v>5.09173536300659</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G1050" t="n">
-        <v>5.25385093688965</v>
+        <v>5.25385046005249</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1053" t="n">
-        <v>5.16121435165405</v>
+        <v>5.16121387481689</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G1054" t="n">
-        <v>5.17444801330566</v>
+        <v>5.17444753646851</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G1055" t="n">
-        <v>5.17444801330566</v>
+        <v>5.17444753646851</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>8.09000015258789</v>
       </c>
       <c r="G1056" t="n">
-        <v>5.35310459136963</v>
+        <v>5.35310506820679</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>8.13000011444092</v>
       </c>
       <c r="G1057" t="n">
-        <v>5.37957239151001</v>
+        <v>5.37957286834717</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G1060" t="n">
-        <v>5.38618993759155</v>
+        <v>5.38618946075439</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>8.65499973297119</v>
       </c>
       <c r="G1063" t="n">
-        <v>5.72696161270142</v>
+        <v>5.72696208953857</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>8.46500015258789</v>
       </c>
       <c r="G1064" t="n">
-        <v>5.6012396812439</v>
+        <v>5.60124015808105</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>8.52999973297119</v>
       </c>
       <c r="G1065" t="n">
-        <v>5.64425039291382</v>
+        <v>5.64424991607666</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>8.51500034332275</v>
       </c>
       <c r="G1066" t="n">
-        <v>5.63432502746582</v>
+        <v>5.63432455062866</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>8.45499992370605</v>
       </c>
       <c r="G1068" t="n">
-        <v>5.59462308883667</v>
+        <v>5.59462356567383</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>8.51500034332275</v>
       </c>
       <c r="G1070" t="n">
-        <v>5.63432502746582</v>
+        <v>5.63432455062866</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G1071" t="n">
-        <v>5.5913143157959</v>
+        <v>5.59131479263306</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>8.625</v>
       </c>
       <c r="G1072" t="n">
-        <v>5.70711135864258</v>
+        <v>5.70711088180542</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1073" t="n">
-        <v>5.69056844711304</v>
+        <v>5.6905689239502</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1074" t="n">
-        <v>5.69056844711304</v>
+        <v>5.6905689239502</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G1075" t="n">
-        <v>5.5780816078186</v>
+        <v>5.57808065414429</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G1076" t="n">
-        <v>5.52514553070068</v>
+        <v>5.52514505386353</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1077" t="n">
-        <v>5.50529336929321</v>
+        <v>5.50529384613037</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G1078" t="n">
-        <v>5.65086650848389</v>
+        <v>5.6508674621582</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1079" t="n">
-        <v>5.55822896957397</v>
+        <v>5.55822992324829</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G1080" t="n">
-        <v>5.5780816078186</v>
+        <v>5.57808065414429</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1081" t="n">
-        <v>5.65748357772827</v>
+        <v>5.65748405456543</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G1088" t="n">
-        <v>5.70380258560181</v>
+        <v>5.70380210876465</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G1089" t="n">
-        <v>5.81629037857056</v>
+        <v>5.81629085540771</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1090" t="n">
-        <v>5.8229079246521</v>
+        <v>5.82290744781494</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1092" t="n">
-        <v>5.88907718658447</v>
+        <v>5.88907670974731</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>8.80500030517578</v>
       </c>
       <c r="G1095" t="n">
-        <v>5.82621574401855</v>
+        <v>5.82621622085571</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G1096" t="n">
-        <v>5.83614063262939</v>
+        <v>5.83614158630371</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>8.05500030517578</v>
       </c>
       <c r="G1098" t="n">
-        <v>5.32994556427002</v>
+        <v>5.32994604110718</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>7.78499984741211</v>
       </c>
       <c r="G1101" t="n">
-        <v>5.15128755569458</v>
+        <v>5.15128803253174</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G1102" t="n">
-        <v>5.1942982673645</v>
+        <v>5.19429779052734</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>7.7649998664856</v>
       </c>
       <c r="G1103" t="n">
-        <v>5.13805389404297</v>
+        <v>5.13805437088013</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>7.79500007629395</v>
       </c>
       <c r="G1104" t="n">
-        <v>5.15790510177612</v>
+        <v>5.15790462493896</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G1105" t="n">
-        <v>5.0619592666626</v>
+        <v>5.06195974349976</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G1106" t="n">
-        <v>5.05534219741821</v>
+        <v>5.05534267425537</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>7.71500015258789</v>
       </c>
       <c r="G1107" t="n">
-        <v>5.10496950149536</v>
+        <v>5.1049690246582</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1112" t="n">
-        <v>5.22738265991211</v>
+        <v>5.22738218307495</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G1115" t="n">
-        <v>5.12151145935059</v>
+        <v>5.12151193618774</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>7.7649998664856</v>
       </c>
       <c r="G1116" t="n">
-        <v>5.13805389404297</v>
+        <v>5.13805437088013</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G1117" t="n">
-        <v>5.25385093688965</v>
+        <v>5.25385046005249</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>8.01500034332275</v>
       </c>
       <c r="G1119" t="n">
-        <v>5.30347728729248</v>
+        <v>5.30347776412964</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>7.91499996185303</v>
       </c>
       <c r="G1120" t="n">
-        <v>5.23730850219727</v>
+        <v>5.23730802536011</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>8.05500030517578</v>
       </c>
       <c r="G1122" t="n">
-        <v>5.32994556427002</v>
+        <v>5.32994604110718</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G1126" t="n">
-        <v>5.32002019882202</v>
+        <v>5.32001972198486</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G1127" t="n">
-        <v>5.3464879989624</v>
+        <v>5.34648752212524</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G1128" t="n">
-        <v>5.3464879989624</v>
+        <v>5.34648752212524</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>8.0649995803833</v>
       </c>
       <c r="G1130" t="n">
-        <v>5.33656215667725</v>
+        <v>5.33656167984009</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G1132" t="n">
-        <v>5.419273853302</v>
+        <v>5.41927433013916</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>8.04500007629395</v>
       </c>
       <c r="G1135" t="n">
-        <v>5.32332897186279</v>
+        <v>5.32332801818848</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>8.39500045776367</v>
       </c>
       <c r="G1137" t="n">
-        <v>5.55492162704468</v>
+        <v>5.55492210388184</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>8.57499980926514</v>
       </c>
       <c r="G1138" t="n">
-        <v>5.67402648925781</v>
+        <v>5.67402601242065</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1139" t="n">
-        <v>5.45235824584961</v>
+        <v>5.45235872268677</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G1140" t="n">
-        <v>5.44574117660522</v>
+        <v>5.44574165344238</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G1142" t="n">
-        <v>5.38618993759155</v>
+        <v>5.38618946075439</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>8.17500019073486</v>
       </c>
       <c r="G1143" t="n">
-        <v>5.409348487854</v>
+        <v>5.40934896469116</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>7.05499982833862</v>
       </c>
       <c r="G1144" t="n">
-        <v>5.24187612533569</v>
+        <v>5.24187660217285</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1151" t="n">
-        <v>5.79541254043579</v>
+        <v>5.79541301727295</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G1152" t="n">
-        <v>5.78798246383667</v>
+        <v>5.78798198699951</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G1153" t="n">
-        <v>5.81027317047119</v>
+        <v>5.81027269363403</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>7.7649998664856</v>
       </c>
       <c r="G1156" t="n">
-        <v>5.76940774917603</v>
+        <v>5.76940727233887</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G1157" t="n">
-        <v>5.74340295791626</v>
+        <v>5.74340152740479</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G1158" t="n">
-        <v>5.75083208084106</v>
+        <v>5.75083255767822</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1162" t="n">
-        <v>5.4982123374939</v>
+        <v>5.49821186065674</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>7.35500001907349</v>
       </c>
       <c r="G1164" t="n">
-        <v>5.46477699279785</v>
+        <v>5.46477651596069</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G1167" t="n">
-        <v>5.49078130722046</v>
+        <v>5.49078178405762</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>7.40999984741211</v>
       </c>
       <c r="G1169" t="n">
-        <v>5.5056414604187</v>
+        <v>5.50564193725586</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G1170" t="n">
-        <v>5.41648101806641</v>
+        <v>5.41648149490356</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G1174" t="n">
-        <v>5.14157104492188</v>
+        <v>5.14157152175903</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G1175" t="n">
-        <v>5.07470083236694</v>
+        <v>5.0747013092041</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>6.82499980926514</v>
       </c>
       <c r="G1176" t="n">
-        <v>5.07098579406738</v>
+        <v>5.07098531723022</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>6.91499996185303</v>
       </c>
       <c r="G1177" t="n">
-        <v>5.13785600662231</v>
+        <v>5.13785552978516</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1179" t="n">
-        <v>4.79979038238525</v>
+        <v>4.7997899055481</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1181" t="n">
-        <v>5.05241060256958</v>
+        <v>5.05241107940674</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>6.5</v>
       </c>
       <c r="G1183" t="n">
-        <v>4.82951021194458</v>
+        <v>4.82951068878174</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>6.63500022888184</v>
       </c>
       <c r="G1184" t="n">
-        <v>4.92981576919556</v>
+        <v>4.92981624603271</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>6.75</v>
       </c>
       <c r="G1185" t="n">
-        <v>5.01526069641113</v>
+        <v>5.01526117324829</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>6.57000017166138</v>
       </c>
       <c r="G1186" t="n">
-        <v>4.88152027130127</v>
+        <v>4.88152074813843</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>6.70499992370605</v>
       </c>
       <c r="G1187" t="n">
-        <v>4.98182535171509</v>
+        <v>4.9818263053894</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>6.61499977111816</v>
       </c>
       <c r="G1188" t="n">
-        <v>4.91495513916016</v>
+        <v>4.91495561599731</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>6.61499977111816</v>
       </c>
       <c r="G1189" t="n">
-        <v>4.91495513916016</v>
+        <v>4.91495561599731</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>6.66499996185303</v>
       </c>
       <c r="G1190" t="n">
-        <v>4.95210599899292</v>
+        <v>4.95210552215576</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G1191" t="n">
-        <v>4.97811079025269</v>
+        <v>4.97811031341553</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G1192" t="n">
-        <v>5.08956098556519</v>
+        <v>5.08956050872803</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>6.7350001335144</v>
       </c>
       <c r="G1194" t="n">
-        <v>5.00411605834961</v>
+        <v>5.00411558151245</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G1198" t="n">
-        <v>5.22330141067505</v>
+        <v>5.22330093383789</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>7.11499977111816</v>
       </c>
       <c r="G1199" t="n">
-        <v>5.2864556312561</v>
+        <v>5.28645658493042</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1200" t="n">
-        <v>5.27531147003174</v>
+        <v>5.2753119468689</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>7.14499998092651</v>
       </c>
       <c r="G1205" t="n">
-        <v>5.30874633789062</v>
+        <v>5.30874681472778</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1209" t="n">
-        <v>5.27531147003174</v>
+        <v>5.2753119468689</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>7.05499982833862</v>
       </c>
       <c r="G1210" t="n">
-        <v>5.24187612533569</v>
+        <v>5.24187660217285</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G1211" t="n">
-        <v>5.2455906867981</v>
+        <v>5.24559116363525</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G1214" t="n">
-        <v>5.22330141067505</v>
+        <v>5.22330093383789</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>6.5</v>
       </c>
       <c r="G1217" t="n">
-        <v>4.82951021194458</v>
+        <v>4.82951068878174</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>6.82499980926514</v>
       </c>
       <c r="G1220" t="n">
-        <v>5.07098579406738</v>
+        <v>5.07098531723022</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>6.81500005722046</v>
       </c>
       <c r="G1221" t="n">
-        <v>5.06355571746826</v>
+        <v>5.06355619430542</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G1222" t="n">
-        <v>5.03755140304565</v>
+        <v>5.0375509262085</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G1223" t="n">
-        <v>5.17872095108032</v>
+        <v>5.17872047424316</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G1226" t="n">
-        <v>5.03755140304565</v>
+        <v>5.0375509262085</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>6.76999998092651</v>
       </c>
       <c r="G1227" t="n">
-        <v>5.03012084960938</v>
+        <v>5.03012132644653</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G1229" t="n">
-        <v>5.21587133407593</v>
+        <v>5.21587085723877</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G1231" t="n">
-        <v>5.7062520980835</v>
+        <v>5.70625257492065</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>7.45499992370605</v>
       </c>
       <c r="G1232" t="n">
-        <v>5.53907680511475</v>
+        <v>5.5390772819519</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>7.67500019073486</v>
       </c>
       <c r="G1233" t="n">
-        <v>5.70253753662109</v>
+        <v>5.70253705978394</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G1236" t="n">
-        <v>5.57994222640991</v>
+        <v>5.57994270324707</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>7.25500011444092</v>
       </c>
       <c r="G1238" t="n">
-        <v>5.3904767036438</v>
+        <v>5.39047622680664</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G1242" t="n">
-        <v>4.79236030578613</v>
+        <v>4.79235982894897</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G1243" t="n">
-        <v>4.7254900932312</v>
+        <v>4.72549057006836</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>6.4850001335144</v>
       </c>
       <c r="G1244" t="n">
-        <v>4.81836605072021</v>
+        <v>4.81836557388306</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G1246" t="n">
-        <v>4.3688497543335</v>
+        <v>4.36884927749634</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G1252" t="n">
-        <v>4.71806001663208</v>
+        <v>4.71806049346924</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>6.4850001335144</v>
       </c>
       <c r="G1255" t="n">
-        <v>4.81836605072021</v>
+        <v>4.81836557388306</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1257" t="n">
-        <v>4.79979038238525</v>
+        <v>4.7997899055481</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>6.68499994277954</v>
       </c>
       <c r="G1262" t="n">
-        <v>4.966965675354</v>
+        <v>4.96696519851685</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>6.82499980926514</v>
       </c>
       <c r="G1263" t="n">
-        <v>5.07098579406738</v>
+        <v>5.07098531723022</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>6.82499980926514</v>
       </c>
       <c r="G1264" t="n">
-        <v>5.07098579406738</v>
+        <v>5.07098531723022</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>6.7350001335144</v>
       </c>
       <c r="G1265" t="n">
-        <v>5.00411605834961</v>
+        <v>5.00411558151245</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G1266" t="n">
-        <v>5.08213138580322</v>
+        <v>5.08213090896606</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G1272" t="n">
-        <v>5.15643167495728</v>
+        <v>5.15643119812012</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>6.15500020980835</v>
       </c>
       <c r="G1276" t="n">
-        <v>5.07072877883911</v>
+        <v>5.07072830200195</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G1278" t="n">
-        <v>5.00894021987915</v>
+        <v>5.00894069671631</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G1283" t="n">
-        <v>4.91831827163696</v>
+        <v>4.9183177947998</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G1285" t="n">
-        <v>4.95127201080322</v>
+        <v>4.95127248764038</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G1289" t="n">
-        <v>5.23961591720581</v>
+        <v>5.23961544036865</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>6.40999984741211</v>
       </c>
       <c r="G1292" t="n">
-        <v>5.28080701828003</v>
+        <v>5.28080749511719</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>7.34499979019165</v>
       </c>
       <c r="G1300" t="n">
-        <v>6.05109643936157</v>
+        <v>6.05109691619873</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G1302" t="n">
-        <v>5.99754762649536</v>
+        <v>5.9975471496582</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G1303" t="n">
-        <v>6.08816909790039</v>
+        <v>6.08816957473755</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>7.33500003814697</v>
       </c>
       <c r="G1304" t="n">
-        <v>6.0428581237793</v>
+        <v>6.04285860061646</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>7.21500015258789</v>
       </c>
       <c r="G1309" t="n">
-        <v>5.94399833679199</v>
+        <v>5.94399785995483</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1310" t="n">
-        <v>5.93164014816284</v>
+        <v>5.93163967132568</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1312" t="n">
-        <v>5.93164014816284</v>
+        <v>5.93163967132568</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G1313" t="n">
-        <v>5.83277893066406</v>
+        <v>5.83277940750122</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>6.86499977111816</v>
       </c>
       <c r="G1317" t="n">
-        <v>5.6556544303894</v>
+        <v>5.65565395355225</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>6.57499980926514</v>
       </c>
       <c r="G1319" t="n">
-        <v>5.41674089431763</v>
+        <v>5.41674041748047</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>6.48999977111816</v>
       </c>
       <c r="G1322" t="n">
-        <v>5.34671449661255</v>
+        <v>5.34671401977539</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>6.5149998664856</v>
       </c>
       <c r="G1323" t="n">
-        <v>5.36731052398682</v>
+        <v>5.36731004714966</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>6.63500022888184</v>
       </c>
       <c r="G1327" t="n">
-        <v>5.46617126464844</v>
+        <v>5.4661717414856</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>6.41499996185303</v>
       </c>
       <c r="G1328" t="n">
-        <v>5.2849268913269</v>
+        <v>5.28492641448975</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>6.25500011444092</v>
       </c>
       <c r="G1331" t="n">
-        <v>5.15311288833618</v>
+        <v>5.15311241149902</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>6.30999994277954</v>
       </c>
       <c r="G1332" t="n">
-        <v>5.19842338562012</v>
+        <v>5.19842290878296</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>6.43499994277954</v>
       </c>
       <c r="G1333" t="n">
-        <v>5.3014030456543</v>
+        <v>5.30140352249146</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>6.57000017166138</v>
       </c>
       <c r="G1334" t="n">
-        <v>5.41262197494507</v>
+        <v>5.41262245178223</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>6.16499996185303</v>
       </c>
       <c r="G1338" t="n">
-        <v>5.07896661758423</v>
+        <v>5.07896709442139</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G1339" t="n">
-        <v>5.04189348220825</v>
+        <v>5.04189395904541</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1340" t="n">
-        <v>5.12427806854248</v>
+        <v>5.12427759170532</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G1344" t="n">
-        <v>5.40438365936279</v>
+        <v>5.40438318252563</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>6.53000020980835</v>
       </c>
       <c r="G1345" t="n">
-        <v>5.37966871261597</v>
+        <v>5.37966823577881</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>6.63500022888184</v>
       </c>
       <c r="G1346" t="n">
-        <v>5.46617126464844</v>
+        <v>5.4661717414856</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>6.86499977111816</v>
       </c>
       <c r="G1350" t="n">
-        <v>5.6556544303894</v>
+        <v>5.65565395355225</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G1351" t="n">
-        <v>5.54443550109863</v>
+        <v>5.54443597793579</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G1353" t="n">
-        <v>5.85749483108521</v>
+        <v>5.85749435424805</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>6.86499977111816</v>
       </c>
       <c r="G1356" t="n">
-        <v>5.6556544303894</v>
+        <v>5.65565395355225</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G1358" t="n">
-        <v>5.72568035125732</v>
+        <v>5.72567987442017</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G1363" t="n">
-        <v>5.67624998092651</v>
+        <v>5.67625045776367</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1365" t="n">
-        <v>5.62401485443115</v>
+        <v>5.62401437759399</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>6.41499996185303</v>
       </c>
       <c r="G1366" t="n">
-        <v>5.58483839035034</v>
+        <v>5.58483791351318</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G1367" t="n">
-        <v>5.54566192626953</v>
+        <v>5.54566097259521</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>6.34499979019165</v>
       </c>
       <c r="G1368" t="n">
-        <v>5.52389717102051</v>
+        <v>5.52389669418335</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>6.07499980926514</v>
       </c>
       <c r="G1376" t="n">
-        <v>5.28883695602417</v>
+        <v>5.28883743286133</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>7.03499984741211</v>
       </c>
       <c r="G1385" t="n">
-        <v>6.12460422515869</v>
+        <v>6.12460374832153</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>7.00500011444092</v>
       </c>
       <c r="G1387" t="n">
-        <v>6.09848690032959</v>
+        <v>6.09848642349243</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G1388" t="n">
-        <v>6.06801605224609</v>
+        <v>6.06801557540894</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>7.10500001907349</v>
       </c>
       <c r="G1389" t="n">
-        <v>6.18554544448853</v>
+        <v>6.18554592132568</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G1390" t="n">
-        <v>6.12025117874146</v>
+        <v>6.12025165557861</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G1391" t="n">
-        <v>5.8242506980896</v>
+        <v>5.82425117492676</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>7</v>
       </c>
       <c r="G1397" t="n">
-        <v>6.09413385391235</v>
+        <v>6.0941333770752</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G1398" t="n">
-        <v>5.98966312408447</v>
+        <v>5.98966264724731</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G1399" t="n">
-        <v>5.88519239425659</v>
+        <v>5.88519191741943</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G1404" t="n">
-        <v>6.12025117874146</v>
+        <v>6.12025165557861</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36899,7 +36899,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G1405" t="n">
-        <v>6.06801605224609</v>
+        <v>6.06801557540894</v>
       </c>
       <c r="H1405" t="s">
         <v>8</v>
@@ -36951,7 +36951,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G1407" t="n">
-        <v>6.11154556274414</v>
+        <v>6.11154508590698</v>
       </c>
       <c r="H1407" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G1408" t="n">
-        <v>6.13766384124756</v>
+        <v>6.13766288757324</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>7.17500019073486</v>
       </c>
       <c r="G1410" t="n">
-        <v>6.24648714065552</v>
+        <v>6.24648761749268</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>7.19500017166138</v>
       </c>
       <c r="G1417" t="n">
-        <v>6.2638988494873</v>
+        <v>6.26389932632446</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37263,7 +37263,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1419" t="n">
-        <v>6.44237041473389</v>
+        <v>6.44236993789673</v>
       </c>
       <c r="H1419" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>7.20499992370605</v>
       </c>
       <c r="G1420" t="n">
-        <v>6.27260446548462</v>
+        <v>6.27260494232178</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37315,7 +37315,7 @@
         <v>7.17500019073486</v>
       </c>
       <c r="G1421" t="n">
-        <v>6.24648714065552</v>
+        <v>6.24648761749268</v>
       </c>
       <c r="H1421" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>6.90999984741211</v>
       </c>
       <c r="G1423" t="n">
-        <v>6.01578092575073</v>
+        <v>6.01578044891357</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>7.16499996185303</v>
       </c>
       <c r="G1427" t="n">
-        <v>6.23778104782104</v>
+        <v>6.2377815246582</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>7.2649998664856</v>
       </c>
       <c r="G1430" t="n">
-        <v>6.32483959197998</v>
+        <v>6.3248405456543</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1432" t="n">
-        <v>6.44237041473389</v>
+        <v>6.44236993789673</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>7.45499992370605</v>
       </c>
       <c r="G1434" t="n">
-        <v>6.49025201797485</v>
+        <v>6.49025249481201</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G1435" t="n">
-        <v>6.47719383239746</v>
+        <v>6.4771933555603</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G1436" t="n">
-        <v>6.49460554122925</v>
+        <v>6.49460506439209</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G1438" t="n">
-        <v>6.49460554122925</v>
+        <v>6.49460506439209</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>7.43499994277954</v>
       </c>
       <c r="G1439" t="n">
-        <v>6.47284030914307</v>
+        <v>6.47284078598022</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>7.31500005722046</v>
       </c>
       <c r="G1440" t="n">
-        <v>6.36836957931519</v>
+        <v>6.36837005615234</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G1442" t="n">
-        <v>6.28566312789917</v>
+        <v>6.28566360473633</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>7.32499980926514</v>
       </c>
       <c r="G1443" t="n">
-        <v>6.37707567214966</v>
+        <v>6.3770751953125</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G1445" t="n">
-        <v>6.47719383239746</v>
+        <v>6.4771933555603</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>7.20499992370605</v>
       </c>
       <c r="G1447" t="n">
-        <v>6.27260446548462</v>
+        <v>6.27260494232178</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>7.41499996185303</v>
       </c>
       <c r="G1450" t="n">
-        <v>6.45542907714844</v>
+        <v>6.45542860031128</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G1451" t="n">
-        <v>6.47719383239746</v>
+        <v>6.4771933555603</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G1452" t="n">
-        <v>6.49460554122925</v>
+        <v>6.49460506439209</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G1453" t="n">
-        <v>6.49460554122925</v>
+        <v>6.49460506439209</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>7.40500020980835</v>
       </c>
       <c r="G1454" t="n">
-        <v>6.44672250747681</v>
+        <v>6.44672298431396</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>7.43499994277954</v>
       </c>
       <c r="G1456" t="n">
-        <v>6.47284030914307</v>
+        <v>6.47284078598022</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>7.45499992370605</v>
       </c>
       <c r="G1458" t="n">
-        <v>6.49025201797485</v>
+        <v>6.49025249481201</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G1465" t="n">
-        <v>7.25201940536499</v>
+        <v>7.25201892852783</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1466" t="n">
-        <v>7.31295967102051</v>
+        <v>7.31296014785767</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G1467" t="n">
-        <v>7.33037233352661</v>
+        <v>7.33037281036377</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>8.42500019073486</v>
       </c>
       <c r="G1468" t="n">
-        <v>7.33472537994385</v>
+        <v>7.33472585678101</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>8.44499969482422</v>
       </c>
       <c r="G1469" t="n">
-        <v>7.35213756561279</v>
+        <v>7.35213661193848</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1470" t="n">
-        <v>7.44354867935181</v>
+        <v>7.44354915618896</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>8.50500011444092</v>
       </c>
       <c r="G1471" t="n">
-        <v>7.404372215271</v>
+        <v>7.40437269210815</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38641,7 +38641,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G1472" t="n">
-        <v>7.45225524902344</v>
+        <v>7.45225477218628</v>
       </c>
       <c r="H1472" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G1473" t="n">
-        <v>7.53931427001953</v>
+        <v>7.53931379318237</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G1474" t="n">
-        <v>7.35648918151855</v>
+        <v>7.35649013519287</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1475" t="n">
-        <v>7.17366600036621</v>
+        <v>7.17366552352905</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38745,7 +38745,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G1476" t="n">
-        <v>7.27813625335693</v>
+        <v>7.27813673019409</v>
       </c>
       <c r="H1476" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>8.48499965667725</v>
       </c>
       <c r="G1479" t="n">
-        <v>7.38696050643921</v>
+        <v>7.38696098327637</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38875,7 +38875,7 @@
         <v>8.6899995803833</v>
       </c>
       <c r="G1481" t="n">
-        <v>7.56543111801147</v>
+        <v>7.56543159484863</v>
       </c>
       <c r="H1481" t="s">
         <v>8</v>
@@ -38979,7 +38979,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G1485" t="n">
-        <v>7.53931427001953</v>
+        <v>7.53931379318237</v>
       </c>
       <c r="H1485" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>8.89000034332275</v>
       </c>
       <c r="G1486" t="n">
-        <v>7.73955011367798</v>
+        <v>7.73954963684082</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G1487" t="n">
-        <v>7.88755035400391</v>
+        <v>7.88755083084106</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>9.41499996185303</v>
       </c>
       <c r="G1488" t="n">
-        <v>8.19661045074463</v>
+        <v>8.19660949707031</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G1489" t="n">
-        <v>8.35766887664795</v>
+        <v>8.35766983032227</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39161,7 +39161,7 @@
         <v>9.71500015258789</v>
       </c>
       <c r="G1492" t="n">
-        <v>8.45778656005859</v>
+        <v>8.45778751373291</v>
       </c>
       <c r="H1492" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G1493" t="n">
-        <v>8.32284641265869</v>
+        <v>8.32284545898438</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G1494" t="n">
-        <v>8.34896373748779</v>
+        <v>8.34896278381348</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G1495" t="n">
-        <v>8.35766887664795</v>
+        <v>8.35766983032227</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G1496" t="n">
-        <v>8.35766887664795</v>
+        <v>8.35766983032227</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1497" t="n">
-        <v>8.21837425231934</v>
+        <v>8.21837520599365</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G1498" t="n">
-        <v>8.25319766998291</v>
+        <v>8.25319862365723</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>9.52499961853027</v>
       </c>
       <c r="G1502" t="n">
-        <v>8.29237365722656</v>
+        <v>8.29237461090088</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39473,7 +39473,7 @@
         <v>9.45499992370605</v>
       </c>
       <c r="G1504" t="n">
-        <v>8.23143291473389</v>
+        <v>8.2314338684082</v>
       </c>
       <c r="H1504" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G1505" t="n">
-        <v>8.29672718048096</v>
+        <v>8.29672813415527</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>9.4350004196167</v>
       </c>
       <c r="G1506" t="n">
-        <v>8.21402168273926</v>
+        <v>8.21402263641357</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39551,7 +39551,7 @@
         <v>9.34500026702881</v>
       </c>
       <c r="G1507" t="n">
-        <v>8.13566875457764</v>
+        <v>8.13566970825195</v>
       </c>
       <c r="H1507" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G1508" t="n">
-        <v>7.90496158599854</v>
+        <v>7.90496206283569</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>9.33500003814697</v>
       </c>
       <c r="G1509" t="n">
-        <v>8.12696266174316</v>
+        <v>8.12696361541748</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39629,7 +39629,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G1510" t="n">
-        <v>7.85272645950317</v>
+        <v>7.85272741317749</v>
       </c>
       <c r="H1510" t="s">
         <v>8</v>
@@ -39655,7 +39655,7 @@
         <v>9.05500030517578</v>
       </c>
       <c r="G1511" t="n">
-        <v>7.88319683074951</v>
+        <v>7.88319730758667</v>
       </c>
       <c r="H1511" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>9.10499954223633</v>
       </c>
       <c r="G1513" t="n">
-        <v>7.92672634124756</v>
+        <v>7.92672681808472</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>9.45499992370605</v>
       </c>
       <c r="G1514" t="n">
-        <v>8.23143291473389</v>
+        <v>8.2314338684082</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39811,7 +39811,7 @@
         <v>9.13000011444092</v>
       </c>
       <c r="G1517" t="n">
-        <v>7.9484920501709</v>
+        <v>7.94849157333374</v>
       </c>
       <c r="H1517" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>9.00500011444092</v>
       </c>
       <c r="G1519" t="n">
-        <v>7.83966827392578</v>
+        <v>7.83966875076294</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>9.0649995803833</v>
       </c>
       <c r="G1520" t="n">
-        <v>7.89190244674683</v>
+        <v>7.89190340042114</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G1521" t="n">
-        <v>8.00072765350342</v>
+        <v>8.00072574615479</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>9.15499973297119</v>
       </c>
       <c r="G1523" t="n">
-        <v>7.97025585174561</v>
+        <v>7.97025632858276</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>8.98999977111816</v>
       </c>
       <c r="G1524" t="n">
-        <v>7.82660818099976</v>
+        <v>7.82660913467407</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40149,7 +40149,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G1530" t="n">
-        <v>8.09649181365967</v>
+        <v>8.09649276733398</v>
       </c>
       <c r="H1530" t="s">
         <v>8</v>
@@ -40201,7 +40201,7 @@
         <v>9.47000026702881</v>
       </c>
       <c r="G1532" t="n">
-        <v>8.24449348449707</v>
+        <v>8.24449253082275</v>
       </c>
       <c r="H1532" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>9.41499996185303</v>
       </c>
       <c r="G1533" t="n">
-        <v>8.19661045074463</v>
+        <v>8.19660949707031</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40279,7 +40279,7 @@
         <v>9.0649995803833</v>
       </c>
       <c r="G1535" t="n">
-        <v>7.89190244674683</v>
+        <v>7.89190340042114</v>
       </c>
       <c r="H1535" t="s">
         <v>8</v>
@@ -62798,6 +62798,32 @@
         <v>2.94799995422363</v>
       </c>
       <c r="H2401" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2402">
+      <c r="A2402" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B2402" t="n">
+        <v>1054487</v>
+      </c>
+      <c r="C2402" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2402" t="n">
+        <v>2.93799996376038</v>
+      </c>
+      <c r="E2402" t="n">
+        <v>2.98000001907349</v>
+      </c>
+      <c r="F2402" t="n">
+        <v>2.94600009918213</v>
+      </c>
+      <c r="G2402" t="n">
+        <v>2.94600009918213</v>
+      </c>
+      <c r="H2402" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/BFF.MI.xlsx
+++ b/data/BFF.MI.xlsx
@@ -447,7 +447,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G3" t="n">
-        <v>2.3690812587738</v>
+        <v>2.36908078193665</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>4.25</v>
       </c>
       <c r="G4" t="n">
-        <v>2.31461977958679</v>
+        <v>2.31461930274963</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>4.29400014877319</v>
       </c>
       <c r="G5" t="n">
-        <v>2.33858251571655</v>
+        <v>2.33858275413513</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G6" t="n">
-        <v>2.26015782356262</v>
+        <v>2.2601580619812</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>4.06599998474121</v>
       </c>
       <c r="G7" t="n">
-        <v>2.21440982818604</v>
+        <v>2.21441006660461</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G9" t="n">
-        <v>2.26015782356262</v>
+        <v>2.2601580619812</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G11" t="n">
-        <v>2.26560378074646</v>
+        <v>2.26560401916504</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G12" t="n">
-        <v>2.28738856315613</v>
+        <v>2.28738880157471</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G13" t="n">
-        <v>2.34185028076172</v>
+        <v>2.34185004234314</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G15" t="n">
-        <v>2.36363530158997</v>
+        <v>2.36363506317139</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>4.36199998855591</v>
       </c>
       <c r="G16" t="n">
-        <v>2.37561655044556</v>
+        <v>2.37561631202698</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G18" t="n">
-        <v>2.40720438957214</v>
+        <v>2.40720415115356</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>4.4520001411438</v>
       </c>
       <c r="G19" t="n">
-        <v>2.42463207244873</v>
+        <v>2.42463231086731</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>4.48600006103516</v>
       </c>
       <c r="G20" t="n">
-        <v>2.44314908981323</v>
+        <v>2.44314932823181</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G21" t="n">
-        <v>2.54335832595825</v>
+        <v>2.54335880279541</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G22" t="n">
-        <v>2.5596969127655</v>
+        <v>2.55969667434692</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>4.85400009155273</v>
       </c>
       <c r="G24" t="n">
-        <v>2.64356756210327</v>
+        <v>2.64356780052185</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G25" t="n">
-        <v>2.5596969127655</v>
+        <v>2.55969667434692</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>4.73199987411499</v>
       </c>
       <c r="G29" t="n">
-        <v>2.57712483406067</v>
+        <v>2.57712459564209</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>4.74200010299683</v>
       </c>
       <c r="G30" t="n">
-        <v>2.58257055282593</v>
+        <v>2.58257079124451</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G34" t="n">
-        <v>2.66317415237427</v>
+        <v>2.66317367553711</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G35" t="n">
-        <v>2.68495845794678</v>
+        <v>2.68495869636536</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G37" t="n">
-        <v>2.68495845794678</v>
+        <v>2.68495869636536</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>4.94799995422363</v>
       </c>
       <c r="G38" t="n">
-        <v>2.69476222991943</v>
+        <v>2.69476175308228</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>4.86800003051758</v>
       </c>
       <c r="G40" t="n">
-        <v>2.6511926651001</v>
+        <v>2.65119242668152</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G42" t="n">
-        <v>2.65772795677185</v>
+        <v>2.65772771835327</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G43" t="n">
-        <v>2.66862034797668</v>
+        <v>2.66862010955811</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>4.87599992752075</v>
       </c>
       <c r="G44" t="n">
-        <v>2.65554928779602</v>
+        <v>2.65554904937744</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>4.84600019454956</v>
       </c>
       <c r="G45" t="n">
-        <v>2.63921117782593</v>
+        <v>2.63921093940735</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>4.89599990844727</v>
       </c>
       <c r="G46" t="n">
-        <v>2.66644191741943</v>
+        <v>2.66644167900085</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>5.06500005722046</v>
       </c>
       <c r="G47" t="n">
-        <v>2.75848197937012</v>
+        <v>2.75848150253296</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>5.07499980926514</v>
       </c>
       <c r="G48" t="n">
-        <v>2.76392793655396</v>
+        <v>2.76392841339111</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G49" t="n">
-        <v>2.72852778434753</v>
+        <v>2.72852826118469</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G50" t="n">
-        <v>2.77754306793213</v>
+        <v>2.77754330635071</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G52" t="n">
-        <v>2.82111287117004</v>
+        <v>2.82111263275146</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G53" t="n">
-        <v>2.80749726295471</v>
+        <v>2.80749773979187</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G57" t="n">
-        <v>2.84289717674255</v>
+        <v>2.84289741516113</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>5.09499979019165</v>
       </c>
       <c r="G60" t="n">
-        <v>2.77482008934021</v>
+        <v>2.77482032775879</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G61" t="n">
-        <v>2.7993278503418</v>
+        <v>2.79932761192322</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G62" t="n">
-        <v>2.7829897403717</v>
+        <v>2.78298950195312</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G63" t="n">
-        <v>2.7993278503418</v>
+        <v>2.79932761192322</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>5.16499996185303</v>
       </c>
       <c r="G64" t="n">
-        <v>2.81294345855713</v>
+        <v>2.81294322013855</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>5.07499980926514</v>
       </c>
       <c r="G66" t="n">
-        <v>2.76392793655396</v>
+        <v>2.76392841339111</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>5.125</v>
       </c>
       <c r="G67" t="n">
-        <v>2.79115891456604</v>
+        <v>2.79115867614746</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G69" t="n">
-        <v>2.78843545913696</v>
+        <v>2.78843569755554</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G70" t="n">
-        <v>2.80477452278137</v>
+        <v>2.80477476119995</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>5.07499980926514</v>
       </c>
       <c r="G71" t="n">
-        <v>2.76392793655396</v>
+        <v>2.76392841339111</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G74" t="n">
-        <v>2.78843545913696</v>
+        <v>2.78843569755554</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G75" t="n">
-        <v>2.80477452278137</v>
+        <v>2.80477476119995</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>5.125</v>
       </c>
       <c r="G76" t="n">
-        <v>2.79115891456604</v>
+        <v>2.79115867614746</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>5.17500019073486</v>
       </c>
       <c r="G77" t="n">
-        <v>2.81838989257812</v>
+        <v>2.81838965415955</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G78" t="n">
-        <v>2.78843545913696</v>
+        <v>2.78843569755554</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G79" t="n">
-        <v>2.82655930519104</v>
+        <v>2.8265585899353</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G80" t="n">
-        <v>2.82111287117004</v>
+        <v>2.82111263275146</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G81" t="n">
-        <v>2.80477452278137</v>
+        <v>2.80477476119995</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G82" t="n">
-        <v>2.80477452278137</v>
+        <v>2.80477476119995</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G83" t="n">
-        <v>2.80477452278137</v>
+        <v>2.80477476119995</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G84" t="n">
-        <v>2.7993278503418</v>
+        <v>2.79932761192322</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G85" t="n">
-        <v>2.80749726295471</v>
+        <v>2.80749773979187</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G86" t="n">
-        <v>2.80477452278137</v>
+        <v>2.80477476119995</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>5.13500022888184</v>
       </c>
       <c r="G88" t="n">
-        <v>2.79660487174988</v>
+        <v>2.79660511016846</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>5.08500003814697</v>
       </c>
       <c r="G89" t="n">
-        <v>2.76937460899353</v>
+        <v>2.76937389373779</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G91" t="n">
-        <v>2.83745121955872</v>
+        <v>2.83745098114014</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G93" t="n">
-        <v>2.80749726295471</v>
+        <v>2.80749773979187</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G94" t="n">
-        <v>2.80749726295471</v>
+        <v>2.80749773979187</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G95" t="n">
-        <v>2.7993278503418</v>
+        <v>2.79932761192322</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>5.16499996185303</v>
       </c>
       <c r="G96" t="n">
-        <v>2.81294345855713</v>
+        <v>2.81294322013855</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G98" t="n">
-        <v>2.7993278503418</v>
+        <v>2.79932761192322</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>5.11499977111816</v>
       </c>
       <c r="G99" t="n">
-        <v>2.78571224212646</v>
+        <v>2.78571248054504</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>4.9520001411438</v>
       </c>
       <c r="G100" t="n">
-        <v>2.69694018363953</v>
+        <v>2.69694042205811</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G101" t="n">
-        <v>2.69585084915161</v>
+        <v>2.69585061073303</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>4.99200010299683</v>
       </c>
       <c r="G102" t="n">
-        <v>2.71872496604919</v>
+        <v>2.71872448921204</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G103" t="n">
-        <v>2.73942017555237</v>
+        <v>2.73942065238953</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G105" t="n">
-        <v>2.77754306793213</v>
+        <v>2.77754330635071</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>5.08500003814697</v>
       </c>
       <c r="G107" t="n">
-        <v>2.76937460899353</v>
+        <v>2.76937389373779</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G108" t="n">
-        <v>2.76665091514587</v>
+        <v>2.76665115356445</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G109" t="n">
-        <v>2.78843545913696</v>
+        <v>2.78843569755554</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>5.16499996185303</v>
       </c>
       <c r="G110" t="n">
-        <v>2.81294345855713</v>
+        <v>2.81294322013855</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G111" t="n">
-        <v>2.84834384918213</v>
+        <v>2.84834361076355</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G112" t="n">
-        <v>2.88102078437805</v>
+        <v>2.88102054595947</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>5.50500011444092</v>
       </c>
       <c r="G114" t="n">
-        <v>2.99811291694641</v>
+        <v>2.99811339378357</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>5.49499988555908</v>
       </c>
       <c r="G115" t="n">
-        <v>2.99266719818115</v>
+        <v>2.99266695976257</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G116" t="n">
-        <v>3.02806711196899</v>
+        <v>3.02806663513184</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G119" t="n">
-        <v>3.08797478675842</v>
+        <v>3.087975025177</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G121" t="n">
-        <v>3.24046683311462</v>
+        <v>3.24046730995178</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G124" t="n">
-        <v>3.19689798355103</v>
+        <v>3.19689774513245</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G126" t="n">
-        <v>3.07708263397217</v>
+        <v>3.07708239555359</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G127" t="n">
-        <v>3.14243602752686</v>
+        <v>3.14243650436401</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G128" t="n">
-        <v>3.10431337356567</v>
+        <v>3.10431289672852</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>5.72499990463257</v>
       </c>
       <c r="G129" t="n">
-        <v>3.11792826652527</v>
+        <v>3.11792802810669</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G130" t="n">
-        <v>3.15877509117126</v>
+        <v>3.15877461433411</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G131" t="n">
-        <v>3.20234441757202</v>
+        <v>3.2023446559906</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>6.125</v>
       </c>
       <c r="G134" t="n">
-        <v>3.33577537536621</v>
+        <v>3.33577513694763</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G135" t="n">
-        <v>3.30582141876221</v>
+        <v>3.30582165718079</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>6.04500007629395</v>
       </c>
       <c r="G137" t="n">
-        <v>3.29220628738403</v>
+        <v>3.29220533370972</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>6</v>
       </c>
       <c r="G138" t="n">
-        <v>3.26769828796387</v>
+        <v>3.26769804954529</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G140" t="n">
-        <v>3.33305215835571</v>
+        <v>3.33305191993713</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G142" t="n">
-        <v>3.34939074516296</v>
+        <v>3.34939098358154</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G143" t="n">
-        <v>3.39296007156372</v>
+        <v>3.39295983314514</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G144" t="n">
-        <v>3.38751339912415</v>
+        <v>3.38751363754272</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>6.25</v>
       </c>
       <c r="G145" t="n">
-        <v>3.40385246276855</v>
+        <v>3.4038519859314</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G146" t="n">
-        <v>3.38206768035889</v>
+        <v>3.38206720352173</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>6.02500009536743</v>
       </c>
       <c r="G148" t="n">
-        <v>3.28131341934204</v>
+        <v>3.28131365776062</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>6.09499979019165</v>
       </c>
       <c r="G150" t="n">
-        <v>3.31943655014038</v>
+        <v>3.3194363117218</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G151" t="n">
-        <v>3.28403687477112</v>
+        <v>3.28403663635254</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G153" t="n">
-        <v>3.2459135055542</v>
+        <v>3.24591326713562</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G156" t="n">
-        <v>3.27314472198486</v>
+        <v>3.27314448356628</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>6</v>
       </c>
       <c r="G157" t="n">
-        <v>3.26769828796387</v>
+        <v>3.26769804954529</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>6.125</v>
       </c>
       <c r="G159" t="n">
-        <v>3.33577537536621</v>
+        <v>3.33577513694763</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G161" t="n">
-        <v>3.38206768035889</v>
+        <v>3.38206720352173</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>6.40999984741211</v>
       </c>
       <c r="G162" t="n">
-        <v>3.49099063873291</v>
+        <v>3.49099087715149</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G163" t="n">
-        <v>3.512775182724</v>
+        <v>3.51277589797974</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G164" t="n">
-        <v>3.47465229034424</v>
+        <v>3.4746527671814</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G165" t="n">
-        <v>3.45831370353699</v>
+        <v>3.45831418037415</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>6.45499992370605</v>
       </c>
       <c r="G167" t="n">
-        <v>3.5154983997345</v>
+        <v>3.51549887657166</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>6.36499977111816</v>
       </c>
       <c r="G168" t="n">
-        <v>3.46648287773132</v>
+        <v>3.46648263931274</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>6.40999984741211</v>
       </c>
       <c r="G171" t="n">
-        <v>3.49099063873291</v>
+        <v>3.49099087715149</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G172" t="n">
-        <v>3.58357548713684</v>
+        <v>3.58357572555542</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G173" t="n">
-        <v>3.56179070472717</v>
+        <v>3.56179046630859</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>6.58500003814697</v>
       </c>
       <c r="G174" t="n">
-        <v>3.58629870414734</v>
+        <v>3.58629846572876</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G175" t="n">
-        <v>3.59446740150452</v>
+        <v>3.59446787834167</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>6.53000020980835</v>
       </c>
       <c r="G176" t="n">
-        <v>3.55634498596191</v>
+        <v>3.55634450912476</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>6.53499984741211</v>
       </c>
       <c r="G178" t="n">
-        <v>3.55906748771667</v>
+        <v>3.55906796455383</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G180" t="n">
-        <v>3.61080646514893</v>
+        <v>3.61080694198608</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>6.375</v>
       </c>
       <c r="G181" t="n">
-        <v>3.47192859649658</v>
+        <v>3.47192883491516</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G182" t="n">
-        <v>3.47465229034424</v>
+        <v>3.4746527671814</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>6.25</v>
       </c>
       <c r="G183" t="n">
-        <v>3.40385246276855</v>
+        <v>3.4038519859314</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G184" t="n">
-        <v>3.44742155075073</v>
+        <v>3.44742107391357</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G186" t="n">
-        <v>3.48554491996765</v>
+        <v>3.48554444313049</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>6.53499984741211</v>
       </c>
       <c r="G188" t="n">
-        <v>3.55906748771667</v>
+        <v>3.55906796455383</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>6.5</v>
       </c>
       <c r="G189" t="n">
-        <v>3.54000639915466</v>
+        <v>3.54000616073608</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G190" t="n">
-        <v>3.54545259475708</v>
+        <v>3.54545307159424</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>6.5</v>
       </c>
       <c r="G191" t="n">
-        <v>3.54000639915466</v>
+        <v>3.54000616073608</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>6.43499994277954</v>
       </c>
       <c r="G192" t="n">
-        <v>3.50460648536682</v>
+        <v>3.50460624694824</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G193" t="n">
-        <v>3.56179070472717</v>
+        <v>3.56179046630859</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G194" t="n">
-        <v>3.47465229034424</v>
+        <v>3.4746527671814</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G196" t="n">
-        <v>3.52911424636841</v>
+        <v>3.52911448478699</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>6.5</v>
       </c>
       <c r="G197" t="n">
-        <v>3.54000639915466</v>
+        <v>3.54000616073608</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G198" t="n">
-        <v>3.54545259475708</v>
+        <v>3.54545307159424</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G199" t="n">
-        <v>3.54545259475708</v>
+        <v>3.54545307159424</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G200" t="n">
-        <v>3.54545259475708</v>
+        <v>3.54545307159424</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>6.57499980926514</v>
       </c>
       <c r="G201" t="n">
-        <v>3.58085250854492</v>
+        <v>3.58085203170776</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G202" t="n">
-        <v>3.58902192115784</v>
+        <v>3.58902144432068</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G203" t="n">
-        <v>3.59446740150452</v>
+        <v>3.59446787834167</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>6.53000020980835</v>
       </c>
       <c r="G204" t="n">
-        <v>3.55634498596191</v>
+        <v>3.55634450912476</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>6.59499979019165</v>
       </c>
       <c r="G205" t="n">
-        <v>3.59174513816833</v>
+        <v>3.5917444229126</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G206" t="n">
-        <v>3.59991455078125</v>
+        <v>3.59991383552551</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G207" t="n">
-        <v>3.54545259475708</v>
+        <v>3.54545307159424</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G211" t="n">
-        <v>3.28403687477112</v>
+        <v>3.28403663635254</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G214" t="n">
-        <v>3.12065148353577</v>
+        <v>3.12065124511719</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G216" t="n">
-        <v>3.1696674823761</v>
+        <v>3.16966724395752</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>5.81500005722046</v>
       </c>
       <c r="G217" t="n">
-        <v>3.16694402694702</v>
+        <v>3.1669442653656</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>5.93499994277954</v>
       </c>
       <c r="G218" t="n">
-        <v>3.23229765892029</v>
+        <v>3.23229813575745</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>6</v>
       </c>
       <c r="G219" t="n">
-        <v>3.26769828796387</v>
+        <v>3.26769804954529</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G220" t="n">
-        <v>3.38206768035889</v>
+        <v>3.38206720352173</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>6.14499998092651</v>
       </c>
       <c r="G221" t="n">
-        <v>3.34666800498962</v>
+        <v>3.34666776657104</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>6.16499996185303</v>
       </c>
       <c r="G222" t="n">
-        <v>3.35755968093872</v>
+        <v>3.3575599193573</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G224" t="n">
-        <v>3.18055987358093</v>
+        <v>3.18055963516235</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G225" t="n">
-        <v>3.1696674823761</v>
+        <v>3.16966724395752</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G226" t="n">
-        <v>3.1696674823761</v>
+        <v>3.16966724395752</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>5.81500005722046</v>
       </c>
       <c r="G227" t="n">
-        <v>3.16694402694702</v>
+        <v>3.1669442653656</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G228" t="n">
-        <v>3.18600535392761</v>
+        <v>3.18600559234619</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G229" t="n">
-        <v>3.18600535392761</v>
+        <v>3.18600559234619</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G230" t="n">
-        <v>3.17511343955994</v>
+        <v>3.17511296272278</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>5.78499984741211</v>
       </c>
       <c r="G231" t="n">
-        <v>3.15060544013977</v>
+        <v>3.15060567855835</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G232" t="n">
-        <v>3.15877509117126</v>
+        <v>3.15877461433411</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G233" t="n">
-        <v>3.15332865715027</v>
+        <v>3.15332841873169</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>5.88500022888184</v>
       </c>
       <c r="G234" t="n">
-        <v>3.20506739616394</v>
+        <v>3.20506715774536</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>5.95499992370605</v>
       </c>
       <c r="G235" t="n">
-        <v>3.24319005012512</v>
+        <v>3.2431902885437</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>6.04500007629395</v>
       </c>
       <c r="G236" t="n">
-        <v>3.29220628738403</v>
+        <v>3.29220533370972</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>5.95499992370605</v>
       </c>
       <c r="G237" t="n">
-        <v>3.24319005012512</v>
+        <v>3.2431902885437</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G238" t="n">
-        <v>3.24046683311462</v>
+        <v>3.24046730995178</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>5.88500022888184</v>
       </c>
       <c r="G239" t="n">
-        <v>3.20506739616394</v>
+        <v>3.20506715774536</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>5.88500022888184</v>
       </c>
       <c r="G241" t="n">
-        <v>3.20506739616394</v>
+        <v>3.20506715774536</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>5.7350001335144</v>
       </c>
       <c r="G243" t="n">
-        <v>3.12337470054626</v>
+        <v>3.12337517738342</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>5.71500015258789</v>
       </c>
       <c r="G244" t="n">
-        <v>3.11248254776001</v>
+        <v>3.11248278617859</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G245" t="n">
-        <v>3.08797478675842</v>
+        <v>3.087975025177</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G247" t="n">
-        <v>3.16422080993652</v>
+        <v>3.16422128677368</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G248" t="n">
-        <v>3.18600535392761</v>
+        <v>3.18600559234619</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G251" t="n">
-        <v>3.18600535392761</v>
+        <v>3.18600559234619</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G252" t="n">
-        <v>3.2077898979187</v>
+        <v>3.20779013633728</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G253" t="n">
-        <v>3.20234441757202</v>
+        <v>3.2023446559906</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>5.5</v>
       </c>
       <c r="G254" t="n">
-        <v>3.26891088485718</v>
+        <v>3.26891136169434</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>5.5</v>
       </c>
       <c r="G257" t="n">
-        <v>3.26891088485718</v>
+        <v>3.26891136169434</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G258" t="n">
-        <v>3.24513697624207</v>
+        <v>3.24513721466064</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G259" t="n">
-        <v>3.21542000770569</v>
+        <v>3.21541976928711</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G260" t="n">
-        <v>3.15598511695862</v>
+        <v>3.15598487854004</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G261" t="n">
-        <v>3.20947647094727</v>
+        <v>3.20947623252869</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>5.36499977111816</v>
       </c>
       <c r="G264" t="n">
-        <v>3.1886739730835</v>
+        <v>3.18867373466492</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>5.25500011444092</v>
       </c>
       <c r="G265" t="n">
-        <v>3.12329626083374</v>
+        <v>3.12329649925232</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G267" t="n">
-        <v>3.13815450668335</v>
+        <v>3.13815474510193</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G271" t="n">
-        <v>3.13815450668335</v>
+        <v>3.13815474510193</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>5.25500011444092</v>
       </c>
       <c r="G272" t="n">
-        <v>3.12329626083374</v>
+        <v>3.12329649925232</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G273" t="n">
-        <v>3.07871985435486</v>
+        <v>3.07872009277344</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G274" t="n">
-        <v>3.09655046463013</v>
+        <v>3.09655022621155</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G275" t="n">
-        <v>3.07277679443359</v>
+        <v>3.07277631759644</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>5.02500009536743</v>
       </c>
       <c r="G276" t="n">
-        <v>2.98659586906433</v>
+        <v>2.98659610748291</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>5.22499990463257</v>
       </c>
       <c r="G278" t="n">
-        <v>3.10546541213989</v>
+        <v>3.10546588897705</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>4.96600008010864</v>
       </c>
       <c r="G280" t="n">
-        <v>2.95152974128723</v>
+        <v>2.95152950286865</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G281" t="n">
-        <v>3.04305911064148</v>
+        <v>3.04305934906006</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G284" t="n">
-        <v>3.03414392471313</v>
+        <v>3.03414416313171</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>4.89200019836426</v>
       </c>
       <c r="G289" t="n">
-        <v>2.90754795074463</v>
+        <v>2.90754818916321</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G293" t="n">
-        <v>3.09060716629028</v>
+        <v>3.09060668945312</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G294" t="n">
-        <v>3.06683301925659</v>
+        <v>3.06683278083801</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G297" t="n">
-        <v>3.03711581230164</v>
+        <v>3.03711557388306</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G299" t="n">
-        <v>3.11438035964966</v>
+        <v>3.11438059806824</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G300" t="n">
-        <v>3.09060716629028</v>
+        <v>3.09060668945312</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>5.29500007629395</v>
       </c>
       <c r="G301" t="n">
-        <v>3.14706945419312</v>
+        <v>3.14706993103027</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G302" t="n">
-        <v>3.13221144676208</v>
+        <v>3.13221096992493</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G303" t="n">
-        <v>3.15598511695862</v>
+        <v>3.15598487854004</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G305" t="n">
-        <v>3.14409828186035</v>
+        <v>3.14409804344177</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>5.34499979019165</v>
       </c>
       <c r="G306" t="n">
-        <v>3.17678737640381</v>
+        <v>3.17678713798523</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>5.13500022888184</v>
       </c>
       <c r="G307" t="n">
-        <v>3.0519745349884</v>
+        <v>3.05197429656982</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G309" t="n">
-        <v>3.01334190368652</v>
+        <v>3.0133421421051</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>4.95599985122681</v>
       </c>
       <c r="G310" t="n">
-        <v>2.94558596611023</v>
+        <v>2.94558572769165</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>4.9539999961853</v>
       </c>
       <c r="G311" t="n">
-        <v>2.94439721107483</v>
+        <v>2.94439744949341</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>5</v>
       </c>
       <c r="G313" t="n">
-        <v>2.97173738479614</v>
+        <v>2.97173762321472</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>5.02500009536743</v>
       </c>
       <c r="G314" t="n">
-        <v>2.98659586906433</v>
+        <v>2.98659610748291</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>4.96199989318848</v>
       </c>
       <c r="G316" t="n">
-        <v>2.94915199279785</v>
+        <v>2.94915223121643</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G317" t="n">
-        <v>2.98956799507141</v>
+        <v>2.98956847190857</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G319" t="n">
-        <v>3.07277679443359</v>
+        <v>3.07277631759644</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G320" t="n">
-        <v>3.04305911064148</v>
+        <v>3.04305934906006</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G321" t="n">
-        <v>3.02522897720337</v>
+        <v>3.02522873878479</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>5.13500022888184</v>
       </c>
       <c r="G322" t="n">
-        <v>3.0519745349884</v>
+        <v>3.05197429656982</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G323" t="n">
-        <v>3.06683301925659</v>
+        <v>3.06683278083801</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G324" t="n">
-        <v>3.13815450668335</v>
+        <v>3.13815474510193</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G325" t="n">
-        <v>3.12626767158508</v>
+        <v>3.1262674331665</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G327" t="n">
-        <v>3.12626767158508</v>
+        <v>3.1262674331665</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G329" t="n">
-        <v>3.10843729972839</v>
+        <v>3.10843753814697</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G330" t="n">
-        <v>3.09060716629028</v>
+        <v>3.09060668945312</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G331" t="n">
-        <v>3.10843729972839</v>
+        <v>3.10843753814697</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>5.29500007629395</v>
       </c>
       <c r="G332" t="n">
-        <v>3.14706945419312</v>
+        <v>3.14706993103027</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G333" t="n">
-        <v>3.18570280075073</v>
+        <v>3.18570232391357</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>5.34499979019165</v>
       </c>
       <c r="G334" t="n">
-        <v>3.17678737640381</v>
+        <v>3.17678713798523</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>5.28499984741211</v>
       </c>
       <c r="G337" t="n">
-        <v>3.14112639427185</v>
+        <v>3.14112615585327</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>5.17500019073486</v>
       </c>
       <c r="G338" t="n">
-        <v>3.07574844360352</v>
+        <v>3.07574868202209</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G339" t="n">
-        <v>3.18570280075073</v>
+        <v>3.18570232391357</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G340" t="n">
-        <v>3.20947647094727</v>
+        <v>3.20947623252869</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>5.44500017166138</v>
       </c>
       <c r="G341" t="n">
-        <v>3.2362220287323</v>
+        <v>3.23622179031372</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G345" t="n">
-        <v>3.10249423980713</v>
+        <v>3.10249352455139</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G346" t="n">
-        <v>3.04900288581848</v>
+        <v>3.0490026473999</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G349" t="n">
-        <v>3.06683301925659</v>
+        <v>3.06683278083801</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>5.21500015258789</v>
       </c>
       <c r="G352" t="n">
-        <v>3.09952211380005</v>
+        <v>3.09952187538147</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>5.17500019073486</v>
       </c>
       <c r="G353" t="n">
-        <v>3.07574844360352</v>
+        <v>3.07574868202209</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>5.16499996185303</v>
       </c>
       <c r="G354" t="n">
-        <v>3.06980490684509</v>
+        <v>3.06980443000793</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G355" t="n">
-        <v>3.07277679443359</v>
+        <v>3.07277631759644</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G359" t="n">
-        <v>3.07277679443359</v>
+        <v>3.07277631759644</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>5.13500022888184</v>
       </c>
       <c r="G360" t="n">
-        <v>3.0519745349884</v>
+        <v>3.05197429656982</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>5.13500022888184</v>
       </c>
       <c r="G361" t="n">
-        <v>3.0519745349884</v>
+        <v>3.05197429656982</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G362" t="n">
-        <v>3.06683301925659</v>
+        <v>3.06683278083801</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>5.13500022888184</v>
       </c>
       <c r="G365" t="n">
-        <v>3.0519745349884</v>
+        <v>3.05197429656982</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G369" t="n">
-        <v>3.09060716629028</v>
+        <v>3.09060668945312</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G370" t="n">
-        <v>3.11438035964966</v>
+        <v>3.11438059806824</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G371" t="n">
-        <v>3.15598511695862</v>
+        <v>3.15598487854004</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G372" t="n">
-        <v>3.09655046463013</v>
+        <v>3.09655022621155</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G373" t="n">
-        <v>3.07277679443359</v>
+        <v>3.07277631759644</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G374" t="n">
-        <v>3.09655046463013</v>
+        <v>3.09655022621155</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>5.25500011444092</v>
       </c>
       <c r="G375" t="n">
-        <v>3.12329626083374</v>
+        <v>3.12329649925232</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G376" t="n">
-        <v>3.06683301925659</v>
+        <v>3.06683278083801</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G379" t="n">
-        <v>3.04900288581848</v>
+        <v>3.0490026473999</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G380" t="n">
-        <v>3.04305911064148</v>
+        <v>3.04305934906006</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>4.98799991607666</v>
       </c>
       <c r="G381" t="n">
-        <v>2.96460485458374</v>
+        <v>2.96460509300232</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G382" t="n">
-        <v>2.81720662117004</v>
+        <v>2.81720685958862</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G383" t="n">
-        <v>2.79937648773193</v>
+        <v>2.79937672615051</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G386" t="n">
-        <v>2.78748989105225</v>
+        <v>2.78748941421509</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>4.68400001525879</v>
       </c>
       <c r="G387" t="n">
-        <v>2.78392314910889</v>
+        <v>2.78392338752747</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G388" t="n">
-        <v>2.85881114006042</v>
+        <v>2.858811378479</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>4.71400022506714</v>
       </c>
       <c r="G389" t="n">
-        <v>2.80175399780273</v>
+        <v>2.80175423622131</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G390" t="n">
-        <v>2.80532002449036</v>
+        <v>2.80531978607178</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>4.59600019454956</v>
       </c>
       <c r="G391" t="n">
-        <v>2.73162078857422</v>
+        <v>2.7316210269928</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>4.58199977874756</v>
       </c>
       <c r="G392" t="n">
-        <v>2.723299741745</v>
+        <v>2.72329998016357</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>4.43400001525879</v>
       </c>
       <c r="G393" t="n">
-        <v>2.63533687591553</v>
+        <v>2.63533663749695</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>4.33599996566772</v>
       </c>
       <c r="G394" t="n">
-        <v>2.57709050178528</v>
+        <v>2.57709074020386</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>4.30600023269653</v>
       </c>
       <c r="G396" t="n">
-        <v>2.55926036834717</v>
+        <v>2.55926060676575</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>4.49599981307983</v>
       </c>
       <c r="G398" t="n">
-        <v>2.67218613624573</v>
+        <v>2.67218589782715</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G399" t="n">
-        <v>2.70428085327148</v>
+        <v>2.70428109169006</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G400" t="n">
-        <v>2.70428085327148</v>
+        <v>2.70428109169006</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>4.73600006103516</v>
       </c>
       <c r="G404" t="n">
-        <v>2.81482982635498</v>
+        <v>2.8148295879364</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>4.61199998855591</v>
       </c>
       <c r="G406" t="n">
-        <v>2.74113059043884</v>
+        <v>2.74113035202026</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G407" t="n">
-        <v>2.73994183540344</v>
+        <v>2.73994207382202</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>4.51599979400635</v>
       </c>
       <c r="G411" t="n">
-        <v>2.68407297134399</v>
+        <v>2.68407320976257</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>4.48799991607666</v>
       </c>
       <c r="G413" t="n">
-        <v>2.66743111610413</v>
+        <v>2.66743135452271</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G414" t="n">
-        <v>2.70428085327148</v>
+        <v>2.70428109169006</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>4.56599998474121</v>
       </c>
       <c r="G416" t="n">
-        <v>2.71379017829895</v>
+        <v>2.71379041671753</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G417" t="n">
-        <v>2.79343271255493</v>
+        <v>2.79343295097351</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>4.67199993133545</v>
       </c>
       <c r="G418" t="n">
-        <v>2.77679109573364</v>
+        <v>2.77679133415222</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G419" t="n">
-        <v>2.72805500030518</v>
+        <v>2.72805523872375</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>4.59800004959106</v>
       </c>
       <c r="G420" t="n">
-        <v>2.73280954360962</v>
+        <v>2.7328097820282</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G421" t="n">
-        <v>2.74588513374329</v>
+        <v>2.74588489532471</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>4.60400009155273</v>
       </c>
       <c r="G422" t="n">
-        <v>2.7363760471344</v>
+        <v>2.73637580871582</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>4.59800004959106</v>
       </c>
       <c r="G424" t="n">
-        <v>2.73280954360962</v>
+        <v>2.7328097820282</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>4.53599977493286</v>
       </c>
       <c r="G425" t="n">
-        <v>2.69595980644226</v>
+        <v>2.69596028327942</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>4.50799989700317</v>
       </c>
       <c r="G427" t="n">
-        <v>2.67931842803955</v>
+        <v>2.67931818962097</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>4.46199989318848</v>
       </c>
       <c r="G428" t="n">
-        <v>2.65197849273682</v>
+        <v>2.65197825431824</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>4.61800003051758</v>
       </c>
       <c r="G430" t="n">
-        <v>2.74469685554504</v>
+        <v>2.74469661712646</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>4.53399991989136</v>
       </c>
       <c r="G431" t="n">
-        <v>2.69477128982544</v>
+        <v>2.69477105140686</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G432" t="n">
-        <v>2.65673303604126</v>
+        <v>2.65673279762268</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>4.48199987411499</v>
       </c>
       <c r="G433" t="n">
-        <v>2.66386532783508</v>
+        <v>2.66386580467224</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>4.49599981307983</v>
       </c>
       <c r="G436" t="n">
-        <v>2.67218613624573</v>
+        <v>2.67218589782715</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>4.45599985122681</v>
       </c>
       <c r="G437" t="n">
-        <v>2.64841198921204</v>
+        <v>2.64841246604919</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>4.72800016403198</v>
       </c>
       <c r="G440" t="n">
-        <v>2.8100745677948</v>
+        <v>2.81007480621338</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>4.90199995040894</v>
       </c>
       <c r="G442" t="n">
-        <v>2.91349172592163</v>
+        <v>2.91349124908447</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G443" t="n">
-        <v>2.95390677452087</v>
+        <v>2.95390725135803</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>4.85599994659424</v>
       </c>
       <c r="G444" t="n">
-        <v>2.88615131378174</v>
+        <v>2.88615155220032</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>4.78399991989136</v>
       </c>
       <c r="G445" t="n">
-        <v>2.84335875511169</v>
+        <v>2.84335827827454</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>4.78399991989136</v>
       </c>
       <c r="G446" t="n">
-        <v>2.84335875511169</v>
+        <v>2.84335827827454</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>4.73199987411499</v>
       </c>
       <c r="G447" t="n">
-        <v>2.81245183944702</v>
+        <v>2.81245231628418</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>4.81199979782104</v>
       </c>
       <c r="G449" t="n">
-        <v>2.86000037193298</v>
+        <v>2.8600001335144</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>4.77400016784668</v>
       </c>
       <c r="G450" t="n">
-        <v>2.83741474151611</v>
+        <v>2.83741497993469</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G451" t="n">
-        <v>2.89447212219238</v>
+        <v>2.8944718837738</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>4.84600019454956</v>
       </c>
       <c r="G452" t="n">
-        <v>2.88020801544189</v>
+        <v>2.88020825386047</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>4.80399990081787</v>
       </c>
       <c r="G453" t="n">
-        <v>2.85524487495422</v>
+        <v>2.85524535179138</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>4.87799978256226</v>
       </c>
       <c r="G455" t="n">
-        <v>2.89922666549683</v>
+        <v>2.89922690391541</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>4.92399978637695</v>
       </c>
       <c r="G456" t="n">
-        <v>2.92656683921814</v>
+        <v>2.92656660079956</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G458" t="n">
-        <v>3.00145483016968</v>
+        <v>3.00145506858826</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G459" t="n">
-        <v>3.03711581230164</v>
+        <v>3.03711557388306</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G460" t="n">
-        <v>3.04305911064148</v>
+        <v>3.04305934906006</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>5.02500009536743</v>
       </c>
       <c r="G461" t="n">
-        <v>2.98659586906433</v>
+        <v>2.98659610748291</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G462" t="n">
-        <v>3.01334190368652</v>
+        <v>3.0133421421051</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G463" t="n">
-        <v>3.04900288581848</v>
+        <v>3.0490026473999</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G464" t="n">
-        <v>3.04305911064148</v>
+        <v>3.04305934906006</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>4.98600006103516</v>
       </c>
       <c r="G465" t="n">
-        <v>2.96341681480408</v>
+        <v>2.96341633796692</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G472" t="n">
-        <v>3.21542000770569</v>
+        <v>3.21541976928711</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G478" t="n">
-        <v>3.09060716629028</v>
+        <v>3.09060668945312</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G479" t="n">
-        <v>3.07871985435486</v>
+        <v>3.07872009277344</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>5.24499988555908</v>
       </c>
       <c r="G480" t="n">
-        <v>3.11735248565674</v>
+        <v>3.11735224723816</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G481" t="n">
-        <v>3.14409828186035</v>
+        <v>3.14409804344177</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>5.30499982833862</v>
       </c>
       <c r="G483" t="n">
-        <v>3.1530134677887</v>
+        <v>3.15301322937012</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G484" t="n">
-        <v>3.17381572723389</v>
+        <v>3.17381548881531</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>5.34499979019165</v>
       </c>
       <c r="G485" t="n">
-        <v>3.17678737640381</v>
+        <v>3.17678713798523</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G487" t="n">
-        <v>3.18570280075073</v>
+        <v>3.18570232391357</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G488" t="n">
-        <v>3.19164538383484</v>
+        <v>3.19164562225342</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G490" t="n">
-        <v>3.22730684280396</v>
+        <v>3.2273063659668</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>5.49499988555908</v>
       </c>
       <c r="G491" t="n">
-        <v>3.26593923568726</v>
+        <v>3.26593947410583</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>5.57499980926514</v>
       </c>
       <c r="G492" t="n">
-        <v>3.31348705291748</v>
+        <v>3.31348752975464</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G493" t="n">
-        <v>3.28079795837402</v>
+        <v>3.28079843521118</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G494" t="n">
-        <v>3.29862809181213</v>
+        <v>3.29862880706787</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G495" t="n">
-        <v>3.29862809181213</v>
+        <v>3.29862880706787</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G496" t="n">
-        <v>3.29268527030945</v>
+        <v>3.29268503189087</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>5.5</v>
       </c>
       <c r="G497" t="n">
-        <v>3.26891088485718</v>
+        <v>3.26891136169434</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>5.54500007629395</v>
       </c>
       <c r="G498" t="n">
-        <v>3.29565644264221</v>
+        <v>3.29565668106079</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>5.60500001907349</v>
       </c>
       <c r="G500" t="n">
-        <v>3.33131742477417</v>
+        <v>3.33131766319275</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>5.42500019073486</v>
       </c>
       <c r="G501" t="n">
-        <v>3.22433495521545</v>
+        <v>3.22433519363403</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>4.99499988555908</v>
       </c>
       <c r="G502" t="n">
-        <v>3.2962658405304</v>
+        <v>3.29626560211182</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G504" t="n">
-        <v>3.28306746482849</v>
+        <v>3.28306722640991</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G505" t="n">
-        <v>3.29296588897705</v>
+        <v>3.29296612739563</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G507" t="n">
-        <v>3.33256101608276</v>
+        <v>3.33256077766418</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G508" t="n">
-        <v>3.32596182823181</v>
+        <v>3.32596158981323</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G512" t="n">
-        <v>3.4051513671875</v>
+        <v>3.40515112876892</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G513" t="n">
-        <v>3.3919529914856</v>
+        <v>3.39195275306702</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G515" t="n">
-        <v>3.41175079345703</v>
+        <v>3.41175055503845</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G516" t="n">
-        <v>3.47114253044128</v>
+        <v>3.47114276885986</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G517" t="n">
-        <v>3.47114253044128</v>
+        <v>3.47114276885986</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G518" t="n">
-        <v>3.49094009399414</v>
+        <v>3.49093961715698</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G519" t="n">
-        <v>3.50413823127747</v>
+        <v>3.50413846969604</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G520" t="n">
-        <v>3.51073718070984</v>
+        <v>3.51073741912842</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G521" t="n">
-        <v>3.47114253044128</v>
+        <v>3.47114276885986</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>5.25</v>
       </c>
       <c r="G522" t="n">
-        <v>3.46454334259033</v>
+        <v>3.46454381942749</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G523" t="n">
-        <v>3.43154811859131</v>
+        <v>3.43154788017273</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G524" t="n">
-        <v>3.39855241775513</v>
+        <v>3.39855194091797</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G526" t="n">
-        <v>3.35895776748657</v>
+        <v>3.35895729064941</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G527" t="n">
-        <v>3.33256101608276</v>
+        <v>3.33256077766418</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G529" t="n">
-        <v>3.27976775169373</v>
+        <v>3.27976751327515</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G531" t="n">
-        <v>3.28306746482849</v>
+        <v>3.28306722640991</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>4.9850001335144</v>
       </c>
       <c r="G532" t="n">
-        <v>3.28966689109802</v>
+        <v>3.28966641426086</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>4.9850001335144</v>
       </c>
       <c r="G533" t="n">
-        <v>3.28966689109802</v>
+        <v>3.28966641426086</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G534" t="n">
-        <v>3.27316880226135</v>
+        <v>3.27316832542419</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G535" t="n">
-        <v>3.30616450309753</v>
+        <v>3.30616402626038</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G536" t="n">
-        <v>3.26656937599182</v>
+        <v>3.26656985282898</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G537" t="n">
-        <v>3.14778470993042</v>
+        <v>3.14778542518616</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G539" t="n">
-        <v>3.22037529945374</v>
+        <v>3.22037577629089</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>4.81500005722046</v>
       </c>
       <c r="G541" t="n">
-        <v>3.17748117446899</v>
+        <v>3.17748141288757</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>4.74499988555908</v>
       </c>
       <c r="G544" t="n">
-        <v>3.13128709793091</v>
+        <v>3.13128733634949</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G545" t="n">
-        <v>3.29296588897705</v>
+        <v>3.29296612739563</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>4.9850001335144</v>
       </c>
       <c r="G546" t="n">
-        <v>3.28966689109802</v>
+        <v>3.28966641426086</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G548" t="n">
-        <v>3.26656937599182</v>
+        <v>3.26656985282898</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G549" t="n">
-        <v>3.28636693954468</v>
+        <v>3.28636717796326</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G550" t="n">
-        <v>3.28306746482849</v>
+        <v>3.28306722640991</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>4.93499994277954</v>
       </c>
       <c r="G553" t="n">
-        <v>3.25667071342468</v>
+        <v>3.25667095184326</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G556" t="n">
-        <v>3.29296588897705</v>
+        <v>3.29296612739563</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G558" t="n">
-        <v>3.28306746482849</v>
+        <v>3.28306722640991</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G559" t="n">
-        <v>3.28306746482849</v>
+        <v>3.28306722640991</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G560" t="n">
-        <v>3.22037529945374</v>
+        <v>3.22037577629089</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G561" t="n">
-        <v>3.20717716217041</v>
+        <v>3.20717763900757</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G563" t="n">
-        <v>3.23357367515564</v>
+        <v>3.2335741519928</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G567" t="n">
-        <v>3.33256101608276</v>
+        <v>3.33256077766418</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G570" t="n">
-        <v>3.33256101608276</v>
+        <v>3.33256077766418</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G571" t="n">
-        <v>3.35895776748657</v>
+        <v>3.35895729064941</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G574" t="n">
-        <v>3.32596182823181</v>
+        <v>3.32596158981323</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>4.99499988555908</v>
       </c>
       <c r="G575" t="n">
-        <v>3.2962658405304</v>
+        <v>3.29626560211182</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>4.99499988555908</v>
       </c>
       <c r="G577" t="n">
-        <v>3.2962658405304</v>
+        <v>3.29626560211182</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>4.92500019073486</v>
       </c>
       <c r="G578" t="n">
-        <v>3.25007200241089</v>
+        <v>3.25007176399231</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G580" t="n">
-        <v>3.23357367515564</v>
+        <v>3.2335741519928</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G581" t="n">
-        <v>3.22037529945374</v>
+        <v>3.22037577629089</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G583" t="n">
-        <v>3.28306746482849</v>
+        <v>3.28306722640991</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>4.92500019073486</v>
       </c>
       <c r="G584" t="n">
-        <v>3.25007200241089</v>
+        <v>3.25007176399231</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G585" t="n">
-        <v>3.22697472572327</v>
+        <v>3.22697448730469</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G586" t="n">
-        <v>3.23357367515564</v>
+        <v>3.2335741519928</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G588" t="n">
-        <v>3.23027443885803</v>
+        <v>3.23027467727661</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G590" t="n">
-        <v>3.27316880226135</v>
+        <v>3.27316832542419</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G592" t="n">
-        <v>3.20717716217041</v>
+        <v>3.20717763900757</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G593" t="n">
-        <v>2.98610687255859</v>
+        <v>2.98610663414001</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G596" t="n">
-        <v>2.94321179389954</v>
+        <v>2.94321227073669</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G597" t="n">
-        <v>3.03560018539429</v>
+        <v>3.03559970855713</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G599" t="n">
-        <v>2.99930500984192</v>
+        <v>2.99930453300476</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G601" t="n">
-        <v>3.03560018539429</v>
+        <v>3.03559970855713</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G602" t="n">
-        <v>2.99930500984192</v>
+        <v>2.99930453300476</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G603" t="n">
-        <v>3.00260424613953</v>
+        <v>3.00260472297668</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G605" t="n">
-        <v>3.01580262184143</v>
+        <v>3.01580238342285</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G607" t="n">
-        <v>3.04219913482666</v>
+        <v>3.04219937324524</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G611" t="n">
-        <v>3.08839249610901</v>
+        <v>3.08839297294617</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>4.75</v>
       </c>
       <c r="G613" t="n">
-        <v>3.13458752632141</v>
+        <v>3.13458681106567</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G614" t="n">
-        <v>3.17418146133423</v>
+        <v>3.17418169975281</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G615" t="n">
-        <v>3.17418146133423</v>
+        <v>3.17418169975281</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G617" t="n">
-        <v>3.20717716217041</v>
+        <v>3.20717763900757</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G618" t="n">
-        <v>3.18737959861755</v>
+        <v>3.18737983703613</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>4.875</v>
       </c>
       <c r="G621" t="n">
-        <v>3.21707630157471</v>
+        <v>3.21707606315613</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>4.81500005722046</v>
       </c>
       <c r="G622" t="n">
-        <v>3.17748117446899</v>
+        <v>3.17748141288757</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>4.74499988555908</v>
       </c>
       <c r="G625" t="n">
-        <v>3.13128709793091</v>
+        <v>3.13128733634949</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G627" t="n">
-        <v>3.17418146133423</v>
+        <v>3.17418169975281</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G630" t="n">
-        <v>3.10159087181091</v>
+        <v>3.10159134864807</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G631" t="n">
-        <v>3.10819029808044</v>
+        <v>3.10819053649902</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>4.75</v>
       </c>
       <c r="G632" t="n">
-        <v>3.13458752632141</v>
+        <v>3.13458681106567</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>4.80499982833862</v>
       </c>
       <c r="G634" t="n">
-        <v>3.17088222503662</v>
+        <v>3.17088198661804</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>4.88500022888184</v>
       </c>
       <c r="G636" t="n">
-        <v>3.22367548942566</v>
+        <v>3.22367525100708</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G637" t="n">
-        <v>3.28306746482849</v>
+        <v>3.28306722640991</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G639" t="n">
-        <v>3.35895776748657</v>
+        <v>3.35895729064941</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>5.25</v>
       </c>
       <c r="G641" t="n">
-        <v>3.46454334259033</v>
+        <v>3.46454381942749</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G642" t="n">
-        <v>3.51073718070984</v>
+        <v>3.51073741912842</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G643" t="n">
-        <v>3.48434066772461</v>
+        <v>3.48434090614319</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G645" t="n">
-        <v>3.54373240470886</v>
+        <v>3.54373288154602</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G646" t="n">
-        <v>3.5305347442627</v>
+        <v>3.53053498268127</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G647" t="n">
-        <v>3.55693125724792</v>
+        <v>3.5569314956665</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G649" t="n">
-        <v>3.61632394790649</v>
+        <v>3.61632299423218</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G650" t="n">
-        <v>3.58332777023315</v>
+        <v>3.58332800865173</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G651" t="n">
-        <v>3.58332777023315</v>
+        <v>3.58332800865173</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G652" t="n">
-        <v>3.60972476005554</v>
+        <v>3.60972428321838</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G653" t="n">
-        <v>3.60972476005554</v>
+        <v>3.60972428321838</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G654" t="n">
-        <v>3.60972476005554</v>
+        <v>3.60972428321838</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G655" t="n">
-        <v>3.56353044509888</v>
+        <v>3.56353068351746</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>5.5</v>
       </c>
       <c r="G656" t="n">
-        <v>3.62952136993408</v>
+        <v>3.6295223236084</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G657" t="n">
-        <v>3.5305347442627</v>
+        <v>3.53053498268127</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G658" t="n">
-        <v>3.48434066772461</v>
+        <v>3.48434090614319</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G659" t="n">
-        <v>3.5305347442627</v>
+        <v>3.53053498268127</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G660" t="n">
-        <v>3.5305347442627</v>
+        <v>3.53053498268127</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G662" t="n">
-        <v>3.56353044509888</v>
+        <v>3.56353068351746</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G663" t="n">
-        <v>3.51733636856079</v>
+        <v>3.51733660697937</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G664" t="n">
-        <v>3.47114253044128</v>
+        <v>3.47114276885986</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G665" t="n">
-        <v>3.44474649429321</v>
+        <v>3.4447455406189</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G666" t="n">
-        <v>3.47114253044128</v>
+        <v>3.47114276885986</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G667" t="n">
-        <v>3.5305347442627</v>
+        <v>3.53053498268127</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G668" t="n">
-        <v>3.55693125724792</v>
+        <v>3.5569314956665</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G669" t="n">
-        <v>3.57012963294983</v>
+        <v>3.57012891769409</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G671" t="n">
-        <v>3.60972476005554</v>
+        <v>3.60972428321838</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G672" t="n">
-        <v>3.60312485694885</v>
+        <v>3.60312509536743</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G673" t="n">
-        <v>3.54373240470886</v>
+        <v>3.54373288154602</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G674" t="n">
-        <v>3.5305347442627</v>
+        <v>3.53053498268127</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G675" t="n">
-        <v>3.53713440895081</v>
+        <v>3.53713345527649</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G677" t="n">
-        <v>3.57012963294983</v>
+        <v>3.57012891769409</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G678" t="n">
-        <v>3.51733636856079</v>
+        <v>3.51733660697937</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G679" t="n">
-        <v>3.49753952026367</v>
+        <v>3.49753928184509</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G680" t="n">
-        <v>3.54373240470886</v>
+        <v>3.54373288154602</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G681" t="n">
-        <v>3.5305347442627</v>
+        <v>3.53053498268127</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G682" t="n">
-        <v>3.51073718070984</v>
+        <v>3.51073741912842</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G683" t="n">
-        <v>3.49094009399414</v>
+        <v>3.49093961715698</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G684" t="n">
-        <v>3.50413823127747</v>
+        <v>3.50413846969604</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G686" t="n">
-        <v>3.5305347442627</v>
+        <v>3.53053498268127</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G687" t="n">
-        <v>3.51733636856079</v>
+        <v>3.51733660697937</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G688" t="n">
-        <v>3.49753952026367</v>
+        <v>3.49753928184509</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G689" t="n">
-        <v>3.47774195671082</v>
+        <v>3.47774147987366</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G691" t="n">
-        <v>3.54373240470886</v>
+        <v>3.54373288154602</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G692" t="n">
-        <v>3.50413823127747</v>
+        <v>3.50413846969604</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G693" t="n">
-        <v>3.49753952026367</v>
+        <v>3.49753928184509</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G694" t="n">
-        <v>3.5305347442627</v>
+        <v>3.53053498268127</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G695" t="n">
-        <v>3.53713440895081</v>
+        <v>3.53713345527649</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G696" t="n">
-        <v>3.55693125724792</v>
+        <v>3.5569314956665</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G697" t="n">
-        <v>3.5305347442627</v>
+        <v>3.53053498268127</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G698" t="n">
-        <v>3.51733636856079</v>
+        <v>3.51733660697937</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G699" t="n">
-        <v>3.55693125724792</v>
+        <v>3.5569314956665</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G700" t="n">
-        <v>3.56353044509888</v>
+        <v>3.56353068351746</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G701" t="n">
-        <v>3.53713440895081</v>
+        <v>3.53713345527649</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G702" t="n">
-        <v>3.58992671966553</v>
+        <v>3.58992695808411</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>5.5</v>
       </c>
       <c r="G703" t="n">
-        <v>3.62952136993408</v>
+        <v>3.6295223236084</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G704" t="n">
-        <v>3.70871090888977</v>
+        <v>3.70871114730835</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G705" t="n">
-        <v>3.72850871086121</v>
+        <v>3.72850894927979</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G706" t="n">
-        <v>3.74170708656311</v>
+        <v>3.74170684814453</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>5.75</v>
       </c>
       <c r="G707" t="n">
-        <v>3.79450011253357</v>
+        <v>3.79449963569641</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>5.75</v>
       </c>
       <c r="G708" t="n">
-        <v>3.79450011253357</v>
+        <v>3.79449963569641</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G709" t="n">
-        <v>3.80769777297974</v>
+        <v>3.80769824981689</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G710" t="n">
-        <v>3.74830532073975</v>
+        <v>3.7483057975769</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G713" t="n">
-        <v>3.68891382217407</v>
+        <v>3.68891406059265</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G714" t="n">
-        <v>3.70871090888977</v>
+        <v>3.70871114730835</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G716" t="n">
-        <v>3.74830532073975</v>
+        <v>3.7483057975769</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G717" t="n">
-        <v>3.74830532073975</v>
+        <v>3.7483057975769</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G719" t="n">
-        <v>3.78130149841309</v>
+        <v>3.78130173683167</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G720" t="n">
-        <v>3.82749533653259</v>
+        <v>3.82749557495117</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G721" t="n">
-        <v>3.82749533653259</v>
+        <v>3.82749557495117</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G723" t="n">
-        <v>3.93308162689209</v>
+        <v>3.93308210372925</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G724" t="n">
-        <v>3.93308162689209</v>
+        <v>3.93308210372925</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G726" t="n">
-        <v>4.0452675819397</v>
+        <v>4.04526710510254</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G727" t="n">
-        <v>3.9924738407135</v>
+        <v>3.99247431755066</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G728" t="n">
-        <v>3.76150393486023</v>
+        <v>3.76150417327881</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G730" t="n">
-        <v>3.84729313850403</v>
+        <v>3.84729337692261</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G731" t="n">
-        <v>3.75490570068359</v>
+        <v>3.75490546226501</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G733" t="n">
-        <v>3.48434066772461</v>
+        <v>3.48434090614319</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G734" t="n">
-        <v>3.55693125724792</v>
+        <v>3.5569314956665</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G735" t="n">
-        <v>3.51073718070984</v>
+        <v>3.51073741912842</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G736" t="n">
-        <v>3.47774195671082</v>
+        <v>3.47774147987366</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G737" t="n">
-        <v>3.28306746482849</v>
+        <v>3.28306722640991</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>4.625</v>
       </c>
       <c r="G740" t="n">
-        <v>3.05209803581238</v>
+        <v>3.05209755897522</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>4.17500019073486</v>
       </c>
       <c r="G741" t="n">
-        <v>2.75513696670532</v>
+        <v>2.7551372051239</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G742" t="n">
-        <v>2.90361738204956</v>
+        <v>2.90361714363098</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G743" t="n">
-        <v>2.76503562927246</v>
+        <v>2.76503586769104</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>4.14499998092651</v>
       </c>
       <c r="G744" t="n">
-        <v>2.73533940315247</v>
+        <v>2.73533916473389</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>4.65500020980835</v>
       </c>
       <c r="G747" t="n">
-        <v>3.07189536094666</v>
+        <v>3.07189512252808</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>4.75</v>
       </c>
       <c r="G749" t="n">
-        <v>3.13458752632141</v>
+        <v>3.13458681106567</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>4.69500017166138</v>
       </c>
       <c r="G751" t="n">
-        <v>3.09829187393188</v>
+        <v>3.09829163551331</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>4.43499994277954</v>
       </c>
       <c r="G753" t="n">
-        <v>2.9267144203186</v>
+        <v>2.92671394348145</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G754" t="n">
-        <v>3.12138867378235</v>
+        <v>3.12138891220093</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G757" t="n">
-        <v>3.01580262184143</v>
+        <v>3.01580238342285</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G758" t="n">
-        <v>3.10159087181091</v>
+        <v>3.10159134864807</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>4.86499977111816</v>
       </c>
       <c r="G763" t="n">
-        <v>3.2104766368866</v>
+        <v>3.21047687530518</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G764" t="n">
-        <v>3.10819029808044</v>
+        <v>3.10819053649902</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G765" t="n">
-        <v>3.08839249610901</v>
+        <v>3.08839297294617</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G768" t="n">
-        <v>3.1147894859314</v>
+        <v>3.11478924751282</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G770" t="n">
-        <v>3.10159087181091</v>
+        <v>3.10159134864807</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>4.71500015258789</v>
       </c>
       <c r="G774" t="n">
-        <v>3.11149048805237</v>
+        <v>3.11149024963379</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G775" t="n">
-        <v>3.00260424613953</v>
+        <v>3.00260472297668</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G776" t="n">
-        <v>2.99600529670715</v>
+        <v>2.99600553512573</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G777" t="n">
-        <v>3.06199622154236</v>
+        <v>3.06199669837952</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G778" t="n">
-        <v>2.98280692100525</v>
+        <v>2.98280668258667</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>4.82499980926514</v>
       </c>
       <c r="G779" t="n">
-        <v>3.18408012390137</v>
+        <v>3.18408060073853</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G780" t="n">
-        <v>3.17418146133423</v>
+        <v>3.17418169975281</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>4.75</v>
       </c>
       <c r="G781" t="n">
-        <v>3.13458752632141</v>
+        <v>3.13458681106567</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G784" t="n">
-        <v>3.22697472572327</v>
+        <v>3.22697448730469</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G785" t="n">
-        <v>3.37875485420227</v>
+        <v>3.37875509262085</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G787" t="n">
-        <v>3.26656937599182</v>
+        <v>3.26656985282898</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>4.92500019073486</v>
       </c>
       <c r="G788" t="n">
-        <v>3.25007200241089</v>
+        <v>3.25007176399231</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G789" t="n">
-        <v>3.30616450309753</v>
+        <v>3.30616402626038</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G790" t="n">
-        <v>3.33256101608276</v>
+        <v>3.33256077766418</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G791" t="n">
-        <v>3.41175079345703</v>
+        <v>3.41175055503845</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G792" t="n">
-        <v>3.44474649429321</v>
+        <v>3.4447455406189</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G793" t="n">
-        <v>3.41175079345703</v>
+        <v>3.41175055503845</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G798" t="n">
-        <v>3.37875485420227</v>
+        <v>3.37875509262085</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G799" t="n">
-        <v>3.4051513671875</v>
+        <v>3.40515112876892</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G800" t="n">
-        <v>3.37875485420227</v>
+        <v>3.37875509262085</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G805" t="n">
-        <v>3.10159087181091</v>
+        <v>3.10159134864807</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>4.7649998664856</v>
       </c>
       <c r="G810" t="n">
-        <v>3.14448595046997</v>
+        <v>3.14448523521423</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>4.7649998664856</v>
       </c>
       <c r="G813" t="n">
-        <v>3.14448595046997</v>
+        <v>3.14448523521423</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G814" t="n">
-        <v>3.26656937599182</v>
+        <v>3.26656985282898</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>4.99499988555908</v>
       </c>
       <c r="G815" t="n">
-        <v>3.2962658405304</v>
+        <v>3.29626560211182</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G818" t="n">
-        <v>3.41175079345703</v>
+        <v>3.41175055503845</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G820" t="n">
-        <v>3.39855241775513</v>
+        <v>3.39855194091797</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G823" t="n">
-        <v>3.3919529914856</v>
+        <v>3.39195275306702</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G824" t="n">
-        <v>3.39855241775513</v>
+        <v>3.39855194091797</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>4.92500019073486</v>
       </c>
       <c r="G826" t="n">
-        <v>3.25007200241089</v>
+        <v>3.25007176399231</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G827" t="n">
-        <v>3.27976775169373</v>
+        <v>3.27976751327515</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G828" t="n">
-        <v>3.32596182823181</v>
+        <v>3.32596158981323</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G829" t="n">
-        <v>3.30616450309753</v>
+        <v>3.30616402626038</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>4.99499988555908</v>
       </c>
       <c r="G830" t="n">
-        <v>3.2962658405304</v>
+        <v>3.29626560211182</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G835" t="n">
-        <v>3.22697472572327</v>
+        <v>3.22697448730469</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>4.88500022888184</v>
       </c>
       <c r="G836" t="n">
-        <v>3.22367548942566</v>
+        <v>3.22367525100708</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>4.81500005722046</v>
       </c>
       <c r="G839" t="n">
-        <v>3.17748117446899</v>
+        <v>3.17748141288757</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>4.80499982833862</v>
       </c>
       <c r="G840" t="n">
-        <v>3.17088222503662</v>
+        <v>3.17088198661804</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>4.86499977111816</v>
       </c>
       <c r="G841" t="n">
-        <v>3.2104766368866</v>
+        <v>3.21047687530518</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G842" t="n">
-        <v>3.23357367515564</v>
+        <v>3.2335741519928</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G844" t="n">
-        <v>3.16098308563232</v>
+        <v>3.1609833240509</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G846" t="n">
-        <v>3.14778470993042</v>
+        <v>3.14778542518616</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G848" t="n">
-        <v>3.14778470993042</v>
+        <v>3.14778542518616</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>4.75</v>
       </c>
       <c r="G849" t="n">
-        <v>3.13458752632141</v>
+        <v>3.13458681106567</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>4.68499994277954</v>
       </c>
       <c r="G850" t="n">
-        <v>3.09169268608093</v>
+        <v>3.09169244766235</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>4.61499977111816</v>
       </c>
       <c r="G851" t="n">
-        <v>3.04549860954285</v>
+        <v>3.04549884796143</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>4.64499998092651</v>
       </c>
       <c r="G854" t="n">
-        <v>3.06529641151428</v>
+        <v>3.06529593467712</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G855" t="n">
-        <v>3.06199622154236</v>
+        <v>3.06199669837952</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>4.65500020980835</v>
       </c>
       <c r="G860" t="n">
-        <v>3.07189536094666</v>
+        <v>3.07189512252808</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G862" t="n">
-        <v>3.07519483566284</v>
+        <v>3.07519507408142</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G863" t="n">
-        <v>3.00590395927429</v>
+        <v>3.00590372085571</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G864" t="n">
-        <v>2.98610687255859</v>
+        <v>2.98610663414001</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>4.625</v>
       </c>
       <c r="G867" t="n">
-        <v>3.05209803581238</v>
+        <v>3.05209755897522</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>4.625</v>
       </c>
       <c r="G868" t="n">
-        <v>3.05209803581238</v>
+        <v>3.05209755897522</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G870" t="n">
-        <v>3.06199622154236</v>
+        <v>3.06199669837952</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>4.7649998664856</v>
       </c>
       <c r="G873" t="n">
-        <v>3.14448595046997</v>
+        <v>3.14448523521423</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>4.7649998664856</v>
       </c>
       <c r="G877" t="n">
-        <v>3.14448595046997</v>
+        <v>3.14448523521423</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>4.7649998664856</v>
       </c>
       <c r="G878" t="n">
-        <v>3.14448595046997</v>
+        <v>3.14448523521423</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G879" t="n">
-        <v>3.16098308563232</v>
+        <v>3.1609833240509</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>4.74499988555908</v>
       </c>
       <c r="G881" t="n">
-        <v>3.13128709793091</v>
+        <v>3.13128733634949</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>4.80499982833862</v>
       </c>
       <c r="G882" t="n">
-        <v>3.17088222503662</v>
+        <v>3.17088198661804</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G883" t="n">
-        <v>3.16098308563232</v>
+        <v>3.1609833240509</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G884" t="n">
-        <v>3.20717716217041</v>
+        <v>3.20717763900757</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G885" t="n">
-        <v>3.22697472572327</v>
+        <v>3.22697448730469</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G886" t="n">
-        <v>3.33256101608276</v>
+        <v>3.33256077766418</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>4.93499994277954</v>
       </c>
       <c r="G887" t="n">
-        <v>3.25667071342468</v>
+        <v>3.25667095184326</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G889" t="n">
-        <v>3.17418146133423</v>
+        <v>3.17418169975281</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>4.81500005722046</v>
       </c>
       <c r="G890" t="n">
-        <v>3.17748117446899</v>
+        <v>3.17748141288757</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G891" t="n">
-        <v>3.08839249610901</v>
+        <v>3.08839297294617</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G893" t="n">
-        <v>2.94321179389954</v>
+        <v>2.94321227073669</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G894" t="n">
-        <v>2.94321179389954</v>
+        <v>2.94321227073669</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G895" t="n">
-        <v>2.91681575775146</v>
+        <v>2.91681551933289</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G896" t="n">
-        <v>2.90361738204956</v>
+        <v>2.90361714363098</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G898" t="n">
-        <v>2.84422492980957</v>
+        <v>2.84422516822815</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>4.16499996185303</v>
       </c>
       <c r="G900" t="n">
-        <v>2.74853754043579</v>
+        <v>2.74853777885437</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>3.97499990463257</v>
       </c>
       <c r="G902" t="n">
-        <v>2.6231541633606</v>
+        <v>2.62315440177917</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G903" t="n">
-        <v>2.61985492706299</v>
+        <v>2.61985445022583</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>3.95499992370605</v>
       </c>
       <c r="G904" t="n">
-        <v>2.60995578765869</v>
+        <v>2.60995626449585</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G905" t="n">
-        <v>2.58685922622681</v>
+        <v>2.58685946464539</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G906" t="n">
-        <v>2.57366108894348</v>
+        <v>2.5736608505249</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>4.02500009536743</v>
       </c>
       <c r="G907" t="n">
-        <v>2.65614986419678</v>
+        <v>2.65615034103394</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G908" t="n">
-        <v>2.75183749198914</v>
+        <v>2.75183725357056</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G912" t="n">
-        <v>3.00260424613953</v>
+        <v>3.00260472297668</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>4.36499977111816</v>
       </c>
       <c r="G914" t="n">
-        <v>2.8805205821991</v>
+        <v>2.88052010536194</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>4.5</v>
       </c>
       <c r="G915" t="n">
-        <v>2.96960878372192</v>
+        <v>2.96960830688477</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G916" t="n">
-        <v>3.00590395927429</v>
+        <v>3.00590372085571</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G918" t="n">
-        <v>3.00260424613953</v>
+        <v>3.00260472297668</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>4.64499998092651</v>
       </c>
       <c r="G920" t="n">
-        <v>3.06529641151428</v>
+        <v>3.06529593467712</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>4.61499977111816</v>
       </c>
       <c r="G921" t="n">
-        <v>3.04549860954285</v>
+        <v>3.04549884796143</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G922" t="n">
-        <v>3.14778470993042</v>
+        <v>3.14778542518616</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>4.7649998664856</v>
       </c>
       <c r="G923" t="n">
-        <v>3.14448595046997</v>
+        <v>3.14448523521423</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G924" t="n">
-        <v>3.12138867378235</v>
+        <v>3.12138891220093</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G925" t="n">
-        <v>3.03560018539429</v>
+        <v>3.03559970855713</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G926" t="n">
-        <v>2.97620797157288</v>
+        <v>2.97620820999146</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G927" t="n">
-        <v>2.98610687255859</v>
+        <v>2.98610663414001</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G928" t="n">
-        <v>2.97290825843811</v>
+        <v>2.97290849685669</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G929" t="n">
-        <v>3.00590395927429</v>
+        <v>3.00590372085571</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>4.53499984741211</v>
       </c>
       <c r="G930" t="n">
-        <v>2.99270534515381</v>
+        <v>2.99270558357239</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G934" t="n">
-        <v>2.97620797157288</v>
+        <v>2.97620820999146</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>4.64499998092651</v>
       </c>
       <c r="G935" t="n">
-        <v>3.06529641151428</v>
+        <v>3.06529593467712</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G937" t="n">
-        <v>3.00590395927429</v>
+        <v>3.00590372085571</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G938" t="n">
-        <v>3.06199622154236</v>
+        <v>3.06199669837952</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>4.65500020980835</v>
       </c>
       <c r="G939" t="n">
-        <v>3.07189536094666</v>
+        <v>3.07189512252808</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>4.5</v>
       </c>
       <c r="G940" t="n">
-        <v>2.96960878372192</v>
+        <v>2.96960830688477</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G942" t="n">
-        <v>3.03560018539429</v>
+        <v>3.03559970855713</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G943" t="n">
-        <v>3.10819029808044</v>
+        <v>3.10819053649902</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G946" t="n">
-        <v>3.16098308563232</v>
+        <v>3.1609833240509</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>4.68499994277954</v>
       </c>
       <c r="G947" t="n">
-        <v>3.09169268608093</v>
+        <v>3.09169244766235</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>4.69500017166138</v>
       </c>
       <c r="G950" t="n">
-        <v>3.09829187393188</v>
+        <v>3.09829163551331</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G952" t="n">
-        <v>3.08839249610901</v>
+        <v>3.08839297294617</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G956" t="n">
-        <v>3.08839249610901</v>
+        <v>3.08839297294617</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G957" t="n">
-        <v>3.08839249610901</v>
+        <v>3.08839297294617</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G960" t="n">
-        <v>3.00260424613953</v>
+        <v>3.00260472297668</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G964" t="n">
-        <v>2.98610687255859</v>
+        <v>2.98610663414001</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G965" t="n">
-        <v>2.99930500984192</v>
+        <v>2.99930453300476</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G966" t="n">
-        <v>3.03560018539429</v>
+        <v>3.03559970855713</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G967" t="n">
-        <v>3.03560018539429</v>
+        <v>3.03559970855713</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G968" t="n">
-        <v>3.1147894859314</v>
+        <v>3.11478924751282</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G970" t="n">
-        <v>3.23027443885803</v>
+        <v>3.23027467727661</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G971" t="n">
-        <v>3.23357367515564</v>
+        <v>3.2335741519928</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G972" t="n">
-        <v>3.2533712387085</v>
+        <v>3.25337076187134</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G973" t="n">
-        <v>3.43154811859131</v>
+        <v>3.43154788017273</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G975" t="n">
-        <v>3.74830532073975</v>
+        <v>3.7483057975769</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G976" t="n">
-        <v>3.76150393486023</v>
+        <v>3.76150417327881</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G977" t="n">
-        <v>3.71531057357788</v>
+        <v>3.7153103351593</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G978" t="n">
-        <v>3.60312485694885</v>
+        <v>3.60312509536743</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G981" t="n">
-        <v>3.64271998405457</v>
+        <v>3.64272022247314</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G983" t="n">
-        <v>3.62292242050171</v>
+        <v>3.62292218208313</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G984" t="n">
-        <v>3.62292242050171</v>
+        <v>3.62292218208313</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G985" t="n">
-        <v>3.58992671966553</v>
+        <v>3.58992695808411</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G987" t="n">
-        <v>3.66911673545837</v>
+        <v>3.66911625862122</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G988" t="n">
-        <v>3.66911673545837</v>
+        <v>3.66911625862122</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G989" t="n">
-        <v>3.64271998405457</v>
+        <v>3.64272022247314</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G990" t="n">
-        <v>3.66911673545837</v>
+        <v>3.66911625862122</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G992" t="n">
-        <v>3.82089638710022</v>
+        <v>3.8208966255188</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>6.30999994277954</v>
       </c>
       <c r="G995" t="n">
-        <v>4.1640510559082</v>
+        <v>4.16405153274536</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>6.3899998664856</v>
       </c>
       <c r="G1001" t="n">
-        <v>4.21684455871582</v>
+        <v>4.2168436050415</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G1003" t="n">
-        <v>4.26963710784912</v>
+        <v>4.26963758468628</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>6.5</v>
       </c>
       <c r="G1005" t="n">
-        <v>4.28943538665771</v>
+        <v>4.28943490982056</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G1006" t="n">
-        <v>4.26130962371826</v>
+        <v>4.26131010055542</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G1007" t="n">
-        <v>4.26130962371826</v>
+        <v>4.26131010055542</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>6.28499984741211</v>
       </c>
       <c r="G1009" t="n">
-        <v>4.15874671936035</v>
+        <v>4.15874719619751</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>6.52500009536743</v>
       </c>
       <c r="G1010" t="n">
-        <v>4.31755399703979</v>
+        <v>4.31755352020264</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G1012" t="n">
-        <v>4.31424474716187</v>
+        <v>4.31424522399902</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>6.55499982833862</v>
       </c>
       <c r="G1013" t="n">
-        <v>4.33740425109863</v>
+        <v>4.33740472793579</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G1014" t="n">
-        <v>4.36056423187256</v>
+        <v>4.3605637550354</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>6.77500009536743</v>
       </c>
       <c r="G1015" t="n">
-        <v>4.48297691345215</v>
+        <v>4.48297739028931</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G1016" t="n">
-        <v>4.51937055587769</v>
+        <v>4.51937007904053</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>6.83500003814697</v>
       </c>
       <c r="G1019" t="n">
-        <v>4.5226788520813</v>
+        <v>4.52267837524414</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G1021" t="n">
-        <v>4.51937055587769</v>
+        <v>4.51937007904053</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G1022" t="n">
-        <v>4.68479347229004</v>
+        <v>4.6847939491272</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>7.17500019073486</v>
       </c>
       <c r="G1023" t="n">
-        <v>4.74765491485596</v>
+        <v>4.7476544380188</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>7.39499998092651</v>
       </c>
       <c r="G1024" t="n">
-        <v>4.89322757720947</v>
+        <v>4.89322710037231</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G1026" t="n">
-        <v>4.86345148086548</v>
+        <v>4.86345100402832</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G1027" t="n">
-        <v>4.85683393478394</v>
+        <v>4.85683441162109</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G1030" t="n">
-        <v>4.87668466567993</v>
+        <v>4.87668514251709</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>7.55499982833862</v>
       </c>
       <c r="G1032" t="n">
-        <v>4.99909782409668</v>
+        <v>4.99909830093384</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1033" t="n">
-        <v>5.16121387481689</v>
+        <v>5.16121339797974</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>7.66499996185303</v>
       </c>
       <c r="G1034" t="n">
-        <v>5.0718846321106</v>
+        <v>5.07188510894775</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1035" t="n">
-        <v>4.87006855010986</v>
+        <v>4.87006807327271</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>7.30999994277954</v>
       </c>
       <c r="G1036" t="n">
-        <v>4.83698320388794</v>
+        <v>4.8369836807251</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>7.61499977111816</v>
       </c>
       <c r="G1037" t="n">
-        <v>5.03880023956299</v>
+        <v>5.03879976272583</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G1039" t="n">
-        <v>5.05534267425537</v>
+        <v>5.05534315109253</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>7.66499996185303</v>
       </c>
       <c r="G1040" t="n">
-        <v>5.0718846321106</v>
+        <v>5.07188510894775</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1043" t="n">
-        <v>5.06857585906982</v>
+        <v>5.06857681274414</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>7.625</v>
       </c>
       <c r="G1045" t="n">
-        <v>5.04541683197021</v>
+        <v>5.04541730880737</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G1046" t="n">
-        <v>5.05534267425537</v>
+        <v>5.05534315109253</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G1049" t="n">
-        <v>5.08842706680298</v>
+        <v>5.08842754364014</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1053" t="n">
-        <v>5.16121387481689</v>
+        <v>5.16121339797974</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G1060" t="n">
-        <v>5.38618946075439</v>
+        <v>5.38618898391724</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G1061" t="n">
-        <v>5.5185284614563</v>
+        <v>5.51852798461914</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G1062" t="n">
-        <v>5.60454893112183</v>
+        <v>5.60454797744751</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>8.52999973297119</v>
       </c>
       <c r="G1065" t="n">
-        <v>5.64424991607666</v>
+        <v>5.64425039291382</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>8.51500034332275</v>
       </c>
       <c r="G1066" t="n">
-        <v>5.63432455062866</v>
+        <v>5.63432502746582</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G1067" t="n">
-        <v>5.61116504669189</v>
+        <v>5.61116552352905</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>8.45499992370605</v>
       </c>
       <c r="G1068" t="n">
-        <v>5.59462356567383</v>
+        <v>5.59462308883667</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>8.51500034332275</v>
       </c>
       <c r="G1070" t="n">
-        <v>5.63432455062866</v>
+        <v>5.63432502746582</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G1071" t="n">
-        <v>5.59131479263306</v>
+        <v>5.59131383895874</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G1076" t="n">
-        <v>5.52514505386353</v>
+        <v>5.52514553070068</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1077" t="n">
-        <v>5.50529384613037</v>
+        <v>5.50529432296753</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G1078" t="n">
-        <v>5.6508674621582</v>
+        <v>5.65086698532104</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1079" t="n">
-        <v>5.55822992324829</v>
+        <v>5.55822944641113</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G1082" t="n">
-        <v>5.51191139221191</v>
+        <v>5.51191091537476</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>7.95499992370605</v>
       </c>
       <c r="G1084" t="n">
-        <v>5.26377582550049</v>
+        <v>5.26377630233765</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>8.07499980926514</v>
       </c>
       <c r="G1085" t="n">
-        <v>5.34317922592163</v>
+        <v>5.34317970275879</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>8.49499988555908</v>
       </c>
       <c r="G1087" t="n">
-        <v>5.62109041213989</v>
+        <v>5.62109088897705</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G1088" t="n">
-        <v>5.70380210876465</v>
+        <v>5.70380258560181</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G1089" t="n">
-        <v>5.81629085540771</v>
+        <v>5.81629037857056</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>8.875</v>
       </c>
       <c r="G1091" t="n">
-        <v>5.87253379821777</v>
+        <v>5.87253427505493</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>8.8100004196167</v>
       </c>
       <c r="G1093" t="n">
-        <v>5.82952499389648</v>
+        <v>5.82952451705933</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>8.86999988555908</v>
       </c>
       <c r="G1094" t="n">
-        <v>5.86922597885132</v>
+        <v>5.86922550201416</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>8.80500030517578</v>
       </c>
       <c r="G1095" t="n">
-        <v>5.82621622085571</v>
+        <v>5.82621669769287</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>8.86999988555908</v>
       </c>
       <c r="G1097" t="n">
-        <v>5.86922597885132</v>
+        <v>5.86922550201416</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>8.05500030517578</v>
       </c>
       <c r="G1098" t="n">
-        <v>5.32994604110718</v>
+        <v>5.32994556427002</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G1100" t="n">
-        <v>4.94285440444946</v>
+        <v>4.94285488128662</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>7.7649998664856</v>
       </c>
       <c r="G1103" t="n">
-        <v>5.13805437088013</v>
+        <v>5.13805389404297</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G1106" t="n">
-        <v>5.05534267425537</v>
+        <v>5.05534315109253</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>7.96500015258789</v>
       </c>
       <c r="G1110" t="n">
-        <v>5.27039337158203</v>
+        <v>5.27039289474487</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1112" t="n">
-        <v>5.22738218307495</v>
+        <v>5.22738313674927</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>7.85500001907349</v>
       </c>
       <c r="G1113" t="n">
-        <v>5.19760656356812</v>
+        <v>5.19760751724243</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>7.75</v>
       </c>
       <c r="G1114" t="n">
-        <v>5.12812900543213</v>
+        <v>5.12812852859497</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>7.7649998664856</v>
       </c>
       <c r="G1116" t="n">
-        <v>5.13805437088013</v>
+        <v>5.13805389404297</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>8.05500030517578</v>
       </c>
       <c r="G1122" t="n">
-        <v>5.32994604110718</v>
+        <v>5.32994556427002</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>8.01000022888184</v>
       </c>
       <c r="G1124" t="n">
-        <v>5.30016946792603</v>
+        <v>5.30016994476318</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G1127" t="n">
-        <v>5.34648752212524</v>
+        <v>5.3464879989624</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G1128" t="n">
-        <v>5.34648752212524</v>
+        <v>5.3464879989624</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>7.95499992370605</v>
       </c>
       <c r="G1129" t="n">
-        <v>5.26377582550049</v>
+        <v>5.26377630233765</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>8.0649995803833</v>
       </c>
       <c r="G1130" t="n">
-        <v>5.33656167984009</v>
+        <v>5.33656215667725</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G1132" t="n">
-        <v>5.41927433013916</v>
+        <v>5.419273853302</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1133" t="n">
-        <v>5.41265726089478</v>
+        <v>5.41265773773193</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1134" t="n">
-        <v>5.49206066131592</v>
+        <v>5.49206113815308</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>8.04500007629395</v>
       </c>
       <c r="G1135" t="n">
-        <v>5.32332801818848</v>
+        <v>5.32332849502563</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>8.19499969482422</v>
       </c>
       <c r="G1136" t="n">
-        <v>5.42258262634277</v>
+        <v>5.42258214950562</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1141" t="n">
-        <v>5.41265726089478</v>
+        <v>5.41265773773193</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G1142" t="n">
-        <v>5.38618946075439</v>
+        <v>5.38618898391724</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>7.05499982833862</v>
       </c>
       <c r="G1144" t="n">
-        <v>5.24187660217285</v>
+        <v>5.24187564849854</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>7.7350001335144</v>
       </c>
       <c r="G1149" t="n">
-        <v>5.7471170425415</v>
+        <v>5.74711751937866</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1151" t="n">
-        <v>5.79541301727295</v>
+        <v>5.79541254043579</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G1152" t="n">
-        <v>5.78798198699951</v>
+        <v>5.78798246383667</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>7.86999988555908</v>
       </c>
       <c r="G1154" t="n">
-        <v>5.84742212295532</v>
+        <v>5.84742259979248</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G1157" t="n">
-        <v>5.74340152740479</v>
+        <v>5.7434024810791</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G1158" t="n">
-        <v>5.75083255767822</v>
+        <v>5.75083208084106</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>7.83500003814697</v>
       </c>
       <c r="G1159" t="n">
-        <v>5.82141733169556</v>
+        <v>5.82141780853271</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>7.66499996185303</v>
       </c>
       <c r="G1160" t="n">
-        <v>5.69510698318481</v>
+        <v>5.69510746002197</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>7.42500019073486</v>
       </c>
       <c r="G1161" t="n">
-        <v>5.51678705215454</v>
+        <v>5.51678657531738</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>7.53499984741211</v>
       </c>
       <c r="G1163" t="n">
-        <v>5.59851694107056</v>
+        <v>5.5985164642334</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>7.42500019073486</v>
       </c>
       <c r="G1168" t="n">
-        <v>5.51678705215454</v>
+        <v>5.51678657531738</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>7.40999984741211</v>
       </c>
       <c r="G1169" t="n">
-        <v>5.50564193725586</v>
+        <v>5.50564098358154</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G1170" t="n">
-        <v>5.41648149490356</v>
+        <v>5.41648197174072</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G1174" t="n">
-        <v>5.14157152175903</v>
+        <v>5.14157104492188</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G1175" t="n">
-        <v>5.0747013092041</v>
+        <v>5.07470083236694</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>6.82499980926514</v>
       </c>
       <c r="G1176" t="n">
-        <v>5.07098531723022</v>
+        <v>5.07098579406738</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>6.91499996185303</v>
       </c>
       <c r="G1177" t="n">
-        <v>5.13785552978516</v>
+        <v>5.13785600662231</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1179" t="n">
-        <v>4.7997899055481</v>
+        <v>4.79979038238525</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G1180" t="n">
-        <v>4.93353033065796</v>
+        <v>4.9335298538208</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G1182" t="n">
-        <v>4.96325063705444</v>
+        <v>4.96325016021729</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>6.5</v>
       </c>
       <c r="G1183" t="n">
-        <v>4.82951068878174</v>
+        <v>4.82951021194458</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>6.63500022888184</v>
       </c>
       <c r="G1184" t="n">
-        <v>4.92981624603271</v>
+        <v>4.92981576919556</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>6.57000017166138</v>
       </c>
       <c r="G1186" t="n">
-        <v>4.88152074813843</v>
+        <v>4.88152027130127</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>6.70499992370605</v>
       </c>
       <c r="G1187" t="n">
-        <v>4.9818263053894</v>
+        <v>4.98182582855225</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G1191" t="n">
-        <v>4.97811031341553</v>
+        <v>4.97811079025269</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G1192" t="n">
-        <v>5.08956050872803</v>
+        <v>5.08956098556519</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G1198" t="n">
-        <v>5.22330093383789</v>
+        <v>5.22330141067505</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1200" t="n">
-        <v>5.2753119468689</v>
+        <v>5.27531147003174</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1202" t="n">
-        <v>5.34961128234863</v>
+        <v>5.34961175918579</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G1203" t="n">
-        <v>5.46106195449829</v>
+        <v>5.46106147766113</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>7.17500019073486</v>
       </c>
       <c r="G1204" t="n">
-        <v>5.33103656768799</v>
+        <v>5.33103609085083</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>7.14499998092651</v>
       </c>
       <c r="G1205" t="n">
-        <v>5.30874681472778</v>
+        <v>5.30874633789062</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>7.21500015258789</v>
       </c>
       <c r="G1206" t="n">
-        <v>5.36075687408447</v>
+        <v>5.36075639724731</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>7.21500015258789</v>
       </c>
       <c r="G1208" t="n">
-        <v>5.36075687408447</v>
+        <v>5.36075639724731</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1209" t="n">
-        <v>5.2753119468689</v>
+        <v>5.27531147003174</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>7.05499982833862</v>
       </c>
       <c r="G1210" t="n">
-        <v>5.24187660217285</v>
+        <v>5.24187564849854</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>7.10500001907349</v>
       </c>
       <c r="G1212" t="n">
-        <v>5.27902603149414</v>
+        <v>5.2790265083313</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>6.94500017166138</v>
       </c>
       <c r="G1213" t="n">
-        <v>5.16014623641968</v>
+        <v>5.16014671325684</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G1214" t="n">
-        <v>5.22330093383789</v>
+        <v>5.22330141067505</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G1216" t="n">
-        <v>5.12671089172363</v>
+        <v>5.12671136856079</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>6.5</v>
       </c>
       <c r="G1217" t="n">
-        <v>4.82951068878174</v>
+        <v>4.82951021194458</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>6.82499980926514</v>
       </c>
       <c r="G1220" t="n">
-        <v>5.07098531723022</v>
+        <v>5.07098579406738</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>6.81500005722046</v>
       </c>
       <c r="G1221" t="n">
-        <v>5.06355619430542</v>
+        <v>5.06355571746826</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G1223" t="n">
-        <v>5.17872047424316</v>
+        <v>5.17872095108032</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>6.76999998092651</v>
       </c>
       <c r="G1227" t="n">
-        <v>5.03012132644653</v>
+        <v>5.03012084960938</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G1229" t="n">
-        <v>5.21587085723877</v>
+        <v>5.21587133407593</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1230" t="n">
-        <v>5.60966157913208</v>
+        <v>5.6096625328064</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>7.45499992370605</v>
       </c>
       <c r="G1232" t="n">
-        <v>5.5390772819519</v>
+        <v>5.53907680511475</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>7.67500019073486</v>
       </c>
       <c r="G1233" t="n">
-        <v>5.70253705978394</v>
+        <v>5.70253753662109</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G1234" t="n">
-        <v>5.54279184341431</v>
+        <v>5.54279232025146</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>7.25500011444092</v>
       </c>
       <c r="G1238" t="n">
-        <v>5.39047622680664</v>
+        <v>5.3904767036438</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G1242" t="n">
-        <v>4.79235982894897</v>
+        <v>4.79236030578613</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1245" t="n">
-        <v>4.60660982131958</v>
+        <v>4.60660934448242</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>6.06500005722046</v>
       </c>
       <c r="G1250" t="n">
-        <v>4.50630474090576</v>
+        <v>4.50630521774292</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1257" t="n">
-        <v>4.7997899055481</v>
+        <v>4.79979038238525</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G1259" t="n">
-        <v>4.93353033065796</v>
+        <v>4.9335298538208</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>6.67000007629395</v>
       </c>
       <c r="G1260" t="n">
-        <v>4.95582056045532</v>
+        <v>4.95582103729248</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G1261" t="n">
-        <v>5.00040054321289</v>
+        <v>5.00040102005005</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>6.82499980926514</v>
       </c>
       <c r="G1263" t="n">
-        <v>5.07098531723022</v>
+        <v>5.07098579406738</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>6.82499980926514</v>
       </c>
       <c r="G1264" t="n">
-        <v>5.07098531723022</v>
+        <v>5.07098579406738</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>6.96500015258789</v>
       </c>
       <c r="G1267" t="n">
-        <v>5.17500638961792</v>
+        <v>5.17500591278076</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>7.00500011444092</v>
       </c>
       <c r="G1268" t="n">
-        <v>5.20472621917725</v>
+        <v>5.20472574234009</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G1269" t="n">
-        <v>5.00040054321289</v>
+        <v>5.00040102005005</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>6.86499977111816</v>
       </c>
       <c r="G1273" t="n">
-        <v>5.10070610046387</v>
+        <v>5.10070562362671</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G1277" t="n">
-        <v>5.03365612030029</v>
+        <v>5.03365564346313</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G1278" t="n">
-        <v>5.00894069671631</v>
+        <v>5.00894021987915</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G1279" t="n">
-        <v>4.98422527313232</v>
+        <v>4.98422574996948</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G1281" t="n">
-        <v>4.79474258422852</v>
+        <v>4.79474306106567</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G1285" t="n">
-        <v>4.95127248764038</v>
+        <v>4.95127201080322</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>6.22499990463257</v>
       </c>
       <c r="G1286" t="n">
-        <v>5.1283974647522</v>
+        <v>5.12839698791504</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>6.28499984741211</v>
       </c>
       <c r="G1287" t="n">
-        <v>5.17782735824585</v>
+        <v>5.17782783508301</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G1289" t="n">
-        <v>5.23961544036865</v>
+        <v>5.23961591720581</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G1290" t="n">
-        <v>5.06660890579224</v>
+        <v>5.06660985946655</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>6.30499982833862</v>
       </c>
       <c r="G1291" t="n">
-        <v>5.1943039894104</v>
+        <v>5.19430446624756</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>6.59499979019165</v>
       </c>
       <c r="G1293" t="n">
-        <v>5.43321704864502</v>
+        <v>5.43321752548218</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G1295" t="n">
-        <v>5.61858177185059</v>
+        <v>5.61858129501343</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G1299" t="n">
-        <v>5.98930883407593</v>
+        <v>5.98930931091309</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G1301" t="n">
-        <v>5.98930883407593</v>
+        <v>5.98930931091309</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G1302" t="n">
-        <v>5.9975471496582</v>
+        <v>5.99754762649536</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>7.25</v>
       </c>
       <c r="G1306" t="n">
-        <v>5.97283220291138</v>
+        <v>5.97283172607422</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1310" t="n">
-        <v>5.93163967132568</v>
+        <v>5.93164014816284</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1312" t="n">
-        <v>5.93163967132568</v>
+        <v>5.93164014816284</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>6.95499992370605</v>
       </c>
       <c r="G1314" t="n">
-        <v>5.72979974746704</v>
+        <v>5.72979927062988</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>6.86499977111816</v>
       </c>
       <c r="G1317" t="n">
-        <v>5.65565395355225</v>
+        <v>5.65565347671509</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>6.60500001907349</v>
       </c>
       <c r="G1320" t="n">
-        <v>5.44145631790161</v>
+        <v>5.44145584106445</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>6.60500001907349</v>
       </c>
       <c r="G1321" t="n">
-        <v>5.44145631790161</v>
+        <v>5.44145584106445</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>6.63500022888184</v>
       </c>
       <c r="G1327" t="n">
-        <v>5.4661717414856</v>
+        <v>5.46617126464844</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>6.30999994277954</v>
       </c>
       <c r="G1332" t="n">
-        <v>5.19842290878296</v>
+        <v>5.19842338562012</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>6.57000017166138</v>
       </c>
       <c r="G1334" t="n">
-        <v>5.41262245178223</v>
+        <v>5.41262197494507</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>6.55499982833862</v>
       </c>
       <c r="G1336" t="n">
-        <v>5.40026426315308</v>
+        <v>5.40026378631592</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>6.16499996185303</v>
       </c>
       <c r="G1338" t="n">
-        <v>5.07896709442139</v>
+        <v>5.07896661758423</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1340" t="n">
-        <v>5.12427759170532</v>
+        <v>5.12427806854248</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>6.42500019073486</v>
       </c>
       <c r="G1341" t="n">
-        <v>5.29316473007202</v>
+        <v>5.29316520690918</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G1342" t="n">
-        <v>5.2231388092041</v>
+        <v>5.22313833236694</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35287,7 +35287,7 @@
         <v>6.47499990463257</v>
       </c>
       <c r="G1343" t="n">
-        <v>5.33435678482056</v>
+        <v>5.33435726165771</v>
       </c>
       <c r="H1343" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G1344" t="n">
-        <v>5.40438318252563</v>
+        <v>5.40438365936279</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>6.63500022888184</v>
       </c>
       <c r="G1346" t="n">
-        <v>5.4661717414856</v>
+        <v>5.46617126464844</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G1348" t="n">
-        <v>5.63505840301514</v>
+        <v>5.63505792617798</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>6.85500001907349</v>
       </c>
       <c r="G1349" t="n">
-        <v>5.64741563796997</v>
+        <v>5.64741611480713</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>6.86499977111816</v>
       </c>
       <c r="G1350" t="n">
-        <v>5.65565395355225</v>
+        <v>5.65565347671509</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>6.94500017166138</v>
       </c>
       <c r="G1352" t="n">
-        <v>5.72156143188477</v>
+        <v>5.72156190872192</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G1353" t="n">
-        <v>5.85749435424805</v>
+        <v>5.85749483108521</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>6.9850001335144</v>
       </c>
       <c r="G1355" t="n">
-        <v>5.75451469421387</v>
+        <v>5.75451517105103</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>6.86499977111816</v>
       </c>
       <c r="G1356" t="n">
-        <v>5.65565395355225</v>
+        <v>5.65565347671509</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G1357" t="n">
-        <v>5.68448829650879</v>
+        <v>5.68448877334595</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G1358" t="n">
-        <v>5.72567987442017</v>
+        <v>5.72568035125732</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>7.0149998664856</v>
       </c>
       <c r="G1359" t="n">
-        <v>5.77922964096069</v>
+        <v>5.77923011779785</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1360" t="n">
-        <v>5.84925603866577</v>
+        <v>5.84925651550293</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>6.95499992370605</v>
       </c>
       <c r="G1361" t="n">
-        <v>5.72979974746704</v>
+        <v>5.72979927062988</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>6.9850001335144</v>
       </c>
       <c r="G1362" t="n">
-        <v>5.75451469421387</v>
+        <v>5.75451517105103</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G1363" t="n">
-        <v>5.67625045776367</v>
+        <v>5.67624950408936</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1365" t="n">
-        <v>5.62401437759399</v>
+        <v>5.62401533126831</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G1367" t="n">
-        <v>5.54566097259521</v>
+        <v>5.54566144943237</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>6.31500005722046</v>
       </c>
       <c r="G1369" t="n">
-        <v>5.49777936935425</v>
+        <v>5.49777889251709</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>6.31500005722046</v>
       </c>
       <c r="G1371" t="n">
-        <v>5.49777936935425</v>
+        <v>5.49777889251709</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>6.46500015258789</v>
       </c>
       <c r="G1378" t="n">
-        <v>5.62836790084839</v>
+        <v>5.62836742401123</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G1383" t="n">
-        <v>5.94613313674927</v>
+        <v>5.94613361358643</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>7.03499984741211</v>
       </c>
       <c r="G1385" t="n">
-        <v>6.12460374832153</v>
+        <v>6.12460422515869</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G1388" t="n">
-        <v>6.06801557540894</v>
+        <v>6.06801605224609</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>7.10500001907349</v>
       </c>
       <c r="G1389" t="n">
-        <v>6.18554592132568</v>
+        <v>6.18554544448853</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G1391" t="n">
-        <v>5.82425117492676</v>
+        <v>5.8242506980896</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>6.42500019073486</v>
       </c>
       <c r="G1392" t="n">
-        <v>5.59354400634766</v>
+        <v>5.59354448318481</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G1394" t="n">
-        <v>5.98095655441284</v>
+        <v>5.98095703125</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>7</v>
       </c>
       <c r="G1397" t="n">
-        <v>6.0941333770752</v>
+        <v>6.09413385391235</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G1399" t="n">
-        <v>5.88519191741943</v>
+        <v>5.88519239425659</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>6.94500017166138</v>
       </c>
       <c r="G1401" t="n">
-        <v>6.04625129699707</v>
+        <v>6.04625177383423</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36899,7 +36899,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G1405" t="n">
-        <v>6.06801557540894</v>
+        <v>6.06801605224609</v>
       </c>
       <c r="H1405" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G1406" t="n">
-        <v>6.0070743560791</v>
+        <v>6.00707483291626</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -36951,7 +36951,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G1407" t="n">
-        <v>6.11154508590698</v>
+        <v>6.11154556274414</v>
       </c>
       <c r="H1407" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G1408" t="n">
-        <v>6.13766288757324</v>
+        <v>6.1376633644104</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>7.17500019073486</v>
       </c>
       <c r="G1410" t="n">
-        <v>6.24648761749268</v>
+        <v>6.24648666381836</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G1411" t="n">
-        <v>6.24213409423828</v>
+        <v>6.24213457107544</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G1413" t="n">
-        <v>6.24213409423828</v>
+        <v>6.24213457107544</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>7.22499990463257</v>
       </c>
       <c r="G1415" t="n">
-        <v>6.29001665115356</v>
+        <v>6.29001617431641</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37263,7 +37263,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1419" t="n">
-        <v>6.44236993789673</v>
+        <v>6.44236946105957</v>
       </c>
       <c r="H1419" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>7.20499992370605</v>
       </c>
       <c r="G1420" t="n">
-        <v>6.27260494232178</v>
+        <v>6.27260446548462</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37315,7 +37315,7 @@
         <v>7.17500019073486</v>
       </c>
       <c r="G1421" t="n">
-        <v>6.24648761749268</v>
+        <v>6.24648666381836</v>
       </c>
       <c r="H1421" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G1426" t="n">
-        <v>6.24213409423828</v>
+        <v>6.24213457107544</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>7.16499996185303</v>
       </c>
       <c r="G1427" t="n">
-        <v>6.2377815246582</v>
+        <v>6.23778104782104</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>7.2649998664856</v>
       </c>
       <c r="G1430" t="n">
-        <v>6.3248405456543</v>
+        <v>6.32484006881714</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G1431" t="n">
-        <v>6.37272262573242</v>
+        <v>6.37272310256958</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1432" t="n">
-        <v>6.44236993789673</v>
+        <v>6.44236946105957</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G1433" t="n">
-        <v>6.41625213623047</v>
+        <v>6.41625261306763</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G1435" t="n">
-        <v>6.4771933555603</v>
+        <v>6.47719383239746</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>7.31500005722046</v>
       </c>
       <c r="G1440" t="n">
-        <v>6.36837005615234</v>
+        <v>6.36836957931519</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G1444" t="n">
-        <v>6.41625213623047</v>
+        <v>6.41625261306763</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G1445" t="n">
-        <v>6.4771933555603</v>
+        <v>6.47719383239746</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -37965,7 +37965,7 @@
         <v>7.40999984741211</v>
       </c>
       <c r="G1446" t="n">
-        <v>6.45107555389404</v>
+        <v>6.4510760307312</v>
       </c>
       <c r="H1446" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>7.20499992370605</v>
       </c>
       <c r="G1447" t="n">
-        <v>6.27260494232178</v>
+        <v>6.27260446548462</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G1451" t="n">
-        <v>6.4771933555603</v>
+        <v>6.47719383239746</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38199,7 +38199,7 @@
         <v>7.39499998092651</v>
       </c>
       <c r="G1455" t="n">
-        <v>6.43801689147949</v>
+        <v>6.43801736831665</v>
       </c>
       <c r="H1455" t="s">
         <v>8</v>
@@ -38251,7 +38251,7 @@
         <v>7.40999984741211</v>
       </c>
       <c r="G1457" t="n">
-        <v>6.45107555389404</v>
+        <v>6.4510760307312</v>
       </c>
       <c r="H1457" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G1462" t="n">
-        <v>6.91248893737793</v>
+        <v>6.91248846054077</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G1465" t="n">
-        <v>7.25201892852783</v>
+        <v>7.25201940536499</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1466" t="n">
-        <v>7.31296014785767</v>
+        <v>7.31295967102051</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G1467" t="n">
-        <v>7.33037281036377</v>
+        <v>7.33037233352661</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>8.42500019073486</v>
       </c>
       <c r="G1468" t="n">
-        <v>7.33472585678101</v>
+        <v>7.33472490310669</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1470" t="n">
-        <v>7.44354915618896</v>
+        <v>7.44354867935181</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>8.50500011444092</v>
       </c>
       <c r="G1471" t="n">
-        <v>7.40437269210815</v>
+        <v>7.40437316894531</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38641,7 +38641,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G1472" t="n">
-        <v>7.45225477218628</v>
+        <v>7.45225524902344</v>
       </c>
       <c r="H1472" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G1474" t="n">
-        <v>7.35649013519287</v>
+        <v>7.35648965835571</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38745,7 +38745,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G1476" t="n">
-        <v>7.27813673019409</v>
+        <v>7.27813625335693</v>
       </c>
       <c r="H1476" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>8.61499977111816</v>
       </c>
       <c r="G1478" t="n">
-        <v>7.50013732910156</v>
+        <v>7.50013780593872</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>8.48499965667725</v>
       </c>
       <c r="G1479" t="n">
-        <v>7.38696098327637</v>
+        <v>7.38696002960205</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38875,7 +38875,7 @@
         <v>8.6899995803833</v>
       </c>
       <c r="G1481" t="n">
-        <v>7.56543159484863</v>
+        <v>7.56543207168579</v>
       </c>
       <c r="H1481" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G1482" t="n">
-        <v>7.64378452301025</v>
+        <v>7.64378547668457</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -38927,7 +38927,7 @@
         <v>8.76500034332275</v>
       </c>
       <c r="G1483" t="n">
-        <v>7.63072633743286</v>
+        <v>7.6307258605957</v>
       </c>
       <c r="H1483" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>8.90499973297119</v>
       </c>
       <c r="G1484" t="n">
-        <v>7.75260829925537</v>
+        <v>7.75260925292969</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>8.89000034332275</v>
       </c>
       <c r="G1486" t="n">
-        <v>7.73954963684082</v>
+        <v>7.73955011367798</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39161,7 +39161,7 @@
         <v>9.71500015258789</v>
       </c>
       <c r="G1492" t="n">
-        <v>8.45778751373291</v>
+        <v>8.45778656005859</v>
       </c>
       <c r="H1492" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1497" t="n">
-        <v>8.21837520599365</v>
+        <v>8.21837329864502</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G1498" t="n">
-        <v>8.25319862365723</v>
+        <v>8.25319766998291</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39343,7 +39343,7 @@
         <v>9.39000034332275</v>
       </c>
       <c r="G1499" t="n">
-        <v>8.17484569549561</v>
+        <v>8.17484474182129</v>
       </c>
       <c r="H1499" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>9.36499977111816</v>
       </c>
       <c r="G1500" t="n">
-        <v>8.15308094024658</v>
+        <v>8.15307998657227</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>9.51500034332275</v>
       </c>
       <c r="G1503" t="n">
-        <v>8.28366947174072</v>
+        <v>8.28366851806641</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39473,7 +39473,7 @@
         <v>9.45499992370605</v>
       </c>
       <c r="G1504" t="n">
-        <v>8.2314338684082</v>
+        <v>8.23143291473389</v>
       </c>
       <c r="H1504" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G1505" t="n">
-        <v>8.29672813415527</v>
+        <v>8.29672718048096</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>9.4350004196167</v>
       </c>
       <c r="G1506" t="n">
-        <v>8.21402263641357</v>
+        <v>8.21402168273926</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39551,7 +39551,7 @@
         <v>9.34500026702881</v>
       </c>
       <c r="G1507" t="n">
-        <v>8.13566970825195</v>
+        <v>8.13566875457764</v>
       </c>
       <c r="H1507" t="s">
         <v>8</v>
@@ -39629,7 +39629,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G1510" t="n">
-        <v>7.85272741317749</v>
+        <v>7.85272693634033</v>
       </c>
       <c r="H1510" t="s">
         <v>8</v>
@@ -39681,7 +39681,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G1512" t="n">
-        <v>7.89625597000122</v>
+        <v>7.89625549316406</v>
       </c>
       <c r="H1512" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>9.45499992370605</v>
       </c>
       <c r="G1514" t="n">
-        <v>8.2314338684082</v>
+        <v>8.23143291473389</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G1516" t="n">
-        <v>8.06166839599609</v>
+        <v>8.06166934967041</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G1518" t="n">
-        <v>7.96590280532837</v>
+        <v>7.96590328216553</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>9.00500011444092</v>
       </c>
       <c r="G1519" t="n">
-        <v>7.83966875076294</v>
+        <v>7.83966827392578</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>9.0649995803833</v>
       </c>
       <c r="G1520" t="n">
-        <v>7.89190340042114</v>
+        <v>7.89190244674683</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G1522" t="n">
-        <v>7.96590280532837</v>
+        <v>7.96590328216553</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>8.98999977111816</v>
       </c>
       <c r="G1524" t="n">
-        <v>7.82660913467407</v>
+        <v>7.82660818099976</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>9.17500019073486</v>
       </c>
       <c r="G1526" t="n">
-        <v>7.98766851425171</v>
+        <v>7.98766803741455</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>9.32999992370605</v>
       </c>
       <c r="G1528" t="n">
-        <v>8.12261009216309</v>
+        <v>8.12260913848877</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40149,7 +40149,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G1530" t="n">
-        <v>8.09649276733398</v>
+        <v>8.09649181365967</v>
       </c>
       <c r="H1530" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G1534" t="n">
-        <v>7.89625597000122</v>
+        <v>7.89625549316406</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40279,7 +40279,7 @@
         <v>9.0649995803833</v>
       </c>
       <c r="G1535" t="n">
-        <v>7.89190340042114</v>
+        <v>7.89190244674683</v>
       </c>
       <c r="H1535" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>8.69499969482422</v>
       </c>
       <c r="G1536" t="n">
-        <v>7.93662881851196</v>
+        <v>7.93662929534912</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G1540" t="n">
-        <v>7.95944976806641</v>
+        <v>7.95944929122925</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>8.57499980926514</v>
       </c>
       <c r="G1543" t="n">
-        <v>7.8270959854126</v>
+        <v>7.82709503173828</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>8.61499977111816</v>
       </c>
       <c r="G1545" t="n">
-        <v>7.86360692977905</v>
+        <v>7.86360740661621</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40565,7 +40565,7 @@
         <v>8.69499969482422</v>
       </c>
       <c r="G1546" t="n">
-        <v>7.93662881851196</v>
+        <v>7.93662929534912</v>
       </c>
       <c r="H1546" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>8.54500007629395</v>
       </c>
       <c r="G1547" t="n">
-        <v>7.79971218109131</v>
+        <v>7.79971265792847</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>8.625</v>
       </c>
       <c r="G1549" t="n">
-        <v>7.87273502349854</v>
+        <v>7.87273454666138</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40669,7 +40669,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G1550" t="n">
-        <v>7.84078741073608</v>
+        <v>7.84078788757324</v>
       </c>
       <c r="H1550" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G1556" t="n">
-        <v>8.38845634460449</v>
+        <v>8.38845539093018</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40851,7 +40851,7 @@
         <v>9.15499973297119</v>
       </c>
       <c r="G1557" t="n">
-        <v>8.35650825500488</v>
+        <v>8.3565092086792</v>
       </c>
       <c r="H1557" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G1567" t="n">
-        <v>8.87222957611084</v>
+        <v>8.87223052978516</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41501,7 +41501,7 @@
         <v>9.78999996185303</v>
       </c>
       <c r="G1582" t="n">
-        <v>8.93612480163574</v>
+        <v>8.93612384796143</v>
       </c>
       <c r="H1582" t="s">
         <v>8</v>
@@ -41553,7 +41553,7 @@
         <v>10.0299997329712</v>
       </c>
       <c r="G1584" t="n">
-        <v>9.15519237518311</v>
+        <v>9.15519142150879</v>
       </c>
       <c r="H1584" t="s">
         <v>8</v>
@@ -41579,7 +41579,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G1585" t="n">
-        <v>9.03652954101562</v>
+        <v>9.03653049468994</v>
       </c>
       <c r="H1585" t="s">
         <v>8</v>
@@ -41631,7 +41631,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G1587" t="n">
-        <v>9.01827526092529</v>
+        <v>9.01827430725098</v>
       </c>
       <c r="H1587" t="s">
         <v>8</v>
@@ -41917,7 +41917,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G1598" t="n">
-        <v>9.2921085357666</v>
+        <v>9.29210948944092</v>
       </c>
       <c r="H1598" t="s">
         <v>8</v>
@@ -42021,7 +42021,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G1602" t="n">
-        <v>9.01827526092529</v>
+        <v>9.01827430725098</v>
       </c>
       <c r="H1602" t="s">
         <v>8</v>
@@ -42125,7 +42125,7 @@
         <v>10.1700000762939</v>
       </c>
       <c r="G1606" t="n">
-        <v>9.28298187255859</v>
+        <v>9.28298091888428</v>
       </c>
       <c r="H1606" t="s">
         <v>8</v>
@@ -42229,7 +42229,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1610" t="n">
-        <v>8.83571910858154</v>
+        <v>8.83571815490723</v>
       </c>
       <c r="H1610" t="s">
         <v>8</v>
@@ -42281,7 +42281,7 @@
         <v>9.5649995803833</v>
       </c>
       <c r="G1612" t="n">
-        <v>8.73074913024902</v>
+        <v>8.73074817657471</v>
       </c>
       <c r="H1612" t="s">
         <v>8</v>
@@ -42307,7 +42307,7 @@
         <v>9.6850004196167</v>
       </c>
       <c r="G1613" t="n">
-        <v>8.84028244018555</v>
+        <v>8.84028339385986</v>
       </c>
       <c r="H1613" t="s">
         <v>8</v>
@@ -42463,7 +42463,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G1619" t="n">
-        <v>8.80833530426025</v>
+        <v>8.80833435058594</v>
       </c>
       <c r="H1619" t="s">
         <v>8</v>
@@ -42541,7 +42541,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G1622" t="n">
-        <v>8.80833530426025</v>
+        <v>8.80833435058594</v>
       </c>
       <c r="H1622" t="s">
         <v>8</v>
@@ -42827,7 +42827,7 @@
         <v>9.6850004196167</v>
       </c>
       <c r="G1633" t="n">
-        <v>8.84028244018555</v>
+        <v>8.84028339385986</v>
       </c>
       <c r="H1633" t="s">
         <v>8</v>
@@ -62824,6 +62824,32 @@
         <v>2.94600009918213</v>
       </c>
       <c r="H2402" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2403">
+      <c r="A2403" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B2403" t="n">
+        <v>2179623</v>
+      </c>
+      <c r="C2403" t="n">
+        <v>2.9300000667572</v>
+      </c>
+      <c r="D2403" t="n">
+        <v>2.8199999332428</v>
+      </c>
+      <c r="E2403" t="n">
+        <v>2.92000007629395</v>
+      </c>
+      <c r="F2403" t="n">
+        <v>2.81399989128113</v>
+      </c>
+      <c r="G2403" t="n">
+        <v>2.81399989128113</v>
+      </c>
+      <c r="H2403" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/BFF.MI.xlsx
+++ b/data/BFF.MI.xlsx
@@ -447,7 +447,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G3" t="n">
-        <v>2.36908078193665</v>
+        <v>2.36908102035522</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G6" t="n">
-        <v>2.2601580619812</v>
+        <v>2.26015830039978</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>4.06599998474121</v>
       </c>
       <c r="G7" t="n">
-        <v>2.21441006660461</v>
+        <v>2.21441030502319</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G9" t="n">
-        <v>2.2601580619812</v>
+        <v>2.26015830039978</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G10" t="n">
-        <v>2.2274808883667</v>
+        <v>2.22748112678528</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G11" t="n">
-        <v>2.26560401916504</v>
+        <v>2.26560378074646</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G13" t="n">
-        <v>2.34185004234314</v>
+        <v>2.3418505191803</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>4.2979998588562</v>
       </c>
       <c r="G14" t="n">
-        <v>2.3407609462738</v>
+        <v>2.34076070785522</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>4.44600009918213</v>
       </c>
       <c r="G17" t="n">
-        <v>2.42136454582214</v>
+        <v>2.42136430740356</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G18" t="n">
-        <v>2.40720415115356</v>
+        <v>2.40720462799072</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>4.4520001411438</v>
       </c>
       <c r="G19" t="n">
-        <v>2.42463231086731</v>
+        <v>2.42463183403015</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>4.48600006103516</v>
       </c>
       <c r="G20" t="n">
-        <v>2.44314932823181</v>
+        <v>2.44314908981323</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G21" t="n">
-        <v>2.54335880279541</v>
+        <v>2.54335808753967</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G22" t="n">
-        <v>2.55969667434692</v>
+        <v>2.55969643592834</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>4.83599996566772</v>
       </c>
       <c r="G23" t="n">
-        <v>2.63376474380493</v>
+        <v>2.63376450538635</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G25" t="n">
-        <v>2.55969667434692</v>
+        <v>2.55969643592834</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>4.73799991607666</v>
       </c>
       <c r="G27" t="n">
-        <v>2.58039236068726</v>
+        <v>2.58039212226868</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>4.83799982070923</v>
       </c>
       <c r="G31" t="n">
-        <v>2.63485360145569</v>
+        <v>2.63485383987427</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>4.77600002288818</v>
       </c>
       <c r="G32" t="n">
-        <v>2.60108757019043</v>
+        <v>2.60108804702759</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G34" t="n">
-        <v>2.66317367553711</v>
+        <v>2.66317415237427</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G35" t="n">
-        <v>2.68495869636536</v>
+        <v>2.68495845794678</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>4.89799976348877</v>
       </c>
       <c r="G36" t="n">
-        <v>2.66753053665161</v>
+        <v>2.66753101348877</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G37" t="n">
-        <v>2.68495869636536</v>
+        <v>2.68495845794678</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>4.87599992752075</v>
       </c>
       <c r="G44" t="n">
-        <v>2.65554904937744</v>
+        <v>2.65554976463318</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>4.84600019454956</v>
       </c>
       <c r="G45" t="n">
-        <v>2.63921093940735</v>
+        <v>2.63921070098877</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>4.89599990844727</v>
       </c>
       <c r="G46" t="n">
-        <v>2.66644167900085</v>
+        <v>2.66644144058228</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>5.06500005722046</v>
       </c>
       <c r="G47" t="n">
-        <v>2.75848150253296</v>
+        <v>2.75848174095154</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>5.07499980926514</v>
       </c>
       <c r="G48" t="n">
-        <v>2.76392841339111</v>
+        <v>2.76392793655396</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G53" t="n">
-        <v>2.80749773979187</v>
+        <v>2.80749750137329</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>5</v>
       </c>
       <c r="G54" t="n">
-        <v>2.72308158874512</v>
+        <v>2.7230818271637</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G56" t="n">
-        <v>2.81566667556763</v>
+        <v>2.81566643714905</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G57" t="n">
-        <v>2.84289741516113</v>
+        <v>2.84289765357971</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>5</v>
       </c>
       <c r="G59" t="n">
-        <v>2.72308158874512</v>
+        <v>2.7230818271637</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G61" t="n">
-        <v>2.79932761192322</v>
+        <v>2.79932808876038</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G62" t="n">
-        <v>2.78298950195312</v>
+        <v>2.7829897403717</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G63" t="n">
-        <v>2.79932761192322</v>
+        <v>2.79932808876038</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>5.16499996185303</v>
       </c>
       <c r="G64" t="n">
-        <v>2.81294322013855</v>
+        <v>2.81294345855713</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G65" t="n">
-        <v>2.79388213157654</v>
+        <v>2.79388236999512</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>5.07499980926514</v>
       </c>
       <c r="G66" t="n">
-        <v>2.76392841339111</v>
+        <v>2.76392793655396</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G68" t="n">
-        <v>2.81566667556763</v>
+        <v>2.81566643714905</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G69" t="n">
-        <v>2.78843569755554</v>
+        <v>2.78843545913696</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G70" t="n">
-        <v>2.80477476119995</v>
+        <v>2.80477428436279</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>5.07499980926514</v>
       </c>
       <c r="G71" t="n">
-        <v>2.76392841339111</v>
+        <v>2.76392793655396</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G72" t="n">
-        <v>2.78026676177979</v>
+        <v>2.78026652336121</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G73" t="n">
-        <v>2.78026676177979</v>
+        <v>2.78026652336121</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G74" t="n">
-        <v>2.78843569755554</v>
+        <v>2.78843545913696</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G75" t="n">
-        <v>2.80477476119995</v>
+        <v>2.80477428436279</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>5.17500019073486</v>
       </c>
       <c r="G77" t="n">
-        <v>2.81838965415955</v>
+        <v>2.81838989257812</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G78" t="n">
-        <v>2.78843569755554</v>
+        <v>2.78843545913696</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G79" t="n">
-        <v>2.8265585899353</v>
+        <v>2.82655882835388</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G81" t="n">
-        <v>2.80477476119995</v>
+        <v>2.80477428436279</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G82" t="n">
-        <v>2.80477476119995</v>
+        <v>2.80477428436279</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G83" t="n">
-        <v>2.80477476119995</v>
+        <v>2.80477428436279</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G84" t="n">
-        <v>2.79932761192322</v>
+        <v>2.79932808876038</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G85" t="n">
-        <v>2.80749773979187</v>
+        <v>2.80749750137329</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G86" t="n">
-        <v>2.80477476119995</v>
+        <v>2.80477428436279</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G87" t="n">
-        <v>2.79388213157654</v>
+        <v>2.79388236999512</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>5.13500022888184</v>
       </c>
       <c r="G88" t="n">
-        <v>2.79660511016846</v>
+        <v>2.79660487174988</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>5.08500003814697</v>
       </c>
       <c r="G89" t="n">
-        <v>2.76937389373779</v>
+        <v>2.76937365531921</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G90" t="n">
-        <v>2.81566667556763</v>
+        <v>2.81566643714905</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G92" t="n">
-        <v>2.81566667556763</v>
+        <v>2.81566643714905</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G93" t="n">
-        <v>2.80749773979187</v>
+        <v>2.80749750137329</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G94" t="n">
-        <v>2.80749773979187</v>
+        <v>2.80749750137329</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G95" t="n">
-        <v>2.79932761192322</v>
+        <v>2.79932808876038</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>5.16499996185303</v>
       </c>
       <c r="G96" t="n">
-        <v>2.81294322013855</v>
+        <v>2.81294345855713</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G97" t="n">
-        <v>2.81566667556763</v>
+        <v>2.81566643714905</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G98" t="n">
-        <v>2.79932761192322</v>
+        <v>2.79932808876038</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>4.9520001411438</v>
       </c>
       <c r="G100" t="n">
-        <v>2.69694042205811</v>
+        <v>2.69694018363953</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G101" t="n">
-        <v>2.69585061073303</v>
+        <v>2.69585084915161</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>4.99200010299683</v>
       </c>
       <c r="G102" t="n">
-        <v>2.71872448921204</v>
+        <v>2.71872472763062</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G106" t="n">
-        <v>2.78026676177979</v>
+        <v>2.78026652336121</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>5.08500003814697</v>
       </c>
       <c r="G107" t="n">
-        <v>2.76937389373779</v>
+        <v>2.76937365531921</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G108" t="n">
-        <v>2.76665115356445</v>
+        <v>2.76665139198303</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G109" t="n">
-        <v>2.78843569755554</v>
+        <v>2.78843545913696</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>5.16499996185303</v>
       </c>
       <c r="G110" t="n">
-        <v>2.81294322013855</v>
+        <v>2.81294345855713</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G111" t="n">
-        <v>2.84834361076355</v>
+        <v>2.84834337234497</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G113" t="n">
-        <v>2.86468195915222</v>
+        <v>2.86468243598938</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>5.49499988555908</v>
       </c>
       <c r="G115" t="n">
-        <v>2.99266695976257</v>
+        <v>2.99266672134399</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G116" t="n">
-        <v>3.02806663513184</v>
+        <v>3.02806735038757</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G117" t="n">
-        <v>3.03895950317383</v>
+        <v>3.03895974159241</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G118" t="n">
-        <v>3.00628232955933</v>
+        <v>3.00628185272217</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G119" t="n">
-        <v>3.087975025177</v>
+        <v>3.08797478675842</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G121" t="n">
-        <v>3.24046730995178</v>
+        <v>3.2404670715332</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>5.75</v>
       </c>
       <c r="G123" t="n">
-        <v>3.13154411315918</v>
+        <v>3.1315438747406</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G124" t="n">
-        <v>3.19689774513245</v>
+        <v>3.19689846038818</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G126" t="n">
-        <v>3.07708239555359</v>
+        <v>3.07708215713501</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G127" t="n">
-        <v>3.14243650436401</v>
+        <v>3.14243626594543</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G128" t="n">
-        <v>3.10431289672852</v>
+        <v>3.10431313514709</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>5.72499990463257</v>
       </c>
       <c r="G129" t="n">
-        <v>3.11792802810669</v>
+        <v>3.11792874336243</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G130" t="n">
-        <v>3.15877461433411</v>
+        <v>3.15877532958984</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G131" t="n">
-        <v>3.2023446559906</v>
+        <v>3.20234370231628</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G133" t="n">
-        <v>3.32215976715088</v>
+        <v>3.3221595287323</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G135" t="n">
-        <v>3.30582165718079</v>
+        <v>3.30582118034363</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>6.11499977111816</v>
       </c>
       <c r="G136" t="n">
-        <v>3.33032870292664</v>
+        <v>3.33032917976379</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>6</v>
       </c>
       <c r="G138" t="n">
-        <v>3.26769804954529</v>
+        <v>3.26769781112671</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>6.11499977111816</v>
       </c>
       <c r="G139" t="n">
-        <v>3.33032870292664</v>
+        <v>3.33032917976379</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G141" t="n">
-        <v>3.32215976715088</v>
+        <v>3.3221595287323</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G142" t="n">
-        <v>3.34939098358154</v>
+        <v>3.34939002990723</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G143" t="n">
-        <v>3.39295983314514</v>
+        <v>3.39296007156372</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G146" t="n">
-        <v>3.38206720352173</v>
+        <v>3.38206744194031</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>6.11499977111816</v>
       </c>
       <c r="G147" t="n">
-        <v>3.33032870292664</v>
+        <v>3.33032917976379</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>6.02500009536743</v>
       </c>
       <c r="G148" t="n">
-        <v>3.28131365776062</v>
+        <v>3.28131294250488</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>6.00500011444092</v>
       </c>
       <c r="G149" t="n">
-        <v>3.27042150497437</v>
+        <v>3.27042126655579</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>6.09499979019165</v>
       </c>
       <c r="G150" t="n">
-        <v>3.3194363117218</v>
+        <v>3.31943607330322</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G152" t="n">
-        <v>3.25680565834045</v>
+        <v>3.25680589675903</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>6</v>
       </c>
       <c r="G157" t="n">
-        <v>3.26769804954529</v>
+        <v>3.26769781112671</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G158" t="n">
-        <v>3.3276059627533</v>
+        <v>3.32760620117188</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G160" t="n">
-        <v>3.36028289794922</v>
+        <v>3.36028265953064</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G161" t="n">
-        <v>3.38206720352173</v>
+        <v>3.38206744194031</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>6.40999984741211</v>
       </c>
       <c r="G162" t="n">
-        <v>3.49099087715149</v>
+        <v>3.49099063873291</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G164" t="n">
-        <v>3.4746527671814</v>
+        <v>3.47465229034424</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G165" t="n">
-        <v>3.45831418037415</v>
+        <v>3.45831394195557</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>6.41499996185303</v>
       </c>
       <c r="G166" t="n">
-        <v>3.49371337890625</v>
+        <v>3.49371385574341</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>6.45499992370605</v>
       </c>
       <c r="G167" t="n">
-        <v>3.51549887657166</v>
+        <v>3.5154983997345</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>6.36499977111816</v>
       </c>
       <c r="G168" t="n">
-        <v>3.46648263931274</v>
+        <v>3.4664831161499</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G169" t="n">
-        <v>3.50732922554016</v>
+        <v>3.50732898712158</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G170" t="n">
-        <v>3.50732922554016</v>
+        <v>3.50732898712158</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>6.40999984741211</v>
       </c>
       <c r="G171" t="n">
-        <v>3.49099087715149</v>
+        <v>3.49099063873291</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G172" t="n">
-        <v>3.58357572555542</v>
+        <v>3.58357548713684</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G173" t="n">
-        <v>3.56179046630859</v>
+        <v>3.56179118156433</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>6.58500003814697</v>
       </c>
       <c r="G174" t="n">
-        <v>3.58629846572876</v>
+        <v>3.58629870414734</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>6.53000020980835</v>
       </c>
       <c r="G176" t="n">
-        <v>3.55634450912476</v>
+        <v>3.55634427070618</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G177" t="n">
-        <v>3.52366781234741</v>
+        <v>3.52366757392883</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>6.53499984741211</v>
       </c>
       <c r="G178" t="n">
-        <v>3.55906796455383</v>
+        <v>3.55906820297241</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G180" t="n">
-        <v>3.61080694198608</v>
+        <v>3.61080622673035</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>6.375</v>
       </c>
       <c r="G181" t="n">
-        <v>3.47192883491516</v>
+        <v>3.4719295501709</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G182" t="n">
-        <v>3.4746527671814</v>
+        <v>3.47465229034424</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G184" t="n">
-        <v>3.44742107391357</v>
+        <v>3.44742131233215</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>6.38500022888184</v>
       </c>
       <c r="G185" t="n">
-        <v>3.47737574577332</v>
+        <v>3.47737526893616</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G186" t="n">
-        <v>3.48554444313049</v>
+        <v>3.48554491996765</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>6.41499996185303</v>
       </c>
       <c r="G187" t="n">
-        <v>3.49371337890625</v>
+        <v>3.49371385574341</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>6.53499984741211</v>
       </c>
       <c r="G188" t="n">
-        <v>3.55906796455383</v>
+        <v>3.55906820297241</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>6.5</v>
       </c>
       <c r="G189" t="n">
-        <v>3.54000616073608</v>
+        <v>3.54000639915466</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G190" t="n">
-        <v>3.54545307159424</v>
+        <v>3.5454523563385</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>6.5</v>
       </c>
       <c r="G191" t="n">
-        <v>3.54000616073608</v>
+        <v>3.54000639915466</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G193" t="n">
-        <v>3.56179046630859</v>
+        <v>3.56179118156433</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G194" t="n">
-        <v>3.4746527671814</v>
+        <v>3.47465229034424</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>6.46500015258789</v>
       </c>
       <c r="G195" t="n">
-        <v>3.52094483375549</v>
+        <v>3.52094459533691</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G196" t="n">
-        <v>3.52911448478699</v>
+        <v>3.52911376953125</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>6.5</v>
       </c>
       <c r="G197" t="n">
-        <v>3.54000616073608</v>
+        <v>3.54000639915466</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G198" t="n">
-        <v>3.54545307159424</v>
+        <v>3.5454523563385</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G199" t="n">
-        <v>3.54545307159424</v>
+        <v>3.5454523563385</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G200" t="n">
-        <v>3.54545307159424</v>
+        <v>3.5454523563385</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>6.57499980926514</v>
       </c>
       <c r="G201" t="n">
-        <v>3.58085203170776</v>
+        <v>3.58085227012634</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G202" t="n">
-        <v>3.58902144432068</v>
+        <v>3.58902192115784</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>6.53000020980835</v>
       </c>
       <c r="G204" t="n">
-        <v>3.55634450912476</v>
+        <v>3.55634427070618</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>6.59499979019165</v>
       </c>
       <c r="G205" t="n">
-        <v>3.5917444229126</v>
+        <v>3.59174466133118</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G207" t="n">
-        <v>3.54545307159424</v>
+        <v>3.5454523563385</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>6.4850001335144</v>
       </c>
       <c r="G208" t="n">
-        <v>3.53183722496033</v>
+        <v>3.53183674812317</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>6.41499996185303</v>
       </c>
       <c r="G209" t="n">
-        <v>3.49371337890625</v>
+        <v>3.49371385574341</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G210" t="n">
-        <v>3.29492902755737</v>
+        <v>3.29492855072021</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G213" t="n">
-        <v>3.27858996391296</v>
+        <v>3.2785906791687</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G214" t="n">
-        <v>3.12065124511719</v>
+        <v>3.12065148353577</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G216" t="n">
-        <v>3.16966724395752</v>
+        <v>3.1696674823761</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>6</v>
       </c>
       <c r="G219" t="n">
-        <v>3.26769804954529</v>
+        <v>3.26769781112671</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G220" t="n">
-        <v>3.38206720352173</v>
+        <v>3.38206744194031</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G224" t="n">
-        <v>3.18055963516235</v>
+        <v>3.18055939674377</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G225" t="n">
-        <v>3.16966724395752</v>
+        <v>3.1696674823761</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G226" t="n">
-        <v>3.16966724395752</v>
+        <v>3.1696674823761</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G228" t="n">
-        <v>3.18600559234619</v>
+        <v>3.18600606918335</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G229" t="n">
-        <v>3.18600559234619</v>
+        <v>3.18600606918335</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G230" t="n">
-        <v>3.17511296272278</v>
+        <v>3.17511343955994</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>5.78499984741211</v>
       </c>
       <c r="G231" t="n">
-        <v>3.15060567855835</v>
+        <v>3.15060544013977</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G232" t="n">
-        <v>3.15877461433411</v>
+        <v>3.15877532958984</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G233" t="n">
-        <v>3.15332841873169</v>
+        <v>3.15332865715027</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>5.88500022888184</v>
       </c>
       <c r="G234" t="n">
-        <v>3.20506715774536</v>
+        <v>3.20506739616394</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G238" t="n">
-        <v>3.24046730995178</v>
+        <v>3.2404670715332</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>5.88500022888184</v>
       </c>
       <c r="G239" t="n">
-        <v>3.20506715774536</v>
+        <v>3.20506739616394</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>5.88500022888184</v>
       </c>
       <c r="G241" t="n">
-        <v>3.20506715774536</v>
+        <v>3.20506739616394</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>5.75</v>
       </c>
       <c r="G242" t="n">
-        <v>3.13154411315918</v>
+        <v>3.1315438747406</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>5.7350001335144</v>
       </c>
       <c r="G243" t="n">
-        <v>3.12337517738342</v>
+        <v>3.12337470054626</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G245" t="n">
-        <v>3.087975025177</v>
+        <v>3.08797478675842</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G246" t="n">
-        <v>3.09342074394226</v>
+        <v>3.09342098236084</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G247" t="n">
-        <v>3.16422128677368</v>
+        <v>3.16422057151794</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G248" t="n">
-        <v>3.18600559234619</v>
+        <v>3.18600606918335</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G251" t="n">
-        <v>3.18600559234619</v>
+        <v>3.18600606918335</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G252" t="n">
-        <v>3.20779013633728</v>
+        <v>3.20779037475586</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G253" t="n">
-        <v>3.2023446559906</v>
+        <v>3.20234370231628</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>5.32499980926514</v>
       </c>
       <c r="G256" t="n">
-        <v>3.16490006446838</v>
+        <v>3.16490030288696</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G258" t="n">
-        <v>3.24513721466064</v>
+        <v>3.24513745307922</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G259" t="n">
-        <v>3.21541976928711</v>
+        <v>3.21541953086853</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G260" t="n">
-        <v>3.15598487854004</v>
+        <v>3.15598511695862</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G261" t="n">
-        <v>3.20947623252869</v>
+        <v>3.20947647094727</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>5.36499977111816</v>
       </c>
       <c r="G264" t="n">
-        <v>3.18867373466492</v>
+        <v>3.18867444992065</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>5.25500011444092</v>
       </c>
       <c r="G265" t="n">
-        <v>3.12329649925232</v>
+        <v>3.12329602241516</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G266" t="n">
-        <v>3.06386137008667</v>
+        <v>3.06386160850525</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G267" t="n">
-        <v>3.13815474510193</v>
+        <v>3.13815450668335</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G268" t="n">
-        <v>3.06088972091675</v>
+        <v>3.06088924407959</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>5.18499994277954</v>
       </c>
       <c r="G269" t="n">
-        <v>3.08169150352478</v>
+        <v>3.08169174194336</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>5.25</v>
       </c>
       <c r="G270" t="n">
-        <v>3.12032413482666</v>
+        <v>3.12032437324524</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G271" t="n">
-        <v>3.13815474510193</v>
+        <v>3.13815450668335</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>5.25500011444092</v>
       </c>
       <c r="G272" t="n">
-        <v>3.12329649925232</v>
+        <v>3.12329602241516</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G273" t="n">
-        <v>3.07872009277344</v>
+        <v>3.07871985435486</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G274" t="n">
-        <v>3.09655022621155</v>
+        <v>3.09655046463013</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G275" t="n">
-        <v>3.07277631759644</v>
+        <v>3.07277584075928</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>5.22499990463257</v>
       </c>
       <c r="G278" t="n">
-        <v>3.10546588897705</v>
+        <v>3.10546493530273</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G279" t="n">
-        <v>3.01928520202637</v>
+        <v>3.01928496360779</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>4.96600008010864</v>
       </c>
       <c r="G280" t="n">
-        <v>2.95152950286865</v>
+        <v>2.95152974128723</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G281" t="n">
-        <v>3.04305934906006</v>
+        <v>3.04305863380432</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>5.07499980926514</v>
       </c>
       <c r="G283" t="n">
-        <v>3.01631331443787</v>
+        <v>3.01631355285645</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G284" t="n">
-        <v>3.03414416313171</v>
+        <v>3.03414392471313</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G286" t="n">
-        <v>3.03117203712463</v>
+        <v>3.03117227554321</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G287" t="n">
-        <v>3.06386137008667</v>
+        <v>3.06386160850525</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>5.04500007629395</v>
       </c>
       <c r="G288" t="n">
-        <v>2.99848318099976</v>
+        <v>2.9984827041626</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>5.07499980926514</v>
       </c>
       <c r="G290" t="n">
-        <v>3.01631331443787</v>
+        <v>3.01631355285645</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>5.07499980926514</v>
       </c>
       <c r="G291" t="n">
-        <v>3.01631331443787</v>
+        <v>3.01631355285645</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G292" t="n">
-        <v>3.05791783332825</v>
+        <v>3.05791807174683</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G293" t="n">
-        <v>3.09060668945312</v>
+        <v>3.0906069278717</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G294" t="n">
-        <v>3.06683278083801</v>
+        <v>3.06683325767517</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G297" t="n">
-        <v>3.03711557388306</v>
+        <v>3.03711581230164</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G298" t="n">
-        <v>3.06088972091675</v>
+        <v>3.06088924407959</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G299" t="n">
-        <v>3.11438059806824</v>
+        <v>3.11438083648682</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G300" t="n">
-        <v>3.09060668945312</v>
+        <v>3.0906069278717</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>5.29500007629395</v>
       </c>
       <c r="G301" t="n">
-        <v>3.14706993103027</v>
+        <v>3.14707040786743</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G302" t="n">
-        <v>3.13221096992493</v>
+        <v>3.13221073150635</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G303" t="n">
-        <v>3.15598487854004</v>
+        <v>3.15598511695862</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G304" t="n">
-        <v>3.20353293418884</v>
+        <v>3.20353317260742</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G305" t="n">
-        <v>3.14409804344177</v>
+        <v>3.14409828186035</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G308" t="n">
-        <v>3.01928520202637</v>
+        <v>3.01928496360779</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G309" t="n">
-        <v>3.0133421421051</v>
+        <v>3.01334166526794</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>4.95599985122681</v>
       </c>
       <c r="G310" t="n">
-        <v>2.94558572769165</v>
+        <v>2.94558596611023</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>4.9539999961853</v>
       </c>
       <c r="G311" t="n">
-        <v>2.94439744949341</v>
+        <v>2.94439721107483</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>5</v>
       </c>
       <c r="G313" t="n">
-        <v>2.97173762321472</v>
+        <v>2.9717378616333</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>4.93200016021729</v>
       </c>
       <c r="G315" t="n">
-        <v>2.93132162094116</v>
+        <v>2.93132185935974</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>4.96199989318848</v>
       </c>
       <c r="G316" t="n">
-        <v>2.94915223121643</v>
+        <v>2.94915246963501</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G317" t="n">
-        <v>2.98956847190857</v>
+        <v>2.98956775665283</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G318" t="n">
-        <v>3.05791783332825</v>
+        <v>3.05791807174683</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G319" t="n">
-        <v>3.07277631759644</v>
+        <v>3.07277584075928</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G320" t="n">
-        <v>3.04305934906006</v>
+        <v>3.04305863380432</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G323" t="n">
-        <v>3.06683278083801</v>
+        <v>3.06683325767517</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G324" t="n">
-        <v>3.13815474510193</v>
+        <v>3.13815450668335</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G325" t="n">
-        <v>3.1262674331665</v>
+        <v>3.12626838684082</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G327" t="n">
-        <v>3.1262674331665</v>
+        <v>3.12626838684082</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G328" t="n">
-        <v>3.08466339111328</v>
+        <v>3.08466362953186</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G329" t="n">
-        <v>3.10843753814697</v>
+        <v>3.10843706130981</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G330" t="n">
-        <v>3.09060668945312</v>
+        <v>3.0906069278717</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G331" t="n">
-        <v>3.10843753814697</v>
+        <v>3.10843706130981</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>5.29500007629395</v>
       </c>
       <c r="G332" t="n">
-        <v>3.14706993103027</v>
+        <v>3.14707040786743</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>5.33500003814697</v>
       </c>
       <c r="G335" t="n">
-        <v>3.17084383964539</v>
+        <v>3.17084336280823</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G336" t="n">
-        <v>3.15004205703735</v>
+        <v>3.15004181861877</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>5.17500019073486</v>
       </c>
       <c r="G338" t="n">
-        <v>3.07574868202209</v>
+        <v>3.07574796676636</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G340" t="n">
-        <v>3.20947623252869</v>
+        <v>3.20947647094727</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>5.44500017166138</v>
       </c>
       <c r="G341" t="n">
-        <v>3.23622179031372</v>
+        <v>3.23622226715088</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G343" t="n">
-        <v>3.16787195205688</v>
+        <v>3.16787171363831</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G344" t="n">
-        <v>3.16192841529846</v>
+        <v>3.16192865371704</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G346" t="n">
-        <v>3.0490026473999</v>
+        <v>3.04900288581848</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G347" t="n">
-        <v>3.05791783332825</v>
+        <v>3.05791807174683</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G348" t="n">
-        <v>3.08466339111328</v>
+        <v>3.08466362953186</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G349" t="n">
-        <v>3.06683278083801</v>
+        <v>3.06683325767517</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G351" t="n">
-        <v>3.06088972091675</v>
+        <v>3.06088924407959</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>5.17500019073486</v>
       </c>
       <c r="G353" t="n">
-        <v>3.07574868202209</v>
+        <v>3.07574796676636</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G355" t="n">
-        <v>3.07277631759644</v>
+        <v>3.07277584075928</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G356" t="n">
-        <v>3.06088972091675</v>
+        <v>3.06088924407959</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G357" t="n">
-        <v>3.05791783332825</v>
+        <v>3.05791807174683</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G359" t="n">
-        <v>3.07277631759644</v>
+        <v>3.07277584075928</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G362" t="n">
-        <v>3.06683278083801</v>
+        <v>3.06683325767517</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G364" t="n">
-        <v>3.05791783332825</v>
+        <v>3.05791807174683</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G368" t="n">
-        <v>3.06088972091675</v>
+        <v>3.06088924407959</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G369" t="n">
-        <v>3.09060668945312</v>
+        <v>3.0906069278717</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G370" t="n">
-        <v>3.11438059806824</v>
+        <v>3.11438083648682</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G371" t="n">
-        <v>3.15598487854004</v>
+        <v>3.15598511695862</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G372" t="n">
-        <v>3.09655022621155</v>
+        <v>3.09655046463013</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G373" t="n">
-        <v>3.07277631759644</v>
+        <v>3.07277584075928</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G374" t="n">
-        <v>3.09655022621155</v>
+        <v>3.09655046463013</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>5.25500011444092</v>
       </c>
       <c r="G375" t="n">
-        <v>3.12329649925232</v>
+        <v>3.12329602241516</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G376" t="n">
-        <v>3.06683278083801</v>
+        <v>3.06683325767517</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G379" t="n">
-        <v>3.0490026473999</v>
+        <v>3.04900288581848</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G380" t="n">
-        <v>3.04305934906006</v>
+        <v>3.04305863380432</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>4.98799991607666</v>
       </c>
       <c r="G381" t="n">
-        <v>2.96460509300232</v>
+        <v>2.96460485458374</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G382" t="n">
-        <v>2.81720685958862</v>
+        <v>2.8172070980072</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>4.71799993515015</v>
       </c>
       <c r="G385" t="n">
-        <v>2.80413126945496</v>
+        <v>2.80413103103638</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G386" t="n">
-        <v>2.78748941421509</v>
+        <v>2.78748965263367</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>4.71400022506714</v>
       </c>
       <c r="G389" t="n">
-        <v>2.80175423622131</v>
+        <v>2.80175399780273</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G390" t="n">
-        <v>2.80531978607178</v>
+        <v>2.80532002449036</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>4.33599996566772</v>
       </c>
       <c r="G394" t="n">
-        <v>2.57709074020386</v>
+        <v>2.57709097862244</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G395" t="n">
-        <v>2.57946825027466</v>
+        <v>2.57946801185608</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G397" t="n">
-        <v>2.63295912742615</v>
+        <v>2.63295936584473</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>4.49599981307983</v>
       </c>
       <c r="G398" t="n">
-        <v>2.67218589782715</v>
+        <v>2.67218613624573</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G402" t="n">
-        <v>2.71022439002991</v>
+        <v>2.71022462844849</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G403" t="n">
-        <v>2.68645048141479</v>
+        <v>2.68645071983337</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>4.61399984359741</v>
       </c>
       <c r="G405" t="n">
-        <v>2.74231934547424</v>
+        <v>2.74231910705566</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>4.57600021362305</v>
       </c>
       <c r="G409" t="n">
-        <v>2.71973419189453</v>
+        <v>2.71973395347595</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>4.57600021362305</v>
       </c>
       <c r="G410" t="n">
-        <v>2.71973419189453</v>
+        <v>2.71973395347595</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>4.51599979400635</v>
       </c>
       <c r="G411" t="n">
-        <v>2.68407320976257</v>
+        <v>2.68407297134399</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G412" t="n">
-        <v>2.71022439002991</v>
+        <v>2.71022462844849</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>4.48799991607666</v>
       </c>
       <c r="G413" t="n">
-        <v>2.66743135452271</v>
+        <v>2.66743111610413</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G419" t="n">
-        <v>2.72805523872375</v>
+        <v>2.72805500030518</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>4.59800004959106</v>
       </c>
       <c r="G420" t="n">
-        <v>2.7328097820282</v>
+        <v>2.73280954360962</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G421" t="n">
-        <v>2.74588489532471</v>
+        <v>2.74588513374329</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>4.59800004959106</v>
       </c>
       <c r="G424" t="n">
-        <v>2.7328097820282</v>
+        <v>2.73280954360962</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>4.53599977493286</v>
       </c>
       <c r="G425" t="n">
-        <v>2.69596028327942</v>
+        <v>2.69595980644226</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>4.50799989700317</v>
       </c>
       <c r="G427" t="n">
-        <v>2.67931818962097</v>
+        <v>2.67931795120239</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>4.46199989318848</v>
       </c>
       <c r="G428" t="n">
-        <v>2.65197825431824</v>
+        <v>2.65197849273682</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>4.57399988174438</v>
       </c>
       <c r="G429" t="n">
-        <v>2.71854519844055</v>
+        <v>2.71854543685913</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>4.53399991989136</v>
       </c>
       <c r="G431" t="n">
-        <v>2.69477105140686</v>
+        <v>2.69477128982544</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G432" t="n">
-        <v>2.65673279762268</v>
+        <v>2.65673327445984</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>4.48199987411499</v>
       </c>
       <c r="G433" t="n">
-        <v>2.66386580467224</v>
+        <v>2.6638650894165</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G434" t="n">
-        <v>2.69239401817322</v>
+        <v>2.6923942565918</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>4.50400018692017</v>
       </c>
       <c r="G435" t="n">
-        <v>2.67694091796875</v>
+        <v>2.67694115638733</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>4.49599981307983</v>
       </c>
       <c r="G436" t="n">
-        <v>2.67218589782715</v>
+        <v>2.67218613624573</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>4.45599985122681</v>
       </c>
       <c r="G437" t="n">
-        <v>2.64841246604919</v>
+        <v>2.64841222763062</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>4.57800006866455</v>
       </c>
       <c r="G439" t="n">
-        <v>2.72092270851135</v>
+        <v>2.72092318534851</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>4.72800016403198</v>
       </c>
       <c r="G440" t="n">
-        <v>2.81007480621338</v>
+        <v>2.81007528305054</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G441" t="n">
-        <v>2.86475491523743</v>
+        <v>2.86475467681885</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G443" t="n">
-        <v>2.95390725135803</v>
+        <v>2.95390653610229</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>4.85599994659424</v>
       </c>
       <c r="G444" t="n">
-        <v>2.88615155220032</v>
+        <v>2.88615131378174</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>4.78399991989136</v>
       </c>
       <c r="G445" t="n">
-        <v>2.84335827827454</v>
+        <v>2.84335803985596</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>4.78399991989136</v>
       </c>
       <c r="G446" t="n">
-        <v>2.84335827827454</v>
+        <v>2.84335803985596</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>4.73199987411499</v>
       </c>
       <c r="G447" t="n">
-        <v>2.81245231628418</v>
+        <v>2.81245183944702</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>4.81199979782104</v>
       </c>
       <c r="G449" t="n">
-        <v>2.8600001335144</v>
+        <v>2.85999989509583</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>4.77400016784668</v>
       </c>
       <c r="G450" t="n">
-        <v>2.83741497993469</v>
+        <v>2.83741521835327</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G451" t="n">
-        <v>2.8944718837738</v>
+        <v>2.89447236061096</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>4.84600019454956</v>
       </c>
       <c r="G452" t="n">
-        <v>2.88020825386047</v>
+        <v>2.88020777702332</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>4.80399990081787</v>
       </c>
       <c r="G453" t="n">
-        <v>2.85524535179138</v>
+        <v>2.8552451133728</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>4.87799978256226</v>
       </c>
       <c r="G455" t="n">
-        <v>2.89922690391541</v>
+        <v>2.89922714233398</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>4.92399978637695</v>
       </c>
       <c r="G456" t="n">
-        <v>2.92656660079956</v>
+        <v>2.92656683921814</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G459" t="n">
-        <v>3.03711557388306</v>
+        <v>3.03711581230164</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G460" t="n">
-        <v>3.04305934906006</v>
+        <v>3.04305863380432</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G462" t="n">
-        <v>3.0133421421051</v>
+        <v>3.01334166526794</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G463" t="n">
-        <v>3.0490026473999</v>
+        <v>3.04900288581848</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G464" t="n">
-        <v>3.04305934906006</v>
+        <v>3.04305863380432</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>4.98600006103516</v>
       </c>
       <c r="G465" t="n">
-        <v>2.96341633796692</v>
+        <v>2.9634165763855</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>5.25</v>
       </c>
       <c r="G468" t="n">
-        <v>3.12032413482666</v>
+        <v>3.12032437324524</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G469" t="n">
-        <v>3.16787195205688</v>
+        <v>3.16787171363831</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>5.25</v>
       </c>
       <c r="G470" t="n">
-        <v>3.12032413482666</v>
+        <v>3.12032437324524</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G471" t="n">
-        <v>3.16192841529846</v>
+        <v>3.16192865371704</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G472" t="n">
-        <v>3.21541976928711</v>
+        <v>3.21541953086853</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G473" t="n">
-        <v>3.16787195205688</v>
+        <v>3.16787171363831</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G474" t="n">
-        <v>3.16787195205688</v>
+        <v>3.16787171363831</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G475" t="n">
-        <v>3.15004205703735</v>
+        <v>3.15004181861877</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G476" t="n">
-        <v>3.13518309593201</v>
+        <v>3.13518285751343</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G477" t="n">
-        <v>3.15004205703735</v>
+        <v>3.15004181861877</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G478" t="n">
-        <v>3.09060668945312</v>
+        <v>3.0906069278717</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G479" t="n">
-        <v>3.07872009277344</v>
+        <v>3.07871985435486</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>5.24499988555908</v>
       </c>
       <c r="G480" t="n">
-        <v>3.11735224723816</v>
+        <v>3.11735248565674</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G481" t="n">
-        <v>3.14409804344177</v>
+        <v>3.14409828186035</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G482" t="n">
-        <v>3.15004205703735</v>
+        <v>3.15004181861877</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G484" t="n">
-        <v>3.17381548881531</v>
+        <v>3.17381572723389</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G486" t="n">
-        <v>3.16787195205688</v>
+        <v>3.16787171363831</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G488" t="n">
-        <v>3.19164562225342</v>
+        <v>3.191645860672</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>5.49499988555908</v>
       </c>
       <c r="G491" t="n">
-        <v>3.26593947410583</v>
+        <v>3.26593899726868</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>5.57499980926514</v>
       </c>
       <c r="G492" t="n">
-        <v>3.31348752975464</v>
+        <v>3.31348657608032</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G493" t="n">
-        <v>3.28079843521118</v>
+        <v>3.28079795837402</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G494" t="n">
-        <v>3.29862880706787</v>
+        <v>3.29862833023071</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G495" t="n">
-        <v>3.29862880706787</v>
+        <v>3.29862833023071</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G496" t="n">
-        <v>3.29268503189087</v>
+        <v>3.29268527030945</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>5.625</v>
       </c>
       <c r="G499" t="n">
-        <v>3.34320449829102</v>
+        <v>3.34320425987244</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>5.60500001907349</v>
       </c>
       <c r="G500" t="n">
-        <v>3.33131766319275</v>
+        <v>3.33131790161133</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>4.96500015258789</v>
       </c>
       <c r="G503" t="n">
-        <v>3.27646851539612</v>
+        <v>3.2764687538147</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G506" t="n">
-        <v>3.3853542804718</v>
+        <v>3.38535451889038</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G507" t="n">
-        <v>3.33256077766418</v>
+        <v>3.33256149291992</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G508" t="n">
-        <v>3.32596158981323</v>
+        <v>3.32596206665039</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G509" t="n">
-        <v>3.31936287879944</v>
+        <v>3.31936311721802</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G510" t="n">
-        <v>3.34575939178467</v>
+        <v>3.34575891494751</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G512" t="n">
-        <v>3.40515112876892</v>
+        <v>3.4051513671875</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G513" t="n">
-        <v>3.39195275306702</v>
+        <v>3.39195322990417</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G514" t="n">
-        <v>3.36555647850037</v>
+        <v>3.36555671691895</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G518" t="n">
-        <v>3.49093961715698</v>
+        <v>3.49093985557556</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>5.25</v>
       </c>
       <c r="G522" t="n">
-        <v>3.46454381942749</v>
+        <v>3.46454358100891</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G523" t="n">
-        <v>3.43154788017273</v>
+        <v>3.43154764175415</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G524" t="n">
-        <v>3.39855194091797</v>
+        <v>3.39855241775513</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G525" t="n">
-        <v>3.3853542804718</v>
+        <v>3.38535451889038</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G527" t="n">
-        <v>3.33256077766418</v>
+        <v>3.33256149291992</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G529" t="n">
-        <v>3.27976751327515</v>
+        <v>3.2797679901123</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>5</v>
       </c>
       <c r="G530" t="n">
-        <v>3.29956531524658</v>
+        <v>3.299565076828</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>4.9850001335144</v>
       </c>
       <c r="G532" t="n">
-        <v>3.28966641426086</v>
+        <v>3.28966665267944</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>4.9850001335144</v>
       </c>
       <c r="G533" t="n">
-        <v>3.28966641426086</v>
+        <v>3.28966665267944</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G534" t="n">
-        <v>3.27316832542419</v>
+        <v>3.27316880226135</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G535" t="n">
-        <v>3.30616402626038</v>
+        <v>3.30616450309753</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G537" t="n">
-        <v>3.14778542518616</v>
+        <v>3.147784948349</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G539" t="n">
-        <v>3.22037577629089</v>
+        <v>3.22037529945374</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G540" t="n">
-        <v>3.2038779258728</v>
+        <v>3.20387744903564</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>4.81500005722046</v>
       </c>
       <c r="G541" t="n">
-        <v>3.17748141288757</v>
+        <v>3.17748093605042</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G542" t="n">
-        <v>3.2038779258728</v>
+        <v>3.20387744903564</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>4.77500009536743</v>
       </c>
       <c r="G543" t="n">
-        <v>3.15108489990234</v>
+        <v>3.15108466148376</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>4.9850001335144</v>
       </c>
       <c r="G546" t="n">
-        <v>3.28966641426086</v>
+        <v>3.28966665267944</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G547" t="n">
-        <v>3.31936287879944</v>
+        <v>3.31936311721802</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>4.94500017166138</v>
       </c>
       <c r="G551" t="n">
-        <v>3.26327013969421</v>
+        <v>3.26327061653137</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>4.96500015258789</v>
       </c>
       <c r="G552" t="n">
-        <v>3.27646851539612</v>
+        <v>3.2764687538147</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>4.93499994277954</v>
       </c>
       <c r="G553" t="n">
-        <v>3.25667095184326</v>
+        <v>3.25667071342468</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G554" t="n">
-        <v>3.24017310142517</v>
+        <v>3.24017286300659</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>4.94500017166138</v>
       </c>
       <c r="G555" t="n">
-        <v>3.26327013969421</v>
+        <v>3.26327061653137</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G557" t="n">
-        <v>3.31936287879944</v>
+        <v>3.31936311721802</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G560" t="n">
-        <v>3.22037577629089</v>
+        <v>3.22037529945374</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G561" t="n">
-        <v>3.20717763900757</v>
+        <v>3.20717740058899</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G562" t="n">
-        <v>3.21377635002136</v>
+        <v>3.21377658843994</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G564" t="n">
-        <v>3.25997042655945</v>
+        <v>3.25997066497803</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>4.94500017166138</v>
       </c>
       <c r="G565" t="n">
-        <v>3.26327013969421</v>
+        <v>3.26327061653137</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>5</v>
       </c>
       <c r="G566" t="n">
-        <v>3.29956531524658</v>
+        <v>3.299565076828</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G567" t="n">
-        <v>3.33256077766418</v>
+        <v>3.33256149291992</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G568" t="n">
-        <v>3.33915996551514</v>
+        <v>3.33916020393372</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G570" t="n">
-        <v>3.33256077766418</v>
+        <v>3.33256149291992</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G572" t="n">
-        <v>3.36555647850037</v>
+        <v>3.36555671691895</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G573" t="n">
-        <v>3.34575939178467</v>
+        <v>3.34575891494751</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G574" t="n">
-        <v>3.32596158981323</v>
+        <v>3.32596206665039</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G576" t="n">
-        <v>3.31936287879944</v>
+        <v>3.31936311721802</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G581" t="n">
-        <v>3.22037577629089</v>
+        <v>3.22037529945374</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G585" t="n">
-        <v>3.22697448730469</v>
+        <v>3.22697472572327</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>4.96500015258789</v>
       </c>
       <c r="G587" t="n">
-        <v>3.27646851539612</v>
+        <v>3.2764687538147</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G588" t="n">
-        <v>3.23027467727661</v>
+        <v>3.23027420043945</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G589" t="n">
-        <v>3.2038779258728</v>
+        <v>3.20387744903564</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G590" t="n">
-        <v>3.27316832542419</v>
+        <v>3.27316880226135</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>4.96500015258789</v>
       </c>
       <c r="G591" t="n">
-        <v>3.27646851539612</v>
+        <v>3.2764687538147</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G592" t="n">
-        <v>3.20717763900757</v>
+        <v>3.20717740058899</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G593" t="n">
-        <v>2.98610663414001</v>
+        <v>2.98610687255859</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G594" t="n">
-        <v>2.93001413345337</v>
+        <v>2.93001389503479</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G595" t="n">
-        <v>3.00920343399048</v>
+        <v>3.00920367240906</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G597" t="n">
-        <v>3.03559970855713</v>
+        <v>3.03559994697571</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>4.7350001335144</v>
       </c>
       <c r="G598" t="n">
-        <v>3.12468838691711</v>
+        <v>3.12468814849854</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G599" t="n">
-        <v>2.99930453300476</v>
+        <v>2.99930500984192</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G601" t="n">
-        <v>3.03559970855713</v>
+        <v>3.03559994697571</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G602" t="n">
-        <v>2.99930453300476</v>
+        <v>2.99930500984192</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G603" t="n">
-        <v>3.00260472297668</v>
+        <v>3.00260424613953</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G604" t="n">
-        <v>3.0224015712738</v>
+        <v>3.02240180969238</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G605" t="n">
-        <v>3.01580238342285</v>
+        <v>3.01580286026001</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G606" t="n">
-        <v>3.03230023384094</v>
+        <v>3.03230047225952</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G609" t="n">
-        <v>3.06859564781189</v>
+        <v>3.06859588623047</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G610" t="n">
-        <v>3.06859564781189</v>
+        <v>3.06859588623047</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G611" t="n">
-        <v>3.08839297294617</v>
+        <v>3.08839321136475</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>4.75</v>
       </c>
       <c r="G613" t="n">
-        <v>3.13458681106567</v>
+        <v>3.13458728790283</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G614" t="n">
-        <v>3.17418169975281</v>
+        <v>3.17418146133423</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G615" t="n">
-        <v>3.17418169975281</v>
+        <v>3.17418146133423</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G616" t="n">
-        <v>3.1576840877533</v>
+        <v>3.15768361091614</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G617" t="n">
-        <v>3.20717763900757</v>
+        <v>3.20717740058899</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G618" t="n">
-        <v>3.18737983703613</v>
+        <v>3.18738007545471</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G619" t="n">
-        <v>3.15438437461853</v>
+        <v>3.15438461303711</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>4.81500005722046</v>
       </c>
       <c r="G622" t="n">
-        <v>3.17748141288757</v>
+        <v>3.17748093605042</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G623" t="n">
-        <v>3.16758298873901</v>
+        <v>3.16758251190186</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>4.77500009536743</v>
       </c>
       <c r="G624" t="n">
-        <v>3.15108489990234</v>
+        <v>3.15108466148376</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G626" t="n">
-        <v>3.1576840877533</v>
+        <v>3.15768361091614</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G627" t="n">
-        <v>3.17418169975281</v>
+        <v>3.17418146133423</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G628" t="n">
-        <v>3.1576840877533</v>
+        <v>3.15768361091614</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G630" t="n">
-        <v>3.10159134864807</v>
+        <v>3.10159111022949</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>4.75</v>
       </c>
       <c r="G632" t="n">
-        <v>3.13458681106567</v>
+        <v>3.13458728790283</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G633" t="n">
-        <v>3.16758298873901</v>
+        <v>3.16758251190186</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G635" t="n">
-        <v>3.20057797431946</v>
+        <v>3.20057845115662</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G638" t="n">
-        <v>3.31936287879944</v>
+        <v>3.31936311721802</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G640" t="n">
-        <v>3.33915996551514</v>
+        <v>3.33916020393372</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>5.25</v>
       </c>
       <c r="G641" t="n">
-        <v>3.46454381942749</v>
+        <v>3.46454358100891</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G643" t="n">
-        <v>3.48434090614319</v>
+        <v>3.48434066772461</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G644" t="n">
-        <v>3.55033254623413</v>
+        <v>3.55033206939697</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G645" t="n">
-        <v>3.54373288154602</v>
+        <v>3.54373240470886</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G646" t="n">
-        <v>3.53053498268127</v>
+        <v>3.53053402900696</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G647" t="n">
-        <v>3.5569314956665</v>
+        <v>3.55693101882935</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G648" t="n">
-        <v>3.59652614593506</v>
+        <v>3.59652590751648</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G649" t="n">
-        <v>3.61632299423218</v>
+        <v>3.61632347106934</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G650" t="n">
-        <v>3.58332800865173</v>
+        <v>3.58332753181458</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G651" t="n">
-        <v>3.58332800865173</v>
+        <v>3.58332753181458</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G652" t="n">
-        <v>3.60972428321838</v>
+        <v>3.60972380638123</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G653" t="n">
-        <v>3.60972428321838</v>
+        <v>3.60972380638123</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G654" t="n">
-        <v>3.60972428321838</v>
+        <v>3.60972380638123</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G655" t="n">
-        <v>3.56353068351746</v>
+        <v>3.56353044509888</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>5.5</v>
       </c>
       <c r="G656" t="n">
-        <v>3.6295223236084</v>
+        <v>3.62952160835266</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G657" t="n">
-        <v>3.53053498268127</v>
+        <v>3.53053402900696</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G658" t="n">
-        <v>3.48434090614319</v>
+        <v>3.48434066772461</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G659" t="n">
-        <v>3.53053498268127</v>
+        <v>3.53053402900696</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G660" t="n">
-        <v>3.53053498268127</v>
+        <v>3.53053402900696</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G662" t="n">
-        <v>3.56353068351746</v>
+        <v>3.56353044509888</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G663" t="n">
-        <v>3.51733660697937</v>
+        <v>3.51733613014221</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G665" t="n">
-        <v>3.4447455406189</v>
+        <v>3.44474601745605</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G667" t="n">
-        <v>3.53053498268127</v>
+        <v>3.53053402900696</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G668" t="n">
-        <v>3.5569314956665</v>
+        <v>3.55693101882935</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G669" t="n">
-        <v>3.57012891769409</v>
+        <v>3.57012963294983</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G670" t="n">
-        <v>3.5767285823822</v>
+        <v>3.57672882080078</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G671" t="n">
-        <v>3.60972428321838</v>
+        <v>3.60972380638123</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G672" t="n">
-        <v>3.60312509536743</v>
+        <v>3.60312533378601</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G673" t="n">
-        <v>3.54373288154602</v>
+        <v>3.54373240470886</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G674" t="n">
-        <v>3.53053498268127</v>
+        <v>3.53053402900696</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G675" t="n">
-        <v>3.53713345527649</v>
+        <v>3.53713369369507</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G676" t="n">
-        <v>3.55033254623413</v>
+        <v>3.55033206939697</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G677" t="n">
-        <v>3.57012891769409</v>
+        <v>3.57012963294983</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G678" t="n">
-        <v>3.51733660697937</v>
+        <v>3.51733613014221</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G679" t="n">
-        <v>3.49753928184509</v>
+        <v>3.49753904342651</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G680" t="n">
-        <v>3.54373288154602</v>
+        <v>3.54373240470886</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G681" t="n">
-        <v>3.53053498268127</v>
+        <v>3.53053402900696</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G683" t="n">
-        <v>3.49093961715698</v>
+        <v>3.49093985557556</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G685" t="n">
-        <v>3.55033254623413</v>
+        <v>3.55033206939697</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G686" t="n">
-        <v>3.53053498268127</v>
+        <v>3.53053402900696</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G687" t="n">
-        <v>3.51733660697937</v>
+        <v>3.51733613014221</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G688" t="n">
-        <v>3.49753928184509</v>
+        <v>3.49753904342651</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G691" t="n">
-        <v>3.54373288154602</v>
+        <v>3.54373240470886</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G693" t="n">
-        <v>3.49753928184509</v>
+        <v>3.49753904342651</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G694" t="n">
-        <v>3.53053498268127</v>
+        <v>3.53053402900696</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G695" t="n">
-        <v>3.53713345527649</v>
+        <v>3.53713369369507</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G696" t="n">
-        <v>3.5569314956665</v>
+        <v>3.55693101882935</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G697" t="n">
-        <v>3.53053498268127</v>
+        <v>3.53053402900696</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G698" t="n">
-        <v>3.51733660697937</v>
+        <v>3.51733613014221</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G699" t="n">
-        <v>3.5569314956665</v>
+        <v>3.55693101882935</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G700" t="n">
-        <v>3.56353068351746</v>
+        <v>3.56353044509888</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G701" t="n">
-        <v>3.53713345527649</v>
+        <v>3.53713369369507</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G702" t="n">
-        <v>3.58992695808411</v>
+        <v>3.58992671966553</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>5.5</v>
       </c>
       <c r="G703" t="n">
-        <v>3.6295223236084</v>
+        <v>3.62952160835266</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G705" t="n">
-        <v>3.72850894927979</v>
+        <v>3.72850847244263</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G706" t="n">
-        <v>3.74170684814453</v>
+        <v>3.74170708656311</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>5.75</v>
       </c>
       <c r="G707" t="n">
-        <v>3.79449963569641</v>
+        <v>3.79449939727783</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>5.75</v>
       </c>
       <c r="G708" t="n">
-        <v>3.79449963569641</v>
+        <v>3.79449939727783</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G709" t="n">
-        <v>3.80769824981689</v>
+        <v>3.80769801139832</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G713" t="n">
-        <v>3.68891406059265</v>
+        <v>3.68891382217407</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G718" t="n">
-        <v>3.78790092468262</v>
+        <v>3.78790044784546</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G720" t="n">
-        <v>3.82749557495117</v>
+        <v>3.82749581336975</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G721" t="n">
-        <v>3.82749557495117</v>
+        <v>3.82749581336975</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G723" t="n">
-        <v>3.93308210372925</v>
+        <v>3.93308138847351</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G724" t="n">
-        <v>3.93308210372925</v>
+        <v>3.93308138847351</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G726" t="n">
-        <v>4.04526710510254</v>
+        <v>4.04526662826538</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G727" t="n">
-        <v>3.99247431755066</v>
+        <v>3.99247407913208</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G728" t="n">
-        <v>3.76150417327881</v>
+        <v>3.76150441169739</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G729" t="n">
-        <v>3.72190952301025</v>
+        <v>3.72190928459167</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G730" t="n">
-        <v>3.84729337692261</v>
+        <v>3.84729313850403</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G731" t="n">
-        <v>3.75490546226501</v>
+        <v>3.75490570068359</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G732" t="n">
-        <v>3.64931893348694</v>
+        <v>3.6493194103241</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G733" t="n">
-        <v>3.48434090614319</v>
+        <v>3.48434066772461</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G734" t="n">
-        <v>3.5569314956665</v>
+        <v>3.55693101882935</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G738" t="n">
-        <v>3.06859564781189</v>
+        <v>3.06859588623047</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>4.625</v>
       </c>
       <c r="G740" t="n">
-        <v>3.05209755897522</v>
+        <v>3.05209803581238</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>4.17500019073486</v>
       </c>
       <c r="G741" t="n">
-        <v>2.7551372051239</v>
+        <v>2.75513696670532</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G742" t="n">
-        <v>2.90361714363098</v>
+        <v>2.90361762046814</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G743" t="n">
-        <v>2.76503586769104</v>
+        <v>2.76503562927246</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>4.14499998092651</v>
       </c>
       <c r="G744" t="n">
-        <v>2.73533916473389</v>
+        <v>2.73533964157104</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>4.07499980926514</v>
       </c>
       <c r="G745" t="n">
-        <v>2.68914532661438</v>
+        <v>2.68914556503296</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>4.27500009536743</v>
       </c>
       <c r="G746" t="n">
-        <v>2.82112812995911</v>
+        <v>2.82112836837769</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>4.65500020980835</v>
       </c>
       <c r="G747" t="n">
-        <v>3.07189512252808</v>
+        <v>3.07189559936523</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>4.75</v>
       </c>
       <c r="G749" t="n">
-        <v>3.13458681106567</v>
+        <v>3.13458728790283</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G750" t="n">
-        <v>3.06859564781189</v>
+        <v>3.06859588623047</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>4.69500017166138</v>
       </c>
       <c r="G751" t="n">
-        <v>3.09829163551331</v>
+        <v>3.09829187393188</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G752" t="n">
-        <v>3.16758298873901</v>
+        <v>3.16758251190186</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G754" t="n">
-        <v>3.12138891220093</v>
+        <v>3.12138867378235</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G755" t="n">
-        <v>3.11808896064758</v>
+        <v>3.11808919906616</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G756" t="n">
-        <v>3.04879808425903</v>
+        <v>3.04879832267761</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G757" t="n">
-        <v>3.01580238342285</v>
+        <v>3.01580286026001</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G758" t="n">
-        <v>3.10159134864807</v>
+        <v>3.10159111022949</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>5</v>
       </c>
       <c r="G759" t="n">
-        <v>3.29956531524658</v>
+        <v>3.299565076828</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G760" t="n">
-        <v>3.33915996551514</v>
+        <v>3.33916020393372</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G761" t="n">
-        <v>3.36555647850037</v>
+        <v>3.36555671691895</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G762" t="n">
-        <v>3.25997042655945</v>
+        <v>3.25997066497803</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G765" t="n">
-        <v>3.08839297294617</v>
+        <v>3.08839321136475</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G767" t="n">
-        <v>3.11808896064758</v>
+        <v>3.11808919906616</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G768" t="n">
-        <v>3.11478924751282</v>
+        <v>3.11478900909424</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G769" t="n">
-        <v>3.11808896064758</v>
+        <v>3.11808919906616</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G770" t="n">
-        <v>3.10159134864807</v>
+        <v>3.10159111022949</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G771" t="n">
-        <v>3.1576840877533</v>
+        <v>3.15768361091614</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G772" t="n">
-        <v>3.24017310142517</v>
+        <v>3.24017286300659</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G773" t="n">
-        <v>3.24017310142517</v>
+        <v>3.24017286300659</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>4.71500015258789</v>
       </c>
       <c r="G774" t="n">
-        <v>3.11149024963379</v>
+        <v>3.11149001121521</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G775" t="n">
-        <v>3.00260472297668</v>
+        <v>3.00260424613953</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G776" t="n">
-        <v>2.99600553512573</v>
+        <v>2.99600529670715</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G777" t="n">
-        <v>3.06199669837952</v>
+        <v>3.06199645996094</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G778" t="n">
-        <v>2.98280668258667</v>
+        <v>2.98280692100525</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>4.82499980926514</v>
       </c>
       <c r="G779" t="n">
-        <v>3.18408060073853</v>
+        <v>3.18408012390137</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G780" t="n">
-        <v>3.17418169975281</v>
+        <v>3.17418146133423</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>4.75</v>
       </c>
       <c r="G781" t="n">
-        <v>3.13458681106567</v>
+        <v>3.13458728790283</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>4.84499979019165</v>
       </c>
       <c r="G783" t="n">
-        <v>3.19727826118469</v>
+        <v>3.19727897644043</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G784" t="n">
-        <v>3.22697448730469</v>
+        <v>3.22697472572327</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G785" t="n">
-        <v>3.37875509262085</v>
+        <v>3.37875485420227</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G786" t="n">
-        <v>3.36555647850037</v>
+        <v>3.36555671691895</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G789" t="n">
-        <v>3.30616402626038</v>
+        <v>3.30616450309753</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G790" t="n">
-        <v>3.33256077766418</v>
+        <v>3.33256149291992</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G792" t="n">
-        <v>3.4447455406189</v>
+        <v>3.44474601745605</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G798" t="n">
-        <v>3.37875509262085</v>
+        <v>3.37875485420227</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G799" t="n">
-        <v>3.40515112876892</v>
+        <v>3.4051513671875</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G800" t="n">
-        <v>3.37875509262085</v>
+        <v>3.37875485420227</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>5</v>
       </c>
       <c r="G801" t="n">
-        <v>3.29956531524658</v>
+        <v>3.299565076828</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>5</v>
       </c>
       <c r="G802" t="n">
-        <v>3.29956531524658</v>
+        <v>3.299565076828</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>4.79500007629395</v>
       </c>
       <c r="G803" t="n">
-        <v>3.16428279876709</v>
+        <v>3.16428303718567</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G804" t="n">
-        <v>3.11808896064758</v>
+        <v>3.11808919906616</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G805" t="n">
-        <v>3.10159134864807</v>
+        <v>3.10159111022949</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G806" t="n">
-        <v>3.16758298873901</v>
+        <v>3.16758251190186</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>4.7649998664856</v>
       </c>
       <c r="G810" t="n">
-        <v>3.14448523521423</v>
+        <v>3.14448547363281</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G811" t="n">
-        <v>3.21377635002136</v>
+        <v>3.21377658843994</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>4.7649998664856</v>
       </c>
       <c r="G813" t="n">
-        <v>3.14448523521423</v>
+        <v>3.14448547363281</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G816" t="n">
-        <v>3.33915996551514</v>
+        <v>3.33916020393372</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G817" t="n">
-        <v>3.33915996551514</v>
+        <v>3.33916020393372</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G819" t="n">
-        <v>3.42494869232178</v>
+        <v>3.4249484539032</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G820" t="n">
-        <v>3.39855194091797</v>
+        <v>3.39855241775513</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G821" t="n">
-        <v>3.36555647850037</v>
+        <v>3.36555671691895</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G822" t="n">
-        <v>3.3853542804718</v>
+        <v>3.38535451889038</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G823" t="n">
-        <v>3.39195275306702</v>
+        <v>3.39195322990417</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G824" t="n">
-        <v>3.39855194091797</v>
+        <v>3.39855241775513</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G825" t="n">
-        <v>3.31936287879944</v>
+        <v>3.31936311721802</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G827" t="n">
-        <v>3.27976751327515</v>
+        <v>3.2797679901123</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G828" t="n">
-        <v>3.32596158981323</v>
+        <v>3.32596206665039</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G829" t="n">
-        <v>3.30616402626038</v>
+        <v>3.30616450309753</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>5</v>
       </c>
       <c r="G831" t="n">
-        <v>3.29956531524658</v>
+        <v>3.299565076828</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G832" t="n">
-        <v>3.33915996551514</v>
+        <v>3.33916020393372</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>5</v>
       </c>
       <c r="G833" t="n">
-        <v>3.29956531524658</v>
+        <v>3.299565076828</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>4.91499996185303</v>
       </c>
       <c r="G834" t="n">
-        <v>3.24347233772278</v>
+        <v>3.24347257614136</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G835" t="n">
-        <v>3.22697448730469</v>
+        <v>3.22697472572327</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>4.81500005722046</v>
       </c>
       <c r="G839" t="n">
-        <v>3.17748141288757</v>
+        <v>3.17748093605042</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G843" t="n">
-        <v>3.16758298873901</v>
+        <v>3.16758251190186</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G845" t="n">
-        <v>3.16758298873901</v>
+        <v>3.16758251190186</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G846" t="n">
-        <v>3.14778542518616</v>
+        <v>3.147784948349</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G848" t="n">
-        <v>3.14778542518616</v>
+        <v>3.147784948349</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>4.75</v>
       </c>
       <c r="G849" t="n">
-        <v>3.13458681106567</v>
+        <v>3.13458728790283</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>4.68499994277954</v>
       </c>
       <c r="G850" t="n">
-        <v>3.09169244766235</v>
+        <v>3.09169268608093</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>4.61499977111816</v>
       </c>
       <c r="G851" t="n">
-        <v>3.04549884796143</v>
+        <v>3.04549860954285</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G852" t="n">
-        <v>3.06859564781189</v>
+        <v>3.06859588623047</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G853" t="n">
-        <v>3.0224015712738</v>
+        <v>3.02240180969238</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G855" t="n">
-        <v>3.06199669837952</v>
+        <v>3.06199645996094</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G858" t="n">
-        <v>3.06859564781189</v>
+        <v>3.06859588623047</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G859" t="n">
-        <v>3.12798738479614</v>
+        <v>3.12798762321472</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>4.65500020980835</v>
       </c>
       <c r="G860" t="n">
-        <v>3.07189512252808</v>
+        <v>3.07189559936523</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G861" t="n">
-        <v>3.03230023384094</v>
+        <v>3.03230047225952</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G863" t="n">
-        <v>3.00590372085571</v>
+        <v>3.00590395927429</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G864" t="n">
-        <v>2.98610663414001</v>
+        <v>2.98610687255859</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>4.5149998664856</v>
       </c>
       <c r="G866" t="n">
-        <v>2.97950744628906</v>
+        <v>2.97950720787048</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>4.625</v>
       </c>
       <c r="G867" t="n">
-        <v>3.05209755897522</v>
+        <v>3.05209803581238</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>4.625</v>
       </c>
       <c r="G868" t="n">
-        <v>3.05209755897522</v>
+        <v>3.05209803581238</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G870" t="n">
-        <v>3.06199669837952</v>
+        <v>3.06199645996094</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G872" t="n">
-        <v>3.06859564781189</v>
+        <v>3.06859588623047</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>4.7649998664856</v>
       </c>
       <c r="G873" t="n">
-        <v>3.14448523521423</v>
+        <v>3.14448547363281</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>4.7649998664856</v>
       </c>
       <c r="G877" t="n">
-        <v>3.14448523521423</v>
+        <v>3.14448547363281</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>4.7649998664856</v>
       </c>
       <c r="G878" t="n">
-        <v>3.14448523521423</v>
+        <v>3.14448547363281</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G880" t="n">
-        <v>3.15438437461853</v>
+        <v>3.15438461303711</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G884" t="n">
-        <v>3.20717763900757</v>
+        <v>3.20717740058899</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G885" t="n">
-        <v>3.22697448730469</v>
+        <v>3.22697472572327</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G886" t="n">
-        <v>3.33256077766418</v>
+        <v>3.33256149291992</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>4.93499994277954</v>
       </c>
       <c r="G887" t="n">
-        <v>3.25667095184326</v>
+        <v>3.25667071342468</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>4.84499979019165</v>
       </c>
       <c r="G888" t="n">
-        <v>3.19727826118469</v>
+        <v>3.19727897644043</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G889" t="n">
-        <v>3.17418169975281</v>
+        <v>3.17418146133423</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>4.81500005722046</v>
       </c>
       <c r="G890" t="n">
-        <v>3.17748141288757</v>
+        <v>3.17748093605042</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G891" t="n">
-        <v>3.08839297294617</v>
+        <v>3.08839321136475</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G895" t="n">
-        <v>2.91681551933289</v>
+        <v>2.91681575775146</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G896" t="n">
-        <v>2.90361714363098</v>
+        <v>2.90361762046814</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G898" t="n">
-        <v>2.84422516822815</v>
+        <v>2.84422540664673</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G899" t="n">
-        <v>2.81122994422913</v>
+        <v>2.81122970581055</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>3.97499990463257</v>
       </c>
       <c r="G902" t="n">
-        <v>2.62315440177917</v>
+        <v>2.6231541633606</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G903" t="n">
-        <v>2.61985445022583</v>
+        <v>2.61985492706299</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>3.95499992370605</v>
       </c>
       <c r="G904" t="n">
-        <v>2.60995626449585</v>
+        <v>2.60995602607727</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G905" t="n">
-        <v>2.58685946464539</v>
+        <v>2.58685898780823</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>4.31500005722046</v>
       </c>
       <c r="G910" t="n">
-        <v>2.84752488136292</v>
+        <v>2.84752511978149</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G912" t="n">
-        <v>3.00260472297668</v>
+        <v>3.00260424613953</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G913" t="n">
-        <v>2.89041924476624</v>
+        <v>2.89041948318481</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>4.5</v>
       </c>
       <c r="G915" t="n">
-        <v>2.96960830688477</v>
+        <v>2.9696090221405</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G916" t="n">
-        <v>3.00590372085571</v>
+        <v>3.00590395927429</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G918" t="n">
-        <v>3.00260472297668</v>
+        <v>3.00260424613953</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G919" t="n">
-        <v>3.03230023384094</v>
+        <v>3.03230047225952</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>4.61499977111816</v>
       </c>
       <c r="G921" t="n">
-        <v>3.04549884796143</v>
+        <v>3.04549860954285</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G922" t="n">
-        <v>3.14778542518616</v>
+        <v>3.147784948349</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>4.7649998664856</v>
       </c>
       <c r="G923" t="n">
-        <v>3.14448523521423</v>
+        <v>3.14448547363281</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G924" t="n">
-        <v>3.12138891220093</v>
+        <v>3.12138867378235</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G925" t="n">
-        <v>3.03559970855713</v>
+        <v>3.03559994697571</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G926" t="n">
-        <v>2.97620820999146</v>
+        <v>2.97620797157288</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G927" t="n">
-        <v>2.98610663414001</v>
+        <v>2.98610687255859</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G928" t="n">
-        <v>2.97290849685669</v>
+        <v>2.97290825843811</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G929" t="n">
-        <v>3.00590372085571</v>
+        <v>3.00590395927429</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>4.53499984741211</v>
       </c>
       <c r="G930" t="n">
-        <v>2.99270558357239</v>
+        <v>2.99270534515381</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G931" t="n">
-        <v>3.00920343399048</v>
+        <v>3.00920367240906</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G934" t="n">
-        <v>2.97620820999146</v>
+        <v>2.97620797157288</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G936" t="n">
-        <v>2.93001413345337</v>
+        <v>2.93001389503479</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G937" t="n">
-        <v>3.00590372085571</v>
+        <v>3.00590395927429</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G938" t="n">
-        <v>3.06199669837952</v>
+        <v>3.06199645996094</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>4.65500020980835</v>
       </c>
       <c r="G939" t="n">
-        <v>3.07189512252808</v>
+        <v>3.07189559936523</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>4.5</v>
       </c>
       <c r="G940" t="n">
-        <v>2.96960830688477</v>
+        <v>2.9696090221405</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G942" t="n">
-        <v>3.03559970855713</v>
+        <v>3.03559994697571</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G944" t="n">
-        <v>3.20057797431946</v>
+        <v>3.20057845115662</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G945" t="n">
-        <v>3.25997042655945</v>
+        <v>3.25997066497803</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>4.68499994277954</v>
       </c>
       <c r="G947" t="n">
-        <v>3.09169244766235</v>
+        <v>3.09169268608093</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>4.7350001335144</v>
       </c>
       <c r="G949" t="n">
-        <v>3.12468838691711</v>
+        <v>3.12468814849854</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>4.69500017166138</v>
       </c>
       <c r="G950" t="n">
-        <v>3.09829163551331</v>
+        <v>3.09829187393188</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G951" t="n">
-        <v>3.2038779258728</v>
+        <v>3.20387744903564</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G952" t="n">
-        <v>3.08839297294617</v>
+        <v>3.08839321136475</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>4.70499992370605</v>
       </c>
       <c r="G953" t="n">
-        <v>3.10489106178284</v>
+        <v>3.10489082336426</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G954" t="n">
-        <v>3.11808896064758</v>
+        <v>3.11808919906616</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G956" t="n">
-        <v>3.08839297294617</v>
+        <v>3.08839321136475</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G957" t="n">
-        <v>3.08839297294617</v>
+        <v>3.08839321136475</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>4.70499992370605</v>
       </c>
       <c r="G958" t="n">
-        <v>3.10489106178284</v>
+        <v>3.10489082336426</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G959" t="n">
-        <v>3.06859564781189</v>
+        <v>3.06859588623047</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G960" t="n">
-        <v>3.00260472297668</v>
+        <v>3.00260424613953</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G963" t="n">
-        <v>3.0224015712738</v>
+        <v>3.02240180969238</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G964" t="n">
-        <v>2.98610663414001</v>
+        <v>2.98610687255859</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G965" t="n">
-        <v>2.99930453300476</v>
+        <v>2.99930500984192</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G966" t="n">
-        <v>3.03559970855713</v>
+        <v>3.03559994697571</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G967" t="n">
-        <v>3.03559970855713</v>
+        <v>3.03559994697571</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G968" t="n">
-        <v>3.11478924751282</v>
+        <v>3.11478900909424</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G969" t="n">
-        <v>3.20057797431946</v>
+        <v>3.20057845115662</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G970" t="n">
-        <v>3.23027467727661</v>
+        <v>3.23027420043945</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G972" t="n">
-        <v>3.25337076187134</v>
+        <v>3.2533712387085</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G973" t="n">
-        <v>3.43154788017273</v>
+        <v>3.43154764175415</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G976" t="n">
-        <v>3.76150417327881</v>
+        <v>3.76150441169739</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G978" t="n">
-        <v>3.60312509536743</v>
+        <v>3.60312533378601</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G979" t="n">
-        <v>3.70211243629456</v>
+        <v>3.70211219787598</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G981" t="n">
-        <v>3.64272022247314</v>
+        <v>3.64271974563599</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G982" t="n">
-        <v>3.59652614593506</v>
+        <v>3.59652590751648</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G985" t="n">
-        <v>3.58992695808411</v>
+        <v>3.58992671966553</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G989" t="n">
-        <v>3.64272022247314</v>
+        <v>3.64271974563599</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G992" t="n">
-        <v>3.8208966255188</v>
+        <v>3.82089614868164</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G993" t="n">
-        <v>4.09146022796631</v>
+        <v>4.09146070480347</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>6.42999982833862</v>
       </c>
       <c r="G997" t="n">
-        <v>4.24324083328247</v>
+        <v>4.24324035644531</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>6.42999982833862</v>
       </c>
       <c r="G1000" t="n">
-        <v>4.24324083328247</v>
+        <v>4.24324035644531</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>6.3899998664856</v>
       </c>
       <c r="G1001" t="n">
-        <v>4.2168436050415</v>
+        <v>4.21684408187866</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G1003" t="n">
-        <v>4.26963758468628</v>
+        <v>4.26963710784912</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>6.5</v>
       </c>
       <c r="G1005" t="n">
-        <v>4.28943490982056</v>
+        <v>4.2894344329834</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G1008" t="n">
-        <v>4.14882183074951</v>
+        <v>4.14882135391235</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>6.52500009536743</v>
       </c>
       <c r="G1010" t="n">
-        <v>4.31755352020264</v>
+        <v>4.31755399703979</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G1011" t="n">
-        <v>4.40026521682739</v>
+        <v>4.40026569366455</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G1012" t="n">
-        <v>4.31424522399902</v>
+        <v>4.31424474716187</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>6.55499982833862</v>
       </c>
       <c r="G1013" t="n">
-        <v>4.33740472793579</v>
+        <v>4.33740377426147</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G1014" t="n">
-        <v>4.3605637550354</v>
+        <v>4.36056327819824</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>6.77500009536743</v>
       </c>
       <c r="G1015" t="n">
-        <v>4.48297739028931</v>
+        <v>4.48297691345215</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G1016" t="n">
-        <v>4.51937007904053</v>
+        <v>4.51937055587769</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G1017" t="n">
-        <v>4.52598714828491</v>
+        <v>4.52598762512207</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>7</v>
       </c>
       <c r="G1018" t="n">
-        <v>4.63185834884644</v>
+        <v>4.63185882568359</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>6.83500003814697</v>
       </c>
       <c r="G1019" t="n">
-        <v>4.52267837524414</v>
+        <v>4.5226788520813</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>6.75</v>
       </c>
       <c r="G1020" t="n">
-        <v>4.46643495559692</v>
+        <v>4.46643447875977</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G1021" t="n">
-        <v>4.51937007904053</v>
+        <v>4.51937055587769</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G1022" t="n">
-        <v>4.6847939491272</v>
+        <v>4.68479347229004</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>7.17500019073486</v>
       </c>
       <c r="G1023" t="n">
-        <v>4.7476544380188</v>
+        <v>4.74765491485596</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>7.39499998092651</v>
       </c>
       <c r="G1024" t="n">
-        <v>4.89322710037231</v>
+        <v>4.89322757720947</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G1025" t="n">
-        <v>4.8899188041687</v>
+        <v>4.88991832733154</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>7.55499982833862</v>
       </c>
       <c r="G1032" t="n">
-        <v>4.99909830093384</v>
+        <v>4.99909782409668</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1033" t="n">
-        <v>5.16121339797974</v>
+        <v>5.16121387481689</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>7.66499996185303</v>
       </c>
       <c r="G1034" t="n">
-        <v>5.07188510894775</v>
+        <v>5.0718846321106</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>7.61499977111816</v>
       </c>
       <c r="G1037" t="n">
-        <v>5.03879976272583</v>
+        <v>5.03879928588867</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>7.6100001335144</v>
       </c>
       <c r="G1038" t="n">
-        <v>5.03549146652222</v>
+        <v>5.03549194335938</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G1039" t="n">
-        <v>5.05534315109253</v>
+        <v>5.05534219741821</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>7.66499996185303</v>
       </c>
       <c r="G1040" t="n">
-        <v>5.07188510894775</v>
+        <v>5.0718846321106</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G1041" t="n">
-        <v>5.06195974349976</v>
+        <v>5.0619592666626</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1043" t="n">
-        <v>5.06857681274414</v>
+        <v>5.06857585906982</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>7.71500015258789</v>
       </c>
       <c r="G1044" t="n">
-        <v>5.1049690246582</v>
+        <v>5.10496997833252</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>7.625</v>
       </c>
       <c r="G1045" t="n">
-        <v>5.04541730880737</v>
+        <v>5.04541683197021</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G1046" t="n">
-        <v>5.05534315109253</v>
+        <v>5.05534219741821</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G1047" t="n">
-        <v>5.06195974349976</v>
+        <v>5.0619592666626</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G1049" t="n">
-        <v>5.08842754364014</v>
+        <v>5.08842706680298</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G1050" t="n">
-        <v>5.25385046005249</v>
+        <v>5.25385141372681</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>8</v>
       </c>
       <c r="G1051" t="n">
-        <v>5.29355239868164</v>
+        <v>5.29355192184448</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>7.93499994277954</v>
       </c>
       <c r="G1052" t="n">
-        <v>5.25054216384888</v>
+        <v>5.25054264068604</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1053" t="n">
-        <v>5.16121339797974</v>
+        <v>5.16121387481689</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>8.09000015258789</v>
       </c>
       <c r="G1056" t="n">
-        <v>5.35310506820679</v>
+        <v>5.35310459136963</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>8.13000011444092</v>
       </c>
       <c r="G1057" t="n">
-        <v>5.37957286834717</v>
+        <v>5.37957239151001</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G1060" t="n">
-        <v>5.38618898391724</v>
+        <v>5.38618946075439</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G1062" t="n">
-        <v>5.60454797744751</v>
+        <v>5.60454845428467</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>8.45499992370605</v>
       </c>
       <c r="G1068" t="n">
-        <v>5.59462308883667</v>
+        <v>5.59462261199951</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G1071" t="n">
-        <v>5.59131383895874</v>
+        <v>5.5913143157959</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G1075" t="n">
-        <v>5.57808065414429</v>
+        <v>5.57808113098145</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1077" t="n">
-        <v>5.50529432296753</v>
+        <v>5.50529384613037</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G1078" t="n">
-        <v>5.65086698532104</v>
+        <v>5.65086650848389</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G1080" t="n">
-        <v>5.57808065414429</v>
+        <v>5.57808113098145</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>7.95499992370605</v>
       </c>
       <c r="G1084" t="n">
-        <v>5.26377630233765</v>
+        <v>5.26377582550049</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>8.07499980926514</v>
       </c>
       <c r="G1085" t="n">
-        <v>5.34317970275879</v>
+        <v>5.34317922592163</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G1086" t="n">
-        <v>5.32663726806641</v>
+        <v>5.32663679122925</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>8.49499988555908</v>
       </c>
       <c r="G1087" t="n">
-        <v>5.62109088897705</v>
+        <v>5.62108993530273</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G1088" t="n">
-        <v>5.70380258560181</v>
+        <v>5.70380306243896</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1090" t="n">
-        <v>5.82290744781494</v>
+        <v>5.8229079246521</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>8.8100004196167</v>
       </c>
       <c r="G1093" t="n">
-        <v>5.82952451705933</v>
+        <v>5.82952499389648</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>8.86999988555908</v>
       </c>
       <c r="G1094" t="n">
-        <v>5.86922550201416</v>
+        <v>5.86922597885132</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>8.80500030517578</v>
       </c>
       <c r="G1095" t="n">
-        <v>5.82621669769287</v>
+        <v>5.82621574401855</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G1096" t="n">
-        <v>5.83614158630371</v>
+        <v>5.83614110946655</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>8.86999988555908</v>
       </c>
       <c r="G1097" t="n">
-        <v>5.86922550201416</v>
+        <v>5.86922597885132</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>8.05500030517578</v>
       </c>
       <c r="G1098" t="n">
-        <v>5.32994556427002</v>
+        <v>5.32994604110718</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G1100" t="n">
-        <v>4.94285488128662</v>
+        <v>4.94285440444946</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>7.7649998664856</v>
       </c>
       <c r="G1103" t="n">
-        <v>5.13805389404297</v>
+        <v>5.13805437088013</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>7.79500007629395</v>
       </c>
       <c r="G1104" t="n">
-        <v>5.15790462493896</v>
+        <v>5.15790510177612</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G1105" t="n">
-        <v>5.06195974349976</v>
+        <v>5.0619592666626</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G1106" t="n">
-        <v>5.05534315109253</v>
+        <v>5.05534219741821</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>7.71500015258789</v>
       </c>
       <c r="G1107" t="n">
-        <v>5.1049690246582</v>
+        <v>5.10496997833252</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>7.74499988555908</v>
       </c>
       <c r="G1108" t="n">
-        <v>5.12482023239136</v>
+        <v>5.1248197555542</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G1109" t="n">
-        <v>5.23399972915649</v>
+        <v>5.23399925231934</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>8</v>
       </c>
       <c r="G1111" t="n">
-        <v>5.29355239868164</v>
+        <v>5.29355192184448</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>7.85500001907349</v>
       </c>
       <c r="G1113" t="n">
-        <v>5.19760751724243</v>
+        <v>5.19760656356812</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>7.75</v>
       </c>
       <c r="G1114" t="n">
-        <v>5.12812852859497</v>
+        <v>5.12812900543213</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G1115" t="n">
-        <v>5.12151193618774</v>
+        <v>5.12151145935059</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>7.7649998664856</v>
       </c>
       <c r="G1116" t="n">
-        <v>5.13805389404297</v>
+        <v>5.13805437088013</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G1117" t="n">
-        <v>5.25385046005249</v>
+        <v>5.25385141372681</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G1118" t="n">
-        <v>5.18768167495728</v>
+        <v>5.18768119812012</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>7.91499996185303</v>
       </c>
       <c r="G1120" t="n">
-        <v>5.23730802536011</v>
+        <v>5.23730850219727</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>8</v>
       </c>
       <c r="G1121" t="n">
-        <v>5.29355239868164</v>
+        <v>5.29355192184448</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>8.05500030517578</v>
       </c>
       <c r="G1122" t="n">
-        <v>5.32994556427002</v>
+        <v>5.32994604110718</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>8.27499961853027</v>
       </c>
       <c r="G1123" t="n">
-        <v>5.47551774978638</v>
+        <v>5.47551822662354</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>8.01000022888184</v>
       </c>
       <c r="G1124" t="n">
-        <v>5.30016994476318</v>
+        <v>5.30016946792603</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>7.95499992370605</v>
       </c>
       <c r="G1129" t="n">
-        <v>5.26377630233765</v>
+        <v>5.26377582550049</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1133" t="n">
-        <v>5.41265773773193</v>
+        <v>5.41265726089478</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1134" t="n">
-        <v>5.49206113815308</v>
+        <v>5.49206018447876</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>8.04500007629395</v>
       </c>
       <c r="G1135" t="n">
-        <v>5.32332849502563</v>
+        <v>5.32332801818848</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>8.19499969482422</v>
       </c>
       <c r="G1136" t="n">
-        <v>5.42258214950562</v>
+        <v>5.42258262634277</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>8.57499980926514</v>
       </c>
       <c r="G1138" t="n">
-        <v>5.67402601242065</v>
+        <v>5.67402696609497</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1141" t="n">
-        <v>5.41265773773193</v>
+        <v>5.41265726089478</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G1142" t="n">
-        <v>5.38618898391724</v>
+        <v>5.38618946075439</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>8.17500019073486</v>
       </c>
       <c r="G1143" t="n">
-        <v>5.40934896469116</v>
+        <v>5.409348487854</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>7.16499996185303</v>
       </c>
       <c r="G1145" t="n">
-        <v>5.32360649108887</v>
+        <v>5.32360696792603</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>7.5</v>
       </c>
       <c r="G1148" t="n">
-        <v>5.57251214981079</v>
+        <v>5.57251167297363</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>7.74499988555908</v>
       </c>
       <c r="G1150" t="n">
-        <v>5.75454711914062</v>
+        <v>5.75454759597778</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1151" t="n">
-        <v>5.79541254043579</v>
+        <v>5.79541301727295</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>7.86999988555908</v>
       </c>
       <c r="G1154" t="n">
-        <v>5.84742259979248</v>
+        <v>5.84742307662964</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>7.7649998664856</v>
       </c>
       <c r="G1156" t="n">
-        <v>5.76940727233887</v>
+        <v>5.76940774917603</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>7.83500003814697</v>
       </c>
       <c r="G1159" t="n">
-        <v>5.82141780853271</v>
+        <v>5.82141733169556</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>7.66499996185303</v>
       </c>
       <c r="G1160" t="n">
-        <v>5.69510746002197</v>
+        <v>5.69510698318481</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>7.42500019073486</v>
       </c>
       <c r="G1161" t="n">
-        <v>5.51678657531738</v>
+        <v>5.5167875289917</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>7.53499984741211</v>
       </c>
       <c r="G1163" t="n">
-        <v>5.5985164642334</v>
+        <v>5.59851694107056</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>7.35500001907349</v>
       </c>
       <c r="G1164" t="n">
-        <v>5.46477651596069</v>
+        <v>5.46477699279785</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>7.32499980926514</v>
       </c>
       <c r="G1165" t="n">
-        <v>5.44248628616333</v>
+        <v>5.44248676300049</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G1166" t="n">
-        <v>5.34218168258667</v>
+        <v>5.34218215942383</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>7.42500019073486</v>
       </c>
       <c r="G1168" t="n">
-        <v>5.51678657531738</v>
+        <v>5.5167875289917</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>7.40999984741211</v>
       </c>
       <c r="G1169" t="n">
-        <v>5.50564098358154</v>
+        <v>5.50564193725586</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G1170" t="n">
-        <v>5.41648197174072</v>
+        <v>5.41648149490356</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>7.16499996185303</v>
       </c>
       <c r="G1171" t="n">
-        <v>5.32360649108887</v>
+        <v>5.32360696792603</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>6.91499996185303</v>
       </c>
       <c r="G1177" t="n">
-        <v>5.13785600662231</v>
+        <v>5.13785552978516</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G1178" t="n">
-        <v>4.92610120773315</v>
+        <v>4.926100730896</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G1180" t="n">
-        <v>4.9335298538208</v>
+        <v>4.93353080749512</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G1182" t="n">
-        <v>4.96325016021729</v>
+        <v>4.96325063705444</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>6.5</v>
       </c>
       <c r="G1183" t="n">
-        <v>4.82951021194458</v>
+        <v>4.82951068878174</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>6.75</v>
       </c>
       <c r="G1185" t="n">
-        <v>5.01526117324829</v>
+        <v>5.01526069641113</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>6.57000017166138</v>
       </c>
       <c r="G1186" t="n">
-        <v>4.88152027130127</v>
+        <v>4.88152074813843</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>6.61499977111816</v>
       </c>
       <c r="G1188" t="n">
-        <v>4.91495561599731</v>
+        <v>4.91495513916016</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>6.61499977111816</v>
       </c>
       <c r="G1189" t="n">
-        <v>4.91495561599731</v>
+        <v>4.91495513916016</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G1192" t="n">
-        <v>5.08956098556519</v>
+        <v>5.08956050872803</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G1195" t="n">
-        <v>5.02269077301025</v>
+        <v>5.02269124984741</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>6.93499994277954</v>
       </c>
       <c r="G1196" t="n">
-        <v>5.15271615982056</v>
+        <v>5.1527156829834</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>6.93499994277954</v>
       </c>
       <c r="G1197" t="n">
-        <v>5.15271615982056</v>
+        <v>5.1527156829834</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G1198" t="n">
-        <v>5.22330141067505</v>
+        <v>5.22330093383789</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>7.11499977111816</v>
       </c>
       <c r="G1199" t="n">
-        <v>5.28645658493042</v>
+        <v>5.28645610809326</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1202" t="n">
-        <v>5.34961175918579</v>
+        <v>5.34961128234863</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>7.17500019073486</v>
       </c>
       <c r="G1204" t="n">
-        <v>5.33103609085083</v>
+        <v>5.33103656768799</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>7.14499998092651</v>
       </c>
       <c r="G1205" t="n">
-        <v>5.30874633789062</v>
+        <v>5.30874681472778</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>7.21500015258789</v>
       </c>
       <c r="G1206" t="n">
-        <v>5.36075639724731</v>
+        <v>5.36075687408447</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>7.16499996185303</v>
       </c>
       <c r="G1207" t="n">
-        <v>5.32360649108887</v>
+        <v>5.32360696792603</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>7.21500015258789</v>
       </c>
       <c r="G1208" t="n">
-        <v>5.36075639724731</v>
+        <v>5.36075687408447</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>6.94500017166138</v>
       </c>
       <c r="G1213" t="n">
-        <v>5.16014671325684</v>
+        <v>5.16014623641968</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G1214" t="n">
-        <v>5.22330141067505</v>
+        <v>5.22330093383789</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>6.5</v>
       </c>
       <c r="G1217" t="n">
-        <v>4.82951021194458</v>
+        <v>4.82951068878174</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G1218" t="n">
-        <v>4.92610120773315</v>
+        <v>4.926100730896</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>6.77500009536743</v>
       </c>
       <c r="G1219" t="n">
-        <v>5.03383588790894</v>
+        <v>5.03383541107178</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>6.81500005722046</v>
       </c>
       <c r="G1221" t="n">
-        <v>5.06355571746826</v>
+        <v>5.06355619430542</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>6.76999998092651</v>
       </c>
       <c r="G1227" t="n">
-        <v>5.03012084960938</v>
+        <v>5.03012132644653</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1230" t="n">
-        <v>5.6096625328064</v>
+        <v>5.60966205596924</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G1231" t="n">
-        <v>5.70625257492065</v>
+        <v>5.7062520980835</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G1234" t="n">
-        <v>5.54279232025146</v>
+        <v>5.54279136657715</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G1236" t="n">
-        <v>5.57994270324707</v>
+        <v>5.57994222640991</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G1237" t="n">
-        <v>5.34218168258667</v>
+        <v>5.34218215942383</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G1239" t="n">
-        <v>5.25302171707153</v>
+        <v>5.25302124023438</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>6.53000020980835</v>
       </c>
       <c r="G1240" t="n">
-        <v>4.8518009185791</v>
+        <v>4.85180044174194</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>6.60500001907349</v>
       </c>
       <c r="G1241" t="n">
-        <v>4.90752553939819</v>
+        <v>4.90752601623535</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G1242" t="n">
-        <v>4.79236030578613</v>
+        <v>4.79235982894897</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G1243" t="n">
-        <v>4.72549057006836</v>
+        <v>4.7254900932312</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1245" t="n">
-        <v>4.60660934448242</v>
+        <v>4.60660982131958</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G1246" t="n">
-        <v>4.36884927749634</v>
+        <v>4.3688497543335</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1247" t="n">
-        <v>4.30940914154053</v>
+        <v>4.30940961837769</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G1248" t="n">
-        <v>4.53974008560181</v>
+        <v>4.53973960876465</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G1252" t="n">
-        <v>4.71806049346924</v>
+        <v>4.71806001663208</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G1259" t="n">
-        <v>4.9335298538208</v>
+        <v>4.93353080749512</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>6.67000007629395</v>
       </c>
       <c r="G1260" t="n">
-        <v>4.95582103729248</v>
+        <v>4.95582056045532</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G1261" t="n">
-        <v>5.00040102005005</v>
+        <v>5.00040054321289</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>6.68499994277954</v>
       </c>
       <c r="G1262" t="n">
-        <v>4.96696519851685</v>
+        <v>4.966965675354</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G1266" t="n">
-        <v>5.08213090896606</v>
+        <v>5.08213138580322</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>6.96500015258789</v>
       </c>
       <c r="G1267" t="n">
-        <v>5.17500591278076</v>
+        <v>5.17500638961792</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>7.00500011444092</v>
       </c>
       <c r="G1268" t="n">
-        <v>5.20472574234009</v>
+        <v>5.20472621917725</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G1269" t="n">
-        <v>5.00040102005005</v>
+        <v>5.00040054321289</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G1274" t="n">
-        <v>5.11185073852539</v>
+        <v>5.11185121536255</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>6.92500019073486</v>
       </c>
       <c r="G1275" t="n">
-        <v>5.14528608322144</v>
+        <v>5.14528656005859</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G1278" t="n">
-        <v>5.00894021987915</v>
+        <v>5.00894069671631</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G1279" t="n">
-        <v>4.98422574996948</v>
+        <v>4.98422527313232</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G1281" t="n">
-        <v>4.79474306106567</v>
+        <v>4.79474258422852</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>5.95499992370605</v>
       </c>
       <c r="G1282" t="n">
-        <v>4.90596055984497</v>
+        <v>4.90596103668213</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G1283" t="n">
-        <v>4.9183177947998</v>
+        <v>4.91831827163696</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>6.28499984741211</v>
       </c>
       <c r="G1287" t="n">
-        <v>5.17782783508301</v>
+        <v>5.17782735824585</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G1289" t="n">
-        <v>5.23961591720581</v>
+        <v>5.23961544036865</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G1290" t="n">
-        <v>5.06660985946655</v>
+        <v>5.06660938262939</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>6.30499982833862</v>
       </c>
       <c r="G1291" t="n">
-        <v>5.19430446624756</v>
+        <v>5.1943039894104</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>6.40999984741211</v>
       </c>
       <c r="G1292" t="n">
-        <v>5.28080749511719</v>
+        <v>5.28080701828003</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G1298" t="n">
-        <v>5.8245415687561</v>
+        <v>5.82454109191895</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G1299" t="n">
-        <v>5.98930931091309</v>
+        <v>5.98930883407593</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G1301" t="n">
-        <v>5.98930931091309</v>
+        <v>5.98930883407593</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>7.33500003814697</v>
       </c>
       <c r="G1304" t="n">
-        <v>6.04285860061646</v>
+        <v>6.0428581237793</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G1305" t="n">
-        <v>6.11288499832153</v>
+        <v>6.11288452148438</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>7.25</v>
       </c>
       <c r="G1306" t="n">
-        <v>5.97283172607422</v>
+        <v>5.97283220291138</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>7.32499980926514</v>
       </c>
       <c r="G1308" t="n">
-        <v>6.03461980819702</v>
+        <v>6.03462028503418</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G1315" t="n">
-        <v>5.470290184021</v>
+        <v>5.47029066085815</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G1316" t="n">
-        <v>5.470290184021</v>
+        <v>5.47029066085815</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>6.86499977111816</v>
       </c>
       <c r="G1317" t="n">
-        <v>5.65565347671509</v>
+        <v>5.65565395355225</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>6.60500001907349</v>
       </c>
       <c r="G1320" t="n">
-        <v>5.44145584106445</v>
+        <v>5.44145631790161</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>6.60500001907349</v>
       </c>
       <c r="G1321" t="n">
-        <v>5.44145584106445</v>
+        <v>5.44145631790161</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>6.48999977111816</v>
       </c>
       <c r="G1322" t="n">
-        <v>5.34671401977539</v>
+        <v>5.34671449661255</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>6.43499994277954</v>
       </c>
       <c r="G1333" t="n">
-        <v>5.30140352249146</v>
+        <v>5.3014030456543</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>6.44500017166138</v>
       </c>
       <c r="G1337" t="n">
-        <v>5.30964183807373</v>
+        <v>5.30964136123657</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>6.42500019073486</v>
       </c>
       <c r="G1341" t="n">
-        <v>5.29316520690918</v>
+        <v>5.29316473007202</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G1342" t="n">
-        <v>5.22313833236694</v>
+        <v>5.2231388092041</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35287,7 +35287,7 @@
         <v>6.47499990463257</v>
       </c>
       <c r="G1343" t="n">
-        <v>5.33435726165771</v>
+        <v>5.33435678482056</v>
       </c>
       <c r="H1343" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G1348" t="n">
-        <v>5.63505792617798</v>
+        <v>5.63505840301514</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>6.85500001907349</v>
       </c>
       <c r="G1349" t="n">
-        <v>5.64741611480713</v>
+        <v>5.64741563796997</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>6.86499977111816</v>
       </c>
       <c r="G1350" t="n">
-        <v>5.65565347671509</v>
+        <v>5.65565395355225</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G1351" t="n">
-        <v>5.54443597793579</v>
+        <v>5.54443550109863</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>6.94500017166138</v>
       </c>
       <c r="G1352" t="n">
-        <v>5.72156190872192</v>
+        <v>5.72156143188477</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>6.9850001335144</v>
       </c>
       <c r="G1355" t="n">
-        <v>5.75451517105103</v>
+        <v>5.75451469421387</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>6.86499977111816</v>
       </c>
       <c r="G1356" t="n">
-        <v>5.65565347671509</v>
+        <v>5.65565395355225</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>7.0149998664856</v>
       </c>
       <c r="G1359" t="n">
-        <v>5.77923011779785</v>
+        <v>5.77922964096069</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>6.9850001335144</v>
       </c>
       <c r="G1362" t="n">
-        <v>5.75451517105103</v>
+        <v>5.75451469421387</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1365" t="n">
-        <v>5.62401533126831</v>
+        <v>5.62401485443115</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35989,7 +35989,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G1370" t="n">
-        <v>5.5108380317688</v>
+        <v>5.51083755493164</v>
       </c>
       <c r="H1370" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>6.46500015258789</v>
       </c>
       <c r="G1378" t="n">
-        <v>5.62836742401123</v>
+        <v>5.62836790084839</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G1383" t="n">
-        <v>5.94613361358643</v>
+        <v>5.94613313674927</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>7.03499984741211</v>
       </c>
       <c r="G1385" t="n">
-        <v>6.12460422515869</v>
+        <v>6.12460374832153</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>7.00500011444092</v>
       </c>
       <c r="G1387" t="n">
-        <v>6.09848642349243</v>
+        <v>6.09848690032959</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G1388" t="n">
-        <v>6.06801605224609</v>
+        <v>6.06801557540894</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>7.10500001907349</v>
       </c>
       <c r="G1389" t="n">
-        <v>6.18554544448853</v>
+        <v>6.18554592132568</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G1390" t="n">
-        <v>6.12025165557861</v>
+        <v>6.12025117874146</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>6.42500019073486</v>
       </c>
       <c r="G1392" t="n">
-        <v>5.59354448318481</v>
+        <v>5.59354400634766</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G1394" t="n">
-        <v>5.98095703125</v>
+        <v>5.98095655441284</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G1398" t="n">
-        <v>5.98966264724731</v>
+        <v>5.98966312408447</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>6.94500017166138</v>
       </c>
       <c r="G1401" t="n">
-        <v>6.04625177383423</v>
+        <v>6.04625129699707</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G1404" t="n">
-        <v>6.12025165557861</v>
+        <v>6.12025117874146</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36899,7 +36899,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G1405" t="n">
-        <v>6.06801605224609</v>
+        <v>6.06801557540894</v>
       </c>
       <c r="H1405" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>7.17500019073486</v>
       </c>
       <c r="G1410" t="n">
-        <v>6.24648666381836</v>
+        <v>6.24648714065552</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G1411" t="n">
-        <v>6.24213457107544</v>
+        <v>6.24213409423828</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37081,7 +37081,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G1412" t="n">
-        <v>6.19860458374023</v>
+        <v>6.19860506057739</v>
       </c>
       <c r="H1412" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G1413" t="n">
-        <v>6.24213457107544</v>
+        <v>6.24213409423828</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G1414" t="n">
-        <v>6.21601629257202</v>
+        <v>6.21601676940918</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>7.22499990463257</v>
       </c>
       <c r="G1415" t="n">
-        <v>6.29001617431641</v>
+        <v>6.29001665115356</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G1416" t="n">
-        <v>6.30307531356812</v>
+        <v>6.30307579040527</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>7.19500017166138</v>
       </c>
       <c r="G1417" t="n">
-        <v>6.26389932632446</v>
+        <v>6.2638988494873</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37263,7 +37263,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1419" t="n">
-        <v>6.44236946105957</v>
+        <v>6.44236993789673</v>
       </c>
       <c r="H1419" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>7.20499992370605</v>
       </c>
       <c r="G1420" t="n">
-        <v>6.27260446548462</v>
+        <v>6.27260494232178</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37315,7 +37315,7 @@
         <v>7.17500019073486</v>
       </c>
       <c r="G1421" t="n">
-        <v>6.24648666381836</v>
+        <v>6.24648714065552</v>
       </c>
       <c r="H1421" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G1426" t="n">
-        <v>6.24213457107544</v>
+        <v>6.24213409423828</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>7.16499996185303</v>
       </c>
       <c r="G1427" t="n">
-        <v>6.23778104782104</v>
+        <v>6.2377815246582</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>7.30499982833862</v>
       </c>
       <c r="G1428" t="n">
-        <v>6.35966348648071</v>
+        <v>6.35966396331787</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G1431" t="n">
-        <v>6.37272310256958</v>
+        <v>6.37272262573242</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1432" t="n">
-        <v>6.44236946105957</v>
+        <v>6.44236993789673</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G1433" t="n">
-        <v>6.41625261306763</v>
+        <v>6.41625213623047</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>7.45499992370605</v>
       </c>
       <c r="G1434" t="n">
-        <v>6.49025249481201</v>
+        <v>6.49025201797485</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G1435" t="n">
-        <v>6.47719383239746</v>
+        <v>6.4771933555603</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>7.43499994277954</v>
       </c>
       <c r="G1439" t="n">
-        <v>6.47284078598022</v>
+        <v>6.47284030914307</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>7.32499980926514</v>
       </c>
       <c r="G1443" t="n">
-        <v>6.3770751953125</v>
+        <v>6.37707567214966</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G1444" t="n">
-        <v>6.41625261306763</v>
+        <v>6.41625213623047</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G1445" t="n">
-        <v>6.47719383239746</v>
+        <v>6.4771933555603</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -37965,7 +37965,7 @@
         <v>7.40999984741211</v>
       </c>
       <c r="G1446" t="n">
-        <v>6.4510760307312</v>
+        <v>6.45107555389404</v>
       </c>
       <c r="H1446" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>7.20499992370605</v>
       </c>
       <c r="G1447" t="n">
-        <v>6.27260446548462</v>
+        <v>6.27260494232178</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G1451" t="n">
-        <v>6.47719383239746</v>
+        <v>6.4771933555603</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38199,7 +38199,7 @@
         <v>7.39499998092651</v>
       </c>
       <c r="G1455" t="n">
-        <v>6.43801736831665</v>
+        <v>6.43801689147949</v>
       </c>
       <c r="H1455" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>7.43499994277954</v>
       </c>
       <c r="G1456" t="n">
-        <v>6.47284078598022</v>
+        <v>6.47284030914307</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38251,7 +38251,7 @@
         <v>7.40999984741211</v>
       </c>
       <c r="G1457" t="n">
-        <v>6.4510760307312</v>
+        <v>6.45107555389404</v>
       </c>
       <c r="H1457" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>7.45499992370605</v>
       </c>
       <c r="G1458" t="n">
-        <v>6.49025249481201</v>
+        <v>6.49025201797485</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>7.88500022888184</v>
       </c>
       <c r="G1461" t="n">
-        <v>6.86460638046265</v>
+        <v>6.8646068572998</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G1462" t="n">
-        <v>6.91248846054077</v>
+        <v>6.91248893737793</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1464" t="n">
-        <v>7.12143087387085</v>
+        <v>7.12143039703369</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G1465" t="n">
-        <v>7.25201940536499</v>
+        <v>7.25201892852783</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>8.42500019073486</v>
       </c>
       <c r="G1468" t="n">
-        <v>7.33472490310669</v>
+        <v>7.33472585678101</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>8.44499969482422</v>
       </c>
       <c r="G1469" t="n">
-        <v>7.35213661193848</v>
+        <v>7.35213756561279</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1470" t="n">
-        <v>7.44354867935181</v>
+        <v>7.44354915618896</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>8.50500011444092</v>
       </c>
       <c r="G1471" t="n">
-        <v>7.40437316894531</v>
+        <v>7.40437269210815</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38745,7 +38745,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G1476" t="n">
-        <v>7.27813625335693</v>
+        <v>7.27813673019409</v>
       </c>
       <c r="H1476" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>8.61499977111816</v>
       </c>
       <c r="G1478" t="n">
-        <v>7.50013780593872</v>
+        <v>7.50013732910156</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>8.48499965667725</v>
       </c>
       <c r="G1479" t="n">
-        <v>7.38696002960205</v>
+        <v>7.38696098327637</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38875,7 +38875,7 @@
         <v>8.6899995803833</v>
       </c>
       <c r="G1481" t="n">
-        <v>7.56543207168579</v>
+        <v>7.56543111801147</v>
       </c>
       <c r="H1481" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G1482" t="n">
-        <v>7.64378547668457</v>
+        <v>7.6437840461731</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -38927,7 +38927,7 @@
         <v>8.76500034332275</v>
       </c>
       <c r="G1483" t="n">
-        <v>7.6307258605957</v>
+        <v>7.63072633743286</v>
       </c>
       <c r="H1483" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>8.90499973297119</v>
       </c>
       <c r="G1484" t="n">
-        <v>7.75260925292969</v>
+        <v>7.75260829925537</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>8.89000034332275</v>
       </c>
       <c r="G1486" t="n">
-        <v>7.73955011367798</v>
+        <v>7.73954963684082</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>9.41499996185303</v>
       </c>
       <c r="G1488" t="n">
-        <v>8.19660949707031</v>
+        <v>8.19661045074463</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G1493" t="n">
-        <v>8.32284545898438</v>
+        <v>8.32284641265869</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G1494" t="n">
-        <v>8.34896278381348</v>
+        <v>8.34896373748779</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1497" t="n">
-        <v>8.21837329864502</v>
+        <v>8.21837425231934</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39343,7 +39343,7 @@
         <v>9.39000034332275</v>
       </c>
       <c r="G1499" t="n">
-        <v>8.17484474182129</v>
+        <v>8.17484569549561</v>
       </c>
       <c r="H1499" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>9.36499977111816</v>
       </c>
       <c r="G1500" t="n">
-        <v>8.15307998657227</v>
+        <v>8.15308094024658</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>9.51500034332275</v>
       </c>
       <c r="G1503" t="n">
-        <v>8.28366851806641</v>
+        <v>8.28366947174072</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39473,7 +39473,7 @@
         <v>9.45499992370605</v>
       </c>
       <c r="G1504" t="n">
-        <v>8.23143291473389</v>
+        <v>8.2314338684082</v>
       </c>
       <c r="H1504" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>9.33500003814697</v>
       </c>
       <c r="G1509" t="n">
-        <v>8.12696361541748</v>
+        <v>8.12696266174316</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39629,7 +39629,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G1510" t="n">
-        <v>7.85272693634033</v>
+        <v>7.85272741317749</v>
       </c>
       <c r="H1510" t="s">
         <v>8</v>
@@ -39681,7 +39681,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G1512" t="n">
-        <v>7.89625549316406</v>
+        <v>7.89625597000122</v>
       </c>
       <c r="H1512" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>9.10499954223633</v>
       </c>
       <c r="G1513" t="n">
-        <v>7.92672681808472</v>
+        <v>7.9267258644104</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>9.45499992370605</v>
       </c>
       <c r="G1514" t="n">
-        <v>8.23143291473389</v>
+        <v>8.2314338684082</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G1516" t="n">
-        <v>8.06166934967041</v>
+        <v>8.06166839599609</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G1518" t="n">
-        <v>7.96590328216553</v>
+        <v>7.96590280532837</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>9.00500011444092</v>
       </c>
       <c r="G1519" t="n">
-        <v>7.83966827392578</v>
+        <v>7.83966875076294</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G1521" t="n">
-        <v>8.00072574615479</v>
+        <v>8.0007266998291</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G1522" t="n">
-        <v>7.96590328216553</v>
+        <v>7.96590280532837</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>9.15499973297119</v>
       </c>
       <c r="G1523" t="n">
-        <v>7.97025632858276</v>
+        <v>7.97025537490845</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>8.98999977111816</v>
       </c>
       <c r="G1524" t="n">
-        <v>7.82660818099976</v>
+        <v>7.82660913467407</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>8.93000030517578</v>
       </c>
       <c r="G1525" t="n">
-        <v>7.77437400817871</v>
+        <v>7.77437305450439</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>9.17500019073486</v>
       </c>
       <c r="G1526" t="n">
-        <v>7.98766803741455</v>
+        <v>7.98766851425171</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>9.32999992370605</v>
       </c>
       <c r="G1528" t="n">
-        <v>8.12260913848877</v>
+        <v>8.12261009216309</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40149,7 +40149,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G1530" t="n">
-        <v>8.09649181365967</v>
+        <v>8.09649276733398</v>
       </c>
       <c r="H1530" t="s">
         <v>8</v>
@@ -40201,7 +40201,7 @@
         <v>9.47000026702881</v>
       </c>
       <c r="G1532" t="n">
-        <v>8.24449253082275</v>
+        <v>8.24449348449707</v>
       </c>
       <c r="H1532" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>9.41499996185303</v>
       </c>
       <c r="G1533" t="n">
-        <v>8.19660949707031</v>
+        <v>8.19661045074463</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G1534" t="n">
-        <v>7.89625549316406</v>
+        <v>7.89625597000122</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>8.69499969482422</v>
       </c>
       <c r="G1536" t="n">
-        <v>7.93662929534912</v>
+        <v>7.93662881851196</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G1540" t="n">
-        <v>7.95944929122925</v>
+        <v>7.95944976806641</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>8.57499980926514</v>
       </c>
       <c r="G1543" t="n">
-        <v>7.82709503173828</v>
+        <v>7.8270959854126</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>8.61499977111816</v>
       </c>
       <c r="G1545" t="n">
-        <v>7.86360740661621</v>
+        <v>7.86360692977905</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40565,7 +40565,7 @@
         <v>8.69499969482422</v>
       </c>
       <c r="G1546" t="n">
-        <v>7.93662929534912</v>
+        <v>7.93662881851196</v>
       </c>
       <c r="H1546" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>8.54500007629395</v>
       </c>
       <c r="G1547" t="n">
-        <v>7.79971265792847</v>
+        <v>7.79971218109131</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>8.625</v>
       </c>
       <c r="G1549" t="n">
-        <v>7.87273454666138</v>
+        <v>7.87273502349854</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40669,7 +40669,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G1550" t="n">
-        <v>7.84078788757324</v>
+        <v>7.84078741073608</v>
       </c>
       <c r="H1550" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G1556" t="n">
-        <v>8.38845539093018</v>
+        <v>8.38845634460449</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40851,7 +40851,7 @@
         <v>9.15499973297119</v>
       </c>
       <c r="G1557" t="n">
-        <v>8.3565092086792</v>
+        <v>8.35650825500488</v>
       </c>
       <c r="H1557" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G1567" t="n">
-        <v>8.87223052978516</v>
+        <v>8.87222957611084</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41501,7 +41501,7 @@
         <v>9.78999996185303</v>
       </c>
       <c r="G1582" t="n">
-        <v>8.93612384796143</v>
+        <v>8.93612480163574</v>
       </c>
       <c r="H1582" t="s">
         <v>8</v>
@@ -41553,7 +41553,7 @@
         <v>10.0299997329712</v>
       </c>
       <c r="G1584" t="n">
-        <v>9.15519142150879</v>
+        <v>9.15519237518311</v>
       </c>
       <c r="H1584" t="s">
         <v>8</v>
@@ -41579,7 +41579,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G1585" t="n">
-        <v>9.03653049468994</v>
+        <v>9.03652954101562</v>
       </c>
       <c r="H1585" t="s">
         <v>8</v>
@@ -41631,7 +41631,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G1587" t="n">
-        <v>9.01827430725098</v>
+        <v>9.01827526092529</v>
       </c>
       <c r="H1587" t="s">
         <v>8</v>
@@ -41917,7 +41917,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G1598" t="n">
-        <v>9.29210948944092</v>
+        <v>9.2921085357666</v>
       </c>
       <c r="H1598" t="s">
         <v>8</v>
@@ -42021,7 +42021,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G1602" t="n">
-        <v>9.01827430725098</v>
+        <v>9.01827526092529</v>
       </c>
       <c r="H1602" t="s">
         <v>8</v>
@@ -42125,7 +42125,7 @@
         <v>10.1700000762939</v>
       </c>
       <c r="G1606" t="n">
-        <v>9.28298091888428</v>
+        <v>9.28298187255859</v>
       </c>
       <c r="H1606" t="s">
         <v>8</v>
@@ -42229,7 +42229,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1610" t="n">
-        <v>8.83571815490723</v>
+        <v>8.83571910858154</v>
       </c>
       <c r="H1610" t="s">
         <v>8</v>
@@ -42281,7 +42281,7 @@
         <v>9.5649995803833</v>
       </c>
       <c r="G1612" t="n">
-        <v>8.73074817657471</v>
+        <v>8.73074913024902</v>
       </c>
       <c r="H1612" t="s">
         <v>8</v>
@@ -42307,7 +42307,7 @@
         <v>9.6850004196167</v>
       </c>
       <c r="G1613" t="n">
-        <v>8.84028339385986</v>
+        <v>8.84028244018555</v>
       </c>
       <c r="H1613" t="s">
         <v>8</v>
@@ -42463,7 +42463,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G1619" t="n">
-        <v>8.80833435058594</v>
+        <v>8.80833530426025</v>
       </c>
       <c r="H1619" t="s">
         <v>8</v>
@@ -42541,7 +42541,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G1622" t="n">
-        <v>8.80833435058594</v>
+        <v>8.80833530426025</v>
       </c>
       <c r="H1622" t="s">
         <v>8</v>
@@ -42827,7 +42827,7 @@
         <v>9.6850004196167</v>
       </c>
       <c r="G1633" t="n">
-        <v>8.84028339385986</v>
+        <v>8.84028244018555</v>
       </c>
       <c r="H1633" t="s">
         <v>8</v>
@@ -62838,7 +62838,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="D2403" t="n">
-        <v>2.8199999332428</v>
+        <v>2.81399989128113</v>
       </c>
       <c r="E2403" t="n">
         <v>2.92000007629395</v>
@@ -62850,6 +62850,32 @@
         <v>2.81399989128113</v>
       </c>
       <c r="H2403" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2404">
+      <c r="A2404" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B2404" t="n">
+        <v>3225599</v>
+      </c>
+      <c r="C2404" t="n">
+        <v>2.85800004005432</v>
+      </c>
+      <c r="D2404" t="n">
+        <v>2.68199992179871</v>
+      </c>
+      <c r="E2404" t="n">
+        <v>2.84599995613098</v>
+      </c>
+      <c r="F2404" t="n">
+        <v>2.74200010299683</v>
+      </c>
+      <c r="G2404" t="n">
+        <v>2.74200010299683</v>
+      </c>
+      <c r="H2404" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/BFF.MI.xlsx
+++ b/data/BFF.MI.xlsx
@@ -473,7 +473,7 @@
         <v>4.25</v>
       </c>
       <c r="G4" t="n">
-        <v>2.31461930274963</v>
+        <v>2.31461954116821</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>4.29400014877319</v>
       </c>
       <c r="G5" t="n">
-        <v>2.33858275413513</v>
+        <v>2.33858251571655</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>4.06599998474121</v>
       </c>
       <c r="G7" t="n">
-        <v>2.21441006660461</v>
+        <v>2.21440982818604</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G8" t="n">
-        <v>2.2220344543457</v>
+        <v>2.22203493118286</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G11" t="n">
-        <v>2.26560378074646</v>
+        <v>2.26560401916504</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G12" t="n">
-        <v>2.28738856315613</v>
+        <v>2.28738880157471</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G15" t="n">
-        <v>2.36363482475281</v>
+        <v>2.36363530158997</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>4.36199998855591</v>
       </c>
       <c r="G16" t="n">
-        <v>2.37561631202698</v>
+        <v>2.37561655044556</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>4.44600009918213</v>
       </c>
       <c r="G17" t="n">
-        <v>2.42136454582214</v>
+        <v>2.42136406898499</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>4.4520001411438</v>
       </c>
       <c r="G19" t="n">
-        <v>2.42463231086731</v>
+        <v>2.42463207244873</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>4.48600006103516</v>
       </c>
       <c r="G20" t="n">
-        <v>2.44314932823181</v>
+        <v>2.44314908981323</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G22" t="n">
-        <v>2.5596969127655</v>
+        <v>2.55969643592834</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>4.83599996566772</v>
       </c>
       <c r="G23" t="n">
-        <v>2.63376474380493</v>
+        <v>2.63376450538635</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>4.85400009155273</v>
       </c>
       <c r="G24" t="n">
-        <v>2.64356756210327</v>
+        <v>2.64356827735901</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G25" t="n">
-        <v>2.5596969127655</v>
+        <v>2.55969643592834</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>4.73799991607666</v>
       </c>
       <c r="G27" t="n">
-        <v>2.58039212226868</v>
+        <v>2.58039236068726</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>4.64200019836426</v>
       </c>
       <c r="G28" t="n">
-        <v>2.5281093120575</v>
+        <v>2.52810907363892</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>4.73199987411499</v>
       </c>
       <c r="G29" t="n">
-        <v>2.57712435722351</v>
+        <v>2.57712459564209</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>4.74200010299683</v>
       </c>
       <c r="G30" t="n">
-        <v>2.58257055282593</v>
+        <v>2.58257079124451</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>4.77600002288818</v>
       </c>
       <c r="G32" t="n">
-        <v>2.60108804702759</v>
+        <v>2.60108780860901</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G34" t="n">
-        <v>2.66317415237427</v>
+        <v>2.66317391395569</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G35" t="n">
-        <v>2.68495869636536</v>
+        <v>2.68495845794678</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>4.89799976348877</v>
       </c>
       <c r="G36" t="n">
-        <v>2.66753053665161</v>
+        <v>2.66753077507019</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G37" t="n">
-        <v>2.68495869636536</v>
+        <v>2.68495845794678</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>4.94799995422363</v>
       </c>
       <c r="G38" t="n">
-        <v>2.6947615146637</v>
+        <v>2.69476175308228</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>4.92199993133545</v>
       </c>
       <c r="G39" t="n">
-        <v>2.68060183525085</v>
+        <v>2.68060159683228</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>4.86800003051758</v>
       </c>
       <c r="G40" t="n">
-        <v>2.65119218826294</v>
+        <v>2.65119242668152</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G41" t="n">
-        <v>2.64138913154602</v>
+        <v>2.6413893699646</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>4.87599992752075</v>
       </c>
       <c r="G44" t="n">
-        <v>2.65554928779602</v>
+        <v>2.65554904937744</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>4.84600019454956</v>
       </c>
       <c r="G45" t="n">
-        <v>2.63921117782593</v>
+        <v>2.63921093940735</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>4.89599990844727</v>
       </c>
       <c r="G46" t="n">
-        <v>2.66644167900085</v>
+        <v>2.66644144058228</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>5.06500005722046</v>
       </c>
       <c r="G47" t="n">
-        <v>2.75848174095154</v>
+        <v>2.75848197937012</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G51" t="n">
-        <v>2.81022000312805</v>
+        <v>2.81022047996521</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G53" t="n">
-        <v>2.80749750137329</v>
+        <v>2.80749773979187</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G56" t="n">
-        <v>2.81566667556763</v>
+        <v>2.81566643714905</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G57" t="n">
-        <v>2.84289741516113</v>
+        <v>2.84289717674255</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G58" t="n">
-        <v>2.81022000312805</v>
+        <v>2.81022047996521</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>5.125</v>
       </c>
       <c r="G67" t="n">
-        <v>2.79115891456604</v>
+        <v>2.79115867614746</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G68" t="n">
-        <v>2.81566667556763</v>
+        <v>2.81566643714905</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G70" t="n">
-        <v>2.80477452278137</v>
+        <v>2.80477428436279</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G75" t="n">
-        <v>2.80477452278137</v>
+        <v>2.80477428436279</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>5.125</v>
       </c>
       <c r="G76" t="n">
-        <v>2.79115891456604</v>
+        <v>2.79115867614746</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>5.17500019073486</v>
       </c>
       <c r="G77" t="n">
-        <v>2.8183901309967</v>
+        <v>2.81838941574097</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G79" t="n">
-        <v>2.82655882835388</v>
+        <v>2.82655906677246</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G81" t="n">
-        <v>2.80477452278137</v>
+        <v>2.80477428436279</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G82" t="n">
-        <v>2.80477452278137</v>
+        <v>2.80477428436279</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G83" t="n">
-        <v>2.80477452278137</v>
+        <v>2.80477428436279</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G85" t="n">
-        <v>2.80749750137329</v>
+        <v>2.80749773979187</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G86" t="n">
-        <v>2.80477452278137</v>
+        <v>2.80477428436279</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>5.13500022888184</v>
       </c>
       <c r="G88" t="n">
-        <v>2.79660487174988</v>
+        <v>2.79660511016846</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G90" t="n">
-        <v>2.81566667556763</v>
+        <v>2.81566643714905</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G91" t="n">
-        <v>2.83745098114014</v>
+        <v>2.83745121955872</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G92" t="n">
-        <v>2.81566667556763</v>
+        <v>2.81566643714905</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G93" t="n">
-        <v>2.80749750137329</v>
+        <v>2.80749773979187</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G94" t="n">
-        <v>2.80749750137329</v>
+        <v>2.80749773979187</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G97" t="n">
-        <v>2.81566667556763</v>
+        <v>2.81566643714905</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>5.11499977111816</v>
       </c>
       <c r="G99" t="n">
-        <v>2.78571224212646</v>
+        <v>2.78571271896362</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>4.9520001411438</v>
       </c>
       <c r="G100" t="n">
-        <v>2.69694018363953</v>
+        <v>2.69693994522095</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>4.99200010299683</v>
       </c>
       <c r="G102" t="n">
-        <v>2.71872448921204</v>
+        <v>2.71872520446777</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G103" t="n">
-        <v>2.73942065238953</v>
+        <v>2.73942041397095</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G104" t="n">
-        <v>2.81022000312805</v>
+        <v>2.81022047996521</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G111" t="n">
-        <v>2.84834384918213</v>
+        <v>2.84834337234497</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G112" t="n">
-        <v>2.88102054595947</v>
+        <v>2.88102078437805</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>5.50500011444092</v>
       </c>
       <c r="G114" t="n">
-        <v>2.99811315536499</v>
+        <v>2.99811339378357</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G116" t="n">
-        <v>3.02806687355042</v>
+        <v>3.02806663513184</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G117" t="n">
-        <v>3.03895926475525</v>
+        <v>3.03895950317383</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G118" t="n">
-        <v>3.00628232955933</v>
+        <v>3.00628185272217</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G119" t="n">
-        <v>3.08797478675842</v>
+        <v>3.08797454833984</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>5.67500019073486</v>
       </c>
       <c r="G120" t="n">
-        <v>3.09069800376892</v>
+        <v>3.09069776535034</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G121" t="n">
-        <v>3.24046754837036</v>
+        <v>3.2404670715332</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G122" t="n">
-        <v>3.2132363319397</v>
+        <v>3.21323657035828</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G124" t="n">
-        <v>3.19689798355103</v>
+        <v>3.1968982219696</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G125" t="n">
-        <v>3.12609767913818</v>
+        <v>3.12609791755676</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G127" t="n">
-        <v>3.14243650436401</v>
+        <v>3.14243602752686</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G128" t="n">
-        <v>3.10431289672852</v>
+        <v>3.10431313514709</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G131" t="n">
-        <v>3.20234417915344</v>
+        <v>3.20234441757202</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G135" t="n">
-        <v>3.30582118034363</v>
+        <v>3.30582094192505</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>6.11499977111816</v>
       </c>
       <c r="G136" t="n">
-        <v>3.33032917976379</v>
+        <v>3.33032894134521</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>6.04500007629395</v>
       </c>
       <c r="G137" t="n">
-        <v>3.2922055721283</v>
+        <v>3.29220604896545</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>6.11499977111816</v>
       </c>
       <c r="G139" t="n">
-        <v>3.33032917976379</v>
+        <v>3.33032894134521</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G140" t="n">
-        <v>3.33305168151855</v>
+        <v>3.33305215835571</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G143" t="n">
-        <v>3.39295983314514</v>
+        <v>3.39296007156372</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G144" t="n">
-        <v>3.38751339912415</v>
+        <v>3.38751363754272</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>6.25</v>
       </c>
       <c r="G145" t="n">
-        <v>3.40385222434998</v>
+        <v>3.40385270118713</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>6.11499977111816</v>
       </c>
       <c r="G147" t="n">
-        <v>3.33032917976379</v>
+        <v>3.33032894134521</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>6.00500011444092</v>
       </c>
       <c r="G149" t="n">
-        <v>3.27042150497437</v>
+        <v>3.27042126655579</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>6.09499979019165</v>
       </c>
       <c r="G150" t="n">
-        <v>3.31943655014038</v>
+        <v>3.31943678855896</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G152" t="n">
-        <v>3.25680565834045</v>
+        <v>3.25680589675903</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G153" t="n">
-        <v>3.2459135055542</v>
+        <v>3.24591326713562</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G155" t="n">
-        <v>3.2132363319397</v>
+        <v>3.21323657035828</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G156" t="n">
-        <v>3.27314424514771</v>
+        <v>3.27314448356628</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G163" t="n">
-        <v>3.51277542114258</v>
+        <v>3.51277565956116</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G164" t="n">
-        <v>3.4746527671814</v>
+        <v>3.47465252876282</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G165" t="n">
-        <v>3.45831370353699</v>
+        <v>3.45831394195557</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>6.41499996185303</v>
       </c>
       <c r="G166" t="n">
-        <v>3.49371385574341</v>
+        <v>3.49371361732483</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>6.45499992370605</v>
       </c>
       <c r="G167" t="n">
-        <v>3.5154983997345</v>
+        <v>3.51549863815308</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>6.36499977111816</v>
       </c>
       <c r="G168" t="n">
-        <v>3.46648287773132</v>
+        <v>3.46648263931274</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G169" t="n">
-        <v>3.50732898712158</v>
+        <v>3.50732922554016</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G170" t="n">
-        <v>3.50732898712158</v>
+        <v>3.50732922554016</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G172" t="n">
-        <v>3.583575963974</v>
+        <v>3.58357524871826</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G173" t="n">
-        <v>3.56179070472717</v>
+        <v>3.56179094314575</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G175" t="n">
-        <v>3.5944676399231</v>
+        <v>3.59446740150452</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>6.53000020980835</v>
       </c>
       <c r="G176" t="n">
-        <v>3.55634522438049</v>
+        <v>3.55634498596191</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>6.53499984741211</v>
       </c>
       <c r="G178" t="n">
-        <v>3.55906820297241</v>
+        <v>3.55906772613525</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>6.5149998664856</v>
       </c>
       <c r="G179" t="n">
-        <v>3.54817533493042</v>
+        <v>3.548175573349</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G180" t="n">
-        <v>3.6108067035675</v>
+        <v>3.61080598831177</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>6.375</v>
       </c>
       <c r="G181" t="n">
-        <v>3.47192931175232</v>
+        <v>3.4719295501709</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G182" t="n">
-        <v>3.4746527671814</v>
+        <v>3.47465252876282</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>6.25</v>
       </c>
       <c r="G183" t="n">
-        <v>3.40385222434998</v>
+        <v>3.40385270118713</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G184" t="n">
-        <v>3.44742155075073</v>
+        <v>3.44742107391357</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G186" t="n">
-        <v>3.48554468154907</v>
+        <v>3.48554491996765</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>6.41499996185303</v>
       </c>
       <c r="G187" t="n">
-        <v>3.49371385574341</v>
+        <v>3.49371361732483</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>6.53499984741211</v>
       </c>
       <c r="G188" t="n">
-        <v>3.55906820297241</v>
+        <v>3.55906772613525</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G190" t="n">
-        <v>3.54545283317566</v>
+        <v>3.54545259475708</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>6.43499994277954</v>
       </c>
       <c r="G192" t="n">
-        <v>3.50460624694824</v>
+        <v>3.50460600852966</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G193" t="n">
-        <v>3.56179070472717</v>
+        <v>3.56179094314575</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G194" t="n">
-        <v>3.4746527671814</v>
+        <v>3.47465252876282</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>6.46500015258789</v>
       </c>
       <c r="G195" t="n">
-        <v>3.52094459533691</v>
+        <v>3.52094507217407</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G198" t="n">
-        <v>3.54545283317566</v>
+        <v>3.54545259475708</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G199" t="n">
-        <v>3.54545283317566</v>
+        <v>3.54545259475708</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G200" t="n">
-        <v>3.54545283317566</v>
+        <v>3.54545259475708</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>6.57499980926514</v>
       </c>
       <c r="G201" t="n">
-        <v>3.58085227012634</v>
+        <v>3.58085250854492</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G202" t="n">
-        <v>3.58902168273926</v>
+        <v>3.58902215957642</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G203" t="n">
-        <v>3.5944676399231</v>
+        <v>3.59446740150452</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>6.53000020980835</v>
       </c>
       <c r="G204" t="n">
-        <v>3.55634522438049</v>
+        <v>3.55634498596191</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>6.59499979019165</v>
       </c>
       <c r="G205" t="n">
-        <v>3.59174489974976</v>
+        <v>3.59174466133118</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G207" t="n">
-        <v>3.54545283317566</v>
+        <v>3.54545259475708</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>6.4850001335144</v>
       </c>
       <c r="G208" t="n">
-        <v>3.53183722496033</v>
+        <v>3.53183746337891</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>6.41499996185303</v>
       </c>
       <c r="G209" t="n">
-        <v>3.49371385574341</v>
+        <v>3.49371361732483</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G210" t="n">
-        <v>3.29492926597595</v>
+        <v>3.29492902755737</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>5.91499996185303</v>
       </c>
       <c r="G212" t="n">
-        <v>3.22140598297119</v>
+        <v>3.22140550613403</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G213" t="n">
-        <v>3.27859044075012</v>
+        <v>3.2785906791687</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G214" t="n">
-        <v>3.12065124511719</v>
+        <v>3.12065148353577</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G216" t="n">
-        <v>3.16966724395752</v>
+        <v>3.16966700553894</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>6.14499998092651</v>
       </c>
       <c r="G221" t="n">
-        <v>3.34666776657104</v>
+        <v>3.34666752815247</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>6.16499996185303</v>
       </c>
       <c r="G222" t="n">
-        <v>3.35756015777588</v>
+        <v>3.35755944252014</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G223" t="n">
-        <v>3.2132363319397</v>
+        <v>3.21323657035828</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G224" t="n">
-        <v>3.18055963516235</v>
+        <v>3.18055939674377</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G225" t="n">
-        <v>3.16966724395752</v>
+        <v>3.16966700553894</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G226" t="n">
-        <v>3.16966724395752</v>
+        <v>3.16966700553894</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G230" t="n">
-        <v>3.17511343955994</v>
+        <v>3.17511296272278</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G233" t="n">
-        <v>3.15332841873169</v>
+        <v>3.15332865715027</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>5.88500022888184</v>
       </c>
       <c r="G234" t="n">
-        <v>3.20506763458252</v>
+        <v>3.20506691932678</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>6.04500007629395</v>
       </c>
       <c r="G236" t="n">
-        <v>3.2922055721283</v>
+        <v>3.29220604896545</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G238" t="n">
-        <v>3.24046754837036</v>
+        <v>3.2404670715332</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>5.88500022888184</v>
       </c>
       <c r="G239" t="n">
-        <v>3.20506763458252</v>
+        <v>3.20506691932678</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>5.91499996185303</v>
       </c>
       <c r="G240" t="n">
-        <v>3.22140598297119</v>
+        <v>3.22140550613403</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>5.88500022888184</v>
       </c>
       <c r="G241" t="n">
-        <v>3.20506763458252</v>
+        <v>3.20506691932678</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>5.7350001335144</v>
       </c>
       <c r="G243" t="n">
-        <v>3.12337517738342</v>
+        <v>3.12337398529053</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>5.71500015258789</v>
       </c>
       <c r="G244" t="n">
-        <v>3.11248278617859</v>
+        <v>3.11248254776001</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G245" t="n">
-        <v>3.08797478675842</v>
+        <v>3.08797454833984</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G247" t="n">
-        <v>3.16422080993652</v>
+        <v>3.16422033309937</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G249" t="n">
-        <v>3.23502111434937</v>
+        <v>3.23502087593079</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G250" t="n">
-        <v>3.2132363319397</v>
+        <v>3.21323657035828</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G253" t="n">
-        <v>3.20234417915344</v>
+        <v>3.20234441757202</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G255" t="n">
-        <v>3.26296758651733</v>
+        <v>3.26296734809875</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>5.32499980926514</v>
       </c>
       <c r="G256" t="n">
-        <v>3.16490030288696</v>
+        <v>3.1648998260498</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G258" t="n">
-        <v>3.24513721466064</v>
+        <v>3.24513745307922</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G260" t="n">
-        <v>3.15598487854004</v>
+        <v>3.1559853553772</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G261" t="n">
-        <v>3.20947670936584</v>
+        <v>3.20947623252869</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>5.41499996185303</v>
       </c>
       <c r="G262" t="n">
-        <v>3.21839165687561</v>
+        <v>3.21839118003845</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>5.36499977111816</v>
       </c>
       <c r="G264" t="n">
-        <v>3.1886739730835</v>
+        <v>3.18867421150208</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>5.25500011444092</v>
       </c>
       <c r="G265" t="n">
-        <v>3.12329626083374</v>
+        <v>3.12329602241516</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G266" t="n">
-        <v>3.06386184692383</v>
+        <v>3.06386160850525</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G267" t="n">
-        <v>3.13815474510193</v>
+        <v>3.13815450668335</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G268" t="n">
-        <v>3.06088995933533</v>
+        <v>3.06088924407959</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>5.18499994277954</v>
       </c>
       <c r="G269" t="n">
-        <v>3.08169174194336</v>
+        <v>3.08169150352478</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>5.25</v>
       </c>
       <c r="G270" t="n">
-        <v>3.12032437324524</v>
+        <v>3.12032413482666</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G271" t="n">
-        <v>3.13815474510193</v>
+        <v>3.13815450668335</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>5.25500011444092</v>
       </c>
       <c r="G272" t="n">
-        <v>3.12329626083374</v>
+        <v>3.12329602241516</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G274" t="n">
-        <v>3.09655022621155</v>
+        <v>3.09655046463013</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G275" t="n">
-        <v>3.07277679443359</v>
+        <v>3.07277655601501</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>5.02500009536743</v>
       </c>
       <c r="G276" t="n">
-        <v>2.98659634590149</v>
+        <v>2.98659610748291</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>5.22499990463257</v>
       </c>
       <c r="G278" t="n">
-        <v>3.10546541213989</v>
+        <v>3.10546565055847</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G279" t="n">
-        <v>3.01928544044495</v>
+        <v>3.01928520202637</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>4.96600008010864</v>
       </c>
       <c r="G280" t="n">
-        <v>2.95152950286865</v>
+        <v>2.95152974128723</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G281" t="n">
-        <v>3.04305911064148</v>
+        <v>3.0430588722229</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G282" t="n">
-        <v>3.05494618415833</v>
+        <v>3.05494594573975</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>5.07499980926514</v>
       </c>
       <c r="G283" t="n">
-        <v>3.01631379127502</v>
+        <v>3.01631331443787</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G284" t="n">
-        <v>3.03414416313171</v>
+        <v>3.03414392471313</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G285" t="n">
-        <v>2.98362445831299</v>
+        <v>2.98362421989441</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G287" t="n">
-        <v>3.06386184692383</v>
+        <v>3.06386160850525</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>5.04500007629395</v>
       </c>
       <c r="G288" t="n">
-        <v>2.99848318099976</v>
+        <v>2.99848294258118</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>5.07499980926514</v>
       </c>
       <c r="G290" t="n">
-        <v>3.01631379127502</v>
+        <v>3.01631331443787</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>5.07499980926514</v>
       </c>
       <c r="G291" t="n">
-        <v>3.01631379127502</v>
+        <v>3.01631331443787</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G292" t="n">
-        <v>3.05791807174683</v>
+        <v>3.05791735649109</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G293" t="n">
-        <v>3.0906069278717</v>
+        <v>3.09060668945312</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>5.11499977111816</v>
       </c>
       <c r="G295" t="n">
-        <v>3.0400869846344</v>
+        <v>3.04008746147156</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G297" t="n">
-        <v>3.03711581230164</v>
+        <v>3.03711557388306</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G298" t="n">
-        <v>3.06088995933533</v>
+        <v>3.06088924407959</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G300" t="n">
-        <v>3.0906069278717</v>
+        <v>3.09060668945312</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>5.29500007629395</v>
       </c>
       <c r="G301" t="n">
-        <v>3.14707016944885</v>
+        <v>3.14706993103027</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G302" t="n">
-        <v>3.13221144676208</v>
+        <v>3.13221096992493</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G303" t="n">
-        <v>3.15598487854004</v>
+        <v>3.1559853553772</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G304" t="n">
-        <v>3.20353293418884</v>
+        <v>3.20353269577026</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G305" t="n">
-        <v>3.14409852027893</v>
+        <v>3.14409804344177</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>5.13500022888184</v>
       </c>
       <c r="G307" t="n">
-        <v>3.05197429656982</v>
+        <v>3.0519745349884</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G308" t="n">
-        <v>3.01928544044495</v>
+        <v>3.01928520202637</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>4.95599985122681</v>
       </c>
       <c r="G310" t="n">
-        <v>2.94558572769165</v>
+        <v>2.94558644294739</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G312" t="n">
-        <v>2.98362445831299</v>
+        <v>2.98362421989441</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>5</v>
       </c>
       <c r="G313" t="n">
-        <v>2.97173762321472</v>
+        <v>2.97173738479614</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>5.02500009536743</v>
       </c>
       <c r="G314" t="n">
-        <v>2.98659634590149</v>
+        <v>2.98659610748291</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>4.93200016021729</v>
       </c>
       <c r="G315" t="n">
-        <v>2.93132162094116</v>
+        <v>2.93132185935974</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G317" t="n">
-        <v>2.98956823348999</v>
+        <v>2.98956799507141</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G318" t="n">
-        <v>3.05791807174683</v>
+        <v>3.05791735649109</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G319" t="n">
-        <v>3.07277679443359</v>
+        <v>3.07277655601501</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G320" t="n">
-        <v>3.04305911064148</v>
+        <v>3.0430588722229</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>5.13500022888184</v>
       </c>
       <c r="G322" t="n">
-        <v>3.05197429656982</v>
+        <v>3.0519745349884</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G324" t="n">
-        <v>3.13815474510193</v>
+        <v>3.13815450668335</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G325" t="n">
-        <v>3.12626814842224</v>
+        <v>3.12626791000366</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G327" t="n">
-        <v>3.12626814842224</v>
+        <v>3.12626791000366</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G328" t="n">
-        <v>3.08466339111328</v>
+        <v>3.08466362953186</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G329" t="n">
-        <v>3.10843753814697</v>
+        <v>3.10843706130981</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G330" t="n">
-        <v>3.0906069278717</v>
+        <v>3.09060668945312</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G331" t="n">
-        <v>3.10843753814697</v>
+        <v>3.10843706130981</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>5.29500007629395</v>
       </c>
       <c r="G332" t="n">
-        <v>3.14707016944885</v>
+        <v>3.14706993103027</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G333" t="n">
-        <v>3.18570256233215</v>
+        <v>3.18570232391357</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G336" t="n">
-        <v>3.15004181861877</v>
+        <v>3.15004110336304</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>5.28499984741211</v>
       </c>
       <c r="G337" t="n">
-        <v>3.14112615585327</v>
+        <v>3.14112663269043</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>5.17500019073486</v>
       </c>
       <c r="G338" t="n">
-        <v>3.07574868202209</v>
+        <v>3.07574796676636</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G339" t="n">
-        <v>3.18570256233215</v>
+        <v>3.18570232391357</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G340" t="n">
-        <v>3.20947670936584</v>
+        <v>3.20947623252869</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>5.44500017166138</v>
       </c>
       <c r="G341" t="n">
-        <v>3.23622250556946</v>
+        <v>3.2362220287323</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G344" t="n">
-        <v>3.16192865371704</v>
+        <v>3.16192889213562</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G346" t="n">
-        <v>3.04900288581848</v>
+        <v>3.0490026473999</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G347" t="n">
-        <v>3.05791807174683</v>
+        <v>3.05791735649109</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G348" t="n">
-        <v>3.08466339111328</v>
+        <v>3.08466362953186</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G350" t="n">
-        <v>3.05494618415833</v>
+        <v>3.05494594573975</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G351" t="n">
-        <v>3.06088995933533</v>
+        <v>3.06088924407959</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>5.21500015258789</v>
       </c>
       <c r="G352" t="n">
-        <v>3.09952235221863</v>
+        <v>3.09952211380005</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>5.17500019073486</v>
       </c>
       <c r="G353" t="n">
-        <v>3.07574868202209</v>
+        <v>3.07574796676636</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>5.16499996185303</v>
       </c>
       <c r="G354" t="n">
-        <v>3.06980490684509</v>
+        <v>3.06980466842651</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G355" t="n">
-        <v>3.07277679443359</v>
+        <v>3.07277655601501</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G356" t="n">
-        <v>3.06088995933533</v>
+        <v>3.06088924407959</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G357" t="n">
-        <v>3.05791807174683</v>
+        <v>3.05791735649109</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>5.125</v>
       </c>
       <c r="G358" t="n">
-        <v>3.04603099822998</v>
+        <v>3.0460307598114</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G359" t="n">
-        <v>3.07277679443359</v>
+        <v>3.07277655601501</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>5.13500022888184</v>
       </c>
       <c r="G360" t="n">
-        <v>3.05197429656982</v>
+        <v>3.0519745349884</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>5.13500022888184</v>
       </c>
       <c r="G361" t="n">
-        <v>3.05197429656982</v>
+        <v>3.0519745349884</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G363" t="n">
-        <v>3.05494618415833</v>
+        <v>3.05494594573975</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G364" t="n">
-        <v>3.05791807174683</v>
+        <v>3.05791735649109</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>5.13500022888184</v>
       </c>
       <c r="G365" t="n">
-        <v>3.05197429656982</v>
+        <v>3.0519745349884</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G366" t="n">
-        <v>3.05494618415833</v>
+        <v>3.05494594573975</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>5.125</v>
       </c>
       <c r="G367" t="n">
-        <v>3.04603099822998</v>
+        <v>3.0460307598114</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G368" t="n">
-        <v>3.06088995933533</v>
+        <v>3.06088924407959</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G369" t="n">
-        <v>3.0906069278717</v>
+        <v>3.09060668945312</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G371" t="n">
-        <v>3.15598487854004</v>
+        <v>3.1559853553772</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G372" t="n">
-        <v>3.09655022621155</v>
+        <v>3.09655046463013</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G373" t="n">
-        <v>3.07277679443359</v>
+        <v>3.07277655601501</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G374" t="n">
-        <v>3.09655022621155</v>
+        <v>3.09655046463013</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>5.25500011444092</v>
       </c>
       <c r="G375" t="n">
-        <v>3.12329626083374</v>
+        <v>3.12329602241516</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>5.09499979019165</v>
       </c>
       <c r="G377" t="n">
-        <v>3.02820014953613</v>
+        <v>3.02820062637329</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>5.09499979019165</v>
       </c>
       <c r="G378" t="n">
-        <v>3.02820014953613</v>
+        <v>3.02820062637329</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G379" t="n">
-        <v>3.04900288581848</v>
+        <v>3.0490026473999</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G380" t="n">
-        <v>3.04305911064148</v>
+        <v>3.0430588722229</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>4.98799991607666</v>
       </c>
       <c r="G381" t="n">
-        <v>2.96460485458374</v>
+        <v>2.96460509300232</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G383" t="n">
-        <v>2.79937696456909</v>
+        <v>2.79937648773193</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G384" t="n">
-        <v>2.7696590423584</v>
+        <v>2.76965928077698</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G386" t="n">
-        <v>2.78748941421509</v>
+        <v>2.78748989105225</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>4.68400001525879</v>
       </c>
       <c r="G387" t="n">
-        <v>2.7839241027832</v>
+        <v>2.78392338752747</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G388" t="n">
-        <v>2.85881161689758</v>
+        <v>2.858811378479</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>4.71400022506714</v>
       </c>
       <c r="G389" t="n">
-        <v>2.80175447463989</v>
+        <v>2.80175423622131</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>4.59600019454956</v>
       </c>
       <c r="G391" t="n">
-        <v>2.7316210269928</v>
+        <v>2.73162078857422</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>4.58199977874756</v>
       </c>
       <c r="G392" t="n">
-        <v>2.723299741745</v>
+        <v>2.72329998016357</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>4.43400001525879</v>
       </c>
       <c r="G393" t="n">
-        <v>2.63533663749695</v>
+        <v>2.63533687591553</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>4.33599996566772</v>
       </c>
       <c r="G394" t="n">
-        <v>2.57709050178528</v>
+        <v>2.57709074020386</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>4.49599981307983</v>
       </c>
       <c r="G398" t="n">
-        <v>2.67218613624573</v>
+        <v>2.67218589782715</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G399" t="n">
-        <v>2.70428109169006</v>
+        <v>2.70428133010864</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G400" t="n">
-        <v>2.70428109169006</v>
+        <v>2.70428133010864</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G402" t="n">
-        <v>2.71022462844849</v>
+        <v>2.71022415161133</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G403" t="n">
-        <v>2.68645024299622</v>
+        <v>2.68645048141479</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G407" t="n">
-        <v>2.73994207382202</v>
+        <v>2.73994183540344</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>4.70599985122681</v>
       </c>
       <c r="G408" t="n">
-        <v>2.79699921607971</v>
+        <v>2.79699873924255</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>4.57600021362305</v>
       </c>
       <c r="G409" t="n">
-        <v>2.71973395347595</v>
+        <v>2.71973443031311</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>4.57600021362305</v>
       </c>
       <c r="G410" t="n">
-        <v>2.71973395347595</v>
+        <v>2.71973443031311</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>4.51599979400635</v>
       </c>
       <c r="G411" t="n">
-        <v>2.68407344818115</v>
+        <v>2.68407297134399</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G412" t="n">
-        <v>2.71022462844849</v>
+        <v>2.71022415161133</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>4.48799991607666</v>
       </c>
       <c r="G413" t="n">
-        <v>2.66743135452271</v>
+        <v>2.66743159294128</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G414" t="n">
-        <v>2.70428109169006</v>
+        <v>2.70428133010864</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>4.56599998474121</v>
       </c>
       <c r="G416" t="n">
-        <v>2.71379041671753</v>
+        <v>2.71379065513611</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G417" t="n">
-        <v>2.79343318939209</v>
+        <v>2.79343295097351</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>4.67199993133545</v>
       </c>
       <c r="G418" t="n">
-        <v>2.77679133415222</v>
+        <v>2.7767915725708</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G419" t="n">
-        <v>2.72805523872375</v>
+        <v>2.7280547618866</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>4.59800004959106</v>
       </c>
       <c r="G420" t="n">
-        <v>2.7328097820282</v>
+        <v>2.73280930519104</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G421" t="n">
-        <v>2.74588513374329</v>
+        <v>2.74588489532471</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>4.6560001373291</v>
       </c>
       <c r="G423" t="n">
-        <v>2.76728200912476</v>
+        <v>2.7672815322876</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>4.59800004959106</v>
       </c>
       <c r="G424" t="n">
-        <v>2.7328097820282</v>
+        <v>2.73280930519104</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>4.53599977493286</v>
       </c>
       <c r="G425" t="n">
-        <v>2.69596028327942</v>
+        <v>2.69596004486084</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>4.46199989318848</v>
       </c>
       <c r="G428" t="n">
-        <v>2.65197825431824</v>
+        <v>2.65197849273682</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>4.61800003051758</v>
       </c>
       <c r="G430" t="n">
-        <v>2.74469685554504</v>
+        <v>2.74469661712646</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>4.53399991989136</v>
       </c>
       <c r="G431" t="n">
-        <v>2.69477128982544</v>
+        <v>2.6947717666626</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G432" t="n">
-        <v>2.65673303604126</v>
+        <v>2.65673327445984</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>4.48199987411499</v>
       </c>
       <c r="G433" t="n">
-        <v>2.66386532783508</v>
+        <v>2.66386485099792</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G434" t="n">
-        <v>2.6923942565918</v>
+        <v>2.69239401817322</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>4.49599981307983</v>
       </c>
       <c r="G436" t="n">
-        <v>2.67218613624573</v>
+        <v>2.67218589782715</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>4.72800016403198</v>
       </c>
       <c r="G440" t="n">
-        <v>2.8100745677948</v>
+        <v>2.81007480621338</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>4.85599994659424</v>
       </c>
       <c r="G444" t="n">
-        <v>2.88615131378174</v>
+        <v>2.88615155220032</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>4.78399991989136</v>
       </c>
       <c r="G445" t="n">
-        <v>2.84335827827454</v>
+        <v>2.84335803985596</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>4.78399991989136</v>
       </c>
       <c r="G446" t="n">
-        <v>2.84335827827454</v>
+        <v>2.84335803985596</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>4.73199987411499</v>
       </c>
       <c r="G447" t="n">
-        <v>2.81245183944702</v>
+        <v>2.81245231628418</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>4.76800012588501</v>
       </c>
       <c r="G448" t="n">
-        <v>2.83384871482849</v>
+        <v>2.83384895324707</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G451" t="n">
-        <v>2.89447236061096</v>
+        <v>2.89447212219238</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>4.84600019454956</v>
       </c>
       <c r="G452" t="n">
-        <v>2.88020801544189</v>
+        <v>2.88020777702332</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>4.86199998855591</v>
       </c>
       <c r="G454" t="n">
-        <v>2.88971757888794</v>
+        <v>2.88971781730652</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>4.87799978256226</v>
       </c>
       <c r="G455" t="n">
-        <v>2.89922666549683</v>
+        <v>2.89922690391541</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>4.92399978637695</v>
       </c>
       <c r="G456" t="n">
-        <v>2.92656660079956</v>
+        <v>2.92656683921814</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G458" t="n">
-        <v>3.00145530700684</v>
+        <v>3.00145506858826</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G459" t="n">
-        <v>3.03711581230164</v>
+        <v>3.03711557388306</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G460" t="n">
-        <v>3.04305911064148</v>
+        <v>3.0430588722229</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>5.02500009536743</v>
       </c>
       <c r="G461" t="n">
-        <v>2.98659634590149</v>
+        <v>2.98659610748291</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G463" t="n">
-        <v>3.04900288581848</v>
+        <v>3.0490026473999</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G464" t="n">
-        <v>3.04305911064148</v>
+        <v>3.0430588722229</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>4.98600006103516</v>
       </c>
       <c r="G465" t="n">
-        <v>2.96341633796692</v>
+        <v>2.9634165763855</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>5.11499977111816</v>
       </c>
       <c r="G466" t="n">
-        <v>3.0400869846344</v>
+        <v>3.04008746147156</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G467" t="n">
-        <v>3.05494618415833</v>
+        <v>3.05494594573975</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>5.25</v>
       </c>
       <c r="G468" t="n">
-        <v>3.12032437324524</v>
+        <v>3.12032413482666</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>5.25</v>
       </c>
       <c r="G470" t="n">
-        <v>3.12032437324524</v>
+        <v>3.12032413482666</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G471" t="n">
-        <v>3.16192865371704</v>
+        <v>3.16192889213562</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G475" t="n">
-        <v>3.15004181861877</v>
+        <v>3.15004110336304</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G476" t="n">
-        <v>3.13518333435059</v>
+        <v>3.13518285751343</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G477" t="n">
-        <v>3.15004181861877</v>
+        <v>3.15004110336304</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G478" t="n">
-        <v>3.0906069278717</v>
+        <v>3.09060668945312</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>5.24499988555908</v>
       </c>
       <c r="G480" t="n">
-        <v>3.11735248565674</v>
+        <v>3.11735272407532</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G481" t="n">
-        <v>3.14409852027893</v>
+        <v>3.14409804344177</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G482" t="n">
-        <v>3.15004181861877</v>
+        <v>3.15004110336304</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>5.30499982833862</v>
       </c>
       <c r="G483" t="n">
-        <v>3.1530134677887</v>
+        <v>3.15301322937012</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G487" t="n">
-        <v>3.18570256233215</v>
+        <v>3.18570232391357</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G490" t="n">
-        <v>3.2273063659668</v>
+        <v>3.22730708122253</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>5.49499988555908</v>
       </c>
       <c r="G491" t="n">
-        <v>3.26593947410583</v>
+        <v>3.26593923568726</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>5.57499980926514</v>
       </c>
       <c r="G492" t="n">
-        <v>3.31348729133606</v>
+        <v>3.31348657608032</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G493" t="n">
-        <v>3.2807981967926</v>
+        <v>3.28079795837402</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G494" t="n">
-        <v>3.29862880706787</v>
+        <v>3.29862833023071</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G495" t="n">
-        <v>3.29862880706787</v>
+        <v>3.29862833023071</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G496" t="n">
-        <v>3.29268503189087</v>
+        <v>3.29268455505371</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>5.54500007629395</v>
       </c>
       <c r="G498" t="n">
-        <v>3.29565691947937</v>
+        <v>3.29565668106079</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>5.42500019073486</v>
       </c>
       <c r="G501" t="n">
-        <v>3.22433543205261</v>
+        <v>3.22433495521545</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>4.99499988555908</v>
       </c>
       <c r="G502" t="n">
-        <v>3.2962658405304</v>
+        <v>3.29626560211182</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>4.96500015258789</v>
       </c>
       <c r="G503" t="n">
-        <v>3.27646851539612</v>
+        <v>3.27646827697754</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G504" t="n">
-        <v>3.28306746482849</v>
+        <v>3.28306722640991</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G506" t="n">
-        <v>3.38535451889038</v>
+        <v>3.38535380363464</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G507" t="n">
-        <v>3.33256125450134</v>
+        <v>3.33256101608276</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G508" t="n">
-        <v>3.32596182823181</v>
+        <v>3.32596135139465</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G509" t="n">
-        <v>3.31936311721802</v>
+        <v>3.31936264038086</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G510" t="n">
-        <v>3.34575963020325</v>
+        <v>3.34575915336609</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G512" t="n">
-        <v>3.40515112876892</v>
+        <v>3.4051513671875</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G515" t="n">
-        <v>3.41175079345703</v>
+        <v>3.41175055503845</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G516" t="n">
-        <v>3.47114276885986</v>
+        <v>3.47114253044128</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G517" t="n">
-        <v>3.47114276885986</v>
+        <v>3.47114253044128</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G518" t="n">
-        <v>3.49094009399414</v>
+        <v>3.49093961715698</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G519" t="n">
-        <v>3.50413846969604</v>
+        <v>3.50413870811462</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G521" t="n">
-        <v>3.47114276885986</v>
+        <v>3.47114253044128</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>5.25</v>
       </c>
       <c r="G522" t="n">
-        <v>3.46454381942749</v>
+        <v>3.46454358100891</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G523" t="n">
-        <v>3.43154788017273</v>
+        <v>3.43154764175415</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G524" t="n">
-        <v>3.39855241775513</v>
+        <v>3.39855289459229</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G525" t="n">
-        <v>3.38535451889038</v>
+        <v>3.38535380363464</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G526" t="n">
-        <v>3.35895776748657</v>
+        <v>3.35895752906799</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G527" t="n">
-        <v>3.33256125450134</v>
+        <v>3.33256101608276</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G529" t="n">
-        <v>3.2797679901123</v>
+        <v>3.27976751327515</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G531" t="n">
-        <v>3.28306746482849</v>
+        <v>3.28306722640991</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G534" t="n">
-        <v>3.27316880226135</v>
+        <v>3.27316856384277</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G535" t="n">
-        <v>3.30616450309753</v>
+        <v>3.30616474151611</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G536" t="n">
-        <v>3.2665696144104</v>
+        <v>3.26656937599182</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G537" t="n">
-        <v>3.14778518676758</v>
+        <v>3.14778542518616</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G538" t="n">
-        <v>3.19397926330566</v>
+        <v>3.19397950172424</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G539" t="n">
-        <v>3.22037601470947</v>
+        <v>3.22037553787231</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G540" t="n">
-        <v>3.2038779258728</v>
+        <v>3.20387768745422</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G542" t="n">
-        <v>3.2038779258728</v>
+        <v>3.20387768745422</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>4.77500009536743</v>
       </c>
       <c r="G543" t="n">
-        <v>3.15108466148376</v>
+        <v>3.15108489990234</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>4.74499988555908</v>
       </c>
       <c r="G544" t="n">
-        <v>3.13128733634949</v>
+        <v>3.13128757476807</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G547" t="n">
-        <v>3.31936311721802</v>
+        <v>3.31936264038086</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G548" t="n">
-        <v>3.2665696144104</v>
+        <v>3.26656937599182</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G550" t="n">
-        <v>3.28306746482849</v>
+        <v>3.28306722640991</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>4.96500015258789</v>
       </c>
       <c r="G552" t="n">
-        <v>3.27646851539612</v>
+        <v>3.27646827697754</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>4.93499994277954</v>
       </c>
       <c r="G553" t="n">
-        <v>3.25667119026184</v>
+        <v>3.25667071342468</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G554" t="n">
-        <v>3.24017310142517</v>
+        <v>3.24017286300659</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G557" t="n">
-        <v>3.31936311721802</v>
+        <v>3.31936264038086</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G558" t="n">
-        <v>3.28306746482849</v>
+        <v>3.28306722640991</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G559" t="n">
-        <v>3.28306746482849</v>
+        <v>3.28306722640991</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G560" t="n">
-        <v>3.22037601470947</v>
+        <v>3.22037553787231</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G561" t="n">
-        <v>3.20717787742615</v>
+        <v>3.20717740058899</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G564" t="n">
-        <v>3.25997042655945</v>
+        <v>3.25997066497803</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G567" t="n">
-        <v>3.33256125450134</v>
+        <v>3.33256101608276</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G569" t="n">
-        <v>3.35235834121704</v>
+        <v>3.35235810279846</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G570" t="n">
-        <v>3.33256125450134</v>
+        <v>3.33256101608276</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G571" t="n">
-        <v>3.35895776748657</v>
+        <v>3.35895752906799</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G573" t="n">
-        <v>3.34575963020325</v>
+        <v>3.34575915336609</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G574" t="n">
-        <v>3.32596182823181</v>
+        <v>3.32596135139465</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>4.99499988555908</v>
       </c>
       <c r="G575" t="n">
-        <v>3.2962658405304</v>
+        <v>3.29626560211182</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G576" t="n">
-        <v>3.31936311721802</v>
+        <v>3.31936264038086</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>4.99499988555908</v>
       </c>
       <c r="G577" t="n">
-        <v>3.2962658405304</v>
+        <v>3.29626560211182</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>4.92500019073486</v>
       </c>
       <c r="G578" t="n">
-        <v>3.25007200241089</v>
+        <v>3.25007176399231</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G581" t="n">
-        <v>3.22037601470947</v>
+        <v>3.22037553787231</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G583" t="n">
-        <v>3.28306746482849</v>
+        <v>3.28306722640991</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>4.92500019073486</v>
       </c>
       <c r="G584" t="n">
-        <v>3.25007200241089</v>
+        <v>3.25007176399231</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G585" t="n">
-        <v>3.22697472572327</v>
+        <v>3.22697448730469</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>4.96500015258789</v>
       </c>
       <c r="G587" t="n">
-        <v>3.27646851539612</v>
+        <v>3.27646827697754</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G588" t="n">
-        <v>3.23027420043945</v>
+        <v>3.23027443885803</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G589" t="n">
-        <v>3.2038779258728</v>
+        <v>3.20387768745422</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G590" t="n">
-        <v>3.27316880226135</v>
+        <v>3.27316856384277</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>4.96500015258789</v>
       </c>
       <c r="G591" t="n">
-        <v>3.27646851539612</v>
+        <v>3.27646827697754</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G592" t="n">
-        <v>3.20717787742615</v>
+        <v>3.20717740058899</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G593" t="n">
-        <v>2.98610663414001</v>
+        <v>2.98610639572144</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G594" t="n">
-        <v>2.93001413345337</v>
+        <v>2.93001365661621</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G595" t="n">
-        <v>3.00920367240906</v>
+        <v>3.00920391082764</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G597" t="n">
-        <v>3.03559994697571</v>
+        <v>3.03560018539429</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>4.7350001335144</v>
       </c>
       <c r="G598" t="n">
-        <v>3.12468838691711</v>
+        <v>3.12468814849854</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G601" t="n">
-        <v>3.03559994697571</v>
+        <v>3.03560018539429</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G603" t="n">
-        <v>3.00260424613953</v>
+        <v>3.00260472297668</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G605" t="n">
-        <v>3.01580238342285</v>
+        <v>3.01580262184143</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G607" t="n">
-        <v>3.04219913482666</v>
+        <v>3.04219889640808</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G608" t="n">
-        <v>3.05539751052856</v>
+        <v>3.05539727210999</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G609" t="n">
-        <v>3.06859564781189</v>
+        <v>3.06859517097473</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G610" t="n">
-        <v>3.06859564781189</v>
+        <v>3.06859517097473</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G611" t="n">
-        <v>3.08839273452759</v>
+        <v>3.08839297294617</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G612" t="n">
-        <v>3.08179378509521</v>
+        <v>3.08179402351379</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G614" t="n">
-        <v>3.17418193817139</v>
+        <v>3.17418146133423</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G615" t="n">
-        <v>3.17418193817139</v>
+        <v>3.17418146133423</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G616" t="n">
-        <v>3.1576840877533</v>
+        <v>3.15768384933472</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G617" t="n">
-        <v>3.20717787742615</v>
+        <v>3.20717740058899</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G618" t="n">
-        <v>3.18738007545471</v>
+        <v>3.18737983703613</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G619" t="n">
-        <v>3.15438485145569</v>
+        <v>3.15438437461853</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G620" t="n">
-        <v>3.18078112602234</v>
+        <v>3.18078064918518</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G623" t="n">
-        <v>3.16758298873901</v>
+        <v>3.16758251190186</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>4.77500009536743</v>
       </c>
       <c r="G624" t="n">
-        <v>3.15108466148376</v>
+        <v>3.15108489990234</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>4.74499988555908</v>
       </c>
       <c r="G625" t="n">
-        <v>3.13128733634949</v>
+        <v>3.13128757476807</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G626" t="n">
-        <v>3.1576840877533</v>
+        <v>3.15768384933472</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G627" t="n">
-        <v>3.17418193817139</v>
+        <v>3.17418146133423</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G628" t="n">
-        <v>3.1576840877533</v>
+        <v>3.15768384933472</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>4.75500011444092</v>
       </c>
       <c r="G629" t="n">
-        <v>3.13788676261902</v>
+        <v>3.13788652420044</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G630" t="n">
-        <v>3.10159134864807</v>
+        <v>3.10159111022949</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G633" t="n">
-        <v>3.16758298873901</v>
+        <v>3.16758251190186</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G635" t="n">
-        <v>3.20057821273804</v>
+        <v>3.20057845115662</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G637" t="n">
-        <v>3.28306746482849</v>
+        <v>3.28306722640991</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G638" t="n">
-        <v>3.31936311721802</v>
+        <v>3.31936264038086</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G639" t="n">
-        <v>3.35895776748657</v>
+        <v>3.35895752906799</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>5.25</v>
       </c>
       <c r="G641" t="n">
-        <v>3.46454381942749</v>
+        <v>3.46454358100891</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G644" t="n">
-        <v>3.55033206939697</v>
+        <v>3.55033230781555</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G645" t="n">
-        <v>3.54373335838318</v>
+        <v>3.54373288154602</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G646" t="n">
-        <v>3.53053498268127</v>
+        <v>3.5305347442627</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G647" t="n">
-        <v>3.55693125724792</v>
+        <v>3.55693101882935</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G648" t="n">
-        <v>3.59652614593506</v>
+        <v>3.59652590751648</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G649" t="n">
-        <v>3.61632323265076</v>
+        <v>3.61632347106934</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G652" t="n">
-        <v>3.60972452163696</v>
+        <v>3.60972476005554</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G653" t="n">
-        <v>3.60972452163696</v>
+        <v>3.60972476005554</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G654" t="n">
-        <v>3.60972452163696</v>
+        <v>3.60972476005554</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G655" t="n">
-        <v>3.56353068351746</v>
+        <v>3.56353092193604</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>5.5</v>
       </c>
       <c r="G656" t="n">
-        <v>3.62952208518982</v>
+        <v>3.62952184677124</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G657" t="n">
-        <v>3.53053498268127</v>
+        <v>3.5305347442627</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G659" t="n">
-        <v>3.53053498268127</v>
+        <v>3.5305347442627</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G660" t="n">
-        <v>3.53053498268127</v>
+        <v>3.5305347442627</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G662" t="n">
-        <v>3.56353068351746</v>
+        <v>3.56353092193604</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G664" t="n">
-        <v>3.47114276885986</v>
+        <v>3.47114253044128</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G665" t="n">
-        <v>3.44474601745605</v>
+        <v>3.4447455406189</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G666" t="n">
-        <v>3.47114276885986</v>
+        <v>3.47114253044128</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G667" t="n">
-        <v>3.53053498268127</v>
+        <v>3.5305347442627</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G668" t="n">
-        <v>3.55693125724792</v>
+        <v>3.55693101882935</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G669" t="n">
-        <v>3.57012963294983</v>
+        <v>3.57012939453125</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G670" t="n">
-        <v>3.57672882080078</v>
+        <v>3.5767285823822</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G671" t="n">
-        <v>3.60972452163696</v>
+        <v>3.60972476005554</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G672" t="n">
-        <v>3.60312509536743</v>
+        <v>3.60312485694885</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G673" t="n">
-        <v>3.54373335838318</v>
+        <v>3.54373288154602</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G674" t="n">
-        <v>3.53053498268127</v>
+        <v>3.5305347442627</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G675" t="n">
-        <v>3.53713393211365</v>
+        <v>3.53713417053223</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G676" t="n">
-        <v>3.55033206939697</v>
+        <v>3.55033230781555</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G677" t="n">
-        <v>3.57012963294983</v>
+        <v>3.57012939453125</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G679" t="n">
-        <v>3.49753952026367</v>
+        <v>3.49753904342651</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G680" t="n">
-        <v>3.54373335838318</v>
+        <v>3.54373288154602</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G681" t="n">
-        <v>3.53053498268127</v>
+        <v>3.5305347442627</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G683" t="n">
-        <v>3.49094009399414</v>
+        <v>3.49093961715698</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G684" t="n">
-        <v>3.50413846969604</v>
+        <v>3.50413870811462</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G685" t="n">
-        <v>3.55033206939697</v>
+        <v>3.55033230781555</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G686" t="n">
-        <v>3.53053498268127</v>
+        <v>3.5305347442627</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G688" t="n">
-        <v>3.49753952026367</v>
+        <v>3.49753904342651</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G689" t="n">
-        <v>3.47774195671082</v>
+        <v>3.47774147987366</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G691" t="n">
-        <v>3.54373335838318</v>
+        <v>3.54373288154602</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G692" t="n">
-        <v>3.50413846969604</v>
+        <v>3.50413870811462</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G693" t="n">
-        <v>3.49753952026367</v>
+        <v>3.49753904342651</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G694" t="n">
-        <v>3.53053498268127</v>
+        <v>3.5305347442627</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G695" t="n">
-        <v>3.53713393211365</v>
+        <v>3.53713417053223</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G696" t="n">
-        <v>3.55693125724792</v>
+        <v>3.55693101882935</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G697" t="n">
-        <v>3.53053498268127</v>
+        <v>3.5305347442627</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G699" t="n">
-        <v>3.55693125724792</v>
+        <v>3.55693101882935</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G700" t="n">
-        <v>3.56353068351746</v>
+        <v>3.56353092193604</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G701" t="n">
-        <v>3.53713393211365</v>
+        <v>3.53713417053223</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G702" t="n">
-        <v>3.58992719650269</v>
+        <v>3.58992648124695</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>5.5</v>
       </c>
       <c r="G703" t="n">
-        <v>3.62952208518982</v>
+        <v>3.62952184677124</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G704" t="n">
-        <v>3.70871138572693</v>
+        <v>3.70871090888977</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G705" t="n">
-        <v>3.72850871086121</v>
+        <v>3.72850894927979</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G706" t="n">
-        <v>3.74170708656311</v>
+        <v>3.74170732498169</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>5.75</v>
       </c>
       <c r="G707" t="n">
-        <v>3.79449987411499</v>
+        <v>3.79450011253357</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>5.75</v>
       </c>
       <c r="G708" t="n">
-        <v>3.79449987411499</v>
+        <v>3.79450011253357</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G709" t="n">
-        <v>3.80769824981689</v>
+        <v>3.80769848823547</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G710" t="n">
-        <v>3.74830555915833</v>
+        <v>3.7483057975769</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G711" t="n">
-        <v>3.66251754760742</v>
+        <v>3.662517786026</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G712" t="n">
-        <v>3.66251754760742</v>
+        <v>3.662517786026</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G713" t="n">
-        <v>3.68891406059265</v>
+        <v>3.68891382217407</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G714" t="n">
-        <v>3.70871138572693</v>
+        <v>3.70871090888977</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G715" t="n">
-        <v>3.77470231056213</v>
+        <v>3.77470302581787</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G716" t="n">
-        <v>3.74830555915833</v>
+        <v>3.7483057975769</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G717" t="n">
-        <v>3.74830555915833</v>
+        <v>3.7483057975769</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G718" t="n">
-        <v>3.78790068626404</v>
+        <v>3.78790044784546</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G719" t="n">
-        <v>3.78130173683167</v>
+        <v>3.78130197525024</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G720" t="n">
-        <v>3.82749533653259</v>
+        <v>3.82749557495117</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G721" t="n">
-        <v>3.82749533653259</v>
+        <v>3.82749557495117</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G722" t="n">
-        <v>3.87368965148926</v>
+        <v>3.87368941307068</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G723" t="n">
-        <v>3.93308186531067</v>
+        <v>3.93308162689209</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G724" t="n">
-        <v>3.93308186531067</v>
+        <v>3.93308162689209</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G727" t="n">
-        <v>3.9924738407135</v>
+        <v>3.99247407913208</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G728" t="n">
-        <v>3.76150393486023</v>
+        <v>3.76150465011597</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G729" t="n">
-        <v>3.72190928459167</v>
+        <v>3.72190976142883</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G731" t="n">
-        <v>3.75490546226501</v>
+        <v>3.75490474700928</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G732" t="n">
-        <v>3.6493194103241</v>
+        <v>3.64931893348694</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G734" t="n">
-        <v>3.55693125724792</v>
+        <v>3.55693101882935</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G736" t="n">
-        <v>3.47774195671082</v>
+        <v>3.47774147987366</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G737" t="n">
-        <v>3.28306746482849</v>
+        <v>3.28306722640991</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G738" t="n">
-        <v>3.06859564781189</v>
+        <v>3.06859517097473</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>4.58500003814697</v>
       </c>
       <c r="G739" t="n">
-        <v>3.02570128440857</v>
+        <v>3.02570152282715</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>4.17500019073486</v>
       </c>
       <c r="G741" t="n">
-        <v>2.75513696670532</v>
+        <v>2.7551372051239</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G742" t="n">
-        <v>2.90361738204956</v>
+        <v>2.90361762046814</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G743" t="n">
-        <v>2.76503586769104</v>
+        <v>2.76503562927246</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>4.07499980926514</v>
       </c>
       <c r="G745" t="n">
-        <v>2.68914532661438</v>
+        <v>2.68914580345154</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>4.27500009536743</v>
       </c>
       <c r="G746" t="n">
-        <v>2.82112836837769</v>
+        <v>2.82112860679626</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>4.65500020980835</v>
       </c>
       <c r="G747" t="n">
-        <v>3.07189559936523</v>
+        <v>3.07189536094666</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>4.56500005722046</v>
       </c>
       <c r="G748" t="n">
-        <v>3.01250338554382</v>
+        <v>3.01250267028809</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G750" t="n">
-        <v>3.06859564781189</v>
+        <v>3.06859517097473</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G752" t="n">
-        <v>3.16758298873901</v>
+        <v>3.16758251190186</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G754" t="n">
-        <v>3.12138891220093</v>
+        <v>3.12138867378235</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G755" t="n">
-        <v>3.11808919906616</v>
+        <v>3.118088722229</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G757" t="n">
-        <v>3.01580238342285</v>
+        <v>3.01580262184143</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G758" t="n">
-        <v>3.10159134864807</v>
+        <v>3.10159111022949</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G762" t="n">
-        <v>3.25997042655945</v>
+        <v>3.25997066497803</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>4.86499977111816</v>
       </c>
       <c r="G763" t="n">
-        <v>3.21047687530518</v>
+        <v>3.2104766368866</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G765" t="n">
-        <v>3.08839273452759</v>
+        <v>3.08839297294617</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G766" t="n">
-        <v>3.08179378509521</v>
+        <v>3.08179402351379</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G767" t="n">
-        <v>3.11808919906616</v>
+        <v>3.118088722229</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G768" t="n">
-        <v>3.1147894859314</v>
+        <v>3.11478972434998</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G769" t="n">
-        <v>3.11808919906616</v>
+        <v>3.118088722229</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G770" t="n">
-        <v>3.10159134864807</v>
+        <v>3.10159111022949</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G771" t="n">
-        <v>3.1576840877533</v>
+        <v>3.15768384933472</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G772" t="n">
-        <v>3.24017310142517</v>
+        <v>3.24017286300659</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G773" t="n">
-        <v>3.24017310142517</v>
+        <v>3.24017286300659</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>4.71500015258789</v>
       </c>
       <c r="G774" t="n">
-        <v>3.11149024963379</v>
+        <v>3.11148977279663</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G775" t="n">
-        <v>3.00260424613953</v>
+        <v>3.00260472297668</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G777" t="n">
-        <v>3.06199645996094</v>
+        <v>3.06199622154236</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G778" t="n">
-        <v>2.98280668258667</v>
+        <v>2.98280692100525</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G780" t="n">
-        <v>3.17418193817139</v>
+        <v>3.17418146133423</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G784" t="n">
-        <v>3.22697472572327</v>
+        <v>3.22697448730469</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G785" t="n">
-        <v>3.37875485420227</v>
+        <v>3.37875437736511</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G787" t="n">
-        <v>3.2665696144104</v>
+        <v>3.26656937599182</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>4.92500019073486</v>
       </c>
       <c r="G788" t="n">
-        <v>3.25007200241089</v>
+        <v>3.25007176399231</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G789" t="n">
-        <v>3.30616450309753</v>
+        <v>3.30616474151611</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G790" t="n">
-        <v>3.33256125450134</v>
+        <v>3.33256101608276</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G791" t="n">
-        <v>3.41175079345703</v>
+        <v>3.41175055503845</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G792" t="n">
-        <v>3.44474601745605</v>
+        <v>3.4447455406189</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G793" t="n">
-        <v>3.41175079345703</v>
+        <v>3.41175055503845</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G796" t="n">
-        <v>3.35235834121704</v>
+        <v>3.35235810279846</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G798" t="n">
-        <v>3.37875485420227</v>
+        <v>3.37875437736511</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G799" t="n">
-        <v>3.40515112876892</v>
+        <v>3.4051513671875</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G800" t="n">
-        <v>3.37875485420227</v>
+        <v>3.37875437736511</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>4.79500007629395</v>
       </c>
       <c r="G803" t="n">
-        <v>3.16428303718567</v>
+        <v>3.16428327560425</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G804" t="n">
-        <v>3.11808919906616</v>
+        <v>3.118088722229</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G805" t="n">
-        <v>3.10159134864807</v>
+        <v>3.10159111022949</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G806" t="n">
-        <v>3.16758298873901</v>
+        <v>3.16758251190186</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G807" t="n">
-        <v>3.18078112602234</v>
+        <v>3.18078064918518</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G808" t="n">
-        <v>3.19397926330566</v>
+        <v>3.19397950172424</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G809" t="n">
-        <v>3.19397926330566</v>
+        <v>3.19397950172424</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G814" t="n">
-        <v>3.2665696144104</v>
+        <v>3.26656937599182</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>4.99499988555908</v>
       </c>
       <c r="G815" t="n">
-        <v>3.2962658405304</v>
+        <v>3.29626560211182</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G818" t="n">
-        <v>3.41175079345703</v>
+        <v>3.41175055503845</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G819" t="n">
-        <v>3.42494893074036</v>
+        <v>3.42494869232178</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G820" t="n">
-        <v>3.39855241775513</v>
+        <v>3.39855289459229</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G822" t="n">
-        <v>3.38535451889038</v>
+        <v>3.38535380363464</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G824" t="n">
-        <v>3.39855241775513</v>
+        <v>3.39855289459229</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G825" t="n">
-        <v>3.31936311721802</v>
+        <v>3.31936264038086</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>4.92500019073486</v>
       </c>
       <c r="G826" t="n">
-        <v>3.25007200241089</v>
+        <v>3.25007176399231</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G827" t="n">
-        <v>3.2797679901123</v>
+        <v>3.27976751327515</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G828" t="n">
-        <v>3.32596182823181</v>
+        <v>3.32596135139465</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G829" t="n">
-        <v>3.30616450309753</v>
+        <v>3.30616474151611</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>4.99499988555908</v>
       </c>
       <c r="G830" t="n">
-        <v>3.2962658405304</v>
+        <v>3.29626560211182</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>4.91499996185303</v>
       </c>
       <c r="G834" t="n">
-        <v>3.24347233772278</v>
+        <v>3.24347257614136</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G835" t="n">
-        <v>3.22697472572327</v>
+        <v>3.22697448730469</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G837" t="n">
-        <v>3.19397926330566</v>
+        <v>3.19397950172424</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G838" t="n">
-        <v>3.18078112602234</v>
+        <v>3.18078064918518</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>4.86499977111816</v>
       </c>
       <c r="G841" t="n">
-        <v>3.21047687530518</v>
+        <v>3.2104766368866</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G843" t="n">
-        <v>3.16758298873901</v>
+        <v>3.16758251190186</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G845" t="n">
-        <v>3.16758298873901</v>
+        <v>3.16758251190186</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G846" t="n">
-        <v>3.14778518676758</v>
+        <v>3.14778542518616</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>4.75500011444092</v>
       </c>
       <c r="G847" t="n">
-        <v>3.13788676261902</v>
+        <v>3.13788652420044</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G848" t="n">
-        <v>3.14778518676758</v>
+        <v>3.14778542518616</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>4.68499994277954</v>
       </c>
       <c r="G850" t="n">
-        <v>3.09169268608093</v>
+        <v>3.09169244766235</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G852" t="n">
-        <v>3.06859564781189</v>
+        <v>3.06859517097473</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>4.64499998092651</v>
       </c>
       <c r="G854" t="n">
-        <v>3.06529569625854</v>
+        <v>3.0652961730957</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G855" t="n">
-        <v>3.06199645996094</v>
+        <v>3.06199622154236</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G856" t="n">
-        <v>3.05539751052856</v>
+        <v>3.05539727210999</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G857" t="n">
-        <v>3.05539751052856</v>
+        <v>3.05539727210999</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G858" t="n">
-        <v>3.06859564781189</v>
+        <v>3.06859517097473</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>4.65500020980835</v>
       </c>
       <c r="G860" t="n">
-        <v>3.07189559936523</v>
+        <v>3.07189536094666</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G863" t="n">
-        <v>3.00590372085571</v>
+        <v>3.00590348243713</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G864" t="n">
-        <v>2.98610663414001</v>
+        <v>2.98610639572144</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>4.58500003814697</v>
       </c>
       <c r="G865" t="n">
-        <v>3.02570128440857</v>
+        <v>3.02570152282715</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>4.5149998664856</v>
       </c>
       <c r="G866" t="n">
-        <v>2.97950744628906</v>
+        <v>2.97950720787048</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G869" t="n">
-        <v>3.05539751052856</v>
+        <v>3.05539727210999</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G870" t="n">
-        <v>3.06199645996094</v>
+        <v>3.06199622154236</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G871" t="n">
-        <v>3.05539751052856</v>
+        <v>3.05539727210999</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G872" t="n">
-        <v>3.06859564781189</v>
+        <v>3.06859517097473</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G874" t="n">
-        <v>3.18078112602234</v>
+        <v>3.18078064918518</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>4.75500011444092</v>
       </c>
       <c r="G876" t="n">
-        <v>3.13788676261902</v>
+        <v>3.13788652420044</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G880" t="n">
-        <v>3.15438485145569</v>
+        <v>3.15438437461853</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>4.74499988555908</v>
       </c>
       <c r="G881" t="n">
-        <v>3.13128733634949</v>
+        <v>3.13128757476807</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G884" t="n">
-        <v>3.20717787742615</v>
+        <v>3.20717740058899</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G885" t="n">
-        <v>3.22697472572327</v>
+        <v>3.22697448730469</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G886" t="n">
-        <v>3.33256125450134</v>
+        <v>3.33256101608276</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>4.93499994277954</v>
       </c>
       <c r="G887" t="n">
-        <v>3.25667119026184</v>
+        <v>3.25667071342468</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G889" t="n">
-        <v>3.17418193817139</v>
+        <v>3.17418146133423</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G891" t="n">
-        <v>3.08839273452759</v>
+        <v>3.08839297294617</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G892" t="n">
-        <v>3.08179378509521</v>
+        <v>3.08179402351379</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G896" t="n">
-        <v>2.90361738204956</v>
+        <v>2.90361762046814</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G898" t="n">
-        <v>2.84422540664673</v>
+        <v>2.84422516822815</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G899" t="n">
-        <v>2.81122970581055</v>
+        <v>2.81122946739197</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>4.16499996185303</v>
       </c>
       <c r="G900" t="n">
-        <v>2.74853777885437</v>
+        <v>2.74853754043579</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G901" t="n">
-        <v>2.75843620300293</v>
+        <v>2.75843644142151</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G903" t="n">
-        <v>2.61985468864441</v>
+        <v>2.61985492706299</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G905" t="n">
-        <v>2.58685898780823</v>
+        <v>2.58685922622681</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>4.02500009536743</v>
       </c>
       <c r="G907" t="n">
-        <v>2.65615010261536</v>
+        <v>2.65615034103394</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G908" t="n">
-        <v>2.75183725357056</v>
+        <v>2.75183773040771</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>4.31500005722046</v>
       </c>
       <c r="G910" t="n">
-        <v>2.84752511978149</v>
+        <v>2.84752464294434</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G912" t="n">
-        <v>3.00260424613953</v>
+        <v>3.00260472297668</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G913" t="n">
-        <v>2.89041924476624</v>
+        <v>2.89041948318481</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>4.36499977111816</v>
       </c>
       <c r="G914" t="n">
-        <v>2.88052034378052</v>
+        <v>2.8805205821991</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>4.5</v>
       </c>
       <c r="G915" t="n">
-        <v>2.96960878372192</v>
+        <v>2.9696090221405</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G916" t="n">
-        <v>3.00590372085571</v>
+        <v>3.00590348243713</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G917" t="n">
-        <v>3.05539751052856</v>
+        <v>3.05539727210999</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G918" t="n">
-        <v>3.00260424613953</v>
+        <v>3.00260472297668</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>4.64499998092651</v>
       </c>
       <c r="G920" t="n">
-        <v>3.06529569625854</v>
+        <v>3.0652961730957</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G922" t="n">
-        <v>3.14778518676758</v>
+        <v>3.14778542518616</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G924" t="n">
-        <v>3.12138891220093</v>
+        <v>3.12138867378235</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G925" t="n">
-        <v>3.03559994697571</v>
+        <v>3.03560018539429</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G927" t="n">
-        <v>2.98610663414001</v>
+        <v>2.98610639572144</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G929" t="n">
-        <v>3.00590372085571</v>
+        <v>3.00590348243713</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>4.53499984741211</v>
       </c>
       <c r="G930" t="n">
-        <v>2.99270558357239</v>
+        <v>2.99270534515381</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G931" t="n">
-        <v>3.00920367240906</v>
+        <v>3.00920391082764</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G932" t="n">
-        <v>2.95971012115479</v>
+        <v>2.95971035957336</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G933" t="n">
-        <v>2.94981098175049</v>
+        <v>2.94981122016907</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>4.64499998092651</v>
       </c>
       <c r="G935" t="n">
-        <v>3.06529569625854</v>
+        <v>3.0652961730957</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G936" t="n">
-        <v>2.93001413345337</v>
+        <v>2.93001365661621</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G937" t="n">
-        <v>3.00590372085571</v>
+        <v>3.00590348243713</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G938" t="n">
-        <v>3.06199645996094</v>
+        <v>3.06199622154236</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>4.65500020980835</v>
       </c>
       <c r="G939" t="n">
-        <v>3.07189559936523</v>
+        <v>3.07189536094666</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>4.5</v>
       </c>
       <c r="G940" t="n">
-        <v>2.96960878372192</v>
+        <v>2.9696090221405</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G942" t="n">
-        <v>3.03559994697571</v>
+        <v>3.03560018539429</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G944" t="n">
-        <v>3.20057821273804</v>
+        <v>3.20057845115662</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G945" t="n">
-        <v>3.25997042655945</v>
+        <v>3.25997066497803</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>4.68499994277954</v>
       </c>
       <c r="G947" t="n">
-        <v>3.09169268608093</v>
+        <v>3.09169244766235</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>4.7350001335144</v>
       </c>
       <c r="G949" t="n">
-        <v>3.12468838691711</v>
+        <v>3.12468814849854</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G951" t="n">
-        <v>3.2038779258728</v>
+        <v>3.20387768745422</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G952" t="n">
-        <v>3.08839273452759</v>
+        <v>3.08839297294617</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G954" t="n">
-        <v>3.11808919906616</v>
+        <v>3.118088722229</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G955" t="n">
-        <v>3.08179378509521</v>
+        <v>3.08179402351379</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G956" t="n">
-        <v>3.08839273452759</v>
+        <v>3.08839297294617</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G957" t="n">
-        <v>3.08839273452759</v>
+        <v>3.08839297294617</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G959" t="n">
-        <v>3.06859564781189</v>
+        <v>3.06859517097473</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G960" t="n">
-        <v>3.00260424613953</v>
+        <v>3.00260472297668</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G961" t="n">
-        <v>2.94981098175049</v>
+        <v>2.94981122016907</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>4.60500001907349</v>
       </c>
       <c r="G962" t="n">
-        <v>3.03889942169189</v>
+        <v>3.03889966011047</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G964" t="n">
-        <v>2.98610663414001</v>
+        <v>2.98610639572144</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G966" t="n">
-        <v>3.03559994697571</v>
+        <v>3.03560018539429</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G967" t="n">
-        <v>3.03559994697571</v>
+        <v>3.03560018539429</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G968" t="n">
-        <v>3.1147894859314</v>
+        <v>3.11478972434998</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G969" t="n">
-        <v>3.20057821273804</v>
+        <v>3.20057845115662</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G970" t="n">
-        <v>3.23027420043945</v>
+        <v>3.23027443885803</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G973" t="n">
-        <v>3.43154788017273</v>
+        <v>3.43154764175415</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G974" t="n">
-        <v>3.69551301002502</v>
+        <v>3.69551253318787</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G975" t="n">
-        <v>3.74830555915833</v>
+        <v>3.7483057975769</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G976" t="n">
-        <v>3.76150393486023</v>
+        <v>3.76150465011597</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G978" t="n">
-        <v>3.60312509536743</v>
+        <v>3.60312485694885</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G979" t="n">
-        <v>3.70211243629456</v>
+        <v>3.7021119594574</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G980" t="n">
-        <v>3.66251754760742</v>
+        <v>3.662517786026</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G981" t="n">
-        <v>3.64272022247314</v>
+        <v>3.64272046089172</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G982" t="n">
-        <v>3.59652614593506</v>
+        <v>3.59652590751648</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G983" t="n">
-        <v>3.62292242050171</v>
+        <v>3.62292289733887</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G984" t="n">
-        <v>3.62292242050171</v>
+        <v>3.62292289733887</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G985" t="n">
-        <v>3.58992719650269</v>
+        <v>3.58992648124695</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G986" t="n">
-        <v>3.68231463432312</v>
+        <v>3.6823148727417</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G987" t="n">
-        <v>3.66911673545837</v>
+        <v>3.66911625862122</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G988" t="n">
-        <v>3.66911673545837</v>
+        <v>3.66911625862122</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G989" t="n">
-        <v>3.64272022247314</v>
+        <v>3.64272046089172</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G990" t="n">
-        <v>3.66911673545837</v>
+        <v>3.66911625862122</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G991" t="n">
-        <v>3.66251754760742</v>
+        <v>3.662517786026</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>6.30999994277954</v>
       </c>
       <c r="G995" t="n">
-        <v>4.16405153274536</v>
+        <v>4.1640510559082</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>6.42999982833862</v>
       </c>
       <c r="G997" t="n">
-        <v>4.24324131011963</v>
+        <v>4.24324035644531</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>6.40999984741211</v>
       </c>
       <c r="G999" t="n">
-        <v>4.23004245758057</v>
+        <v>4.23004198074341</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>6.42999982833862</v>
       </c>
       <c r="G1000" t="n">
-        <v>4.24324131011963</v>
+        <v>4.24324035644531</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G1004" t="n">
-        <v>4.27623653411865</v>
+        <v>4.27623605728149</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>6.5</v>
       </c>
       <c r="G1005" t="n">
-        <v>4.28943538665771</v>
+        <v>4.28943395614624</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G1006" t="n">
-        <v>4.2613091468811</v>
+        <v>4.26130962371826</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G1007" t="n">
-        <v>4.2613091468811</v>
+        <v>4.26130962371826</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G1008" t="n">
-        <v>4.14882183074951</v>
+        <v>4.14882135391235</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>6.28499984741211</v>
       </c>
       <c r="G1009" t="n">
-        <v>4.15874719619751</v>
+        <v>4.15874671936035</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>6.52500009536743</v>
       </c>
       <c r="G1010" t="n">
-        <v>4.31755399703979</v>
+        <v>4.31755352020264</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G1011" t="n">
-        <v>4.40026521682739</v>
+        <v>4.40026569366455</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G1012" t="n">
-        <v>4.31424474716187</v>
+        <v>4.31424522399902</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G1017" t="n">
-        <v>4.52598762512207</v>
+        <v>4.52598714828491</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>6.83500003814697</v>
       </c>
       <c r="G1019" t="n">
-        <v>4.52267837524414</v>
+        <v>4.5226788520813</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>6.75</v>
       </c>
       <c r="G1020" t="n">
-        <v>4.46643495559692</v>
+        <v>4.46643447875977</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>7.17500019073486</v>
       </c>
       <c r="G1023" t="n">
-        <v>4.7476544380188</v>
+        <v>4.74765491485596</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G1028" t="n">
-        <v>4.92962074279785</v>
+        <v>4.92962026596069</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G1029" t="n">
-        <v>4.92962074279785</v>
+        <v>4.92962026596069</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G1030" t="n">
-        <v>4.87668561935425</v>
+        <v>4.87668514251709</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>7.66499996185303</v>
       </c>
       <c r="G1034" t="n">
-        <v>5.07188510894775</v>
+        <v>5.0718846321106</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1035" t="n">
-        <v>4.87006855010986</v>
+        <v>4.87006807327271</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>7.66499996185303</v>
       </c>
       <c r="G1040" t="n">
-        <v>5.07188510894775</v>
+        <v>5.0718846321106</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G1041" t="n">
-        <v>5.06195974349976</v>
+        <v>5.0619592666626</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G1042" t="n">
-        <v>5.10827827453613</v>
+        <v>5.10827779769897</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1043" t="n">
-        <v>5.06857633590698</v>
+        <v>5.06857585906982</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>7.71500015258789</v>
       </c>
       <c r="G1044" t="n">
-        <v>5.10496997833252</v>
+        <v>5.1049690246582</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G1047" t="n">
-        <v>5.06195974349976</v>
+        <v>5.0619592666626</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>7.69500017166138</v>
       </c>
       <c r="G1048" t="n">
-        <v>5.09173536300659</v>
+        <v>5.09173631668091</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G1049" t="n">
-        <v>5.08842754364014</v>
+        <v>5.08842706680298</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>8</v>
       </c>
       <c r="G1051" t="n">
-        <v>5.29355192184448</v>
+        <v>5.29355239868164</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G1054" t="n">
-        <v>5.17444753646851</v>
+        <v>5.17444801330566</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G1055" t="n">
-        <v>5.17444753646851</v>
+        <v>5.17444801330566</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>8.09000015258789</v>
       </c>
       <c r="G1056" t="n">
-        <v>5.35310459136963</v>
+        <v>5.35310506820679</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>8.13000011444092</v>
       </c>
       <c r="G1057" t="n">
-        <v>5.37957239151001</v>
+        <v>5.37957286834717</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1058" t="n">
-        <v>5.46559286117554</v>
+        <v>5.4655933380127</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G1060" t="n">
-        <v>5.38618946075439</v>
+        <v>5.38618993759155</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G1061" t="n">
-        <v>5.51852798461914</v>
+        <v>5.5185284614563</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>8.65499973297119</v>
       </c>
       <c r="G1063" t="n">
-        <v>5.72696208953857</v>
+        <v>5.72696161270142</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>8.51500034332275</v>
       </c>
       <c r="G1066" t="n">
-        <v>5.63432502746582</v>
+        <v>5.63432550430298</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>8.45499992370605</v>
       </c>
       <c r="G1068" t="n">
-        <v>5.59462308883667</v>
+        <v>5.59462261199951</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G1069" t="n">
-        <v>5.54499626159668</v>
+        <v>5.54499578475952</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>8.51500034332275</v>
       </c>
       <c r="G1070" t="n">
-        <v>5.63432502746582</v>
+        <v>5.63432550430298</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1073" t="n">
-        <v>5.69056844711304</v>
+        <v>5.69056940078735</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1074" t="n">
-        <v>5.69056844711304</v>
+        <v>5.69056940078735</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1077" t="n">
-        <v>5.50529384613037</v>
+        <v>5.50529432296753</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G1078" t="n">
-        <v>5.65086698532104</v>
+        <v>5.65086650848389</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1079" t="n">
-        <v>5.55822896957397</v>
+        <v>5.55822944641113</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1081" t="n">
-        <v>5.65748405456543</v>
+        <v>5.65748453140259</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>7.95499992370605</v>
       </c>
       <c r="G1084" t="n">
-        <v>5.26377630233765</v>
+        <v>5.26377582550049</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G1086" t="n">
-        <v>5.32663726806641</v>
+        <v>5.32663774490356</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G1088" t="n">
-        <v>5.70380258560181</v>
+        <v>5.70380210876465</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1090" t="n">
-        <v>5.82290744781494</v>
+        <v>5.8229079246521</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>8.875</v>
       </c>
       <c r="G1091" t="n">
-        <v>5.87253427505493</v>
+        <v>5.87253475189209</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>8.86999988555908</v>
       </c>
       <c r="G1094" t="n">
-        <v>5.86922597885132</v>
+        <v>5.86922645568848</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>8.80500030517578</v>
       </c>
       <c r="G1095" t="n">
-        <v>5.82621669769287</v>
+        <v>5.82621622085571</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G1096" t="n">
-        <v>5.83614158630371</v>
+        <v>5.83614110946655</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>8.86999988555908</v>
       </c>
       <c r="G1097" t="n">
-        <v>5.86922597885132</v>
+        <v>5.86922645568848</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>8.05500030517578</v>
       </c>
       <c r="G1098" t="n">
-        <v>5.32994556427002</v>
+        <v>5.32994508743286</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>7.7649998664856</v>
       </c>
       <c r="G1103" t="n">
-        <v>5.13805389404297</v>
+        <v>5.13805437088013</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G1105" t="n">
-        <v>5.06195974349976</v>
+        <v>5.0619592666626</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>7.71500015258789</v>
       </c>
       <c r="G1107" t="n">
-        <v>5.10496997833252</v>
+        <v>5.1049690246582</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>7.96500015258789</v>
       </c>
       <c r="G1110" t="n">
-        <v>5.27039289474487</v>
+        <v>5.27039337158203</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>8</v>
       </c>
       <c r="G1111" t="n">
-        <v>5.29355192184448</v>
+        <v>5.29355239868164</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1112" t="n">
-        <v>5.22738313674927</v>
+        <v>5.22738265991211</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>7.85500001907349</v>
       </c>
       <c r="G1113" t="n">
-        <v>5.19760656356812</v>
+        <v>5.19760704040527</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>7.75</v>
       </c>
       <c r="G1114" t="n">
-        <v>5.12812852859497</v>
+        <v>5.12812805175781</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G1115" t="n">
-        <v>5.12151193618774</v>
+        <v>5.12151145935059</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>7.7649998664856</v>
       </c>
       <c r="G1116" t="n">
-        <v>5.13805389404297</v>
+        <v>5.13805437088013</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>8.01500034332275</v>
       </c>
       <c r="G1119" t="n">
-        <v>5.30347776412964</v>
+        <v>5.3034782409668</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>8</v>
       </c>
       <c r="G1121" t="n">
-        <v>5.29355192184448</v>
+        <v>5.29355239868164</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>8.05500030517578</v>
       </c>
       <c r="G1122" t="n">
-        <v>5.32994556427002</v>
+        <v>5.32994508743286</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>8.09500026702881</v>
       </c>
       <c r="G1125" t="n">
-        <v>5.35641288757324</v>
+        <v>5.3564133644104</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G1127" t="n">
-        <v>5.34648752212524</v>
+        <v>5.3464879989624</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G1128" t="n">
-        <v>5.34648752212524</v>
+        <v>5.3464879989624</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>7.95499992370605</v>
       </c>
       <c r="G1129" t="n">
-        <v>5.26377630233765</v>
+        <v>5.26377582550049</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>8.0649995803833</v>
       </c>
       <c r="G1130" t="n">
-        <v>5.33656215667725</v>
+        <v>5.3365626335144</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>8.19499969482422</v>
       </c>
       <c r="G1136" t="n">
-        <v>5.42258214950562</v>
+        <v>5.42258262634277</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1139" t="n">
-        <v>5.45235824584961</v>
+        <v>5.45235872268677</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G1140" t="n">
-        <v>5.44574165344238</v>
+        <v>5.44574213027954</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G1142" t="n">
-        <v>5.38618946075439</v>
+        <v>5.38618993759155</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>8.17500019073486</v>
       </c>
       <c r="G1143" t="n">
-        <v>5.409348487854</v>
+        <v>5.40934944152832</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G1146" t="n">
-        <v>5.32732152938843</v>
+        <v>5.32732200622559</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>7.7350001335144</v>
       </c>
       <c r="G1149" t="n">
-        <v>5.74711751937866</v>
+        <v>5.7471170425415</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>7.74499988555908</v>
       </c>
       <c r="G1150" t="n">
-        <v>5.75454711914062</v>
+        <v>5.75454664230347</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G1152" t="n">
-        <v>5.78798246383667</v>
+        <v>5.78798198699951</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G1153" t="n">
-        <v>5.81027221679688</v>
+        <v>5.81027269363403</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>7.7649998664856</v>
       </c>
       <c r="G1156" t="n">
-        <v>5.76940727233887</v>
+        <v>5.76940774917603</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G1158" t="n">
-        <v>5.75083208084106</v>
+        <v>5.75083160400391</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>7.83500003814697</v>
       </c>
       <c r="G1159" t="n">
-        <v>5.82141780853271</v>
+        <v>5.82141733169556</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>7.53499984741211</v>
       </c>
       <c r="G1163" t="n">
-        <v>5.59851694107056</v>
+        <v>5.59851741790771</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>7.35500001907349</v>
       </c>
       <c r="G1164" t="n">
-        <v>5.46477651596069</v>
+        <v>5.46477699279785</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>7.32499980926514</v>
       </c>
       <c r="G1165" t="n">
-        <v>5.44248628616333</v>
+        <v>5.44248676300049</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G1173" t="n">
-        <v>5.16386127471924</v>
+        <v>5.16386032104492</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G1174" t="n">
-        <v>5.14157152175903</v>
+        <v>5.14157104492188</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>6.82499980926514</v>
       </c>
       <c r="G1176" t="n">
-        <v>5.07098579406738</v>
+        <v>5.07098531723022</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>6.91499996185303</v>
       </c>
       <c r="G1177" t="n">
-        <v>5.13785600662231</v>
+        <v>5.13785552978516</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G1178" t="n">
-        <v>4.92610120773315</v>
+        <v>4.926100730896</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1179" t="n">
-        <v>4.79979038238525</v>
+        <v>4.7997899055481</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1181" t="n">
-        <v>5.05241107940674</v>
+        <v>5.05241060256958</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G1182" t="n">
-        <v>4.96325063705444</v>
+        <v>4.96325016021729</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>6.5</v>
       </c>
       <c r="G1183" t="n">
-        <v>4.82951021194458</v>
+        <v>4.82950973510742</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>6.63500022888184</v>
       </c>
       <c r="G1184" t="n">
-        <v>4.9298152923584</v>
+        <v>4.92981576919556</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>6.70499992370605</v>
       </c>
       <c r="G1187" t="n">
-        <v>4.98182535171509</v>
+        <v>4.9818263053894</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>6.61499977111816</v>
       </c>
       <c r="G1188" t="n">
-        <v>4.91495513916016</v>
+        <v>4.91495561599731</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>6.61499977111816</v>
       </c>
       <c r="G1189" t="n">
-        <v>4.91495513916016</v>
+        <v>4.91495561599731</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>6.66499996185303</v>
       </c>
       <c r="G1190" t="n">
-        <v>4.95210552215576</v>
+        <v>4.95210599899292</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G1191" t="n">
-        <v>4.97811079025269</v>
+        <v>4.97811126708984</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G1192" t="n">
-        <v>5.08956146240234</v>
+        <v>5.08956098556519</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>6.93499994277954</v>
       </c>
       <c r="G1196" t="n">
-        <v>5.1527156829834</v>
+        <v>5.15271615982056</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>6.93499994277954</v>
       </c>
       <c r="G1197" t="n">
-        <v>5.1527156829834</v>
+        <v>5.15271615982056</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1200" t="n">
-        <v>5.27531147003174</v>
+        <v>5.27531099319458</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G1203" t="n">
-        <v>5.46106147766113</v>
+        <v>5.46106195449829</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>7.17500019073486</v>
       </c>
       <c r="G1204" t="n">
-        <v>5.33103609085083</v>
+        <v>5.33103656768799</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>7.14499998092651</v>
       </c>
       <c r="G1205" t="n">
-        <v>5.30874681472778</v>
+        <v>5.30874633789062</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1209" t="n">
-        <v>5.27531147003174</v>
+        <v>5.27531099319458</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G1211" t="n">
-        <v>5.2455906867981</v>
+        <v>5.24559116363525</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>7.10500001907349</v>
       </c>
       <c r="G1212" t="n">
-        <v>5.27902603149414</v>
+        <v>5.2790265083313</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G1216" t="n">
-        <v>5.12671136856079</v>
+        <v>5.12671089172363</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>6.5</v>
       </c>
       <c r="G1217" t="n">
-        <v>4.82951021194458</v>
+        <v>4.82950973510742</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G1218" t="n">
-        <v>4.92610120773315</v>
+        <v>4.926100730896</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>6.82499980926514</v>
       </c>
       <c r="G1220" t="n">
-        <v>5.07098579406738</v>
+        <v>5.07098531723022</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G1222" t="n">
-        <v>5.03755140304565</v>
+        <v>5.0375509262085</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G1223" t="n">
-        <v>5.17872047424316</v>
+        <v>5.17872095108032</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>6.80499982833862</v>
       </c>
       <c r="G1225" t="n">
-        <v>5.05612564086914</v>
+        <v>5.05612516403198</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G1226" t="n">
-        <v>5.03755140304565</v>
+        <v>5.0375509262085</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>6.76999998092651</v>
       </c>
       <c r="G1227" t="n">
-        <v>5.03012084960938</v>
+        <v>5.03012037277222</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>6.80499982833862</v>
       </c>
       <c r="G1228" t="n">
-        <v>5.05612564086914</v>
+        <v>5.05612516403198</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1230" t="n">
-        <v>5.6096625328064</v>
+        <v>5.60966205596924</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>7.67500019073486</v>
       </c>
       <c r="G1233" t="n">
-        <v>5.70253753662109</v>
+        <v>5.70253801345825</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G1234" t="n">
-        <v>5.54279184341431</v>
+        <v>5.54279232025146</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>7.375</v>
       </c>
       <c r="G1235" t="n">
-        <v>5.47963666915894</v>
+        <v>5.47963714599609</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G1236" t="n">
-        <v>5.57994270324707</v>
+        <v>5.57994174957275</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>7.25500011444092</v>
       </c>
       <c r="G1238" t="n">
-        <v>5.3904767036438</v>
+        <v>5.39047622680664</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G1239" t="n">
-        <v>5.25302171707153</v>
+        <v>5.25302124023438</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>6.53000020980835</v>
       </c>
       <c r="G1240" t="n">
-        <v>4.85180044174194</v>
+        <v>4.8518009185791</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G1242" t="n">
-        <v>4.79236030578613</v>
+        <v>4.79235982894897</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G1246" t="n">
-        <v>4.36884927749634</v>
+        <v>4.3688497543335</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1247" t="n">
-        <v>4.30940914154053</v>
+        <v>4.30940961837769</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G1248" t="n">
-        <v>4.53974008560181</v>
+        <v>4.53973960876465</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>6.25</v>
       </c>
       <c r="G1249" t="n">
-        <v>4.64375972747803</v>
+        <v>4.64376020431519</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G1252" t="n">
-        <v>4.71805953979492</v>
+        <v>4.71806001663208</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>6.2649998664856</v>
       </c>
       <c r="G1253" t="n">
-        <v>4.65490484237671</v>
+        <v>4.65490436553955</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G1254" t="n">
-        <v>4.90381097793579</v>
+        <v>4.90381050109863</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1257" t="n">
-        <v>4.79979038238525</v>
+        <v>4.7997899055481</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G1258" t="n">
-        <v>4.90381097793579</v>
+        <v>4.90381050109863</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>6.67000007629395</v>
       </c>
       <c r="G1260" t="n">
-        <v>4.95582103729248</v>
+        <v>4.95582056045532</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G1261" t="n">
-        <v>5.00040102005005</v>
+        <v>5.00040054321289</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>6.68499994277954</v>
       </c>
       <c r="G1262" t="n">
-        <v>4.96696519851685</v>
+        <v>4.966965675354</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>6.82499980926514</v>
       </c>
       <c r="G1263" t="n">
-        <v>5.07098579406738</v>
+        <v>5.07098531723022</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>6.82499980926514</v>
       </c>
       <c r="G1264" t="n">
-        <v>5.07098579406738</v>
+        <v>5.07098531723022</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>6.96500015258789</v>
       </c>
       <c r="G1267" t="n">
-        <v>5.17500638961792</v>
+        <v>5.17500591278076</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G1269" t="n">
-        <v>5.00040102005005</v>
+        <v>5.00040054321289</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>6.80499982833862</v>
       </c>
       <c r="G1270" t="n">
-        <v>5.05612564086914</v>
+        <v>5.05612516403198</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G1271" t="n">
-        <v>5.16386127471924</v>
+        <v>5.16386032104492</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>6.86499977111816</v>
       </c>
       <c r="G1273" t="n">
-        <v>5.10070562362671</v>
+        <v>5.10070610046387</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G1274" t="n">
-        <v>5.11185073852539</v>
+        <v>5.11185121536255</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>6.92500019073486</v>
       </c>
       <c r="G1275" t="n">
-        <v>5.14528608322144</v>
+        <v>5.14528656005859</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>6.15500020980835</v>
       </c>
       <c r="G1276" t="n">
-        <v>5.07072877883911</v>
+        <v>5.07072830200195</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G1277" t="n">
-        <v>5.03365612030029</v>
+        <v>5.03365564346313</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G1279" t="n">
-        <v>4.98422527313232</v>
+        <v>4.98422574996948</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G1281" t="n">
-        <v>4.79474306106567</v>
+        <v>4.79474258422852</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G1285" t="n">
-        <v>4.95127201080322</v>
+        <v>4.95127248764038</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>6.22499990463257</v>
       </c>
       <c r="G1286" t="n">
-        <v>5.12839698791504</v>
+        <v>5.1283974647522</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>6.28499984741211</v>
       </c>
       <c r="G1287" t="n">
-        <v>5.17782735824585</v>
+        <v>5.17782783508301</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G1290" t="n">
-        <v>5.06660890579224</v>
+        <v>5.06660985946655</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>6.30499982833862</v>
       </c>
       <c r="G1291" t="n">
-        <v>5.19430446624756</v>
+        <v>5.1943039894104</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>6.40999984741211</v>
       </c>
       <c r="G1292" t="n">
-        <v>5.28080749511719</v>
+        <v>5.28080701828003</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>6.59499979019165</v>
       </c>
       <c r="G1293" t="n">
-        <v>5.43321704864502</v>
+        <v>5.43321752548218</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G1295" t="n">
-        <v>5.61858177185059</v>
+        <v>5.61858129501343</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G1298" t="n">
-        <v>5.8245415687561</v>
+        <v>5.82454109191895</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G1303" t="n">
-        <v>6.08817005157471</v>
+        <v>6.08816957473755</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>7.25</v>
       </c>
       <c r="G1306" t="n">
-        <v>5.97283220291138</v>
+        <v>5.97283172607422</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>7.21500015258789</v>
       </c>
       <c r="G1309" t="n">
-        <v>5.94399785995483</v>
+        <v>5.94399738311768</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>7.31500005722046</v>
       </c>
       <c r="G1311" t="n">
-        <v>6.02638149261475</v>
+        <v>6.0263819694519</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G1313" t="n">
-        <v>5.83277893066406</v>
+        <v>5.83277940750122</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>6.95499992370605</v>
       </c>
       <c r="G1314" t="n">
-        <v>5.72979927062988</v>
+        <v>5.72979974746704</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>6.57499980926514</v>
       </c>
       <c r="G1319" t="n">
-        <v>5.41674041748047</v>
+        <v>5.41674089431763</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>6.48999977111816</v>
       </c>
       <c r="G1322" t="n">
-        <v>5.34671449661255</v>
+        <v>5.34671401977539</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>6.5149998664856</v>
       </c>
       <c r="G1323" t="n">
-        <v>5.36731052398682</v>
+        <v>5.36731004714966</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>6.58500003814697</v>
       </c>
       <c r="G1326" t="n">
-        <v>5.4249792098999</v>
+        <v>5.42497968673706</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>6.63500022888184</v>
       </c>
       <c r="G1327" t="n">
-        <v>5.46617078781128</v>
+        <v>5.46617126464844</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>6.41499996185303</v>
       </c>
       <c r="G1328" t="n">
-        <v>5.2849268913269</v>
+        <v>5.28492641448975</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G1329" t="n">
-        <v>5.25609254837036</v>
+        <v>5.2560920715332</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>6.30999994277954</v>
       </c>
       <c r="G1332" t="n">
-        <v>5.19842386245728</v>
+        <v>5.19842338562012</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>6.43499994277954</v>
       </c>
       <c r="G1333" t="n">
-        <v>5.30140352249146</v>
+        <v>5.3014030456543</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>6.44500017166138</v>
       </c>
       <c r="G1337" t="n">
-        <v>5.30964231491089</v>
+        <v>5.30964183807373</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>6.16499996185303</v>
       </c>
       <c r="G1338" t="n">
-        <v>5.07896709442139</v>
+        <v>5.07896661758423</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G1339" t="n">
-        <v>5.04189348220825</v>
+        <v>5.04189395904541</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1340" t="n">
-        <v>5.12427806854248</v>
+        <v>5.12427759170532</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35287,7 +35287,7 @@
         <v>6.47499990463257</v>
       </c>
       <c r="G1343" t="n">
-        <v>5.33435726165771</v>
+        <v>5.33435678482056</v>
       </c>
       <c r="H1343" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>6.63500022888184</v>
       </c>
       <c r="G1346" t="n">
-        <v>5.46617078781128</v>
+        <v>5.46617126464844</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>6.85500001907349</v>
       </c>
       <c r="G1349" t="n">
-        <v>5.64741611480713</v>
+        <v>5.64741563796997</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>6.94500017166138</v>
       </c>
       <c r="G1352" t="n">
-        <v>5.72156190872192</v>
+        <v>5.72156143188477</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>6.9850001335144</v>
       </c>
       <c r="G1355" t="n">
-        <v>5.75451517105103</v>
+        <v>5.75451469421387</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>6.95499992370605</v>
       </c>
       <c r="G1361" t="n">
-        <v>5.72979927062988</v>
+        <v>5.72979974746704</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>6.9850001335144</v>
       </c>
       <c r="G1362" t="n">
-        <v>5.75451517105103</v>
+        <v>5.75451469421387</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1364" t="n">
-        <v>5.48472023010254</v>
+        <v>5.4847207069397</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>6.31500005722046</v>
       </c>
       <c r="G1369" t="n">
-        <v>5.49777889251709</v>
+        <v>5.49777936935425</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>6.31500005722046</v>
       </c>
       <c r="G1371" t="n">
-        <v>5.49777889251709</v>
+        <v>5.49777936935425</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1373" t="n">
-        <v>5.48472023010254</v>
+        <v>5.4847207069397</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>6.07499980926514</v>
       </c>
       <c r="G1376" t="n">
-        <v>5.28883695602417</v>
+        <v>5.28883743286133</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G1377" t="n">
-        <v>5.43248510360718</v>
+        <v>5.43248462677002</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G1383" t="n">
-        <v>5.94613361358643</v>
+        <v>5.94613313674927</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>7.09499979019165</v>
       </c>
       <c r="G1386" t="n">
-        <v>6.17683982849121</v>
+        <v>6.17683935165405</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>7.10500001907349</v>
       </c>
       <c r="G1389" t="n">
-        <v>6.18554544448853</v>
+        <v>6.18554592132568</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G1390" t="n">
-        <v>6.12025117874146</v>
+        <v>6.12025165557861</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>6.42500019073486</v>
       </c>
       <c r="G1392" t="n">
-        <v>5.59354400634766</v>
+        <v>5.59354448318481</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G1394" t="n">
-        <v>5.98095703125</v>
+        <v>5.98095655441284</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>7</v>
       </c>
       <c r="G1397" t="n">
-        <v>6.09413385391235</v>
+        <v>6.0941333770752</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G1398" t="n">
-        <v>5.98966264724731</v>
+        <v>5.98966312408447</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G1404" t="n">
-        <v>6.12025117874146</v>
+        <v>6.12025165557861</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G1406" t="n">
-        <v>6.00707483291626</v>
+        <v>6.0070743560791</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G1408" t="n">
-        <v>6.13766384124756</v>
+        <v>6.13766288757324</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>7.125</v>
       </c>
       <c r="G1409" t="n">
-        <v>6.20295810699463</v>
+        <v>6.20295715332031</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>7.22499990463257</v>
       </c>
       <c r="G1415" t="n">
-        <v>6.29001665115356</v>
+        <v>6.29001617431641</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G1416" t="n">
-        <v>6.30307483673096</v>
+        <v>6.30307531356812</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37263,7 +37263,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1419" t="n">
-        <v>6.44236993789673</v>
+        <v>6.44236946105957</v>
       </c>
       <c r="H1419" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>7.20499992370605</v>
       </c>
       <c r="G1420" t="n">
-        <v>6.27260446548462</v>
+        <v>6.27260494232178</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G1429" t="n">
-        <v>6.43366432189941</v>
+        <v>6.43366384506226</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1432" t="n">
-        <v>6.44236993789673</v>
+        <v>6.44236946105957</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>7.45499992370605</v>
       </c>
       <c r="G1434" t="n">
-        <v>6.49025201797485</v>
+        <v>6.49025249481201</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G1435" t="n">
-        <v>6.47719383239746</v>
+        <v>6.4771933555603</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G1436" t="n">
-        <v>6.49460554122925</v>
+        <v>6.49460506439209</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G1438" t="n">
-        <v>6.49460554122925</v>
+        <v>6.49460506439209</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>7.09499979019165</v>
       </c>
       <c r="G1441" t="n">
-        <v>6.17683982849121</v>
+        <v>6.17683935165405</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G1445" t="n">
-        <v>6.47719383239746</v>
+        <v>6.4771933555603</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -37965,7 +37965,7 @@
         <v>7.40999984741211</v>
       </c>
       <c r="G1446" t="n">
-        <v>6.45107555389404</v>
+        <v>6.4510760307312</v>
       </c>
       <c r="H1446" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>7.20499992370605</v>
       </c>
       <c r="G1447" t="n">
-        <v>6.27260446548462</v>
+        <v>6.27260494232178</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>7.41499996185303</v>
       </c>
       <c r="G1450" t="n">
-        <v>6.45542907714844</v>
+        <v>6.45542860031128</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G1451" t="n">
-        <v>6.47719383239746</v>
+        <v>6.4771933555603</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G1452" t="n">
-        <v>6.49460554122925</v>
+        <v>6.49460506439209</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G1453" t="n">
-        <v>6.49460554122925</v>
+        <v>6.49460506439209</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>7.40500020980835</v>
       </c>
       <c r="G1454" t="n">
-        <v>6.44672298431396</v>
+        <v>6.44672346115112</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38251,7 +38251,7 @@
         <v>7.40999984741211</v>
       </c>
       <c r="G1457" t="n">
-        <v>6.45107555389404</v>
+        <v>6.4510760307312</v>
       </c>
       <c r="H1457" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>7.45499992370605</v>
       </c>
       <c r="G1458" t="n">
-        <v>6.49025201797485</v>
+        <v>6.49025249481201</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>8.42500019073486</v>
       </c>
       <c r="G1468" t="n">
-        <v>7.33472490310669</v>
+        <v>7.33472585678101</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>8.44499969482422</v>
       </c>
       <c r="G1469" t="n">
-        <v>7.35213708877563</v>
+        <v>7.35213661193848</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1470" t="n">
-        <v>7.44354867935181</v>
+        <v>7.44354915618896</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G1474" t="n">
-        <v>7.35648918151855</v>
+        <v>7.35648965835571</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1475" t="n">
-        <v>7.17366552352905</v>
+        <v>7.17366600036621</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>8.61499977111816</v>
       </c>
       <c r="G1478" t="n">
-        <v>7.50013780593872</v>
+        <v>7.50013732910156</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>8.48499965667725</v>
       </c>
       <c r="G1479" t="n">
-        <v>7.38696002960205</v>
+        <v>7.38696050643921</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G1482" t="n">
-        <v>7.64378452301025</v>
+        <v>7.64378547668457</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -38927,7 +38927,7 @@
         <v>8.76500034332275</v>
       </c>
       <c r="G1483" t="n">
-        <v>7.63072538375854</v>
+        <v>7.63072681427002</v>
       </c>
       <c r="H1483" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>8.89000034332275</v>
       </c>
       <c r="G1486" t="n">
-        <v>7.73954916000366</v>
+        <v>7.73955011367798</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G1487" t="n">
-        <v>7.88755035400391</v>
+        <v>7.88755083084106</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G1489" t="n">
-        <v>8.35766887664795</v>
+        <v>8.35766983032227</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G1491" t="n">
-        <v>8.4621410369873</v>
+        <v>8.46214008331299</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39161,7 +39161,7 @@
         <v>9.71500015258789</v>
       </c>
       <c r="G1492" t="n">
-        <v>8.45778751373291</v>
+        <v>8.45778656005859</v>
       </c>
       <c r="H1492" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G1493" t="n">
-        <v>8.32284641265869</v>
+        <v>8.32284545898438</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G1494" t="n">
-        <v>8.34896373748779</v>
+        <v>8.34896278381348</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G1495" t="n">
-        <v>8.35766887664795</v>
+        <v>8.35766983032227</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G1496" t="n">
-        <v>8.35766887664795</v>
+        <v>8.35766983032227</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G1498" t="n">
-        <v>8.25319766998291</v>
+        <v>8.25319862365723</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39343,7 +39343,7 @@
         <v>9.39000034332275</v>
       </c>
       <c r="G1499" t="n">
-        <v>8.17484569549561</v>
+        <v>8.17484474182129</v>
       </c>
       <c r="H1499" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G1501" t="n">
-        <v>8.15743350982666</v>
+        <v>8.15743255615234</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>9.52499961853027</v>
       </c>
       <c r="G1502" t="n">
-        <v>8.29237365722656</v>
+        <v>8.29237461090088</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>9.51500034332275</v>
       </c>
       <c r="G1503" t="n">
-        <v>8.28366947174072</v>
+        <v>8.28366851806641</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39473,7 +39473,7 @@
         <v>9.45499992370605</v>
       </c>
       <c r="G1504" t="n">
-        <v>8.23143291473389</v>
+        <v>8.2314338684082</v>
       </c>
       <c r="H1504" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G1505" t="n">
-        <v>8.29672718048096</v>
+        <v>8.29672813415527</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>9.4350004196167</v>
       </c>
       <c r="G1506" t="n">
-        <v>8.21402263641357</v>
+        <v>8.21402168273926</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39551,7 +39551,7 @@
         <v>9.34500026702881</v>
       </c>
       <c r="G1507" t="n">
-        <v>8.13566970825195</v>
+        <v>8.13566875457764</v>
       </c>
       <c r="H1507" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G1508" t="n">
-        <v>7.90496253967285</v>
+        <v>7.90496206283569</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>9.33500003814697</v>
       </c>
       <c r="G1509" t="n">
-        <v>8.12696266174316</v>
+        <v>8.12696361541748</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39629,7 +39629,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G1510" t="n">
-        <v>7.85272741317749</v>
+        <v>7.85272693634033</v>
       </c>
       <c r="H1510" t="s">
         <v>8</v>
@@ -39655,7 +39655,7 @@
         <v>9.05500030517578</v>
       </c>
       <c r="G1511" t="n">
-        <v>7.88319778442383</v>
+        <v>7.88319730758667</v>
       </c>
       <c r="H1511" t="s">
         <v>8</v>
@@ -39681,7 +39681,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G1512" t="n">
-        <v>7.89625597000122</v>
+        <v>7.89625549316406</v>
       </c>
       <c r="H1512" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>9.45499992370605</v>
       </c>
       <c r="G1514" t="n">
-        <v>8.23143291473389</v>
+        <v>8.2314338684082</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>9.19499969482422</v>
       </c>
       <c r="G1515" t="n">
-        <v>8.0050802230835</v>
+        <v>8.00507926940918</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G1516" t="n">
-        <v>8.06166839599609</v>
+        <v>8.06166934967041</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39811,7 +39811,7 @@
         <v>9.13000011444092</v>
       </c>
       <c r="G1517" t="n">
-        <v>7.9484920501709</v>
+        <v>7.94849157333374</v>
       </c>
       <c r="H1517" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G1518" t="n">
-        <v>7.96590280532837</v>
+        <v>7.96590328216553</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>9.0649995803833</v>
       </c>
       <c r="G1520" t="n">
-        <v>7.89190244674683</v>
+        <v>7.89190340042114</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G1521" t="n">
-        <v>8.0007266998291</v>
+        <v>8.00072574615479</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G1522" t="n">
-        <v>7.96590280532837</v>
+        <v>7.96590328216553</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>9.15499973297119</v>
       </c>
       <c r="G1523" t="n">
-        <v>7.97025680541992</v>
+        <v>7.97025632858276</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>8.98999977111816</v>
       </c>
       <c r="G1524" t="n">
-        <v>7.82660818099976</v>
+        <v>7.82660913467407</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>9.17500019073486</v>
       </c>
       <c r="G1526" t="n">
-        <v>7.98766851425171</v>
+        <v>7.98766803741455</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>9.32999992370605</v>
       </c>
       <c r="G1528" t="n">
-        <v>8.12260913848877</v>
+        <v>8.12261009216309</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40201,7 +40201,7 @@
         <v>9.47000026702881</v>
       </c>
       <c r="G1532" t="n">
-        <v>8.24449348449707</v>
+        <v>8.24449157714844</v>
       </c>
       <c r="H1532" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G1534" t="n">
-        <v>7.89625597000122</v>
+        <v>7.89625549316406</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40279,7 +40279,7 @@
         <v>9.0649995803833</v>
       </c>
       <c r="G1535" t="n">
-        <v>7.89190244674683</v>
+        <v>7.89190340042114</v>
       </c>
       <c r="H1535" t="s">
         <v>8</v>
@@ -62928,6 +62928,32 @@
         <v>2.64599990844727</v>
       </c>
       <c r="H2406" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2407">
+      <c r="A2407" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B2407" t="n">
+        <v>2839391</v>
+      </c>
+      <c r="C2407" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="D2407" t="n">
+        <v>2.65400004386902</v>
+      </c>
+      <c r="E2407" t="n">
+        <v>2.67600011825562</v>
+      </c>
+      <c r="F2407" t="n">
+        <v>2.71600008010864</v>
+      </c>
+      <c r="G2407" t="n">
+        <v>2.71600008010864</v>
+      </c>
+      <c r="H2407" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/BFF.MI.xlsx
+++ b/data/BFF.MI.xlsx
@@ -55795,8 +55795,31 @@
       <c r="E2410" t="n">
         <v>2.33599996566772</v>
       </c>
-      <c r="F2410"/>
+      <c r="F2410" t="n">
+        <v>2.36800003051758</v>
+      </c>
       <c r="G2410" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2411">
+      <c r="A2411" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2411" t="n">
+        <v>6209357</v>
+      </c>
+      <c r="C2411" t="n">
+        <v>2.4300000667572</v>
+      </c>
+      <c r="D2411" t="n">
+        <v>2.17600011825562</v>
+      </c>
+      <c r="E2411" t="n">
+        <v>2.35999989509583</v>
+      </c>
+      <c r="F2411"/>
+      <c r="G2411" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/BFF.MI.xlsx
+++ b/data/BFF.MI.xlsx
@@ -55818,8 +55818,31 @@
       <c r="E2411" t="n">
         <v>2.35999989509583</v>
       </c>
-      <c r="F2411"/>
+      <c r="F2411" t="n">
+        <v>2.1800000667572</v>
+      </c>
       <c r="G2411" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2412">
+      <c r="A2412" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2412" t="n">
+        <v>10798383</v>
+      </c>
+      <c r="C2412" t="n">
+        <v>2.18799996376038</v>
+      </c>
+      <c r="D2412" t="n">
+        <v>1.99100005626678</v>
+      </c>
+      <c r="E2412" t="n">
+        <v>2.17199993133545</v>
+      </c>
+      <c r="F2412"/>
+      <c r="G2412" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/BFF.MI.xlsx
+++ b/data/BFF.MI.xlsx
@@ -55841,8 +55841,31 @@
       <c r="E2412" t="n">
         <v>2.17199993133545</v>
       </c>
-      <c r="F2412"/>
+      <c r="F2412" t="n">
+        <v>2.01999998092651</v>
+      </c>
       <c r="G2412" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2413">
+      <c r="A2413" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2413" t="n">
+        <v>6510277</v>
+      </c>
+      <c r="C2413" t="n">
+        <v>2.02999997138977</v>
+      </c>
+      <c r="D2413" t="n">
+        <v>1.92400002479553</v>
+      </c>
+      <c r="E2413" t="n">
+        <v>1.99399995803833</v>
+      </c>
+      <c r="F2413"/>
+      <c r="G2413" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/BFF.MI.xlsx
+++ b/data/BFF.MI.xlsx
@@ -55864,8 +55864,31 @@
       <c r="E2413" t="n">
         <v>1.99399995803833</v>
       </c>
-      <c r="F2413"/>
+      <c r="F2413" t="n">
+        <v>1.93099999427795</v>
+      </c>
       <c r="G2413" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2414">
+      <c r="A2414" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2414" t="n">
+        <v>3913266</v>
+      </c>
+      <c r="C2414" t="n">
+        <v>1.98000001907349</v>
+      </c>
+      <c r="D2414" t="n">
+        <v>1.88999998569489</v>
+      </c>
+      <c r="E2414" t="n">
+        <v>1.97399997711182</v>
+      </c>
+      <c r="F2414"/>
+      <c r="G2414" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/BFF.MI.xlsx
+++ b/data/BFF.MI.xlsx
@@ -55894,6 +55894,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2415">
+      <c r="A2415" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2415" t="n">
+        <v>4002816</v>
+      </c>
+      <c r="C2415" t="n">
+        <v>2.05399990081787</v>
+      </c>
+      <c r="D2415" t="n">
+        <v>1.92999994754791</v>
+      </c>
+      <c r="E2415" t="n">
+        <v>1.95200002193451</v>
+      </c>
+      <c r="F2415" t="n">
+        <v>2.01200008392334</v>
+      </c>
+      <c r="G2415" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BFF.MI.xlsx
+++ b/data/BFF.MI.xlsx
@@ -421,7 +421,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G2" t="n">
-        <v>2.25471162796021</v>
+        <v>2.25471186637878</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G3" t="n">
-        <v>2.3690812587738</v>
+        <v>2.36908102035522</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>4.25</v>
       </c>
       <c r="G4" t="n">
-        <v>2.31461954116821</v>
+        <v>2.31461930274963</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>4.29400014877319</v>
       </c>
       <c r="G5" t="n">
-        <v>2.33858251571655</v>
+        <v>2.33858275413513</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G6" t="n">
-        <v>2.2601580619812</v>
+        <v>2.26015782356262</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>4.06599998474121</v>
       </c>
       <c r="G7" t="n">
-        <v>2.21441030502319</v>
+        <v>2.21441006660461</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G8" t="n">
-        <v>2.22203469276428</v>
+        <v>2.22203493118286</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G9" t="n">
-        <v>2.2601580619812</v>
+        <v>2.26015782356262</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G11" t="n">
-        <v>2.26560378074646</v>
+        <v>2.26560401916504</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G12" t="n">
-        <v>2.28738832473755</v>
+        <v>2.28738856315613</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G13" t="n">
-        <v>2.34185028076172</v>
+        <v>2.3418505191803</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>4.2979998588562</v>
       </c>
       <c r="G14" t="n">
-        <v>2.3407609462738</v>
+        <v>2.34076118469238</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G15" t="n">
-        <v>2.36363482475281</v>
+        <v>2.36363506317139</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>4.48600006103516</v>
       </c>
       <c r="G20" t="n">
-        <v>2.44314885139465</v>
+        <v>2.44314932823181</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G22" t="n">
-        <v>2.5596969127655</v>
+        <v>2.55969667434692</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>4.83599996566772</v>
       </c>
       <c r="G23" t="n">
-        <v>2.63376474380493</v>
+        <v>2.63376450538635</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G25" t="n">
-        <v>2.5596969127655</v>
+        <v>2.55969667434692</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>4.73799991607666</v>
       </c>
       <c r="G27" t="n">
-        <v>2.58039236068726</v>
+        <v>2.58039259910583</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>4.64200019836426</v>
       </c>
       <c r="G28" t="n">
-        <v>2.52810907363892</v>
+        <v>2.5281093120575</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>4.74200010299683</v>
       </c>
       <c r="G30" t="n">
-        <v>2.58257102966309</v>
+        <v>2.58257079124451</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>4.83799982070923</v>
       </c>
       <c r="G31" t="n">
-        <v>2.63485383987427</v>
+        <v>2.63485407829285</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>4.77600002288818</v>
       </c>
       <c r="G32" t="n">
-        <v>2.60108757019043</v>
+        <v>2.60108780860901</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>4.92399978637695</v>
       </c>
       <c r="G33" t="n">
-        <v>2.68169093132019</v>
+        <v>2.68169069290161</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G35" t="n">
-        <v>2.68495845794678</v>
+        <v>2.6849582195282</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>4.89799976348877</v>
       </c>
       <c r="G36" t="n">
-        <v>2.66753077507019</v>
+        <v>2.66753053665161</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G37" t="n">
-        <v>2.68495845794678</v>
+        <v>2.6849582195282</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>4.92199993133545</v>
       </c>
       <c r="G39" t="n">
-        <v>2.68060183525085</v>
+        <v>2.6806013584137</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>4.86800003051758</v>
       </c>
       <c r="G40" t="n">
-        <v>2.65119218826294</v>
+        <v>2.65119194984436</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G41" t="n">
-        <v>2.64138913154602</v>
+        <v>2.6413893699646</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G42" t="n">
-        <v>2.65772771835327</v>
+        <v>2.65772795677185</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G43" t="n">
-        <v>2.66862010955811</v>
+        <v>2.66862034797668</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>4.87599992752075</v>
       </c>
       <c r="G44" t="n">
-        <v>2.65554928779602</v>
+        <v>2.65554904937744</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>4.89599990844727</v>
       </c>
       <c r="G46" t="n">
-        <v>2.66644167900085</v>
+        <v>2.66644144058228</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>5.06500005722046</v>
       </c>
       <c r="G47" t="n">
-        <v>2.75848150253296</v>
+        <v>2.75848197937012</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G51" t="n">
-        <v>2.81022000312805</v>
+        <v>2.81022024154663</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G52" t="n">
-        <v>2.82111287117004</v>
+        <v>2.82111310958862</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G53" t="n">
-        <v>2.80749750137329</v>
+        <v>2.80749726295471</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>5</v>
       </c>
       <c r="G54" t="n">
-        <v>2.72308158874512</v>
+        <v>2.7230818271637</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G56" t="n">
-        <v>2.81566643714905</v>
+        <v>2.81566667556763</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G57" t="n">
-        <v>2.84289717674255</v>
+        <v>2.84289693832397</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G58" t="n">
-        <v>2.81022000312805</v>
+        <v>2.81022024154663</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>5</v>
       </c>
       <c r="G59" t="n">
-        <v>2.72308158874512</v>
+        <v>2.7230818271637</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>5.09499979019165</v>
       </c>
       <c r="G60" t="n">
-        <v>2.77482032775879</v>
+        <v>2.77481985092163</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G62" t="n">
-        <v>2.78298950195312</v>
+        <v>2.78298997879028</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>5.16499996185303</v>
       </c>
       <c r="G64" t="n">
-        <v>2.81294369697571</v>
+        <v>2.81294274330139</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G68" t="n">
-        <v>2.81566643714905</v>
+        <v>2.81566667556763</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G69" t="n">
-        <v>2.78843569755554</v>
+        <v>2.78843545913696</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G70" t="n">
-        <v>2.80477476119995</v>
+        <v>2.80477428436279</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G72" t="n">
-        <v>2.78026676177979</v>
+        <v>2.78026652336121</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G73" t="n">
-        <v>2.78026676177979</v>
+        <v>2.78026652336121</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G74" t="n">
-        <v>2.78843569755554</v>
+        <v>2.78843545913696</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G75" t="n">
-        <v>2.80477476119995</v>
+        <v>2.80477428436279</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>5.17500019073486</v>
       </c>
       <c r="G77" t="n">
-        <v>2.8183901309967</v>
+        <v>2.81838989257812</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G78" t="n">
-        <v>2.78843569755554</v>
+        <v>2.78843545913696</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G79" t="n">
-        <v>2.82655906677246</v>
+        <v>2.82655882835388</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G80" t="n">
-        <v>2.82111287117004</v>
+        <v>2.82111310958862</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G81" t="n">
-        <v>2.80477476119995</v>
+        <v>2.80477428436279</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G82" t="n">
-        <v>2.80477476119995</v>
+        <v>2.80477428436279</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G83" t="n">
-        <v>2.80477476119995</v>
+        <v>2.80477428436279</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G85" t="n">
-        <v>2.80749750137329</v>
+        <v>2.80749726295471</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G86" t="n">
-        <v>2.80477476119995</v>
+        <v>2.80477428436279</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G90" t="n">
-        <v>2.81566643714905</v>
+        <v>2.81566667556763</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G91" t="n">
-        <v>2.83745145797729</v>
+        <v>2.83745098114014</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G92" t="n">
-        <v>2.81566643714905</v>
+        <v>2.81566667556763</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G93" t="n">
-        <v>2.80749750137329</v>
+        <v>2.80749726295471</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G94" t="n">
-        <v>2.80749750137329</v>
+        <v>2.80749726295471</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>5.16499996185303</v>
       </c>
       <c r="G96" t="n">
-        <v>2.81294369697571</v>
+        <v>2.81294274330139</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G97" t="n">
-        <v>2.81566643714905</v>
+        <v>2.81566667556763</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>5.11499977111816</v>
       </c>
       <c r="G99" t="n">
-        <v>2.78571271896362</v>
+        <v>2.78571248054504</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>4.9520001411438</v>
       </c>
       <c r="G100" t="n">
-        <v>2.69693994522095</v>
+        <v>2.69694042205811</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G101" t="n">
-        <v>2.69585132598877</v>
+        <v>2.69585084915161</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>4.99200010299683</v>
       </c>
       <c r="G102" t="n">
-        <v>2.71872472763062</v>
+        <v>2.71872496604919</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G103" t="n">
-        <v>2.73942065238953</v>
+        <v>2.73942017555237</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G104" t="n">
-        <v>2.81022000312805</v>
+        <v>2.81022024154663</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G106" t="n">
-        <v>2.78026676177979</v>
+        <v>2.78026652336121</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G108" t="n">
-        <v>2.76665139198303</v>
+        <v>2.76665091514587</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G109" t="n">
-        <v>2.78843569755554</v>
+        <v>2.78843545913696</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>5.16499996185303</v>
       </c>
       <c r="G110" t="n">
-        <v>2.81294369697571</v>
+        <v>2.81294274330139</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G111" t="n">
-        <v>2.84834361076355</v>
+        <v>2.84834384918213</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G113" t="n">
-        <v>2.86468243598938</v>
+        <v>2.86468195915222</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>5.50500011444092</v>
       </c>
       <c r="G114" t="n">
-        <v>2.99811339378357</v>
+        <v>2.99811315536499</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>5.49499988555908</v>
       </c>
       <c r="G115" t="n">
-        <v>2.99266743659973</v>
+        <v>2.99266695976257</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G117" t="n">
-        <v>3.03895902633667</v>
+        <v>3.03895950317383</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G119" t="n">
-        <v>3.08797478675842</v>
+        <v>3.08797454833984</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>5.67500019073486</v>
       </c>
       <c r="G120" t="n">
-        <v>3.09069776535034</v>
+        <v>3.0906982421875</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G121" t="n">
-        <v>3.24046730995178</v>
+        <v>3.2404670715332</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G122" t="n">
-        <v>3.21323657035828</v>
+        <v>3.2132363319397</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G124" t="n">
-        <v>3.1968982219696</v>
+        <v>3.19689798355103</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G125" t="n">
-        <v>3.12609767913818</v>
+        <v>3.1260974407196</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G128" t="n">
-        <v>3.10431337356567</v>
+        <v>3.10431313514709</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>5.72499990463257</v>
       </c>
       <c r="G129" t="n">
-        <v>3.11792850494385</v>
+        <v>3.11792898178101</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G130" t="n">
-        <v>3.15877485275269</v>
+        <v>3.15877461433411</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G133" t="n">
-        <v>3.32216000556946</v>
+        <v>3.32215929031372</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>6.125</v>
       </c>
       <c r="G134" t="n">
-        <v>3.33577466011047</v>
+        <v>3.33577489852905</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G135" t="n">
-        <v>3.30582141876221</v>
+        <v>3.30582165718079</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>6.11499977111816</v>
       </c>
       <c r="G136" t="n">
-        <v>3.33032894134521</v>
+        <v>3.33032870292664</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>6</v>
       </c>
       <c r="G138" t="n">
-        <v>3.26769828796387</v>
+        <v>3.26769804954529</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>6.11499977111816</v>
       </c>
       <c r="G139" t="n">
-        <v>3.33032894134521</v>
+        <v>3.33032870292664</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G140" t="n">
-        <v>3.33305239677429</v>
+        <v>3.33305215835571</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G141" t="n">
-        <v>3.32216000556946</v>
+        <v>3.32215929031372</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G142" t="n">
-        <v>3.34939026832581</v>
+        <v>3.34939050674438</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G143" t="n">
-        <v>3.39295959472656</v>
+        <v>3.39295983314514</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G144" t="n">
-        <v>3.38751363754272</v>
+        <v>3.3875138759613</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>6.25</v>
       </c>
       <c r="G145" t="n">
-        <v>3.40385174751282</v>
+        <v>3.40385246276855</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G146" t="n">
-        <v>3.38206720352173</v>
+        <v>3.38206744194031</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>6.11499977111816</v>
       </c>
       <c r="G147" t="n">
-        <v>3.33032894134521</v>
+        <v>3.33032870292664</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G152" t="n">
-        <v>3.25680589675903</v>
+        <v>3.25680565834045</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G153" t="n">
-        <v>3.24591398239136</v>
+        <v>3.24591302871704</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>5.92999982833862</v>
       </c>
       <c r="G154" t="n">
-        <v>3.22957468032837</v>
+        <v>3.22957539558411</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G155" t="n">
-        <v>3.21323657035828</v>
+        <v>3.2132363319397</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G156" t="n">
-        <v>3.27314496040344</v>
+        <v>3.27314472198486</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>6</v>
       </c>
       <c r="G157" t="n">
-        <v>3.26769828796387</v>
+        <v>3.26769804954529</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G158" t="n">
-        <v>3.32760548591614</v>
+        <v>3.32760620117188</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>6.125</v>
       </c>
       <c r="G159" t="n">
-        <v>3.33577466011047</v>
+        <v>3.33577489852905</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G160" t="n">
-        <v>3.36028265953064</v>
+        <v>3.36028337478638</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G161" t="n">
-        <v>3.38206720352173</v>
+        <v>3.38206744194031</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>6.40999984741211</v>
       </c>
       <c r="G162" t="n">
-        <v>3.49099063873291</v>
+        <v>3.49099040031433</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G163" t="n">
-        <v>3.512775182724</v>
+        <v>3.51277542114258</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G164" t="n">
-        <v>3.47465252876282</v>
+        <v>3.47465229034424</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G165" t="n">
-        <v>3.45831394195557</v>
+        <v>3.45831418037415</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>6.41499996185303</v>
       </c>
       <c r="G166" t="n">
-        <v>3.49371409416199</v>
+        <v>3.49371385574341</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>6.45499992370605</v>
       </c>
       <c r="G167" t="n">
-        <v>3.51549863815308</v>
+        <v>3.5154983997345</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>6.36499977111816</v>
       </c>
       <c r="G168" t="n">
-        <v>3.46648240089417</v>
+        <v>3.46648263931274</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>6.40999984741211</v>
       </c>
       <c r="G171" t="n">
-        <v>3.49099063873291</v>
+        <v>3.49099040031433</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G172" t="n">
-        <v>3.58357572555542</v>
+        <v>3.58357548713684</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G173" t="n">
-        <v>3.56179118156433</v>
+        <v>3.56179070472717</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G175" t="n">
-        <v>3.59446787834167</v>
+        <v>3.59446811676025</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>6.53000020980835</v>
       </c>
       <c r="G176" t="n">
-        <v>3.55634474754333</v>
+        <v>3.55634498596191</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G177" t="n">
-        <v>3.52366757392883</v>
+        <v>3.52366805076599</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>6.5149998664856</v>
       </c>
       <c r="G179" t="n">
-        <v>3.54817581176758</v>
+        <v>3.548175573349</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G180" t="n">
-        <v>3.61080622673035</v>
+        <v>3.61080646514893</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>6.375</v>
       </c>
       <c r="G181" t="n">
-        <v>3.4719295501709</v>
+        <v>3.47192883491516</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G182" t="n">
-        <v>3.47465252876282</v>
+        <v>3.47465229034424</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>6.25</v>
       </c>
       <c r="G183" t="n">
-        <v>3.40385174751282</v>
+        <v>3.40385246276855</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G184" t="n">
-        <v>3.44742131233215</v>
+        <v>3.44742155075073</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>6.38500022888184</v>
       </c>
       <c r="G185" t="n">
-        <v>3.47737574577332</v>
+        <v>3.47737550735474</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>6.41499996185303</v>
       </c>
       <c r="G187" t="n">
-        <v>3.49371409416199</v>
+        <v>3.49371385574341</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>6.5</v>
       </c>
       <c r="G189" t="n">
-        <v>3.54000616073608</v>
+        <v>3.54000639915466</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>6.5</v>
       </c>
       <c r="G191" t="n">
-        <v>3.54000616073608</v>
+        <v>3.54000639915466</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G193" t="n">
-        <v>3.56179118156433</v>
+        <v>3.56179070472717</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G194" t="n">
-        <v>3.47465252876282</v>
+        <v>3.47465229034424</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>6.46500015258789</v>
       </c>
       <c r="G195" t="n">
-        <v>3.52094531059265</v>
+        <v>3.52094483375549</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G196" t="n">
-        <v>3.52911400794983</v>
+        <v>3.52911424636841</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>6.5</v>
       </c>
       <c r="G197" t="n">
-        <v>3.54000616073608</v>
+        <v>3.54000639915466</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>6.57499980926514</v>
       </c>
       <c r="G201" t="n">
-        <v>3.58085227012634</v>
+        <v>3.5808527469635</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G202" t="n">
-        <v>3.58902168273926</v>
+        <v>3.58902192115784</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G203" t="n">
-        <v>3.59446787834167</v>
+        <v>3.59446811676025</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>6.53000020980835</v>
       </c>
       <c r="G204" t="n">
-        <v>3.55634474754333</v>
+        <v>3.55634498596191</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>6.59499979019165</v>
       </c>
       <c r="G205" t="n">
-        <v>3.59174489974976</v>
+        <v>3.59174418449402</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G206" t="n">
-        <v>3.59991407394409</v>
+        <v>3.59991431236267</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>6.41499996185303</v>
       </c>
       <c r="G209" t="n">
-        <v>3.49371409416199</v>
+        <v>3.49371385574341</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G210" t="n">
-        <v>3.29492926597595</v>
+        <v>3.29492950439453</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G213" t="n">
-        <v>3.2785906791687</v>
+        <v>3.27859020233154</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>5.92999982833862</v>
       </c>
       <c r="G215" t="n">
-        <v>3.22957468032837</v>
+        <v>3.22957539558411</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>5.81500005722046</v>
       </c>
       <c r="G217" t="n">
-        <v>3.16694402694702</v>
+        <v>3.1669442653656</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>6</v>
       </c>
       <c r="G219" t="n">
-        <v>3.26769828796387</v>
+        <v>3.26769804954529</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G220" t="n">
-        <v>3.38206720352173</v>
+        <v>3.38206744194031</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>6.14499998092651</v>
       </c>
       <c r="G221" t="n">
-        <v>3.34666776657104</v>
+        <v>3.34666752815247</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>6.16499996185303</v>
       </c>
       <c r="G222" t="n">
-        <v>3.35756015777588</v>
+        <v>3.3575599193573</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G223" t="n">
-        <v>3.21323657035828</v>
+        <v>3.2132363319397</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G224" t="n">
-        <v>3.18056011199951</v>
+        <v>3.18055939674377</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>5.81500005722046</v>
       </c>
       <c r="G227" t="n">
-        <v>3.16694402694702</v>
+        <v>3.1669442653656</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G228" t="n">
-        <v>3.18600559234619</v>
+        <v>3.18600535392761</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G229" t="n">
-        <v>3.18600559234619</v>
+        <v>3.18600535392761</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G230" t="n">
-        <v>3.17511343955994</v>
+        <v>3.17511320114136</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G232" t="n">
-        <v>3.15877485275269</v>
+        <v>3.15877461433411</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G233" t="n">
-        <v>3.15332889556885</v>
+        <v>3.15332841873169</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>5.88500022888184</v>
       </c>
       <c r="G234" t="n">
-        <v>3.20506763458252</v>
+        <v>3.20506739616394</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>5.95499992370605</v>
       </c>
       <c r="G235" t="n">
-        <v>3.2431902885437</v>
+        <v>3.24319052696228</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>5.95499992370605</v>
       </c>
       <c r="G237" t="n">
-        <v>3.2431902885437</v>
+        <v>3.24319052696228</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G238" t="n">
-        <v>3.24046730995178</v>
+        <v>3.2404670715332</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>5.88500022888184</v>
       </c>
       <c r="G239" t="n">
-        <v>3.20506763458252</v>
+        <v>3.20506739616394</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>5.88500022888184</v>
       </c>
       <c r="G241" t="n">
-        <v>3.20506763458252</v>
+        <v>3.20506739616394</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>5.7350001335144</v>
       </c>
       <c r="G243" t="n">
-        <v>3.12337493896484</v>
+        <v>3.12337517738342</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G245" t="n">
-        <v>3.08797478675842</v>
+        <v>3.08797454833984</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G246" t="n">
-        <v>3.09342050552368</v>
+        <v>3.09342098236084</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G247" t="n">
-        <v>3.16422057151794</v>
+        <v>3.1642210483551</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G248" t="n">
-        <v>3.18600559234619</v>
+        <v>3.18600535392761</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G249" t="n">
-        <v>3.23502087593079</v>
+        <v>3.23502111434937</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G250" t="n">
-        <v>3.21323657035828</v>
+        <v>3.2132363319397</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G251" t="n">
-        <v>3.18600559234619</v>
+        <v>3.18600535392761</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>5.5</v>
       </c>
       <c r="G254" t="n">
-        <v>3.26891088485718</v>
+        <v>3.26891112327576</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G255" t="n">
-        <v>3.26296734809875</v>
+        <v>3.26296710968018</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>5.32499980926514</v>
       </c>
       <c r="G256" t="n">
-        <v>3.16490006446838</v>
+        <v>3.16490030288696</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>5.5</v>
       </c>
       <c r="G257" t="n">
-        <v>3.26891088485718</v>
+        <v>3.26891112327576</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G259" t="n">
-        <v>3.21541953086853</v>
+        <v>3.21542000770569</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G261" t="n">
-        <v>3.20947623252869</v>
+        <v>3.20947599411011</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>5.41499996185303</v>
       </c>
       <c r="G262" t="n">
-        <v>3.21839165687561</v>
+        <v>3.21839141845703</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>5.35500001907349</v>
       </c>
       <c r="G263" t="n">
-        <v>3.18273091316223</v>
+        <v>3.18273067474365</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>5.36499977111816</v>
       </c>
       <c r="G264" t="n">
-        <v>3.1886739730835</v>
+        <v>3.18867421150208</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G267" t="n">
-        <v>3.13815450668335</v>
+        <v>3.13815474510193</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G268" t="n">
-        <v>3.06089019775391</v>
+        <v>3.06088972091675</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>5.18499994277954</v>
       </c>
       <c r="G269" t="n">
-        <v>3.08169150352478</v>
+        <v>3.08169174194336</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>5.25</v>
       </c>
       <c r="G270" t="n">
-        <v>3.12032437324524</v>
+        <v>3.12032413482666</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G271" t="n">
-        <v>3.13815450668335</v>
+        <v>3.13815474510193</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G274" t="n">
-        <v>3.09655070304871</v>
+        <v>3.09655022621155</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G277" t="n">
-        <v>3.00739812850952</v>
+        <v>3.0073983669281</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>5.22499990463257</v>
       </c>
       <c r="G278" t="n">
-        <v>3.10546588897705</v>
+        <v>3.10546541213989</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G279" t="n">
-        <v>3.01928567886353</v>
+        <v>3.01928496360779</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G282" t="n">
-        <v>3.05494618415833</v>
+        <v>3.05494570732117</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G284" t="n">
-        <v>3.03414416313171</v>
+        <v>3.03414368629456</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>5.04500007629395</v>
       </c>
       <c r="G288" t="n">
-        <v>2.99848341941833</v>
+        <v>2.99848318099976</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G292" t="n">
-        <v>3.05791759490967</v>
+        <v>3.05791783332825</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G293" t="n">
-        <v>3.0906069278717</v>
+        <v>3.09060668945312</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G298" t="n">
-        <v>3.06089019775391</v>
+        <v>3.06088972091675</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G299" t="n">
-        <v>3.11438035964966</v>
+        <v>3.11438059806824</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G300" t="n">
-        <v>3.0906069278717</v>
+        <v>3.09060668945312</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>5.29500007629395</v>
       </c>
       <c r="G301" t="n">
-        <v>3.14706993103027</v>
+        <v>3.14706945419312</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>5.34499979019165</v>
       </c>
       <c r="G306" t="n">
-        <v>3.17678689956665</v>
+        <v>3.17678713798523</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>5.13500022888184</v>
       </c>
       <c r="G307" t="n">
-        <v>3.05197477340698</v>
+        <v>3.0519745349884</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G308" t="n">
-        <v>3.01928567886353</v>
+        <v>3.01928496360779</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G309" t="n">
-        <v>3.01334190368652</v>
+        <v>3.0133421421051</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>4.95599985122681</v>
       </c>
       <c r="G310" t="n">
-        <v>2.94558572769165</v>
+        <v>2.94558596611023</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>4.9539999961853</v>
       </c>
       <c r="G311" t="n">
-        <v>2.94439721107483</v>
+        <v>2.94439768791199</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>5</v>
       </c>
       <c r="G313" t="n">
-        <v>2.97173738479614</v>
+        <v>2.97173762321472</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>4.96199989318848</v>
       </c>
       <c r="G316" t="n">
-        <v>2.94915175437927</v>
+        <v>2.94915199279785</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G317" t="n">
-        <v>2.98956799507141</v>
+        <v>2.98956775665283</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G318" t="n">
-        <v>3.05791759490967</v>
+        <v>3.05791783332825</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G321" t="n">
-        <v>3.02522873878479</v>
+        <v>3.02522897720337</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>5.13500022888184</v>
       </c>
       <c r="G322" t="n">
-        <v>3.05197477340698</v>
+        <v>3.0519745349884</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G324" t="n">
-        <v>3.13815450668335</v>
+        <v>3.13815474510193</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G325" t="n">
-        <v>3.12626814842224</v>
+        <v>3.1262674331665</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G327" t="n">
-        <v>3.12626814842224</v>
+        <v>3.1262674331665</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G328" t="n">
-        <v>3.08466339111328</v>
+        <v>3.08466362953186</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G329" t="n">
-        <v>3.10843729972839</v>
+        <v>3.10843753814697</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G330" t="n">
-        <v>3.0906069278717</v>
+        <v>3.09060668945312</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G331" t="n">
-        <v>3.10843729972839</v>
+        <v>3.10843753814697</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>5.29500007629395</v>
       </c>
       <c r="G332" t="n">
-        <v>3.14706993103027</v>
+        <v>3.14706945419312</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G333" t="n">
-        <v>3.18570256233215</v>
+        <v>3.18570280075073</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>5.34499979019165</v>
       </c>
       <c r="G334" t="n">
-        <v>3.17678689956665</v>
+        <v>3.17678713798523</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>5.33500003814697</v>
       </c>
       <c r="G335" t="n">
-        <v>3.17084383964539</v>
+        <v>3.17084360122681</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G336" t="n">
-        <v>3.1500415802002</v>
+        <v>3.15004181861877</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>5.28499984741211</v>
       </c>
       <c r="G337" t="n">
-        <v>3.14112639427185</v>
+        <v>3.14112687110901</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G339" t="n">
-        <v>3.18570256233215</v>
+        <v>3.18570280075073</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G340" t="n">
-        <v>3.20947623252869</v>
+        <v>3.20947599411011</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>5.44500017166138</v>
       </c>
       <c r="G341" t="n">
-        <v>3.23622250556946</v>
+        <v>3.23622179031372</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>5.35500001907349</v>
       </c>
       <c r="G342" t="n">
-        <v>3.18273091316223</v>
+        <v>3.18273067474365</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G343" t="n">
-        <v>3.16787195205688</v>
+        <v>3.16787219047546</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G346" t="n">
-        <v>3.0490026473999</v>
+        <v>3.04900288581848</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G347" t="n">
-        <v>3.05791759490967</v>
+        <v>3.05791783332825</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G348" t="n">
-        <v>3.08466339111328</v>
+        <v>3.08466362953186</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G350" t="n">
-        <v>3.05494618415833</v>
+        <v>3.05494570732117</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G351" t="n">
-        <v>3.06089019775391</v>
+        <v>3.06088972091675</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>5.21500015258789</v>
       </c>
       <c r="G352" t="n">
-        <v>3.09952187538147</v>
+        <v>3.09952163696289</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>5.16499996185303</v>
       </c>
       <c r="G354" t="n">
-        <v>3.06980514526367</v>
+        <v>3.06980443000793</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G356" t="n">
-        <v>3.06089019775391</v>
+        <v>3.06088972091675</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G357" t="n">
-        <v>3.05791759490967</v>
+        <v>3.05791783332825</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>5.13500022888184</v>
       </c>
       <c r="G360" t="n">
-        <v>3.05197477340698</v>
+        <v>3.0519745349884</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>5.13500022888184</v>
       </c>
       <c r="G361" t="n">
-        <v>3.05197477340698</v>
+        <v>3.0519745349884</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G363" t="n">
-        <v>3.05494618415833</v>
+        <v>3.05494570732117</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G364" t="n">
-        <v>3.05791759490967</v>
+        <v>3.05791783332825</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>5.13500022888184</v>
       </c>
       <c r="G365" t="n">
-        <v>3.05197477340698</v>
+        <v>3.0519745349884</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G366" t="n">
-        <v>3.05494618415833</v>
+        <v>3.05494570732117</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G368" t="n">
-        <v>3.06089019775391</v>
+        <v>3.06088972091675</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G369" t="n">
-        <v>3.0906069278717</v>
+        <v>3.09060668945312</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G370" t="n">
-        <v>3.11438035964966</v>
+        <v>3.11438059806824</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G372" t="n">
-        <v>3.09655070304871</v>
+        <v>3.09655022621155</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G374" t="n">
-        <v>3.09655070304871</v>
+        <v>3.09655022621155</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>5.09499979019165</v>
       </c>
       <c r="G377" t="n">
-        <v>3.02820038795471</v>
+        <v>3.02820014953613</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>5.09499979019165</v>
       </c>
       <c r="G378" t="n">
-        <v>3.02820038795471</v>
+        <v>3.02820014953613</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G379" t="n">
-        <v>3.0490026473999</v>
+        <v>3.04900288581848</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>4.98799991607666</v>
       </c>
       <c r="G381" t="n">
-        <v>2.96460556983948</v>
+        <v>2.96460509300232</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>4.71799993515015</v>
       </c>
       <c r="G385" t="n">
-        <v>2.80413126945496</v>
+        <v>2.80413103103638</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>4.71400022506714</v>
       </c>
       <c r="G389" t="n">
-        <v>2.80175423622131</v>
+        <v>2.80175399780273</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G390" t="n">
-        <v>2.80532026290894</v>
+        <v>2.80532002449036</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>4.59600019454956</v>
       </c>
       <c r="G391" t="n">
-        <v>2.73162126541138</v>
+        <v>2.7316210269928</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>4.58199977874756</v>
       </c>
       <c r="G392" t="n">
-        <v>2.723299741745</v>
+        <v>2.72329998016357</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G395" t="n">
-        <v>2.57946801185608</v>
+        <v>2.57946825027466</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G399" t="n">
-        <v>2.70428133010864</v>
+        <v>2.70428109169006</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G400" t="n">
-        <v>2.70428133010864</v>
+        <v>2.70428109169006</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G401" t="n">
-        <v>2.71616816520691</v>
+        <v>2.71616792678833</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G402" t="n">
-        <v>2.71022439002991</v>
+        <v>2.71022415161133</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>4.73600006103516</v>
       </c>
       <c r="G404" t="n">
-        <v>2.8148295879364</v>
+        <v>2.81482982635498</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>4.61199998855591</v>
       </c>
       <c r="G406" t="n">
-        <v>2.74113059043884</v>
+        <v>2.74113082885742</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>4.70599985122681</v>
       </c>
       <c r="G408" t="n">
-        <v>2.79699945449829</v>
+        <v>2.79699897766113</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>4.57600021362305</v>
       </c>
       <c r="G409" t="n">
-        <v>2.71973419189453</v>
+        <v>2.71973443031311</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>4.57600021362305</v>
       </c>
       <c r="G410" t="n">
-        <v>2.71973419189453</v>
+        <v>2.71973443031311</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>4.51599979400635</v>
       </c>
       <c r="G411" t="n">
-        <v>2.68407273292542</v>
+        <v>2.68407297134399</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G412" t="n">
-        <v>2.71022439002991</v>
+        <v>2.71022415161133</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>4.48799991607666</v>
       </c>
       <c r="G413" t="n">
-        <v>2.66743111610413</v>
+        <v>2.66743135452271</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G414" t="n">
-        <v>2.70428133010864</v>
+        <v>2.70428109169006</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G415" t="n">
-        <v>2.71616816520691</v>
+        <v>2.71616792678833</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>4.56599998474121</v>
       </c>
       <c r="G416" t="n">
-        <v>2.71379089355469</v>
+        <v>2.71379041671753</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G417" t="n">
-        <v>2.79343318939209</v>
+        <v>2.79343295097351</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>4.67199993133545</v>
       </c>
       <c r="G418" t="n">
-        <v>2.77679133415222</v>
+        <v>2.7767915725708</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>4.60400009155273</v>
       </c>
       <c r="G422" t="n">
-        <v>2.73637580871582</v>
+        <v>2.7363760471344</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>4.6560001373291</v>
       </c>
       <c r="G423" t="n">
-        <v>2.76728177070618</v>
+        <v>2.76728200912476</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>4.53599977493286</v>
       </c>
       <c r="G425" t="n">
-        <v>2.69595980644226</v>
+        <v>2.69596004486084</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>4.55600023269653</v>
       </c>
       <c r="G426" t="n">
-        <v>2.70784735679626</v>
+        <v>2.70784687995911</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>4.46199989318848</v>
       </c>
       <c r="G428" t="n">
-        <v>2.65197801589966</v>
+        <v>2.65197825431824</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>4.53399991989136</v>
       </c>
       <c r="G431" t="n">
-        <v>2.69477128982544</v>
+        <v>2.69477152824402</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G432" t="n">
-        <v>2.65673327445984</v>
+        <v>2.65673279762268</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>4.48199987411499</v>
       </c>
       <c r="G433" t="n">
-        <v>2.66386532783508</v>
+        <v>2.66386556625366</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>4.50400018692017</v>
       </c>
       <c r="G435" t="n">
-        <v>2.67694139480591</v>
+        <v>2.67694091796875</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>4.45599985122681</v>
       </c>
       <c r="G437" t="n">
-        <v>2.64841222763062</v>
+        <v>2.64841198921204</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>4.57800006866455</v>
       </c>
       <c r="G439" t="n">
-        <v>2.72092247009277</v>
+        <v>2.72092270851135</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G441" t="n">
-        <v>2.86475491523743</v>
+        <v>2.86475515365601</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>4.90199995040894</v>
       </c>
       <c r="G442" t="n">
-        <v>2.91349124908447</v>
+        <v>2.91349148750305</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G443" t="n">
-        <v>2.95390701293945</v>
+        <v>2.95390677452087</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>4.85599994659424</v>
       </c>
       <c r="G444" t="n">
-        <v>2.88615107536316</v>
+        <v>2.88615155220032</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>4.77400016784668</v>
       </c>
       <c r="G450" t="n">
-        <v>2.83741497993469</v>
+        <v>2.83741521835327</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>4.86199998855591</v>
       </c>
       <c r="G454" t="n">
-        <v>2.88971757888794</v>
+        <v>2.88971710205078</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>4.87799978256226</v>
       </c>
       <c r="G455" t="n">
-        <v>2.89922690391541</v>
+        <v>2.89922714233398</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>4.92600011825562</v>
       </c>
       <c r="G457" t="n">
-        <v>2.92775559425354</v>
+        <v>2.92775535583496</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G462" t="n">
-        <v>3.01334190368652</v>
+        <v>3.0133421421051</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G463" t="n">
-        <v>3.0490026473999</v>
+        <v>3.04900288581848</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G467" t="n">
-        <v>3.05494618415833</v>
+        <v>3.05494570732117</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>5.25</v>
       </c>
       <c r="G468" t="n">
-        <v>3.12032437324524</v>
+        <v>3.12032413482666</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G469" t="n">
-        <v>3.16787195205688</v>
+        <v>3.16787219047546</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>5.25</v>
       </c>
       <c r="G470" t="n">
-        <v>3.12032437324524</v>
+        <v>3.12032413482666</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G472" t="n">
-        <v>3.21541953086853</v>
+        <v>3.21542000770569</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G473" t="n">
-        <v>3.16787195205688</v>
+        <v>3.16787219047546</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G474" t="n">
-        <v>3.16787195205688</v>
+        <v>3.16787219047546</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G475" t="n">
-        <v>3.1500415802002</v>
+        <v>3.15004181861877</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G476" t="n">
-        <v>3.13518333435059</v>
+        <v>3.13518309593201</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G477" t="n">
-        <v>3.1500415802002</v>
+        <v>3.15004181861877</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G478" t="n">
-        <v>3.0906069278717</v>
+        <v>3.09060668945312</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>5.24499988555908</v>
       </c>
       <c r="G480" t="n">
-        <v>3.11735224723816</v>
+        <v>3.11735272407532</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G482" t="n">
-        <v>3.1500415802002</v>
+        <v>3.15004181861877</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>5.30499982833862</v>
       </c>
       <c r="G483" t="n">
-        <v>3.15301299095154</v>
+        <v>3.15301275253296</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>5.34499979019165</v>
       </c>
       <c r="G485" t="n">
-        <v>3.17678689956665</v>
+        <v>3.17678713798523</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G486" t="n">
-        <v>3.16787195205688</v>
+        <v>3.16787219047546</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G487" t="n">
-        <v>3.18570256233215</v>
+        <v>3.18570280075073</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G488" t="n">
-        <v>3.19164562225342</v>
+        <v>3.191645860672</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>5.35500001907349</v>
       </c>
       <c r="G489" t="n">
-        <v>3.18273091316223</v>
+        <v>3.18273067474365</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G490" t="n">
-        <v>3.22730684280396</v>
+        <v>3.22730660438538</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>5.49499988555908</v>
       </c>
       <c r="G491" t="n">
-        <v>3.26593971252441</v>
+        <v>3.26593947410583</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G496" t="n">
-        <v>3.29268527030945</v>
+        <v>3.29268550872803</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>5.5</v>
       </c>
       <c r="G497" t="n">
-        <v>3.26891088485718</v>
+        <v>3.26891112327576</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>5.54500007629395</v>
       </c>
       <c r="G498" t="n">
-        <v>3.29565668106079</v>
+        <v>3.29565691947937</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>5.625</v>
       </c>
       <c r="G499" t="n">
-        <v>3.34320449829102</v>
+        <v>3.34320425987244</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>5.60500001907349</v>
       </c>
       <c r="G500" t="n">
-        <v>3.33131718635559</v>
+        <v>3.33131742477417</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>5.42500019073486</v>
       </c>
       <c r="G501" t="n">
-        <v>3.22433495521545</v>
+        <v>3.22433519363403</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G504" t="n">
-        <v>3.28306722640991</v>
+        <v>3.28306746482849</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G505" t="n">
-        <v>3.29296612739563</v>
+        <v>3.29296565055847</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G507" t="n">
-        <v>3.33256101608276</v>
+        <v>3.33256077766418</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G508" t="n">
-        <v>3.32596182823181</v>
+        <v>3.32596158981323</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G509" t="n">
-        <v>3.31936287879944</v>
+        <v>3.31936240196228</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G510" t="n">
-        <v>3.34575915336609</v>
+        <v>3.34575939178467</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G513" t="n">
-        <v>3.39195322990417</v>
+        <v>3.3919529914856</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G514" t="n">
-        <v>3.36555647850037</v>
+        <v>3.36555624008179</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G516" t="n">
-        <v>3.47114229202271</v>
+        <v>3.47114253044128</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G517" t="n">
-        <v>3.47114229202271</v>
+        <v>3.47114253044128</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G518" t="n">
-        <v>3.49093985557556</v>
+        <v>3.49094033241272</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G520" t="n">
-        <v>3.51073718070984</v>
+        <v>3.510737657547</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G521" t="n">
-        <v>3.47114229202271</v>
+        <v>3.47114253044128</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>5.25</v>
       </c>
       <c r="G522" t="n">
-        <v>3.46454334259033</v>
+        <v>3.46454381942749</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G523" t="n">
-        <v>3.43154788017273</v>
+        <v>3.43154764175415</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G527" t="n">
-        <v>3.33256101608276</v>
+        <v>3.33256077766418</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G531" t="n">
-        <v>3.28306722640991</v>
+        <v>3.28306746482849</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>4.9850001335144</v>
       </c>
       <c r="G532" t="n">
-        <v>3.28966641426086</v>
+        <v>3.28966617584229</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>4.9850001335144</v>
       </c>
       <c r="G533" t="n">
-        <v>3.28966641426086</v>
+        <v>3.28966617584229</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G536" t="n">
-        <v>3.26656937599182</v>
+        <v>3.2665696144104</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G538" t="n">
-        <v>3.19397902488708</v>
+        <v>3.19397926330566</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G539" t="n">
-        <v>3.22037577629089</v>
+        <v>3.22037601470947</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G540" t="n">
-        <v>3.20387816429138</v>
+        <v>3.2038779258728</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>4.81500005722046</v>
       </c>
       <c r="G541" t="n">
-        <v>3.17748141288757</v>
+        <v>3.17748117446899</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G542" t="n">
-        <v>3.20387816429138</v>
+        <v>3.2038779258728</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>4.77500009536743</v>
       </c>
       <c r="G543" t="n">
-        <v>3.15108489990234</v>
+        <v>3.15108466148376</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>4.74499988555908</v>
       </c>
       <c r="G544" t="n">
-        <v>3.13128709793091</v>
+        <v>3.13128733634949</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G545" t="n">
-        <v>3.29296612739563</v>
+        <v>3.29296565055847</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>4.9850001335144</v>
       </c>
       <c r="G546" t="n">
-        <v>3.28966641426086</v>
+        <v>3.28966617584229</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G547" t="n">
-        <v>3.31936287879944</v>
+        <v>3.31936240196228</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G548" t="n">
-        <v>3.26656937599182</v>
+        <v>3.2665696144104</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G550" t="n">
-        <v>3.28306722640991</v>
+        <v>3.28306746482849</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>4.94500017166138</v>
       </c>
       <c r="G551" t="n">
-        <v>3.26327037811279</v>
+        <v>3.26327013969421</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>4.93499994277954</v>
       </c>
       <c r="G553" t="n">
-        <v>3.2566704750061</v>
+        <v>3.25667095184326</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G554" t="n">
-        <v>3.24017262458801</v>
+        <v>3.24017310142517</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>4.94500017166138</v>
       </c>
       <c r="G555" t="n">
-        <v>3.26327037811279</v>
+        <v>3.26327013969421</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G556" t="n">
-        <v>3.29296612739563</v>
+        <v>3.29296565055847</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G557" t="n">
-        <v>3.31936287879944</v>
+        <v>3.31936240196228</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G558" t="n">
-        <v>3.28306722640991</v>
+        <v>3.28306746482849</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G559" t="n">
-        <v>3.28306722640991</v>
+        <v>3.28306746482849</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G560" t="n">
-        <v>3.22037577629089</v>
+        <v>3.22037601470947</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G561" t="n">
-        <v>3.20717787742615</v>
+        <v>3.20717716217041</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G563" t="n">
-        <v>3.23357439041138</v>
+        <v>3.2335741519928</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G564" t="n">
-        <v>3.25997042655945</v>
+        <v>3.25997066497803</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>4.94500017166138</v>
       </c>
       <c r="G565" t="n">
-        <v>3.26327037811279</v>
+        <v>3.26327013969421</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G567" t="n">
-        <v>3.33256101608276</v>
+        <v>3.33256077766418</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G568" t="n">
-        <v>3.33915996551514</v>
+        <v>3.33916044235229</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G569" t="n">
-        <v>3.35235810279846</v>
+        <v>3.35235834121704</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G570" t="n">
-        <v>3.33256101608276</v>
+        <v>3.33256077766418</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G572" t="n">
-        <v>3.36555647850037</v>
+        <v>3.36555624008179</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G573" t="n">
-        <v>3.34575915336609</v>
+        <v>3.34575939178467</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G574" t="n">
-        <v>3.32596182823181</v>
+        <v>3.32596158981323</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G576" t="n">
-        <v>3.31936287879944</v>
+        <v>3.31936240196228</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>4.92500019073486</v>
       </c>
       <c r="G578" t="n">
-        <v>3.25007152557373</v>
+        <v>3.25007176399231</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G580" t="n">
-        <v>3.23357439041138</v>
+        <v>3.2335741519928</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G581" t="n">
-        <v>3.22037577629089</v>
+        <v>3.22037601470947</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G583" t="n">
-        <v>3.28306722640991</v>
+        <v>3.28306746482849</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>4.92500019073486</v>
       </c>
       <c r="G584" t="n">
-        <v>3.25007152557373</v>
+        <v>3.25007176399231</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G586" t="n">
-        <v>3.23357439041138</v>
+        <v>3.2335741519928</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G588" t="n">
-        <v>3.23027396202087</v>
+        <v>3.23027467727661</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G589" t="n">
-        <v>3.20387816429138</v>
+        <v>3.2038779258728</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G592" t="n">
-        <v>3.20717787742615</v>
+        <v>3.20717716217041</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G593" t="n">
-        <v>2.98610639572144</v>
+        <v>2.98610663414001</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G594" t="n">
-        <v>2.93001413345337</v>
+        <v>2.93001437187195</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G596" t="n">
-        <v>2.94321250915527</v>
+        <v>2.94321227073669</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>4.7350001335144</v>
       </c>
       <c r="G598" t="n">
-        <v>3.12468838691711</v>
+        <v>3.12468814849854</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G599" t="n">
-        <v>2.99930477142334</v>
+        <v>2.99930500984192</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G600" t="n">
-        <v>2.98940634727478</v>
+        <v>2.98940587043762</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G602" t="n">
-        <v>2.99930477142334</v>
+        <v>2.99930500984192</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G603" t="n">
-        <v>3.00260448455811</v>
+        <v>3.00260472297668</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G604" t="n">
-        <v>3.0224015712738</v>
+        <v>3.02240180969238</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G605" t="n">
-        <v>3.01580262184143</v>
+        <v>3.01580286026001</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G606" t="n">
-        <v>3.03230047225952</v>
+        <v>3.03230023384094</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G607" t="n">
-        <v>3.04219889640808</v>
+        <v>3.04219913482666</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G608" t="n">
-        <v>3.05539751052856</v>
+        <v>3.05539774894714</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G611" t="n">
-        <v>3.08839297294617</v>
+        <v>3.08839249610901</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G612" t="n">
-        <v>3.08179402351379</v>
+        <v>3.08179426193237</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>4.75</v>
       </c>
       <c r="G613" t="n">
-        <v>3.13458657264709</v>
+        <v>3.13458704948425</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G614" t="n">
-        <v>3.17418146133423</v>
+        <v>3.17418169975281</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G615" t="n">
-        <v>3.17418146133423</v>
+        <v>3.17418169975281</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G616" t="n">
-        <v>3.15768384933472</v>
+        <v>3.15768361091614</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G617" t="n">
-        <v>3.20717787742615</v>
+        <v>3.20717716217041</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G618" t="n">
-        <v>3.18738007545471</v>
+        <v>3.18737959861755</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G619" t="n">
-        <v>3.15438413619995</v>
+        <v>3.15438461303711</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>4.81500005722046</v>
       </c>
       <c r="G622" t="n">
-        <v>3.17748141288757</v>
+        <v>3.17748117446899</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G623" t="n">
-        <v>3.16758251190186</v>
+        <v>3.16758275032043</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>4.77500009536743</v>
       </c>
       <c r="G624" t="n">
-        <v>3.15108489990234</v>
+        <v>3.15108466148376</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>4.74499988555908</v>
       </c>
       <c r="G625" t="n">
-        <v>3.13128709793091</v>
+        <v>3.13128733634949</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G626" t="n">
-        <v>3.15768384933472</v>
+        <v>3.15768361091614</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G627" t="n">
-        <v>3.17418146133423</v>
+        <v>3.17418169975281</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G628" t="n">
-        <v>3.15768384933472</v>
+        <v>3.15768361091614</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G630" t="n">
-        <v>3.10159111022949</v>
+        <v>3.10159087181091</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G631" t="n">
-        <v>3.10819005966187</v>
+        <v>3.10819053649902</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>4.75</v>
       </c>
       <c r="G632" t="n">
-        <v>3.13458657264709</v>
+        <v>3.13458704948425</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G633" t="n">
-        <v>3.16758251190186</v>
+        <v>3.16758275032043</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>4.80499982833862</v>
       </c>
       <c r="G634" t="n">
-        <v>3.17088222503662</v>
+        <v>3.1708824634552</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G637" t="n">
-        <v>3.28306722640991</v>
+        <v>3.28306746482849</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G638" t="n">
-        <v>3.31936287879944</v>
+        <v>3.31936240196228</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G640" t="n">
-        <v>3.33915996551514</v>
+        <v>3.33916044235229</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>5.25</v>
       </c>
       <c r="G641" t="n">
-        <v>3.46454334259033</v>
+        <v>3.46454381942749</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G642" t="n">
-        <v>3.51073718070984</v>
+        <v>3.510737657547</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G643" t="n">
-        <v>3.48434090614319</v>
+        <v>3.48434114456177</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G646" t="n">
-        <v>3.53053426742554</v>
+        <v>3.53053450584412</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G647" t="n">
-        <v>3.55693173408508</v>
+        <v>3.55693101882935</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G648" t="n">
-        <v>3.5965256690979</v>
+        <v>3.59652590751648</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G649" t="n">
-        <v>3.61632347106934</v>
+        <v>3.61632323265076</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G650" t="n">
-        <v>3.58332800865173</v>
+        <v>3.58332753181458</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G651" t="n">
-        <v>3.58332800865173</v>
+        <v>3.58332753181458</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G655" t="n">
-        <v>3.56353044509888</v>
+        <v>3.5635302066803</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>5.5</v>
       </c>
       <c r="G656" t="n">
-        <v>3.62952208518982</v>
+        <v>3.62952184677124</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G657" t="n">
-        <v>3.53053426742554</v>
+        <v>3.53053450584412</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G658" t="n">
-        <v>3.48434090614319</v>
+        <v>3.48434114456177</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G659" t="n">
-        <v>3.53053426742554</v>
+        <v>3.53053450584412</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G660" t="n">
-        <v>3.53053426742554</v>
+        <v>3.53053450584412</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G661" t="n">
-        <v>3.52393579483032</v>
+        <v>3.52393531799316</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G662" t="n">
-        <v>3.56353044509888</v>
+        <v>3.5635302066803</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G663" t="n">
-        <v>3.51733660697937</v>
+        <v>3.51733636856079</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G664" t="n">
-        <v>3.47114229202271</v>
+        <v>3.47114253044128</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G665" t="n">
-        <v>3.44474577903748</v>
+        <v>3.44474601745605</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G666" t="n">
-        <v>3.47114229202271</v>
+        <v>3.47114253044128</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G667" t="n">
-        <v>3.53053426742554</v>
+        <v>3.53053450584412</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G668" t="n">
-        <v>3.55693173408508</v>
+        <v>3.55693101882935</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G670" t="n">
-        <v>3.5767285823822</v>
+        <v>3.57672882080078</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G672" t="n">
-        <v>3.60312557220459</v>
+        <v>3.60312533378601</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G674" t="n">
-        <v>3.53053426742554</v>
+        <v>3.53053450584412</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G678" t="n">
-        <v>3.51733660697937</v>
+        <v>3.51733636856079</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G679" t="n">
-        <v>3.49753952026367</v>
+        <v>3.49753904342651</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G681" t="n">
-        <v>3.53053426742554</v>
+        <v>3.53053450584412</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G682" t="n">
-        <v>3.51073718070984</v>
+        <v>3.510737657547</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G683" t="n">
-        <v>3.49093985557556</v>
+        <v>3.49094033241272</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G686" t="n">
-        <v>3.53053426742554</v>
+        <v>3.53053450584412</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G687" t="n">
-        <v>3.51733660697937</v>
+        <v>3.51733636856079</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G688" t="n">
-        <v>3.49753952026367</v>
+        <v>3.49753904342651</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G689" t="n">
-        <v>3.47774195671082</v>
+        <v>3.47774171829224</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G690" t="n">
-        <v>3.52393579483032</v>
+        <v>3.52393531799316</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G693" t="n">
-        <v>3.49753952026367</v>
+        <v>3.49753904342651</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G694" t="n">
-        <v>3.53053426742554</v>
+        <v>3.53053450584412</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G696" t="n">
-        <v>3.55693173408508</v>
+        <v>3.55693101882935</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G697" t="n">
-        <v>3.53053426742554</v>
+        <v>3.53053450584412</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G698" t="n">
-        <v>3.51733660697937</v>
+        <v>3.51733636856079</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G699" t="n">
-        <v>3.55693173408508</v>
+        <v>3.55693101882935</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G700" t="n">
-        <v>3.56353044509888</v>
+        <v>3.5635302066803</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>5.5</v>
       </c>
       <c r="G703" t="n">
-        <v>3.62952208518982</v>
+        <v>3.62952184677124</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G704" t="n">
-        <v>3.70871067047119</v>
+        <v>3.70871114730835</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G705" t="n">
-        <v>3.72850894927979</v>
+        <v>3.72850871086121</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G706" t="n">
-        <v>3.74170660972595</v>
+        <v>3.74170684814453</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G709" t="n">
-        <v>3.80769777297974</v>
+        <v>3.80769824981689</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G710" t="n">
-        <v>3.74830627441406</v>
+        <v>3.74830603599548</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G711" t="n">
-        <v>3.66251754760742</v>
+        <v>3.662517786026</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G712" t="n">
-        <v>3.66251754760742</v>
+        <v>3.662517786026</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G714" t="n">
-        <v>3.70871067047119</v>
+        <v>3.70871114730835</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G715" t="n">
-        <v>3.77470207214355</v>
+        <v>3.77470254898071</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G716" t="n">
-        <v>3.74830627441406</v>
+        <v>3.74830603599548</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G717" t="n">
-        <v>3.74830627441406</v>
+        <v>3.74830603599548</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G718" t="n">
-        <v>3.78790068626404</v>
+        <v>3.7878999710083</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G719" t="n">
-        <v>3.78130173683167</v>
+        <v>3.78130221366882</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G720" t="n">
-        <v>3.82749533653259</v>
+        <v>3.82749557495117</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G721" t="n">
-        <v>3.82749533653259</v>
+        <v>3.82749557495117</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G722" t="n">
-        <v>3.87368965148926</v>
+        <v>3.87368941307068</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G723" t="n">
-        <v>3.93308234214783</v>
+        <v>3.93308162689209</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G724" t="n">
-        <v>3.93308234214783</v>
+        <v>3.93308162689209</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G727" t="n">
-        <v>3.99247407913208</v>
+        <v>3.99247431755066</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G728" t="n">
-        <v>3.76150441169739</v>
+        <v>3.76150417327881</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G729" t="n">
-        <v>3.72190928459167</v>
+        <v>3.72190976142883</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G730" t="n">
-        <v>3.84729337692261</v>
+        <v>3.84729290008545</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G731" t="n">
-        <v>3.75490546226501</v>
+        <v>3.75490522384644</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G732" t="n">
-        <v>3.6493194103241</v>
+        <v>3.64931917190552</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G733" t="n">
-        <v>3.48434090614319</v>
+        <v>3.48434114456177</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G734" t="n">
-        <v>3.55693173408508</v>
+        <v>3.55693101882935</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G735" t="n">
-        <v>3.51073718070984</v>
+        <v>3.510737657547</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G736" t="n">
-        <v>3.47774195671082</v>
+        <v>3.47774171829224</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G737" t="n">
-        <v>3.28306722640991</v>
+        <v>3.28306746482849</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>4.625</v>
       </c>
       <c r="G740" t="n">
-        <v>3.05209803581238</v>
+        <v>3.0520977973938</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G742" t="n">
-        <v>2.90361738204956</v>
+        <v>2.90361762046814</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G743" t="n">
-        <v>2.76503586769104</v>
+        <v>2.76503562927246</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>4.07499980926514</v>
       </c>
       <c r="G745" t="n">
-        <v>2.68914556503296</v>
+        <v>2.68914532661438</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>4.65500020980835</v>
       </c>
       <c r="G747" t="n">
-        <v>3.07189536094666</v>
+        <v>3.07189512252808</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>4.75</v>
       </c>
       <c r="G749" t="n">
-        <v>3.13458657264709</v>
+        <v>3.13458704948425</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G752" t="n">
-        <v>3.16758251190186</v>
+        <v>3.16758275032043</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>4.43499994277954</v>
       </c>
       <c r="G753" t="n">
-        <v>2.92671394348145</v>
+        <v>2.92671418190002</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G754" t="n">
-        <v>3.12138891220093</v>
+        <v>3.12138867378235</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G755" t="n">
-        <v>3.11808943748474</v>
+        <v>3.11808896064758</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G756" t="n">
-        <v>3.04879808425903</v>
+        <v>3.04879832267761</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G757" t="n">
-        <v>3.01580262184143</v>
+        <v>3.01580286026001</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G758" t="n">
-        <v>3.10159111022949</v>
+        <v>3.10159087181091</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G760" t="n">
-        <v>3.33915996551514</v>
+        <v>3.33916044235229</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G761" t="n">
-        <v>3.36555647850037</v>
+        <v>3.36555624008179</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G762" t="n">
-        <v>3.25997042655945</v>
+        <v>3.25997066497803</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G764" t="n">
-        <v>3.10819005966187</v>
+        <v>3.10819053649902</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G765" t="n">
-        <v>3.08839297294617</v>
+        <v>3.08839249610901</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G766" t="n">
-        <v>3.08179402351379</v>
+        <v>3.08179426193237</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G767" t="n">
-        <v>3.11808943748474</v>
+        <v>3.11808896064758</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G769" t="n">
-        <v>3.11808943748474</v>
+        <v>3.11808896064758</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G770" t="n">
-        <v>3.10159111022949</v>
+        <v>3.10159087181091</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G771" t="n">
-        <v>3.15768384933472</v>
+        <v>3.15768361091614</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G772" t="n">
-        <v>3.24017262458801</v>
+        <v>3.24017310142517</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G773" t="n">
-        <v>3.24017262458801</v>
+        <v>3.24017310142517</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G775" t="n">
-        <v>3.00260448455811</v>
+        <v>3.00260472297668</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G778" t="n">
-        <v>2.98280692100525</v>
+        <v>2.98280668258667</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G780" t="n">
-        <v>3.17418146133423</v>
+        <v>3.17418169975281</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>4.75</v>
       </c>
       <c r="G781" t="n">
-        <v>3.13458657264709</v>
+        <v>3.13458704948425</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>4.84499979019165</v>
       </c>
       <c r="G783" t="n">
-        <v>3.19727826118469</v>
+        <v>3.19727849960327</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G785" t="n">
-        <v>3.37875461578369</v>
+        <v>3.37875437736511</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G786" t="n">
-        <v>3.36555647850037</v>
+        <v>3.36555624008179</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G787" t="n">
-        <v>3.26656937599182</v>
+        <v>3.2665696144104</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>4.92500019073486</v>
       </c>
       <c r="G788" t="n">
-        <v>3.25007152557373</v>
+        <v>3.25007176399231</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G790" t="n">
-        <v>3.33256101608276</v>
+        <v>3.33256077766418</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G792" t="n">
-        <v>3.44474577903748</v>
+        <v>3.44474601745605</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G794" t="n">
-        <v>3.52393579483032</v>
+        <v>3.52393531799316</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G795" t="n">
-        <v>3.52393579483032</v>
+        <v>3.52393531799316</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G796" t="n">
-        <v>3.35235810279846</v>
+        <v>3.35235834121704</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G798" t="n">
-        <v>3.37875461578369</v>
+        <v>3.37875437736511</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G800" t="n">
-        <v>3.37875461578369</v>
+        <v>3.37875437736511</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>4.79500007629395</v>
       </c>
       <c r="G803" t="n">
-        <v>3.16428303718567</v>
+        <v>3.16428327560425</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G804" t="n">
-        <v>3.11808943748474</v>
+        <v>3.11808896064758</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G805" t="n">
-        <v>3.10159111022949</v>
+        <v>3.10159087181091</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G806" t="n">
-        <v>3.16758251190186</v>
+        <v>3.16758275032043</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G808" t="n">
-        <v>3.19397902488708</v>
+        <v>3.19397926330566</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G809" t="n">
-        <v>3.19397902488708</v>
+        <v>3.19397926330566</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>4.7649998664856</v>
       </c>
       <c r="G810" t="n">
-        <v>3.14448571205139</v>
+        <v>3.14448547363281</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G812" t="n">
-        <v>3.14118623733521</v>
+        <v>3.14118599891663</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>4.7649998664856</v>
       </c>
       <c r="G813" t="n">
-        <v>3.14448571205139</v>
+        <v>3.14448547363281</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G814" t="n">
-        <v>3.26656937599182</v>
+        <v>3.2665696144104</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G816" t="n">
-        <v>3.33915996551514</v>
+        <v>3.33916044235229</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G817" t="n">
-        <v>3.33915996551514</v>
+        <v>3.33916044235229</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G821" t="n">
-        <v>3.36555647850037</v>
+        <v>3.36555624008179</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G823" t="n">
-        <v>3.39195322990417</v>
+        <v>3.3919529914856</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G825" t="n">
-        <v>3.31936287879944</v>
+        <v>3.31936240196228</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>4.92500019073486</v>
       </c>
       <c r="G826" t="n">
-        <v>3.25007152557373</v>
+        <v>3.25007176399231</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G828" t="n">
-        <v>3.32596182823181</v>
+        <v>3.32596158981323</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G832" t="n">
-        <v>3.33915996551514</v>
+        <v>3.33916044235229</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>4.91499996185303</v>
       </c>
       <c r="G834" t="n">
-        <v>3.24347281455994</v>
+        <v>3.24347233772278</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G837" t="n">
-        <v>3.19397902488708</v>
+        <v>3.19397926330566</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>4.81500005722046</v>
       </c>
       <c r="G839" t="n">
-        <v>3.17748141288757</v>
+        <v>3.17748117446899</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>4.80499982833862</v>
       </c>
       <c r="G840" t="n">
-        <v>3.17088222503662</v>
+        <v>3.1708824634552</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G842" t="n">
-        <v>3.23357439041138</v>
+        <v>3.2335741519928</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G843" t="n">
-        <v>3.16758251190186</v>
+        <v>3.16758275032043</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G844" t="n">
-        <v>3.16098356246948</v>
+        <v>3.1609833240509</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G845" t="n">
-        <v>3.16758251190186</v>
+        <v>3.16758275032043</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>4.75</v>
       </c>
       <c r="G849" t="n">
-        <v>3.13458657264709</v>
+        <v>3.13458704948425</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>4.68499994277954</v>
       </c>
       <c r="G850" t="n">
-        <v>3.09169268608093</v>
+        <v>3.09169244766235</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>4.61499977111816</v>
       </c>
       <c r="G851" t="n">
-        <v>3.04549860954285</v>
+        <v>3.04549837112427</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G853" t="n">
-        <v>3.0224015712738</v>
+        <v>3.02240180969238</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>4.64499998092651</v>
       </c>
       <c r="G854" t="n">
-        <v>3.06529593467712</v>
+        <v>3.0652961730957</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G856" t="n">
-        <v>3.05539751052856</v>
+        <v>3.05539774894714</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G857" t="n">
-        <v>3.05539751052856</v>
+        <v>3.05539774894714</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G859" t="n">
-        <v>3.12798738479614</v>
+        <v>3.12798762321472</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>4.65500020980835</v>
       </c>
       <c r="G860" t="n">
-        <v>3.07189536094666</v>
+        <v>3.07189512252808</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G861" t="n">
-        <v>3.03230047225952</v>
+        <v>3.03230023384094</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G862" t="n">
-        <v>3.07519459724426</v>
+        <v>3.07519483566284</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G864" t="n">
-        <v>2.98610639572144</v>
+        <v>2.98610663414001</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>4.5149998664856</v>
       </c>
       <c r="G866" t="n">
-        <v>2.9795069694519</v>
+        <v>2.97950720787048</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>4.625</v>
       </c>
       <c r="G867" t="n">
-        <v>3.05209803581238</v>
+        <v>3.0520977973938</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>4.625</v>
       </c>
       <c r="G868" t="n">
-        <v>3.05209803581238</v>
+        <v>3.0520977973938</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G869" t="n">
-        <v>3.05539751052856</v>
+        <v>3.05539774894714</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G871" t="n">
-        <v>3.05539751052856</v>
+        <v>3.05539774894714</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>4.7649998664856</v>
       </c>
       <c r="G873" t="n">
-        <v>3.14448571205139</v>
+        <v>3.14448547363281</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G875" t="n">
-        <v>3.14118623733521</v>
+        <v>3.14118599891663</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>4.7649998664856</v>
       </c>
       <c r="G877" t="n">
-        <v>3.14448571205139</v>
+        <v>3.14448547363281</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>4.7649998664856</v>
       </c>
       <c r="G878" t="n">
-        <v>3.14448571205139</v>
+        <v>3.14448547363281</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G879" t="n">
-        <v>3.16098356246948</v>
+        <v>3.1609833240509</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G880" t="n">
-        <v>3.15438413619995</v>
+        <v>3.15438461303711</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>4.74499988555908</v>
       </c>
       <c r="G881" t="n">
-        <v>3.13128709793091</v>
+        <v>3.13128733634949</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>4.80499982833862</v>
       </c>
       <c r="G882" t="n">
-        <v>3.17088222503662</v>
+        <v>3.1708824634552</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G883" t="n">
-        <v>3.16098356246948</v>
+        <v>3.1609833240509</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G884" t="n">
-        <v>3.20717787742615</v>
+        <v>3.20717716217041</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G886" t="n">
-        <v>3.33256101608276</v>
+        <v>3.33256077766418</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>4.93499994277954</v>
       </c>
       <c r="G887" t="n">
-        <v>3.2566704750061</v>
+        <v>3.25667095184326</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>4.84499979019165</v>
       </c>
       <c r="G888" t="n">
-        <v>3.19727826118469</v>
+        <v>3.19727849960327</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G889" t="n">
-        <v>3.17418146133423</v>
+        <v>3.17418169975281</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>4.81500005722046</v>
       </c>
       <c r="G890" t="n">
-        <v>3.17748141288757</v>
+        <v>3.17748117446899</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G891" t="n">
-        <v>3.08839297294617</v>
+        <v>3.08839249610901</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G892" t="n">
-        <v>3.08179402351379</v>
+        <v>3.08179426193237</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G893" t="n">
-        <v>2.94321250915527</v>
+        <v>2.94321227073669</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G894" t="n">
-        <v>2.94321250915527</v>
+        <v>2.94321227073669</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G895" t="n">
-        <v>2.91681551933289</v>
+        <v>2.91681528091431</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G896" t="n">
-        <v>2.90361738204956</v>
+        <v>2.90361762046814</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G899" t="n">
-        <v>2.81122970581055</v>
+        <v>2.81122994422913</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>4.16499996185303</v>
       </c>
       <c r="G900" t="n">
-        <v>2.74853754043579</v>
+        <v>2.74853801727295</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G908" t="n">
-        <v>2.75183749198914</v>
+        <v>2.75183725357056</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G909" t="n">
-        <v>2.78483271598816</v>
+        <v>2.7848334312439</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G911" t="n">
-        <v>2.96300959587097</v>
+        <v>2.96300935745239</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G912" t="n">
-        <v>3.00260448455811</v>
+        <v>3.00260472297668</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G913" t="n">
-        <v>2.89041900634766</v>
+        <v>2.89041924476624</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>4.5</v>
       </c>
       <c r="G915" t="n">
-        <v>2.96960878372192</v>
+        <v>2.96960854530334</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G917" t="n">
-        <v>3.05539751052856</v>
+        <v>3.05539774894714</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G918" t="n">
-        <v>3.00260448455811</v>
+        <v>3.00260472297668</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G919" t="n">
-        <v>3.03230047225952</v>
+        <v>3.03230023384094</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>4.64499998092651</v>
       </c>
       <c r="G920" t="n">
-        <v>3.06529593467712</v>
+        <v>3.0652961730957</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>4.61499977111816</v>
       </c>
       <c r="G921" t="n">
-        <v>3.04549860954285</v>
+        <v>3.04549837112427</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>4.7649998664856</v>
       </c>
       <c r="G923" t="n">
-        <v>3.14448571205139</v>
+        <v>3.14448547363281</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G924" t="n">
-        <v>3.12138891220093</v>
+        <v>3.12138867378235</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G927" t="n">
-        <v>2.98610639572144</v>
+        <v>2.98610663414001</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>4.53499984741211</v>
       </c>
       <c r="G930" t="n">
-        <v>2.99270534515381</v>
+        <v>2.99270558357239</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G932" t="n">
-        <v>2.95971012115479</v>
+        <v>2.95971035957336</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>4.64499998092651</v>
       </c>
       <c r="G935" t="n">
-        <v>3.06529593467712</v>
+        <v>3.0652961730957</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G936" t="n">
-        <v>2.93001413345337</v>
+        <v>2.93001437187195</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>4.65500020980835</v>
       </c>
       <c r="G939" t="n">
-        <v>3.07189536094666</v>
+        <v>3.07189512252808</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>4.5</v>
       </c>
       <c r="G940" t="n">
-        <v>2.96960878372192</v>
+        <v>2.96960854530334</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G941" t="n">
-        <v>2.98940634727478</v>
+        <v>2.98940587043762</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G943" t="n">
-        <v>3.10819005966187</v>
+        <v>3.10819053649902</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G945" t="n">
-        <v>3.25997042655945</v>
+        <v>3.25997066497803</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G946" t="n">
-        <v>3.16098356246948</v>
+        <v>3.1609833240509</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>4.68499994277954</v>
       </c>
       <c r="G947" t="n">
-        <v>3.09169268608093</v>
+        <v>3.09169244766235</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G948" t="n">
-        <v>3.14118623733521</v>
+        <v>3.14118599891663</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>4.7350001335144</v>
       </c>
       <c r="G949" t="n">
-        <v>3.12468838691711</v>
+        <v>3.12468814849854</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G951" t="n">
-        <v>3.20387816429138</v>
+        <v>3.2038779258728</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G952" t="n">
-        <v>3.08839297294617</v>
+        <v>3.08839249610901</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G954" t="n">
-        <v>3.11808943748474</v>
+        <v>3.11808896064758</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G955" t="n">
-        <v>3.08179402351379</v>
+        <v>3.08179426193237</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G956" t="n">
-        <v>3.08839297294617</v>
+        <v>3.08839249610901</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G957" t="n">
-        <v>3.08839297294617</v>
+        <v>3.08839249610901</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G960" t="n">
-        <v>3.00260448455811</v>
+        <v>3.00260472297668</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>4.60500001907349</v>
       </c>
       <c r="G962" t="n">
-        <v>3.03889966011047</v>
+        <v>3.03889942169189</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G963" t="n">
-        <v>3.0224015712738</v>
+        <v>3.02240180969238</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G964" t="n">
-        <v>2.98610639572144</v>
+        <v>2.98610663414001</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G965" t="n">
-        <v>2.99930477142334</v>
+        <v>2.99930500984192</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G970" t="n">
-        <v>3.23027396202087</v>
+        <v>3.23027467727661</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G971" t="n">
-        <v>3.23357439041138</v>
+        <v>3.2335741519928</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G972" t="n">
-        <v>3.2533712387085</v>
+        <v>3.25337100028992</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G973" t="n">
-        <v>3.43154788017273</v>
+        <v>3.43154764175415</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G975" t="n">
-        <v>3.74830627441406</v>
+        <v>3.74830603599548</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G976" t="n">
-        <v>3.76150441169739</v>
+        <v>3.76150417327881</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G977" t="n">
-        <v>3.7153103351593</v>
+        <v>3.71531009674072</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G978" t="n">
-        <v>3.60312557220459</v>
+        <v>3.60312533378601</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G979" t="n">
-        <v>3.70211243629456</v>
+        <v>3.7021119594574</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G980" t="n">
-        <v>3.66251754760742</v>
+        <v>3.662517786026</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G981" t="n">
-        <v>3.64272022247314</v>
+        <v>3.64271998405457</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G982" t="n">
-        <v>3.5965256690979</v>
+        <v>3.59652590751648</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G983" t="n">
-        <v>3.62292242050171</v>
+        <v>3.62292194366455</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G984" t="n">
-        <v>3.62292242050171</v>
+        <v>3.62292194366455</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G986" t="n">
-        <v>3.68231415748596</v>
+        <v>3.6823148727417</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G987" t="n">
-        <v>3.66911673545837</v>
+        <v>3.66911649703979</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G988" t="n">
-        <v>3.66911673545837</v>
+        <v>3.66911649703979</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G989" t="n">
-        <v>3.64272022247314</v>
+        <v>3.64271998405457</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G990" t="n">
-        <v>3.66911673545837</v>
+        <v>3.66911649703979</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G991" t="n">
-        <v>3.66251754760742</v>
+        <v>3.662517786026</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G992" t="n">
-        <v>3.82089686393738</v>
+        <v>3.82089638710022</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>6.30999994277954</v>
       </c>
       <c r="G995" t="n">
-        <v>4.1640510559082</v>
+        <v>4.16405153274536</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>6.3899998664856</v>
       </c>
       <c r="G1001" t="n">
-        <v>4.21684408187866</v>
+        <v>4.2168436050415</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G1003" t="n">
-        <v>4.26963663101196</v>
+        <v>4.26963758468628</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G1006" t="n">
-        <v>4.2613091468811</v>
+        <v>4.26130962371826</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G1007" t="n">
-        <v>4.2613091468811</v>
+        <v>4.26130962371826</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G1008" t="n">
-        <v>4.14882183074951</v>
+        <v>4.1488208770752</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>6.28499984741211</v>
       </c>
       <c r="G1009" t="n">
-        <v>4.15874671936035</v>
+        <v>4.15874719619751</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>6.52500009536743</v>
       </c>
       <c r="G1010" t="n">
-        <v>4.31755399703979</v>
+        <v>4.31755352020264</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G1012" t="n">
-        <v>4.31424474716187</v>
+        <v>4.31424570083618</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>6.55499982833862</v>
       </c>
       <c r="G1013" t="n">
-        <v>4.33740425109863</v>
+        <v>4.33740472793579</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G1014" t="n">
-        <v>4.3605637550354</v>
+        <v>4.36056327819824</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G1016" t="n">
-        <v>4.51937007904053</v>
+        <v>4.51937055587769</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>6.83500003814697</v>
       </c>
       <c r="G1019" t="n">
-        <v>4.52267932891846</v>
+        <v>4.5226788520813</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>6.75</v>
       </c>
       <c r="G1020" t="n">
-        <v>4.46643495559692</v>
+        <v>4.46643543243408</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G1021" t="n">
-        <v>4.51937007904053</v>
+        <v>4.51937055587769</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G1022" t="n">
-        <v>4.68479347229004</v>
+        <v>4.6847939491272</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>7.17500019073486</v>
       </c>
       <c r="G1023" t="n">
-        <v>4.7476544380188</v>
+        <v>4.74765491485596</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G1025" t="n">
-        <v>4.8899188041687</v>
+        <v>4.88991928100586</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G1027" t="n">
-        <v>4.85683393478394</v>
+        <v>4.85683488845825</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G1030" t="n">
-        <v>4.87668466567993</v>
+        <v>4.87668514251709</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>7.55499982833862</v>
       </c>
       <c r="G1032" t="n">
-        <v>4.99909830093384</v>
+        <v>4.99909734725952</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>7.66499996185303</v>
       </c>
       <c r="G1034" t="n">
-        <v>5.07188510894775</v>
+        <v>5.0718846321106</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1035" t="n">
-        <v>4.87006855010986</v>
+        <v>4.87006807327271</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>7.61499977111816</v>
       </c>
       <c r="G1037" t="n">
-        <v>5.03880023956299</v>
+        <v>5.03879928588867</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>7.66499996185303</v>
       </c>
       <c r="G1040" t="n">
-        <v>5.07188510894775</v>
+        <v>5.0718846321106</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>7.625</v>
       </c>
       <c r="G1045" t="n">
-        <v>5.04541635513306</v>
+        <v>5.04541730880737</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>7.69500017166138</v>
       </c>
       <c r="G1048" t="n">
-        <v>5.09173583984375</v>
+        <v>5.09173536300659</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G1049" t="n">
-        <v>5.08842706680298</v>
+        <v>5.08842658996582</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>8.09000015258789</v>
       </c>
       <c r="G1056" t="n">
-        <v>5.35310459136963</v>
+        <v>5.35310506820679</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1058" t="n">
-        <v>5.46559286117554</v>
+        <v>5.4655933380127</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G1062" t="n">
-        <v>5.60454893112183</v>
+        <v>5.60454845428467</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>8.51500034332275</v>
       </c>
       <c r="G1066" t="n">
-        <v>5.63432502746582</v>
+        <v>5.63432550430298</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G1067" t="n">
-        <v>5.61116456985474</v>
+        <v>5.61116504669189</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>8.51500034332275</v>
       </c>
       <c r="G1070" t="n">
-        <v>5.63432502746582</v>
+        <v>5.63432550430298</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G1071" t="n">
-        <v>5.59131479263306</v>
+        <v>5.5913143157959</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>8.625</v>
       </c>
       <c r="G1072" t="n">
-        <v>5.70711183547974</v>
+        <v>5.70711135864258</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G1075" t="n">
-        <v>5.57808113098145</v>
+        <v>5.57808065414429</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1079" t="n">
-        <v>5.55822944641113</v>
+        <v>5.55822992324829</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G1080" t="n">
-        <v>5.57808113098145</v>
+        <v>5.57808065414429</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1081" t="n">
-        <v>5.65748405456543</v>
+        <v>5.65748453140259</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G1082" t="n">
-        <v>5.51191091537476</v>
+        <v>5.51191139221191</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1083" t="n">
-        <v>5.42589044570923</v>
+        <v>5.42589092254639</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>7.95499992370605</v>
       </c>
       <c r="G1084" t="n">
-        <v>5.26377630233765</v>
+        <v>5.26377582550049</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>8.49499988555908</v>
       </c>
       <c r="G1087" t="n">
-        <v>5.62109136581421</v>
+        <v>5.62109041213989</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>8.8100004196167</v>
       </c>
       <c r="G1093" t="n">
-        <v>5.82952451705933</v>
+        <v>5.82952499389648</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>8.86999988555908</v>
       </c>
       <c r="G1094" t="n">
-        <v>5.86922550201416</v>
+        <v>5.86922597885132</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>8.80500030517578</v>
       </c>
       <c r="G1095" t="n">
-        <v>5.82621574401855</v>
+        <v>5.82621622085571</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>8.86999988555908</v>
       </c>
       <c r="G1097" t="n">
-        <v>5.86922550201416</v>
+        <v>5.86922597885132</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G1102" t="n">
-        <v>5.1942982673645</v>
+        <v>5.19429779052734</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>7.79500007629395</v>
       </c>
       <c r="G1104" t="n">
-        <v>5.15790557861328</v>
+        <v>5.15790510177612</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>7.74499988555908</v>
       </c>
       <c r="G1108" t="n">
-        <v>5.1248197555542</v>
+        <v>5.12482023239136</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G1109" t="n">
-        <v>5.23399925231934</v>
+        <v>5.23399972915649</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>7.96500015258789</v>
       </c>
       <c r="G1110" t="n">
-        <v>5.27039289474487</v>
+        <v>5.27039241790771</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>7.75</v>
       </c>
       <c r="G1114" t="n">
-        <v>5.12812900543213</v>
+        <v>5.12812852859497</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G1118" t="n">
-        <v>5.18768167495728</v>
+        <v>5.18768119812012</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>8.01500034332275</v>
       </c>
       <c r="G1119" t="n">
-        <v>5.3034782409668</v>
+        <v>5.30347776412964</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>7.91499996185303</v>
       </c>
       <c r="G1120" t="n">
-        <v>5.23730802536011</v>
+        <v>5.23730850219727</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>8.27499961853027</v>
       </c>
       <c r="G1123" t="n">
-        <v>5.47551822662354</v>
+        <v>5.47551774978638</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>8.09500026702881</v>
       </c>
       <c r="G1125" t="n">
-        <v>5.3564133644104</v>
+        <v>5.35641384124756</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>7.95499992370605</v>
       </c>
       <c r="G1129" t="n">
-        <v>5.26377630233765</v>
+        <v>5.26377582550049</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>8.0649995803833</v>
       </c>
       <c r="G1130" t="n">
-        <v>5.33656215667725</v>
+        <v>5.3365626335144</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>8.15499973297119</v>
       </c>
       <c r="G1131" t="n">
-        <v>5.39611434936523</v>
+        <v>5.39611482620239</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G1132" t="n">
-        <v>5.41927433013916</v>
+        <v>5.41927337646484</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1133" t="n">
-        <v>5.41265773773193</v>
+        <v>5.41265726089478</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>8.19499969482422</v>
       </c>
       <c r="G1136" t="n">
-        <v>5.42258167266846</v>
+        <v>5.42258214950562</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1141" t="n">
-        <v>5.41265773773193</v>
+        <v>5.41265726089478</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>7.16499996185303</v>
       </c>
       <c r="G1145" t="n">
-        <v>5.32360601425171</v>
+        <v>5.32360649108887</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>7.7350001335144</v>
       </c>
       <c r="G1149" t="n">
-        <v>5.74711751937866</v>
+        <v>5.7471170425415</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>7.74499988555908</v>
       </c>
       <c r="G1150" t="n">
-        <v>5.75454664230347</v>
+        <v>5.75454711914062</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G1152" t="n">
-        <v>5.78798246383667</v>
+        <v>5.78798198699951</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>7.96500015258789</v>
       </c>
       <c r="G1155" t="n">
-        <v>5.91800737380981</v>
+        <v>5.91800785064697</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>7.7649998664856</v>
       </c>
       <c r="G1156" t="n">
-        <v>5.76940727233887</v>
+        <v>5.76940774917603</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G1157" t="n">
-        <v>5.7434024810791</v>
+        <v>5.74340200424194</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>7.42500019073486</v>
       </c>
       <c r="G1161" t="n">
-        <v>5.51678705215454</v>
+        <v>5.51678657531738</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1162" t="n">
-        <v>5.49821186065674</v>
+        <v>5.4982123374939</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>7.53499984741211</v>
       </c>
       <c r="G1163" t="n">
-        <v>5.59851741790771</v>
+        <v>5.59851694107056</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>7.35500001907349</v>
       </c>
       <c r="G1164" t="n">
-        <v>5.46477651596069</v>
+        <v>5.46477699279785</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>7.42500019073486</v>
       </c>
       <c r="G1168" t="n">
-        <v>5.51678705215454</v>
+        <v>5.51678657531738</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>7.16499996185303</v>
       </c>
       <c r="G1171" t="n">
-        <v>5.32360601425171</v>
+        <v>5.32360649108887</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G1173" t="n">
-        <v>5.16386127471924</v>
+        <v>5.16386079788208</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G1174" t="n">
-        <v>5.14157056808472</v>
+        <v>5.14157104492188</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G1175" t="n">
-        <v>5.07470083236694</v>
+        <v>5.0747013092041</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>6.82499980926514</v>
       </c>
       <c r="G1176" t="n">
-        <v>5.07098531723022</v>
+        <v>5.07098579406738</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1181" t="n">
-        <v>5.05241107940674</v>
+        <v>5.05241060256958</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G1182" t="n">
-        <v>4.96325063705444</v>
+        <v>4.96325016021729</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>6.63500022888184</v>
       </c>
       <c r="G1184" t="n">
-        <v>4.9298152923584</v>
+        <v>4.92981576919556</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>6.75</v>
       </c>
       <c r="G1185" t="n">
-        <v>5.01526069641113</v>
+        <v>5.01526117324829</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>6.57000017166138</v>
       </c>
       <c r="G1186" t="n">
-        <v>4.88152027130127</v>
+        <v>4.88152074813843</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G1191" t="n">
-        <v>4.97811031341553</v>
+        <v>4.97811079025269</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G1192" t="n">
-        <v>5.08956098556519</v>
+        <v>5.08956050872803</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G1193" t="n">
-        <v>5.10442066192627</v>
+        <v>5.10442113876343</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>6.7350001335144</v>
       </c>
       <c r="G1194" t="n">
-        <v>5.00411605834961</v>
+        <v>5.00411558151245</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>6.93499994277954</v>
       </c>
       <c r="G1196" t="n">
-        <v>5.1527156829834</v>
+        <v>5.15271615982056</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>6.93499994277954</v>
       </c>
       <c r="G1197" t="n">
-        <v>5.1527156829834</v>
+        <v>5.15271615982056</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G1198" t="n">
-        <v>5.22330188751221</v>
+        <v>5.22330141067505</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1200" t="n">
-        <v>5.27531099319458</v>
+        <v>5.27531147003174</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G1201" t="n">
-        <v>5.26788187026978</v>
+        <v>5.26788091659546</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>7.17500019073486</v>
       </c>
       <c r="G1204" t="n">
-        <v>5.33103609085083</v>
+        <v>5.33103656768799</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>7.21500015258789</v>
       </c>
       <c r="G1206" t="n">
-        <v>5.36075639724731</v>
+        <v>5.36075687408447</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>7.16499996185303</v>
       </c>
       <c r="G1207" t="n">
-        <v>5.32360601425171</v>
+        <v>5.32360649108887</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>7.21500015258789</v>
       </c>
       <c r="G1208" t="n">
-        <v>5.36075639724731</v>
+        <v>5.36075687408447</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1209" t="n">
-        <v>5.27531099319458</v>
+        <v>5.27531147003174</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G1211" t="n">
-        <v>5.24559116363525</v>
+        <v>5.24559164047241</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>7.10500001907349</v>
       </c>
       <c r="G1212" t="n">
-        <v>5.2790265083313</v>
+        <v>5.27902698516846</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>6.94500017166138</v>
       </c>
       <c r="G1213" t="n">
-        <v>5.16014575958252</v>
+        <v>5.16014623641968</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G1214" t="n">
-        <v>5.22330188751221</v>
+        <v>5.22330141067505</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G1216" t="n">
-        <v>5.12671136856079</v>
+        <v>5.12671089172363</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>6.82499980926514</v>
       </c>
       <c r="G1220" t="n">
-        <v>5.07098531723022</v>
+        <v>5.07098579406738</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>6.76999998092651</v>
       </c>
       <c r="G1227" t="n">
-        <v>5.03012084960938</v>
+        <v>5.03012037277222</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G1231" t="n">
-        <v>5.7062520980835</v>
+        <v>5.70625257492065</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G1234" t="n">
-        <v>5.54279136657715</v>
+        <v>5.54279232025146</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>7.375</v>
       </c>
       <c r="G1235" t="n">
-        <v>5.47963714599609</v>
+        <v>5.47963666915894</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G1239" t="n">
-        <v>5.25302171707153</v>
+        <v>5.25302124023438</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>6.53000020980835</v>
       </c>
       <c r="G1240" t="n">
-        <v>4.85180044174194</v>
+        <v>4.8518009185791</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G1242" t="n">
-        <v>4.79236030578613</v>
+        <v>4.79235982894897</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G1243" t="n">
-        <v>4.7254900932312</v>
+        <v>4.72548961639404</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>6.4850001335144</v>
       </c>
       <c r="G1244" t="n">
-        <v>4.81836605072021</v>
+        <v>4.81836557388306</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1245" t="n">
-        <v>4.60660982131958</v>
+        <v>4.60660934448242</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G1246" t="n">
-        <v>4.3688497543335</v>
+        <v>4.36884927749634</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G1248" t="n">
-        <v>4.53973960876465</v>
+        <v>4.53974008560181</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>6.25</v>
       </c>
       <c r="G1249" t="n">
-        <v>4.64375972747803</v>
+        <v>4.64376020431519</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G1251" t="n">
-        <v>4.53231000900269</v>
+        <v>4.53230953216553</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G1252" t="n">
-        <v>4.71805953979492</v>
+        <v>4.71806049346924</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>6.4850001335144</v>
       </c>
       <c r="G1255" t="n">
-        <v>4.81836605072021</v>
+        <v>4.81836557388306</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G1256" t="n">
-        <v>4.85923051834106</v>
+        <v>4.85923004150391</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>6.68499994277954</v>
       </c>
       <c r="G1262" t="n">
-        <v>4.96696519851685</v>
+        <v>4.966965675354</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>6.82499980926514</v>
       </c>
       <c r="G1263" t="n">
-        <v>5.07098531723022</v>
+        <v>5.07098579406738</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>6.82499980926514</v>
       </c>
       <c r="G1264" t="n">
-        <v>5.07098531723022</v>
+        <v>5.07098579406738</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>6.7350001335144</v>
       </c>
       <c r="G1265" t="n">
-        <v>5.00411605834961</v>
+        <v>5.00411558151245</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G1266" t="n">
-        <v>5.08213138580322</v>
+        <v>5.08213090896606</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>6.96500015258789</v>
       </c>
       <c r="G1267" t="n">
-        <v>5.17500638961792</v>
+        <v>5.17500591278076</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G1271" t="n">
-        <v>5.16386127471924</v>
+        <v>5.16386079788208</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>6.86499977111816</v>
       </c>
       <c r="G1273" t="n">
-        <v>5.10070562362671</v>
+        <v>5.10070610046387</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G1274" t="n">
-        <v>5.11185073852539</v>
+        <v>5.11185121536255</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>6.92500019073486</v>
       </c>
       <c r="G1275" t="n">
-        <v>5.14528608322144</v>
+        <v>5.14528656005859</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G1278" t="n">
-        <v>5.00894021987915</v>
+        <v>5.00894069671631</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>5.95499992370605</v>
       </c>
       <c r="G1282" t="n">
-        <v>4.90596055984497</v>
+        <v>4.90596103668213</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G1284" t="n">
-        <v>4.90184116363525</v>
+        <v>4.90184164047241</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G1285" t="n">
-        <v>4.95127201080322</v>
+        <v>4.95127248764038</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G1289" t="n">
-        <v>5.23961591720581</v>
+        <v>5.23961544036865</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>6.30499982833862</v>
       </c>
       <c r="G1291" t="n">
-        <v>5.19430446624756</v>
+        <v>5.1943039894104</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>6.40999984741211</v>
       </c>
       <c r="G1292" t="n">
-        <v>5.28080749511719</v>
+        <v>5.28080701828003</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>6.59499979019165</v>
       </c>
       <c r="G1293" t="n">
-        <v>5.43321704864502</v>
+        <v>5.43321752548218</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G1295" t="n">
-        <v>5.61858177185059</v>
+        <v>5.61858129501343</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G1296" t="n">
-        <v>5.70096588134766</v>
+        <v>5.7009654045105</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>7.34499979019165</v>
       </c>
       <c r="G1300" t="n">
-        <v>6.05109643936157</v>
+        <v>6.05109691619873</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G1303" t="n">
-        <v>6.08817005157471</v>
+        <v>6.08816957473755</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1310" t="n">
-        <v>5.93163967132568</v>
+        <v>5.93164014816284</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>7.31500005722046</v>
       </c>
       <c r="G1311" t="n">
-        <v>6.02638149261475</v>
+        <v>6.0263819694519</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1312" t="n">
-        <v>5.93163967132568</v>
+        <v>5.93164014816284</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G1315" t="n">
-        <v>5.470290184021</v>
+        <v>5.47029066085815</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G1316" t="n">
-        <v>5.470290184021</v>
+        <v>5.47029066085815</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>6.86499977111816</v>
       </c>
       <c r="G1317" t="n">
-        <v>5.65565395355225</v>
+        <v>5.65565347671509</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G1318" t="n">
-        <v>5.44557571411133</v>
+        <v>5.44557523727417</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>6.60500001907349</v>
       </c>
       <c r="G1320" t="n">
-        <v>5.44145584106445</v>
+        <v>5.44145631790161</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>6.60500001907349</v>
       </c>
       <c r="G1321" t="n">
-        <v>5.44145584106445</v>
+        <v>5.44145631790161</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>6.48999977111816</v>
       </c>
       <c r="G1322" t="n">
-        <v>5.34671449661255</v>
+        <v>5.34671401977539</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G1324" t="n">
-        <v>5.5032434463501</v>
+        <v>5.50324392318726</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G1325" t="n">
-        <v>5.5032434463501</v>
+        <v>5.50324392318726</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>6.58500003814697</v>
       </c>
       <c r="G1326" t="n">
-        <v>5.4249792098999</v>
+        <v>5.42497968673706</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>6.63500022888184</v>
       </c>
       <c r="G1327" t="n">
-        <v>5.46617078781128</v>
+        <v>5.4661717414856</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>6.41499996185303</v>
       </c>
       <c r="G1328" t="n">
-        <v>5.2849268913269</v>
+        <v>5.28492641448975</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G1329" t="n">
-        <v>5.25609254837036</v>
+        <v>5.2560920715332</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>6.30999994277954</v>
       </c>
       <c r="G1332" t="n">
-        <v>5.19842386245728</v>
+        <v>5.19842338562012</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>6.57000017166138</v>
       </c>
       <c r="G1334" t="n">
-        <v>5.41262197494507</v>
+        <v>5.41262245178223</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>6.55499982833862</v>
       </c>
       <c r="G1336" t="n">
-        <v>5.40026378631592</v>
+        <v>5.40026426315308</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>6.44500017166138</v>
       </c>
       <c r="G1337" t="n">
-        <v>5.30964231491089</v>
+        <v>5.30964136123657</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>6.16499996185303</v>
       </c>
       <c r="G1338" t="n">
-        <v>5.07896661758423</v>
+        <v>5.07896709442139</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G1339" t="n">
-        <v>5.04189348220825</v>
+        <v>5.04189395904541</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>6.42500019073486</v>
       </c>
       <c r="G1341" t="n">
-        <v>5.29316520690918</v>
+        <v>5.29316473007202</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G1342" t="n">
-        <v>5.2231388092041</v>
+        <v>5.22313833236694</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>6.63500022888184</v>
       </c>
       <c r="G1346" t="n">
-        <v>5.46617078781128</v>
+        <v>5.4661717414856</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G1348" t="n">
-        <v>5.63505840301514</v>
+        <v>5.63505792617798</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>6.86499977111816</v>
       </c>
       <c r="G1350" t="n">
-        <v>5.65565395355225</v>
+        <v>5.65565347671509</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G1354" t="n">
-        <v>5.70096588134766</v>
+        <v>5.7009654045105</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>6.9850001335144</v>
       </c>
       <c r="G1355" t="n">
-        <v>5.75451517105103</v>
+        <v>5.75451469421387</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>6.86499977111816</v>
       </c>
       <c r="G1356" t="n">
-        <v>5.65565395355225</v>
+        <v>5.65565347671509</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1360" t="n">
-        <v>5.84925603866577</v>
+        <v>5.84925651550293</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>6.9850001335144</v>
       </c>
       <c r="G1362" t="n">
-        <v>5.75451517105103</v>
+        <v>5.75451469421387</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1364" t="n">
-        <v>5.48472023010254</v>
+        <v>5.4847207069397</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1365" t="n">
-        <v>5.62401485443115</v>
+        <v>5.62401437759399</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G1367" t="n">
-        <v>5.54566144943237</v>
+        <v>5.54566097259521</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>6.31500005722046</v>
       </c>
       <c r="G1369" t="n">
-        <v>5.49777889251709</v>
+        <v>5.49777936935425</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>6.31500005722046</v>
       </c>
       <c r="G1371" t="n">
-        <v>5.49777889251709</v>
+        <v>5.49777936935425</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1373" t="n">
-        <v>5.48472023010254</v>
+        <v>5.4847207069397</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>6.07499980926514</v>
       </c>
       <c r="G1376" t="n">
-        <v>5.28883695602417</v>
+        <v>5.28883743286133</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G1377" t="n">
-        <v>5.43248510360718</v>
+        <v>5.43248462677002</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G1383" t="n">
-        <v>5.94613361358643</v>
+        <v>5.94613313674927</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>7.03499984741211</v>
       </c>
       <c r="G1385" t="n">
-        <v>6.12460422515869</v>
+        <v>6.12460374832153</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G1388" t="n">
-        <v>6.06801605224609</v>
+        <v>6.06801557540894</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>7.10500001907349</v>
       </c>
       <c r="G1389" t="n">
-        <v>6.18554544448853</v>
+        <v>6.18554592132568</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G1390" t="n">
-        <v>6.12025117874146</v>
+        <v>6.12025165557861</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G1391" t="n">
-        <v>5.8242506980896</v>
+        <v>5.82425117492676</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G1394" t="n">
-        <v>5.98095703125</v>
+        <v>5.98095655441284</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>7</v>
       </c>
       <c r="G1397" t="n">
-        <v>6.09413385391235</v>
+        <v>6.0941333770752</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G1399" t="n">
-        <v>5.88519239425659</v>
+        <v>5.88519191741943</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G1404" t="n">
-        <v>6.12025117874146</v>
+        <v>6.12025165557861</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36899,7 +36899,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G1405" t="n">
-        <v>6.06801605224609</v>
+        <v>6.06801557540894</v>
       </c>
       <c r="H1405" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G1406" t="n">
-        <v>6.00707483291626</v>
+        <v>6.0070743560791</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -36951,7 +36951,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G1407" t="n">
-        <v>6.11154556274414</v>
+        <v>6.11154508590698</v>
       </c>
       <c r="H1407" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G1408" t="n">
-        <v>6.13766384124756</v>
+        <v>6.13766288757324</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>7.125</v>
       </c>
       <c r="G1409" t="n">
-        <v>6.20295810699463</v>
+        <v>6.20295763015747</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>7.17500019073486</v>
       </c>
       <c r="G1410" t="n">
-        <v>6.24648714065552</v>
+        <v>6.24648761749268</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G1416" t="n">
-        <v>6.30307483673096</v>
+        <v>6.30307531356812</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>7.20499992370605</v>
       </c>
       <c r="G1420" t="n">
-        <v>6.27260446548462</v>
+        <v>6.27260494232178</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37315,7 +37315,7 @@
         <v>7.17500019073486</v>
       </c>
       <c r="G1421" t="n">
-        <v>6.24648714065552</v>
+        <v>6.24648761749268</v>
       </c>
       <c r="H1421" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>7.16499996185303</v>
       </c>
       <c r="G1427" t="n">
-        <v>6.23778104782104</v>
+        <v>6.2377815246582</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G1429" t="n">
-        <v>6.43366432189941</v>
+        <v>6.43366384506226</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>7.2649998664856</v>
       </c>
       <c r="G1430" t="n">
-        <v>6.32484006881714</v>
+        <v>6.3248405456543</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G1431" t="n">
-        <v>6.37272310256958</v>
+        <v>6.37272262573242</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>7.45499992370605</v>
       </c>
       <c r="G1434" t="n">
-        <v>6.49025201797485</v>
+        <v>6.49025249481201</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G1435" t="n">
-        <v>6.47719383239746</v>
+        <v>6.4771933555603</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G1436" t="n">
-        <v>6.49460554122925</v>
+        <v>6.49460506439209</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G1438" t="n">
-        <v>6.49460554122925</v>
+        <v>6.49460506439209</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>7.31500005722046</v>
       </c>
       <c r="G1440" t="n">
-        <v>6.36836957931519</v>
+        <v>6.36837005615234</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G1445" t="n">
-        <v>6.47719383239746</v>
+        <v>6.4771933555603</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>7.20499992370605</v>
       </c>
       <c r="G1447" t="n">
-        <v>6.27260446548462</v>
+        <v>6.27260494232178</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>7.41499996185303</v>
       </c>
       <c r="G1450" t="n">
-        <v>6.45542907714844</v>
+        <v>6.45542860031128</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G1451" t="n">
-        <v>6.47719383239746</v>
+        <v>6.4771933555603</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G1452" t="n">
-        <v>6.49460554122925</v>
+        <v>6.49460506439209</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G1453" t="n">
-        <v>6.49460554122925</v>
+        <v>6.49460506439209</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>7.45499992370605</v>
       </c>
       <c r="G1458" t="n">
-        <v>6.49025201797485</v>
+        <v>6.49025249481201</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G1465" t="n">
-        <v>7.25201940536499</v>
+        <v>7.25201892852783</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1466" t="n">
-        <v>7.31295967102051</v>
+        <v>7.31296014785767</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G1467" t="n">
-        <v>7.33037233352661</v>
+        <v>7.33037281036377</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>8.42500019073486</v>
       </c>
       <c r="G1468" t="n">
-        <v>7.33472490310669</v>
+        <v>7.33472585678101</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>8.44499969482422</v>
       </c>
       <c r="G1469" t="n">
-        <v>7.35213708877563</v>
+        <v>7.35213661193848</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1470" t="n">
-        <v>7.44354867935181</v>
+        <v>7.44354915618896</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G1474" t="n">
-        <v>7.35648918151855</v>
+        <v>7.35649013519287</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38745,7 +38745,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G1476" t="n">
-        <v>7.27813625335693</v>
+        <v>7.27813673019409</v>
       </c>
       <c r="H1476" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>8.61499977111816</v>
       </c>
       <c r="G1478" t="n">
-        <v>7.50013780593872</v>
+        <v>7.50013732910156</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>8.48499965667725</v>
       </c>
       <c r="G1479" t="n">
-        <v>7.38696002960205</v>
+        <v>7.38696098327637</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38927,7 +38927,7 @@
         <v>8.76500034332275</v>
       </c>
       <c r="G1483" t="n">
-        <v>7.63072538375854</v>
+        <v>7.63072633743286</v>
       </c>
       <c r="H1483" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>8.89000034332275</v>
       </c>
       <c r="G1486" t="n">
-        <v>7.73954916000366</v>
+        <v>7.73954963684082</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G1487" t="n">
-        <v>7.88755035400391</v>
+        <v>7.88755083084106</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G1489" t="n">
-        <v>8.35766887664795</v>
+        <v>8.35766983032227</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G1491" t="n">
-        <v>8.4621410369873</v>
+        <v>8.46214008331299</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G1493" t="n">
-        <v>8.32284641265869</v>
+        <v>8.32284545898438</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G1494" t="n">
-        <v>8.34896373748779</v>
+        <v>8.34896278381348</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G1495" t="n">
-        <v>8.35766887664795</v>
+        <v>8.35766983032227</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G1496" t="n">
-        <v>8.35766887664795</v>
+        <v>8.35766983032227</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1497" t="n">
-        <v>8.21837425231934</v>
+        <v>8.21837520599365</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G1498" t="n">
-        <v>8.25319766998291</v>
+        <v>8.25319862365723</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>9.36499977111816</v>
       </c>
       <c r="G1500" t="n">
-        <v>8.15307998657227</v>
+        <v>8.15308094024658</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>9.52499961853027</v>
       </c>
       <c r="G1502" t="n">
-        <v>8.29237365722656</v>
+        <v>8.29237461090088</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39473,7 +39473,7 @@
         <v>9.45499992370605</v>
       </c>
       <c r="G1504" t="n">
-        <v>8.23143291473389</v>
+        <v>8.2314338684082</v>
       </c>
       <c r="H1504" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G1505" t="n">
-        <v>8.29672718048096</v>
+        <v>8.29672813415527</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G1508" t="n">
-        <v>7.90496253967285</v>
+        <v>7.90496206283569</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>9.33500003814697</v>
       </c>
       <c r="G1509" t="n">
-        <v>8.12696266174316</v>
+        <v>8.12696361541748</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39655,7 +39655,7 @@
         <v>9.05500030517578</v>
       </c>
       <c r="G1511" t="n">
-        <v>7.88319778442383</v>
+        <v>7.88319730758667</v>
       </c>
       <c r="H1511" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>9.10499954223633</v>
       </c>
       <c r="G1513" t="n">
-        <v>7.92672634124756</v>
+        <v>7.92672681808472</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>9.45499992370605</v>
       </c>
       <c r="G1514" t="n">
-        <v>8.23143291473389</v>
+        <v>8.2314338684082</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>9.19499969482422</v>
       </c>
       <c r="G1515" t="n">
-        <v>8.0050802230835</v>
+        <v>8.00507926940918</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39811,7 +39811,7 @@
         <v>9.13000011444092</v>
       </c>
       <c r="G1517" t="n">
-        <v>7.9484920501709</v>
+        <v>7.94849157333374</v>
       </c>
       <c r="H1517" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>9.00500011444092</v>
       </c>
       <c r="G1519" t="n">
-        <v>7.83966827392578</v>
+        <v>7.83966875076294</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>9.0649995803833</v>
       </c>
       <c r="G1520" t="n">
-        <v>7.89190244674683</v>
+        <v>7.89190340042114</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G1521" t="n">
-        <v>8.0007266998291</v>
+        <v>8.00072574615479</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>9.15499973297119</v>
       </c>
       <c r="G1523" t="n">
-        <v>7.97025680541992</v>
+        <v>7.97025632858276</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>8.98999977111816</v>
       </c>
       <c r="G1524" t="n">
-        <v>7.82660818099976</v>
+        <v>7.82660913467407</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>9.32999992370605</v>
       </c>
       <c r="G1528" t="n">
-        <v>8.12260913848877</v>
+        <v>8.12261009216309</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40149,7 +40149,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G1530" t="n">
-        <v>8.09649181365967</v>
+        <v>8.09649276733398</v>
       </c>
       <c r="H1530" t="s">
         <v>8</v>
@@ -40201,7 +40201,7 @@
         <v>9.47000026702881</v>
       </c>
       <c r="G1532" t="n">
-        <v>8.24449348449707</v>
+        <v>8.24449253082275</v>
       </c>
       <c r="H1532" t="s">
         <v>8</v>
@@ -40279,7 +40279,7 @@
         <v>9.0649995803833</v>
       </c>
       <c r="G1535" t="n">
-        <v>7.89190244674683</v>
+        <v>7.89190340042114</v>
       </c>
       <c r="H1535" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>8.69499969482422</v>
       </c>
       <c r="G1536" t="n">
-        <v>7.93662929534912</v>
+        <v>7.93662881851196</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G1540" t="n">
-        <v>7.95944929122925</v>
+        <v>7.95944976806641</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>8.57499980926514</v>
       </c>
       <c r="G1543" t="n">
-        <v>7.82709503173828</v>
+        <v>7.8270959854126</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>8.61499977111816</v>
       </c>
       <c r="G1545" t="n">
-        <v>7.86360740661621</v>
+        <v>7.86360692977905</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40565,7 +40565,7 @@
         <v>8.69499969482422</v>
       </c>
       <c r="G1546" t="n">
-        <v>7.93662929534912</v>
+        <v>7.93662881851196</v>
       </c>
       <c r="H1546" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>8.54500007629395</v>
       </c>
       <c r="G1547" t="n">
-        <v>7.79971265792847</v>
+        <v>7.79971218109131</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>8.625</v>
       </c>
       <c r="G1549" t="n">
-        <v>7.87273454666138</v>
+        <v>7.87273502349854</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40669,7 +40669,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G1550" t="n">
-        <v>7.84078788757324</v>
+        <v>7.84078741073608</v>
       </c>
       <c r="H1550" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G1556" t="n">
-        <v>8.38845539093018</v>
+        <v>8.38845634460449</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40851,7 +40851,7 @@
         <v>9.15499973297119</v>
       </c>
       <c r="G1557" t="n">
-        <v>8.3565092086792</v>
+        <v>8.35650825500488</v>
       </c>
       <c r="H1557" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G1567" t="n">
-        <v>8.87223052978516</v>
+        <v>8.87222957611084</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41501,7 +41501,7 @@
         <v>9.78999996185303</v>
       </c>
       <c r="G1582" t="n">
-        <v>8.93612384796143</v>
+        <v>8.93612480163574</v>
       </c>
       <c r="H1582" t="s">
         <v>8</v>
@@ -41553,7 +41553,7 @@
         <v>10.0299997329712</v>
       </c>
       <c r="G1584" t="n">
-        <v>9.15519142150879</v>
+        <v>9.15519237518311</v>
       </c>
       <c r="H1584" t="s">
         <v>8</v>
@@ -41579,7 +41579,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G1585" t="n">
-        <v>9.03653049468994</v>
+        <v>9.03652954101562</v>
       </c>
       <c r="H1585" t="s">
         <v>8</v>
@@ -41631,7 +41631,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G1587" t="n">
-        <v>9.01827430725098</v>
+        <v>9.01827526092529</v>
       </c>
       <c r="H1587" t="s">
         <v>8</v>
@@ -41917,7 +41917,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G1598" t="n">
-        <v>9.29210948944092</v>
+        <v>9.2921085357666</v>
       </c>
       <c r="H1598" t="s">
         <v>8</v>
@@ -42021,7 +42021,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G1602" t="n">
-        <v>9.01827430725098</v>
+        <v>9.01827526092529</v>
       </c>
       <c r="H1602" t="s">
         <v>8</v>
@@ -42125,7 +42125,7 @@
         <v>10.1700000762939</v>
       </c>
       <c r="G1606" t="n">
-        <v>9.28298091888428</v>
+        <v>9.28298187255859</v>
       </c>
       <c r="H1606" t="s">
         <v>8</v>
@@ -42229,7 +42229,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1610" t="n">
-        <v>8.83571815490723</v>
+        <v>8.83571910858154</v>
       </c>
       <c r="H1610" t="s">
         <v>8</v>
@@ -42281,7 +42281,7 @@
         <v>9.5649995803833</v>
       </c>
       <c r="G1612" t="n">
-        <v>8.73074817657471</v>
+        <v>8.73074913024902</v>
       </c>
       <c r="H1612" t="s">
         <v>8</v>
@@ -42307,7 +42307,7 @@
         <v>9.6850004196167</v>
       </c>
       <c r="G1613" t="n">
-        <v>8.84028339385986</v>
+        <v>8.84028244018555</v>
       </c>
       <c r="H1613" t="s">
         <v>8</v>
@@ -42463,7 +42463,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G1619" t="n">
-        <v>8.80833435058594</v>
+        <v>8.80833530426025</v>
       </c>
       <c r="H1619" t="s">
         <v>8</v>
@@ -42541,7 +42541,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G1622" t="n">
-        <v>8.80833435058594</v>
+        <v>8.80833530426025</v>
       </c>
       <c r="H1622" t="s">
         <v>8</v>
@@ -42827,7 +42827,7 @@
         <v>9.6850004196167</v>
       </c>
       <c r="G1633" t="n">
-        <v>8.84028339385986</v>
+        <v>8.84028244018555</v>
       </c>
       <c r="H1633" t="s">
         <v>8</v>
@@ -63214,6 +63214,32 @@
         <v>2.07999992370605</v>
       </c>
       <c r="H2417" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2418">
+      <c r="A2418" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B2418" t="n">
+        <v>5220367</v>
+      </c>
+      <c r="C2418" t="n">
+        <v>2.30999994277954</v>
+      </c>
+      <c r="D2418" t="n">
+        <v>2.04399991035461</v>
+      </c>
+      <c r="E2418" t="n">
+        <v>2.04999995231628</v>
+      </c>
+      <c r="F2418" t="n">
+        <v>2.26999998092651</v>
+      </c>
+      <c r="G2418" t="n">
+        <v>2.26999998092651</v>
+      </c>
+      <c r="H2418" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/BFF.MI.xlsx
+++ b/data/BFF.MI.xlsx
@@ -421,7 +421,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G2" t="n">
-        <v>2.25471186637878</v>
+        <v>2.25471138954163</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>4.25</v>
       </c>
       <c r="G4" t="n">
-        <v>2.31461930274963</v>
+        <v>2.31461977958679</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G6" t="n">
-        <v>2.26015782356262</v>
+        <v>2.2601580619812</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>4.06599998474121</v>
       </c>
       <c r="G7" t="n">
-        <v>2.21441006660461</v>
+        <v>2.21440982818604</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G8" t="n">
-        <v>2.22203493118286</v>
+        <v>2.22203469276428</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G9" t="n">
-        <v>2.26015782356262</v>
+        <v>2.2601580619812</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G11" t="n">
-        <v>2.26560401916504</v>
+        <v>2.26560378074646</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G13" t="n">
-        <v>2.3418505191803</v>
+        <v>2.34185028076172</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>4.2979998588562</v>
       </c>
       <c r="G14" t="n">
-        <v>2.34076118469238</v>
+        <v>2.34076142311096</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G15" t="n">
-        <v>2.36363506317139</v>
+        <v>2.36363530158997</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G18" t="n">
-        <v>2.40720415115356</v>
+        <v>2.40720438957214</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>4.4520001411438</v>
       </c>
       <c r="G19" t="n">
-        <v>2.42463183403015</v>
+        <v>2.42463207244873</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>4.48600006103516</v>
       </c>
       <c r="G20" t="n">
-        <v>2.44314932823181</v>
+        <v>2.44314908981323</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G21" t="n">
-        <v>2.54335880279541</v>
+        <v>2.54335856437683</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>4.83599996566772</v>
       </c>
       <c r="G23" t="n">
-        <v>2.63376450538635</v>
+        <v>2.63376498222351</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>4.85400009155273</v>
       </c>
       <c r="G24" t="n">
-        <v>2.64356780052185</v>
+        <v>2.64356803894043</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>4.73799991607666</v>
       </c>
       <c r="G27" t="n">
-        <v>2.58039259910583</v>
+        <v>2.58039212226868</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>4.64200019836426</v>
       </c>
       <c r="G28" t="n">
-        <v>2.5281093120575</v>
+        <v>2.52810907363892</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>4.77600002288818</v>
       </c>
       <c r="G32" t="n">
-        <v>2.60108780860901</v>
+        <v>2.60108757019043</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>4.92399978637695</v>
       </c>
       <c r="G33" t="n">
-        <v>2.68169069290161</v>
+        <v>2.68169093132019</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G35" t="n">
-        <v>2.6849582195282</v>
+        <v>2.68495869636536</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G37" t="n">
-        <v>2.6849582195282</v>
+        <v>2.68495869636536</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>4.94799995422363</v>
       </c>
       <c r="G38" t="n">
-        <v>2.69476175308228</v>
+        <v>2.6947615146637</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>4.92199993133545</v>
       </c>
       <c r="G39" t="n">
-        <v>2.6806013584137</v>
+        <v>2.68060183525085</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>4.86800003051758</v>
       </c>
       <c r="G40" t="n">
-        <v>2.65119194984436</v>
+        <v>2.65119290351868</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G41" t="n">
-        <v>2.6413893699646</v>
+        <v>2.64138913154602</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G43" t="n">
-        <v>2.66862034797668</v>
+        <v>2.66862010955811</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>4.87599992752075</v>
       </c>
       <c r="G44" t="n">
-        <v>2.65554904937744</v>
+        <v>2.65554928779602</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>4.84600019454956</v>
       </c>
       <c r="G45" t="n">
-        <v>2.63921117782593</v>
+        <v>2.63921141624451</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>5.07499980926514</v>
       </c>
       <c r="G48" t="n">
-        <v>2.76392769813538</v>
+        <v>2.76392793655396</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G50" t="n">
-        <v>2.77754330635071</v>
+        <v>2.77754306793213</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G51" t="n">
-        <v>2.81022024154663</v>
+        <v>2.81022047996521</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G52" t="n">
-        <v>2.82111310958862</v>
+        <v>2.82111287117004</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>5</v>
       </c>
       <c r="G54" t="n">
-        <v>2.7230818271637</v>
+        <v>2.72308158874512</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G55" t="n">
-        <v>2.76120519638062</v>
+        <v>2.76120471954346</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G58" t="n">
-        <v>2.81022024154663</v>
+        <v>2.81022047996521</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>5</v>
       </c>
       <c r="G59" t="n">
-        <v>2.7230818271637</v>
+        <v>2.72308158874512</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>5.09499979019165</v>
       </c>
       <c r="G60" t="n">
-        <v>2.77481985092163</v>
+        <v>2.77482008934021</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G61" t="n">
-        <v>2.79932808876038</v>
+        <v>2.7993278503418</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G62" t="n">
-        <v>2.78298997879028</v>
+        <v>2.78298950195312</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G63" t="n">
-        <v>2.79932808876038</v>
+        <v>2.7993278503418</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>5.16499996185303</v>
       </c>
       <c r="G64" t="n">
-        <v>2.81294274330139</v>
+        <v>2.81294345855713</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G65" t="n">
-        <v>2.79388213157654</v>
+        <v>2.79388189315796</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>5.07499980926514</v>
       </c>
       <c r="G66" t="n">
-        <v>2.76392769813538</v>
+        <v>2.76392793655396</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>5.125</v>
       </c>
       <c r="G67" t="n">
-        <v>2.79115843772888</v>
+        <v>2.79115867614746</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G70" t="n">
-        <v>2.80477428436279</v>
+        <v>2.80477452278137</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>5.07499980926514</v>
       </c>
       <c r="G71" t="n">
-        <v>2.76392769813538</v>
+        <v>2.76392793655396</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G75" t="n">
-        <v>2.80477428436279</v>
+        <v>2.80477452278137</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>5.125</v>
       </c>
       <c r="G76" t="n">
-        <v>2.79115843772888</v>
+        <v>2.79115867614746</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G80" t="n">
-        <v>2.82111310958862</v>
+        <v>2.82111287117004</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G81" t="n">
-        <v>2.80477428436279</v>
+        <v>2.80477452278137</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G82" t="n">
-        <v>2.80477428436279</v>
+        <v>2.80477452278137</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G83" t="n">
-        <v>2.80477428436279</v>
+        <v>2.80477452278137</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G84" t="n">
-        <v>2.79932808876038</v>
+        <v>2.7993278503418</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G86" t="n">
-        <v>2.80477428436279</v>
+        <v>2.80477452278137</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G87" t="n">
-        <v>2.79388213157654</v>
+        <v>2.79388189315796</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>5.13500022888184</v>
       </c>
       <c r="G88" t="n">
-        <v>2.79660534858704</v>
+        <v>2.79660487174988</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G91" t="n">
-        <v>2.83745098114014</v>
+        <v>2.83745121955872</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G95" t="n">
-        <v>2.79932808876038</v>
+        <v>2.7993278503418</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>5.16499996185303</v>
       </c>
       <c r="G96" t="n">
-        <v>2.81294274330139</v>
+        <v>2.81294345855713</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G98" t="n">
-        <v>2.79932808876038</v>
+        <v>2.7993278503418</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>4.9520001411438</v>
       </c>
       <c r="G100" t="n">
-        <v>2.69694042205811</v>
+        <v>2.69693994522095</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G101" t="n">
-        <v>2.69585084915161</v>
+        <v>2.69585061073303</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G103" t="n">
-        <v>2.73942017555237</v>
+        <v>2.73942041397095</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G104" t="n">
-        <v>2.81022024154663</v>
+        <v>2.81022047996521</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G105" t="n">
-        <v>2.77754330635071</v>
+        <v>2.77754306793213</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G108" t="n">
-        <v>2.76665091514587</v>
+        <v>2.76665115356445</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>5.16499996185303</v>
       </c>
       <c r="G110" t="n">
-        <v>2.81294274330139</v>
+        <v>2.81294345855713</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G111" t="n">
-        <v>2.84834384918213</v>
+        <v>2.84834361076355</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G113" t="n">
-        <v>2.86468195915222</v>
+        <v>2.86468172073364</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>5.50500011444092</v>
       </c>
       <c r="G114" t="n">
-        <v>2.99811315536499</v>
+        <v>2.99811291694641</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>5.49499988555908</v>
       </c>
       <c r="G115" t="n">
-        <v>2.99266695976257</v>
+        <v>2.99266672134399</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G116" t="n">
-        <v>3.02806663513184</v>
+        <v>3.02806711196899</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G117" t="n">
-        <v>3.03895950317383</v>
+        <v>3.03895926475525</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G118" t="n">
-        <v>3.00628232955933</v>
+        <v>3.00628256797791</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G119" t="n">
-        <v>3.08797454833984</v>
+        <v>3.08797478675842</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>5.67500019073486</v>
       </c>
       <c r="G120" t="n">
-        <v>3.0906982421875</v>
+        <v>3.09069776535034</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G122" t="n">
-        <v>3.2132363319397</v>
+        <v>3.21323657035828</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>5.75</v>
       </c>
       <c r="G123" t="n">
-        <v>3.1315438747406</v>
+        <v>3.13154411315918</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G126" t="n">
-        <v>3.07708263397217</v>
+        <v>3.07708287239075</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G127" t="n">
-        <v>3.14243650436401</v>
+        <v>3.14243674278259</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G130" t="n">
-        <v>3.15877461433411</v>
+        <v>3.15877485275269</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>5.875</v>
       </c>
       <c r="G132" t="n">
-        <v>3.19962120056152</v>
+        <v>3.19962072372437</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G133" t="n">
-        <v>3.32215929031372</v>
+        <v>3.32215976715088</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>6.125</v>
       </c>
       <c r="G134" t="n">
-        <v>3.33577489852905</v>
+        <v>3.33577537536621</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G135" t="n">
-        <v>3.30582165718079</v>
+        <v>3.30582141876221</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>6.11499977111816</v>
       </c>
       <c r="G136" t="n">
-        <v>3.33032870292664</v>
+        <v>3.33032917976379</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>6</v>
       </c>
       <c r="G138" t="n">
-        <v>3.26769804954529</v>
+        <v>3.26769828796387</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>6.11499977111816</v>
       </c>
       <c r="G139" t="n">
-        <v>3.33032870292664</v>
+        <v>3.33032917976379</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G141" t="n">
-        <v>3.32215929031372</v>
+        <v>3.32215976715088</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G142" t="n">
-        <v>3.34939050674438</v>
+        <v>3.34939098358154</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G143" t="n">
-        <v>3.39295983314514</v>
+        <v>3.39296007156372</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G144" t="n">
-        <v>3.3875138759613</v>
+        <v>3.38751339912415</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>6.25</v>
       </c>
       <c r="G145" t="n">
-        <v>3.40385246276855</v>
+        <v>3.4038519859314</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G146" t="n">
-        <v>3.38206744194031</v>
+        <v>3.38206720352173</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>6.11499977111816</v>
       </c>
       <c r="G147" t="n">
-        <v>3.33032870292664</v>
+        <v>3.33032917976379</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>6.02500009536743</v>
       </c>
       <c r="G148" t="n">
-        <v>3.28131365776062</v>
+        <v>3.28131341934204</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>6.00500011444092</v>
       </c>
       <c r="G149" t="n">
-        <v>3.27042126655579</v>
+        <v>3.27042150497437</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>6.09499979019165</v>
       </c>
       <c r="G150" t="n">
-        <v>3.31943655014038</v>
+        <v>3.31943607330322</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G151" t="n">
-        <v>3.28403663635254</v>
+        <v>3.2840371131897</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>5.92999982833862</v>
       </c>
       <c r="G154" t="n">
-        <v>3.22957539558411</v>
+        <v>3.22957444190979</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G155" t="n">
-        <v>3.2132363319397</v>
+        <v>3.21323657035828</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G156" t="n">
-        <v>3.27314472198486</v>
+        <v>3.27314448356628</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>6</v>
       </c>
       <c r="G157" t="n">
-        <v>3.26769804954529</v>
+        <v>3.26769828796387</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G158" t="n">
-        <v>3.32760620117188</v>
+        <v>3.3276059627533</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>6.125</v>
       </c>
       <c r="G159" t="n">
-        <v>3.33577489852905</v>
+        <v>3.33577537536621</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G161" t="n">
-        <v>3.38206744194031</v>
+        <v>3.38206720352173</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>6.40999984741211</v>
       </c>
       <c r="G162" t="n">
-        <v>3.49099040031433</v>
+        <v>3.49099063873291</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G163" t="n">
-        <v>3.51277542114258</v>
+        <v>3.512775182724</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G164" t="n">
-        <v>3.47465229034424</v>
+        <v>3.4746527671814</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G165" t="n">
-        <v>3.45831418037415</v>
+        <v>3.45831370353699</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>6.36499977111816</v>
       </c>
       <c r="G168" t="n">
-        <v>3.46648263931274</v>
+        <v>3.46648335456848</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G169" t="n">
-        <v>3.50732922554016</v>
+        <v>3.50732970237732</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G170" t="n">
-        <v>3.50732922554016</v>
+        <v>3.50732970237732</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>6.40999984741211</v>
       </c>
       <c r="G171" t="n">
-        <v>3.49099040031433</v>
+        <v>3.49099063873291</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G172" t="n">
-        <v>3.58357548713684</v>
+        <v>3.58357572555542</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G175" t="n">
-        <v>3.59446811676025</v>
+        <v>3.59446692466736</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>6.53499984741211</v>
       </c>
       <c r="G178" t="n">
-        <v>3.55906748771667</v>
+        <v>3.55906796455383</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>6.375</v>
       </c>
       <c r="G181" t="n">
-        <v>3.47192883491516</v>
+        <v>3.4719295501709</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G182" t="n">
-        <v>3.47465229034424</v>
+        <v>3.4746527671814</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>6.25</v>
       </c>
       <c r="G183" t="n">
-        <v>3.40385246276855</v>
+        <v>3.4038519859314</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>6.38500022888184</v>
       </c>
       <c r="G185" t="n">
-        <v>3.47737550735474</v>
+        <v>3.47737574577332</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G186" t="n">
-        <v>3.48554491996765</v>
+        <v>3.48554444313049</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>6.53499984741211</v>
       </c>
       <c r="G188" t="n">
-        <v>3.55906748771667</v>
+        <v>3.55906796455383</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>6.43499994277954</v>
       </c>
       <c r="G192" t="n">
-        <v>3.50460624694824</v>
+        <v>3.50460600852966</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G194" t="n">
-        <v>3.47465229034424</v>
+        <v>3.4746527671814</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>6.46500015258789</v>
       </c>
       <c r="G195" t="n">
-        <v>3.52094483375549</v>
+        <v>3.52094507217407</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G196" t="n">
-        <v>3.52911424636841</v>
+        <v>3.52911400794983</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>6.57499980926514</v>
       </c>
       <c r="G201" t="n">
-        <v>3.5808527469635</v>
+        <v>3.58085250854492</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G202" t="n">
-        <v>3.58902192115784</v>
+        <v>3.58902168273926</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G203" t="n">
-        <v>3.59446811676025</v>
+        <v>3.59446692466736</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>6.59499979019165</v>
       </c>
       <c r="G205" t="n">
-        <v>3.59174418449402</v>
+        <v>3.59174466133118</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G206" t="n">
-        <v>3.59991431236267</v>
+        <v>3.59991407394409</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>6.4850001335144</v>
       </c>
       <c r="G208" t="n">
-        <v>3.53183722496033</v>
+        <v>3.53183674812317</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G210" t="n">
-        <v>3.29492950439453</v>
+        <v>3.29492855072021</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G211" t="n">
-        <v>3.28403663635254</v>
+        <v>3.2840371131897</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G213" t="n">
-        <v>3.27859020233154</v>
+        <v>3.2785906791687</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G214" t="n">
-        <v>3.12065172195435</v>
+        <v>3.12065148353577</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>5.92999982833862</v>
       </c>
       <c r="G215" t="n">
-        <v>3.22957539558411</v>
+        <v>3.22957444190979</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G216" t="n">
-        <v>3.16966772079468</v>
+        <v>3.1696674823761</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>5.93499994277954</v>
       </c>
       <c r="G218" t="n">
-        <v>3.23229813575745</v>
+        <v>3.23229765892029</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>6</v>
       </c>
       <c r="G219" t="n">
-        <v>3.26769804954529</v>
+        <v>3.26769828796387</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G220" t="n">
-        <v>3.38206744194031</v>
+        <v>3.38206720352173</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>6.14499998092651</v>
       </c>
       <c r="G221" t="n">
-        <v>3.34666752815247</v>
+        <v>3.34666776657104</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>6.16499996185303</v>
       </c>
       <c r="G222" t="n">
-        <v>3.3575599193573</v>
+        <v>3.35755920410156</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G223" t="n">
-        <v>3.2132363319397</v>
+        <v>3.21323657035828</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G225" t="n">
-        <v>3.16966772079468</v>
+        <v>3.1696674823761</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G226" t="n">
-        <v>3.16966772079468</v>
+        <v>3.1696674823761</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G228" t="n">
-        <v>3.18600535392761</v>
+        <v>3.18600583076477</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G229" t="n">
-        <v>3.18600535392761</v>
+        <v>3.18600583076477</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G230" t="n">
-        <v>3.17511320114136</v>
+        <v>3.17511343955994</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G232" t="n">
-        <v>3.15877461433411</v>
+        <v>3.15877485275269</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G233" t="n">
-        <v>3.15332841873169</v>
+        <v>3.15332865715027</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>5.75</v>
       </c>
       <c r="G242" t="n">
-        <v>3.1315438747406</v>
+        <v>3.13154411315918</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>5.7350001335144</v>
       </c>
       <c r="G243" t="n">
-        <v>3.12337517738342</v>
+        <v>3.12337493896484</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>5.71500015258789</v>
       </c>
       <c r="G244" t="n">
-        <v>3.11248254776001</v>
+        <v>3.11248230934143</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G245" t="n">
-        <v>3.08797454833984</v>
+        <v>3.08797478675842</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G246" t="n">
-        <v>3.09342098236084</v>
+        <v>3.09342074394226</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G248" t="n">
-        <v>3.18600535392761</v>
+        <v>3.18600583076477</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G250" t="n">
-        <v>3.2132363319397</v>
+        <v>3.21323657035828</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G251" t="n">
-        <v>3.18600535392761</v>
+        <v>3.18600583076477</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G252" t="n">
-        <v>3.20779037475586</v>
+        <v>3.2077898979187</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G255" t="n">
-        <v>3.26296710968018</v>
+        <v>3.26296758651733</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>5.32499980926514</v>
       </c>
       <c r="G256" t="n">
-        <v>3.16490030288696</v>
+        <v>3.16490006446838</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G258" t="n">
-        <v>3.24513721466064</v>
+        <v>3.24513697624207</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G259" t="n">
-        <v>3.21542000770569</v>
+        <v>3.21541976928711</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G260" t="n">
-        <v>3.15598511695862</v>
+        <v>3.1559853553772</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G261" t="n">
-        <v>3.20947599411011</v>
+        <v>3.20947647094727</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>5.41499996185303</v>
       </c>
       <c r="G262" t="n">
-        <v>3.21839141845703</v>
+        <v>3.21839165687561</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>5.36499977111816</v>
       </c>
       <c r="G264" t="n">
-        <v>3.18867421150208</v>
+        <v>3.18867373466492</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>5.25500011444092</v>
       </c>
       <c r="G265" t="n">
-        <v>3.12329578399658</v>
+        <v>3.12329602241516</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G266" t="n">
-        <v>3.06386137008667</v>
+        <v>3.06386113166809</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>5.25500011444092</v>
       </c>
       <c r="G272" t="n">
-        <v>3.12329578399658</v>
+        <v>3.12329602241516</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G273" t="n">
-        <v>3.07872009277344</v>
+        <v>3.07871985435486</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G275" t="n">
-        <v>3.07277631759644</v>
+        <v>3.07277655601501</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>5.02500009536743</v>
       </c>
       <c r="G276" t="n">
-        <v>2.98659610748291</v>
+        <v>2.98659586906433</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G277" t="n">
-        <v>3.0073983669281</v>
+        <v>3.00739812850952</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>5.22499990463257</v>
       </c>
       <c r="G278" t="n">
-        <v>3.10546541213989</v>
+        <v>3.10546565055847</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>4.96600008010864</v>
       </c>
       <c r="G280" t="n">
-        <v>2.95152974128723</v>
+        <v>2.95152950286865</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G281" t="n">
-        <v>3.0430588722229</v>
+        <v>3.04305863380432</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G282" t="n">
-        <v>3.05494570732117</v>
+        <v>3.05494594573975</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>5.07499980926514</v>
       </c>
       <c r="G283" t="n">
-        <v>3.01631307601929</v>
+        <v>3.01631331443787</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G285" t="n">
-        <v>2.98362421989441</v>
+        <v>2.98362398147583</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G287" t="n">
-        <v>3.06386137008667</v>
+        <v>3.06386113166809</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>4.89200019836426</v>
       </c>
       <c r="G289" t="n">
-        <v>2.90754818916321</v>
+        <v>2.90754795074463</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>5.07499980926514</v>
       </c>
       <c r="G290" t="n">
-        <v>3.01631307601929</v>
+        <v>3.01631331443787</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>5.07499980926514</v>
       </c>
       <c r="G291" t="n">
-        <v>3.01631307601929</v>
+        <v>3.01631331443787</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G292" t="n">
-        <v>3.05791783332825</v>
+        <v>3.05791759490967</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G293" t="n">
-        <v>3.09060668945312</v>
+        <v>3.09060716629028</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G294" t="n">
-        <v>3.06683254241943</v>
+        <v>3.06683301925659</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>5.11499977111816</v>
       </c>
       <c r="G295" t="n">
-        <v>3.04008722305298</v>
+        <v>3.04008746147156</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G299" t="n">
-        <v>3.11438059806824</v>
+        <v>3.11438035964966</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G300" t="n">
-        <v>3.09060668945312</v>
+        <v>3.09060716629028</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>5.29500007629395</v>
       </c>
       <c r="G301" t="n">
-        <v>3.14706945419312</v>
+        <v>3.14706969261169</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G303" t="n">
-        <v>3.15598511695862</v>
+        <v>3.1559853553772</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G304" t="n">
-        <v>3.20353245735168</v>
+        <v>3.20353293418884</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G305" t="n">
-        <v>3.14409828186035</v>
+        <v>3.14409804344177</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>5.34499979019165</v>
       </c>
       <c r="G306" t="n">
-        <v>3.17678713798523</v>
+        <v>3.17678689956665</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>5.13500022888184</v>
       </c>
       <c r="G307" t="n">
-        <v>3.0519745349884</v>
+        <v>3.05197429656982</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G309" t="n">
-        <v>3.0133421421051</v>
+        <v>3.01334166526794</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>4.95599985122681</v>
       </c>
       <c r="G310" t="n">
-        <v>2.94558596611023</v>
+        <v>2.94558572769165</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>4.9539999961853</v>
       </c>
       <c r="G311" t="n">
-        <v>2.94439768791199</v>
+        <v>2.94439744949341</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G312" t="n">
-        <v>2.98362421989441</v>
+        <v>2.98362398147583</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>5</v>
       </c>
       <c r="G313" t="n">
-        <v>2.97173762321472</v>
+        <v>2.97173738479614</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>5.02500009536743</v>
       </c>
       <c r="G314" t="n">
-        <v>2.98659610748291</v>
+        <v>2.98659586906433</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G317" t="n">
-        <v>2.98956775665283</v>
+        <v>2.98956823348999</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G318" t="n">
-        <v>3.05791783332825</v>
+        <v>3.05791759490967</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G319" t="n">
-        <v>3.07277631759644</v>
+        <v>3.07277655601501</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G320" t="n">
-        <v>3.0430588722229</v>
+        <v>3.04305863380432</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G321" t="n">
-        <v>3.02522897720337</v>
+        <v>3.02522873878479</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>5.13500022888184</v>
       </c>
       <c r="G322" t="n">
-        <v>3.0519745349884</v>
+        <v>3.05197429656982</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G323" t="n">
-        <v>3.06683254241943</v>
+        <v>3.06683301925659</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G325" t="n">
-        <v>3.1262674331665</v>
+        <v>3.12626767158508</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>5.2350001335144</v>
       </c>
       <c r="G326" t="n">
-        <v>3.11140942573547</v>
+        <v>3.11140918731689</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G327" t="n">
-        <v>3.1262674331665</v>
+        <v>3.12626767158508</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G328" t="n">
-        <v>3.08466362953186</v>
+        <v>3.08466339111328</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G330" t="n">
-        <v>3.09060668945312</v>
+        <v>3.09060716629028</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>5.29500007629395</v>
       </c>
       <c r="G332" t="n">
-        <v>3.14706945419312</v>
+        <v>3.14706969261169</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>5.34499979019165</v>
       </c>
       <c r="G334" t="n">
-        <v>3.17678713798523</v>
+        <v>3.17678689956665</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>5.33500003814697</v>
       </c>
       <c r="G335" t="n">
-        <v>3.17084360122681</v>
+        <v>3.17084383964539</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G336" t="n">
-        <v>3.15004181861877</v>
+        <v>3.1500415802002</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>5.28499984741211</v>
       </c>
       <c r="G337" t="n">
-        <v>3.14112687110901</v>
+        <v>3.14112663269043</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>5.17500019073486</v>
       </c>
       <c r="G338" t="n">
-        <v>3.07574844360352</v>
+        <v>3.07574820518494</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G340" t="n">
-        <v>3.20947599411011</v>
+        <v>3.20947647094727</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>5.44500017166138</v>
       </c>
       <c r="G341" t="n">
-        <v>3.23622179031372</v>
+        <v>3.23622226715088</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G344" t="n">
-        <v>3.16192889213562</v>
+        <v>3.16192865371704</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G345" t="n">
-        <v>3.10249376296997</v>
+        <v>3.10249328613281</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G346" t="n">
-        <v>3.04900288581848</v>
+        <v>3.0490026473999</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G347" t="n">
-        <v>3.05791783332825</v>
+        <v>3.05791759490967</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G348" t="n">
-        <v>3.08466362953186</v>
+        <v>3.08466339111328</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G349" t="n">
-        <v>3.06683254241943</v>
+        <v>3.06683301925659</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G350" t="n">
-        <v>3.05494570732117</v>
+        <v>3.05494594573975</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>5.21500015258789</v>
       </c>
       <c r="G352" t="n">
-        <v>3.09952163696289</v>
+        <v>3.09952235221863</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>5.17500019073486</v>
       </c>
       <c r="G353" t="n">
-        <v>3.07574844360352</v>
+        <v>3.07574820518494</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>5.16499996185303</v>
       </c>
       <c r="G354" t="n">
-        <v>3.06980443000793</v>
+        <v>3.06980466842651</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G355" t="n">
-        <v>3.07277631759644</v>
+        <v>3.07277655601501</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G357" t="n">
-        <v>3.05791783332825</v>
+        <v>3.05791759490967</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>5.125</v>
       </c>
       <c r="G358" t="n">
-        <v>3.04603052139282</v>
+        <v>3.0460307598114</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G359" t="n">
-        <v>3.07277631759644</v>
+        <v>3.07277655601501</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>5.13500022888184</v>
       </c>
       <c r="G360" t="n">
-        <v>3.0519745349884</v>
+        <v>3.05197429656982</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>5.13500022888184</v>
       </c>
       <c r="G361" t="n">
-        <v>3.0519745349884</v>
+        <v>3.05197429656982</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G362" t="n">
-        <v>3.06683254241943</v>
+        <v>3.06683301925659</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G363" t="n">
-        <v>3.05494570732117</v>
+        <v>3.05494594573975</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G364" t="n">
-        <v>3.05791783332825</v>
+        <v>3.05791759490967</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>5.13500022888184</v>
       </c>
       <c r="G365" t="n">
-        <v>3.0519745349884</v>
+        <v>3.05197429656982</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G366" t="n">
-        <v>3.05494570732117</v>
+        <v>3.05494594573975</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>5.125</v>
       </c>
       <c r="G367" t="n">
-        <v>3.04603052139282</v>
+        <v>3.0460307598114</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G369" t="n">
-        <v>3.09060668945312</v>
+        <v>3.09060716629028</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G370" t="n">
-        <v>3.11438059806824</v>
+        <v>3.11438035964966</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G371" t="n">
-        <v>3.15598511695862</v>
+        <v>3.1559853553772</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G373" t="n">
-        <v>3.07277631759644</v>
+        <v>3.07277655601501</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>5.25500011444092</v>
       </c>
       <c r="G375" t="n">
-        <v>3.12329578399658</v>
+        <v>3.12329602241516</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G376" t="n">
-        <v>3.06683254241943</v>
+        <v>3.06683301925659</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>5.09499979019165</v>
       </c>
       <c r="G377" t="n">
-        <v>3.02820014953613</v>
+        <v>3.02820038795471</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>5.09499979019165</v>
       </c>
       <c r="G378" t="n">
-        <v>3.02820014953613</v>
+        <v>3.02820038795471</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G379" t="n">
-        <v>3.04900288581848</v>
+        <v>3.0490026473999</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G380" t="n">
-        <v>3.0430588722229</v>
+        <v>3.04305863380432</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>4.98799991607666</v>
       </c>
       <c r="G381" t="n">
-        <v>2.96460509300232</v>
+        <v>2.9646053314209</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G382" t="n">
-        <v>2.81720662117004</v>
+        <v>2.81720685958862</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G383" t="n">
-        <v>2.79937648773193</v>
+        <v>2.79937672615051</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G384" t="n">
-        <v>2.7696590423584</v>
+        <v>2.76965928077698</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>4.71799993515015</v>
       </c>
       <c r="G385" t="n">
-        <v>2.80413103103638</v>
+        <v>2.80413174629211</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G386" t="n">
-        <v>2.78748965263367</v>
+        <v>2.78748989105225</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>4.68400001525879</v>
       </c>
       <c r="G387" t="n">
-        <v>2.78392386436462</v>
+        <v>2.78392362594604</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G388" t="n">
-        <v>2.858811378479</v>
+        <v>2.85881114006042</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>4.71400022506714</v>
       </c>
       <c r="G389" t="n">
-        <v>2.80175399780273</v>
+        <v>2.80175423622131</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G390" t="n">
-        <v>2.80532002449036</v>
+        <v>2.80531978607178</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>4.59600019454956</v>
       </c>
       <c r="G391" t="n">
-        <v>2.7316210269928</v>
+        <v>2.73162078857422</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>4.33599996566772</v>
       </c>
       <c r="G394" t="n">
-        <v>2.57709050178528</v>
+        <v>2.57709074020386</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>4.30600023269653</v>
       </c>
       <c r="G396" t="n">
-        <v>2.55926060676575</v>
+        <v>2.55926036834717</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>4.49599981307983</v>
       </c>
       <c r="G398" t="n">
-        <v>2.67218613624573</v>
+        <v>2.67218637466431</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G399" t="n">
-        <v>2.70428109169006</v>
+        <v>2.70428133010864</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G400" t="n">
-        <v>2.70428109169006</v>
+        <v>2.70428133010864</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G402" t="n">
-        <v>2.71022415161133</v>
+        <v>2.71022439002991</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>4.73600006103516</v>
       </c>
       <c r="G404" t="n">
-        <v>2.81482982635498</v>
+        <v>2.8148295879364</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>4.61399984359741</v>
       </c>
       <c r="G405" t="n">
-        <v>2.74231910705566</v>
+        <v>2.74231886863708</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>4.61199998855591</v>
       </c>
       <c r="G406" t="n">
-        <v>2.74113082885742</v>
+        <v>2.74113059043884</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>4.70599985122681</v>
       </c>
       <c r="G408" t="n">
-        <v>2.79699897766113</v>
+        <v>2.79699945449829</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>4.57600021362305</v>
       </c>
       <c r="G409" t="n">
-        <v>2.71973443031311</v>
+        <v>2.71973395347595</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>4.57600021362305</v>
       </c>
       <c r="G410" t="n">
-        <v>2.71973443031311</v>
+        <v>2.71973395347595</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>4.51599979400635</v>
       </c>
       <c r="G411" t="n">
-        <v>2.68407297134399</v>
+        <v>2.68407320976257</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G412" t="n">
-        <v>2.71022415161133</v>
+        <v>2.71022439002991</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G414" t="n">
-        <v>2.70428109169006</v>
+        <v>2.70428133010864</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>4.56599998474121</v>
       </c>
       <c r="G416" t="n">
-        <v>2.71379041671753</v>
+        <v>2.71379065513611</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G417" t="n">
-        <v>2.79343295097351</v>
+        <v>2.79343318939209</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>4.67199993133545</v>
       </c>
       <c r="G418" t="n">
-        <v>2.7767915725708</v>
+        <v>2.77679109573364</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>4.6560001373291</v>
       </c>
       <c r="G423" t="n">
-        <v>2.76728200912476</v>
+        <v>2.76728177070618</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>4.55600023269653</v>
       </c>
       <c r="G426" t="n">
-        <v>2.70784687995911</v>
+        <v>2.70784735679626</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>4.50799989700317</v>
       </c>
       <c r="G427" t="n">
-        <v>2.67931842803955</v>
+        <v>2.67931866645813</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>4.57399988174438</v>
       </c>
       <c r="G429" t="n">
-        <v>2.71854543685913</v>
+        <v>2.71854519844055</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>4.61800003051758</v>
       </c>
       <c r="G430" t="n">
-        <v>2.74469685554504</v>
+        <v>2.74469661712646</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>4.53399991989136</v>
       </c>
       <c r="G431" t="n">
-        <v>2.69477152824402</v>
+        <v>2.6947717666626</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G432" t="n">
-        <v>2.65673279762268</v>
+        <v>2.65673303604126</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>4.48199987411499</v>
       </c>
       <c r="G433" t="n">
-        <v>2.66386556625366</v>
+        <v>2.66386532783508</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>4.50400018692017</v>
       </c>
       <c r="G435" t="n">
-        <v>2.67694091796875</v>
+        <v>2.67694139480591</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>4.49599981307983</v>
       </c>
       <c r="G436" t="n">
-        <v>2.67218613624573</v>
+        <v>2.67218637466431</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>4.72800016403198</v>
       </c>
       <c r="G440" t="n">
-        <v>2.81007504463196</v>
+        <v>2.81007480621338</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G441" t="n">
-        <v>2.86475515365601</v>
+        <v>2.86475491523743</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>4.90199995040894</v>
       </c>
       <c r="G442" t="n">
-        <v>2.91349148750305</v>
+        <v>2.91349124908447</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>4.85599994659424</v>
       </c>
       <c r="G444" t="n">
-        <v>2.88615155220032</v>
+        <v>2.88615131378174</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>4.73199987411499</v>
       </c>
       <c r="G447" t="n">
-        <v>2.8124520778656</v>
+        <v>2.81245231628418</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>4.76800012588501</v>
       </c>
       <c r="G448" t="n">
-        <v>2.83384871482849</v>
+        <v>2.83384895324707</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>4.81199979782104</v>
       </c>
       <c r="G449" t="n">
-        <v>2.85999989509583</v>
+        <v>2.8600001335144</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>4.77400016784668</v>
       </c>
       <c r="G450" t="n">
-        <v>2.83741521835327</v>
+        <v>2.83741474151611</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G451" t="n">
-        <v>2.89447212219238</v>
+        <v>2.89447236061096</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>4.86199998855591</v>
       </c>
       <c r="G454" t="n">
-        <v>2.88971710205078</v>
+        <v>2.88971757888794</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>4.92600011825562</v>
       </c>
       <c r="G457" t="n">
-        <v>2.92775535583496</v>
+        <v>2.92775559425354</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G458" t="n">
-        <v>3.0014545917511</v>
+        <v>3.00145506858826</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G460" t="n">
-        <v>3.0430588722229</v>
+        <v>3.04305863380432</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>5.02500009536743</v>
       </c>
       <c r="G461" t="n">
-        <v>2.98659610748291</v>
+        <v>2.98659586906433</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G462" t="n">
-        <v>3.0133421421051</v>
+        <v>3.01334166526794</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G463" t="n">
-        <v>3.04900288581848</v>
+        <v>3.0490026473999</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G464" t="n">
-        <v>3.0430588722229</v>
+        <v>3.04305863380432</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>5.11499977111816</v>
       </c>
       <c r="G466" t="n">
-        <v>3.04008722305298</v>
+        <v>3.04008746147156</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G467" t="n">
-        <v>3.05494570732117</v>
+        <v>3.05494594573975</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G471" t="n">
-        <v>3.16192889213562</v>
+        <v>3.16192865371704</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G472" t="n">
-        <v>3.21542000770569</v>
+        <v>3.21541976928711</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G475" t="n">
-        <v>3.15004181861877</v>
+        <v>3.1500415802002</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G476" t="n">
-        <v>3.13518309593201</v>
+        <v>3.13518333435059</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G477" t="n">
-        <v>3.15004181861877</v>
+        <v>3.1500415802002</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G478" t="n">
-        <v>3.09060668945312</v>
+        <v>3.09060716629028</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G479" t="n">
-        <v>3.07872009277344</v>
+        <v>3.07871985435486</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>5.24499988555908</v>
       </c>
       <c r="G480" t="n">
-        <v>3.11735272407532</v>
+        <v>3.11735248565674</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G481" t="n">
-        <v>3.14409828186035</v>
+        <v>3.14409804344177</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G482" t="n">
-        <v>3.15004181861877</v>
+        <v>3.1500415802002</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>5.30499982833862</v>
       </c>
       <c r="G483" t="n">
-        <v>3.15301275253296</v>
+        <v>3.1530134677887</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G484" t="n">
-        <v>3.17381548881531</v>
+        <v>3.17381572723389</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>5.34499979019165</v>
       </c>
       <c r="G485" t="n">
-        <v>3.17678713798523</v>
+        <v>3.17678689956665</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G488" t="n">
-        <v>3.191645860672</v>
+        <v>3.19164562225342</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>5.49499988555908</v>
       </c>
       <c r="G491" t="n">
-        <v>3.26593947410583</v>
+        <v>3.26593923568726</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G493" t="n">
-        <v>3.28079795837402</v>
+        <v>3.28079843521118</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G494" t="n">
-        <v>3.29862856864929</v>
+        <v>3.29862880706787</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G495" t="n">
-        <v>3.29862856864929</v>
+        <v>3.29862880706787</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G496" t="n">
-        <v>3.29268550872803</v>
+        <v>3.29268455505371</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>5.54500007629395</v>
       </c>
       <c r="G498" t="n">
-        <v>3.29565691947937</v>
+        <v>3.29565620422363</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>5.625</v>
       </c>
       <c r="G499" t="n">
-        <v>3.34320425987244</v>
+        <v>3.34320449829102</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>5.42500019073486</v>
       </c>
       <c r="G501" t="n">
-        <v>3.22433519363403</v>
+        <v>3.22433495521545</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>4.96500015258789</v>
       </c>
       <c r="G503" t="n">
-        <v>3.27646851539612</v>
+        <v>3.27646827697754</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G505" t="n">
-        <v>3.29296565055847</v>
+        <v>3.29296612739563</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G507" t="n">
-        <v>3.33256077766418</v>
+        <v>3.33256125450134</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G509" t="n">
-        <v>3.31936240196228</v>
+        <v>3.31936311721802</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G510" t="n">
-        <v>3.34575939178467</v>
+        <v>3.34575915336609</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G512" t="n">
-        <v>3.40515112876892</v>
+        <v>3.4051513671875</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G514" t="n">
-        <v>3.36555624008179</v>
+        <v>3.36555647850037</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G515" t="n">
-        <v>3.41175031661987</v>
+        <v>3.41175055503845</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G518" t="n">
-        <v>3.49094033241272</v>
+        <v>3.49093985557556</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G519" t="n">
-        <v>3.50413823127747</v>
+        <v>3.50413846969604</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G520" t="n">
-        <v>3.510737657547</v>
+        <v>3.51073741912842</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>5.25</v>
       </c>
       <c r="G522" t="n">
-        <v>3.46454381942749</v>
+        <v>3.46454334259033</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G523" t="n">
-        <v>3.43154764175415</v>
+        <v>3.43154811859131</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G524" t="n">
-        <v>3.39855217933655</v>
+        <v>3.39855241775513</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G527" t="n">
-        <v>3.33256077766418</v>
+        <v>3.33256125450134</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G528" t="n">
-        <v>3.31276345252991</v>
+        <v>3.31276321411133</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G529" t="n">
-        <v>3.27976775169373</v>
+        <v>3.27976751327515</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>4.9850001335144</v>
       </c>
       <c r="G532" t="n">
-        <v>3.28966617584229</v>
+        <v>3.28966665267944</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>4.9850001335144</v>
       </c>
       <c r="G533" t="n">
-        <v>3.28966617584229</v>
+        <v>3.28966665267944</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G535" t="n">
-        <v>3.30616450309753</v>
+        <v>3.30616474151611</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G536" t="n">
-        <v>3.2665696144104</v>
+        <v>3.26656913757324</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G538" t="n">
-        <v>3.19397926330566</v>
+        <v>3.19397950172424</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G539" t="n">
-        <v>3.22037601470947</v>
+        <v>3.22037577629089</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G540" t="n">
-        <v>3.2038779258728</v>
+        <v>3.20387768745422</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>4.81500005722046</v>
       </c>
       <c r="G541" t="n">
-        <v>3.17748117446899</v>
+        <v>3.17748141288757</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G542" t="n">
-        <v>3.2038779258728</v>
+        <v>3.20387768745422</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>4.77500009536743</v>
       </c>
       <c r="G543" t="n">
-        <v>3.15108466148376</v>
+        <v>3.15108513832092</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>4.74499988555908</v>
       </c>
       <c r="G544" t="n">
-        <v>3.13128733634949</v>
+        <v>3.13128757476807</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G545" t="n">
-        <v>3.29296565055847</v>
+        <v>3.29296612739563</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>4.9850001335144</v>
       </c>
       <c r="G546" t="n">
-        <v>3.28966617584229</v>
+        <v>3.28966665267944</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G547" t="n">
-        <v>3.31936240196228</v>
+        <v>3.31936311721802</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G548" t="n">
-        <v>3.2665696144104</v>
+        <v>3.26656913757324</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G549" t="n">
-        <v>3.28636693954468</v>
+        <v>3.2863667011261</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>4.94500017166138</v>
       </c>
       <c r="G551" t="n">
-        <v>3.26327013969421</v>
+        <v>3.26327037811279</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>4.96500015258789</v>
       </c>
       <c r="G552" t="n">
-        <v>3.27646851539612</v>
+        <v>3.27646827697754</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>4.93499994277954</v>
       </c>
       <c r="G553" t="n">
-        <v>3.25667095184326</v>
+        <v>3.25667071342468</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G554" t="n">
-        <v>3.24017310142517</v>
+        <v>3.24017286300659</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>4.94500017166138</v>
       </c>
       <c r="G555" t="n">
-        <v>3.26327013969421</v>
+        <v>3.26327037811279</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G556" t="n">
-        <v>3.29296565055847</v>
+        <v>3.29296612739563</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G557" t="n">
-        <v>3.31936240196228</v>
+        <v>3.31936311721802</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G560" t="n">
-        <v>3.22037601470947</v>
+        <v>3.22037577629089</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G561" t="n">
-        <v>3.20717716217041</v>
+        <v>3.20717740058899</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G564" t="n">
-        <v>3.25997066497803</v>
+        <v>3.25997042655945</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>4.94500017166138</v>
       </c>
       <c r="G565" t="n">
-        <v>3.26327013969421</v>
+        <v>3.26327037811279</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G567" t="n">
-        <v>3.33256077766418</v>
+        <v>3.33256125450134</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G568" t="n">
-        <v>3.33916044235229</v>
+        <v>3.33915996551514</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G569" t="n">
-        <v>3.35235834121704</v>
+        <v>3.35235810279846</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G570" t="n">
-        <v>3.33256077766418</v>
+        <v>3.33256125450134</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G572" t="n">
-        <v>3.36555624008179</v>
+        <v>3.36555647850037</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G573" t="n">
-        <v>3.34575939178467</v>
+        <v>3.34575915336609</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G576" t="n">
-        <v>3.31936240196228</v>
+        <v>3.31936311721802</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>4.92500019073486</v>
       </c>
       <c r="G578" t="n">
-        <v>3.25007176399231</v>
+        <v>3.25007200241089</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G581" t="n">
-        <v>3.22037601470947</v>
+        <v>3.22037577629089</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>4.92500019073486</v>
       </c>
       <c r="G584" t="n">
-        <v>3.25007176399231</v>
+        <v>3.25007200241089</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G585" t="n">
-        <v>3.22697472572327</v>
+        <v>3.22697448730469</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>4.96500015258789</v>
       </c>
       <c r="G587" t="n">
-        <v>3.27646851539612</v>
+        <v>3.27646827697754</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G588" t="n">
-        <v>3.23027467727661</v>
+        <v>3.23027396202087</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G589" t="n">
-        <v>3.2038779258728</v>
+        <v>3.20387768745422</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>4.96500015258789</v>
       </c>
       <c r="G591" t="n">
-        <v>3.27646851539612</v>
+        <v>3.27646827697754</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G592" t="n">
-        <v>3.20717716217041</v>
+        <v>3.20717740058899</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G594" t="n">
-        <v>2.93001437187195</v>
+        <v>2.93001389503479</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G599" t="n">
-        <v>2.99930500984192</v>
+        <v>2.99930477142334</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G600" t="n">
-        <v>2.98940587043762</v>
+        <v>2.9894061088562</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G602" t="n">
-        <v>2.99930500984192</v>
+        <v>2.99930477142334</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G604" t="n">
-        <v>3.02240180969238</v>
+        <v>3.02240133285522</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G605" t="n">
-        <v>3.01580286026001</v>
+        <v>3.01580262184143</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G607" t="n">
-        <v>3.04219913482666</v>
+        <v>3.04219937324524</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G608" t="n">
-        <v>3.05539774894714</v>
+        <v>3.05539751052856</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G609" t="n">
-        <v>3.06859564781189</v>
+        <v>3.06859540939331</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G610" t="n">
-        <v>3.06859564781189</v>
+        <v>3.06859540939331</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G611" t="n">
-        <v>3.08839249610901</v>
+        <v>3.08839297294617</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G612" t="n">
-        <v>3.08179426193237</v>
+        <v>3.08179402351379</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G614" t="n">
-        <v>3.17418169975281</v>
+        <v>3.17418146133423</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G615" t="n">
-        <v>3.17418169975281</v>
+        <v>3.17418146133423</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G616" t="n">
-        <v>3.15768361091614</v>
+        <v>3.15768384933472</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G617" t="n">
-        <v>3.20717716217041</v>
+        <v>3.20717740058899</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G618" t="n">
-        <v>3.18737959861755</v>
+        <v>3.18738007545471</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G619" t="n">
-        <v>3.15438461303711</v>
+        <v>3.15438413619995</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>4.875</v>
       </c>
       <c r="G621" t="n">
-        <v>3.21707582473755</v>
+        <v>3.21707606315613</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>4.81500005722046</v>
       </c>
       <c r="G622" t="n">
-        <v>3.17748117446899</v>
+        <v>3.17748141288757</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>4.77500009536743</v>
       </c>
       <c r="G624" t="n">
-        <v>3.15108466148376</v>
+        <v>3.15108513832092</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>4.74499988555908</v>
       </c>
       <c r="G625" t="n">
-        <v>3.13128733634949</v>
+        <v>3.13128757476807</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G626" t="n">
-        <v>3.15768361091614</v>
+        <v>3.15768384933472</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G627" t="n">
-        <v>3.17418169975281</v>
+        <v>3.17418146133423</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G628" t="n">
-        <v>3.15768361091614</v>
+        <v>3.15768384933472</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>4.75500011444092</v>
       </c>
       <c r="G629" t="n">
-        <v>3.13788652420044</v>
+        <v>3.13788676261902</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G630" t="n">
-        <v>3.10159087181091</v>
+        <v>3.10159134864807</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>4.80499982833862</v>
       </c>
       <c r="G634" t="n">
-        <v>3.1708824634552</v>
+        <v>3.17088174819946</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G635" t="n">
-        <v>3.20057845115662</v>
+        <v>3.20057821273804</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>4.88500022888184</v>
       </c>
       <c r="G636" t="n">
-        <v>3.22367548942566</v>
+        <v>3.22367525100708</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G638" t="n">
-        <v>3.31936240196228</v>
+        <v>3.31936311721802</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G640" t="n">
-        <v>3.33916044235229</v>
+        <v>3.33915996551514</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>5.25</v>
       </c>
       <c r="G641" t="n">
-        <v>3.46454381942749</v>
+        <v>3.46454334259033</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G642" t="n">
-        <v>3.510737657547</v>
+        <v>3.51073741912842</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G643" t="n">
-        <v>3.48434114456177</v>
+        <v>3.48434090614319</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G644" t="n">
-        <v>3.55033230781555</v>
+        <v>3.55033206939697</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G645" t="n">
-        <v>3.54373335838318</v>
+        <v>3.54373264312744</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G646" t="n">
-        <v>3.53053450584412</v>
+        <v>3.53053498268127</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G647" t="n">
-        <v>3.55693101882935</v>
+        <v>3.55693125724792</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G648" t="n">
-        <v>3.59652590751648</v>
+        <v>3.5965256690979</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G649" t="n">
-        <v>3.61632323265076</v>
+        <v>3.61632394790649</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G655" t="n">
-        <v>3.5635302066803</v>
+        <v>3.56353068351746</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G657" t="n">
-        <v>3.53053450584412</v>
+        <v>3.53053498268127</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G658" t="n">
-        <v>3.48434114456177</v>
+        <v>3.48434090614319</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G659" t="n">
-        <v>3.53053450584412</v>
+        <v>3.53053498268127</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G660" t="n">
-        <v>3.53053450584412</v>
+        <v>3.53053498268127</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G661" t="n">
-        <v>3.52393531799316</v>
+        <v>3.52393579483032</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G662" t="n">
-        <v>3.5635302066803</v>
+        <v>3.56353068351746</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G663" t="n">
-        <v>3.51733636856079</v>
+        <v>3.51733660697937</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G665" t="n">
-        <v>3.44474601745605</v>
+        <v>3.4447455406189</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G667" t="n">
-        <v>3.53053450584412</v>
+        <v>3.53053498268127</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G668" t="n">
-        <v>3.55693101882935</v>
+        <v>3.55693125724792</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G669" t="n">
-        <v>3.57012963294983</v>
+        <v>3.57012939453125</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G670" t="n">
-        <v>3.57672882080078</v>
+        <v>3.5767285823822</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G672" t="n">
-        <v>3.60312533378601</v>
+        <v>3.60312509536743</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G673" t="n">
-        <v>3.54373335838318</v>
+        <v>3.54373264312744</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G674" t="n">
-        <v>3.53053450584412</v>
+        <v>3.53053498268127</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G675" t="n">
-        <v>3.53713417053223</v>
+        <v>3.53713440895081</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G676" t="n">
-        <v>3.55033230781555</v>
+        <v>3.55033206939697</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G677" t="n">
-        <v>3.57012963294983</v>
+        <v>3.57012939453125</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G678" t="n">
-        <v>3.51733636856079</v>
+        <v>3.51733660697937</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G680" t="n">
-        <v>3.54373335838318</v>
+        <v>3.54373264312744</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G681" t="n">
-        <v>3.53053450584412</v>
+        <v>3.53053498268127</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G682" t="n">
-        <v>3.510737657547</v>
+        <v>3.51073741912842</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G683" t="n">
-        <v>3.49094033241272</v>
+        <v>3.49093985557556</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G684" t="n">
-        <v>3.50413823127747</v>
+        <v>3.50413846969604</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G685" t="n">
-        <v>3.55033230781555</v>
+        <v>3.55033206939697</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G686" t="n">
-        <v>3.53053450584412</v>
+        <v>3.53053498268127</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G687" t="n">
-        <v>3.51733636856079</v>
+        <v>3.51733660697937</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G690" t="n">
-        <v>3.52393531799316</v>
+        <v>3.52393579483032</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G691" t="n">
-        <v>3.54373335838318</v>
+        <v>3.54373264312744</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G692" t="n">
-        <v>3.50413823127747</v>
+        <v>3.50413846969604</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G694" t="n">
-        <v>3.53053450584412</v>
+        <v>3.53053498268127</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G695" t="n">
-        <v>3.53713417053223</v>
+        <v>3.53713440895081</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G696" t="n">
-        <v>3.55693101882935</v>
+        <v>3.55693125724792</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G697" t="n">
-        <v>3.53053450584412</v>
+        <v>3.53053498268127</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G698" t="n">
-        <v>3.51733636856079</v>
+        <v>3.51733660697937</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G699" t="n">
-        <v>3.55693101882935</v>
+        <v>3.55693125724792</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G700" t="n">
-        <v>3.5635302066803</v>
+        <v>3.56353068351746</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G701" t="n">
-        <v>3.53713417053223</v>
+        <v>3.53713440895081</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G705" t="n">
-        <v>3.72850871086121</v>
+        <v>3.72850918769836</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G706" t="n">
-        <v>3.74170684814453</v>
+        <v>3.74170732498169</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>5.75</v>
       </c>
       <c r="G707" t="n">
-        <v>3.79449963569641</v>
+        <v>3.79449987411499</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>5.75</v>
       </c>
       <c r="G708" t="n">
-        <v>3.79449963569641</v>
+        <v>3.79449987411499</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G709" t="n">
-        <v>3.80769824981689</v>
+        <v>3.80769848823547</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G710" t="n">
-        <v>3.74830603599548</v>
+        <v>3.74830555915833</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G713" t="n">
-        <v>3.68891453742981</v>
+        <v>3.68891334533691</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G716" t="n">
-        <v>3.74830603599548</v>
+        <v>3.74830555915833</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G717" t="n">
-        <v>3.74830603599548</v>
+        <v>3.74830555915833</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G718" t="n">
-        <v>3.7878999710083</v>
+        <v>3.78790044784546</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G719" t="n">
-        <v>3.78130221366882</v>
+        <v>3.78130149841309</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G720" t="n">
-        <v>3.82749557495117</v>
+        <v>3.82749533653259</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G721" t="n">
-        <v>3.82749557495117</v>
+        <v>3.82749533653259</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G722" t="n">
-        <v>3.87368941307068</v>
+        <v>3.87368988990784</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G725" t="n">
-        <v>4.03866767883301</v>
+        <v>4.03866815567017</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G726" t="n">
-        <v>4.04526710510254</v>
+        <v>4.0452675819397</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G727" t="n">
-        <v>3.99247431755066</v>
+        <v>3.9924738407135</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G728" t="n">
-        <v>3.76150417327881</v>
+        <v>3.76150441169739</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G729" t="n">
-        <v>3.72190976142883</v>
+        <v>3.72190952301025</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G730" t="n">
-        <v>3.84729290008545</v>
+        <v>3.84729313850403</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G731" t="n">
-        <v>3.75490522384644</v>
+        <v>3.75490546226501</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G733" t="n">
-        <v>3.48434114456177</v>
+        <v>3.48434090614319</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G734" t="n">
-        <v>3.55693101882935</v>
+        <v>3.55693125724792</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G735" t="n">
-        <v>3.510737657547</v>
+        <v>3.51073741912842</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G738" t="n">
-        <v>3.06859564781189</v>
+        <v>3.06859540939331</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>4.58500003814697</v>
       </c>
       <c r="G739" t="n">
-        <v>3.02570152282715</v>
+        <v>3.02570176124573</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>4.625</v>
       </c>
       <c r="G740" t="n">
-        <v>3.0520977973938</v>
+        <v>3.05209803581238</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G742" t="n">
-        <v>2.90361762046814</v>
+        <v>2.90361785888672</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G743" t="n">
-        <v>2.76503562927246</v>
+        <v>2.76503586769104</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>4.14499998092651</v>
       </c>
       <c r="G744" t="n">
-        <v>2.73533964157104</v>
+        <v>2.73533940315247</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>4.27500009536743</v>
       </c>
       <c r="G746" t="n">
-        <v>2.82112836837769</v>
+        <v>2.82112812995911</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>4.65500020980835</v>
       </c>
       <c r="G747" t="n">
-        <v>3.07189512252808</v>
+        <v>3.07189536094666</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G750" t="n">
-        <v>3.06859564781189</v>
+        <v>3.06859540939331</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G754" t="n">
-        <v>3.12138867378235</v>
+        <v>3.12138891220093</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G755" t="n">
-        <v>3.11808896064758</v>
+        <v>3.118088722229</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G756" t="n">
-        <v>3.04879832267761</v>
+        <v>3.04879808425903</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G757" t="n">
-        <v>3.01580286026001</v>
+        <v>3.01580262184143</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G758" t="n">
-        <v>3.10159087181091</v>
+        <v>3.10159134864807</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G760" t="n">
-        <v>3.33916044235229</v>
+        <v>3.33915996551514</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G761" t="n">
-        <v>3.36555624008179</v>
+        <v>3.36555647850037</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G762" t="n">
-        <v>3.25997066497803</v>
+        <v>3.25997042655945</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>4.86499977111816</v>
       </c>
       <c r="G763" t="n">
-        <v>3.21047687530518</v>
+        <v>3.21047639846802</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G765" t="n">
-        <v>3.08839249610901</v>
+        <v>3.08839297294617</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G766" t="n">
-        <v>3.08179426193237</v>
+        <v>3.08179402351379</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G767" t="n">
-        <v>3.11808896064758</v>
+        <v>3.118088722229</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G768" t="n">
-        <v>3.1147894859314</v>
+        <v>3.11478924751282</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G769" t="n">
-        <v>3.11808896064758</v>
+        <v>3.118088722229</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G770" t="n">
-        <v>3.10159087181091</v>
+        <v>3.10159134864807</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G771" t="n">
-        <v>3.15768361091614</v>
+        <v>3.15768384933472</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G772" t="n">
-        <v>3.24017310142517</v>
+        <v>3.24017286300659</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G773" t="n">
-        <v>3.24017310142517</v>
+        <v>3.24017286300659</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>4.71500015258789</v>
       </c>
       <c r="G774" t="n">
-        <v>3.11149024963379</v>
+        <v>3.11149001121521</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G777" t="n">
-        <v>3.06199645996094</v>
+        <v>3.06199598312378</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G778" t="n">
-        <v>2.98280668258667</v>
+        <v>2.98280692100525</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>4.82499980926514</v>
       </c>
       <c r="G779" t="n">
-        <v>3.18408036231995</v>
+        <v>3.18408012390137</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G780" t="n">
-        <v>3.17418169975281</v>
+        <v>3.17418146133423</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G782" t="n">
-        <v>3.31276345252991</v>
+        <v>3.31276321411133</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>4.84499979019165</v>
       </c>
       <c r="G783" t="n">
-        <v>3.19727849960327</v>
+        <v>3.19727873802185</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G784" t="n">
-        <v>3.22697472572327</v>
+        <v>3.22697448730469</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G786" t="n">
-        <v>3.36555624008179</v>
+        <v>3.36555647850037</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G787" t="n">
-        <v>3.2665696144104</v>
+        <v>3.26656913757324</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>4.92500019073486</v>
       </c>
       <c r="G788" t="n">
-        <v>3.25007176399231</v>
+        <v>3.25007200241089</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G789" t="n">
-        <v>3.30616450309753</v>
+        <v>3.30616474151611</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G790" t="n">
-        <v>3.33256077766418</v>
+        <v>3.33256125450134</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G791" t="n">
-        <v>3.41175031661987</v>
+        <v>3.41175055503845</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G792" t="n">
-        <v>3.44474601745605</v>
+        <v>3.4447455406189</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G793" t="n">
-        <v>3.41175031661987</v>
+        <v>3.41175055503845</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G794" t="n">
-        <v>3.52393531799316</v>
+        <v>3.52393579483032</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G795" t="n">
-        <v>3.52393531799316</v>
+        <v>3.52393579483032</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G796" t="n">
-        <v>3.35235834121704</v>
+        <v>3.35235810279846</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G799" t="n">
-        <v>3.40515112876892</v>
+        <v>3.4051513671875</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G804" t="n">
-        <v>3.11808896064758</v>
+        <v>3.118088722229</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G805" t="n">
-        <v>3.10159087181091</v>
+        <v>3.10159134864807</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G808" t="n">
-        <v>3.19397926330566</v>
+        <v>3.19397950172424</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G809" t="n">
-        <v>3.19397926330566</v>
+        <v>3.19397950172424</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>4.7649998664856</v>
       </c>
       <c r="G810" t="n">
-        <v>3.14448547363281</v>
+        <v>3.14448571205139</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G812" t="n">
-        <v>3.14118599891663</v>
+        <v>3.14118623733521</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>4.7649998664856</v>
       </c>
       <c r="G813" t="n">
-        <v>3.14448547363281</v>
+        <v>3.14448571205139</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G814" t="n">
-        <v>3.2665696144104</v>
+        <v>3.26656913757324</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G816" t="n">
-        <v>3.33916044235229</v>
+        <v>3.33915996551514</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G817" t="n">
-        <v>3.33916044235229</v>
+        <v>3.33915996551514</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G818" t="n">
-        <v>3.41175031661987</v>
+        <v>3.41175055503845</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G820" t="n">
-        <v>3.39855217933655</v>
+        <v>3.39855241775513</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G821" t="n">
-        <v>3.36555624008179</v>
+        <v>3.36555647850037</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G824" t="n">
-        <v>3.39855217933655</v>
+        <v>3.39855241775513</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G825" t="n">
-        <v>3.31936240196228</v>
+        <v>3.31936311721802</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>4.92500019073486</v>
       </c>
       <c r="G826" t="n">
-        <v>3.25007176399231</v>
+        <v>3.25007200241089</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G827" t="n">
-        <v>3.27976775169373</v>
+        <v>3.27976751327515</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G829" t="n">
-        <v>3.30616450309753</v>
+        <v>3.30616474151611</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G832" t="n">
-        <v>3.33916044235229</v>
+        <v>3.33915996551514</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>4.91499996185303</v>
       </c>
       <c r="G834" t="n">
-        <v>3.24347233772278</v>
+        <v>3.24347281455994</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G835" t="n">
-        <v>3.22697472572327</v>
+        <v>3.22697448730469</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>4.88500022888184</v>
       </c>
       <c r="G836" t="n">
-        <v>3.22367548942566</v>
+        <v>3.22367525100708</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G837" t="n">
-        <v>3.19397926330566</v>
+        <v>3.19397950172424</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>4.81500005722046</v>
       </c>
       <c r="G839" t="n">
-        <v>3.17748117446899</v>
+        <v>3.17748141288757</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>4.80499982833862</v>
       </c>
       <c r="G840" t="n">
-        <v>3.1708824634552</v>
+        <v>3.17088174819946</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>4.86499977111816</v>
       </c>
       <c r="G841" t="n">
-        <v>3.21047687530518</v>
+        <v>3.21047639846802</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G844" t="n">
-        <v>3.1609833240509</v>
+        <v>3.16098308563232</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>4.75500011444092</v>
       </c>
       <c r="G847" t="n">
-        <v>3.13788652420044</v>
+        <v>3.13788676261902</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>4.61499977111816</v>
       </c>
       <c r="G851" t="n">
-        <v>3.04549837112427</v>
+        <v>3.04549860954285</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G852" t="n">
-        <v>3.06859564781189</v>
+        <v>3.06859540939331</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G853" t="n">
-        <v>3.02240180969238</v>
+        <v>3.02240133285522</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G855" t="n">
-        <v>3.06199645996094</v>
+        <v>3.06199598312378</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G856" t="n">
-        <v>3.05539774894714</v>
+        <v>3.05539751052856</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G857" t="n">
-        <v>3.05539774894714</v>
+        <v>3.05539751052856</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G858" t="n">
-        <v>3.06859564781189</v>
+        <v>3.06859540939331</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>4.65500020980835</v>
       </c>
       <c r="G860" t="n">
-        <v>3.07189512252808</v>
+        <v>3.07189536094666</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>4.58500003814697</v>
       </c>
       <c r="G865" t="n">
-        <v>3.02570152282715</v>
+        <v>3.02570176124573</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>4.625</v>
       </c>
       <c r="G867" t="n">
-        <v>3.0520977973938</v>
+        <v>3.05209803581238</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>4.625</v>
       </c>
       <c r="G868" t="n">
-        <v>3.0520977973938</v>
+        <v>3.05209803581238</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G869" t="n">
-        <v>3.05539774894714</v>
+        <v>3.05539751052856</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G870" t="n">
-        <v>3.06199645996094</v>
+        <v>3.06199598312378</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G871" t="n">
-        <v>3.05539774894714</v>
+        <v>3.05539751052856</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G872" t="n">
-        <v>3.06859564781189</v>
+        <v>3.06859540939331</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>4.7649998664856</v>
       </c>
       <c r="G873" t="n">
-        <v>3.14448547363281</v>
+        <v>3.14448571205139</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G875" t="n">
-        <v>3.14118599891663</v>
+        <v>3.14118623733521</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>4.75500011444092</v>
       </c>
       <c r="G876" t="n">
-        <v>3.13788652420044</v>
+        <v>3.13788676261902</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>4.7649998664856</v>
       </c>
       <c r="G877" t="n">
-        <v>3.14448547363281</v>
+        <v>3.14448571205139</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>4.7649998664856</v>
       </c>
       <c r="G878" t="n">
-        <v>3.14448547363281</v>
+        <v>3.14448571205139</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G879" t="n">
-        <v>3.1609833240509</v>
+        <v>3.16098308563232</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G880" t="n">
-        <v>3.15438461303711</v>
+        <v>3.15438413619995</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>4.74499988555908</v>
       </c>
       <c r="G881" t="n">
-        <v>3.13128733634949</v>
+        <v>3.13128757476807</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>4.80499982833862</v>
       </c>
       <c r="G882" t="n">
-        <v>3.1708824634552</v>
+        <v>3.17088174819946</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G883" t="n">
-        <v>3.1609833240509</v>
+        <v>3.16098308563232</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G884" t="n">
-        <v>3.20717716217041</v>
+        <v>3.20717740058899</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G885" t="n">
-        <v>3.22697472572327</v>
+        <v>3.22697448730469</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G886" t="n">
-        <v>3.33256077766418</v>
+        <v>3.33256125450134</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>4.93499994277954</v>
       </c>
       <c r="G887" t="n">
-        <v>3.25667095184326</v>
+        <v>3.25667071342468</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>4.84499979019165</v>
       </c>
       <c r="G888" t="n">
-        <v>3.19727849960327</v>
+        <v>3.19727873802185</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G889" t="n">
-        <v>3.17418169975281</v>
+        <v>3.17418146133423</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>4.81500005722046</v>
       </c>
       <c r="G890" t="n">
-        <v>3.17748117446899</v>
+        <v>3.17748141288757</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G891" t="n">
-        <v>3.08839249610901</v>
+        <v>3.08839297294617</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G892" t="n">
-        <v>3.08179426193237</v>
+        <v>3.08179402351379</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G895" t="n">
-        <v>2.91681528091431</v>
+        <v>2.91681551933289</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G896" t="n">
-        <v>2.90361762046814</v>
+        <v>2.90361785888672</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G897" t="n">
-        <v>2.87062168121338</v>
+        <v>2.8706214427948</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G899" t="n">
-        <v>2.81122994422913</v>
+        <v>2.81122970581055</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G901" t="n">
-        <v>2.75843620300293</v>
+        <v>2.75843644142151</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>3.95499992370605</v>
       </c>
       <c r="G904" t="n">
-        <v>2.60995578765869</v>
+        <v>2.60995626449585</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G906" t="n">
-        <v>2.57366108894348</v>
+        <v>2.5736608505249</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>4.02500009536743</v>
       </c>
       <c r="G907" t="n">
-        <v>2.65615010261536</v>
+        <v>2.65615034103394</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G908" t="n">
-        <v>2.75183725357056</v>
+        <v>2.75183749198914</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G909" t="n">
-        <v>2.7848334312439</v>
+        <v>2.78483271598816</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G911" t="n">
-        <v>2.96300935745239</v>
+        <v>2.96300911903381</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>4.5</v>
       </c>
       <c r="G915" t="n">
-        <v>2.96960854530334</v>
+        <v>2.9696090221405</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G917" t="n">
-        <v>3.05539774894714</v>
+        <v>3.05539751052856</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>4.61499977111816</v>
       </c>
       <c r="G921" t="n">
-        <v>3.04549837112427</v>
+        <v>3.04549860954285</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>4.7649998664856</v>
       </c>
       <c r="G923" t="n">
-        <v>3.14448547363281</v>
+        <v>3.14448571205139</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G924" t="n">
-        <v>3.12138867378235</v>
+        <v>3.12138891220093</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G926" t="n">
-        <v>2.9762077331543</v>
+        <v>2.97620797157288</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G928" t="n">
-        <v>2.97290849685669</v>
+        <v>2.97290825843811</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>4.53499984741211</v>
       </c>
       <c r="G930" t="n">
-        <v>2.99270558357239</v>
+        <v>2.99270534515381</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G933" t="n">
-        <v>2.94981098175049</v>
+        <v>2.94981122016907</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G934" t="n">
-        <v>2.9762077331543</v>
+        <v>2.97620797157288</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G936" t="n">
-        <v>2.93001437187195</v>
+        <v>2.93001389503479</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G938" t="n">
-        <v>3.06199645996094</v>
+        <v>3.06199598312378</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>4.65500020980835</v>
       </c>
       <c r="G939" t="n">
-        <v>3.07189512252808</v>
+        <v>3.07189536094666</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>4.5</v>
       </c>
       <c r="G940" t="n">
-        <v>2.96960854530334</v>
+        <v>2.9696090221405</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G941" t="n">
-        <v>2.98940587043762</v>
+        <v>2.9894061088562</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G944" t="n">
-        <v>3.20057845115662</v>
+        <v>3.20057821273804</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G945" t="n">
-        <v>3.25997066497803</v>
+        <v>3.25997042655945</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G946" t="n">
-        <v>3.1609833240509</v>
+        <v>3.16098308563232</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G948" t="n">
-        <v>3.14118599891663</v>
+        <v>3.14118623733521</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G951" t="n">
-        <v>3.2038779258728</v>
+        <v>3.20387768745422</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G952" t="n">
-        <v>3.08839249610901</v>
+        <v>3.08839297294617</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>4.70499992370605</v>
       </c>
       <c r="G953" t="n">
-        <v>3.10489082336426</v>
+        <v>3.10489058494568</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G954" t="n">
-        <v>3.11808896064758</v>
+        <v>3.118088722229</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G955" t="n">
-        <v>3.08179426193237</v>
+        <v>3.08179402351379</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G956" t="n">
-        <v>3.08839249610901</v>
+        <v>3.08839297294617</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G957" t="n">
-        <v>3.08839249610901</v>
+        <v>3.08839297294617</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>4.70499992370605</v>
       </c>
       <c r="G958" t="n">
-        <v>3.10489082336426</v>
+        <v>3.10489058494568</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G959" t="n">
-        <v>3.06859564781189</v>
+        <v>3.06859540939331</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G961" t="n">
-        <v>2.94981098175049</v>
+        <v>2.94981122016907</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>4.60500001907349</v>
       </c>
       <c r="G962" t="n">
-        <v>3.03889942169189</v>
+        <v>3.03889966011047</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G963" t="n">
-        <v>3.02240180969238</v>
+        <v>3.02240133285522</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G965" t="n">
-        <v>2.99930500984192</v>
+        <v>2.99930477142334</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G968" t="n">
-        <v>3.1147894859314</v>
+        <v>3.11478924751282</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G969" t="n">
-        <v>3.20057845115662</v>
+        <v>3.20057821273804</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G970" t="n">
-        <v>3.23027467727661</v>
+        <v>3.23027396202087</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G973" t="n">
-        <v>3.43154764175415</v>
+        <v>3.43154811859131</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G975" t="n">
-        <v>3.74830603599548</v>
+        <v>3.74830555915833</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G976" t="n">
-        <v>3.76150417327881</v>
+        <v>3.76150441169739</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G977" t="n">
-        <v>3.71531009674072</v>
+        <v>3.7153103351593</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G978" t="n">
-        <v>3.60312533378601</v>
+        <v>3.60312509536743</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G979" t="n">
-        <v>3.7021119594574</v>
+        <v>3.70211219787598</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G981" t="n">
-        <v>3.64271998405457</v>
+        <v>3.64272046089172</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G982" t="n">
-        <v>3.59652590751648</v>
+        <v>3.5965256690979</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G983" t="n">
-        <v>3.62292194366455</v>
+        <v>3.62292265892029</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G984" t="n">
-        <v>3.62292194366455</v>
+        <v>3.62292265892029</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G989" t="n">
-        <v>3.64271998405457</v>
+        <v>3.64272046089172</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G992" t="n">
-        <v>3.82089638710022</v>
+        <v>3.82089614868164</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G993" t="n">
-        <v>4.09146070480347</v>
+        <v>4.09146118164062</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>6.30999994277954</v>
       </c>
       <c r="G995" t="n">
-        <v>4.16405153274536</v>
+        <v>4.1640510559082</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G996" t="n">
-        <v>4.29603385925293</v>
+        <v>4.29603338241577</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>6.42999982833862</v>
       </c>
       <c r="G997" t="n">
-        <v>4.24324083328247</v>
+        <v>4.24324035644531</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>6.42999982833862</v>
       </c>
       <c r="G1000" t="n">
-        <v>4.24324083328247</v>
+        <v>4.24324035644531</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>6.3899998664856</v>
       </c>
       <c r="G1001" t="n">
-        <v>4.2168436050415</v>
+        <v>4.21684408187866</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G1002" t="n">
-        <v>4.29603385925293</v>
+        <v>4.29603338241577</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>6.5</v>
       </c>
       <c r="G1005" t="n">
-        <v>4.2894344329834</v>
+        <v>4.28943490982056</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G1008" t="n">
-        <v>4.1488208770752</v>
+        <v>4.14882230758667</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>6.52500009536743</v>
       </c>
       <c r="G1010" t="n">
-        <v>4.31755352020264</v>
+        <v>4.31755399703979</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G1012" t="n">
-        <v>4.31424570083618</v>
+        <v>4.31424522399902</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>6.55499982833862</v>
       </c>
       <c r="G1013" t="n">
-        <v>4.33740472793579</v>
+        <v>4.33740425109863</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G1014" t="n">
-        <v>4.36056327819824</v>
+        <v>4.36056423187256</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>6.77500009536743</v>
       </c>
       <c r="G1015" t="n">
-        <v>4.48297691345215</v>
+        <v>4.48297786712646</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G1016" t="n">
-        <v>4.51937055587769</v>
+        <v>4.51937007904053</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>6.75</v>
       </c>
       <c r="G1020" t="n">
-        <v>4.46643543243408</v>
+        <v>4.46643447875977</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G1021" t="n">
-        <v>4.51937055587769</v>
+        <v>4.51937007904053</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G1025" t="n">
-        <v>4.88991928100586</v>
+        <v>4.8899188041687</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G1026" t="n">
-        <v>4.86345148086548</v>
+        <v>4.86345100402832</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G1027" t="n">
-        <v>4.85683488845825</v>
+        <v>4.85683393478394</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G1030" t="n">
-        <v>4.87668514251709</v>
+        <v>4.87668466567993</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G1031" t="n">
-        <v>4.91638660430908</v>
+        <v>4.91638708114624</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>7.55499982833862</v>
       </c>
       <c r="G1032" t="n">
-        <v>4.99909734725952</v>
+        <v>4.99909782409668</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1033" t="n">
-        <v>5.16121387481689</v>
+        <v>5.16121339797974</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>7.66499996185303</v>
       </c>
       <c r="G1034" t="n">
-        <v>5.0718846321106</v>
+        <v>5.07188510894775</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1035" t="n">
-        <v>4.87006807327271</v>
+        <v>4.87006855010986</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>7.30999994277954</v>
       </c>
       <c r="G1036" t="n">
-        <v>4.8369836807251</v>
+        <v>4.83698320388794</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>7.61499977111816</v>
       </c>
       <c r="G1037" t="n">
-        <v>5.03879928588867</v>
+        <v>5.03880023956299</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>7.6100001335144</v>
       </c>
       <c r="G1038" t="n">
-        <v>5.03549146652222</v>
+        <v>5.03549194335938</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G1039" t="n">
-        <v>5.05534267425537</v>
+        <v>5.05534219741821</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>7.66499996185303</v>
       </c>
       <c r="G1040" t="n">
-        <v>5.0718846321106</v>
+        <v>5.07188510894775</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G1042" t="n">
-        <v>5.10827779769897</v>
+        <v>5.10827732086182</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>7.625</v>
       </c>
       <c r="G1045" t="n">
-        <v>5.04541730880737</v>
+        <v>5.04541683197021</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G1046" t="n">
-        <v>5.05534267425537</v>
+        <v>5.05534219741821</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>7.69500017166138</v>
       </c>
       <c r="G1048" t="n">
-        <v>5.09173536300659</v>
+        <v>5.09173583984375</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>7.93499994277954</v>
       </c>
       <c r="G1052" t="n">
-        <v>5.25054216384888</v>
+        <v>5.25054168701172</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1053" t="n">
-        <v>5.16121387481689</v>
+        <v>5.16121339797974</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>8.13000011444092</v>
       </c>
       <c r="G1057" t="n">
-        <v>5.37957239151001</v>
+        <v>5.37957286834717</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G1060" t="n">
-        <v>5.38618946075439</v>
+        <v>5.38618993759155</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G1062" t="n">
-        <v>5.60454845428467</v>
+        <v>5.60454893112183</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>8.52999973297119</v>
       </c>
       <c r="G1065" t="n">
-        <v>5.64424991607666</v>
+        <v>5.6442494392395</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>8.45499992370605</v>
       </c>
       <c r="G1068" t="n">
-        <v>5.59462308883667</v>
+        <v>5.59462261199951</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G1071" t="n">
-        <v>5.5913143157959</v>
+        <v>5.59131479263306</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>8.625</v>
       </c>
       <c r="G1072" t="n">
-        <v>5.70711135864258</v>
+        <v>5.70711088180542</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1077" t="n">
-        <v>5.50529432296753</v>
+        <v>5.50529336929321</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G1078" t="n">
-        <v>5.65086698532104</v>
+        <v>5.6508674621582</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1079" t="n">
-        <v>5.55822992324829</v>
+        <v>5.55823040008545</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1081" t="n">
-        <v>5.65748453140259</v>
+        <v>5.65748405456543</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G1082" t="n">
-        <v>5.51191139221191</v>
+        <v>5.51191186904907</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>7.95499992370605</v>
       </c>
       <c r="G1084" t="n">
-        <v>5.26377582550049</v>
+        <v>5.26377630233765</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G1086" t="n">
-        <v>5.32663726806641</v>
+        <v>5.32663774490356</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>8.49499988555908</v>
       </c>
       <c r="G1087" t="n">
-        <v>5.62109041213989</v>
+        <v>5.62109136581421</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1090" t="n">
-        <v>5.82290744781494</v>
+        <v>5.8229079246521</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>8.8100004196167</v>
       </c>
       <c r="G1093" t="n">
-        <v>5.82952499389648</v>
+        <v>5.82952451705933</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>8.86999988555908</v>
       </c>
       <c r="G1094" t="n">
-        <v>5.86922597885132</v>
+        <v>5.86922550201416</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>8.80500030517578</v>
       </c>
       <c r="G1095" t="n">
-        <v>5.82621622085571</v>
+        <v>5.82621574401855</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>8.86999988555908</v>
       </c>
       <c r="G1097" t="n">
-        <v>5.86922597885132</v>
+        <v>5.86922550201416</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>8.05500030517578</v>
       </c>
       <c r="G1098" t="n">
-        <v>5.32994556427002</v>
+        <v>5.32994604110718</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G1106" t="n">
-        <v>5.05534267425537</v>
+        <v>5.05534219741821</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>7.74499988555908</v>
       </c>
       <c r="G1108" t="n">
-        <v>5.12482023239136</v>
+        <v>5.12482070922852</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G1109" t="n">
-        <v>5.23399972915649</v>
+        <v>5.23400020599365</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>7.96500015258789</v>
       </c>
       <c r="G1110" t="n">
-        <v>5.27039241790771</v>
+        <v>5.27039289474487</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1112" t="n">
-        <v>5.22738313674927</v>
+        <v>5.22738218307495</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>7.85500001907349</v>
       </c>
       <c r="G1113" t="n">
-        <v>5.19760704040527</v>
+        <v>5.19760656356812</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G1115" t="n">
-        <v>5.12151145935059</v>
+        <v>5.12151193618774</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G1118" t="n">
-        <v>5.18768119812012</v>
+        <v>5.18768167495728</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>7.91499996185303</v>
       </c>
       <c r="G1120" t="n">
-        <v>5.23730850219727</v>
+        <v>5.23730897903442</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>8.05500030517578</v>
       </c>
       <c r="G1122" t="n">
-        <v>5.32994556427002</v>
+        <v>5.32994604110718</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>8.27499961853027</v>
       </c>
       <c r="G1123" t="n">
-        <v>5.47551774978638</v>
+        <v>5.47551727294922</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>8.01000022888184</v>
       </c>
       <c r="G1124" t="n">
-        <v>5.30016899108887</v>
+        <v>5.30016946792603</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G1126" t="n">
-        <v>5.32002019882202</v>
+        <v>5.32001972198486</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>7.95499992370605</v>
       </c>
       <c r="G1129" t="n">
-        <v>5.26377582550049</v>
+        <v>5.26377630233765</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>8.0649995803833</v>
       </c>
       <c r="G1130" t="n">
-        <v>5.3365626335144</v>
+        <v>5.33656215667725</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G1132" t="n">
-        <v>5.41927337646484</v>
+        <v>5.419273853302</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1134" t="n">
-        <v>5.49206066131592</v>
+        <v>5.49206113815308</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>8.19499969482422</v>
       </c>
       <c r="G1136" t="n">
-        <v>5.42258214950562</v>
+        <v>5.42258262634277</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>8.57499980926514</v>
       </c>
       <c r="G1138" t="n">
-        <v>5.67402648925781</v>
+        <v>5.67402601242065</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G1142" t="n">
-        <v>5.38618946075439</v>
+        <v>5.38618993759155</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>8.17500019073486</v>
       </c>
       <c r="G1143" t="n">
-        <v>5.409348487854</v>
+        <v>5.40934896469116</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>7.5</v>
       </c>
       <c r="G1148" t="n">
-        <v>5.57251167297363</v>
+        <v>5.57251214981079</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>7.7350001335144</v>
       </c>
       <c r="G1149" t="n">
-        <v>5.7471170425415</v>
+        <v>5.74711751937866</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1151" t="n">
-        <v>5.79541301727295</v>
+        <v>5.79541254043579</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G1152" t="n">
-        <v>5.78798198699951</v>
+        <v>5.78798246383667</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G1153" t="n">
-        <v>5.81027221679688</v>
+        <v>5.81027269363403</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>7.86999988555908</v>
       </c>
       <c r="G1154" t="n">
-        <v>5.84742212295532</v>
+        <v>5.84742259979248</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>7.7649998664856</v>
       </c>
       <c r="G1156" t="n">
-        <v>5.76940774917603</v>
+        <v>5.76940727233887</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1162" t="n">
-        <v>5.4982123374939</v>
+        <v>5.49821186065674</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>7.35500001907349</v>
       </c>
       <c r="G1164" t="n">
-        <v>5.46477699279785</v>
+        <v>5.46477651596069</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G1166" t="n">
-        <v>5.34218168258667</v>
+        <v>5.34218120574951</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>7.03499984741211</v>
       </c>
       <c r="G1172" t="n">
-        <v>5.22701597213745</v>
+        <v>5.22701644897461</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>6.82499980926514</v>
       </c>
       <c r="G1176" t="n">
-        <v>5.07098579406738</v>
+        <v>5.07098531723022</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>6.91499996185303</v>
       </c>
       <c r="G1177" t="n">
-        <v>5.13785600662231</v>
+        <v>5.13785552978516</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1179" t="n">
-        <v>4.79979038238525</v>
+        <v>4.7997899055481</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1181" t="n">
-        <v>5.05241060256958</v>
+        <v>5.05241107940674</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G1182" t="n">
-        <v>4.96325016021729</v>
+        <v>4.96325063705444</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>6.5</v>
       </c>
       <c r="G1183" t="n">
-        <v>4.82951021194458</v>
+        <v>4.82951068878174</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>6.75</v>
       </c>
       <c r="G1185" t="n">
-        <v>5.01526117324829</v>
+        <v>5.01526069641113</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>6.70499992370605</v>
       </c>
       <c r="G1187" t="n">
-        <v>4.98182582855225</v>
+        <v>4.9818263053894</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>6.66499996185303</v>
       </c>
       <c r="G1190" t="n">
-        <v>4.95210599899292</v>
+        <v>4.95210552215576</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G1191" t="n">
-        <v>4.97811079025269</v>
+        <v>4.97811031341553</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G1192" t="n">
-        <v>5.08956050872803</v>
+        <v>5.08956098556519</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G1193" t="n">
-        <v>5.10442113876343</v>
+        <v>5.10442066192627</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>6.7350001335144</v>
       </c>
       <c r="G1194" t="n">
-        <v>5.00411558151245</v>
+        <v>5.00411605834961</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>6.93499994277954</v>
       </c>
       <c r="G1196" t="n">
-        <v>5.15271615982056</v>
+        <v>5.1527156829834</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>6.93499994277954</v>
       </c>
       <c r="G1197" t="n">
-        <v>5.15271615982056</v>
+        <v>5.1527156829834</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G1198" t="n">
-        <v>5.22330141067505</v>
+        <v>5.22330093383789</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>7.11499977111816</v>
       </c>
       <c r="G1199" t="n">
-        <v>5.28645610809326</v>
+        <v>5.28645658493042</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G1201" t="n">
-        <v>5.26788091659546</v>
+        <v>5.26788139343262</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1202" t="n">
-        <v>5.34961128234863</v>
+        <v>5.34961175918579</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>7.17500019073486</v>
       </c>
       <c r="G1204" t="n">
-        <v>5.33103656768799</v>
+        <v>5.33103609085083</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>7.14499998092651</v>
       </c>
       <c r="G1205" t="n">
-        <v>5.30874633789062</v>
+        <v>5.30874681472778</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G1211" t="n">
-        <v>5.24559164047241</v>
+        <v>5.24559116363525</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>7.10500001907349</v>
       </c>
       <c r="G1212" t="n">
-        <v>5.27902698516846</v>
+        <v>5.27902603149414</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G1214" t="n">
-        <v>5.22330141067505</v>
+        <v>5.22330093383789</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>6.5</v>
       </c>
       <c r="G1217" t="n">
-        <v>4.82951021194458</v>
+        <v>4.82951068878174</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>6.82499980926514</v>
       </c>
       <c r="G1220" t="n">
-        <v>5.07098579406738</v>
+        <v>5.07098531723022</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>6.76999998092651</v>
       </c>
       <c r="G1227" t="n">
-        <v>5.03012037277222</v>
+        <v>5.03012084960938</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>7.67500019073486</v>
       </c>
       <c r="G1233" t="n">
-        <v>5.70253753662109</v>
+        <v>5.70253705978394</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G1234" t="n">
-        <v>5.54279232025146</v>
+        <v>5.54279184341431</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G1237" t="n">
-        <v>5.34218168258667</v>
+        <v>5.34218120574951</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G1239" t="n">
-        <v>5.25302124023438</v>
+        <v>5.25302171707153</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>6.53000020980835</v>
       </c>
       <c r="G1240" t="n">
-        <v>4.8518009185791</v>
+        <v>4.85180044174194</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G1242" t="n">
-        <v>4.79235982894897</v>
+        <v>4.79235935211182</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G1243" t="n">
-        <v>4.72548961639404</v>
+        <v>4.72549057006836</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1245" t="n">
-        <v>4.60660934448242</v>
+        <v>4.60661029815674</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G1251" t="n">
-        <v>4.53230953216553</v>
+        <v>4.53231000900269</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G1252" t="n">
-        <v>4.71806049346924</v>
+        <v>4.71806001663208</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1257" t="n">
-        <v>4.79979038238525</v>
+        <v>4.7997899055481</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>6.68499994277954</v>
       </c>
       <c r="G1262" t="n">
-        <v>4.966965675354</v>
+        <v>4.96696519851685</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>6.82499980926514</v>
       </c>
       <c r="G1263" t="n">
-        <v>5.07098579406738</v>
+        <v>5.07098531723022</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>6.82499980926514</v>
       </c>
       <c r="G1264" t="n">
-        <v>5.07098579406738</v>
+        <v>5.07098531723022</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>6.7350001335144</v>
       </c>
       <c r="G1265" t="n">
-        <v>5.00411558151245</v>
+        <v>5.00411605834961</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G1266" t="n">
-        <v>5.08213090896606</v>
+        <v>5.08213138580322</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G1272" t="n">
-        <v>5.15643119812012</v>
+        <v>5.15643167495728</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G1277" t="n">
-        <v>5.03365564346313</v>
+        <v>5.03365612030029</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>5.95499992370605</v>
       </c>
       <c r="G1282" t="n">
-        <v>4.90596103668213</v>
+        <v>4.90596055984497</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G1283" t="n">
-        <v>4.91831827163696</v>
+        <v>4.9183177947998</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G1285" t="n">
-        <v>4.95127248764038</v>
+        <v>4.95127201080322</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>6.22499990463257</v>
       </c>
       <c r="G1286" t="n">
-        <v>5.12839698791504</v>
+        <v>5.1283974647522</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G1290" t="n">
-        <v>5.06660938262939</v>
+        <v>5.06660890579224</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>6.40999984741211</v>
       </c>
       <c r="G1292" t="n">
-        <v>5.28080701828003</v>
+        <v>5.28080749511719</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>6.59499979019165</v>
       </c>
       <c r="G1293" t="n">
-        <v>5.43321752548218</v>
+        <v>5.43321704864502</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G1295" t="n">
-        <v>5.61858129501343</v>
+        <v>5.61858177185059</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G1298" t="n">
-        <v>5.82454109191895</v>
+        <v>5.8245415687561</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G1302" t="n">
-        <v>5.99754762649536</v>
+        <v>5.9975471496582</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>7.33500003814697</v>
       </c>
       <c r="G1304" t="n">
-        <v>6.04285860061646</v>
+        <v>6.0428581237793</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G1305" t="n">
-        <v>6.11288499832153</v>
+        <v>6.11288452148438</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1310" t="n">
-        <v>5.93164014816284</v>
+        <v>5.93163967132568</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>7.31500005722046</v>
       </c>
       <c r="G1311" t="n">
-        <v>6.0263819694519</v>
+        <v>6.02638101577759</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1312" t="n">
-        <v>5.93164014816284</v>
+        <v>5.93163967132568</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>6.95499992370605</v>
       </c>
       <c r="G1314" t="n">
-        <v>5.72979927062988</v>
+        <v>5.72979974746704</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G1315" t="n">
-        <v>5.47029066085815</v>
+        <v>5.470290184021</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G1316" t="n">
-        <v>5.47029066085815</v>
+        <v>5.470290184021</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>6.86499977111816</v>
       </c>
       <c r="G1317" t="n">
-        <v>5.65565347671509</v>
+        <v>5.6556544303894</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>6.48999977111816</v>
       </c>
       <c r="G1322" t="n">
-        <v>5.34671401977539</v>
+        <v>5.34671449661255</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>6.5149998664856</v>
       </c>
       <c r="G1323" t="n">
-        <v>5.36731052398682</v>
+        <v>5.3673095703125</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>6.58500003814697</v>
       </c>
       <c r="G1326" t="n">
-        <v>5.42497968673706</v>
+        <v>5.42497873306274</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>6.63500022888184</v>
       </c>
       <c r="G1327" t="n">
-        <v>5.4661717414856</v>
+        <v>5.46617126464844</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>6.30999994277954</v>
       </c>
       <c r="G1332" t="n">
-        <v>5.19842338562012</v>
+        <v>5.19842290878296</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>6.43499994277954</v>
       </c>
       <c r="G1333" t="n">
-        <v>5.30140352249146</v>
+        <v>5.3014030456543</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>6.57000017166138</v>
       </c>
       <c r="G1334" t="n">
-        <v>5.41262245178223</v>
+        <v>5.41262197494507</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G1335" t="n">
-        <v>5.33023738861084</v>
+        <v>5.33023691177368</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>6.55499982833862</v>
       </c>
       <c r="G1336" t="n">
-        <v>5.40026426315308</v>
+        <v>5.40026378631592</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>6.44500017166138</v>
       </c>
       <c r="G1337" t="n">
-        <v>5.30964136123657</v>
+        <v>5.30964183807373</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>6.16499996185303</v>
       </c>
       <c r="G1338" t="n">
-        <v>5.07896709442139</v>
+        <v>5.07896661758423</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1340" t="n">
-        <v>5.12427806854248</v>
+        <v>5.12427759170532</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G1342" t="n">
-        <v>5.22313833236694</v>
+        <v>5.22313928604126</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>6.63500022888184</v>
       </c>
       <c r="G1346" t="n">
-        <v>5.4661717414856</v>
+        <v>5.46617126464844</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G1348" t="n">
-        <v>5.63505792617798</v>
+        <v>5.63505887985229</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>6.86499977111816</v>
       </c>
       <c r="G1350" t="n">
-        <v>5.65565347671509</v>
+        <v>5.6556544303894</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G1351" t="n">
-        <v>5.54443550109863</v>
+        <v>5.54443597793579</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G1353" t="n">
-        <v>5.85749483108521</v>
+        <v>5.85749435424805</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>6.86499977111816</v>
       </c>
       <c r="G1356" t="n">
-        <v>5.65565347671509</v>
+        <v>5.6556544303894</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G1357" t="n">
-        <v>5.68448829650879</v>
+        <v>5.68448877334595</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G1358" t="n">
-        <v>5.72568035125732</v>
+        <v>5.72567987442017</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1360" t="n">
-        <v>5.84925651550293</v>
+        <v>5.84925603866577</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>6.95499992370605</v>
       </c>
       <c r="G1361" t="n">
-        <v>5.72979927062988</v>
+        <v>5.72979974746704</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1365" t="n">
-        <v>5.62401437759399</v>
+        <v>5.62401485443115</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G1367" t="n">
-        <v>5.54566097259521</v>
+        <v>5.54566144943237</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>6.31500005722046</v>
       </c>
       <c r="G1369" t="n">
-        <v>5.49777936935425</v>
+        <v>5.49777889251709</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -35989,7 +35989,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G1370" t="n">
-        <v>5.5108380317688</v>
+        <v>5.51083755493164</v>
       </c>
       <c r="H1370" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>6.31500005722046</v>
       </c>
       <c r="G1371" t="n">
-        <v>5.49777936935425</v>
+        <v>5.49777889251709</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>7.00500011444092</v>
       </c>
       <c r="G1387" t="n">
-        <v>6.09848642349243</v>
+        <v>6.09848690032959</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G1390" t="n">
-        <v>6.12025165557861</v>
+        <v>6.12025117874146</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G1391" t="n">
-        <v>5.82425117492676</v>
+        <v>5.8242506980896</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>7</v>
       </c>
       <c r="G1397" t="n">
-        <v>6.0941333770752</v>
+        <v>6.09413385391235</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G1398" t="n">
-        <v>5.98966264724731</v>
+        <v>5.98966312408447</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G1399" t="n">
-        <v>5.88519191741943</v>
+        <v>5.88519239425659</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G1404" t="n">
-        <v>6.12025165557861</v>
+        <v>6.12025117874146</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G1406" t="n">
-        <v>6.0070743560791</v>
+        <v>6.00707483291626</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -36951,7 +36951,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G1407" t="n">
-        <v>6.11154508590698</v>
+        <v>6.11154556274414</v>
       </c>
       <c r="H1407" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G1408" t="n">
-        <v>6.13766288757324</v>
+        <v>6.1376633644104</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>7.17500019073486</v>
       </c>
       <c r="G1410" t="n">
-        <v>6.24648761749268</v>
+        <v>6.24648714065552</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37081,7 +37081,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G1412" t="n">
-        <v>6.19860458374023</v>
+        <v>6.19860506057739</v>
       </c>
       <c r="H1412" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G1414" t="n">
-        <v>6.21601629257202</v>
+        <v>6.21601676940918</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G1416" t="n">
-        <v>6.30307531356812</v>
+        <v>6.30307579040527</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>7.19500017166138</v>
       </c>
       <c r="G1417" t="n">
-        <v>6.26389932632446</v>
+        <v>6.2638988494873</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37315,7 +37315,7 @@
         <v>7.17500019073486</v>
       </c>
       <c r="G1421" t="n">
-        <v>6.24648761749268</v>
+        <v>6.24648714065552</v>
       </c>
       <c r="H1421" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>7.30499982833862</v>
       </c>
       <c r="G1428" t="n">
-        <v>6.35966348648071</v>
+        <v>6.35966396331787</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>7.2649998664856</v>
       </c>
       <c r="G1430" t="n">
-        <v>6.3248405456543</v>
+        <v>6.32484006881714</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>7.45499992370605</v>
       </c>
       <c r="G1434" t="n">
-        <v>6.49025249481201</v>
+        <v>6.49025201797485</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>7.43499994277954</v>
       </c>
       <c r="G1439" t="n">
-        <v>6.47284078598022</v>
+        <v>6.47284030914307</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>7.31500005722046</v>
       </c>
       <c r="G1440" t="n">
-        <v>6.36837005615234</v>
+        <v>6.36836957931519</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>7.32499980926514</v>
       </c>
       <c r="G1443" t="n">
-        <v>6.3770751953125</v>
+        <v>6.37707567214966</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>7.43499994277954</v>
       </c>
       <c r="G1456" t="n">
-        <v>6.47284078598022</v>
+        <v>6.47284030914307</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>7.45499992370605</v>
       </c>
       <c r="G1458" t="n">
-        <v>6.49025249481201</v>
+        <v>6.49025201797485</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>7.88500022888184</v>
       </c>
       <c r="G1461" t="n">
-        <v>6.86460638046265</v>
+        <v>6.8646068572998</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1464" t="n">
-        <v>7.12143087387085</v>
+        <v>7.12143039703369</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1466" t="n">
-        <v>7.31296014785767</v>
+        <v>7.31295967102051</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G1467" t="n">
-        <v>7.33037281036377</v>
+        <v>7.33037233352661</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>8.44499969482422</v>
       </c>
       <c r="G1469" t="n">
-        <v>7.35213661193848</v>
+        <v>7.35213756561279</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38641,7 +38641,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G1472" t="n">
-        <v>7.45225477218628</v>
+        <v>7.45225524902344</v>
       </c>
       <c r="H1472" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G1474" t="n">
-        <v>7.35649013519287</v>
+        <v>7.35648965835571</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38875,7 +38875,7 @@
         <v>8.6899995803833</v>
       </c>
       <c r="G1481" t="n">
-        <v>7.56543159484863</v>
+        <v>7.56543111801147</v>
       </c>
       <c r="H1481" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G1482" t="n">
-        <v>7.64378452301025</v>
+        <v>7.6437840461731</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>9.41499996185303</v>
       </c>
       <c r="G1488" t="n">
-        <v>8.19660949707031</v>
+        <v>8.19661045074463</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39161,7 +39161,7 @@
         <v>9.71500015258789</v>
       </c>
       <c r="G1492" t="n">
-        <v>8.45778751373291</v>
+        <v>8.45778656005859</v>
       </c>
       <c r="H1492" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G1493" t="n">
-        <v>8.32284545898438</v>
+        <v>8.32284641265869</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G1494" t="n">
-        <v>8.34896278381348</v>
+        <v>8.34896373748779</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1497" t="n">
-        <v>8.21837520599365</v>
+        <v>8.21837425231934</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G1498" t="n">
-        <v>8.25319862365723</v>
+        <v>8.25319766998291</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G1505" t="n">
-        <v>8.29672813415527</v>
+        <v>8.29672718048096</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>9.4350004196167</v>
       </c>
       <c r="G1506" t="n">
-        <v>8.21402263641357</v>
+        <v>8.21402168273926</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39551,7 +39551,7 @@
         <v>9.34500026702881</v>
       </c>
       <c r="G1507" t="n">
-        <v>8.13566970825195</v>
+        <v>8.13566875457764</v>
       </c>
       <c r="H1507" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>9.33500003814697</v>
       </c>
       <c r="G1509" t="n">
-        <v>8.12696361541748</v>
+        <v>8.12696266174316</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>9.10499954223633</v>
       </c>
       <c r="G1513" t="n">
-        <v>7.92672681808472</v>
+        <v>7.9267258644104</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>9.0649995803833</v>
       </c>
       <c r="G1520" t="n">
-        <v>7.89190340042114</v>
+        <v>7.89190244674683</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G1521" t="n">
-        <v>8.00072574615479</v>
+        <v>8.0007266998291</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>9.15499973297119</v>
       </c>
       <c r="G1523" t="n">
-        <v>7.97025632858276</v>
+        <v>7.97025537490845</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>8.93000030517578</v>
       </c>
       <c r="G1525" t="n">
-        <v>7.77437400817871</v>
+        <v>7.77437305450439</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40201,7 +40201,7 @@
         <v>9.47000026702881</v>
       </c>
       <c r="G1532" t="n">
-        <v>8.24449253082275</v>
+        <v>8.24449348449707</v>
       </c>
       <c r="H1532" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>9.41499996185303</v>
       </c>
       <c r="G1533" t="n">
-        <v>8.19660949707031</v>
+        <v>8.19661045074463</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40279,7 +40279,7 @@
         <v>9.0649995803833</v>
       </c>
       <c r="G1535" t="n">
-        <v>7.89190340042114</v>
+        <v>7.89190244674683</v>
       </c>
       <c r="H1535" t="s">
         <v>8</v>
@@ -63222,7 +63222,7 @@
         <v>46310.2916666667</v>
       </c>
       <c r="B2418" t="n">
-        <v>5220367</v>
+        <v>5221367</v>
       </c>
       <c r="C2418" t="n">
         <v>2.30999994277954</v>
@@ -63240,6 +63240,32 @@
         <v>2.26999998092651</v>
       </c>
       <c r="H2418" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2419">
+      <c r="A2419" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B2419" t="n">
+        <v>5080146</v>
+      </c>
+      <c r="C2419" t="n">
+        <v>2.39000010490417</v>
+      </c>
+      <c r="D2419" t="n">
+        <v>2.24200010299683</v>
+      </c>
+      <c r="E2419" t="n">
+        <v>2.28800010681152</v>
+      </c>
+      <c r="F2419" t="n">
+        <v>2.26799988746643</v>
+      </c>
+      <c r="G2419" t="n">
+        <v>2.26799988746643</v>
+      </c>
+      <c r="H2419" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/BFF.MI.xlsx
+++ b/data/BFF.MI.xlsx
@@ -514,7 +514,7 @@
         <v>4.29400014877319</v>
       </c>
       <c r="G5" t="n">
-        <v>2.33858299255371</v>
+        <v>2.33858251571655</v>
       </c>
       <c r="H5" t="n">
         <v>392814</v>
@@ -543,7 +543,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G6" t="n">
-        <v>2.2601580619812</v>
+        <v>2.26015782356262</v>
       </c>
       <c r="H6" t="n">
         <v>1404759</v>
@@ -630,7 +630,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G9" t="n">
-        <v>2.2601580619812</v>
+        <v>2.26015782356262</v>
       </c>
       <c r="H9" t="n">
         <v>772016</v>
@@ -659,7 +659,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G10" t="n">
-        <v>2.22748112678528</v>
+        <v>2.2274808883667</v>
       </c>
       <c r="H10" t="n">
         <v>428382</v>
@@ -688,7 +688,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G11" t="n">
-        <v>2.26560401916504</v>
+        <v>2.26560425758362</v>
       </c>
       <c r="H11" t="n">
         <v>791191</v>
@@ -746,7 +746,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G13" t="n">
-        <v>2.3418505191803</v>
+        <v>2.34185028076172</v>
       </c>
       <c r="H13" t="n">
         <v>345195</v>
@@ -775,7 +775,7 @@
         <v>4.2979998588562</v>
       </c>
       <c r="G14" t="n">
-        <v>2.3407609462738</v>
+        <v>2.34076118469238</v>
       </c>
       <c r="H14" t="n">
         <v>134855</v>
@@ -804,7 +804,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G15" t="n">
-        <v>2.36363482475281</v>
+        <v>2.36363506317139</v>
       </c>
       <c r="H15" t="n">
         <v>270123</v>
@@ -833,7 +833,7 @@
         <v>4.36199998855591</v>
       </c>
       <c r="G16" t="n">
-        <v>2.37561655044556</v>
+        <v>2.37561678886414</v>
       </c>
       <c r="H16" t="n">
         <v>470779</v>
@@ -862,7 +862,7 @@
         <v>4.44600009918213</v>
       </c>
       <c r="G17" t="n">
-        <v>2.42136406898499</v>
+        <v>2.42136454582214</v>
       </c>
       <c r="H17" t="n">
         <v>136910</v>
@@ -891,7 +891,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G18" t="n">
-        <v>2.40720438957214</v>
+        <v>2.40720462799072</v>
       </c>
       <c r="H18" t="n">
         <v>216629</v>
@@ -920,7 +920,7 @@
         <v>4.4520001411438</v>
       </c>
       <c r="G19" t="n">
-        <v>2.42463207244873</v>
+        <v>2.42463231086731</v>
       </c>
       <c r="H19" t="n">
         <v>339492</v>
@@ -949,7 +949,7 @@
         <v>4.48600006103516</v>
       </c>
       <c r="G20" t="n">
-        <v>2.44314885139465</v>
+        <v>2.44314908981323</v>
       </c>
       <c r="H20" t="n">
         <v>218126</v>
@@ -978,7 +978,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G21" t="n">
-        <v>2.54335832595825</v>
+        <v>2.54335856437683</v>
       </c>
       <c r="H21" t="n">
         <v>983059</v>
@@ -1007,7 +1007,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G22" t="n">
-        <v>2.55969643592834</v>
+        <v>2.5596969127655</v>
       </c>
       <c r="H22" t="n">
         <v>1178689</v>
@@ -1036,7 +1036,7 @@
         <v>4.83599996566772</v>
       </c>
       <c r="G23" t="n">
-        <v>2.63376498222351</v>
+        <v>2.63376450538635</v>
       </c>
       <c r="H23" t="n">
         <v>2581507</v>
@@ -1065,7 +1065,7 @@
         <v>4.85400009155273</v>
       </c>
       <c r="G24" t="n">
-        <v>2.64356827735901</v>
+        <v>2.64356780052185</v>
       </c>
       <c r="H24" t="n">
         <v>436457</v>
@@ -1094,7 +1094,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G25" t="n">
-        <v>2.55969643592834</v>
+        <v>2.5596969127655</v>
       </c>
       <c r="H25" t="n">
         <v>657690</v>
@@ -1123,7 +1123,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G26" t="n">
-        <v>2.63049721717834</v>
+        <v>2.63049697875977</v>
       </c>
       <c r="H26" t="n">
         <v>546498</v>
@@ -1210,7 +1210,7 @@
         <v>4.73199987411499</v>
       </c>
       <c r="G29" t="n">
-        <v>2.57712435722351</v>
+        <v>2.57712459564209</v>
       </c>
       <c r="H29" t="n">
         <v>243474</v>
@@ -1239,7 +1239,7 @@
         <v>4.74200010299683</v>
       </c>
       <c r="G30" t="n">
-        <v>2.58257079124451</v>
+        <v>2.58257102966309</v>
       </c>
       <c r="H30" t="n">
         <v>138384</v>
@@ -1268,7 +1268,7 @@
         <v>4.83799982070923</v>
       </c>
       <c r="G31" t="n">
-        <v>2.63485407829285</v>
+        <v>2.63485383987427</v>
       </c>
       <c r="H31" t="n">
         <v>253749</v>
@@ -1297,7 +1297,7 @@
         <v>4.77600002288818</v>
       </c>
       <c r="G32" t="n">
-        <v>2.60108757019043</v>
+        <v>2.60108780860901</v>
       </c>
       <c r="H32" t="n">
         <v>224481</v>
@@ -1355,7 +1355,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G34" t="n">
-        <v>2.66317391395569</v>
+        <v>2.66317415237427</v>
       </c>
       <c r="H34" t="n">
         <v>156895</v>
@@ -1413,7 +1413,7 @@
         <v>4.89799976348877</v>
       </c>
       <c r="G36" t="n">
-        <v>2.66753077507019</v>
+        <v>2.66753101348877</v>
       </c>
       <c r="H36" t="n">
         <v>234988</v>
@@ -1471,7 +1471,7 @@
         <v>4.94799995422363</v>
       </c>
       <c r="G38" t="n">
-        <v>2.69476175308228</v>
+        <v>2.69476127624512</v>
       </c>
       <c r="H38" t="n">
         <v>178328</v>
@@ -1500,7 +1500,7 @@
         <v>4.92199993133545</v>
       </c>
       <c r="G39" t="n">
-        <v>2.68060159683228</v>
+        <v>2.6806013584137</v>
       </c>
       <c r="H39" t="n">
         <v>31918</v>
@@ -1587,7 +1587,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G42" t="n">
-        <v>2.65772771835327</v>
+        <v>2.65772747993469</v>
       </c>
       <c r="H42" t="n">
         <v>195614</v>
@@ -1674,7 +1674,7 @@
         <v>4.84600019454956</v>
       </c>
       <c r="G45" t="n">
-        <v>2.63921117782593</v>
+        <v>2.63921093940735</v>
       </c>
       <c r="H45" t="n">
         <v>152647</v>
@@ -1703,7 +1703,7 @@
         <v>4.89599990844727</v>
       </c>
       <c r="G46" t="n">
-        <v>2.66644167900085</v>
+        <v>2.66644191741943</v>
       </c>
       <c r="H46" t="n">
         <v>263706</v>
@@ -1761,7 +1761,7 @@
         <v>5.07499980926514</v>
       </c>
       <c r="G48" t="n">
-        <v>2.76392793655396</v>
+        <v>2.76392769813538</v>
       </c>
       <c r="H48" t="n">
         <v>196923</v>
@@ -1790,7 +1790,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G49" t="n">
-        <v>2.72852826118469</v>
+        <v>2.72852802276611</v>
       </c>
       <c r="H49" t="n">
         <v>1316892</v>
@@ -1819,7 +1819,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G50" t="n">
-        <v>2.77754354476929</v>
+        <v>2.77754330635071</v>
       </c>
       <c r="H50" t="n">
         <v>289872</v>
@@ -1848,7 +1848,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G51" t="n">
-        <v>2.81022000312805</v>
+        <v>2.81022071838379</v>
       </c>
       <c r="H51" t="n">
         <v>347203</v>
@@ -1877,7 +1877,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G52" t="n">
-        <v>2.82111287117004</v>
+        <v>2.82111263275146</v>
       </c>
       <c r="H52" t="n">
         <v>326242</v>
@@ -1906,7 +1906,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G53" t="n">
-        <v>2.80749750137329</v>
+        <v>2.80749773979187</v>
       </c>
       <c r="H53" t="n">
         <v>204010</v>
@@ -1935,7 +1935,7 @@
         <v>5</v>
       </c>
       <c r="G54" t="n">
-        <v>2.72308158874512</v>
+        <v>2.7230818271637</v>
       </c>
       <c r="H54" t="n">
         <v>408160</v>
@@ -1964,7 +1964,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G55" t="n">
-        <v>2.76120495796204</v>
+        <v>2.76120471954346</v>
       </c>
       <c r="H55" t="n">
         <v>232368</v>
@@ -2022,7 +2022,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G57" t="n">
-        <v>2.84289717674255</v>
+        <v>2.84289741516113</v>
       </c>
       <c r="H57" t="n">
         <v>238257</v>
@@ -2051,7 +2051,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G58" t="n">
-        <v>2.81022000312805</v>
+        <v>2.81022071838379</v>
       </c>
       <c r="H58" t="n">
         <v>260985</v>
@@ -2080,7 +2080,7 @@
         <v>5</v>
       </c>
       <c r="G59" t="n">
-        <v>2.72308158874512</v>
+        <v>2.7230818271637</v>
       </c>
       <c r="H59" t="n">
         <v>282562</v>
@@ -2138,7 +2138,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G61" t="n">
-        <v>2.79932832717896</v>
+        <v>2.7993278503418</v>
       </c>
       <c r="H61" t="n">
         <v>158805</v>
@@ -2196,7 +2196,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G63" t="n">
-        <v>2.79932832717896</v>
+        <v>2.7993278503418</v>
       </c>
       <c r="H63" t="n">
         <v>150641</v>
@@ -2225,7 +2225,7 @@
         <v>5.16499996185303</v>
       </c>
       <c r="G64" t="n">
-        <v>2.81294345855713</v>
+        <v>2.81294322013855</v>
       </c>
       <c r="H64" t="n">
         <v>39984</v>
@@ -2283,7 +2283,7 @@
         <v>5.07499980926514</v>
       </c>
       <c r="G66" t="n">
-        <v>2.76392793655396</v>
+        <v>2.76392769813538</v>
       </c>
       <c r="H66" t="n">
         <v>89307</v>
@@ -2370,7 +2370,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G69" t="n">
-        <v>2.78843545913696</v>
+        <v>2.78843569755554</v>
       </c>
       <c r="H69" t="n">
         <v>225985</v>
@@ -2399,7 +2399,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G70" t="n">
-        <v>2.80477452278137</v>
+        <v>2.80477476119995</v>
       </c>
       <c r="H70" t="n">
         <v>110557</v>
@@ -2428,7 +2428,7 @@
         <v>5.07499980926514</v>
       </c>
       <c r="G71" t="n">
-        <v>2.76392793655396</v>
+        <v>2.76392769813538</v>
       </c>
       <c r="H71" t="n">
         <v>212116</v>
@@ -2457,7 +2457,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G72" t="n">
-        <v>2.78026652336121</v>
+        <v>2.78026628494263</v>
       </c>
       <c r="H72" t="n">
         <v>78741</v>
@@ -2486,7 +2486,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G73" t="n">
-        <v>2.78026652336121</v>
+        <v>2.78026628494263</v>
       </c>
       <c r="H73" t="n">
         <v>162459</v>
@@ -2515,7 +2515,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G74" t="n">
-        <v>2.78843545913696</v>
+        <v>2.78843569755554</v>
       </c>
       <c r="H74" t="n">
         <v>163329</v>
@@ -2544,7 +2544,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G75" t="n">
-        <v>2.80477452278137</v>
+        <v>2.80477476119995</v>
       </c>
       <c r="H75" t="n">
         <v>69294</v>
@@ -2631,7 +2631,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G78" t="n">
-        <v>2.78843545913696</v>
+        <v>2.78843569755554</v>
       </c>
       <c r="H78" t="n">
         <v>136329</v>
@@ -2660,7 +2660,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G79" t="n">
-        <v>2.82655930519104</v>
+        <v>2.82655882835388</v>
       </c>
       <c r="H79" t="n">
         <v>89963</v>
@@ -2689,7 +2689,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G80" t="n">
-        <v>2.82111287117004</v>
+        <v>2.82111263275146</v>
       </c>
       <c r="H80" t="n">
         <v>96649</v>
@@ -2718,7 +2718,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G81" t="n">
-        <v>2.80477452278137</v>
+        <v>2.80477476119995</v>
       </c>
       <c r="H81" t="n">
         <v>169020</v>
@@ -2747,7 +2747,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G82" t="n">
-        <v>2.80477452278137</v>
+        <v>2.80477476119995</v>
       </c>
       <c r="H82" t="n">
         <v>173934</v>
@@ -2776,7 +2776,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G83" t="n">
-        <v>2.80477452278137</v>
+        <v>2.80477476119995</v>
       </c>
       <c r="H83" t="n">
         <v>134385</v>
@@ -2805,7 +2805,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G84" t="n">
-        <v>2.79932832717896</v>
+        <v>2.7993278503418</v>
       </c>
       <c r="H84" t="n">
         <v>92528</v>
@@ -2834,7 +2834,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G85" t="n">
-        <v>2.80749750137329</v>
+        <v>2.80749773979187</v>
       </c>
       <c r="H85" t="n">
         <v>646041</v>
@@ -2863,7 +2863,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G86" t="n">
-        <v>2.80477452278137</v>
+        <v>2.80477476119995</v>
       </c>
       <c r="H86" t="n">
         <v>338706</v>
@@ -2921,7 +2921,7 @@
         <v>5.13500022888184</v>
       </c>
       <c r="G88" t="n">
-        <v>2.79660511016846</v>
+        <v>2.79660487174988</v>
       </c>
       <c r="H88" t="n">
         <v>115656</v>
@@ -2950,7 +2950,7 @@
         <v>5.08500003814697</v>
       </c>
       <c r="G89" t="n">
-        <v>2.76937437057495</v>
+        <v>2.76937413215637</v>
       </c>
       <c r="H89" t="n">
         <v>158274</v>
@@ -3008,7 +3008,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G91" t="n">
-        <v>2.83745145797729</v>
+        <v>2.83745121955872</v>
       </c>
       <c r="H91" t="n">
         <v>178885</v>
@@ -3066,7 +3066,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G93" t="n">
-        <v>2.80749750137329</v>
+        <v>2.80749773979187</v>
       </c>
       <c r="H93" t="n">
         <v>91566</v>
@@ -3095,7 +3095,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G94" t="n">
-        <v>2.80749750137329</v>
+        <v>2.80749773979187</v>
       </c>
       <c r="H94" t="n">
         <v>86354</v>
@@ -3124,7 +3124,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G95" t="n">
-        <v>2.79932832717896</v>
+        <v>2.7993278503418</v>
       </c>
       <c r="H95" t="n">
         <v>110787</v>
@@ -3153,7 +3153,7 @@
         <v>5.16499996185303</v>
       </c>
       <c r="G96" t="n">
-        <v>2.81294345855713</v>
+        <v>2.81294322013855</v>
       </c>
       <c r="H96" t="n">
         <v>55521</v>
@@ -3211,7 +3211,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G98" t="n">
-        <v>2.79932832717896</v>
+        <v>2.7993278503418</v>
       </c>
       <c r="H98" t="n">
         <v>73538</v>
@@ -3240,7 +3240,7 @@
         <v>5.11499977111816</v>
       </c>
       <c r="G99" t="n">
-        <v>2.78571271896362</v>
+        <v>2.78571224212646</v>
       </c>
       <c r="H99" t="n">
         <v>76893</v>
@@ -3269,7 +3269,7 @@
         <v>4.9520001411438</v>
       </c>
       <c r="G100" t="n">
-        <v>2.69694018363953</v>
+        <v>2.69694042205811</v>
       </c>
       <c r="H100" t="n">
         <v>430990</v>
@@ -3298,7 +3298,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G101" t="n">
-        <v>2.69585084915161</v>
+        <v>2.69585061073303</v>
       </c>
       <c r="H101" t="n">
         <v>151734</v>
@@ -3327,7 +3327,7 @@
         <v>4.99200010299683</v>
       </c>
       <c r="G102" t="n">
-        <v>2.71872544288635</v>
+        <v>2.71872520446777</v>
       </c>
       <c r="H102" t="n">
         <v>128275</v>
@@ -3356,7 +3356,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G103" t="n">
-        <v>2.73942065238953</v>
+        <v>2.73942041397095</v>
       </c>
       <c r="H103" t="n">
         <v>67808</v>
@@ -3385,7 +3385,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G104" t="n">
-        <v>2.81022000312805</v>
+        <v>2.81022071838379</v>
       </c>
       <c r="H104" t="n">
         <v>322247</v>
@@ -3414,7 +3414,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G105" t="n">
-        <v>2.77754354476929</v>
+        <v>2.77754330635071</v>
       </c>
       <c r="H105" t="n">
         <v>176036</v>
@@ -3443,7 +3443,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G106" t="n">
-        <v>2.78026652336121</v>
+        <v>2.78026628494263</v>
       </c>
       <c r="H106" t="n">
         <v>70314</v>
@@ -3472,7 +3472,7 @@
         <v>5.08500003814697</v>
       </c>
       <c r="G107" t="n">
-        <v>2.76937437057495</v>
+        <v>2.76937413215637</v>
       </c>
       <c r="H107" t="n">
         <v>55988</v>
@@ -3530,7 +3530,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G109" t="n">
-        <v>2.78843545913696</v>
+        <v>2.78843569755554</v>
       </c>
       <c r="H109" t="n">
         <v>78441</v>
@@ -3559,7 +3559,7 @@
         <v>5.16499996185303</v>
       </c>
       <c r="G110" t="n">
-        <v>2.81294345855713</v>
+        <v>2.81294322013855</v>
       </c>
       <c r="H110" t="n">
         <v>155443</v>
@@ -3588,7 +3588,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G111" t="n">
-        <v>2.84834337234497</v>
+        <v>2.84834361076355</v>
       </c>
       <c r="H111" t="n">
         <v>187422</v>
@@ -3675,7 +3675,7 @@
         <v>5.50500011444092</v>
       </c>
       <c r="G114" t="n">
-        <v>2.99811291694641</v>
+        <v>2.99811339378357</v>
       </c>
       <c r="H114" t="n">
         <v>826293</v>
@@ -3704,7 +3704,7 @@
         <v>5.49499988555908</v>
       </c>
       <c r="G115" t="n">
-        <v>2.99266648292542</v>
+        <v>2.99266672134399</v>
       </c>
       <c r="H115" t="n">
         <v>356186</v>
@@ -3733,7 +3733,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G116" t="n">
-        <v>3.02806687355042</v>
+        <v>3.02806663513184</v>
       </c>
       <c r="H116" t="n">
         <v>223092</v>
@@ -3762,7 +3762,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G117" t="n">
-        <v>3.03895974159241</v>
+        <v>3.03895902633667</v>
       </c>
       <c r="H117" t="n">
         <v>490409</v>
@@ -3791,7 +3791,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G118" t="n">
-        <v>3.00628161430359</v>
+        <v>3.00628209114075</v>
       </c>
       <c r="H118" t="n">
         <v>307618</v>
@@ -3820,7 +3820,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G119" t="n">
-        <v>3.08797454833984</v>
+        <v>3.08797478675842</v>
       </c>
       <c r="H119" t="n">
         <v>355437</v>
@@ -3849,7 +3849,7 @@
         <v>5.67500019073486</v>
       </c>
       <c r="G120" t="n">
-        <v>3.09069776535034</v>
+        <v>3.0906982421875</v>
       </c>
       <c r="H120" t="n">
         <v>228201</v>
@@ -3878,7 +3878,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G121" t="n">
-        <v>3.2404670715332</v>
+        <v>3.24046754837036</v>
       </c>
       <c r="H121" t="n">
         <v>464316</v>
@@ -3907,7 +3907,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G122" t="n">
-        <v>3.2132363319397</v>
+        <v>3.21323657035828</v>
       </c>
       <c r="H122" t="n">
         <v>312872</v>
@@ -3936,7 +3936,7 @@
         <v>5.75</v>
       </c>
       <c r="G123" t="n">
-        <v>3.1315438747406</v>
+        <v>3.13154411315918</v>
       </c>
       <c r="H123" t="n">
         <v>633225</v>
@@ -3965,7 +3965,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G124" t="n">
-        <v>3.19689774513245</v>
+        <v>3.19689798355103</v>
       </c>
       <c r="H124" t="n">
         <v>236136</v>
@@ -3994,7 +3994,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G125" t="n">
-        <v>3.1260974407196</v>
+        <v>3.12609767913818</v>
       </c>
       <c r="H125" t="n">
         <v>258170</v>
@@ -4023,7 +4023,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G126" t="n">
-        <v>3.07708287239075</v>
+        <v>3.07708263397217</v>
       </c>
       <c r="H126" t="n">
         <v>291514</v>
@@ -4052,7 +4052,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G127" t="n">
-        <v>3.14243626594543</v>
+        <v>3.14243650436401</v>
       </c>
       <c r="H127" t="n">
         <v>218228</v>
@@ -4081,7 +4081,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G128" t="n">
-        <v>3.10431337356567</v>
+        <v>3.10431289672852</v>
       </c>
       <c r="H128" t="n">
         <v>185479</v>
@@ -4110,7 +4110,7 @@
         <v>5.72499990463257</v>
       </c>
       <c r="G129" t="n">
-        <v>3.11792874336243</v>
+        <v>3.11792850494385</v>
       </c>
       <c r="H129" t="n">
         <v>166825</v>
@@ -4139,7 +4139,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G130" t="n">
-        <v>3.15877437591553</v>
+        <v>3.15877509117126</v>
       </c>
       <c r="H130" t="n">
         <v>217232</v>
@@ -4197,7 +4197,7 @@
         <v>5.875</v>
       </c>
       <c r="G132" t="n">
-        <v>3.19962096214294</v>
+        <v>3.19962072372437</v>
       </c>
       <c r="H132" t="n">
         <v>107432</v>
@@ -4226,7 +4226,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G133" t="n">
-        <v>3.32215976715088</v>
+        <v>3.32215905189514</v>
       </c>
       <c r="H133" t="n">
         <v>490719</v>
@@ -4284,7 +4284,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G135" t="n">
-        <v>3.30582165718079</v>
+        <v>3.30582141876221</v>
       </c>
       <c r="H135" t="n">
         <v>362617</v>
@@ -4342,7 +4342,7 @@
         <v>6.04500007629395</v>
       </c>
       <c r="G137" t="n">
-        <v>3.29220604896545</v>
+        <v>3.29220581054688</v>
       </c>
       <c r="H137" t="n">
         <v>375661</v>
@@ -4429,7 +4429,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G140" t="n">
-        <v>3.33305239677429</v>
+        <v>3.33305191993713</v>
       </c>
       <c r="H140" t="n">
         <v>196694</v>
@@ -4458,7 +4458,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G141" t="n">
-        <v>3.32215976715088</v>
+        <v>3.32215905189514</v>
       </c>
       <c r="H141" t="n">
         <v>185465</v>
@@ -4487,7 +4487,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G142" t="n">
-        <v>3.34939050674438</v>
+        <v>3.34939074516296</v>
       </c>
       <c r="H142" t="n">
         <v>178387</v>
@@ -4545,7 +4545,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G144" t="n">
-        <v>3.38751363754272</v>
+        <v>3.38751339912415</v>
       </c>
       <c r="H144" t="n">
         <v>271554</v>
@@ -4574,7 +4574,7 @@
         <v>6.25</v>
       </c>
       <c r="G145" t="n">
-        <v>3.40385222434998</v>
+        <v>3.40385174751282</v>
       </c>
       <c r="H145" t="n">
         <v>169413</v>
@@ -4603,7 +4603,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G146" t="n">
-        <v>3.38206791877747</v>
+        <v>3.38206768035889</v>
       </c>
       <c r="H146" t="n">
         <v>189558</v>
@@ -4661,7 +4661,7 @@
         <v>6.02500009536743</v>
       </c>
       <c r="G148" t="n">
-        <v>3.28131365776062</v>
+        <v>3.28131341934204</v>
       </c>
       <c r="H148" t="n">
         <v>424488</v>
@@ -4690,7 +4690,7 @@
         <v>6.00500011444092</v>
       </c>
       <c r="G149" t="n">
-        <v>3.27042126655579</v>
+        <v>3.27042174339294</v>
       </c>
       <c r="H149" t="n">
         <v>352526</v>
@@ -4719,7 +4719,7 @@
         <v>6.09499979019165</v>
       </c>
       <c r="G150" t="n">
-        <v>3.31943702697754</v>
+        <v>3.3194363117218</v>
       </c>
       <c r="H150" t="n">
         <v>360242</v>
@@ -4748,7 +4748,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G151" t="n">
-        <v>3.28403687477112</v>
+        <v>3.28403663635254</v>
       </c>
       <c r="H151" t="n">
         <v>1050651</v>
@@ -4835,7 +4835,7 @@
         <v>5.92999982833862</v>
       </c>
       <c r="G154" t="n">
-        <v>3.22957468032837</v>
+        <v>3.22957491874695</v>
       </c>
       <c r="H154" t="n">
         <v>449614</v>
@@ -4864,7 +4864,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G155" t="n">
-        <v>3.2132363319397</v>
+        <v>3.21323657035828</v>
       </c>
       <c r="H155" t="n">
         <v>247331</v>
@@ -4893,7 +4893,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G156" t="n">
-        <v>3.27314448356628</v>
+        <v>3.27314400672913</v>
       </c>
       <c r="H156" t="n">
         <v>248030</v>
@@ -4951,7 +4951,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G158" t="n">
-        <v>3.32760572433472</v>
+        <v>3.3276059627533</v>
       </c>
       <c r="H158" t="n">
         <v>187242</v>
@@ -5038,7 +5038,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G161" t="n">
-        <v>3.38206791877747</v>
+        <v>3.38206768035889</v>
       </c>
       <c r="H161" t="n">
         <v>102667</v>
@@ -5067,7 +5067,7 @@
         <v>6.40999984741211</v>
       </c>
       <c r="G162" t="n">
-        <v>3.49099016189575</v>
+        <v>3.49099135398865</v>
       </c>
       <c r="H162" t="n">
         <v>474666</v>
@@ -5096,7 +5096,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G163" t="n">
-        <v>3.51277565956116</v>
+        <v>3.51277542114258</v>
       </c>
       <c r="H163" t="n">
         <v>427038</v>
@@ -5154,7 +5154,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G165" t="n">
-        <v>3.45831394195557</v>
+        <v>3.45831346511841</v>
       </c>
       <c r="H165" t="n">
         <v>177233</v>
@@ -5183,7 +5183,7 @@
         <v>6.41499996185303</v>
       </c>
       <c r="G166" t="n">
-        <v>3.49371385574341</v>
+        <v>3.49371409416199</v>
       </c>
       <c r="H166" t="n">
         <v>319302</v>
@@ -5212,7 +5212,7 @@
         <v>6.45499992370605</v>
       </c>
       <c r="G167" t="n">
-        <v>3.51549863815308</v>
+        <v>3.51549816131592</v>
       </c>
       <c r="H167" t="n">
         <v>1366720</v>
@@ -5241,7 +5241,7 @@
         <v>6.36499977111816</v>
       </c>
       <c r="G168" t="n">
-        <v>3.4664831161499</v>
+        <v>3.46648263931274</v>
       </c>
       <c r="H168" t="n">
         <v>241433</v>
@@ -5328,7 +5328,7 @@
         <v>6.40999984741211</v>
       </c>
       <c r="G171" t="n">
-        <v>3.49099016189575</v>
+        <v>3.49099135398865</v>
       </c>
       <c r="H171" t="n">
         <v>199264</v>
@@ -5357,7 +5357,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G172" t="n">
-        <v>3.58357524871826</v>
+        <v>3.583575963974</v>
       </c>
       <c r="H172" t="n">
         <v>262965</v>
@@ -5386,7 +5386,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G173" t="n">
-        <v>3.56179094314575</v>
+        <v>3.56179070472717</v>
       </c>
       <c r="H173" t="n">
         <v>238411</v>
@@ -5415,7 +5415,7 @@
         <v>6.58500003814697</v>
       </c>
       <c r="G174" t="n">
-        <v>3.58629846572876</v>
+        <v>3.58629894256592</v>
       </c>
       <c r="H174" t="n">
         <v>218569</v>
@@ -5444,7 +5444,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G175" t="n">
-        <v>3.5944676399231</v>
+        <v>3.59446740150452</v>
       </c>
       <c r="H175" t="n">
         <v>269404</v>
@@ -5473,7 +5473,7 @@
         <v>6.53000020980835</v>
       </c>
       <c r="G176" t="n">
-        <v>3.55634450912476</v>
+        <v>3.55634522438049</v>
       </c>
       <c r="H176" t="n">
         <v>106003</v>
@@ -5502,7 +5502,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G177" t="n">
-        <v>3.52366805076599</v>
+        <v>3.52366781234741</v>
       </c>
       <c r="H177" t="n">
         <v>239018</v>
@@ -5531,7 +5531,7 @@
         <v>6.53499984741211</v>
       </c>
       <c r="G178" t="n">
-        <v>3.55906820297241</v>
+        <v>3.55906772613525</v>
       </c>
       <c r="H178" t="n">
         <v>1769120</v>
@@ -5589,7 +5589,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G180" t="n">
-        <v>3.61080646514893</v>
+        <v>3.6108067035675</v>
       </c>
       <c r="H180" t="n">
         <v>190579</v>
@@ -5618,7 +5618,7 @@
         <v>6.375</v>
       </c>
       <c r="G181" t="n">
-        <v>3.47192931175232</v>
+        <v>3.47192883491516</v>
       </c>
       <c r="H181" t="n">
         <v>417337</v>
@@ -5676,7 +5676,7 @@
         <v>6.25</v>
       </c>
       <c r="G183" t="n">
-        <v>3.40385222434998</v>
+        <v>3.40385174751282</v>
       </c>
       <c r="H183" t="n">
         <v>163948</v>
@@ -5705,7 +5705,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G184" t="n">
-        <v>3.44742202758789</v>
+        <v>3.44742131233215</v>
       </c>
       <c r="H184" t="n">
         <v>187122</v>
@@ -5734,7 +5734,7 @@
         <v>6.38500022888184</v>
       </c>
       <c r="G185" t="n">
-        <v>3.47737598419189</v>
+        <v>3.47737503051758</v>
       </c>
       <c r="H185" t="n">
         <v>256687</v>
@@ -5763,7 +5763,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G186" t="n">
-        <v>3.48554515838623</v>
+        <v>3.48554468154907</v>
       </c>
       <c r="H186" t="n">
         <v>124137</v>
@@ -5792,7 +5792,7 @@
         <v>6.41499996185303</v>
       </c>
       <c r="G187" t="n">
-        <v>3.49371385574341</v>
+        <v>3.49371409416199</v>
       </c>
       <c r="H187" t="n">
         <v>155738</v>
@@ -5821,7 +5821,7 @@
         <v>6.53499984741211</v>
       </c>
       <c r="G188" t="n">
-        <v>3.55906820297241</v>
+        <v>3.55906772613525</v>
       </c>
       <c r="H188" t="n">
         <v>188172</v>
@@ -5850,7 +5850,7 @@
         <v>6.5</v>
       </c>
       <c r="G189" t="n">
-        <v>3.54000616073608</v>
+        <v>3.54000663757324</v>
       </c>
       <c r="H189" t="n">
         <v>147545</v>
@@ -5879,7 +5879,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G190" t="n">
-        <v>3.54545307159424</v>
+        <v>3.5454523563385</v>
       </c>
       <c r="H190" t="n">
         <v>100540</v>
@@ -5908,7 +5908,7 @@
         <v>6.5</v>
       </c>
       <c r="G191" t="n">
-        <v>3.54000616073608</v>
+        <v>3.54000663757324</v>
       </c>
       <c r="H191" t="n">
         <v>187692</v>
@@ -5966,7 +5966,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G193" t="n">
-        <v>3.56179094314575</v>
+        <v>3.56179070472717</v>
       </c>
       <c r="H193" t="n">
         <v>366351</v>
@@ -6024,7 +6024,7 @@
         <v>6.46500015258789</v>
       </c>
       <c r="G195" t="n">
-        <v>3.52094483375549</v>
+        <v>3.52094507217407</v>
       </c>
       <c r="H195" t="n">
         <v>418341</v>
@@ -6053,7 +6053,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G196" t="n">
-        <v>3.52911448478699</v>
+        <v>3.52911376953125</v>
       </c>
       <c r="H196" t="n">
         <v>260163</v>
@@ -6082,7 +6082,7 @@
         <v>6.5</v>
       </c>
       <c r="G197" t="n">
-        <v>3.54000616073608</v>
+        <v>3.54000663757324</v>
       </c>
       <c r="H197" t="n">
         <v>305887</v>
@@ -6111,7 +6111,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G198" t="n">
-        <v>3.54545307159424</v>
+        <v>3.5454523563385</v>
       </c>
       <c r="H198" t="n">
         <v>218115</v>
@@ -6140,7 +6140,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G199" t="n">
-        <v>3.54545307159424</v>
+        <v>3.5454523563385</v>
       </c>
       <c r="H199" t="n">
         <v>236976</v>
@@ -6169,7 +6169,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G200" t="n">
-        <v>3.54545307159424</v>
+        <v>3.5454523563385</v>
       </c>
       <c r="H200" t="n">
         <v>242488</v>
@@ -6227,7 +6227,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G202" t="n">
-        <v>3.58902192115784</v>
+        <v>3.58902168273926</v>
       </c>
       <c r="H202" t="n">
         <v>254633</v>
@@ -6256,7 +6256,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G203" t="n">
-        <v>3.5944676399231</v>
+        <v>3.59446740150452</v>
       </c>
       <c r="H203" t="n">
         <v>289318</v>
@@ -6285,7 +6285,7 @@
         <v>6.53000020980835</v>
       </c>
       <c r="G204" t="n">
-        <v>3.55634450912476</v>
+        <v>3.55634522438049</v>
       </c>
       <c r="H204" t="n">
         <v>263917</v>
@@ -6314,7 +6314,7 @@
         <v>6.59499979019165</v>
       </c>
       <c r="G205" t="n">
-        <v>3.5917444229126</v>
+        <v>3.59174513816833</v>
       </c>
       <c r="H205" t="n">
         <v>305878</v>
@@ -6372,7 +6372,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G207" t="n">
-        <v>3.54545307159424</v>
+        <v>3.5454523563385</v>
       </c>
       <c r="H207" t="n">
         <v>240046</v>
@@ -6401,7 +6401,7 @@
         <v>6.4850001335144</v>
       </c>
       <c r="G208" t="n">
-        <v>3.53183674812317</v>
+        <v>3.53183698654175</v>
       </c>
       <c r="H208" t="n">
         <v>191731</v>
@@ -6430,7 +6430,7 @@
         <v>6.41499996185303</v>
       </c>
       <c r="G209" t="n">
-        <v>3.49371385574341</v>
+        <v>3.49371409416199</v>
       </c>
       <c r="H209" t="n">
         <v>424467</v>
@@ -6459,7 +6459,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G210" t="n">
-        <v>3.29492902755737</v>
+        <v>3.29492950439453</v>
       </c>
       <c r="H210" t="n">
         <v>1379424</v>
@@ -6488,7 +6488,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G211" t="n">
-        <v>3.28403687477112</v>
+        <v>3.28403663635254</v>
       </c>
       <c r="H211" t="n">
         <v>569842</v>
@@ -6575,7 +6575,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G214" t="n">
-        <v>3.12065148353577</v>
+        <v>3.12065172195435</v>
       </c>
       <c r="H214" t="n">
         <v>491862</v>
@@ -6604,7 +6604,7 @@
         <v>5.92999982833862</v>
       </c>
       <c r="G215" t="n">
-        <v>3.22957468032837</v>
+        <v>3.22957491874695</v>
       </c>
       <c r="H215" t="n">
         <v>595831</v>
@@ -6633,7 +6633,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G216" t="n">
-        <v>3.16966724395752</v>
+        <v>3.16966700553894</v>
       </c>
       <c r="H216" t="n">
         <v>367575</v>
@@ -6662,7 +6662,7 @@
         <v>5.81500005722046</v>
       </c>
       <c r="G217" t="n">
-        <v>3.16694402694702</v>
+        <v>3.1669442653656</v>
       </c>
       <c r="H217" t="n">
         <v>376884</v>
@@ -6749,7 +6749,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G220" t="n">
-        <v>3.38206791877747</v>
+        <v>3.38206768035889</v>
       </c>
       <c r="H220" t="n">
         <v>329166</v>
@@ -6778,7 +6778,7 @@
         <v>6.14499998092651</v>
       </c>
       <c r="G221" t="n">
-        <v>3.34666752815247</v>
+        <v>3.34666776657104</v>
       </c>
       <c r="H221" t="n">
         <v>229142</v>
@@ -6836,7 +6836,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G223" t="n">
-        <v>3.2132363319397</v>
+        <v>3.21323657035828</v>
       </c>
       <c r="H223" t="n">
         <v>6562008</v>
@@ -6865,7 +6865,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G224" t="n">
-        <v>3.18055987358093</v>
+        <v>3.1805591583252</v>
       </c>
       <c r="H224" t="n">
         <v>610892</v>
@@ -6894,7 +6894,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G225" t="n">
-        <v>3.16966724395752</v>
+        <v>3.16966700553894</v>
       </c>
       <c r="H225" t="n">
         <v>433654</v>
@@ -6923,7 +6923,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G226" t="n">
-        <v>3.16966724395752</v>
+        <v>3.16966700553894</v>
       </c>
       <c r="H226" t="n">
         <v>403818</v>
@@ -6952,7 +6952,7 @@
         <v>5.81500005722046</v>
       </c>
       <c r="G227" t="n">
-        <v>3.16694402694702</v>
+        <v>3.1669442653656</v>
       </c>
       <c r="H227" t="n">
         <v>613256</v>
@@ -7039,7 +7039,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G230" t="n">
-        <v>3.17511320114136</v>
+        <v>3.17511343955994</v>
       </c>
       <c r="H230" t="n">
         <v>422499</v>
@@ -7097,7 +7097,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G232" t="n">
-        <v>3.15877437591553</v>
+        <v>3.15877509117126</v>
       </c>
       <c r="H232" t="n">
         <v>351826</v>
@@ -7126,7 +7126,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G233" t="n">
-        <v>3.15332841873169</v>
+        <v>3.15332913398743</v>
       </c>
       <c r="H233" t="n">
         <v>666571</v>
@@ -7155,7 +7155,7 @@
         <v>5.88500022888184</v>
       </c>
       <c r="G234" t="n">
-        <v>3.20506739616394</v>
+        <v>3.20506763458252</v>
       </c>
       <c r="H234" t="n">
         <v>425600</v>
@@ -7184,7 +7184,7 @@
         <v>5.95499992370605</v>
       </c>
       <c r="G235" t="n">
-        <v>3.24319076538086</v>
+        <v>3.2431902885437</v>
       </c>
       <c r="H235" t="n">
         <v>392036</v>
@@ -7213,7 +7213,7 @@
         <v>6.04500007629395</v>
       </c>
       <c r="G236" t="n">
-        <v>3.29220604896545</v>
+        <v>3.29220581054688</v>
       </c>
       <c r="H236" t="n">
         <v>640079</v>
@@ -7242,7 +7242,7 @@
         <v>5.95499992370605</v>
       </c>
       <c r="G237" t="n">
-        <v>3.24319076538086</v>
+        <v>3.2431902885437</v>
       </c>
       <c r="H237" t="n">
         <v>445041</v>
@@ -7271,7 +7271,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G238" t="n">
-        <v>3.2404670715332</v>
+        <v>3.24046754837036</v>
       </c>
       <c r="H238" t="n">
         <v>309233</v>
@@ -7300,7 +7300,7 @@
         <v>5.88500022888184</v>
       </c>
       <c r="G239" t="n">
-        <v>3.20506739616394</v>
+        <v>3.20506763458252</v>
       </c>
       <c r="H239" t="n">
         <v>420138</v>
@@ -7358,7 +7358,7 @@
         <v>5.88500022888184</v>
       </c>
       <c r="G241" t="n">
-        <v>3.20506739616394</v>
+        <v>3.20506763458252</v>
       </c>
       <c r="H241" t="n">
         <v>352034</v>
@@ -7387,7 +7387,7 @@
         <v>5.75</v>
       </c>
       <c r="G242" t="n">
-        <v>3.1315438747406</v>
+        <v>3.13154411315918</v>
       </c>
       <c r="H242" t="n">
         <v>1209727</v>
@@ -7445,7 +7445,7 @@
         <v>5.71500015258789</v>
       </c>
       <c r="G244" t="n">
-        <v>3.11248230934143</v>
+        <v>3.11248278617859</v>
       </c>
       <c r="H244" t="n">
         <v>350856</v>
@@ -7474,7 +7474,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G245" t="n">
-        <v>3.08797454833984</v>
+        <v>3.08797478675842</v>
       </c>
       <c r="H245" t="n">
         <v>494103</v>
@@ -7503,7 +7503,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G246" t="n">
-        <v>3.09342074394226</v>
+        <v>3.09342098236084</v>
       </c>
       <c r="H246" t="n">
         <v>298347</v>
@@ -7532,7 +7532,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G247" t="n">
-        <v>3.16422128677368</v>
+        <v>3.16422080993652</v>
       </c>
       <c r="H247" t="n">
         <v>360292</v>
@@ -7590,7 +7590,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G249" t="n">
-        <v>3.23502087593079</v>
+        <v>3.23502135276794</v>
       </c>
       <c r="H249" t="n">
         <v>513814</v>
@@ -7619,7 +7619,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G250" t="n">
-        <v>3.2132363319397</v>
+        <v>3.21323657035828</v>
       </c>
       <c r="H250" t="n">
         <v>872993</v>
@@ -7677,7 +7677,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G252" t="n">
-        <v>3.20779013633728</v>
+        <v>3.20779037475586</v>
       </c>
       <c r="H252" t="n">
         <v>1027562</v>
@@ -7735,7 +7735,7 @@
         <v>5.5</v>
       </c>
       <c r="G254" t="n">
-        <v>3.26891136169434</v>
+        <v>3.2689106464386</v>
       </c>
       <c r="H254" t="n">
         <v>1331386</v>
@@ -7822,7 +7822,7 @@
         <v>5.5</v>
       </c>
       <c r="G257" t="n">
-        <v>3.26891136169434</v>
+        <v>3.2689106464386</v>
       </c>
       <c r="H257" t="n">
         <v>490521</v>
@@ -7851,7 +7851,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G258" t="n">
-        <v>3.24513721466064</v>
+        <v>3.24513745307922</v>
       </c>
       <c r="H258" t="n">
         <v>595648</v>
@@ -7909,7 +7909,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G260" t="n">
-        <v>3.15598511695862</v>
+        <v>3.1559853553772</v>
       </c>
       <c r="H260" t="n">
         <v>979931</v>
@@ -7938,7 +7938,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G261" t="n">
-        <v>3.20947647094727</v>
+        <v>3.20947670936584</v>
       </c>
       <c r="H261" t="n">
         <v>631640</v>
@@ -7996,7 +7996,7 @@
         <v>5.35500001907349</v>
       </c>
       <c r="G263" t="n">
-        <v>3.18273067474365</v>
+        <v>3.18273091316223</v>
       </c>
       <c r="H263" t="n">
         <v>387880</v>
@@ -8054,7 +8054,7 @@
         <v>5.25500011444092</v>
       </c>
       <c r="G265" t="n">
-        <v>3.12329578399658</v>
+        <v>3.12329626083374</v>
       </c>
       <c r="H265" t="n">
         <v>577217</v>
@@ -8141,7 +8141,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G268" t="n">
-        <v>3.06088972091675</v>
+        <v>3.06088948249817</v>
       </c>
       <c r="H268" t="n">
         <v>438786</v>
@@ -8170,7 +8170,7 @@
         <v>5.18499994277954</v>
       </c>
       <c r="G269" t="n">
-        <v>3.0816912651062</v>
+        <v>3.08169174194336</v>
       </c>
       <c r="H269" t="n">
         <v>231544</v>
@@ -8199,7 +8199,7 @@
         <v>5.25</v>
       </c>
       <c r="G270" t="n">
-        <v>3.12032437324524</v>
+        <v>3.12032413482666</v>
       </c>
       <c r="H270" t="n">
         <v>329941</v>
@@ -8257,7 +8257,7 @@
         <v>5.25500011444092</v>
       </c>
       <c r="G272" t="n">
-        <v>3.12329578399658</v>
+        <v>3.12329626083374</v>
       </c>
       <c r="H272" t="n">
         <v>328311</v>
@@ -8286,7 +8286,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G273" t="n">
-        <v>3.07872009277344</v>
+        <v>3.07871961593628</v>
       </c>
       <c r="H273" t="n">
         <v>369534</v>
@@ -8315,7 +8315,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G274" t="n">
-        <v>3.09655046463013</v>
+        <v>3.09655022621155</v>
       </c>
       <c r="H274" t="n">
         <v>417330</v>
@@ -8344,7 +8344,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G275" t="n">
-        <v>3.07277655601501</v>
+        <v>3.07277631759644</v>
       </c>
       <c r="H275" t="n">
         <v>698355</v>
@@ -8489,7 +8489,7 @@
         <v>4.96600008010864</v>
       </c>
       <c r="G280" t="n">
-        <v>2.95152974128723</v>
+        <v>2.95152997970581</v>
       </c>
       <c r="H280" t="n">
         <v>674444</v>
@@ -8547,7 +8547,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G282" t="n">
-        <v>3.05494618415833</v>
+        <v>3.05494594573975</v>
       </c>
       <c r="H282" t="n">
         <v>828859</v>
@@ -8576,7 +8576,7 @@
         <v>5.07499980926514</v>
       </c>
       <c r="G283" t="n">
-        <v>3.01631331443787</v>
+        <v>3.01631355285645</v>
       </c>
       <c r="H283" t="n">
         <v>226230</v>
@@ -8634,7 +8634,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G285" t="n">
-        <v>2.98362445831299</v>
+        <v>2.98362421989441</v>
       </c>
       <c r="H285" t="n">
         <v>352758</v>
@@ -8663,7 +8663,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G286" t="n">
-        <v>3.03117203712463</v>
+        <v>3.03117227554321</v>
       </c>
       <c r="H286" t="n">
         <v>247206</v>
@@ -8750,7 +8750,7 @@
         <v>4.89200019836426</v>
       </c>
       <c r="G289" t="n">
-        <v>2.90754795074463</v>
+        <v>2.90754818916321</v>
       </c>
       <c r="H289" t="n">
         <v>537893</v>
@@ -8779,7 +8779,7 @@
         <v>5.07499980926514</v>
       </c>
       <c r="G290" t="n">
-        <v>3.01631331443787</v>
+        <v>3.01631355285645</v>
       </c>
       <c r="H290" t="n">
         <v>585591</v>
@@ -8808,7 +8808,7 @@
         <v>5.07499980926514</v>
       </c>
       <c r="G291" t="n">
-        <v>3.01631331443787</v>
+        <v>3.01631355285645</v>
       </c>
       <c r="H291" t="n">
         <v>697953</v>
@@ -8837,7 +8837,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G292" t="n">
-        <v>3.05791759490967</v>
+        <v>3.05791735649109</v>
       </c>
       <c r="H292" t="n">
         <v>416047</v>
@@ -8866,7 +8866,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G293" t="n">
-        <v>3.09060645103455</v>
+        <v>3.0906069278717</v>
       </c>
       <c r="H293" t="n">
         <v>267972</v>
@@ -8895,7 +8895,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G294" t="n">
-        <v>3.06683278083801</v>
+        <v>3.06683301925659</v>
       </c>
       <c r="H294" t="n">
         <v>263638</v>
@@ -8924,7 +8924,7 @@
         <v>5.11499977111816</v>
       </c>
       <c r="G295" t="n">
-        <v>3.04008722305298</v>
+        <v>3.04008769989014</v>
       </c>
       <c r="H295" t="n">
         <v>461713</v>
@@ -8982,7 +8982,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G297" t="n">
-        <v>3.03711557388306</v>
+        <v>3.03711581230164</v>
       </c>
       <c r="H297" t="n">
         <v>116870</v>
@@ -9011,7 +9011,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G298" t="n">
-        <v>3.06088972091675</v>
+        <v>3.06088948249817</v>
       </c>
       <c r="H298" t="n">
         <v>328764</v>
@@ -9040,7 +9040,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G299" t="n">
-        <v>3.11438035964966</v>
+        <v>3.11438083648682</v>
       </c>
       <c r="H299" t="n">
         <v>344162</v>
@@ -9069,7 +9069,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G300" t="n">
-        <v>3.09060645103455</v>
+        <v>3.0906069278717</v>
       </c>
       <c r="H300" t="n">
         <v>174295</v>
@@ -9098,7 +9098,7 @@
         <v>5.29500007629395</v>
       </c>
       <c r="G301" t="n">
-        <v>3.14706969261169</v>
+        <v>3.14706993103027</v>
       </c>
       <c r="H301" t="n">
         <v>597621</v>
@@ -9156,7 +9156,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G303" t="n">
-        <v>3.15598511695862</v>
+        <v>3.1559853553772</v>
       </c>
       <c r="H303" t="n">
         <v>235545</v>
@@ -9185,7 +9185,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G304" t="n">
-        <v>3.20353269577026</v>
+        <v>3.20353293418884</v>
       </c>
       <c r="H304" t="n">
         <v>235936</v>
@@ -9214,7 +9214,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G305" t="n">
-        <v>3.14409828186035</v>
+        <v>3.14409780502319</v>
       </c>
       <c r="H305" t="n">
         <v>283594</v>
@@ -9243,7 +9243,7 @@
         <v>5.34499979019165</v>
       </c>
       <c r="G306" t="n">
-        <v>3.17678713798523</v>
+        <v>3.17678689956665</v>
       </c>
       <c r="H306" t="n">
         <v>272584</v>
@@ -9330,7 +9330,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G309" t="n">
-        <v>3.01334166526794</v>
+        <v>3.01334142684937</v>
       </c>
       <c r="H309" t="n">
         <v>403149</v>
@@ -9359,7 +9359,7 @@
         <v>4.95599985122681</v>
       </c>
       <c r="G310" t="n">
-        <v>2.94558596611023</v>
+        <v>2.94558572769165</v>
       </c>
       <c r="H310" t="n">
         <v>428973</v>
@@ -9388,7 +9388,7 @@
         <v>4.9539999961853</v>
       </c>
       <c r="G311" t="n">
-        <v>2.94439721107483</v>
+        <v>2.94439744949341</v>
       </c>
       <c r="H311" t="n">
         <v>179330</v>
@@ -9417,7 +9417,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G312" t="n">
-        <v>2.98362445831299</v>
+        <v>2.98362421989441</v>
       </c>
       <c r="H312" t="n">
         <v>142945</v>
@@ -9446,7 +9446,7 @@
         <v>5</v>
       </c>
       <c r="G313" t="n">
-        <v>2.97173714637756</v>
+        <v>2.97173762321472</v>
       </c>
       <c r="H313" t="n">
         <v>154813</v>
@@ -9504,7 +9504,7 @@
         <v>4.93200016021729</v>
       </c>
       <c r="G315" t="n">
-        <v>2.93132162094116</v>
+        <v>2.93132209777832</v>
       </c>
       <c r="H315" t="n">
         <v>154692</v>
@@ -9562,7 +9562,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G317" t="n">
-        <v>2.98956823348999</v>
+        <v>2.98956751823425</v>
       </c>
       <c r="H317" t="n">
         <v>166858</v>
@@ -9591,7 +9591,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G318" t="n">
-        <v>3.05791759490967</v>
+        <v>3.05791735649109</v>
       </c>
       <c r="H318" t="n">
         <v>170278</v>
@@ -9620,7 +9620,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G319" t="n">
-        <v>3.07277655601501</v>
+        <v>3.07277631759644</v>
       </c>
       <c r="H319" t="n">
         <v>153750</v>
@@ -9678,7 +9678,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G321" t="n">
-        <v>3.02522850036621</v>
+        <v>3.02522873878479</v>
       </c>
       <c r="H321" t="n">
         <v>173975</v>
@@ -9736,7 +9736,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G323" t="n">
-        <v>3.06683278083801</v>
+        <v>3.06683301925659</v>
       </c>
       <c r="H323" t="n">
         <v>58760</v>
@@ -9794,7 +9794,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G325" t="n">
-        <v>3.12626767158508</v>
+        <v>3.12626791000366</v>
       </c>
       <c r="H325" t="n">
         <v>127239</v>
@@ -9823,7 +9823,7 @@
         <v>5.2350001335144</v>
       </c>
       <c r="G326" t="n">
-        <v>3.11140942573547</v>
+        <v>3.11140918731689</v>
       </c>
       <c r="H326" t="n">
         <v>76315</v>
@@ -9852,7 +9852,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G327" t="n">
-        <v>3.12626767158508</v>
+        <v>3.12626791000366</v>
       </c>
       <c r="H327" t="n">
         <v>103691</v>
@@ -9881,7 +9881,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G328" t="n">
-        <v>3.08466386795044</v>
+        <v>3.08466339111328</v>
       </c>
       <c r="H328" t="n">
         <v>66700</v>
@@ -9939,7 +9939,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G330" t="n">
-        <v>3.09060645103455</v>
+        <v>3.0906069278717</v>
       </c>
       <c r="H330" t="n">
         <v>128424</v>
@@ -9997,7 +9997,7 @@
         <v>5.29500007629395</v>
       </c>
       <c r="G332" t="n">
-        <v>3.14706969261169</v>
+        <v>3.14706993103027</v>
       </c>
       <c r="H332" t="n">
         <v>90503</v>
@@ -10026,7 +10026,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G333" t="n">
-        <v>3.18570280075073</v>
+        <v>3.18570256233215</v>
       </c>
       <c r="H333" t="n">
         <v>140475</v>
@@ -10055,7 +10055,7 @@
         <v>5.34499979019165</v>
       </c>
       <c r="G334" t="n">
-        <v>3.17678713798523</v>
+        <v>3.17678689956665</v>
       </c>
       <c r="H334" t="n">
         <v>99856</v>
@@ -10084,7 +10084,7 @@
         <v>5.33500003814697</v>
       </c>
       <c r="G335" t="n">
-        <v>3.17084383964539</v>
+        <v>3.17084407806396</v>
       </c>
       <c r="H335" t="n">
         <v>72100</v>
@@ -10113,7 +10113,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G336" t="n">
-        <v>3.15004110336304</v>
+        <v>3.15004205703735</v>
       </c>
       <c r="H336" t="n">
         <v>364841</v>
@@ -10171,7 +10171,7 @@
         <v>5.17500019073486</v>
       </c>
       <c r="G338" t="n">
-        <v>3.07574820518494</v>
+        <v>3.07574844360352</v>
       </c>
       <c r="H338" t="n">
         <v>106130</v>
@@ -10200,7 +10200,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G339" t="n">
-        <v>3.18570280075073</v>
+        <v>3.18570256233215</v>
       </c>
       <c r="H339" t="n">
         <v>115723</v>
@@ -10229,7 +10229,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G340" t="n">
-        <v>3.20947647094727</v>
+        <v>3.20947670936584</v>
       </c>
       <c r="H340" t="n">
         <v>1238146</v>
@@ -10258,7 +10258,7 @@
         <v>5.44500017166138</v>
       </c>
       <c r="G341" t="n">
-        <v>3.23622226715088</v>
+        <v>3.2362220287323</v>
       </c>
       <c r="H341" t="n">
         <v>228216</v>
@@ -10287,7 +10287,7 @@
         <v>5.35500001907349</v>
       </c>
       <c r="G342" t="n">
-        <v>3.18273067474365</v>
+        <v>3.18273091316223</v>
       </c>
       <c r="H342" t="n">
         <v>130806</v>
@@ -10316,7 +10316,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G343" t="n">
-        <v>3.16787219047546</v>
+        <v>3.16787171363831</v>
       </c>
       <c r="H343" t="n">
         <v>197982</v>
@@ -10345,7 +10345,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G344" t="n">
-        <v>3.1619291305542</v>
+        <v>3.16192889213562</v>
       </c>
       <c r="H344" t="n">
         <v>70903</v>
@@ -10374,7 +10374,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G345" t="n">
-        <v>3.10249352455139</v>
+        <v>3.10249376296997</v>
       </c>
       <c r="H345" t="n">
         <v>223546</v>
@@ -10432,7 +10432,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G347" t="n">
-        <v>3.05791759490967</v>
+        <v>3.05791735649109</v>
       </c>
       <c r="H347" t="n">
         <v>74239</v>
@@ -10461,7 +10461,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G348" t="n">
-        <v>3.08466386795044</v>
+        <v>3.08466339111328</v>
       </c>
       <c r="H348" t="n">
         <v>453065</v>
@@ -10490,7 +10490,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G349" t="n">
-        <v>3.06683278083801</v>
+        <v>3.06683301925659</v>
       </c>
       <c r="H349" t="n">
         <v>92763</v>
@@ -10519,7 +10519,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G350" t="n">
-        <v>3.05494618415833</v>
+        <v>3.05494594573975</v>
       </c>
       <c r="H350" t="n">
         <v>106495</v>
@@ -10548,7 +10548,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G351" t="n">
-        <v>3.06088972091675</v>
+        <v>3.06088948249817</v>
       </c>
       <c r="H351" t="n">
         <v>97494</v>
@@ -10577,7 +10577,7 @@
         <v>5.21500015258789</v>
       </c>
       <c r="G352" t="n">
-        <v>3.09952187538147</v>
+        <v>3.09952235221863</v>
       </c>
       <c r="H352" t="n">
         <v>118988</v>
@@ -10606,7 +10606,7 @@
         <v>5.17500019073486</v>
       </c>
       <c r="G353" t="n">
-        <v>3.07574820518494</v>
+        <v>3.07574844360352</v>
       </c>
       <c r="H353" t="n">
         <v>108557</v>
@@ -10635,7 +10635,7 @@
         <v>5.16499996185303</v>
       </c>
       <c r="G354" t="n">
-        <v>3.06980466842651</v>
+        <v>3.06980490684509</v>
       </c>
       <c r="H354" t="n">
         <v>82105</v>
@@ -10664,7 +10664,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G355" t="n">
-        <v>3.07277655601501</v>
+        <v>3.07277631759644</v>
       </c>
       <c r="H355" t="n">
         <v>230549</v>
@@ -10693,7 +10693,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G356" t="n">
-        <v>3.06088972091675</v>
+        <v>3.06088948249817</v>
       </c>
       <c r="H356" t="n">
         <v>91142</v>
@@ -10722,7 +10722,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G357" t="n">
-        <v>3.05791759490967</v>
+        <v>3.05791735649109</v>
       </c>
       <c r="H357" t="n">
         <v>28290</v>
@@ -10751,7 +10751,7 @@
         <v>5.125</v>
       </c>
       <c r="G358" t="n">
-        <v>3.0460307598114</v>
+        <v>3.04603052139282</v>
       </c>
       <c r="H358" t="n">
         <v>40886</v>
@@ -10780,7 +10780,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G359" t="n">
-        <v>3.07277655601501</v>
+        <v>3.07277631759644</v>
       </c>
       <c r="H359" t="n">
         <v>186054</v>
@@ -10867,7 +10867,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G362" t="n">
-        <v>3.06683278083801</v>
+        <v>3.06683301925659</v>
       </c>
       <c r="H362" t="n">
         <v>194545</v>
@@ -10896,7 +10896,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G363" t="n">
-        <v>3.05494618415833</v>
+        <v>3.05494594573975</v>
       </c>
       <c r="H363" t="n">
         <v>74473</v>
@@ -10925,7 +10925,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G364" t="n">
-        <v>3.05791759490967</v>
+        <v>3.05791735649109</v>
       </c>
       <c r="H364" t="n">
         <v>87130</v>
@@ -10983,7 +10983,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G366" t="n">
-        <v>3.05494618415833</v>
+        <v>3.05494594573975</v>
       </c>
       <c r="H366" t="n">
         <v>46236</v>
@@ -11012,7 +11012,7 @@
         <v>5.125</v>
       </c>
       <c r="G367" t="n">
-        <v>3.0460307598114</v>
+        <v>3.04603052139282</v>
       </c>
       <c r="H367" t="n">
         <v>120227</v>
@@ -11041,7 +11041,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G368" t="n">
-        <v>3.06088972091675</v>
+        <v>3.06088948249817</v>
       </c>
       <c r="H368" t="n">
         <v>56278</v>
@@ -11070,7 +11070,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G369" t="n">
-        <v>3.09060645103455</v>
+        <v>3.0906069278717</v>
       </c>
       <c r="H369" t="n">
         <v>221869</v>
@@ -11099,7 +11099,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G370" t="n">
-        <v>3.11438035964966</v>
+        <v>3.11438083648682</v>
       </c>
       <c r="H370" t="n">
         <v>151879</v>
@@ -11128,7 +11128,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G371" t="n">
-        <v>3.15598511695862</v>
+        <v>3.1559853553772</v>
       </c>
       <c r="H371" t="n">
         <v>203445</v>
@@ -11157,7 +11157,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G372" t="n">
-        <v>3.09655046463013</v>
+        <v>3.09655022621155</v>
       </c>
       <c r="H372" t="n">
         <v>46233</v>
@@ -11186,7 +11186,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G373" t="n">
-        <v>3.07277655601501</v>
+        <v>3.07277631759644</v>
       </c>
       <c r="H373" t="n">
         <v>246726</v>
@@ -11215,7 +11215,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G374" t="n">
-        <v>3.09655046463013</v>
+        <v>3.09655022621155</v>
       </c>
       <c r="H374" t="n">
         <v>132834</v>
@@ -11244,7 +11244,7 @@
         <v>5.25500011444092</v>
       </c>
       <c r="G375" t="n">
-        <v>3.12329578399658</v>
+        <v>3.12329626083374</v>
       </c>
       <c r="H375" t="n">
         <v>154023</v>
@@ -11273,7 +11273,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G376" t="n">
-        <v>3.06683278083801</v>
+        <v>3.06683301925659</v>
       </c>
       <c r="H376" t="n">
         <v>286681</v>
@@ -11418,7 +11418,7 @@
         <v>4.98799991607666</v>
       </c>
       <c r="G381" t="n">
-        <v>2.9646053314209</v>
+        <v>2.96460509300232</v>
       </c>
       <c r="H381" t="n">
         <v>137253</v>
@@ -11447,7 +11447,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G382" t="n">
-        <v>2.81720685958862</v>
+        <v>2.8172070980072</v>
       </c>
       <c r="H382" t="n">
         <v>320617</v>
@@ -11476,7 +11476,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G383" t="n">
-        <v>2.79937672615051</v>
+        <v>2.79937624931335</v>
       </c>
       <c r="H383" t="n">
         <v>488102</v>
@@ -11505,7 +11505,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G384" t="n">
-        <v>2.76965928077698</v>
+        <v>2.76965880393982</v>
       </c>
       <c r="H384" t="n">
         <v>576950</v>
@@ -11534,7 +11534,7 @@
         <v>4.71799993515015</v>
       </c>
       <c r="G385" t="n">
-        <v>2.80413103103638</v>
+        <v>2.80413150787354</v>
       </c>
       <c r="H385" t="n">
         <v>265565</v>
@@ -11563,7 +11563,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G386" t="n">
-        <v>2.78748989105225</v>
+        <v>2.78749012947083</v>
       </c>
       <c r="H386" t="n">
         <v>196107</v>
@@ -11621,7 +11621,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G388" t="n">
-        <v>2.85881090164185</v>
+        <v>2.858811378479</v>
       </c>
       <c r="H388" t="n">
         <v>182848</v>
@@ -11650,7 +11650,7 @@
         <v>4.71400022506714</v>
       </c>
       <c r="G389" t="n">
-        <v>2.80175423622131</v>
+        <v>2.80175399780273</v>
       </c>
       <c r="H389" t="n">
         <v>271772</v>
@@ -11679,7 +11679,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G390" t="n">
-        <v>2.80532002449036</v>
+        <v>2.8053195476532</v>
       </c>
       <c r="H390" t="n">
         <v>91615</v>
@@ -11708,7 +11708,7 @@
         <v>4.59600019454956</v>
       </c>
       <c r="G391" t="n">
-        <v>2.73162078857422</v>
+        <v>2.7316210269928</v>
       </c>
       <c r="H391" t="n">
         <v>286266</v>
@@ -11737,7 +11737,7 @@
         <v>4.58199977874756</v>
       </c>
       <c r="G392" t="n">
-        <v>2.72330021858215</v>
+        <v>2.72329998016357</v>
       </c>
       <c r="H392" t="n">
         <v>122845</v>
@@ -11766,7 +11766,7 @@
         <v>4.43400001525879</v>
       </c>
       <c r="G393" t="n">
-        <v>2.63533663749695</v>
+        <v>2.63533639907837</v>
       </c>
       <c r="H393" t="n">
         <v>176582</v>
@@ -11824,7 +11824,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G395" t="n">
-        <v>2.5794677734375</v>
+        <v>2.57946801185608</v>
       </c>
       <c r="H395" t="n">
         <v>323191</v>
@@ -11853,7 +11853,7 @@
         <v>4.30600023269653</v>
       </c>
       <c r="G396" t="n">
-        <v>2.55926012992859</v>
+        <v>2.55926036834717</v>
       </c>
       <c r="H396" t="n">
         <v>285753</v>
@@ -11882,7 +11882,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G397" t="n">
-        <v>2.63295912742615</v>
+        <v>2.63295936584473</v>
       </c>
       <c r="H397" t="n">
         <v>580470</v>
@@ -11911,7 +11911,7 @@
         <v>4.49599981307983</v>
       </c>
       <c r="G398" t="n">
-        <v>2.67218637466431</v>
+        <v>2.67218613624573</v>
       </c>
       <c r="H398" t="n">
         <v>359368</v>
@@ -11940,7 +11940,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G399" t="n">
-        <v>2.70428109169006</v>
+        <v>2.70428085327148</v>
       </c>
       <c r="H399" t="n">
         <v>360794</v>
@@ -11969,7 +11969,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G400" t="n">
-        <v>2.70428109169006</v>
+        <v>2.70428085327148</v>
       </c>
       <c r="H400" t="n">
         <v>99931</v>
@@ -12056,7 +12056,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G403" t="n">
-        <v>2.68645048141479</v>
+        <v>2.68645071983337</v>
       </c>
       <c r="H403" t="n">
         <v>276905</v>
@@ -12085,7 +12085,7 @@
         <v>4.73600006103516</v>
       </c>
       <c r="G404" t="n">
-        <v>2.8148295879364</v>
+        <v>2.81482934951782</v>
       </c>
       <c r="H404" t="n">
         <v>608489</v>
@@ -12114,7 +12114,7 @@
         <v>4.61399984359741</v>
       </c>
       <c r="G405" t="n">
-        <v>2.74231910705566</v>
+        <v>2.74231886863708</v>
       </c>
       <c r="H405" t="n">
         <v>143504</v>
@@ -12143,7 +12143,7 @@
         <v>4.61199998855591</v>
       </c>
       <c r="G406" t="n">
-        <v>2.74113059043884</v>
+        <v>2.74113035202026</v>
       </c>
       <c r="H406" t="n">
         <v>114731</v>
@@ -12172,7 +12172,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G407" t="n">
-        <v>2.73994207382202</v>
+        <v>2.73994183540344</v>
       </c>
       <c r="H407" t="n">
         <v>174008</v>
@@ -12230,7 +12230,7 @@
         <v>4.57600021362305</v>
       </c>
       <c r="G409" t="n">
-        <v>2.71973443031311</v>
+        <v>2.71973419189453</v>
       </c>
       <c r="H409" t="n">
         <v>65945</v>
@@ -12259,7 +12259,7 @@
         <v>4.57600021362305</v>
       </c>
       <c r="G410" t="n">
-        <v>2.71973443031311</v>
+        <v>2.71973419189453</v>
       </c>
       <c r="H410" t="n">
         <v>83746</v>
@@ -12288,7 +12288,7 @@
         <v>4.51599979400635</v>
       </c>
       <c r="G411" t="n">
-        <v>2.68407297134399</v>
+        <v>2.68407273292542</v>
       </c>
       <c r="H411" t="n">
         <v>70296</v>
@@ -12346,7 +12346,7 @@
         <v>4.48799991607666</v>
       </c>
       <c r="G413" t="n">
-        <v>2.66743159294128</v>
+        <v>2.66743135452271</v>
       </c>
       <c r="H413" t="n">
         <v>168191</v>
@@ -12375,7 +12375,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G414" t="n">
-        <v>2.70428109169006</v>
+        <v>2.70428085327148</v>
       </c>
       <c r="H414" t="n">
         <v>160385</v>
@@ -12433,7 +12433,7 @@
         <v>4.56599998474121</v>
       </c>
       <c r="G416" t="n">
-        <v>2.71379041671753</v>
+        <v>2.71379065513611</v>
       </c>
       <c r="H416" t="n">
         <v>159063</v>
@@ -12462,7 +12462,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G417" t="n">
-        <v>2.79343295097351</v>
+        <v>2.79343318939209</v>
       </c>
       <c r="H417" t="n">
         <v>148154</v>
@@ -12491,7 +12491,7 @@
         <v>4.67199993133545</v>
       </c>
       <c r="G418" t="n">
-        <v>2.7767915725708</v>
+        <v>2.77679133415222</v>
       </c>
       <c r="H418" t="n">
         <v>157427</v>
@@ -12520,7 +12520,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G419" t="n">
-        <v>2.7280547618866</v>
+        <v>2.72805500030518</v>
       </c>
       <c r="H419" t="n">
         <v>217141</v>
@@ -12549,7 +12549,7 @@
         <v>4.59800004959106</v>
       </c>
       <c r="G420" t="n">
-        <v>2.73280954360962</v>
+        <v>2.73281002044678</v>
       </c>
       <c r="H420" t="n">
         <v>71919</v>
@@ -12607,7 +12607,7 @@
         <v>4.60400009155273</v>
       </c>
       <c r="G422" t="n">
-        <v>2.73637580871582</v>
+        <v>2.7363760471344</v>
       </c>
       <c r="H422" t="n">
         <v>268621</v>
@@ -12636,7 +12636,7 @@
         <v>4.6560001373291</v>
       </c>
       <c r="G423" t="n">
-        <v>2.76728177070618</v>
+        <v>2.76728200912476</v>
       </c>
       <c r="H423" t="n">
         <v>87837</v>
@@ -12665,7 +12665,7 @@
         <v>4.59800004959106</v>
       </c>
       <c r="G424" t="n">
-        <v>2.73280954360962</v>
+        <v>2.73281002044678</v>
       </c>
       <c r="H424" t="n">
         <v>54186</v>
@@ -12694,7 +12694,7 @@
         <v>4.53599977493286</v>
       </c>
       <c r="G425" t="n">
-        <v>2.69596028327942</v>
+        <v>2.69596004486084</v>
       </c>
       <c r="H425" t="n">
         <v>103550</v>
@@ -12723,7 +12723,7 @@
         <v>4.55600023269653</v>
       </c>
       <c r="G426" t="n">
-        <v>2.70784711837769</v>
+        <v>2.70784735679626</v>
       </c>
       <c r="H426" t="n">
         <v>83993</v>
@@ -12752,7 +12752,7 @@
         <v>4.50799989700317</v>
       </c>
       <c r="G427" t="n">
-        <v>2.67931842803955</v>
+        <v>2.67931818962097</v>
       </c>
       <c r="H427" t="n">
         <v>62972</v>
@@ -12781,7 +12781,7 @@
         <v>4.46199989318848</v>
       </c>
       <c r="G428" t="n">
-        <v>2.65197849273682</v>
+        <v>2.65197825431824</v>
       </c>
       <c r="H428" t="n">
         <v>105523</v>
@@ -12810,7 +12810,7 @@
         <v>4.57399988174438</v>
       </c>
       <c r="G429" t="n">
-        <v>2.71854519844055</v>
+        <v>2.71854543685913</v>
       </c>
       <c r="H429" t="n">
         <v>164053</v>
@@ -12868,7 +12868,7 @@
         <v>4.53399991989136</v>
       </c>
       <c r="G431" t="n">
-        <v>2.69477128982544</v>
+        <v>2.69477105140686</v>
       </c>
       <c r="H431" t="n">
         <v>67005</v>
@@ -12955,7 +12955,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G434" t="n">
-        <v>2.69239401817322</v>
+        <v>2.6923942565918</v>
       </c>
       <c r="H434" t="n">
         <v>80551</v>
@@ -12984,7 +12984,7 @@
         <v>4.50400018692017</v>
       </c>
       <c r="G435" t="n">
-        <v>2.67694139480591</v>
+        <v>2.67694115638733</v>
       </c>
       <c r="H435" t="n">
         <v>90846</v>
@@ -13013,7 +13013,7 @@
         <v>4.49599981307983</v>
       </c>
       <c r="G436" t="n">
-        <v>2.67218637466431</v>
+        <v>2.67218613624573</v>
       </c>
       <c r="H436" t="n">
         <v>248723</v>
@@ -13042,7 +13042,7 @@
         <v>4.45599985122681</v>
       </c>
       <c r="G437" t="n">
-        <v>2.64841246604919</v>
+        <v>2.64841222763062</v>
       </c>
       <c r="H437" t="n">
         <v>112182</v>
@@ -13071,7 +13071,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G438" t="n">
-        <v>2.69833779335022</v>
+        <v>2.69833731651306</v>
       </c>
       <c r="H438" t="n">
         <v>49751</v>
@@ -13129,7 +13129,7 @@
         <v>4.72800016403198</v>
       </c>
       <c r="G440" t="n">
-        <v>2.81007504463196</v>
+        <v>2.81007480621338</v>
       </c>
       <c r="H440" t="n">
         <v>246774</v>
@@ -13158,7 +13158,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G441" t="n">
-        <v>2.86475443840027</v>
+        <v>2.86475467681885</v>
       </c>
       <c r="H441" t="n">
         <v>258995</v>
@@ -13216,7 +13216,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G443" t="n">
-        <v>2.95390677452087</v>
+        <v>2.95390653610229</v>
       </c>
       <c r="H443" t="n">
         <v>243923</v>
@@ -13245,7 +13245,7 @@
         <v>4.85599994659424</v>
       </c>
       <c r="G444" t="n">
-        <v>2.88615155220032</v>
+        <v>2.88615131378174</v>
       </c>
       <c r="H444" t="n">
         <v>231839</v>
@@ -13274,7 +13274,7 @@
         <v>4.78399991989136</v>
       </c>
       <c r="G445" t="n">
-        <v>2.84335780143738</v>
+        <v>2.84335827827454</v>
       </c>
       <c r="H445" t="n">
         <v>179349</v>
@@ -13303,7 +13303,7 @@
         <v>4.78399991989136</v>
       </c>
       <c r="G446" t="n">
-        <v>2.84335780143738</v>
+        <v>2.84335827827454</v>
       </c>
       <c r="H446" t="n">
         <v>104630</v>
@@ -13332,7 +13332,7 @@
         <v>4.73199987411499</v>
       </c>
       <c r="G447" t="n">
-        <v>2.81245183944702</v>
+        <v>2.8124520778656</v>
       </c>
       <c r="H447" t="n">
         <v>98851</v>
@@ -13419,7 +13419,7 @@
         <v>4.77400016784668</v>
       </c>
       <c r="G450" t="n">
-        <v>2.83741497993469</v>
+        <v>2.83741521835327</v>
       </c>
       <c r="H450" t="n">
         <v>115804</v>
@@ -13477,7 +13477,7 @@
         <v>4.84600019454956</v>
       </c>
       <c r="G452" t="n">
-        <v>2.88020825386047</v>
+        <v>2.88020801544189</v>
       </c>
       <c r="H452" t="n">
         <v>128912</v>
@@ -13506,7 +13506,7 @@
         <v>4.80399990081787</v>
       </c>
       <c r="G453" t="n">
-        <v>2.8552451133728</v>
+        <v>2.85524487495422</v>
       </c>
       <c r="H453" t="n">
         <v>129776</v>
@@ -13535,7 +13535,7 @@
         <v>4.86199998855591</v>
       </c>
       <c r="G454" t="n">
-        <v>2.88971734046936</v>
+        <v>2.88971757888794</v>
       </c>
       <c r="H454" t="n">
         <v>129650</v>
@@ -13593,7 +13593,7 @@
         <v>4.92399978637695</v>
       </c>
       <c r="G456" t="n">
-        <v>2.92656660079956</v>
+        <v>2.92656707763672</v>
       </c>
       <c r="H456" t="n">
         <v>147514</v>
@@ -13622,7 +13622,7 @@
         <v>4.92600011825562</v>
       </c>
       <c r="G457" t="n">
-        <v>2.92775559425354</v>
+        <v>2.92775583267212</v>
       </c>
       <c r="H457" t="n">
         <v>149968</v>
@@ -13651,7 +13651,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G458" t="n">
-        <v>3.00145483016968</v>
+        <v>3.00145506858826</v>
       </c>
       <c r="H458" t="n">
         <v>653587</v>
@@ -13680,7 +13680,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G459" t="n">
-        <v>3.03711557388306</v>
+        <v>3.03711581230164</v>
       </c>
       <c r="H459" t="n">
         <v>507410</v>
@@ -13767,7 +13767,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G462" t="n">
-        <v>3.01334166526794</v>
+        <v>3.01334142684937</v>
       </c>
       <c r="H462" t="n">
         <v>189433</v>
@@ -13854,7 +13854,7 @@
         <v>4.98600006103516</v>
       </c>
       <c r="G465" t="n">
-        <v>2.96341681480408</v>
+        <v>2.9634165763855</v>
       </c>
       <c r="H465" t="n">
         <v>365178</v>
@@ -13883,7 +13883,7 @@
         <v>5.11499977111816</v>
       </c>
       <c r="G466" t="n">
-        <v>3.04008722305298</v>
+        <v>3.04008769989014</v>
       </c>
       <c r="H466" t="n">
         <v>920387</v>
@@ -13912,7 +13912,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G467" t="n">
-        <v>3.05494618415833</v>
+        <v>3.05494594573975</v>
       </c>
       <c r="H467" t="n">
         <v>1080876</v>
@@ -13941,7 +13941,7 @@
         <v>5.25</v>
       </c>
       <c r="G468" t="n">
-        <v>3.12032437324524</v>
+        <v>3.12032413482666</v>
       </c>
       <c r="H468" t="n">
         <v>599209</v>
@@ -13970,7 +13970,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G469" t="n">
-        <v>3.16787219047546</v>
+        <v>3.16787171363831</v>
       </c>
       <c r="H469" t="n">
         <v>981203</v>
@@ -13999,7 +13999,7 @@
         <v>5.25</v>
       </c>
       <c r="G470" t="n">
-        <v>3.12032437324524</v>
+        <v>3.12032413482666</v>
       </c>
       <c r="H470" t="n">
         <v>864726</v>
@@ -14028,7 +14028,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G471" t="n">
-        <v>3.1619291305542</v>
+        <v>3.16192889213562</v>
       </c>
       <c r="H471" t="n">
         <v>695141</v>
@@ -14086,7 +14086,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G473" t="n">
-        <v>3.16787219047546</v>
+        <v>3.16787171363831</v>
       </c>
       <c r="H473" t="n">
         <v>424757</v>
@@ -14115,7 +14115,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G474" t="n">
-        <v>3.16787219047546</v>
+        <v>3.16787171363831</v>
       </c>
       <c r="H474" t="n">
         <v>504964</v>
@@ -14144,7 +14144,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G475" t="n">
-        <v>3.15004110336304</v>
+        <v>3.15004205703735</v>
       </c>
       <c r="H475" t="n">
         <v>493758</v>
@@ -14202,7 +14202,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G477" t="n">
-        <v>3.15004110336304</v>
+        <v>3.15004205703735</v>
       </c>
       <c r="H477" t="n">
         <v>466486</v>
@@ -14231,7 +14231,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G478" t="n">
-        <v>3.09060645103455</v>
+        <v>3.0906069278717</v>
       </c>
       <c r="H478" t="n">
         <v>609117</v>
@@ -14260,7 +14260,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G479" t="n">
-        <v>3.07872009277344</v>
+        <v>3.07871961593628</v>
       </c>
       <c r="H479" t="n">
         <v>588665</v>
@@ -14318,7 +14318,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G481" t="n">
-        <v>3.14409828186035</v>
+        <v>3.14409780502319</v>
       </c>
       <c r="H481" t="n">
         <v>420743</v>
@@ -14347,7 +14347,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G482" t="n">
-        <v>3.15004110336304</v>
+        <v>3.15004205703735</v>
       </c>
       <c r="H482" t="n">
         <v>297729</v>
@@ -14376,7 +14376,7 @@
         <v>5.30499982833862</v>
       </c>
       <c r="G483" t="n">
-        <v>3.15301322937012</v>
+        <v>3.15301299095154</v>
       </c>
       <c r="H483" t="n">
         <v>452499</v>
@@ -14405,7 +14405,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G484" t="n">
-        <v>3.17381572723389</v>
+        <v>3.17381548881531</v>
       </c>
       <c r="H484" t="n">
         <v>513873</v>
@@ -14434,7 +14434,7 @@
         <v>5.34499979019165</v>
       </c>
       <c r="G485" t="n">
-        <v>3.17678713798523</v>
+        <v>3.17678689956665</v>
       </c>
       <c r="H485" t="n">
         <v>257835</v>
@@ -14463,7 +14463,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G486" t="n">
-        <v>3.16787219047546</v>
+        <v>3.16787171363831</v>
       </c>
       <c r="H486" t="n">
         <v>302610</v>
@@ -14492,7 +14492,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G487" t="n">
-        <v>3.18570280075073</v>
+        <v>3.18570256233215</v>
       </c>
       <c r="H487" t="n">
         <v>273552</v>
@@ -14521,7 +14521,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G488" t="n">
-        <v>3.19164562225342</v>
+        <v>3.19164609909058</v>
       </c>
       <c r="H488" t="n">
         <v>323925</v>
@@ -14550,7 +14550,7 @@
         <v>5.35500001907349</v>
       </c>
       <c r="G489" t="n">
-        <v>3.18273067474365</v>
+        <v>3.18273091316223</v>
       </c>
       <c r="H489" t="n">
         <v>247576</v>
@@ -14579,7 +14579,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G490" t="n">
-        <v>3.2273063659668</v>
+        <v>3.22730660438538</v>
       </c>
       <c r="H490" t="n">
         <v>437671</v>
@@ -14608,7 +14608,7 @@
         <v>5.49499988555908</v>
       </c>
       <c r="G491" t="n">
-        <v>3.26593899726868</v>
+        <v>3.26593923568726</v>
       </c>
       <c r="H491" t="n">
         <v>696421</v>
@@ -14637,7 +14637,7 @@
         <v>5.57499980926514</v>
       </c>
       <c r="G492" t="n">
-        <v>3.31348705291748</v>
+        <v>3.3134868144989</v>
       </c>
       <c r="H492" t="n">
         <v>414361</v>
@@ -14666,7 +14666,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G493" t="n">
-        <v>3.28079748153687</v>
+        <v>3.28079795837402</v>
       </c>
       <c r="H493" t="n">
         <v>427626</v>
@@ -14695,7 +14695,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G494" t="n">
-        <v>3.29862856864929</v>
+        <v>3.29862880706787</v>
       </c>
       <c r="H494" t="n">
         <v>486720</v>
@@ -14724,7 +14724,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G495" t="n">
-        <v>3.29862856864929</v>
+        <v>3.29862880706787</v>
       </c>
       <c r="H495" t="n">
         <v>335472</v>
@@ -14753,7 +14753,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G496" t="n">
-        <v>3.29268503189087</v>
+        <v>3.29268455505371</v>
       </c>
       <c r="H496" t="n">
         <v>426777</v>
@@ -14782,7 +14782,7 @@
         <v>5.5</v>
       </c>
       <c r="G497" t="n">
-        <v>3.26891136169434</v>
+        <v>3.2689106464386</v>
       </c>
       <c r="H497" t="n">
         <v>672154</v>
@@ -14811,7 +14811,7 @@
         <v>5.54500007629395</v>
       </c>
       <c r="G498" t="n">
-        <v>3.29565668106079</v>
+        <v>3.29565715789795</v>
       </c>
       <c r="H498" t="n">
         <v>524663</v>
@@ -14840,7 +14840,7 @@
         <v>5.625</v>
       </c>
       <c r="G499" t="n">
-        <v>3.34320497512817</v>
+        <v>3.34320473670959</v>
       </c>
       <c r="H499" t="n">
         <v>778967</v>
@@ -14898,7 +14898,7 @@
         <v>5.42500019073486</v>
       </c>
       <c r="G501" t="n">
-        <v>3.22433519363403</v>
+        <v>3.22433543205261</v>
       </c>
       <c r="H501" t="n">
         <v>5303704</v>
@@ -14927,7 +14927,7 @@
         <v>4.99499988555908</v>
       </c>
       <c r="G502" t="n">
-        <v>3.29626560211182</v>
+        <v>3.29626536369324</v>
       </c>
       <c r="H502" t="n">
         <v>1748822</v>
@@ -14956,7 +14956,7 @@
         <v>4.96500015258789</v>
       </c>
       <c r="G503" t="n">
-        <v>3.27646827697754</v>
+        <v>3.2764687538147</v>
       </c>
       <c r="H503" t="n">
         <v>1438467</v>
@@ -15014,7 +15014,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G505" t="n">
-        <v>3.29296636581421</v>
+        <v>3.29296588897705</v>
       </c>
       <c r="H505" t="n">
         <v>579212</v>
@@ -15043,7 +15043,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G506" t="n">
-        <v>3.38535380363464</v>
+        <v>3.38535404205322</v>
       </c>
       <c r="H506" t="n">
         <v>1022015</v>
@@ -15072,7 +15072,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G507" t="n">
-        <v>3.33256101608276</v>
+        <v>3.33256149291992</v>
       </c>
       <c r="H507" t="n">
         <v>310695</v>
@@ -15101,7 +15101,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G508" t="n">
-        <v>3.32596135139465</v>
+        <v>3.32596182823181</v>
       </c>
       <c r="H508" t="n">
         <v>497133</v>
@@ -15130,7 +15130,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G509" t="n">
-        <v>3.31936287879944</v>
+        <v>3.31936264038086</v>
       </c>
       <c r="H509" t="n">
         <v>378358</v>
@@ -15159,7 +15159,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G510" t="n">
-        <v>3.34575915336609</v>
+        <v>3.34575939178467</v>
       </c>
       <c r="H510" t="n">
         <v>268427</v>
@@ -15188,7 +15188,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G511" t="n">
-        <v>3.37215566635132</v>
+        <v>3.37215542793274</v>
       </c>
       <c r="H511" t="n">
         <v>270711</v>
@@ -15217,7 +15217,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G512" t="n">
-        <v>3.40515112876892</v>
+        <v>3.4051513671875</v>
       </c>
       <c r="H512" t="n">
         <v>346400</v>
@@ -15246,7 +15246,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G513" t="n">
-        <v>3.39195322990417</v>
+        <v>3.3919529914856</v>
       </c>
       <c r="H513" t="n">
         <v>270878</v>
@@ -15275,7 +15275,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G514" t="n">
-        <v>3.36555671691895</v>
+        <v>3.36555624008179</v>
       </c>
       <c r="H514" t="n">
         <v>602895</v>
@@ -15304,7 +15304,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G515" t="n">
-        <v>3.41175079345703</v>
+        <v>3.41175055503845</v>
       </c>
       <c r="H515" t="n">
         <v>430306</v>
@@ -15333,7 +15333,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G516" t="n">
-        <v>3.47114253044128</v>
+        <v>3.47114300727844</v>
       </c>
       <c r="H516" t="n">
         <v>419765</v>
@@ -15362,7 +15362,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G517" t="n">
-        <v>3.47114253044128</v>
+        <v>3.47114300727844</v>
       </c>
       <c r="H517" t="n">
         <v>482592</v>
@@ -15391,7 +15391,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G518" t="n">
-        <v>3.49094009399414</v>
+        <v>3.49093961715698</v>
       </c>
       <c r="H518" t="n">
         <v>195188</v>
@@ -15420,7 +15420,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G519" t="n">
-        <v>3.50413823127747</v>
+        <v>3.50413846969604</v>
       </c>
       <c r="H519" t="n">
         <v>436693</v>
@@ -15449,7 +15449,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G520" t="n">
-        <v>3.51073789596558</v>
+        <v>3.510737657547</v>
       </c>
       <c r="H520" t="n">
         <v>264870</v>
@@ -15478,7 +15478,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G521" t="n">
-        <v>3.47114253044128</v>
+        <v>3.47114300727844</v>
       </c>
       <c r="H521" t="n">
         <v>297721</v>
@@ -15536,7 +15536,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G523" t="n">
-        <v>3.43154764175415</v>
+        <v>3.43154788017273</v>
       </c>
       <c r="H523" t="n">
         <v>607512</v>
@@ -15565,7 +15565,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G524" t="n">
-        <v>3.39855265617371</v>
+        <v>3.39855217933655</v>
       </c>
       <c r="H524" t="n">
         <v>501174</v>
@@ -15594,7 +15594,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G525" t="n">
-        <v>3.38535380363464</v>
+        <v>3.38535404205322</v>
       </c>
       <c r="H525" t="n">
         <v>210811</v>
@@ -15623,7 +15623,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G526" t="n">
-        <v>3.35895729064941</v>
+        <v>3.35895752906799</v>
       </c>
       <c r="H526" t="n">
         <v>209893</v>
@@ -15652,7 +15652,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G527" t="n">
-        <v>3.33256101608276</v>
+        <v>3.33256149291992</v>
       </c>
       <c r="H527" t="n">
         <v>267715</v>
@@ -15710,7 +15710,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G529" t="n">
-        <v>3.27976751327515</v>
+        <v>3.27976775169373</v>
       </c>
       <c r="H529" t="n">
         <v>302738</v>
@@ -15797,7 +15797,7 @@
         <v>4.9850001335144</v>
       </c>
       <c r="G532" t="n">
-        <v>3.28966641426086</v>
+        <v>3.28966617584229</v>
       </c>
       <c r="H532" t="n">
         <v>183355</v>
@@ -15826,7 +15826,7 @@
         <v>4.9850001335144</v>
       </c>
       <c r="G533" t="n">
-        <v>3.28966641426086</v>
+        <v>3.28966617584229</v>
       </c>
       <c r="H533" t="n">
         <v>185408</v>
@@ -15855,7 +15855,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G534" t="n">
-        <v>3.27316856384277</v>
+        <v>3.27316904067993</v>
       </c>
       <c r="H534" t="n">
         <v>291730</v>
@@ -15884,7 +15884,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G535" t="n">
-        <v>3.30616450309753</v>
+        <v>3.30616474151611</v>
       </c>
       <c r="H535" t="n">
         <v>112782</v>
@@ -15942,7 +15942,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G537" t="n">
-        <v>3.14778542518616</v>
+        <v>3.14778518676758</v>
       </c>
       <c r="H537" t="n">
         <v>607886</v>
@@ -16000,7 +16000,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G539" t="n">
-        <v>3.22037577629089</v>
+        <v>3.22037601470947</v>
       </c>
       <c r="H539" t="n">
         <v>191125</v>
@@ -16029,7 +16029,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G540" t="n">
-        <v>3.20387768745422</v>
+        <v>3.20387816429138</v>
       </c>
       <c r="H540" t="n">
         <v>360189</v>
@@ -16058,7 +16058,7 @@
         <v>4.81500005722046</v>
       </c>
       <c r="G541" t="n">
-        <v>3.17748141288757</v>
+        <v>3.17748117446899</v>
       </c>
       <c r="H541" t="n">
         <v>159569</v>
@@ -16087,7 +16087,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G542" t="n">
-        <v>3.20387768745422</v>
+        <v>3.20387816429138</v>
       </c>
       <c r="H542" t="n">
         <v>307336</v>
@@ -16116,7 +16116,7 @@
         <v>4.77500009536743</v>
       </c>
       <c r="G543" t="n">
-        <v>3.15108489990234</v>
+        <v>3.15108466148376</v>
       </c>
       <c r="H543" t="n">
         <v>428166</v>
@@ -16145,7 +16145,7 @@
         <v>4.74499988555908</v>
       </c>
       <c r="G544" t="n">
-        <v>3.13128709793091</v>
+        <v>3.13128757476807</v>
       </c>
       <c r="H544" t="n">
         <v>338813</v>
@@ -16174,7 +16174,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G545" t="n">
-        <v>3.29296636581421</v>
+        <v>3.29296588897705</v>
       </c>
       <c r="H545" t="n">
         <v>324729</v>
@@ -16203,7 +16203,7 @@
         <v>4.9850001335144</v>
       </c>
       <c r="G546" t="n">
-        <v>3.28966641426086</v>
+        <v>3.28966617584229</v>
       </c>
       <c r="H546" t="n">
         <v>250598</v>
@@ -16232,7 +16232,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G547" t="n">
-        <v>3.31936287879944</v>
+        <v>3.31936264038086</v>
       </c>
       <c r="H547" t="n">
         <v>180843</v>
@@ -16377,7 +16377,7 @@
         <v>4.96500015258789</v>
       </c>
       <c r="G552" t="n">
-        <v>3.27646827697754</v>
+        <v>3.2764687538147</v>
       </c>
       <c r="H552" t="n">
         <v>244304</v>
@@ -16406,7 +16406,7 @@
         <v>4.93499994277954</v>
       </c>
       <c r="G553" t="n">
-        <v>3.25667119026184</v>
+        <v>3.25667095184326</v>
       </c>
       <c r="H553" t="n">
         <v>159508</v>
@@ -16435,7 +16435,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G554" t="n">
-        <v>3.24017310142517</v>
+        <v>3.24017286300659</v>
       </c>
       <c r="H554" t="n">
         <v>201398</v>
@@ -16493,7 +16493,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G556" t="n">
-        <v>3.29296636581421</v>
+        <v>3.29296588897705</v>
       </c>
       <c r="H556" t="n">
         <v>732921</v>
@@ -16522,7 +16522,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G557" t="n">
-        <v>3.31936287879944</v>
+        <v>3.31936264038086</v>
       </c>
       <c r="H557" t="n">
         <v>705472</v>
@@ -16609,7 +16609,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G560" t="n">
-        <v>3.22037577629089</v>
+        <v>3.22037601470947</v>
       </c>
       <c r="H560" t="n">
         <v>229037</v>
@@ -16638,7 +16638,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G561" t="n">
-        <v>3.20717763900757</v>
+        <v>3.20717740058899</v>
       </c>
       <c r="H561" t="n">
         <v>164491</v>
@@ -16667,7 +16667,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G562" t="n">
-        <v>3.21377658843994</v>
+        <v>3.21377635002136</v>
       </c>
       <c r="H562" t="n">
         <v>261298</v>
@@ -16812,7 +16812,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G567" t="n">
-        <v>3.33256101608276</v>
+        <v>3.33256149291992</v>
       </c>
       <c r="H567" t="n">
         <v>658583</v>
@@ -16841,7 +16841,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G568" t="n">
-        <v>3.33916020393372</v>
+        <v>3.33916044235229</v>
       </c>
       <c r="H568" t="n">
         <v>424813</v>
@@ -16870,7 +16870,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G569" t="n">
-        <v>3.35235786437988</v>
+        <v>3.35235810279846</v>
       </c>
       <c r="H569" t="n">
         <v>293303</v>
@@ -16899,7 +16899,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G570" t="n">
-        <v>3.33256101608276</v>
+        <v>3.33256149291992</v>
       </c>
       <c r="H570" t="n">
         <v>189800</v>
@@ -16928,7 +16928,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G571" t="n">
-        <v>3.35895729064941</v>
+        <v>3.35895752906799</v>
       </c>
       <c r="H571" t="n">
         <v>455695</v>
@@ -16957,7 +16957,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G572" t="n">
-        <v>3.36555671691895</v>
+        <v>3.36555624008179</v>
       </c>
       <c r="H572" t="n">
         <v>211464</v>
@@ -16986,7 +16986,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G573" t="n">
-        <v>3.34575915336609</v>
+        <v>3.34575939178467</v>
       </c>
       <c r="H573" t="n">
         <v>194648</v>
@@ -17015,7 +17015,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G574" t="n">
-        <v>3.32596135139465</v>
+        <v>3.32596182823181</v>
       </c>
       <c r="H574" t="n">
         <v>241099</v>
@@ -17044,7 +17044,7 @@
         <v>4.99499988555908</v>
       </c>
       <c r="G575" t="n">
-        <v>3.29626560211182</v>
+        <v>3.29626536369324</v>
       </c>
       <c r="H575" t="n">
         <v>489413</v>
@@ -17073,7 +17073,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G576" t="n">
-        <v>3.31936287879944</v>
+        <v>3.31936264038086</v>
       </c>
       <c r="H576" t="n">
         <v>553332</v>
@@ -17102,7 +17102,7 @@
         <v>4.99499988555908</v>
       </c>
       <c r="G577" t="n">
-        <v>3.29626560211182</v>
+        <v>3.29626536369324</v>
       </c>
       <c r="H577" t="n">
         <v>400508</v>
@@ -17160,7 +17160,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G579" t="n">
-        <v>3.24677228927612</v>
+        <v>3.24677205085754</v>
       </c>
       <c r="H579" t="n">
         <v>142859</v>
@@ -17218,7 +17218,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G581" t="n">
-        <v>3.22037577629089</v>
+        <v>3.22037601470947</v>
       </c>
       <c r="H581" t="n">
         <v>211872</v>
@@ -17247,7 +17247,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G582" t="n">
-        <v>3.24677228927612</v>
+        <v>3.24677205085754</v>
       </c>
       <c r="H582" t="n">
         <v>266759</v>
@@ -17334,7 +17334,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G585" t="n">
-        <v>3.22697448730469</v>
+        <v>3.22697472572327</v>
       </c>
       <c r="H585" t="n">
         <v>392732</v>
@@ -17392,7 +17392,7 @@
         <v>4.96500015258789</v>
       </c>
       <c r="G587" t="n">
-        <v>3.27646827697754</v>
+        <v>3.2764687538147</v>
       </c>
       <c r="H587" t="n">
         <v>337593</v>
@@ -17421,7 +17421,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G588" t="n">
-        <v>3.23027420043945</v>
+        <v>3.23027467727661</v>
       </c>
       <c r="H588" t="n">
         <v>169004</v>
@@ -17450,7 +17450,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G589" t="n">
-        <v>3.20387768745422</v>
+        <v>3.20387816429138</v>
       </c>
       <c r="H589" t="n">
         <v>262105</v>
@@ -17479,7 +17479,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G590" t="n">
-        <v>3.27316856384277</v>
+        <v>3.27316904067993</v>
       </c>
       <c r="H590" t="n">
         <v>306419</v>
@@ -17508,7 +17508,7 @@
         <v>4.96500015258789</v>
       </c>
       <c r="G591" t="n">
-        <v>3.27646827697754</v>
+        <v>3.2764687538147</v>
       </c>
       <c r="H591" t="n">
         <v>197893</v>
@@ -17537,7 +17537,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G592" t="n">
-        <v>3.20717763900757</v>
+        <v>3.20717740058899</v>
       </c>
       <c r="H592" t="n">
         <v>433144</v>
@@ -17595,7 +17595,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G594" t="n">
-        <v>2.93001365661621</v>
+        <v>2.93001437187195</v>
       </c>
       <c r="H594" t="n">
         <v>554636</v>
@@ -17624,7 +17624,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G595" t="n">
-        <v>3.00920343399048</v>
+        <v>3.0092031955719</v>
       </c>
       <c r="H595" t="n">
         <v>548032</v>
@@ -17653,7 +17653,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G596" t="n">
-        <v>2.94321203231812</v>
+        <v>2.94321227073669</v>
       </c>
       <c r="H596" t="n">
         <v>369522</v>
@@ -17711,7 +17711,7 @@
         <v>4.7350001335144</v>
       </c>
       <c r="G598" t="n">
-        <v>3.12468862533569</v>
+        <v>3.12468838691711</v>
       </c>
       <c r="H598" t="n">
         <v>362477</v>
@@ -17740,7 +17740,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G599" t="n">
-        <v>2.99930477142334</v>
+        <v>2.9993052482605</v>
       </c>
       <c r="H599" t="n">
         <v>459016</v>
@@ -17827,7 +17827,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G602" t="n">
-        <v>2.99930477142334</v>
+        <v>2.9993052482605</v>
       </c>
       <c r="H602" t="n">
         <v>294153</v>
@@ -17856,7 +17856,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G603" t="n">
-        <v>3.00260424613953</v>
+        <v>3.00260448455811</v>
       </c>
       <c r="H603" t="n">
         <v>113692</v>
@@ -17914,7 +17914,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G605" t="n">
-        <v>3.01580286026001</v>
+        <v>3.01580262184143</v>
       </c>
       <c r="H605" t="n">
         <v>412759</v>
@@ -17943,7 +17943,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G606" t="n">
-        <v>3.03230047225952</v>
+        <v>3.03230023384094</v>
       </c>
       <c r="H606" t="n">
         <v>628721</v>
@@ -18001,7 +18001,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G608" t="n">
-        <v>3.05539727210999</v>
+        <v>3.05539751052856</v>
       </c>
       <c r="H608" t="n">
         <v>214042</v>
@@ -18030,7 +18030,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G609" t="n">
-        <v>3.06859564781189</v>
+        <v>3.06859540939331</v>
       </c>
       <c r="H609" t="n">
         <v>181645</v>
@@ -18059,7 +18059,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G610" t="n">
-        <v>3.06859564781189</v>
+        <v>3.06859540939331</v>
       </c>
       <c r="H610" t="n">
         <v>433730</v>
@@ -18088,7 +18088,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G611" t="n">
-        <v>3.08839297294617</v>
+        <v>3.08839273452759</v>
       </c>
       <c r="H611" t="n">
         <v>391802</v>
@@ -18175,7 +18175,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G614" t="n">
-        <v>3.17418122291565</v>
+        <v>3.17418146133423</v>
       </c>
       <c r="H614" t="n">
         <v>516589</v>
@@ -18204,7 +18204,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G615" t="n">
-        <v>3.17418122291565</v>
+        <v>3.17418146133423</v>
       </c>
       <c r="H615" t="n">
         <v>772590</v>
@@ -18233,7 +18233,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G616" t="n">
-        <v>3.15768337249756</v>
+        <v>3.15768384933472</v>
       </c>
       <c r="H616" t="n">
         <v>413605</v>
@@ -18262,7 +18262,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G617" t="n">
-        <v>3.20717763900757</v>
+        <v>3.20717740058899</v>
       </c>
       <c r="H617" t="n">
         <v>392932</v>
@@ -18291,7 +18291,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G618" t="n">
-        <v>3.18738007545471</v>
+        <v>3.18737983703613</v>
       </c>
       <c r="H618" t="n">
         <v>209724</v>
@@ -18349,7 +18349,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G620" t="n">
-        <v>3.1807804107666</v>
+        <v>3.18078064918518</v>
       </c>
       <c r="H620" t="n">
         <v>233302</v>
@@ -18378,7 +18378,7 @@
         <v>4.875</v>
       </c>
       <c r="G621" t="n">
-        <v>3.21707606315613</v>
+        <v>3.21707582473755</v>
       </c>
       <c r="H621" t="n">
         <v>150933</v>
@@ -18407,7 +18407,7 @@
         <v>4.81500005722046</v>
       </c>
       <c r="G622" t="n">
-        <v>3.17748141288757</v>
+        <v>3.17748117446899</v>
       </c>
       <c r="H622" t="n">
         <v>343744</v>
@@ -18436,7 +18436,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G623" t="n">
-        <v>3.16758251190186</v>
+        <v>3.16758322715759</v>
       </c>
       <c r="H623" t="n">
         <v>230869</v>
@@ -18465,7 +18465,7 @@
         <v>4.77500009536743</v>
       </c>
       <c r="G624" t="n">
-        <v>3.15108489990234</v>
+        <v>3.15108466148376</v>
       </c>
       <c r="H624" t="n">
         <v>214584</v>
@@ -18494,7 +18494,7 @@
         <v>4.74499988555908</v>
       </c>
       <c r="G625" t="n">
-        <v>3.13128709793091</v>
+        <v>3.13128757476807</v>
       </c>
       <c r="H625" t="n">
         <v>321351</v>
@@ -18523,7 +18523,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G626" t="n">
-        <v>3.15768337249756</v>
+        <v>3.15768384933472</v>
       </c>
       <c r="H626" t="n">
         <v>165203</v>
@@ -18552,7 +18552,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G627" t="n">
-        <v>3.17418122291565</v>
+        <v>3.17418146133423</v>
       </c>
       <c r="H627" t="n">
         <v>513181</v>
@@ -18581,7 +18581,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G628" t="n">
-        <v>3.15768337249756</v>
+        <v>3.15768384933472</v>
       </c>
       <c r="H628" t="n">
         <v>241411</v>
@@ -18610,7 +18610,7 @@
         <v>4.75500011444092</v>
       </c>
       <c r="G629" t="n">
-        <v>3.13788676261902</v>
+        <v>3.13788652420044</v>
       </c>
       <c r="H629" t="n">
         <v>196694</v>
@@ -18639,7 +18639,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G630" t="n">
-        <v>3.10159111022949</v>
+        <v>3.10159134864807</v>
       </c>
       <c r="H630" t="n">
         <v>399107</v>
@@ -18668,7 +18668,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G631" t="n">
-        <v>3.10819053649902</v>
+        <v>3.10819029808044</v>
       </c>
       <c r="H631" t="n">
         <v>267135</v>
@@ -18726,7 +18726,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G633" t="n">
-        <v>3.16758251190186</v>
+        <v>3.16758322715759</v>
       </c>
       <c r="H633" t="n">
         <v>124776</v>
@@ -18755,7 +18755,7 @@
         <v>4.80499982833862</v>
       </c>
       <c r="G634" t="n">
-        <v>3.17088222503662</v>
+        <v>3.17088198661804</v>
       </c>
       <c r="H634" t="n">
         <v>318243</v>
@@ -18784,7 +18784,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G635" t="n">
-        <v>3.20057797431946</v>
+        <v>3.20057821273804</v>
       </c>
       <c r="H635" t="n">
         <v>355617</v>
@@ -18813,7 +18813,7 @@
         <v>4.88500022888184</v>
       </c>
       <c r="G636" t="n">
-        <v>3.22367525100708</v>
+        <v>3.22367548942566</v>
       </c>
       <c r="H636" t="n">
         <v>347918</v>
@@ -18871,7 +18871,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G638" t="n">
-        <v>3.31936287879944</v>
+        <v>3.31936264038086</v>
       </c>
       <c r="H638" t="n">
         <v>324782</v>
@@ -18900,7 +18900,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G639" t="n">
-        <v>3.35895729064941</v>
+        <v>3.35895752906799</v>
       </c>
       <c r="H639" t="n">
         <v>367299</v>
@@ -18929,7 +18929,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G640" t="n">
-        <v>3.33916020393372</v>
+        <v>3.33916044235229</v>
       </c>
       <c r="H640" t="n">
         <v>413174</v>
@@ -18987,7 +18987,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G642" t="n">
-        <v>3.51073789596558</v>
+        <v>3.510737657547</v>
       </c>
       <c r="H642" t="n">
         <v>498133</v>
@@ -19045,7 +19045,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G644" t="n">
-        <v>3.55033230781555</v>
+        <v>3.55033183097839</v>
       </c>
       <c r="H644" t="n">
         <v>810423</v>
@@ -19074,7 +19074,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G645" t="n">
-        <v>3.54373288154602</v>
+        <v>3.5437331199646</v>
       </c>
       <c r="H645" t="n">
         <v>270515</v>
@@ -19103,7 +19103,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G646" t="n">
-        <v>3.5305347442627</v>
+        <v>3.53053498268127</v>
       </c>
       <c r="H646" t="n">
         <v>298286</v>
@@ -19132,7 +19132,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G647" t="n">
-        <v>3.55693125724792</v>
+        <v>3.55693101882935</v>
       </c>
       <c r="H647" t="n">
         <v>182303</v>
@@ -19161,7 +19161,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G648" t="n">
-        <v>3.5965256690979</v>
+        <v>3.59652614593506</v>
       </c>
       <c r="H648" t="n">
         <v>386804</v>
@@ -19190,7 +19190,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G649" t="n">
-        <v>3.61632323265076</v>
+        <v>3.61632370948792</v>
       </c>
       <c r="H649" t="n">
         <v>682311</v>
@@ -19219,7 +19219,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G650" t="n">
-        <v>3.58332753181458</v>
+        <v>3.58332800865173</v>
       </c>
       <c r="H650" t="n">
         <v>463002</v>
@@ -19248,7 +19248,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G651" t="n">
-        <v>3.58332753181458</v>
+        <v>3.58332800865173</v>
       </c>
       <c r="H651" t="n">
         <v>259823</v>
@@ -19277,7 +19277,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G652" t="n">
-        <v>3.60972452163696</v>
+        <v>3.6097240447998</v>
       </c>
       <c r="H652" t="n">
         <v>205376</v>
@@ -19306,7 +19306,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G653" t="n">
-        <v>3.60972452163696</v>
+        <v>3.6097240447998</v>
       </c>
       <c r="H653" t="n">
         <v>774761</v>
@@ -19335,7 +19335,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G654" t="n">
-        <v>3.60972452163696</v>
+        <v>3.6097240447998</v>
       </c>
       <c r="H654" t="n">
         <v>518047</v>
@@ -19364,7 +19364,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G655" t="n">
-        <v>3.56353068351746</v>
+        <v>3.56353044509888</v>
       </c>
       <c r="H655" t="n">
         <v>465278</v>
@@ -19393,7 +19393,7 @@
         <v>5.5</v>
       </c>
       <c r="G656" t="n">
-        <v>3.62952208518982</v>
+        <v>3.6295211315155</v>
       </c>
       <c r="H656" t="n">
         <v>522326</v>
@@ -19422,7 +19422,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G657" t="n">
-        <v>3.5305347442627</v>
+        <v>3.53053498268127</v>
       </c>
       <c r="H657" t="n">
         <v>819041</v>
@@ -19480,7 +19480,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G659" t="n">
-        <v>3.5305347442627</v>
+        <v>3.53053498268127</v>
       </c>
       <c r="H659" t="n">
         <v>882957</v>
@@ -19509,7 +19509,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G660" t="n">
-        <v>3.5305347442627</v>
+        <v>3.53053498268127</v>
       </c>
       <c r="H660" t="n">
         <v>685814</v>
@@ -19538,7 +19538,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G661" t="n">
-        <v>3.52393579483032</v>
+        <v>3.52393555641174</v>
       </c>
       <c r="H661" t="n">
         <v>322262</v>
@@ -19567,7 +19567,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G662" t="n">
-        <v>3.56353068351746</v>
+        <v>3.56353044509888</v>
       </c>
       <c r="H662" t="n">
         <v>423318</v>
@@ -19596,7 +19596,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G663" t="n">
-        <v>3.51733660697937</v>
+        <v>3.51733589172363</v>
       </c>
       <c r="H663" t="n">
         <v>264447</v>
@@ -19625,7 +19625,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G664" t="n">
-        <v>3.47114253044128</v>
+        <v>3.47114300727844</v>
       </c>
       <c r="H664" t="n">
         <v>357968</v>
@@ -19654,7 +19654,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G665" t="n">
-        <v>3.4447455406189</v>
+        <v>3.44474577903748</v>
       </c>
       <c r="H665" t="n">
         <v>534929</v>
@@ -19683,7 +19683,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G666" t="n">
-        <v>3.47114253044128</v>
+        <v>3.47114300727844</v>
       </c>
       <c r="H666" t="n">
         <v>307259</v>
@@ -19712,7 +19712,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G667" t="n">
-        <v>3.5305347442627</v>
+        <v>3.53053498268127</v>
       </c>
       <c r="H667" t="n">
         <v>427480</v>
@@ -19741,7 +19741,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G668" t="n">
-        <v>3.55693125724792</v>
+        <v>3.55693101882935</v>
       </c>
       <c r="H668" t="n">
         <v>462341</v>
@@ -19770,7 +19770,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G669" t="n">
-        <v>3.57012891769409</v>
+        <v>3.57012963294983</v>
       </c>
       <c r="H669" t="n">
         <v>900918</v>
@@ -19799,7 +19799,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G670" t="n">
-        <v>3.5767285823822</v>
+        <v>3.57672929763794</v>
       </c>
       <c r="H670" t="n">
         <v>1287483</v>
@@ -19828,7 +19828,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G671" t="n">
-        <v>3.60972452163696</v>
+        <v>3.6097240447998</v>
       </c>
       <c r="H671" t="n">
         <v>439505</v>
@@ -19886,7 +19886,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G673" t="n">
-        <v>3.54373288154602</v>
+        <v>3.5437331199646</v>
       </c>
       <c r="H673" t="n">
         <v>753716</v>
@@ -19915,7 +19915,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G674" t="n">
-        <v>3.5305347442627</v>
+        <v>3.53053498268127</v>
       </c>
       <c r="H674" t="n">
         <v>371452</v>
@@ -19944,7 +19944,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G675" t="n">
-        <v>3.53713440895081</v>
+        <v>3.53713393211365</v>
       </c>
       <c r="H675" t="n">
         <v>179341</v>
@@ -19973,7 +19973,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G676" t="n">
-        <v>3.55033230781555</v>
+        <v>3.55033183097839</v>
       </c>
       <c r="H676" t="n">
         <v>194556</v>
@@ -20002,7 +20002,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G677" t="n">
-        <v>3.57012891769409</v>
+        <v>3.57012963294983</v>
       </c>
       <c r="H677" t="n">
         <v>177748</v>
@@ -20031,7 +20031,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G678" t="n">
-        <v>3.51733660697937</v>
+        <v>3.51733589172363</v>
       </c>
       <c r="H678" t="n">
         <v>447708</v>
@@ -20060,7 +20060,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G679" t="n">
-        <v>3.49753880500793</v>
+        <v>3.49753928184509</v>
       </c>
       <c r="H679" t="n">
         <v>182643</v>
@@ -20089,7 +20089,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G680" t="n">
-        <v>3.54373288154602</v>
+        <v>3.5437331199646</v>
       </c>
       <c r="H680" t="n">
         <v>144245</v>
@@ -20118,7 +20118,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G681" t="n">
-        <v>3.5305347442627</v>
+        <v>3.53053498268127</v>
       </c>
       <c r="H681" t="n">
         <v>280241</v>
@@ -20147,7 +20147,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G682" t="n">
-        <v>3.51073789596558</v>
+        <v>3.510737657547</v>
       </c>
       <c r="H682" t="n">
         <v>373119</v>
@@ -20176,7 +20176,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G683" t="n">
-        <v>3.49094009399414</v>
+        <v>3.49093961715698</v>
       </c>
       <c r="H683" t="n">
         <v>378018</v>
@@ -20205,7 +20205,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G684" t="n">
-        <v>3.50413823127747</v>
+        <v>3.50413846969604</v>
       </c>
       <c r="H684" t="n">
         <v>311667</v>
@@ -20234,7 +20234,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G685" t="n">
-        <v>3.55033230781555</v>
+        <v>3.55033183097839</v>
       </c>
       <c r="H685" t="n">
         <v>218627</v>
@@ -20263,7 +20263,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G686" t="n">
-        <v>3.5305347442627</v>
+        <v>3.53053498268127</v>
       </c>
       <c r="H686" t="n">
         <v>333103</v>
@@ -20292,7 +20292,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G687" t="n">
-        <v>3.51733660697937</v>
+        <v>3.51733589172363</v>
       </c>
       <c r="H687" t="n">
         <v>264164</v>
@@ -20321,7 +20321,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G688" t="n">
-        <v>3.49753880500793</v>
+        <v>3.49753928184509</v>
       </c>
       <c r="H688" t="n">
         <v>161714</v>
@@ -20379,7 +20379,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G690" t="n">
-        <v>3.52393579483032</v>
+        <v>3.52393555641174</v>
       </c>
       <c r="H690" t="n">
         <v>131707</v>
@@ -20408,7 +20408,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G691" t="n">
-        <v>3.54373288154602</v>
+        <v>3.5437331199646</v>
       </c>
       <c r="H691" t="n">
         <v>183512</v>
@@ -20437,7 +20437,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G692" t="n">
-        <v>3.50413823127747</v>
+        <v>3.50413846969604</v>
       </c>
       <c r="H692" t="n">
         <v>281512</v>
@@ -20466,7 +20466,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G693" t="n">
-        <v>3.49753880500793</v>
+        <v>3.49753928184509</v>
       </c>
       <c r="H693" t="n">
         <v>236744</v>
@@ -20495,7 +20495,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G694" t="n">
-        <v>3.5305347442627</v>
+        <v>3.53053498268127</v>
       </c>
       <c r="H694" t="n">
         <v>305166</v>
@@ -20524,7 +20524,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G695" t="n">
-        <v>3.53713440895081</v>
+        <v>3.53713393211365</v>
       </c>
       <c r="H695" t="n">
         <v>235432</v>
@@ -20553,7 +20553,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G696" t="n">
-        <v>3.55693125724792</v>
+        <v>3.55693101882935</v>
       </c>
       <c r="H696" t="n">
         <v>284871</v>
@@ -20582,7 +20582,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G697" t="n">
-        <v>3.5305347442627</v>
+        <v>3.53053498268127</v>
       </c>
       <c r="H697" t="n">
         <v>2007774</v>
@@ -20611,7 +20611,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G698" t="n">
-        <v>3.51733660697937</v>
+        <v>3.51733589172363</v>
       </c>
       <c r="H698" t="n">
         <v>584668</v>
@@ -20640,7 +20640,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G699" t="n">
-        <v>3.55693125724792</v>
+        <v>3.55693101882935</v>
       </c>
       <c r="H699" t="n">
         <v>963684</v>
@@ -20669,7 +20669,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G700" t="n">
-        <v>3.56353068351746</v>
+        <v>3.56353044509888</v>
       </c>
       <c r="H700" t="n">
         <v>462682</v>
@@ -20698,7 +20698,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G701" t="n">
-        <v>3.53713440895081</v>
+        <v>3.53713393211365</v>
       </c>
       <c r="H701" t="n">
         <v>340867</v>
@@ -20727,7 +20727,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G702" t="n">
-        <v>3.58992695808411</v>
+        <v>3.58992719650269</v>
       </c>
       <c r="H702" t="n">
         <v>385089</v>
@@ -20756,7 +20756,7 @@
         <v>5.5</v>
       </c>
       <c r="G703" t="n">
-        <v>3.62952208518982</v>
+        <v>3.6295211315155</v>
       </c>
       <c r="H703" t="n">
         <v>607552</v>
@@ -20785,7 +20785,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G704" t="n">
-        <v>3.70871090888977</v>
+        <v>3.70871162414551</v>
       </c>
       <c r="H704" t="n">
         <v>835923</v>
@@ -20814,7 +20814,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G705" t="n">
-        <v>3.72850942611694</v>
+        <v>3.72850894927979</v>
       </c>
       <c r="H705" t="n">
         <v>1055303</v>
@@ -20959,7 +20959,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G710" t="n">
-        <v>3.74830627441406</v>
+        <v>3.74830555915833</v>
       </c>
       <c r="H710" t="n">
         <v>838597</v>
@@ -20988,7 +20988,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G711" t="n">
-        <v>3.66251754760742</v>
+        <v>3.66251730918884</v>
       </c>
       <c r="H711" t="n">
         <v>543254</v>
@@ -21017,7 +21017,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G712" t="n">
-        <v>3.66251754760742</v>
+        <v>3.66251730918884</v>
       </c>
       <c r="H712" t="n">
         <v>667564</v>
@@ -21046,7 +21046,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G713" t="n">
-        <v>3.68891334533691</v>
+        <v>3.68891406059265</v>
       </c>
       <c r="H713" t="n">
         <v>447125</v>
@@ -21075,7 +21075,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G714" t="n">
-        <v>3.70871090888977</v>
+        <v>3.70871162414551</v>
       </c>
       <c r="H714" t="n">
         <v>295322</v>
@@ -21104,7 +21104,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G715" t="n">
-        <v>3.77470254898071</v>
+        <v>3.77470231056213</v>
       </c>
       <c r="H715" t="n">
         <v>632836</v>
@@ -21133,7 +21133,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G716" t="n">
-        <v>3.74830627441406</v>
+        <v>3.74830555915833</v>
       </c>
       <c r="H716" t="n">
         <v>696688</v>
@@ -21162,7 +21162,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G717" t="n">
-        <v>3.74830627441406</v>
+        <v>3.74830555915833</v>
       </c>
       <c r="H717" t="n">
         <v>330391</v>
@@ -21220,7 +21220,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G719" t="n">
-        <v>3.78130173683167</v>
+        <v>3.78130149841309</v>
       </c>
       <c r="H719" t="n">
         <v>510577</v>
@@ -21249,7 +21249,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G720" t="n">
-        <v>3.82749509811401</v>
+        <v>3.82749557495117</v>
       </c>
       <c r="H720" t="n">
         <v>1225246</v>
@@ -21278,7 +21278,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G721" t="n">
-        <v>3.82749509811401</v>
+        <v>3.82749557495117</v>
       </c>
       <c r="H721" t="n">
         <v>435487</v>
@@ -21307,7 +21307,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G722" t="n">
-        <v>3.87368941307068</v>
+        <v>3.8736891746521</v>
       </c>
       <c r="H722" t="n">
         <v>580517</v>
@@ -21336,7 +21336,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G723" t="n">
-        <v>3.93308210372925</v>
+        <v>3.93308162689209</v>
       </c>
       <c r="H723" t="n">
         <v>848063</v>
@@ -21365,7 +21365,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G724" t="n">
-        <v>3.93308210372925</v>
+        <v>3.93308162689209</v>
       </c>
       <c r="H724" t="n">
         <v>494606</v>
@@ -21394,7 +21394,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G725" t="n">
-        <v>4.03866815567017</v>
+        <v>4.03866767883301</v>
       </c>
       <c r="H725" t="n">
         <v>1308208</v>
@@ -21481,7 +21481,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G728" t="n">
-        <v>3.76150465011597</v>
+        <v>3.76150393486023</v>
       </c>
       <c r="H728" t="n">
         <v>1413864</v>
@@ -21510,7 +21510,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G729" t="n">
-        <v>3.72190952301025</v>
+        <v>3.72190976142883</v>
       </c>
       <c r="H729" t="n">
         <v>888399</v>
@@ -21539,7 +21539,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G730" t="n">
-        <v>3.84729313850403</v>
+        <v>3.84729337692261</v>
       </c>
       <c r="H730" t="n">
         <v>878154</v>
@@ -21568,7 +21568,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G731" t="n">
-        <v>3.75490522384644</v>
+        <v>3.75490474700928</v>
       </c>
       <c r="H731" t="n">
         <v>972068</v>
@@ -21597,7 +21597,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G732" t="n">
-        <v>3.6493194103241</v>
+        <v>3.64931917190552</v>
       </c>
       <c r="H732" t="n">
         <v>1140649</v>
@@ -21655,7 +21655,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G734" t="n">
-        <v>3.55693125724792</v>
+        <v>3.55693101882935</v>
       </c>
       <c r="H734" t="n">
         <v>945739</v>
@@ -21684,7 +21684,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G735" t="n">
-        <v>3.51073789596558</v>
+        <v>3.510737657547</v>
       </c>
       <c r="H735" t="n">
         <v>447939</v>
@@ -21771,7 +21771,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G738" t="n">
-        <v>3.06859564781189</v>
+        <v>3.06859540939331</v>
       </c>
       <c r="H738" t="n">
         <v>1138697</v>
@@ -21916,7 +21916,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G743" t="n">
-        <v>2.76503562927246</v>
+        <v>2.76503539085388</v>
       </c>
       <c r="H743" t="n">
         <v>1314392</v>
@@ -21974,7 +21974,7 @@
         <v>4.07499980926514</v>
       </c>
       <c r="G745" t="n">
-        <v>2.68914556503296</v>
+        <v>2.68914532661438</v>
       </c>
       <c r="H745" t="n">
         <v>431233</v>
@@ -22061,7 +22061,7 @@
         <v>4.56500005722046</v>
       </c>
       <c r="G748" t="n">
-        <v>3.01250267028809</v>
+        <v>3.01250314712524</v>
       </c>
       <c r="H748" t="n">
         <v>779278</v>
@@ -22119,7 +22119,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G750" t="n">
-        <v>3.06859564781189</v>
+        <v>3.06859540939331</v>
       </c>
       <c r="H750" t="n">
         <v>518902</v>
@@ -22177,7 +22177,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G752" t="n">
-        <v>3.16758251190186</v>
+        <v>3.16758322715759</v>
       </c>
       <c r="H752" t="n">
         <v>382070</v>
@@ -22206,7 +22206,7 @@
         <v>4.43499994277954</v>
       </c>
       <c r="G753" t="n">
-        <v>2.9267144203186</v>
+        <v>2.92671465873718</v>
       </c>
       <c r="H753" t="n">
         <v>370305</v>
@@ -22235,7 +22235,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G754" t="n">
-        <v>3.12138867378235</v>
+        <v>3.12138891220093</v>
       </c>
       <c r="H754" t="n">
         <v>1180069</v>
@@ -22264,7 +22264,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G755" t="n">
-        <v>3.11808919906616</v>
+        <v>3.11808896064758</v>
       </c>
       <c r="H755" t="n">
         <v>339120</v>
@@ -22322,7 +22322,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G757" t="n">
-        <v>3.01580286026001</v>
+        <v>3.01580262184143</v>
       </c>
       <c r="H757" t="n">
         <v>273018</v>
@@ -22351,7 +22351,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G758" t="n">
-        <v>3.10159111022949</v>
+        <v>3.10159134864807</v>
       </c>
       <c r="H758" t="n">
         <v>354219</v>
@@ -22409,7 +22409,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G760" t="n">
-        <v>3.33916020393372</v>
+        <v>3.33916044235229</v>
       </c>
       <c r="H760" t="n">
         <v>280545</v>
@@ -22438,7 +22438,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G761" t="n">
-        <v>3.36555671691895</v>
+        <v>3.36555624008179</v>
       </c>
       <c r="H761" t="n">
         <v>237082</v>
@@ -22525,7 +22525,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G764" t="n">
-        <v>3.10819053649902</v>
+        <v>3.10819029808044</v>
       </c>
       <c r="H764" t="n">
         <v>368449</v>
@@ -22554,7 +22554,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G765" t="n">
-        <v>3.08839297294617</v>
+        <v>3.08839273452759</v>
       </c>
       <c r="H765" t="n">
         <v>200989</v>
@@ -22612,7 +22612,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G767" t="n">
-        <v>3.11808919906616</v>
+        <v>3.11808896064758</v>
       </c>
       <c r="H767" t="n">
         <v>311282</v>
@@ -22641,7 +22641,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G768" t="n">
-        <v>3.11478972434998</v>
+        <v>3.11478924751282</v>
       </c>
       <c r="H768" t="n">
         <v>157163</v>
@@ -22670,7 +22670,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G769" t="n">
-        <v>3.11808919906616</v>
+        <v>3.11808896064758</v>
       </c>
       <c r="H769" t="n">
         <v>179026</v>
@@ -22699,7 +22699,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G770" t="n">
-        <v>3.10159111022949</v>
+        <v>3.10159134864807</v>
       </c>
       <c r="H770" t="n">
         <v>148040</v>
@@ -22728,7 +22728,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G771" t="n">
-        <v>3.15768337249756</v>
+        <v>3.15768384933472</v>
       </c>
       <c r="H771" t="n">
         <v>152570</v>
@@ -22757,7 +22757,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G772" t="n">
-        <v>3.24017310142517</v>
+        <v>3.24017286300659</v>
       </c>
       <c r="H772" t="n">
         <v>273705</v>
@@ -22786,7 +22786,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G773" t="n">
-        <v>3.24017310142517</v>
+        <v>3.24017286300659</v>
       </c>
       <c r="H773" t="n">
         <v>440452</v>
@@ -22815,7 +22815,7 @@
         <v>4.71500015258789</v>
       </c>
       <c r="G774" t="n">
-        <v>3.11148977279663</v>
+        <v>3.11149024963379</v>
       </c>
       <c r="H774" t="n">
         <v>282307</v>
@@ -22844,7 +22844,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G775" t="n">
-        <v>3.00260424613953</v>
+        <v>3.00260448455811</v>
       </c>
       <c r="H775" t="n">
         <v>200490</v>
@@ -22902,7 +22902,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G777" t="n">
-        <v>3.06199598312378</v>
+        <v>3.0619969367981</v>
       </c>
       <c r="H777" t="n">
         <v>234472</v>
@@ -22960,7 +22960,7 @@
         <v>4.82499980926514</v>
       </c>
       <c r="G779" t="n">
-        <v>3.18408012390137</v>
+        <v>3.18408036231995</v>
       </c>
       <c r="H779" t="n">
         <v>351158</v>
@@ -22989,7 +22989,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G780" t="n">
-        <v>3.17418122291565</v>
+        <v>3.17418146133423</v>
       </c>
       <c r="H780" t="n">
         <v>293195</v>
@@ -23105,7 +23105,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G784" t="n">
-        <v>3.22697448730469</v>
+        <v>3.22697472572327</v>
       </c>
       <c r="H784" t="n">
         <v>256228</v>
@@ -23163,7 +23163,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G786" t="n">
-        <v>3.36555671691895</v>
+        <v>3.36555624008179</v>
       </c>
       <c r="H786" t="n">
         <v>387278</v>
@@ -23250,7 +23250,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G789" t="n">
-        <v>3.30616450309753</v>
+        <v>3.30616474151611</v>
       </c>
       <c r="H789" t="n">
         <v>459020</v>
@@ -23279,7 +23279,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G790" t="n">
-        <v>3.33256101608276</v>
+        <v>3.33256149291992</v>
       </c>
       <c r="H790" t="n">
         <v>113121</v>
@@ -23308,7 +23308,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G791" t="n">
-        <v>3.41175079345703</v>
+        <v>3.41175055503845</v>
       </c>
       <c r="H791" t="n">
         <v>215956</v>
@@ -23337,7 +23337,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G792" t="n">
-        <v>3.4447455406189</v>
+        <v>3.44474577903748</v>
       </c>
       <c r="H792" t="n">
         <v>514453</v>
@@ -23366,7 +23366,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G793" t="n">
-        <v>3.41175079345703</v>
+        <v>3.41175055503845</v>
       </c>
       <c r="H793" t="n">
         <v>387835</v>
@@ -23395,7 +23395,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G794" t="n">
-        <v>3.52393579483032</v>
+        <v>3.52393555641174</v>
       </c>
       <c r="H794" t="n">
         <v>1051283</v>
@@ -23424,7 +23424,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G795" t="n">
-        <v>3.52393579483032</v>
+        <v>3.52393555641174</v>
       </c>
       <c r="H795" t="n">
         <v>712372</v>
@@ -23453,7 +23453,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G796" t="n">
-        <v>3.35235786437988</v>
+        <v>3.35235810279846</v>
       </c>
       <c r="H796" t="n">
         <v>2450292</v>
@@ -23482,7 +23482,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G797" t="n">
-        <v>3.37215566635132</v>
+        <v>3.37215542793274</v>
       </c>
       <c r="H797" t="n">
         <v>923096</v>
@@ -23540,7 +23540,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G799" t="n">
-        <v>3.40515112876892</v>
+        <v>3.4051513671875</v>
       </c>
       <c r="H799" t="n">
         <v>1096765</v>
@@ -23685,7 +23685,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G804" t="n">
-        <v>3.11808919906616</v>
+        <v>3.11808896064758</v>
       </c>
       <c r="H804" t="n">
         <v>611616</v>
@@ -23714,7 +23714,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G805" t="n">
-        <v>3.10159111022949</v>
+        <v>3.10159134864807</v>
       </c>
       <c r="H805" t="n">
         <v>465659</v>
@@ -23743,7 +23743,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G806" t="n">
-        <v>3.16758251190186</v>
+        <v>3.16758322715759</v>
       </c>
       <c r="H806" t="n">
         <v>651462</v>
@@ -23772,7 +23772,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G807" t="n">
-        <v>3.1807804107666</v>
+        <v>3.18078064918518</v>
       </c>
       <c r="H807" t="n">
         <v>428355</v>
@@ -23859,7 +23859,7 @@
         <v>4.7649998664856</v>
       </c>
       <c r="G810" t="n">
-        <v>3.14448571205139</v>
+        <v>3.14448523521423</v>
       </c>
       <c r="H810" t="n">
         <v>226133</v>
@@ -23888,7 +23888,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G811" t="n">
-        <v>3.21377658843994</v>
+        <v>3.21377635002136</v>
       </c>
       <c r="H811" t="n">
         <v>468615</v>
@@ -23917,7 +23917,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G812" t="n">
-        <v>3.14118623733521</v>
+        <v>3.14118599891663</v>
       </c>
       <c r="H812" t="n">
         <v>381021</v>
@@ -23946,7 +23946,7 @@
         <v>4.7649998664856</v>
       </c>
       <c r="G813" t="n">
-        <v>3.14448571205139</v>
+        <v>3.14448523521423</v>
       </c>
       <c r="H813" t="n">
         <v>264508</v>
@@ -24004,7 +24004,7 @@
         <v>4.99499988555908</v>
       </c>
       <c r="G815" t="n">
-        <v>3.29626560211182</v>
+        <v>3.29626536369324</v>
       </c>
       <c r="H815" t="n">
         <v>513516</v>
@@ -24033,7 +24033,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G816" t="n">
-        <v>3.33916020393372</v>
+        <v>3.33916044235229</v>
       </c>
       <c r="H816" t="n">
         <v>453513</v>
@@ -24062,7 +24062,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G817" t="n">
-        <v>3.33916020393372</v>
+        <v>3.33916044235229</v>
       </c>
       <c r="H817" t="n">
         <v>318896</v>
@@ -24091,7 +24091,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G818" t="n">
-        <v>3.41175079345703</v>
+        <v>3.41175055503845</v>
       </c>
       <c r="H818" t="n">
         <v>401571</v>
@@ -24120,7 +24120,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G819" t="n">
-        <v>3.42494893074036</v>
+        <v>3.42494869232178</v>
       </c>
       <c r="H819" t="n">
         <v>249494</v>
@@ -24149,7 +24149,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G820" t="n">
-        <v>3.39855265617371</v>
+        <v>3.39855217933655</v>
       </c>
       <c r="H820" t="n">
         <v>289895</v>
@@ -24178,7 +24178,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G821" t="n">
-        <v>3.36555671691895</v>
+        <v>3.36555624008179</v>
       </c>
       <c r="H821" t="n">
         <v>199410</v>
@@ -24207,7 +24207,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G822" t="n">
-        <v>3.38535380363464</v>
+        <v>3.38535404205322</v>
       </c>
       <c r="H822" t="n">
         <v>204538</v>
@@ -24236,7 +24236,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G823" t="n">
-        <v>3.39195322990417</v>
+        <v>3.3919529914856</v>
       </c>
       <c r="H823" t="n">
         <v>276929</v>
@@ -24265,7 +24265,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G824" t="n">
-        <v>3.39855265617371</v>
+        <v>3.39855217933655</v>
       </c>
       <c r="H824" t="n">
         <v>274315</v>
@@ -24294,7 +24294,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G825" t="n">
-        <v>3.31936287879944</v>
+        <v>3.31936264038086</v>
       </c>
       <c r="H825" t="n">
         <v>473756</v>
@@ -24352,7 +24352,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G827" t="n">
-        <v>3.27976751327515</v>
+        <v>3.27976775169373</v>
       </c>
       <c r="H827" t="n">
         <v>264280</v>
@@ -24381,7 +24381,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G828" t="n">
-        <v>3.32596135139465</v>
+        <v>3.32596182823181</v>
       </c>
       <c r="H828" t="n">
         <v>384641</v>
@@ -24410,7 +24410,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G829" t="n">
-        <v>3.30616450309753</v>
+        <v>3.30616474151611</v>
       </c>
       <c r="H829" t="n">
         <v>225351</v>
@@ -24439,7 +24439,7 @@
         <v>4.99499988555908</v>
       </c>
       <c r="G830" t="n">
-        <v>3.29626560211182</v>
+        <v>3.29626536369324</v>
       </c>
       <c r="H830" t="n">
         <v>222276</v>
@@ -24497,7 +24497,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G832" t="n">
-        <v>3.33916020393372</v>
+        <v>3.33916044235229</v>
       </c>
       <c r="H832" t="n">
         <v>393150</v>
@@ -24555,7 +24555,7 @@
         <v>4.91499996185303</v>
       </c>
       <c r="G834" t="n">
-        <v>3.24347281455994</v>
+        <v>3.24347257614136</v>
       </c>
       <c r="H834" t="n">
         <v>218245</v>
@@ -24584,7 +24584,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G835" t="n">
-        <v>3.22697448730469</v>
+        <v>3.22697472572327</v>
       </c>
       <c r="H835" t="n">
         <v>219258</v>
@@ -24613,7 +24613,7 @@
         <v>4.88500022888184</v>
       </c>
       <c r="G836" t="n">
-        <v>3.22367525100708</v>
+        <v>3.22367548942566</v>
       </c>
       <c r="H836" t="n">
         <v>288743</v>
@@ -24671,7 +24671,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G838" t="n">
-        <v>3.1807804107666</v>
+        <v>3.18078064918518</v>
       </c>
       <c r="H838" t="n">
         <v>1642514</v>
@@ -24700,7 +24700,7 @@
         <v>4.81500005722046</v>
       </c>
       <c r="G839" t="n">
-        <v>3.17748141288757</v>
+        <v>3.17748117446899</v>
       </c>
       <c r="H839" t="n">
         <v>213007</v>
@@ -24729,7 +24729,7 @@
         <v>4.80499982833862</v>
       </c>
       <c r="G840" t="n">
-        <v>3.17088222503662</v>
+        <v>3.17088198661804</v>
       </c>
       <c r="H840" t="n">
         <v>190395</v>
@@ -24816,7 +24816,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G843" t="n">
-        <v>3.16758251190186</v>
+        <v>3.16758322715759</v>
       </c>
       <c r="H843" t="n">
         <v>356628</v>
@@ -24874,7 +24874,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G845" t="n">
-        <v>3.16758251190186</v>
+        <v>3.16758322715759</v>
       </c>
       <c r="H845" t="n">
         <v>298505</v>
@@ -24903,7 +24903,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G846" t="n">
-        <v>3.14778542518616</v>
+        <v>3.14778518676758</v>
       </c>
       <c r="H846" t="n">
         <v>388358</v>
@@ -24932,7 +24932,7 @@
         <v>4.75500011444092</v>
       </c>
       <c r="G847" t="n">
-        <v>3.13788676261902</v>
+        <v>3.13788652420044</v>
       </c>
       <c r="H847" t="n">
         <v>208092</v>
@@ -24961,7 +24961,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G848" t="n">
-        <v>3.14778542518616</v>
+        <v>3.14778518676758</v>
       </c>
       <c r="H848" t="n">
         <v>542694</v>
@@ -25019,7 +25019,7 @@
         <v>4.68499994277954</v>
       </c>
       <c r="G850" t="n">
-        <v>3.09169268608093</v>
+        <v>3.09169244766235</v>
       </c>
       <c r="H850" t="n">
         <v>341704</v>
@@ -25048,7 +25048,7 @@
         <v>4.61499977111816</v>
       </c>
       <c r="G851" t="n">
-        <v>3.04549860954285</v>
+        <v>3.04549837112427</v>
       </c>
       <c r="H851" t="n">
         <v>522574</v>
@@ -25077,7 +25077,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G852" t="n">
-        <v>3.06859564781189</v>
+        <v>3.06859540939331</v>
       </c>
       <c r="H852" t="n">
         <v>323856</v>
@@ -25135,7 +25135,7 @@
         <v>4.64499998092651</v>
       </c>
       <c r="G854" t="n">
-        <v>3.0652961730957</v>
+        <v>3.06529641151428</v>
       </c>
       <c r="H854" t="n">
         <v>235160</v>
@@ -25164,7 +25164,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G855" t="n">
-        <v>3.06199598312378</v>
+        <v>3.0619969367981</v>
       </c>
       <c r="H855" t="n">
         <v>280411</v>
@@ -25193,7 +25193,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G856" t="n">
-        <v>3.05539727210999</v>
+        <v>3.05539751052856</v>
       </c>
       <c r="H856" t="n">
         <v>287160</v>
@@ -25222,7 +25222,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G857" t="n">
-        <v>3.05539727210999</v>
+        <v>3.05539751052856</v>
       </c>
       <c r="H857" t="n">
         <v>310238</v>
@@ -25251,7 +25251,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G858" t="n">
-        <v>3.06859564781189</v>
+        <v>3.06859540939331</v>
       </c>
       <c r="H858" t="n">
         <v>269563</v>
@@ -25280,7 +25280,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G859" t="n">
-        <v>3.12798738479614</v>
+        <v>3.12798810005188</v>
       </c>
       <c r="H859" t="n">
         <v>676151</v>
@@ -25338,7 +25338,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G861" t="n">
-        <v>3.03230047225952</v>
+        <v>3.03230023384094</v>
       </c>
       <c r="H861" t="n">
         <v>305675</v>
@@ -25367,7 +25367,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G862" t="n">
-        <v>3.07519483566284</v>
+        <v>3.07519459724426</v>
       </c>
       <c r="H862" t="n">
         <v>323471</v>
@@ -25396,7 +25396,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G863" t="n">
-        <v>3.00590348243713</v>
+        <v>3.00590372085571</v>
       </c>
       <c r="H863" t="n">
         <v>399027</v>
@@ -25570,7 +25570,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G869" t="n">
-        <v>3.05539727210999</v>
+        <v>3.05539751052856</v>
       </c>
       <c r="H869" t="n">
         <v>307248</v>
@@ -25599,7 +25599,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G870" t="n">
-        <v>3.06199598312378</v>
+        <v>3.0619969367981</v>
       </c>
       <c r="H870" t="n">
         <v>228965</v>
@@ -25628,7 +25628,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G871" t="n">
-        <v>3.05539727210999</v>
+        <v>3.05539751052856</v>
       </c>
       <c r="H871" t="n">
         <v>255547</v>
@@ -25657,7 +25657,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G872" t="n">
-        <v>3.06859564781189</v>
+        <v>3.06859540939331</v>
       </c>
       <c r="H872" t="n">
         <v>182329</v>
@@ -25686,7 +25686,7 @@
         <v>4.7649998664856</v>
       </c>
       <c r="G873" t="n">
-        <v>3.14448571205139</v>
+        <v>3.14448523521423</v>
       </c>
       <c r="H873" t="n">
         <v>387190</v>
@@ -25715,7 +25715,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G874" t="n">
-        <v>3.1807804107666</v>
+        <v>3.18078064918518</v>
       </c>
       <c r="H874" t="n">
         <v>1195620</v>
@@ -25744,7 +25744,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G875" t="n">
-        <v>3.14118623733521</v>
+        <v>3.14118599891663</v>
       </c>
       <c r="H875" t="n">
         <v>855482</v>
@@ -25773,7 +25773,7 @@
         <v>4.75500011444092</v>
       </c>
       <c r="G876" t="n">
-        <v>3.13788676261902</v>
+        <v>3.13788652420044</v>
       </c>
       <c r="H876" t="n">
         <v>519622</v>
@@ -25802,7 +25802,7 @@
         <v>4.7649998664856</v>
       </c>
       <c r="G877" t="n">
-        <v>3.14448571205139</v>
+        <v>3.14448523521423</v>
       </c>
       <c r="H877" t="n">
         <v>391893</v>
@@ -25831,7 +25831,7 @@
         <v>4.7649998664856</v>
       </c>
       <c r="G878" t="n">
-        <v>3.14448571205139</v>
+        <v>3.14448523521423</v>
       </c>
       <c r="H878" t="n">
         <v>399152</v>
@@ -25918,7 +25918,7 @@
         <v>4.74499988555908</v>
       </c>
       <c r="G881" t="n">
-        <v>3.13128709793091</v>
+        <v>3.13128757476807</v>
       </c>
       <c r="H881" t="n">
         <v>154996</v>
@@ -25947,7 +25947,7 @@
         <v>4.80499982833862</v>
       </c>
       <c r="G882" t="n">
-        <v>3.17088222503662</v>
+        <v>3.17088198661804</v>
       </c>
       <c r="H882" t="n">
         <v>237202</v>
@@ -26005,7 +26005,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G884" t="n">
-        <v>3.20717763900757</v>
+        <v>3.20717740058899</v>
       </c>
       <c r="H884" t="n">
         <v>338216</v>
@@ -26034,7 +26034,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G885" t="n">
-        <v>3.22697448730469</v>
+        <v>3.22697472572327</v>
       </c>
       <c r="H885" t="n">
         <v>428907</v>
@@ -26063,7 +26063,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G886" t="n">
-        <v>3.33256101608276</v>
+        <v>3.33256149291992</v>
       </c>
       <c r="H886" t="n">
         <v>506092</v>
@@ -26092,7 +26092,7 @@
         <v>4.93499994277954</v>
       </c>
       <c r="G887" t="n">
-        <v>3.25667119026184</v>
+        <v>3.25667095184326</v>
       </c>
       <c r="H887" t="n">
         <v>648324</v>
@@ -26150,7 +26150,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G889" t="n">
-        <v>3.17418122291565</v>
+        <v>3.17418146133423</v>
       </c>
       <c r="H889" t="n">
         <v>237516</v>
@@ -26179,7 +26179,7 @@
         <v>4.81500005722046</v>
       </c>
       <c r="G890" t="n">
-        <v>3.17748141288757</v>
+        <v>3.17748117446899</v>
       </c>
       <c r="H890" t="n">
         <v>161863</v>
@@ -26208,7 +26208,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G891" t="n">
-        <v>3.08839297294617</v>
+        <v>3.08839273452759</v>
       </c>
       <c r="H891" t="n">
         <v>265471</v>
@@ -26266,7 +26266,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G893" t="n">
-        <v>2.94321203231812</v>
+        <v>2.94321227073669</v>
       </c>
       <c r="H893" t="n">
         <v>532914</v>
@@ -26295,7 +26295,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G894" t="n">
-        <v>2.94321203231812</v>
+        <v>2.94321227073669</v>
       </c>
       <c r="H894" t="n">
         <v>431208</v>
@@ -26324,7 +26324,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G895" t="n">
-        <v>2.91681551933289</v>
+        <v>2.91681575775146</v>
       </c>
       <c r="H895" t="n">
         <v>162337</v>
@@ -26469,7 +26469,7 @@
         <v>4.16499996185303</v>
       </c>
       <c r="G900" t="n">
-        <v>2.74853754043579</v>
+        <v>2.74853801727295</v>
       </c>
       <c r="H900" t="n">
         <v>321962</v>
@@ -26498,7 +26498,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G901" t="n">
-        <v>2.75843644142151</v>
+        <v>2.75843620300293</v>
       </c>
       <c r="H901" t="n">
         <v>275017</v>
@@ -26556,7 +26556,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G903" t="n">
-        <v>2.61985468864441</v>
+        <v>2.61985492706299</v>
       </c>
       <c r="H903" t="n">
         <v>608301</v>
@@ -26585,7 +26585,7 @@
         <v>3.95499992370605</v>
       </c>
       <c r="G904" t="n">
-        <v>2.60995578765869</v>
+        <v>2.60995626449585</v>
       </c>
       <c r="H904" t="n">
         <v>489725</v>
@@ -26643,7 +26643,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G906" t="n">
-        <v>2.57366108894348</v>
+        <v>2.5736608505249</v>
       </c>
       <c r="H906" t="n">
         <v>687548</v>
@@ -26672,7 +26672,7 @@
         <v>4.02500009536743</v>
       </c>
       <c r="G907" t="n">
-        <v>2.65614986419678</v>
+        <v>2.65615010261536</v>
       </c>
       <c r="H907" t="n">
         <v>832606</v>
@@ -26817,7 +26817,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G912" t="n">
-        <v>3.00260424613953</v>
+        <v>3.00260448455811</v>
       </c>
       <c r="H912" t="n">
         <v>731447</v>
@@ -26904,7 +26904,7 @@
         <v>4.5</v>
       </c>
       <c r="G915" t="n">
-        <v>2.9696090221405</v>
+        <v>2.96960854530334</v>
       </c>
       <c r="H915" t="n">
         <v>732358</v>
@@ -26933,7 +26933,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G916" t="n">
-        <v>3.00590348243713</v>
+        <v>3.00590372085571</v>
       </c>
       <c r="H916" t="n">
         <v>523382</v>
@@ -26962,7 +26962,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G917" t="n">
-        <v>3.05539727210999</v>
+        <v>3.05539751052856</v>
       </c>
       <c r="H917" t="n">
         <v>697949</v>
@@ -26991,7 +26991,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G918" t="n">
-        <v>3.00260424613953</v>
+        <v>3.00260448455811</v>
       </c>
       <c r="H918" t="n">
         <v>403577</v>
@@ -27020,7 +27020,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G919" t="n">
-        <v>3.03230047225952</v>
+        <v>3.03230023384094</v>
       </c>
       <c r="H919" t="n">
         <v>328304</v>
@@ -27049,7 +27049,7 @@
         <v>4.64499998092651</v>
       </c>
       <c r="G920" t="n">
-        <v>3.0652961730957</v>
+        <v>3.06529641151428</v>
       </c>
       <c r="H920" t="n">
         <v>305216</v>
@@ -27078,7 +27078,7 @@
         <v>4.61499977111816</v>
       </c>
       <c r="G921" t="n">
-        <v>3.04549860954285</v>
+        <v>3.04549837112427</v>
       </c>
       <c r="H921" t="n">
         <v>474140</v>
@@ -27107,7 +27107,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G922" t="n">
-        <v>3.14778542518616</v>
+        <v>3.14778518676758</v>
       </c>
       <c r="H922" t="n">
         <v>776068</v>
@@ -27136,7 +27136,7 @@
         <v>4.7649998664856</v>
       </c>
       <c r="G923" t="n">
-        <v>3.14448571205139</v>
+        <v>3.14448523521423</v>
       </c>
       <c r="H923" t="n">
         <v>433661</v>
@@ -27165,7 +27165,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G924" t="n">
-        <v>3.12138867378235</v>
+        <v>3.12138891220093</v>
       </c>
       <c r="H924" t="n">
         <v>241795</v>
@@ -27223,7 +27223,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G926" t="n">
-        <v>2.97620844841003</v>
+        <v>2.97620797157288</v>
       </c>
       <c r="H926" t="n">
         <v>885053</v>
@@ -27281,7 +27281,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G928" t="n">
-        <v>2.97290825843811</v>
+        <v>2.97290802001953</v>
       </c>
       <c r="H928" t="n">
         <v>263796</v>
@@ -27310,7 +27310,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G929" t="n">
-        <v>3.00590348243713</v>
+        <v>3.00590372085571</v>
       </c>
       <c r="H929" t="n">
         <v>317790</v>
@@ -27368,7 +27368,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G931" t="n">
-        <v>3.00920343399048</v>
+        <v>3.0092031955719</v>
       </c>
       <c r="H931" t="n">
         <v>282480</v>
@@ -27455,7 +27455,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G934" t="n">
-        <v>2.97620844841003</v>
+        <v>2.97620797157288</v>
       </c>
       <c r="H934" t="n">
         <v>365832</v>
@@ -27484,7 +27484,7 @@
         <v>4.64499998092651</v>
       </c>
       <c r="G935" t="n">
-        <v>3.0652961730957</v>
+        <v>3.06529641151428</v>
       </c>
       <c r="H935" t="n">
         <v>427415</v>
@@ -27513,7 +27513,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G936" t="n">
-        <v>2.93001365661621</v>
+        <v>2.93001437187195</v>
       </c>
       <c r="H936" t="n">
         <v>999582</v>
@@ -27542,7 +27542,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G937" t="n">
-        <v>3.00590348243713</v>
+        <v>3.00590372085571</v>
       </c>
       <c r="H937" t="n">
         <v>1076257</v>
@@ -27571,7 +27571,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G938" t="n">
-        <v>3.06199598312378</v>
+        <v>3.0619969367981</v>
       </c>
       <c r="H938" t="n">
         <v>428241</v>
@@ -27629,7 +27629,7 @@
         <v>4.5</v>
       </c>
       <c r="G940" t="n">
-        <v>2.9696090221405</v>
+        <v>2.96960854530334</v>
       </c>
       <c r="H940" t="n">
         <v>412958</v>
@@ -27716,7 +27716,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G943" t="n">
-        <v>3.10819053649902</v>
+        <v>3.10819029808044</v>
       </c>
       <c r="H943" t="n">
         <v>359459</v>
@@ -27745,7 +27745,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G944" t="n">
-        <v>3.20057797431946</v>
+        <v>3.20057821273804</v>
       </c>
       <c r="H944" t="n">
         <v>931314</v>
@@ -27832,7 +27832,7 @@
         <v>4.68499994277954</v>
       </c>
       <c r="G947" t="n">
-        <v>3.09169268608093</v>
+        <v>3.09169244766235</v>
       </c>
       <c r="H947" t="n">
         <v>349670</v>
@@ -27861,7 +27861,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G948" t="n">
-        <v>3.14118623733521</v>
+        <v>3.14118599891663</v>
       </c>
       <c r="H948" t="n">
         <v>365815</v>
@@ -27890,7 +27890,7 @@
         <v>4.7350001335144</v>
       </c>
       <c r="G949" t="n">
-        <v>3.12468862533569</v>
+        <v>3.12468838691711</v>
       </c>
       <c r="H949" t="n">
         <v>383014</v>
@@ -27948,7 +27948,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G951" t="n">
-        <v>3.20387768745422</v>
+        <v>3.20387816429138</v>
       </c>
       <c r="H951" t="n">
         <v>693773</v>
@@ -27977,7 +27977,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G952" t="n">
-        <v>3.08839297294617</v>
+        <v>3.08839273452759</v>
       </c>
       <c r="H952" t="n">
         <v>747349</v>
@@ -28035,7 +28035,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G954" t="n">
-        <v>3.11808919906616</v>
+        <v>3.11808896064758</v>
       </c>
       <c r="H954" t="n">
         <v>352110</v>
@@ -28093,7 +28093,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G956" t="n">
-        <v>3.08839297294617</v>
+        <v>3.08839273452759</v>
       </c>
       <c r="H956" t="n">
         <v>211957</v>
@@ -28122,7 +28122,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G957" t="n">
-        <v>3.08839297294617</v>
+        <v>3.08839273452759</v>
       </c>
       <c r="H957" t="n">
         <v>217582</v>
@@ -28180,7 +28180,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G959" t="n">
-        <v>3.06859564781189</v>
+        <v>3.06859540939331</v>
       </c>
       <c r="H959" t="n">
         <v>215020</v>
@@ -28209,7 +28209,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G960" t="n">
-        <v>3.00260424613953</v>
+        <v>3.00260448455811</v>
       </c>
       <c r="H960" t="n">
         <v>980745</v>
@@ -28267,7 +28267,7 @@
         <v>4.60500001907349</v>
       </c>
       <c r="G962" t="n">
-        <v>3.03889966011047</v>
+        <v>3.03889942169189</v>
       </c>
       <c r="H962" t="n">
         <v>455979</v>
@@ -28354,7 +28354,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G965" t="n">
-        <v>2.99930477142334</v>
+        <v>2.9993052482605</v>
       </c>
       <c r="H965" t="n">
         <v>244958</v>
@@ -28441,7 +28441,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G968" t="n">
-        <v>3.11478972434998</v>
+        <v>3.11478924751282</v>
       </c>
       <c r="H968" t="n">
         <v>633821</v>
@@ -28470,7 +28470,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G969" t="n">
-        <v>3.20057797431946</v>
+        <v>3.20057821273804</v>
       </c>
       <c r="H969" t="n">
         <v>732691</v>
@@ -28499,7 +28499,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G970" t="n">
-        <v>3.23027420043945</v>
+        <v>3.23027467727661</v>
       </c>
       <c r="H970" t="n">
         <v>547564</v>
@@ -28586,7 +28586,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G973" t="n">
-        <v>3.43154764175415</v>
+        <v>3.43154788017273</v>
       </c>
       <c r="H973" t="n">
         <v>1763486</v>
@@ -28615,7 +28615,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G974" t="n">
-        <v>3.69551253318787</v>
+        <v>3.6955132484436</v>
       </c>
       <c r="H974" t="n">
         <v>4422675</v>
@@ -28644,7 +28644,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G975" t="n">
-        <v>3.74830627441406</v>
+        <v>3.74830555915833</v>
       </c>
       <c r="H975" t="n">
         <v>2499166</v>
@@ -28673,7 +28673,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G976" t="n">
-        <v>3.76150465011597</v>
+        <v>3.76150393486023</v>
       </c>
       <c r="H976" t="n">
         <v>982089</v>
@@ -28702,7 +28702,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G977" t="n">
-        <v>3.71531009674072</v>
+        <v>3.71531105041504</v>
       </c>
       <c r="H977" t="n">
         <v>728136</v>
@@ -28760,7 +28760,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G979" t="n">
-        <v>3.7021119594574</v>
+        <v>3.70211243629456</v>
       </c>
       <c r="H979" t="n">
         <v>913001</v>
@@ -28789,7 +28789,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G980" t="n">
-        <v>3.66251754760742</v>
+        <v>3.66251730918884</v>
       </c>
       <c r="H980" t="n">
         <v>720088</v>
@@ -28818,7 +28818,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G981" t="n">
-        <v>3.64271950721741</v>
+        <v>3.64271998405457</v>
       </c>
       <c r="H981" t="n">
         <v>485656</v>
@@ -28847,7 +28847,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G982" t="n">
-        <v>3.5965256690979</v>
+        <v>3.59652614593506</v>
       </c>
       <c r="H982" t="n">
         <v>349406</v>
@@ -28934,7 +28934,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G985" t="n">
-        <v>3.58992695808411</v>
+        <v>3.58992719650269</v>
       </c>
       <c r="H985" t="n">
         <v>863819</v>
@@ -28963,7 +28963,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G986" t="n">
-        <v>3.68231511116028</v>
+        <v>3.68231439590454</v>
       </c>
       <c r="H986" t="n">
         <v>494261</v>
@@ -28992,7 +28992,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G987" t="n">
-        <v>3.66911649703979</v>
+        <v>3.66911625862122</v>
       </c>
       <c r="H987" t="n">
         <v>285276</v>
@@ -29021,7 +29021,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G988" t="n">
-        <v>3.66911649703979</v>
+        <v>3.66911625862122</v>
       </c>
       <c r="H988" t="n">
         <v>407898</v>
@@ -29050,7 +29050,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G989" t="n">
-        <v>3.64271950721741</v>
+        <v>3.64271998405457</v>
       </c>
       <c r="H989" t="n">
         <v>307155</v>
@@ -29079,7 +29079,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G990" t="n">
-        <v>3.66911649703979</v>
+        <v>3.66911625862122</v>
       </c>
       <c r="H990" t="n">
         <v>585702</v>
@@ -29108,7 +29108,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G991" t="n">
-        <v>3.66251754760742</v>
+        <v>3.66251730918884</v>
       </c>
       <c r="H991" t="n">
         <v>260821</v>
@@ -29166,7 +29166,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G993" t="n">
-        <v>4.09146022796631</v>
+        <v>4.09146070480347</v>
       </c>
       <c r="H993" t="n">
         <v>2120881</v>
@@ -29224,7 +29224,7 @@
         <v>6.30999994277954</v>
       </c>
       <c r="G995" t="n">
-        <v>4.1640510559082</v>
+        <v>4.16405153274536</v>
       </c>
       <c r="H995" t="n">
         <v>875121</v>
@@ -29340,7 +29340,7 @@
         <v>6.40999984741211</v>
       </c>
       <c r="G999" t="n">
-        <v>4.23004198074341</v>
+        <v>4.23004245758057</v>
       </c>
       <c r="H999" t="n">
         <v>326842</v>
@@ -29485,7 +29485,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G1004" t="n">
-        <v>4.27623701095581</v>
+        <v>4.27623605728149</v>
       </c>
       <c r="H1004" t="n">
         <v>357589</v>
@@ -29514,7 +29514,7 @@
         <v>6.5</v>
       </c>
       <c r="G1005" t="n">
-        <v>4.2894344329834</v>
+        <v>4.28943490982056</v>
       </c>
       <c r="H1005" t="n">
         <v>388051</v>
@@ -29630,7 +29630,7 @@
         <v>6.28499984741211</v>
       </c>
       <c r="G1009" t="n">
-        <v>4.15874671936035</v>
+        <v>4.15874719619751</v>
       </c>
       <c r="H1009" t="n">
         <v>379429</v>
@@ -29688,7 +29688,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G1011" t="n">
-        <v>4.40026521682739</v>
+        <v>4.40026569366455</v>
       </c>
       <c r="H1011" t="n">
         <v>900186</v>
@@ -29717,7 +29717,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G1012" t="n">
-        <v>4.31424522399902</v>
+        <v>4.31424474716187</v>
       </c>
       <c r="H1012" t="n">
         <v>833502</v>
@@ -29746,7 +29746,7 @@
         <v>6.55499982833862</v>
       </c>
       <c r="G1013" t="n">
-        <v>4.33740425109863</v>
+        <v>4.33740472793579</v>
       </c>
       <c r="H1013" t="n">
         <v>353997</v>
@@ -29804,7 +29804,7 @@
         <v>6.77500009536743</v>
       </c>
       <c r="G1015" t="n">
-        <v>4.48297739028931</v>
+        <v>4.48297691345215</v>
       </c>
       <c r="H1015" t="n">
         <v>765547</v>
@@ -29920,7 +29920,7 @@
         <v>6.83500003814697</v>
       </c>
       <c r="G1019" t="n">
-        <v>4.52267837524414</v>
+        <v>4.5226788520813</v>
       </c>
       <c r="H1019" t="n">
         <v>531492</v>
@@ -29949,7 +29949,7 @@
         <v>6.75</v>
       </c>
       <c r="G1020" t="n">
-        <v>4.46643447875977</v>
+        <v>4.46643495559692</v>
       </c>
       <c r="H1020" t="n">
         <v>587439</v>
@@ -30007,7 +30007,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G1022" t="n">
-        <v>4.68479347229004</v>
+        <v>4.68479442596436</v>
       </c>
       <c r="H1022" t="n">
         <v>926752</v>
@@ -30065,7 +30065,7 @@
         <v>7.39499998092651</v>
       </c>
       <c r="G1024" t="n">
-        <v>4.89322805404663</v>
+        <v>4.89322757720947</v>
       </c>
       <c r="H1024" t="n">
         <v>1260401</v>
@@ -30094,7 +30094,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G1025" t="n">
-        <v>4.88991832733154</v>
+        <v>4.8899188041687</v>
       </c>
       <c r="H1025" t="n">
         <v>2231676</v>
@@ -30123,7 +30123,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G1026" t="n">
-        <v>4.86345052719116</v>
+        <v>4.86345148086548</v>
       </c>
       <c r="H1026" t="n">
         <v>1249943</v>
@@ -30152,7 +30152,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G1027" t="n">
-        <v>4.85683488845825</v>
+        <v>4.85683441162109</v>
       </c>
       <c r="H1027" t="n">
         <v>1039594</v>
@@ -30181,7 +30181,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G1028" t="n">
-        <v>4.92962074279785</v>
+        <v>4.92962026596069</v>
       </c>
       <c r="H1028" t="n">
         <v>950804</v>
@@ -30210,7 +30210,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G1029" t="n">
-        <v>4.92962074279785</v>
+        <v>4.92962026596069</v>
       </c>
       <c r="H1029" t="n">
         <v>522366</v>
@@ -30413,7 +30413,7 @@
         <v>7.30999994277954</v>
       </c>
       <c r="G1036" t="n">
-        <v>4.8369836807251</v>
+        <v>4.83698272705078</v>
       </c>
       <c r="H1036" t="n">
         <v>1386184</v>
@@ -30471,7 +30471,7 @@
         <v>7.6100001335144</v>
       </c>
       <c r="G1038" t="n">
-        <v>5.03549194335938</v>
+        <v>5.03549146652222</v>
       </c>
       <c r="H1038" t="n">
         <v>940339</v>
@@ -30500,7 +30500,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G1039" t="n">
-        <v>5.05534267425537</v>
+        <v>5.05534219741821</v>
       </c>
       <c r="H1039" t="n">
         <v>666470</v>
@@ -30558,7 +30558,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G1041" t="n">
-        <v>5.06195974349976</v>
+        <v>5.0619592666626</v>
       </c>
       <c r="H1041" t="n">
         <v>411523</v>
@@ -30587,7 +30587,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G1042" t="n">
-        <v>5.10827827453613</v>
+        <v>5.10827779769897</v>
       </c>
       <c r="H1042" t="n">
         <v>660095</v>
@@ -30616,7 +30616,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1043" t="n">
-        <v>5.06857633590698</v>
+        <v>5.06857585906982</v>
       </c>
       <c r="H1043" t="n">
         <v>779852</v>
@@ -30645,7 +30645,7 @@
         <v>7.71500015258789</v>
       </c>
       <c r="G1044" t="n">
-        <v>5.10496997833252</v>
+        <v>5.1049690246582</v>
       </c>
       <c r="H1044" t="n">
         <v>471610</v>
@@ -30674,7 +30674,7 @@
         <v>7.625</v>
       </c>
       <c r="G1045" t="n">
-        <v>5.04541730880737</v>
+        <v>5.04541683197021</v>
       </c>
       <c r="H1045" t="n">
         <v>833832</v>
@@ -30703,7 +30703,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G1046" t="n">
-        <v>5.05534267425537</v>
+        <v>5.05534219741821</v>
       </c>
       <c r="H1046" t="n">
         <v>475182</v>
@@ -30732,7 +30732,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G1047" t="n">
-        <v>5.06195974349976</v>
+        <v>5.0619592666626</v>
       </c>
       <c r="H1047" t="n">
         <v>944084</v>
@@ -30790,7 +30790,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G1049" t="n">
-        <v>5.08842706680298</v>
+        <v>5.08842754364014</v>
       </c>
       <c r="H1049" t="n">
         <v>484828</v>
@@ -30848,7 +30848,7 @@
         <v>8</v>
       </c>
       <c r="G1051" t="n">
-        <v>5.29355192184448</v>
+        <v>5.29355239868164</v>
       </c>
       <c r="H1051" t="n">
         <v>384872</v>
@@ -30877,7 +30877,7 @@
         <v>7.93499994277954</v>
       </c>
       <c r="G1052" t="n">
-        <v>5.25054216384888</v>
+        <v>5.25054168701172</v>
       </c>
       <c r="H1052" t="n">
         <v>575834</v>
@@ -30993,7 +30993,7 @@
         <v>8.09000015258789</v>
       </c>
       <c r="G1056" t="n">
-        <v>5.35310554504395</v>
+        <v>5.35310506820679</v>
       </c>
       <c r="H1056" t="n">
         <v>1659648</v>
@@ -31022,7 +31022,7 @@
         <v>8.13000011444092</v>
       </c>
       <c r="G1057" t="n">
-        <v>5.37957239151001</v>
+        <v>5.37957191467285</v>
       </c>
       <c r="H1057" t="n">
         <v>987878</v>
@@ -31138,7 +31138,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G1061" t="n">
-        <v>5.51852798461914</v>
+        <v>5.5185284614563</v>
       </c>
       <c r="H1061" t="n">
         <v>613919</v>
@@ -31225,7 +31225,7 @@
         <v>8.46500015258789</v>
       </c>
       <c r="G1064" t="n">
-        <v>5.6012396812439</v>
+        <v>5.60124015808105</v>
       </c>
       <c r="H1064" t="n">
         <v>676239</v>
@@ -31341,7 +31341,7 @@
         <v>8.45499992370605</v>
       </c>
       <c r="G1068" t="n">
-        <v>5.59462261199951</v>
+        <v>5.59462308883667</v>
       </c>
       <c r="H1068" t="n">
         <v>250918</v>
@@ -31573,7 +31573,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G1076" t="n">
-        <v>5.52514553070068</v>
+        <v>5.52514505386353</v>
       </c>
       <c r="H1076" t="n">
         <v>527736</v>
@@ -31602,7 +31602,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1077" t="n">
-        <v>5.50529384613037</v>
+        <v>5.50529432296753</v>
       </c>
       <c r="H1077" t="n">
         <v>619248</v>
@@ -31631,7 +31631,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G1078" t="n">
-        <v>5.65086698532104</v>
+        <v>5.6508674621582</v>
       </c>
       <c r="H1078" t="n">
         <v>262421</v>
@@ -31718,7 +31718,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1081" t="n">
-        <v>5.65748405456543</v>
+        <v>5.65748453140259</v>
       </c>
       <c r="H1081" t="n">
         <v>299157</v>
@@ -31776,7 +31776,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1083" t="n">
-        <v>5.42589044570923</v>
+        <v>5.42589092254639</v>
       </c>
       <c r="H1083" t="n">
         <v>416896</v>
@@ -31892,7 +31892,7 @@
         <v>8.49499988555908</v>
       </c>
       <c r="G1087" t="n">
-        <v>5.62109041213989</v>
+        <v>5.62109136581421</v>
       </c>
       <c r="H1087" t="n">
         <v>830197</v>
@@ -31950,7 +31950,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G1089" t="n">
-        <v>5.81629085540771</v>
+        <v>5.8162899017334</v>
       </c>
       <c r="H1089" t="n">
         <v>541031</v>
@@ -31979,7 +31979,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1090" t="n">
-        <v>5.8229079246521</v>
+        <v>5.82290744781494</v>
       </c>
       <c r="H1090" t="n">
         <v>557330</v>
@@ -32008,7 +32008,7 @@
         <v>8.875</v>
       </c>
       <c r="G1091" t="n">
-        <v>5.87253475189209</v>
+        <v>5.87253427505493</v>
       </c>
       <c r="H1091" t="n">
         <v>247077</v>
@@ -32037,7 +32037,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1092" t="n">
-        <v>5.88907718658447</v>
+        <v>5.88907623291016</v>
       </c>
       <c r="H1092" t="n">
         <v>242107</v>
@@ -32095,7 +32095,7 @@
         <v>8.86999988555908</v>
       </c>
       <c r="G1094" t="n">
-        <v>5.86922597885132</v>
+        <v>5.86922645568848</v>
       </c>
       <c r="H1094" t="n">
         <v>310467</v>
@@ -32153,7 +32153,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G1096" t="n">
-        <v>5.83614158630371</v>
+        <v>5.83614110946655</v>
       </c>
       <c r="H1096" t="n">
         <v>326978</v>
@@ -32182,7 +32182,7 @@
         <v>8.86999988555908</v>
       </c>
       <c r="G1097" t="n">
-        <v>5.86922597885132</v>
+        <v>5.86922645568848</v>
       </c>
       <c r="H1097" t="n">
         <v>404572</v>
@@ -32211,7 +32211,7 @@
         <v>8.05500030517578</v>
       </c>
       <c r="G1098" t="n">
-        <v>5.32994556427002</v>
+        <v>5.32994604110718</v>
       </c>
       <c r="H1098" t="n">
         <v>2049380</v>
@@ -32414,7 +32414,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G1105" t="n">
-        <v>5.06195974349976</v>
+        <v>5.0619592666626</v>
       </c>
       <c r="H1105" t="n">
         <v>261213</v>
@@ -32443,7 +32443,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G1106" t="n">
-        <v>5.05534267425537</v>
+        <v>5.05534219741821</v>
       </c>
       <c r="H1106" t="n">
         <v>303462</v>
@@ -32472,7 +32472,7 @@
         <v>7.71500015258789</v>
       </c>
       <c r="G1107" t="n">
-        <v>5.10496997833252</v>
+        <v>5.1049690246582</v>
       </c>
       <c r="H1107" t="n">
         <v>374750</v>
@@ -32530,7 +32530,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G1109" t="n">
-        <v>5.23399925231934</v>
+        <v>5.23400020599365</v>
       </c>
       <c r="H1109" t="n">
         <v>436719</v>
@@ -32588,7 +32588,7 @@
         <v>8</v>
       </c>
       <c r="G1111" t="n">
-        <v>5.29355192184448</v>
+        <v>5.29355239868164</v>
       </c>
       <c r="H1111" t="n">
         <v>398454</v>
@@ -32617,7 +32617,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1112" t="n">
-        <v>5.22738265991211</v>
+        <v>5.22738313674927</v>
       </c>
       <c r="H1112" t="n">
         <v>405945</v>
@@ -32820,7 +32820,7 @@
         <v>8.01500034332275</v>
       </c>
       <c r="G1119" t="n">
-        <v>5.30347776412964</v>
+        <v>5.3034782409668</v>
       </c>
       <c r="H1119" t="n">
         <v>896226</v>
@@ -32849,7 +32849,7 @@
         <v>7.91499996185303</v>
       </c>
       <c r="G1120" t="n">
-        <v>5.23730802536011</v>
+        <v>5.23730850219727</v>
       </c>
       <c r="H1120" t="n">
         <v>484197</v>
@@ -32878,7 +32878,7 @@
         <v>8</v>
       </c>
       <c r="G1121" t="n">
-        <v>5.29355192184448</v>
+        <v>5.29355239868164</v>
       </c>
       <c r="H1121" t="n">
         <v>677107</v>
@@ -32907,7 +32907,7 @@
         <v>8.05500030517578</v>
       </c>
       <c r="G1122" t="n">
-        <v>5.32994556427002</v>
+        <v>5.32994604110718</v>
       </c>
       <c r="H1122" t="n">
         <v>766397</v>
@@ -32936,7 +32936,7 @@
         <v>8.27499961853027</v>
       </c>
       <c r="G1123" t="n">
-        <v>5.47551822662354</v>
+        <v>5.47551774978638</v>
       </c>
       <c r="H1123" t="n">
         <v>882854</v>
@@ -33023,7 +33023,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G1126" t="n">
-        <v>5.32001972198486</v>
+        <v>5.32002019882202</v>
       </c>
       <c r="H1126" t="n">
         <v>353846</v>
@@ -33052,7 +33052,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G1127" t="n">
-        <v>5.34648752212524</v>
+        <v>5.3464879989624</v>
       </c>
       <c r="H1127" t="n">
         <v>474334</v>
@@ -33081,7 +33081,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G1128" t="n">
-        <v>5.34648752212524</v>
+        <v>5.3464879989624</v>
       </c>
       <c r="H1128" t="n">
         <v>753182</v>
@@ -33168,7 +33168,7 @@
         <v>8.15499973297119</v>
       </c>
       <c r="G1131" t="n">
-        <v>5.39611482620239</v>
+        <v>5.39611434936523</v>
       </c>
       <c r="H1131" t="n">
         <v>427051</v>
@@ -33255,7 +33255,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1134" t="n">
-        <v>5.49206066131592</v>
+        <v>5.49206018447876</v>
       </c>
       <c r="H1134" t="n">
         <v>478244</v>
@@ -33284,7 +33284,7 @@
         <v>8.04500007629395</v>
       </c>
       <c r="G1135" t="n">
-        <v>5.32332801818848</v>
+        <v>5.32332849502563</v>
       </c>
       <c r="H1135" t="n">
         <v>734036</v>
@@ -33400,7 +33400,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1139" t="n">
-        <v>5.45235872268677</v>
+        <v>5.45235824584961</v>
       </c>
       <c r="H1139" t="n">
         <v>1384647</v>
@@ -33429,7 +33429,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G1140" t="n">
-        <v>5.44574165344238</v>
+        <v>5.44574117660522</v>
       </c>
       <c r="H1140" t="n">
         <v>913516</v>
@@ -33516,7 +33516,7 @@
         <v>8.17500019073486</v>
       </c>
       <c r="G1143" t="n">
-        <v>5.40934896469116</v>
+        <v>5.409348487854</v>
       </c>
       <c r="H1143" t="n">
         <v>1350278</v>
@@ -33574,7 +33574,7 @@
         <v>7.16499996185303</v>
       </c>
       <c r="G1145" t="n">
-        <v>5.32360696792603</v>
+        <v>5.32360649108887</v>
       </c>
       <c r="H1145" t="n">
         <v>1106183</v>
@@ -33661,7 +33661,7 @@
         <v>7.5</v>
       </c>
       <c r="G1148" t="n">
-        <v>5.57251214981079</v>
+        <v>5.57251262664795</v>
       </c>
       <c r="H1148" t="n">
         <v>725174</v>
@@ -33806,7 +33806,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G1153" t="n">
-        <v>5.81027221679688</v>
+        <v>5.81027269363403</v>
       </c>
       <c r="H1153" t="n">
         <v>499090</v>
@@ -33980,7 +33980,7 @@
         <v>7.83500003814697</v>
       </c>
       <c r="G1159" t="n">
-        <v>5.82141780853271</v>
+        <v>5.82141733169556</v>
       </c>
       <c r="H1159" t="n">
         <v>328269</v>
@@ -34009,7 +34009,7 @@
         <v>7.66499996185303</v>
       </c>
       <c r="G1160" t="n">
-        <v>5.69510746002197</v>
+        <v>5.69510698318481</v>
       </c>
       <c r="H1160" t="n">
         <v>521334</v>
@@ -34067,7 +34067,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1162" t="n">
-        <v>5.49821186065674</v>
+        <v>5.4982123374939</v>
       </c>
       <c r="H1162" t="n">
         <v>2125447</v>
@@ -34154,7 +34154,7 @@
         <v>7.32499980926514</v>
       </c>
       <c r="G1165" t="n">
-        <v>5.44248676300049</v>
+        <v>5.44248628616333</v>
       </c>
       <c r="H1165" t="n">
         <v>540600</v>
@@ -34183,7 +34183,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G1166" t="n">
-        <v>5.34218168258667</v>
+        <v>5.34218120574951</v>
       </c>
       <c r="H1166" t="n">
         <v>865639</v>
@@ -34328,7 +34328,7 @@
         <v>7.16499996185303</v>
       </c>
       <c r="G1171" t="n">
-        <v>5.32360696792603</v>
+        <v>5.32360649108887</v>
       </c>
       <c r="H1171" t="n">
         <v>426178</v>
@@ -34502,7 +34502,7 @@
         <v>6.91499996185303</v>
       </c>
       <c r="G1177" t="n">
-        <v>5.13785552978516</v>
+        <v>5.13785648345947</v>
       </c>
       <c r="H1177" t="n">
         <v>182140</v>
@@ -34531,7 +34531,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G1178" t="n">
-        <v>4.92610120773315</v>
+        <v>4.92610025405884</v>
       </c>
       <c r="H1178" t="n">
         <v>787105</v>
@@ -34618,7 +34618,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1181" t="n">
-        <v>5.05241107940674</v>
+        <v>5.05241060256958</v>
       </c>
       <c r="H1181" t="n">
         <v>350530</v>
@@ -34676,7 +34676,7 @@
         <v>6.5</v>
       </c>
       <c r="G1183" t="n">
-        <v>4.82951021194458</v>
+        <v>4.82951068878174</v>
       </c>
       <c r="H1183" t="n">
         <v>441280</v>
@@ -34734,7 +34734,7 @@
         <v>6.75</v>
       </c>
       <c r="G1185" t="n">
-        <v>5.01526069641113</v>
+        <v>5.01526117324829</v>
       </c>
       <c r="H1185" t="n">
         <v>303646</v>
@@ -34763,7 +34763,7 @@
         <v>6.57000017166138</v>
       </c>
       <c r="G1186" t="n">
-        <v>4.88152027130127</v>
+        <v>4.88152122497559</v>
       </c>
       <c r="H1186" t="n">
         <v>247408</v>
@@ -34821,7 +34821,7 @@
         <v>6.61499977111816</v>
       </c>
       <c r="G1188" t="n">
-        <v>4.91495513916016</v>
+        <v>4.91495561599731</v>
       </c>
       <c r="H1188" t="n">
         <v>283092</v>
@@ -34850,7 +34850,7 @@
         <v>6.61499977111816</v>
       </c>
       <c r="G1189" t="n">
-        <v>4.91495513916016</v>
+        <v>4.91495561599731</v>
       </c>
       <c r="H1189" t="n">
         <v>316285</v>
@@ -34879,7 +34879,7 @@
         <v>6.66499996185303</v>
       </c>
       <c r="G1190" t="n">
-        <v>4.9521050453186</v>
+        <v>4.95210599899292</v>
       </c>
       <c r="H1190" t="n">
         <v>373430</v>
@@ -34908,7 +34908,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G1191" t="n">
-        <v>4.97811079025269</v>
+        <v>4.97811031341553</v>
       </c>
       <c r="H1191" t="n">
         <v>784430</v>
@@ -34937,7 +34937,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G1192" t="n">
-        <v>5.08956146240234</v>
+        <v>5.08956098556519</v>
       </c>
       <c r="H1192" t="n">
         <v>481573</v>
@@ -34966,7 +34966,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G1193" t="n">
-        <v>5.10442113876343</v>
+        <v>5.10442066192627</v>
       </c>
       <c r="H1193" t="n">
         <v>368322</v>
@@ -34995,7 +34995,7 @@
         <v>6.7350001335144</v>
       </c>
       <c r="G1194" t="n">
-        <v>5.00411558151245</v>
+        <v>5.00411605834961</v>
       </c>
       <c r="H1194" t="n">
         <v>250517</v>
@@ -35053,7 +35053,7 @@
         <v>6.93499994277954</v>
       </c>
       <c r="G1196" t="n">
-        <v>5.1527156829834</v>
+        <v>5.15271615982056</v>
       </c>
       <c r="H1196" t="n">
         <v>264368</v>
@@ -35082,7 +35082,7 @@
         <v>6.93499994277954</v>
       </c>
       <c r="G1197" t="n">
-        <v>5.1527156829834</v>
+        <v>5.15271615982056</v>
       </c>
       <c r="H1197" t="n">
         <v>109721</v>
@@ -35169,7 +35169,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1200" t="n">
-        <v>5.27531147003174</v>
+        <v>5.27531099319458</v>
       </c>
       <c r="H1200" t="n">
         <v>154414</v>
@@ -35227,7 +35227,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1202" t="n">
-        <v>5.34961175918579</v>
+        <v>5.34961080551147</v>
       </c>
       <c r="H1202" t="n">
         <v>307369</v>
@@ -35256,7 +35256,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G1203" t="n">
-        <v>5.46106147766113</v>
+        <v>5.46106195449829</v>
       </c>
       <c r="H1203" t="n">
         <v>364301</v>
@@ -35285,7 +35285,7 @@
         <v>7.17500019073486</v>
       </c>
       <c r="G1204" t="n">
-        <v>5.33103656768799</v>
+        <v>5.33103609085083</v>
       </c>
       <c r="H1204" t="n">
         <v>404955</v>
@@ -35314,7 +35314,7 @@
         <v>7.14499998092651</v>
       </c>
       <c r="G1205" t="n">
-        <v>5.30874681472778</v>
+        <v>5.30874586105347</v>
       </c>
       <c r="H1205" t="n">
         <v>369898</v>
@@ -35343,7 +35343,7 @@
         <v>7.21500015258789</v>
       </c>
       <c r="G1206" t="n">
-        <v>5.36075687408447</v>
+        <v>5.36075639724731</v>
       </c>
       <c r="H1206" t="n">
         <v>254866</v>
@@ -35372,7 +35372,7 @@
         <v>7.16499996185303</v>
       </c>
       <c r="G1207" t="n">
-        <v>5.32360696792603</v>
+        <v>5.32360649108887</v>
       </c>
       <c r="H1207" t="n">
         <v>425328</v>
@@ -35401,7 +35401,7 @@
         <v>7.21500015258789</v>
       </c>
       <c r="G1208" t="n">
-        <v>5.36075687408447</v>
+        <v>5.36075639724731</v>
       </c>
       <c r="H1208" t="n">
         <v>285788</v>
@@ -35430,7 +35430,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1209" t="n">
-        <v>5.27531147003174</v>
+        <v>5.27531099319458</v>
       </c>
       <c r="H1209" t="n">
         <v>331176</v>
@@ -35488,7 +35488,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G1211" t="n">
-        <v>5.24559116363525</v>
+        <v>5.2455906867981</v>
       </c>
       <c r="H1211" t="n">
         <v>185931</v>
@@ -35546,7 +35546,7 @@
         <v>6.94500017166138</v>
       </c>
       <c r="G1213" t="n">
-        <v>5.16014623641968</v>
+        <v>5.16014671325684</v>
       </c>
       <c r="H1213" t="n">
         <v>399759</v>
@@ -35633,7 +35633,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G1216" t="n">
-        <v>5.12671089172363</v>
+        <v>5.12671136856079</v>
       </c>
       <c r="H1216" t="n">
         <v>217888</v>
@@ -35662,7 +35662,7 @@
         <v>6.5</v>
       </c>
       <c r="G1217" t="n">
-        <v>4.82951021194458</v>
+        <v>4.82951068878174</v>
       </c>
       <c r="H1217" t="n">
         <v>538361</v>
@@ -35691,7 +35691,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G1218" t="n">
-        <v>4.92610120773315</v>
+        <v>4.92610025405884</v>
       </c>
       <c r="H1218" t="n">
         <v>536678</v>
@@ -35836,7 +35836,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G1223" t="n">
-        <v>5.17872047424316</v>
+        <v>5.17872142791748</v>
       </c>
       <c r="H1223" t="n">
         <v>363502</v>
@@ -35865,7 +35865,7 @@
         <v>7</v>
       </c>
       <c r="G1224" t="n">
-        <v>5.20101165771484</v>
+        <v>5.20101118087769</v>
       </c>
       <c r="H1224" t="n">
         <v>304813</v>
@@ -35894,7 +35894,7 @@
         <v>6.80499982833862</v>
       </c>
       <c r="G1225" t="n">
-        <v>5.05612564086914</v>
+        <v>5.0561261177063</v>
       </c>
       <c r="H1225" t="n">
         <v>495232</v>
@@ -35981,7 +35981,7 @@
         <v>6.80499982833862</v>
       </c>
       <c r="G1228" t="n">
-        <v>5.05612564086914</v>
+        <v>5.0561261177063</v>
       </c>
       <c r="H1228" t="n">
         <v>481192</v>
@@ -36010,7 +36010,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G1229" t="n">
-        <v>5.21587133407593</v>
+        <v>5.21587085723877</v>
       </c>
       <c r="H1229" t="n">
         <v>373729</v>
@@ -36039,7 +36039,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1230" t="n">
-        <v>5.60966205596924</v>
+        <v>5.60966157913208</v>
       </c>
       <c r="H1230" t="n">
         <v>2500586</v>
@@ -36068,7 +36068,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G1231" t="n">
-        <v>5.70625257492065</v>
+        <v>5.7062520980835</v>
       </c>
       <c r="H1231" t="n">
         <v>1441593</v>
@@ -36097,7 +36097,7 @@
         <v>7.45499992370605</v>
       </c>
       <c r="G1232" t="n">
-        <v>5.53907680511475</v>
+        <v>5.5390772819519</v>
       </c>
       <c r="H1232" t="n">
         <v>1054531</v>
@@ -36126,7 +36126,7 @@
         <v>7.67500019073486</v>
       </c>
       <c r="G1233" t="n">
-        <v>5.70253753662109</v>
+        <v>5.70253705978394</v>
       </c>
       <c r="H1233" t="n">
         <v>913504</v>
@@ -36155,7 +36155,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G1234" t="n">
-        <v>5.54279232025146</v>
+        <v>5.54279184341431</v>
       </c>
       <c r="H1234" t="n">
         <v>698987</v>
@@ -36184,7 +36184,7 @@
         <v>7.375</v>
       </c>
       <c r="G1235" t="n">
-        <v>5.47963666915894</v>
+        <v>5.47963714599609</v>
       </c>
       <c r="H1235" t="n">
         <v>514007</v>
@@ -36242,7 +36242,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G1237" t="n">
-        <v>5.34218168258667</v>
+        <v>5.34218120574951</v>
       </c>
       <c r="H1237" t="n">
         <v>603372</v>
@@ -36271,7 +36271,7 @@
         <v>7.25500011444092</v>
       </c>
       <c r="G1238" t="n">
-        <v>5.3904767036438</v>
+        <v>5.39047622680664</v>
       </c>
       <c r="H1238" t="n">
         <v>659127</v>
@@ -36300,7 +36300,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G1239" t="n">
-        <v>5.25302124023438</v>
+        <v>5.25302171707153</v>
       </c>
       <c r="H1239" t="n">
         <v>606686</v>
@@ -36387,7 +36387,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G1242" t="n">
-        <v>4.79236030578613</v>
+        <v>4.79235982894897</v>
       </c>
       <c r="H1242" t="n">
         <v>1200518</v>
@@ -36561,7 +36561,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G1248" t="n">
-        <v>4.53974008560181</v>
+        <v>4.53973960876465</v>
       </c>
       <c r="H1248" t="n">
         <v>1277935</v>
@@ -36590,7 +36590,7 @@
         <v>6.25</v>
       </c>
       <c r="G1249" t="n">
-        <v>4.64375972747803</v>
+        <v>4.64376068115234</v>
       </c>
       <c r="H1249" t="n">
         <v>3209768</v>
@@ -36619,7 +36619,7 @@
         <v>6.06500005722046</v>
       </c>
       <c r="G1250" t="n">
-        <v>4.50630521774292</v>
+        <v>4.5063042640686</v>
       </c>
       <c r="H1250" t="n">
         <v>1013000</v>
@@ -36648,7 +36648,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G1251" t="n">
-        <v>4.53230953216553</v>
+        <v>4.53231000900269</v>
       </c>
       <c r="H1251" t="n">
         <v>894445</v>
@@ -36677,7 +36677,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G1252" t="n">
-        <v>4.71806001663208</v>
+        <v>4.71806049346924</v>
       </c>
       <c r="H1252" t="n">
         <v>1225760</v>
@@ -36706,7 +36706,7 @@
         <v>6.2649998664856</v>
       </c>
       <c r="G1253" t="n">
-        <v>4.65490436553955</v>
+        <v>4.65490484237671</v>
       </c>
       <c r="H1253" t="n">
         <v>956969</v>
@@ -36938,7 +36938,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G1261" t="n">
-        <v>5.00040102005005</v>
+        <v>5.00040054321289</v>
       </c>
       <c r="H1261" t="n">
         <v>916045</v>
@@ -36967,7 +36967,7 @@
         <v>6.68499994277954</v>
       </c>
       <c r="G1262" t="n">
-        <v>4.966965675354</v>
+        <v>4.96696519851685</v>
       </c>
       <c r="H1262" t="n">
         <v>954750</v>
@@ -37054,7 +37054,7 @@
         <v>6.7350001335144</v>
       </c>
       <c r="G1265" t="n">
-        <v>5.00411558151245</v>
+        <v>5.00411605834961</v>
       </c>
       <c r="H1265" t="n">
         <v>721014</v>
@@ -37083,7 +37083,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G1266" t="n">
-        <v>5.08213138580322</v>
+        <v>5.08213090896606</v>
       </c>
       <c r="H1266" t="n">
         <v>1127939</v>
@@ -37141,7 +37141,7 @@
         <v>7.00500011444092</v>
       </c>
       <c r="G1268" t="n">
-        <v>5.20472621917725</v>
+        <v>5.20472574234009</v>
       </c>
       <c r="H1268" t="n">
         <v>1084901</v>
@@ -37170,7 +37170,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G1269" t="n">
-        <v>5.00040102005005</v>
+        <v>5.00040054321289</v>
       </c>
       <c r="H1269" t="n">
         <v>1325263</v>
@@ -37199,7 +37199,7 @@
         <v>6.80499982833862</v>
       </c>
       <c r="G1270" t="n">
-        <v>5.05612564086914</v>
+        <v>5.0561261177063</v>
       </c>
       <c r="H1270" t="n">
         <v>924463</v>
@@ -37257,7 +37257,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G1272" t="n">
-        <v>5.15643119812012</v>
+        <v>5.15643072128296</v>
       </c>
       <c r="H1272" t="n">
         <v>982597</v>
@@ -37460,7 +37460,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G1279" t="n">
-        <v>4.98422527313232</v>
+        <v>4.98422574996948</v>
       </c>
       <c r="H1279" t="n">
         <v>706800</v>
@@ -37489,7 +37489,7 @@
         <v>5.96500015258789</v>
       </c>
       <c r="G1280" t="n">
-        <v>4.91419887542725</v>
+        <v>4.9141993522644</v>
       </c>
       <c r="H1280" t="n">
         <v>605329</v>
@@ -37518,7 +37518,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G1281" t="n">
-        <v>4.79474306106567</v>
+        <v>4.79474258422852</v>
       </c>
       <c r="H1281" t="n">
         <v>557631</v>
@@ -37576,7 +37576,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G1283" t="n">
-        <v>4.9183177947998</v>
+        <v>4.91831827163696</v>
       </c>
       <c r="H1283" t="n">
         <v>584822</v>
@@ -37808,7 +37808,7 @@
         <v>6.30499982833862</v>
       </c>
       <c r="G1291" t="n">
-        <v>5.1943039894104</v>
+        <v>5.19430446624756</v>
       </c>
       <c r="H1291" t="n">
         <v>899123</v>
@@ -37866,7 +37866,7 @@
         <v>6.59499979019165</v>
       </c>
       <c r="G1293" t="n">
-        <v>5.43321752548218</v>
+        <v>5.43321704864502</v>
       </c>
       <c r="H1293" t="n">
         <v>1115862</v>
@@ -37895,7 +37895,7 @@
         <v>6.71500015258789</v>
       </c>
       <c r="G1294" t="n">
-        <v>5.5320782661438</v>
+        <v>5.53207874298096</v>
       </c>
       <c r="H1294" t="n">
         <v>1703942</v>
@@ -37924,7 +37924,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G1295" t="n">
-        <v>5.61858129501343</v>
+        <v>5.61858177185059</v>
       </c>
       <c r="H1295" t="n">
         <v>1888570</v>
@@ -38011,7 +38011,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G1298" t="n">
-        <v>5.8245415687561</v>
+        <v>5.82454109191895</v>
       </c>
       <c r="H1298" t="n">
         <v>729162</v>
@@ -38040,7 +38040,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G1299" t="n">
-        <v>5.98930883407593</v>
+        <v>5.98930835723877</v>
       </c>
       <c r="H1299" t="n">
         <v>1579602</v>
@@ -38069,7 +38069,7 @@
         <v>7.34499979019165</v>
       </c>
       <c r="G1300" t="n">
-        <v>6.05109643936157</v>
+        <v>6.05109691619873</v>
       </c>
       <c r="H1300" t="n">
         <v>792527</v>
@@ -38098,7 +38098,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G1301" t="n">
-        <v>5.98930883407593</v>
+        <v>5.98930835723877</v>
       </c>
       <c r="H1301" t="n">
         <v>683265</v>
@@ -38127,7 +38127,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G1302" t="n">
-        <v>5.99754762649536</v>
+        <v>5.9975471496582</v>
       </c>
       <c r="H1302" t="n">
         <v>585533</v>
@@ -38214,7 +38214,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G1305" t="n">
-        <v>6.11288499832153</v>
+        <v>6.11288452148438</v>
       </c>
       <c r="H1305" t="n">
         <v>723894</v>
@@ -38243,7 +38243,7 @@
         <v>7.25</v>
       </c>
       <c r="G1306" t="n">
-        <v>5.97283220291138</v>
+        <v>5.97283172607422</v>
       </c>
       <c r="H1306" t="n">
         <v>849175</v>
@@ -38272,7 +38272,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G1307" t="n">
-        <v>6.00578546524048</v>
+        <v>6.00578594207764</v>
       </c>
       <c r="H1307" t="n">
         <v>464920</v>
@@ -38359,7 +38359,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1310" t="n">
-        <v>5.93164014816284</v>
+        <v>5.93163967132568</v>
       </c>
       <c r="H1310" t="n">
         <v>373983</v>
@@ -38388,7 +38388,7 @@
         <v>7.31500005722046</v>
       </c>
       <c r="G1311" t="n">
-        <v>6.0263819694519</v>
+        <v>6.02638149261475</v>
       </c>
       <c r="H1311" t="n">
         <v>314418</v>
@@ -38417,7 +38417,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1312" t="n">
-        <v>5.93164014816284</v>
+        <v>5.93163967132568</v>
       </c>
       <c r="H1312" t="n">
         <v>222590</v>
@@ -38475,7 +38475,7 @@
         <v>6.95499992370605</v>
       </c>
       <c r="G1314" t="n">
-        <v>5.72979927062988</v>
+        <v>5.72979974746704</v>
       </c>
       <c r="H1314" t="n">
         <v>920535</v>
@@ -38562,7 +38562,7 @@
         <v>6.86499977111816</v>
       </c>
       <c r="G1317" t="n">
-        <v>5.65565395355225</v>
+        <v>5.6556544303894</v>
       </c>
       <c r="H1317" t="n">
         <v>519132</v>
@@ -38649,7 +38649,7 @@
         <v>6.60500001907349</v>
       </c>
       <c r="G1320" t="n">
-        <v>5.44145584106445</v>
+        <v>5.44145631790161</v>
       </c>
       <c r="H1320" t="n">
         <v>313265</v>
@@ -38678,7 +38678,7 @@
         <v>6.60500001907349</v>
       </c>
       <c r="G1321" t="n">
-        <v>5.44145584106445</v>
+        <v>5.44145631790161</v>
       </c>
       <c r="H1321" t="n">
         <v>384962</v>
@@ -38707,7 +38707,7 @@
         <v>6.48999977111816</v>
       </c>
       <c r="G1322" t="n">
-        <v>5.34671401977539</v>
+        <v>5.34671449661255</v>
       </c>
       <c r="H1322" t="n">
         <v>475353</v>
@@ -38736,7 +38736,7 @@
         <v>6.5149998664856</v>
       </c>
       <c r="G1323" t="n">
-        <v>5.36731004714966</v>
+        <v>5.36731052398682</v>
       </c>
       <c r="H1323" t="n">
         <v>581058</v>
@@ -38765,7 +38765,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G1324" t="n">
-        <v>5.50324392318726</v>
+        <v>5.5032434463501</v>
       </c>
       <c r="H1324" t="n">
         <v>619799</v>
@@ -38794,7 +38794,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G1325" t="n">
-        <v>5.50324392318726</v>
+        <v>5.5032434463501</v>
       </c>
       <c r="H1325" t="n">
         <v>464277</v>
@@ -38852,7 +38852,7 @@
         <v>6.63500022888184</v>
       </c>
       <c r="G1327" t="n">
-        <v>5.46617078781128</v>
+        <v>5.46617126464844</v>
       </c>
       <c r="H1327" t="n">
         <v>342171</v>
@@ -38997,7 +38997,7 @@
         <v>6.30999994277954</v>
       </c>
       <c r="G1332" t="n">
-        <v>5.19842386245728</v>
+        <v>5.19842338562012</v>
       </c>
       <c r="H1332" t="n">
         <v>302909</v>
@@ -39055,7 +39055,7 @@
         <v>6.57000017166138</v>
       </c>
       <c r="G1334" t="n">
-        <v>5.41262149810791</v>
+        <v>5.41262197494507</v>
       </c>
       <c r="H1334" t="n">
         <v>455465</v>
@@ -39084,7 +39084,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G1335" t="n">
-        <v>5.33023738861084</v>
+        <v>5.33023691177368</v>
       </c>
       <c r="H1335" t="n">
         <v>362879</v>
@@ -39142,7 +39142,7 @@
         <v>6.44500017166138</v>
       </c>
       <c r="G1337" t="n">
-        <v>5.30964183807373</v>
+        <v>5.30964231491089</v>
       </c>
       <c r="H1337" t="n">
         <v>327664</v>
@@ -39258,7 +39258,7 @@
         <v>6.42500019073486</v>
       </c>
       <c r="G1341" t="n">
-        <v>5.29316520690918</v>
+        <v>5.29316473007202</v>
       </c>
       <c r="H1341" t="n">
         <v>595388</v>
@@ -39403,7 +39403,7 @@
         <v>6.63500022888184</v>
       </c>
       <c r="G1346" t="n">
-        <v>5.46617078781128</v>
+        <v>5.46617126464844</v>
       </c>
       <c r="H1346" t="n">
         <v>301137</v>
@@ -39432,7 +39432,7 @@
         <v>6.67000007629395</v>
       </c>
       <c r="G1347" t="n">
-        <v>5.49500560760498</v>
+        <v>5.49500608444214</v>
       </c>
       <c r="H1347" t="n">
         <v>330416</v>
@@ -39519,7 +39519,7 @@
         <v>6.86499977111816</v>
       </c>
       <c r="G1350" t="n">
-        <v>5.65565395355225</v>
+        <v>5.6556544303894</v>
       </c>
       <c r="H1350" t="n">
         <v>463464</v>
@@ -39548,7 +39548,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G1351" t="n">
-        <v>5.54443645477295</v>
+        <v>5.54443597793579</v>
       </c>
       <c r="H1351" t="n">
         <v>316292</v>
@@ -39606,7 +39606,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G1353" t="n">
-        <v>5.85749483108521</v>
+        <v>5.85749435424805</v>
       </c>
       <c r="H1353" t="n">
         <v>1026522</v>
@@ -39693,7 +39693,7 @@
         <v>6.86499977111816</v>
       </c>
       <c r="G1356" t="n">
-        <v>5.65565395355225</v>
+        <v>5.6556544303894</v>
       </c>
       <c r="H1356" t="n">
         <v>779460</v>
@@ -39722,7 +39722,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G1357" t="n">
-        <v>5.68448925018311</v>
+        <v>5.68448877334595</v>
       </c>
       <c r="H1357" t="n">
         <v>382672</v>
@@ -39780,7 +39780,7 @@
         <v>7.0149998664856</v>
       </c>
       <c r="G1359" t="n">
-        <v>5.77922964096069</v>
+        <v>5.77923011779785</v>
       </c>
       <c r="H1359" t="n">
         <v>307914</v>
@@ -39809,7 +39809,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1360" t="n">
-        <v>5.84925651550293</v>
+        <v>5.84925556182861</v>
       </c>
       <c r="H1360" t="n">
         <v>390352</v>
@@ -39838,7 +39838,7 @@
         <v>6.95499992370605</v>
       </c>
       <c r="G1361" t="n">
-        <v>5.72979927062988</v>
+        <v>5.72979974746704</v>
       </c>
       <c r="H1361" t="n">
         <v>401580</v>
@@ -39954,7 +39954,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1365" t="n">
-        <v>5.62401533126831</v>
+        <v>5.62401437759399</v>
       </c>
       <c r="H1365" t="n">
         <v>368046</v>
@@ -40012,7 +40012,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G1367" t="n">
-        <v>5.54566144943237</v>
+        <v>5.54566097259521</v>
       </c>
       <c r="H1367" t="n">
         <v>279712</v>
@@ -40070,7 +40070,7 @@
         <v>6.31500005722046</v>
       </c>
       <c r="G1369" t="n">
-        <v>5.49777889251709</v>
+        <v>5.49777936935425</v>
       </c>
       <c r="H1369" t="n">
         <v>338884</v>
@@ -40128,7 +40128,7 @@
         <v>6.31500005722046</v>
       </c>
       <c r="G1371" t="n">
-        <v>5.49777889251709</v>
+        <v>5.49777936935425</v>
       </c>
       <c r="H1371" t="n">
         <v>311946</v>
@@ -40331,7 +40331,7 @@
         <v>6.46500015258789</v>
       </c>
       <c r="G1378" t="n">
-        <v>5.62836742401123</v>
+        <v>5.62836790084839</v>
       </c>
       <c r="H1378" t="n">
         <v>569369</v>
@@ -40476,7 +40476,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G1383" t="n">
-        <v>5.94613361358643</v>
+        <v>5.94613313674927</v>
       </c>
       <c r="H1383" t="n">
         <v>486257</v>
@@ -40534,7 +40534,7 @@
         <v>7.03499984741211</v>
       </c>
       <c r="G1385" t="n">
-        <v>6.12460422515869</v>
+        <v>6.12460374832153</v>
       </c>
       <c r="H1385" t="n">
         <v>1104845</v>
@@ -40621,7 +40621,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G1388" t="n">
-        <v>6.06801605224609</v>
+        <v>6.06801557540894</v>
       </c>
       <c r="H1388" t="n">
         <v>745839</v>
@@ -40650,7 +40650,7 @@
         <v>7.10500001907349</v>
       </c>
       <c r="G1389" t="n">
-        <v>6.18554544448853</v>
+        <v>6.18554592132568</v>
       </c>
       <c r="H1389" t="n">
         <v>809398</v>
@@ -40708,7 +40708,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G1391" t="n">
-        <v>5.8242506980896</v>
+        <v>5.82425117492676</v>
       </c>
       <c r="H1391" t="n">
         <v>1019242</v>
@@ -40737,7 +40737,7 @@
         <v>6.42500019073486</v>
       </c>
       <c r="G1392" t="n">
-        <v>5.59354448318481</v>
+        <v>5.59354400634766</v>
       </c>
       <c r="H1392" t="n">
         <v>679007</v>
@@ -40795,7 +40795,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G1394" t="n">
-        <v>5.98095703125</v>
+        <v>5.98095655441284</v>
       </c>
       <c r="H1394" t="n">
         <v>462641</v>
@@ -40882,7 +40882,7 @@
         <v>7</v>
       </c>
       <c r="G1397" t="n">
-        <v>6.09413385391235</v>
+        <v>6.0941333770752</v>
       </c>
       <c r="H1397" t="n">
         <v>570126</v>
@@ -40940,7 +40940,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G1399" t="n">
-        <v>5.88519239425659</v>
+        <v>5.88519191741943</v>
       </c>
       <c r="H1399" t="n">
         <v>284601</v>
@@ -40998,7 +40998,7 @@
         <v>6.94500017166138</v>
       </c>
       <c r="G1401" t="n">
-        <v>6.04625177383423</v>
+        <v>6.04625129699707</v>
       </c>
       <c r="H1401" t="n">
         <v>355087</v>
@@ -41114,7 +41114,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G1405" t="n">
-        <v>6.06801605224609</v>
+        <v>6.06801557540894</v>
       </c>
       <c r="H1405" t="n">
         <v>602527</v>
@@ -41143,7 +41143,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G1406" t="n">
-        <v>6.00707483291626</v>
+        <v>6.0070743560791</v>
       </c>
       <c r="H1406" t="n">
         <v>425630</v>
@@ -41172,7 +41172,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G1407" t="n">
-        <v>6.11154556274414</v>
+        <v>6.11154508590698</v>
       </c>
       <c r="H1407" t="n">
         <v>474824</v>
@@ -41201,7 +41201,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G1408" t="n">
-        <v>6.1376633644104</v>
+        <v>6.13766288757324</v>
       </c>
       <c r="H1408" t="n">
         <v>248163</v>
@@ -41259,7 +41259,7 @@
         <v>7.17500019073486</v>
       </c>
       <c r="G1410" t="n">
-        <v>6.24648666381836</v>
+        <v>6.24648761749268</v>
       </c>
       <c r="H1410" t="n">
         <v>828079</v>
@@ -41288,7 +41288,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G1411" t="n">
-        <v>6.24213457107544</v>
+        <v>6.24213409423828</v>
       </c>
       <c r="H1411" t="n">
         <v>595908</v>
@@ -41346,7 +41346,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G1413" t="n">
-        <v>6.24213457107544</v>
+        <v>6.24213409423828</v>
       </c>
       <c r="H1413" t="n">
         <v>458732</v>
@@ -41404,7 +41404,7 @@
         <v>7.22499990463257</v>
       </c>
       <c r="G1415" t="n">
-        <v>6.29001617431641</v>
+        <v>6.29001665115356</v>
       </c>
       <c r="H1415" t="n">
         <v>360806</v>
@@ -41520,7 +41520,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1419" t="n">
-        <v>6.44236946105957</v>
+        <v>6.44236993789673</v>
       </c>
       <c r="H1419" t="n">
         <v>1090483</v>
@@ -41549,7 +41549,7 @@
         <v>7.20499992370605</v>
       </c>
       <c r="G1420" t="n">
-        <v>6.27260446548462</v>
+        <v>6.27260494232178</v>
       </c>
       <c r="H1420" t="n">
         <v>988314</v>
@@ -41578,7 +41578,7 @@
         <v>7.17500019073486</v>
       </c>
       <c r="G1421" t="n">
-        <v>6.24648666381836</v>
+        <v>6.24648761749268</v>
       </c>
       <c r="H1421" t="n">
         <v>574768</v>
@@ -41723,7 +41723,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G1426" t="n">
-        <v>6.24213457107544</v>
+        <v>6.24213409423828</v>
       </c>
       <c r="H1426" t="n">
         <v>603569</v>
@@ -41752,7 +41752,7 @@
         <v>7.16499996185303</v>
       </c>
       <c r="G1427" t="n">
-        <v>6.23778104782104</v>
+        <v>6.2377815246582</v>
       </c>
       <c r="H1427" t="n">
         <v>274142</v>
@@ -41839,7 +41839,7 @@
         <v>7.2649998664856</v>
       </c>
       <c r="G1430" t="n">
-        <v>6.32484006881714</v>
+        <v>6.3248405456543</v>
       </c>
       <c r="H1430" t="n">
         <v>376384</v>
@@ -41868,7 +41868,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G1431" t="n">
-        <v>6.37272310256958</v>
+        <v>6.37272262573242</v>
       </c>
       <c r="H1431" t="n">
         <v>372047</v>
@@ -41897,7 +41897,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1432" t="n">
-        <v>6.44236946105957</v>
+        <v>6.44236993789673</v>
       </c>
       <c r="H1432" t="n">
         <v>623104</v>
@@ -41926,7 +41926,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G1433" t="n">
-        <v>6.41625261306763</v>
+        <v>6.41625213623047</v>
       </c>
       <c r="H1433" t="n">
         <v>599465</v>
@@ -41984,7 +41984,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G1435" t="n">
-        <v>6.47719383239746</v>
+        <v>6.4771933555603</v>
       </c>
       <c r="H1435" t="n">
         <v>306662</v>
@@ -42129,7 +42129,7 @@
         <v>7.31500005722046</v>
       </c>
       <c r="G1440" t="n">
-        <v>6.36836957931519</v>
+        <v>6.36837005615234</v>
       </c>
       <c r="H1440" t="n">
         <v>564027</v>
@@ -42245,7 +42245,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G1444" t="n">
-        <v>6.41625261306763</v>
+        <v>6.41625213623047</v>
       </c>
       <c r="H1444" t="n">
         <v>486129</v>
@@ -42274,7 +42274,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G1445" t="n">
-        <v>6.47719383239746</v>
+        <v>6.4771933555603</v>
       </c>
       <c r="H1445" t="n">
         <v>662103</v>
@@ -42303,7 +42303,7 @@
         <v>7.40999984741211</v>
       </c>
       <c r="G1446" t="n">
-        <v>6.4510760307312</v>
+        <v>6.45107555389404</v>
       </c>
       <c r="H1446" t="n">
         <v>215878</v>
@@ -42332,7 +42332,7 @@
         <v>7.20499992370605</v>
       </c>
       <c r="G1447" t="n">
-        <v>6.27260446548462</v>
+        <v>6.27260494232178</v>
       </c>
       <c r="H1447" t="n">
         <v>488297</v>
@@ -42448,7 +42448,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G1451" t="n">
-        <v>6.47719383239746</v>
+        <v>6.4771933555603</v>
       </c>
       <c r="H1451" t="n">
         <v>526858</v>
@@ -42564,7 +42564,7 @@
         <v>7.39499998092651</v>
       </c>
       <c r="G1455" t="n">
-        <v>6.43801736831665</v>
+        <v>6.43801689147949</v>
       </c>
       <c r="H1455" t="n">
         <v>233389</v>
@@ -42622,7 +42622,7 @@
         <v>7.40999984741211</v>
       </c>
       <c r="G1457" t="n">
-        <v>6.4510760307312</v>
+        <v>6.45107555389404</v>
       </c>
       <c r="H1457" t="n">
         <v>267610</v>
@@ -42767,7 +42767,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G1462" t="n">
-        <v>6.91248846054077</v>
+        <v>6.91248893737793</v>
       </c>
       <c r="H1462" t="n">
         <v>370330</v>
@@ -42854,7 +42854,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G1465" t="n">
-        <v>7.25201940536499</v>
+        <v>7.25201892852783</v>
       </c>
       <c r="H1465" t="n">
         <v>830336</v>
@@ -42883,7 +42883,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1466" t="n">
-        <v>7.31295967102051</v>
+        <v>7.31296014785767</v>
       </c>
       <c r="H1466" t="n">
         <v>634077</v>
@@ -42912,7 +42912,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G1467" t="n">
-        <v>7.33037233352661</v>
+        <v>7.33037281036377</v>
       </c>
       <c r="H1467" t="n">
         <v>932195</v>
@@ -42941,7 +42941,7 @@
         <v>8.42500019073486</v>
       </c>
       <c r="G1468" t="n">
-        <v>7.33472490310669</v>
+        <v>7.33472585678101</v>
       </c>
       <c r="H1468" t="n">
         <v>301354</v>
@@ -42999,7 +42999,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1470" t="n">
-        <v>7.44354867935181</v>
+        <v>7.44354915618896</v>
       </c>
       <c r="H1470" t="n">
         <v>784780</v>
@@ -43028,7 +43028,7 @@
         <v>8.50500011444092</v>
       </c>
       <c r="G1471" t="n">
-        <v>7.40437316894531</v>
+        <v>7.40437269210815</v>
       </c>
       <c r="H1471" t="n">
         <v>333173</v>
@@ -43057,7 +43057,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G1472" t="n">
-        <v>7.45225524902344</v>
+        <v>7.45225477218628</v>
       </c>
       <c r="H1472" t="n">
         <v>494651</v>
@@ -43115,7 +43115,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G1474" t="n">
-        <v>7.35648965835571</v>
+        <v>7.35649013519287</v>
       </c>
       <c r="H1474" t="n">
         <v>1337680</v>
@@ -43173,7 +43173,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G1476" t="n">
-        <v>7.27813625335693</v>
+        <v>7.27813673019409</v>
       </c>
       <c r="H1476" t="n">
         <v>955978</v>
@@ -43231,7 +43231,7 @@
         <v>8.61499977111816</v>
       </c>
       <c r="G1478" t="n">
-        <v>7.50013780593872</v>
+        <v>7.50013732910156</v>
       </c>
       <c r="H1478" t="n">
         <v>996632</v>
@@ -43260,7 +43260,7 @@
         <v>8.48499965667725</v>
       </c>
       <c r="G1479" t="n">
-        <v>7.38696002960205</v>
+        <v>7.38696098327637</v>
       </c>
       <c r="H1479" t="n">
         <v>971538</v>
@@ -43318,7 +43318,7 @@
         <v>8.6899995803833</v>
       </c>
       <c r="G1481" t="n">
-        <v>7.56543207168579</v>
+        <v>7.56543159484863</v>
       </c>
       <c r="H1481" t="n">
         <v>1037153</v>
@@ -43347,7 +43347,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G1482" t="n">
-        <v>7.64378547668457</v>
+        <v>7.64378452301025</v>
       </c>
       <c r="H1482" t="n">
         <v>701740</v>
@@ -43376,7 +43376,7 @@
         <v>8.76500034332275</v>
       </c>
       <c r="G1483" t="n">
-        <v>7.6307258605957</v>
+        <v>7.63072633743286</v>
       </c>
       <c r="H1483" t="n">
         <v>409479</v>
@@ -43405,7 +43405,7 @@
         <v>8.90499973297119</v>
       </c>
       <c r="G1484" t="n">
-        <v>7.75260925292969</v>
+        <v>7.75260829925537</v>
       </c>
       <c r="H1484" t="n">
         <v>521714</v>
@@ -43463,7 +43463,7 @@
         <v>8.89000034332275</v>
       </c>
       <c r="G1486" t="n">
-        <v>7.73955011367798</v>
+        <v>7.73954963684082</v>
       </c>
       <c r="H1486" t="n">
         <v>1406501</v>
@@ -43637,7 +43637,7 @@
         <v>9.71500015258789</v>
       </c>
       <c r="G1492" t="n">
-        <v>8.45778656005859</v>
+        <v>8.45778751373291</v>
       </c>
       <c r="H1492" t="n">
         <v>784053</v>
@@ -43782,7 +43782,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1497" t="n">
-        <v>8.21837329864502</v>
+        <v>8.21837520599365</v>
       </c>
       <c r="H1497" t="n">
         <v>383904</v>
@@ -43811,7 +43811,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G1498" t="n">
-        <v>8.25319766998291</v>
+        <v>8.25319862365723</v>
       </c>
       <c r="H1498" t="n">
         <v>366213</v>
@@ -43840,7 +43840,7 @@
         <v>9.39000034332275</v>
       </c>
       <c r="G1499" t="n">
-        <v>8.17484474182129</v>
+        <v>8.17484569549561</v>
       </c>
       <c r="H1499" t="n">
         <v>1011227</v>
@@ -43869,7 +43869,7 @@
         <v>9.36499977111816</v>
       </c>
       <c r="G1500" t="n">
-        <v>8.15307998657227</v>
+        <v>8.15308094024658</v>
       </c>
       <c r="H1500" t="n">
         <v>582165</v>
@@ -43956,7 +43956,7 @@
         <v>9.51500034332275</v>
       </c>
       <c r="G1503" t="n">
-        <v>8.28366851806641</v>
+        <v>8.28366947174072</v>
       </c>
       <c r="H1503" t="n">
         <v>391527</v>
@@ -43985,7 +43985,7 @@
         <v>9.45499992370605</v>
       </c>
       <c r="G1504" t="n">
-        <v>8.23143291473389</v>
+        <v>8.2314338684082</v>
       </c>
       <c r="H1504" t="n">
         <v>569207</v>
@@ -44014,7 +44014,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G1505" t="n">
-        <v>8.29672718048096</v>
+        <v>8.29672813415527</v>
       </c>
       <c r="H1505" t="n">
         <v>510466</v>
@@ -44043,7 +44043,7 @@
         <v>9.4350004196167</v>
       </c>
       <c r="G1506" t="n">
-        <v>8.21402168273926</v>
+        <v>8.21402263641357</v>
       </c>
       <c r="H1506" t="n">
         <v>558152</v>
@@ -44072,7 +44072,7 @@
         <v>9.34500026702881</v>
       </c>
       <c r="G1507" t="n">
-        <v>8.13566875457764</v>
+        <v>8.13566970825195</v>
       </c>
       <c r="H1507" t="n">
         <v>486793</v>
@@ -44159,7 +44159,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G1510" t="n">
-        <v>7.85272693634033</v>
+        <v>7.85272741317749</v>
       </c>
       <c r="H1510" t="n">
         <v>985781</v>
@@ -44217,7 +44217,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G1512" t="n">
-        <v>7.89625549316406</v>
+        <v>7.89625597000122</v>
       </c>
       <c r="H1512" t="n">
         <v>978207</v>
@@ -44275,7 +44275,7 @@
         <v>9.45499992370605</v>
       </c>
       <c r="G1514" t="n">
-        <v>8.23143291473389</v>
+        <v>8.2314338684082</v>
       </c>
       <c r="H1514" t="n">
         <v>505040</v>
@@ -44333,7 +44333,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G1516" t="n">
-        <v>8.06166934967041</v>
+        <v>8.06166839599609</v>
       </c>
       <c r="H1516" t="n">
         <v>309833</v>
@@ -44391,7 +44391,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G1518" t="n">
-        <v>7.96590328216553</v>
+        <v>7.96590280532837</v>
       </c>
       <c r="H1518" t="n">
         <v>277209</v>
@@ -44420,7 +44420,7 @@
         <v>9.00500011444092</v>
       </c>
       <c r="G1519" t="n">
-        <v>7.83966827392578</v>
+        <v>7.83966875076294</v>
       </c>
       <c r="H1519" t="n">
         <v>335752</v>
@@ -44449,7 +44449,7 @@
         <v>9.0649995803833</v>
       </c>
       <c r="G1520" t="n">
-        <v>7.89190244674683</v>
+        <v>7.89190340042114</v>
       </c>
       <c r="H1520" t="n">
         <v>362751</v>
@@ -44507,7 +44507,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G1522" t="n">
-        <v>7.96590328216553</v>
+        <v>7.96590280532837</v>
       </c>
       <c r="H1522" t="n">
         <v>378678</v>
@@ -44565,7 +44565,7 @@
         <v>8.98999977111816</v>
       </c>
       <c r="G1524" t="n">
-        <v>7.82660818099976</v>
+        <v>7.82660913467407</v>
       </c>
       <c r="H1524" t="n">
         <v>463133</v>
@@ -44623,7 +44623,7 @@
         <v>9.17500019073486</v>
       </c>
       <c r="G1526" t="n">
-        <v>7.98766803741455</v>
+        <v>7.98766851425171</v>
       </c>
       <c r="H1526" t="n">
         <v>600996</v>
@@ -44681,7 +44681,7 @@
         <v>9.32999992370605</v>
       </c>
       <c r="G1528" t="n">
-        <v>8.12260913848877</v>
+        <v>8.12261009216309</v>
       </c>
       <c r="H1528" t="n">
         <v>786329</v>
@@ -44739,7 +44739,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G1530" t="n">
-        <v>8.09649181365967</v>
+        <v>8.09649276733398</v>
       </c>
       <c r="H1530" t="n">
         <v>265762</v>
@@ -44855,7 +44855,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G1534" t="n">
-        <v>7.89625549316406</v>
+        <v>7.89625597000122</v>
       </c>
       <c r="H1534" t="n">
         <v>802316</v>
@@ -44884,7 +44884,7 @@
         <v>9.0649995803833</v>
       </c>
       <c r="G1535" t="n">
-        <v>7.89190244674683</v>
+        <v>7.89190340042114</v>
       </c>
       <c r="H1535" t="n">
         <v>704474</v>
@@ -44913,7 +44913,7 @@
         <v>8.69499969482422</v>
       </c>
       <c r="G1536" t="n">
-        <v>7.93662929534912</v>
+        <v>7.93662881851196</v>
       </c>
       <c r="H1536" t="n">
         <v>507202</v>
@@ -45029,7 +45029,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G1540" t="n">
-        <v>7.95944929122925</v>
+        <v>7.95944976806641</v>
       </c>
       <c r="H1540" t="n">
         <v>550498</v>
@@ -45116,7 +45116,7 @@
         <v>8.57499980926514</v>
       </c>
       <c r="G1543" t="n">
-        <v>7.82709503173828</v>
+        <v>7.8270959854126</v>
       </c>
       <c r="H1543" t="n">
         <v>487978</v>
@@ -45174,7 +45174,7 @@
         <v>8.61499977111816</v>
       </c>
       <c r="G1545" t="n">
-        <v>7.86360740661621</v>
+        <v>7.86360692977905</v>
       </c>
       <c r="H1545" t="n">
         <v>314147</v>
@@ -45203,7 +45203,7 @@
         <v>8.69499969482422</v>
       </c>
       <c r="G1546" t="n">
-        <v>7.93662929534912</v>
+        <v>7.93662881851196</v>
       </c>
       <c r="H1546" t="n">
         <v>343437</v>
@@ -45232,7 +45232,7 @@
         <v>8.54500007629395</v>
       </c>
       <c r="G1547" t="n">
-        <v>7.79971265792847</v>
+        <v>7.79971218109131</v>
       </c>
       <c r="H1547" t="n">
         <v>435110</v>
@@ -45290,7 +45290,7 @@
         <v>8.625</v>
       </c>
       <c r="G1549" t="n">
-        <v>7.87273454666138</v>
+        <v>7.87273502349854</v>
       </c>
       <c r="H1549" t="n">
         <v>1110761</v>
@@ -45319,7 +45319,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G1550" t="n">
-        <v>7.84078788757324</v>
+        <v>7.84078741073608</v>
       </c>
       <c r="H1550" t="n">
         <v>460886</v>
@@ -45493,7 +45493,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G1556" t="n">
-        <v>8.38845539093018</v>
+        <v>8.38845634460449</v>
       </c>
       <c r="H1556" t="n">
         <v>600568</v>
@@ -45522,7 +45522,7 @@
         <v>9.15499973297119</v>
       </c>
       <c r="G1557" t="n">
-        <v>8.3565092086792</v>
+        <v>8.35650825500488</v>
       </c>
       <c r="H1557" t="n">
         <v>616000</v>
@@ -45812,7 +45812,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G1567" t="n">
-        <v>8.87223052978516</v>
+        <v>8.87222957611084</v>
       </c>
       <c r="H1567" t="n">
         <v>278612</v>
@@ -46247,7 +46247,7 @@
         <v>9.78999996185303</v>
       </c>
       <c r="G1582" t="n">
-        <v>8.93612384796143</v>
+        <v>8.93612480163574</v>
       </c>
       <c r="H1582" t="n">
         <v>877076</v>
@@ -46305,7 +46305,7 @@
         <v>10.0299997329712</v>
       </c>
       <c r="G1584" t="n">
-        <v>9.15519142150879</v>
+        <v>9.15519237518311</v>
       </c>
       <c r="H1584" t="n">
         <v>631978</v>
@@ -46334,7 +46334,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G1585" t="n">
-        <v>9.03653049468994</v>
+        <v>9.03652954101562</v>
       </c>
       <c r="H1585" t="n">
         <v>526871</v>
@@ -46392,7 +46392,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G1587" t="n">
-        <v>9.01827430725098</v>
+        <v>9.01827526092529</v>
       </c>
       <c r="H1587" t="n">
         <v>377602</v>
@@ -46711,7 +46711,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G1598" t="n">
-        <v>9.29210948944092</v>
+        <v>9.2921085357666</v>
       </c>
       <c r="H1598" t="n">
         <v>415824</v>
@@ -46827,7 +46827,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G1602" t="n">
-        <v>9.01827430725098</v>
+        <v>9.01827526092529</v>
       </c>
       <c r="H1602" t="n">
         <v>292452</v>
@@ -46943,7 +46943,7 @@
         <v>10.1700000762939</v>
       </c>
       <c r="G1606" t="n">
-        <v>9.28298091888428</v>
+        <v>9.28298187255859</v>
       </c>
       <c r="H1606" t="n">
         <v>326344</v>
@@ -47059,7 +47059,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1610" t="n">
-        <v>8.83571815490723</v>
+        <v>8.83571910858154</v>
       </c>
       <c r="H1610" t="n">
         <v>276276</v>
@@ -47117,7 +47117,7 @@
         <v>9.5649995803833</v>
       </c>
       <c r="G1612" t="n">
-        <v>8.73074817657471</v>
+        <v>8.73074913024902</v>
       </c>
       <c r="H1612" t="n">
         <v>318351</v>
@@ -47146,7 +47146,7 @@
         <v>9.6850004196167</v>
       </c>
       <c r="G1613" t="n">
-        <v>8.84028339385986</v>
+        <v>8.84028244018555</v>
       </c>
       <c r="H1613" t="n">
         <v>253429</v>
@@ -47320,7 +47320,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G1619" t="n">
-        <v>8.80833435058594</v>
+        <v>8.80833530426025</v>
       </c>
       <c r="H1619" t="n">
         <v>325458</v>
@@ -47407,7 +47407,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G1622" t="n">
-        <v>8.80833435058594</v>
+        <v>8.80833530426025</v>
       </c>
       <c r="H1622" t="n">
         <v>303708</v>
@@ -47726,7 +47726,7 @@
         <v>9.6850004196167</v>
       </c>
       <c r="G1633" t="n">
-        <v>8.84028339385986</v>
+        <v>8.84028244018555</v>
       </c>
       <c r="H1633" t="n">
         <v>682525</v>
@@ -70555,6 +70555,35 @@
         <v>3606572</v>
       </c>
       <c r="I2420" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2421">
+      <c r="A2421" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2421" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2421" t="n">
+        <v>2.12800002098083</v>
+      </c>
+      <c r="D2421" t="n">
+        <v>2.12800002098083</v>
+      </c>
+      <c r="E2421" t="n">
+        <v>2.03800010681152</v>
+      </c>
+      <c r="F2421" t="n">
+        <v>2.07200002670288</v>
+      </c>
+      <c r="G2421" t="n">
+        <v>2.07200002670288</v>
+      </c>
+      <c r="H2421" t="n">
+        <v>2175619</v>
+      </c>
+      <c r="I2421" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BFF.MI.xlsx
+++ b/data/BFF.MI.xlsx
@@ -456,7 +456,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G3" t="n">
-        <v>2.36908102035522</v>
+        <v>2.36908078193665</v>
       </c>
       <c r="H3" t="n">
         <v>5515143</v>
@@ -514,7 +514,7 @@
         <v>4.29400014877319</v>
       </c>
       <c r="G5" t="n">
-        <v>2.33858251571655</v>
+        <v>2.33858299255371</v>
       </c>
       <c r="H5" t="n">
         <v>392814</v>
@@ -572,7 +572,7 @@
         <v>4.06599998474121</v>
       </c>
       <c r="G7" t="n">
-        <v>2.21441006660461</v>
+        <v>2.21440982818604</v>
       </c>
       <c r="H7" t="n">
         <v>485751</v>
@@ -601,7 +601,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G8" t="n">
-        <v>2.22203469276428</v>
+        <v>2.22203493118286</v>
       </c>
       <c r="H8" t="n">
         <v>362054</v>
@@ -659,7 +659,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G10" t="n">
-        <v>2.2274808883667</v>
+        <v>2.22748112678528</v>
       </c>
       <c r="H10" t="n">
         <v>428382</v>
@@ -688,7 +688,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G11" t="n">
-        <v>2.26560425758362</v>
+        <v>2.26560378074646</v>
       </c>
       <c r="H11" t="n">
         <v>791191</v>
@@ -775,7 +775,7 @@
         <v>4.2979998588562</v>
       </c>
       <c r="G14" t="n">
-        <v>2.34076118469238</v>
+        <v>2.3407609462738</v>
       </c>
       <c r="H14" t="n">
         <v>134855</v>
@@ -804,7 +804,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G15" t="n">
-        <v>2.36363506317139</v>
+        <v>2.36363482475281</v>
       </c>
       <c r="H15" t="n">
         <v>270123</v>
@@ -833,7 +833,7 @@
         <v>4.36199998855591</v>
       </c>
       <c r="G16" t="n">
-        <v>2.37561678886414</v>
+        <v>2.37561655044556</v>
       </c>
       <c r="H16" t="n">
         <v>470779</v>
@@ -862,7 +862,7 @@
         <v>4.44600009918213</v>
       </c>
       <c r="G17" t="n">
-        <v>2.42136454582214</v>
+        <v>2.42136406898499</v>
       </c>
       <c r="H17" t="n">
         <v>136910</v>
@@ -891,7 +891,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G18" t="n">
-        <v>2.40720462799072</v>
+        <v>2.40720438957214</v>
       </c>
       <c r="H18" t="n">
         <v>216629</v>
@@ -920,7 +920,7 @@
         <v>4.4520001411438</v>
       </c>
       <c r="G19" t="n">
-        <v>2.42463231086731</v>
+        <v>2.42463207244873</v>
       </c>
       <c r="H19" t="n">
         <v>339492</v>
@@ -949,7 +949,7 @@
         <v>4.48600006103516</v>
       </c>
       <c r="G20" t="n">
-        <v>2.44314908981323</v>
+        <v>2.44314885139465</v>
       </c>
       <c r="H20" t="n">
         <v>218126</v>
@@ -978,7 +978,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G21" t="n">
-        <v>2.54335856437683</v>
+        <v>2.54335832595825</v>
       </c>
       <c r="H21" t="n">
         <v>983059</v>
@@ -1036,7 +1036,7 @@
         <v>4.83599996566772</v>
       </c>
       <c r="G23" t="n">
-        <v>2.63376450538635</v>
+        <v>2.63376474380493</v>
       </c>
       <c r="H23" t="n">
         <v>2581507</v>
@@ -1065,7 +1065,7 @@
         <v>4.85400009155273</v>
       </c>
       <c r="G24" t="n">
-        <v>2.64356780052185</v>
+        <v>2.64356827735901</v>
       </c>
       <c r="H24" t="n">
         <v>436457</v>
@@ -1123,7 +1123,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G26" t="n">
-        <v>2.63049697875977</v>
+        <v>2.63049650192261</v>
       </c>
       <c r="H26" t="n">
         <v>546498</v>
@@ -1181,7 +1181,7 @@
         <v>4.64200019836426</v>
       </c>
       <c r="G28" t="n">
-        <v>2.52810883522034</v>
+        <v>2.5281093120575</v>
       </c>
       <c r="H28" t="n">
         <v>712797</v>
@@ -1268,7 +1268,7 @@
         <v>4.83799982070923</v>
       </c>
       <c r="G31" t="n">
-        <v>2.63485383987427</v>
+        <v>2.63485336303711</v>
       </c>
       <c r="H31" t="n">
         <v>253749</v>
@@ -1297,7 +1297,7 @@
         <v>4.77600002288818</v>
       </c>
       <c r="G32" t="n">
-        <v>2.60108780860901</v>
+        <v>2.60108757019043</v>
       </c>
       <c r="H32" t="n">
         <v>224481</v>
@@ -1326,7 +1326,7 @@
         <v>4.92399978637695</v>
       </c>
       <c r="G33" t="n">
-        <v>2.68169069290161</v>
+        <v>2.68169045448303</v>
       </c>
       <c r="H33" t="n">
         <v>289211</v>
@@ -1355,7 +1355,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G34" t="n">
-        <v>2.66317415237427</v>
+        <v>2.66317391395569</v>
       </c>
       <c r="H34" t="n">
         <v>156895</v>
@@ -1384,7 +1384,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G35" t="n">
-        <v>2.6849582195282</v>
+        <v>2.68495869636536</v>
       </c>
       <c r="H35" t="n">
         <v>134645</v>
@@ -1413,7 +1413,7 @@
         <v>4.89799976348877</v>
       </c>
       <c r="G36" t="n">
-        <v>2.66753101348877</v>
+        <v>2.66753053665161</v>
       </c>
       <c r="H36" t="n">
         <v>234988</v>
@@ -1442,7 +1442,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G37" t="n">
-        <v>2.6849582195282</v>
+        <v>2.68495869636536</v>
       </c>
       <c r="H37" t="n">
         <v>213166</v>
@@ -1471,7 +1471,7 @@
         <v>4.94799995422363</v>
       </c>
       <c r="G38" t="n">
-        <v>2.69476127624512</v>
+        <v>2.6947615146637</v>
       </c>
       <c r="H38" t="n">
         <v>178328</v>
@@ -1500,7 +1500,7 @@
         <v>4.92199993133545</v>
       </c>
       <c r="G39" t="n">
-        <v>2.6806013584137</v>
+        <v>2.68060159683228</v>
       </c>
       <c r="H39" t="n">
         <v>31918</v>
@@ -1558,7 +1558,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G41" t="n">
-        <v>2.64138913154602</v>
+        <v>2.64138889312744</v>
       </c>
       <c r="H41" t="n">
         <v>200735</v>
@@ -1587,7 +1587,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G42" t="n">
-        <v>2.65772747993469</v>
+        <v>2.65772795677185</v>
       </c>
       <c r="H42" t="n">
         <v>195614</v>
@@ -1645,7 +1645,7 @@
         <v>4.87599992752075</v>
       </c>
       <c r="G44" t="n">
-        <v>2.65554928779602</v>
+        <v>2.6555495262146</v>
       </c>
       <c r="H44" t="n">
         <v>74237</v>
@@ -1703,7 +1703,7 @@
         <v>4.89599990844727</v>
       </c>
       <c r="G46" t="n">
-        <v>2.66644191741943</v>
+        <v>2.66644144058228</v>
       </c>
       <c r="H46" t="n">
         <v>263706</v>
@@ -1732,7 +1732,7 @@
         <v>5.06500005722046</v>
       </c>
       <c r="G47" t="n">
-        <v>2.75848197937012</v>
+        <v>2.7584822177887</v>
       </c>
       <c r="H47" t="n">
         <v>666612</v>
@@ -1761,7 +1761,7 @@
         <v>5.07499980926514</v>
       </c>
       <c r="G48" t="n">
-        <v>2.76392769813538</v>
+        <v>2.76392817497253</v>
       </c>
       <c r="H48" t="n">
         <v>196923</v>
@@ -1790,7 +1790,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G49" t="n">
-        <v>2.72852802276611</v>
+        <v>2.72852754592896</v>
       </c>
       <c r="H49" t="n">
         <v>1316892</v>
@@ -1848,7 +1848,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G51" t="n">
-        <v>2.81022071838379</v>
+        <v>2.81022024154663</v>
       </c>
       <c r="H51" t="n">
         <v>347203</v>
@@ -1906,7 +1906,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G53" t="n">
-        <v>2.80749773979187</v>
+        <v>2.80749750137329</v>
       </c>
       <c r="H53" t="n">
         <v>204010</v>
@@ -2051,7 +2051,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G58" t="n">
-        <v>2.81022071838379</v>
+        <v>2.81022024154663</v>
       </c>
       <c r="H58" t="n">
         <v>260985</v>
@@ -2109,7 +2109,7 @@
         <v>5.09499979019165</v>
       </c>
       <c r="G60" t="n">
-        <v>2.77482032775879</v>
+        <v>2.77482008934021</v>
       </c>
       <c r="H60" t="n">
         <v>176285</v>
@@ -2138,7 +2138,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G61" t="n">
-        <v>2.7993278503418</v>
+        <v>2.79932808876038</v>
       </c>
       <c r="H61" t="n">
         <v>158805</v>
@@ -2167,7 +2167,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G62" t="n">
-        <v>2.7829897403717</v>
+        <v>2.78298997879028</v>
       </c>
       <c r="H62" t="n">
         <v>49073</v>
@@ -2196,7 +2196,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G63" t="n">
-        <v>2.7993278503418</v>
+        <v>2.79932808876038</v>
       </c>
       <c r="H63" t="n">
         <v>150641</v>
@@ -2225,7 +2225,7 @@
         <v>5.16499996185303</v>
       </c>
       <c r="G64" t="n">
-        <v>2.81294322013855</v>
+        <v>2.81294369697571</v>
       </c>
       <c r="H64" t="n">
         <v>39984</v>
@@ -2254,7 +2254,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G65" t="n">
-        <v>2.79388189315796</v>
+        <v>2.79388213157654</v>
       </c>
       <c r="H65" t="n">
         <v>62383</v>
@@ -2283,7 +2283,7 @@
         <v>5.07499980926514</v>
       </c>
       <c r="G66" t="n">
-        <v>2.76392769813538</v>
+        <v>2.76392817497253</v>
       </c>
       <c r="H66" t="n">
         <v>89307</v>
@@ -2312,7 +2312,7 @@
         <v>5.125</v>
       </c>
       <c r="G67" t="n">
-        <v>2.79115891456604</v>
+        <v>2.79115867614746</v>
       </c>
       <c r="H67" t="n">
         <v>95184</v>
@@ -2370,7 +2370,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G69" t="n">
-        <v>2.78843569755554</v>
+        <v>2.78843545913696</v>
       </c>
       <c r="H69" t="n">
         <v>225985</v>
@@ -2399,7 +2399,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G70" t="n">
-        <v>2.80477476119995</v>
+        <v>2.80477452278137</v>
       </c>
       <c r="H70" t="n">
         <v>110557</v>
@@ -2428,7 +2428,7 @@
         <v>5.07499980926514</v>
       </c>
       <c r="G71" t="n">
-        <v>2.76392769813538</v>
+        <v>2.76392817497253</v>
       </c>
       <c r="H71" t="n">
         <v>212116</v>
@@ -2457,7 +2457,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G72" t="n">
-        <v>2.78026628494263</v>
+        <v>2.78026652336121</v>
       </c>
       <c r="H72" t="n">
         <v>78741</v>
@@ -2486,7 +2486,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G73" t="n">
-        <v>2.78026628494263</v>
+        <v>2.78026652336121</v>
       </c>
       <c r="H73" t="n">
         <v>162459</v>
@@ -2515,7 +2515,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G74" t="n">
-        <v>2.78843569755554</v>
+        <v>2.78843545913696</v>
       </c>
       <c r="H74" t="n">
         <v>163329</v>
@@ -2544,7 +2544,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G75" t="n">
-        <v>2.80477476119995</v>
+        <v>2.80477452278137</v>
       </c>
       <c r="H75" t="n">
         <v>69294</v>
@@ -2573,7 +2573,7 @@
         <v>5.125</v>
       </c>
       <c r="G76" t="n">
-        <v>2.79115891456604</v>
+        <v>2.79115867614746</v>
       </c>
       <c r="H76" t="n">
         <v>179479</v>
@@ -2602,7 +2602,7 @@
         <v>5.17500019073486</v>
       </c>
       <c r="G77" t="n">
-        <v>2.81838965415955</v>
+        <v>2.81838917732239</v>
       </c>
       <c r="H77" t="n">
         <v>63737</v>
@@ -2631,7 +2631,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G78" t="n">
-        <v>2.78843569755554</v>
+        <v>2.78843545913696</v>
       </c>
       <c r="H78" t="n">
         <v>136329</v>
@@ -2718,7 +2718,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G81" t="n">
-        <v>2.80477476119995</v>
+        <v>2.80477452278137</v>
       </c>
       <c r="H81" t="n">
         <v>169020</v>
@@ -2747,7 +2747,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G82" t="n">
-        <v>2.80477476119995</v>
+        <v>2.80477452278137</v>
       </c>
       <c r="H82" t="n">
         <v>173934</v>
@@ -2776,7 +2776,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G83" t="n">
-        <v>2.80477476119995</v>
+        <v>2.80477452278137</v>
       </c>
       <c r="H83" t="n">
         <v>134385</v>
@@ -2805,7 +2805,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G84" t="n">
-        <v>2.7993278503418</v>
+        <v>2.79932808876038</v>
       </c>
       <c r="H84" t="n">
         <v>92528</v>
@@ -2834,7 +2834,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G85" t="n">
-        <v>2.80749773979187</v>
+        <v>2.80749750137329</v>
       </c>
       <c r="H85" t="n">
         <v>646041</v>
@@ -2863,7 +2863,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G86" t="n">
-        <v>2.80477476119995</v>
+        <v>2.80477452278137</v>
       </c>
       <c r="H86" t="n">
         <v>338706</v>
@@ -2892,7 +2892,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G87" t="n">
-        <v>2.79388189315796</v>
+        <v>2.79388213157654</v>
       </c>
       <c r="H87" t="n">
         <v>216904</v>
@@ -2921,7 +2921,7 @@
         <v>5.13500022888184</v>
       </c>
       <c r="G88" t="n">
-        <v>2.79660487174988</v>
+        <v>2.79660511016846</v>
       </c>
       <c r="H88" t="n">
         <v>115656</v>
@@ -2950,7 +2950,7 @@
         <v>5.08500003814697</v>
       </c>
       <c r="G89" t="n">
-        <v>2.76937413215637</v>
+        <v>2.76937437057495</v>
       </c>
       <c r="H89" t="n">
         <v>158274</v>
@@ -3008,7 +3008,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G91" t="n">
-        <v>2.83745121955872</v>
+        <v>2.83745169639587</v>
       </c>
       <c r="H91" t="n">
         <v>178885</v>
@@ -3066,7 +3066,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G93" t="n">
-        <v>2.80749773979187</v>
+        <v>2.80749750137329</v>
       </c>
       <c r="H93" t="n">
         <v>91566</v>
@@ -3095,7 +3095,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G94" t="n">
-        <v>2.80749773979187</v>
+        <v>2.80749750137329</v>
       </c>
       <c r="H94" t="n">
         <v>86354</v>
@@ -3124,7 +3124,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G95" t="n">
-        <v>2.7993278503418</v>
+        <v>2.79932808876038</v>
       </c>
       <c r="H95" t="n">
         <v>110787</v>
@@ -3153,7 +3153,7 @@
         <v>5.16499996185303</v>
       </c>
       <c r="G96" t="n">
-        <v>2.81294322013855</v>
+        <v>2.81294369697571</v>
       </c>
       <c r="H96" t="n">
         <v>55521</v>
@@ -3211,7 +3211,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G98" t="n">
-        <v>2.7993278503418</v>
+        <v>2.79932808876038</v>
       </c>
       <c r="H98" t="n">
         <v>73538</v>
@@ -3385,7 +3385,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G104" t="n">
-        <v>2.81022071838379</v>
+        <v>2.81022024154663</v>
       </c>
       <c r="H104" t="n">
         <v>322247</v>
@@ -3443,7 +3443,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G106" t="n">
-        <v>2.78026628494263</v>
+        <v>2.78026652336121</v>
       </c>
       <c r="H106" t="n">
         <v>70314</v>
@@ -3472,7 +3472,7 @@
         <v>5.08500003814697</v>
       </c>
       <c r="G107" t="n">
-        <v>2.76937413215637</v>
+        <v>2.76937437057495</v>
       </c>
       <c r="H107" t="n">
         <v>55988</v>
@@ -3501,7 +3501,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G108" t="n">
-        <v>2.76665091514587</v>
+        <v>2.76665115356445</v>
       </c>
       <c r="H108" t="n">
         <v>67296</v>
@@ -3530,7 +3530,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G109" t="n">
-        <v>2.78843569755554</v>
+        <v>2.78843545913696</v>
       </c>
       <c r="H109" t="n">
         <v>78441</v>
@@ -3559,7 +3559,7 @@
         <v>5.16499996185303</v>
       </c>
       <c r="G110" t="n">
-        <v>2.81294322013855</v>
+        <v>2.81294369697571</v>
       </c>
       <c r="H110" t="n">
         <v>155443</v>
@@ -3617,7 +3617,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G112" t="n">
-        <v>2.88102054595947</v>
+        <v>2.88102030754089</v>
       </c>
       <c r="H112" t="n">
         <v>159939</v>
@@ -3646,7 +3646,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G113" t="n">
-        <v>2.8646821975708</v>
+        <v>2.86468195915222</v>
       </c>
       <c r="H113" t="n">
         <v>458239</v>
@@ -3675,7 +3675,7 @@
         <v>5.50500011444092</v>
       </c>
       <c r="G114" t="n">
-        <v>2.99811339378357</v>
+        <v>2.99811315536499</v>
       </c>
       <c r="H114" t="n">
         <v>826293</v>
@@ -3704,7 +3704,7 @@
         <v>5.49499988555908</v>
       </c>
       <c r="G115" t="n">
-        <v>2.99266672134399</v>
+        <v>2.99266695976257</v>
       </c>
       <c r="H115" t="n">
         <v>356186</v>
@@ -3733,7 +3733,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G116" t="n">
-        <v>3.02806663513184</v>
+        <v>3.02806735038757</v>
       </c>
       <c r="H116" t="n">
         <v>223092</v>
@@ -3762,7 +3762,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G117" t="n">
-        <v>3.03895902633667</v>
+        <v>3.03895926475525</v>
       </c>
       <c r="H117" t="n">
         <v>490409</v>
@@ -3791,7 +3791,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G118" t="n">
-        <v>3.00628209114075</v>
+        <v>3.00628232955933</v>
       </c>
       <c r="H118" t="n">
         <v>307618</v>
@@ -3849,7 +3849,7 @@
         <v>5.67500019073486</v>
       </c>
       <c r="G120" t="n">
-        <v>3.0906982421875</v>
+        <v>3.09069800376892</v>
       </c>
       <c r="H120" t="n">
         <v>228201</v>
@@ -3878,7 +3878,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G121" t="n">
-        <v>3.24046754837036</v>
+        <v>3.2404670715332</v>
       </c>
       <c r="H121" t="n">
         <v>464316</v>
@@ -3936,7 +3936,7 @@
         <v>5.75</v>
       </c>
       <c r="G123" t="n">
-        <v>3.13154411315918</v>
+        <v>3.1315438747406</v>
       </c>
       <c r="H123" t="n">
         <v>633225</v>
@@ -3965,7 +3965,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G124" t="n">
-        <v>3.19689798355103</v>
+        <v>3.1968982219696</v>
       </c>
       <c r="H124" t="n">
         <v>236136</v>
@@ -3994,7 +3994,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G125" t="n">
-        <v>3.12609767913818</v>
+        <v>3.12609791755676</v>
       </c>
       <c r="H125" t="n">
         <v>258170</v>
@@ -4023,7 +4023,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G126" t="n">
-        <v>3.07708263397217</v>
+        <v>3.07708239555359</v>
       </c>
       <c r="H126" t="n">
         <v>291514</v>
@@ -4081,7 +4081,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G128" t="n">
-        <v>3.10431289672852</v>
+        <v>3.10431313514709</v>
       </c>
       <c r="H128" t="n">
         <v>185479</v>
@@ -4168,7 +4168,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G131" t="n">
-        <v>3.20234394073486</v>
+        <v>3.20234441757202</v>
       </c>
       <c r="H131" t="n">
         <v>262047</v>
@@ -4197,7 +4197,7 @@
         <v>5.875</v>
       </c>
       <c r="G132" t="n">
-        <v>3.19962072372437</v>
+        <v>3.19962120056152</v>
       </c>
       <c r="H132" t="n">
         <v>107432</v>
@@ -4226,7 +4226,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G133" t="n">
-        <v>3.32215905189514</v>
+        <v>3.32215929031372</v>
       </c>
       <c r="H133" t="n">
         <v>490719</v>
@@ -4255,7 +4255,7 @@
         <v>6.125</v>
       </c>
       <c r="G134" t="n">
-        <v>3.33577537536621</v>
+        <v>3.33577513694763</v>
       </c>
       <c r="H134" t="n">
         <v>653279</v>
@@ -4284,7 +4284,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G135" t="n">
-        <v>3.30582141876221</v>
+        <v>3.30582165718079</v>
       </c>
       <c r="H135" t="n">
         <v>362617</v>
@@ -4313,7 +4313,7 @@
         <v>6.11499977111816</v>
       </c>
       <c r="G136" t="n">
-        <v>3.33032870292664</v>
+        <v>3.33032846450806</v>
       </c>
       <c r="H136" t="n">
         <v>223437</v>
@@ -4371,7 +4371,7 @@
         <v>6</v>
       </c>
       <c r="G138" t="n">
-        <v>3.26769828796387</v>
+        <v>3.26769804954529</v>
       </c>
       <c r="H138" t="n">
         <v>214993</v>
@@ -4400,7 +4400,7 @@
         <v>6.11499977111816</v>
       </c>
       <c r="G139" t="n">
-        <v>3.33032870292664</v>
+        <v>3.33032846450806</v>
       </c>
       <c r="H139" t="n">
         <v>151537</v>
@@ -4429,7 +4429,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G140" t="n">
-        <v>3.33305191993713</v>
+        <v>3.33305239677429</v>
       </c>
       <c r="H140" t="n">
         <v>196694</v>
@@ -4458,7 +4458,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G141" t="n">
-        <v>3.32215905189514</v>
+        <v>3.32215929031372</v>
       </c>
       <c r="H141" t="n">
         <v>185465</v>
@@ -4487,7 +4487,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G142" t="n">
-        <v>3.34939074516296</v>
+        <v>3.34939050674438</v>
       </c>
       <c r="H142" t="n">
         <v>178387</v>
@@ -4545,7 +4545,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G144" t="n">
-        <v>3.38751339912415</v>
+        <v>3.3875138759613</v>
       </c>
       <c r="H144" t="n">
         <v>271554</v>
@@ -4574,7 +4574,7 @@
         <v>6.25</v>
       </c>
       <c r="G145" t="n">
-        <v>3.40385174751282</v>
+        <v>3.40385222434998</v>
       </c>
       <c r="H145" t="n">
         <v>169413</v>
@@ -4632,7 +4632,7 @@
         <v>6.11499977111816</v>
       </c>
       <c r="G147" t="n">
-        <v>3.33032870292664</v>
+        <v>3.33032846450806</v>
       </c>
       <c r="H147" t="n">
         <v>211124</v>
@@ -4661,7 +4661,7 @@
         <v>6.02500009536743</v>
       </c>
       <c r="G148" t="n">
-        <v>3.28131341934204</v>
+        <v>3.28131365776062</v>
       </c>
       <c r="H148" t="n">
         <v>424488</v>
@@ -4690,7 +4690,7 @@
         <v>6.00500011444092</v>
       </c>
       <c r="G149" t="n">
-        <v>3.27042174339294</v>
+        <v>3.27042198181152</v>
       </c>
       <c r="H149" t="n">
         <v>352526</v>
@@ -4719,7 +4719,7 @@
         <v>6.09499979019165</v>
       </c>
       <c r="G150" t="n">
-        <v>3.3194363117218</v>
+        <v>3.31943655014038</v>
       </c>
       <c r="H150" t="n">
         <v>360242</v>
@@ -4748,7 +4748,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G151" t="n">
-        <v>3.28403663635254</v>
+        <v>3.28403687477112</v>
       </c>
       <c r="H151" t="n">
         <v>1050651</v>
@@ -4806,7 +4806,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G153" t="n">
-        <v>3.2459135055542</v>
+        <v>3.24591326713562</v>
       </c>
       <c r="H153" t="n">
         <v>259079</v>
@@ -4835,7 +4835,7 @@
         <v>5.92999982833862</v>
       </c>
       <c r="G154" t="n">
-        <v>3.22957491874695</v>
+        <v>3.22957468032837</v>
       </c>
       <c r="H154" t="n">
         <v>449614</v>
@@ -4893,7 +4893,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G156" t="n">
-        <v>3.27314400672913</v>
+        <v>3.27314448356628</v>
       </c>
       <c r="H156" t="n">
         <v>248030</v>
@@ -4922,7 +4922,7 @@
         <v>6</v>
       </c>
       <c r="G157" t="n">
-        <v>3.26769828796387</v>
+        <v>3.26769804954529</v>
       </c>
       <c r="H157" t="n">
         <v>312140</v>
@@ -4951,7 +4951,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G158" t="n">
-        <v>3.3276059627533</v>
+        <v>3.32760620117188</v>
       </c>
       <c r="H158" t="n">
         <v>187242</v>
@@ -4980,7 +4980,7 @@
         <v>6.125</v>
       </c>
       <c r="G159" t="n">
-        <v>3.33577537536621</v>
+        <v>3.33577513694763</v>
       </c>
       <c r="H159" t="n">
         <v>172302</v>
@@ -5009,7 +5009,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G160" t="n">
-        <v>3.36028337478638</v>
+        <v>3.36028289794922</v>
       </c>
       <c r="H160" t="n">
         <v>149678</v>
@@ -5067,7 +5067,7 @@
         <v>6.40999984741211</v>
       </c>
       <c r="G162" t="n">
-        <v>3.49099135398865</v>
+        <v>3.49099087715149</v>
       </c>
       <c r="H162" t="n">
         <v>474666</v>
@@ -5096,7 +5096,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G163" t="n">
-        <v>3.51277542114258</v>
+        <v>3.512775182724</v>
       </c>
       <c r="H163" t="n">
         <v>427038</v>
@@ -5125,7 +5125,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G164" t="n">
-        <v>3.47465229034424</v>
+        <v>3.4746527671814</v>
       </c>
       <c r="H164" t="n">
         <v>234446</v>
@@ -5154,7 +5154,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G165" t="n">
-        <v>3.45831346511841</v>
+        <v>3.45831394195557</v>
       </c>
       <c r="H165" t="n">
         <v>177233</v>
@@ -5183,7 +5183,7 @@
         <v>6.41499996185303</v>
       </c>
       <c r="G166" t="n">
-        <v>3.49371409416199</v>
+        <v>3.49371337890625</v>
       </c>
       <c r="H166" t="n">
         <v>319302</v>
@@ -5212,7 +5212,7 @@
         <v>6.45499992370605</v>
       </c>
       <c r="G167" t="n">
-        <v>3.51549816131592</v>
+        <v>3.51549863815308</v>
       </c>
       <c r="H167" t="n">
         <v>1366720</v>
@@ -5241,7 +5241,7 @@
         <v>6.36499977111816</v>
       </c>
       <c r="G168" t="n">
-        <v>3.46648263931274</v>
+        <v>3.4664831161499</v>
       </c>
       <c r="H168" t="n">
         <v>241433</v>
@@ -5328,7 +5328,7 @@
         <v>6.40999984741211</v>
       </c>
       <c r="G171" t="n">
-        <v>3.49099135398865</v>
+        <v>3.49099087715149</v>
       </c>
       <c r="H171" t="n">
         <v>199264</v>
@@ -5357,7 +5357,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G172" t="n">
-        <v>3.583575963974</v>
+        <v>3.58357548713684</v>
       </c>
       <c r="H172" t="n">
         <v>262965</v>
@@ -5386,7 +5386,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G173" t="n">
-        <v>3.56179070472717</v>
+        <v>3.56179118156433</v>
       </c>
       <c r="H173" t="n">
         <v>238411</v>
@@ -5444,7 +5444,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G175" t="n">
-        <v>3.59446740150452</v>
+        <v>3.59446787834167</v>
       </c>
       <c r="H175" t="n">
         <v>269404</v>
@@ -5473,7 +5473,7 @@
         <v>6.53000020980835</v>
       </c>
       <c r="G176" t="n">
-        <v>3.55634522438049</v>
+        <v>3.55634498596191</v>
       </c>
       <c r="H176" t="n">
         <v>106003</v>
@@ -5502,7 +5502,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G177" t="n">
-        <v>3.52366781234741</v>
+        <v>3.52366757392883</v>
       </c>
       <c r="H177" t="n">
         <v>239018</v>
@@ -5531,7 +5531,7 @@
         <v>6.53499984741211</v>
       </c>
       <c r="G178" t="n">
-        <v>3.55906772613525</v>
+        <v>3.5590672492981</v>
       </c>
       <c r="H178" t="n">
         <v>1769120</v>
@@ -5589,7 +5589,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G180" t="n">
-        <v>3.6108067035675</v>
+        <v>3.61080598831177</v>
       </c>
       <c r="H180" t="n">
         <v>190579</v>
@@ -5647,7 +5647,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G182" t="n">
-        <v>3.47465229034424</v>
+        <v>3.4746527671814</v>
       </c>
       <c r="H182" t="n">
         <v>177623</v>
@@ -5676,7 +5676,7 @@
         <v>6.25</v>
       </c>
       <c r="G183" t="n">
-        <v>3.40385174751282</v>
+        <v>3.40385222434998</v>
       </c>
       <c r="H183" t="n">
         <v>163948</v>
@@ -5705,7 +5705,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G184" t="n">
-        <v>3.44742131233215</v>
+        <v>3.44742107391357</v>
       </c>
       <c r="H184" t="n">
         <v>187122</v>
@@ -5792,7 +5792,7 @@
         <v>6.41499996185303</v>
       </c>
       <c r="G187" t="n">
-        <v>3.49371409416199</v>
+        <v>3.49371337890625</v>
       </c>
       <c r="H187" t="n">
         <v>155738</v>
@@ -5821,7 +5821,7 @@
         <v>6.53499984741211</v>
       </c>
       <c r="G188" t="n">
-        <v>3.55906772613525</v>
+        <v>3.5590672492981</v>
       </c>
       <c r="H188" t="n">
         <v>188172</v>
@@ -5879,7 +5879,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G190" t="n">
-        <v>3.5454523563385</v>
+        <v>3.54545283317566</v>
       </c>
       <c r="H190" t="n">
         <v>100540</v>
@@ -5966,7 +5966,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G193" t="n">
-        <v>3.56179070472717</v>
+        <v>3.56179118156433</v>
       </c>
       <c r="H193" t="n">
         <v>366351</v>
@@ -5995,7 +5995,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G194" t="n">
-        <v>3.47465229034424</v>
+        <v>3.4746527671814</v>
       </c>
       <c r="H194" t="n">
         <v>362021</v>
@@ -6024,7 +6024,7 @@
         <v>6.46500015258789</v>
       </c>
       <c r="G195" t="n">
-        <v>3.52094507217407</v>
+        <v>3.52094483375549</v>
       </c>
       <c r="H195" t="n">
         <v>418341</v>
@@ -6053,7 +6053,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G196" t="n">
-        <v>3.52911376953125</v>
+        <v>3.52911424636841</v>
       </c>
       <c r="H196" t="n">
         <v>260163</v>
@@ -6111,7 +6111,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G198" t="n">
-        <v>3.5454523563385</v>
+        <v>3.54545283317566</v>
       </c>
       <c r="H198" t="n">
         <v>218115</v>
@@ -6140,7 +6140,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G199" t="n">
-        <v>3.5454523563385</v>
+        <v>3.54545283317566</v>
       </c>
       <c r="H199" t="n">
         <v>236976</v>
@@ -6169,7 +6169,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G200" t="n">
-        <v>3.5454523563385</v>
+        <v>3.54545283317566</v>
       </c>
       <c r="H200" t="n">
         <v>242488</v>
@@ -6198,7 +6198,7 @@
         <v>6.57499980926514</v>
       </c>
       <c r="G201" t="n">
-        <v>3.58085227012634</v>
+        <v>3.58085250854492</v>
       </c>
       <c r="H201" t="n">
         <v>324190</v>
@@ -6256,7 +6256,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G203" t="n">
-        <v>3.59446740150452</v>
+        <v>3.59446787834167</v>
       </c>
       <c r="H203" t="n">
         <v>289318</v>
@@ -6285,7 +6285,7 @@
         <v>6.53000020980835</v>
       </c>
       <c r="G204" t="n">
-        <v>3.55634522438049</v>
+        <v>3.55634498596191</v>
       </c>
       <c r="H204" t="n">
         <v>263917</v>
@@ -6314,7 +6314,7 @@
         <v>6.59499979019165</v>
       </c>
       <c r="G205" t="n">
-        <v>3.59174513816833</v>
+        <v>3.59174489974976</v>
       </c>
       <c r="H205" t="n">
         <v>305878</v>
@@ -6372,7 +6372,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G207" t="n">
-        <v>3.5454523563385</v>
+        <v>3.54545283317566</v>
       </c>
       <c r="H207" t="n">
         <v>240046</v>
@@ -6401,7 +6401,7 @@
         <v>6.4850001335144</v>
       </c>
       <c r="G208" t="n">
-        <v>3.53183698654175</v>
+        <v>3.53183674812317</v>
       </c>
       <c r="H208" t="n">
         <v>191731</v>
@@ -6430,7 +6430,7 @@
         <v>6.41499996185303</v>
       </c>
       <c r="G209" t="n">
-        <v>3.49371409416199</v>
+        <v>3.49371337890625</v>
       </c>
       <c r="H209" t="n">
         <v>424467</v>
@@ -6459,7 +6459,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G210" t="n">
-        <v>3.29492950439453</v>
+        <v>3.29492902755737</v>
       </c>
       <c r="H210" t="n">
         <v>1379424</v>
@@ -6488,7 +6488,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G211" t="n">
-        <v>3.28403663635254</v>
+        <v>3.28403687477112</v>
       </c>
       <c r="H211" t="n">
         <v>569842</v>
@@ -6517,7 +6517,7 @@
         <v>5.91499996185303</v>
       </c>
       <c r="G212" t="n">
-        <v>3.22140574455261</v>
+        <v>3.22140526771545</v>
       </c>
       <c r="H212" t="n">
         <v>551509</v>
@@ -6546,7 +6546,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G213" t="n">
-        <v>3.27859020233154</v>
+        <v>3.2785906791687</v>
       </c>
       <c r="H213" t="n">
         <v>502251</v>
@@ -6604,7 +6604,7 @@
         <v>5.92999982833862</v>
       </c>
       <c r="G215" t="n">
-        <v>3.22957491874695</v>
+        <v>3.22957468032837</v>
       </c>
       <c r="H215" t="n">
         <v>595831</v>
@@ -6633,7 +6633,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G216" t="n">
-        <v>3.16966700553894</v>
+        <v>3.1696674823761</v>
       </c>
       <c r="H216" t="n">
         <v>367575</v>
@@ -6720,7 +6720,7 @@
         <v>6</v>
       </c>
       <c r="G219" t="n">
-        <v>3.26769828796387</v>
+        <v>3.26769804954529</v>
       </c>
       <c r="H219" t="n">
         <v>193373</v>
@@ -6778,7 +6778,7 @@
         <v>6.14499998092651</v>
       </c>
       <c r="G221" t="n">
-        <v>3.34666776657104</v>
+        <v>3.34666728973389</v>
       </c>
       <c r="H221" t="n">
         <v>229142</v>
@@ -6865,7 +6865,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G224" t="n">
-        <v>3.1805591583252</v>
+        <v>3.18055939674377</v>
       </c>
       <c r="H224" t="n">
         <v>610892</v>
@@ -6894,7 +6894,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G225" t="n">
-        <v>3.16966700553894</v>
+        <v>3.1696674823761</v>
       </c>
       <c r="H225" t="n">
         <v>433654</v>
@@ -6923,7 +6923,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G226" t="n">
-        <v>3.16966700553894</v>
+        <v>3.1696674823761</v>
       </c>
       <c r="H226" t="n">
         <v>403818</v>
@@ -6981,7 +6981,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G228" t="n">
-        <v>3.18600535392761</v>
+        <v>3.18600559234619</v>
       </c>
       <c r="H228" t="n">
         <v>292988</v>
@@ -7010,7 +7010,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G229" t="n">
-        <v>3.18600535392761</v>
+        <v>3.18600559234619</v>
       </c>
       <c r="H229" t="n">
         <v>343071</v>
@@ -7039,7 +7039,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G230" t="n">
-        <v>3.17511343955994</v>
+        <v>3.17511296272278</v>
       </c>
       <c r="H230" t="n">
         <v>422499</v>
@@ -7068,7 +7068,7 @@
         <v>5.78499984741211</v>
       </c>
       <c r="G231" t="n">
-        <v>3.15060520172119</v>
+        <v>3.15060567855835</v>
       </c>
       <c r="H231" t="n">
         <v>350773</v>
@@ -7126,7 +7126,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G233" t="n">
-        <v>3.15332913398743</v>
+        <v>3.15332865715027</v>
       </c>
       <c r="H233" t="n">
         <v>666571</v>
@@ -7155,7 +7155,7 @@
         <v>5.88500022888184</v>
       </c>
       <c r="G234" t="n">
-        <v>3.20506763458252</v>
+        <v>3.20506691932678</v>
       </c>
       <c r="H234" t="n">
         <v>425600</v>
@@ -7271,7 +7271,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G238" t="n">
-        <v>3.24046754837036</v>
+        <v>3.2404670715332</v>
       </c>
       <c r="H238" t="n">
         <v>309233</v>
@@ -7300,7 +7300,7 @@
         <v>5.88500022888184</v>
       </c>
       <c r="G239" t="n">
-        <v>3.20506763458252</v>
+        <v>3.20506691932678</v>
       </c>
       <c r="H239" t="n">
         <v>420138</v>
@@ -7329,7 +7329,7 @@
         <v>5.91499996185303</v>
       </c>
       <c r="G240" t="n">
-        <v>3.22140574455261</v>
+        <v>3.22140526771545</v>
       </c>
       <c r="H240" t="n">
         <v>647032</v>
@@ -7358,7 +7358,7 @@
         <v>5.88500022888184</v>
       </c>
       <c r="G241" t="n">
-        <v>3.20506763458252</v>
+        <v>3.20506691932678</v>
       </c>
       <c r="H241" t="n">
         <v>352034</v>
@@ -7387,7 +7387,7 @@
         <v>5.75</v>
       </c>
       <c r="G242" t="n">
-        <v>3.13154411315918</v>
+        <v>3.1315438747406</v>
       </c>
       <c r="H242" t="n">
         <v>1209727</v>
@@ -7416,7 +7416,7 @@
         <v>5.7350001335144</v>
       </c>
       <c r="G243" t="n">
-        <v>3.12337493896484</v>
+        <v>3.12337470054626</v>
       </c>
       <c r="H243" t="n">
         <v>509155</v>
@@ -7445,7 +7445,7 @@
         <v>5.71500015258789</v>
       </c>
       <c r="G244" t="n">
-        <v>3.11248278617859</v>
+        <v>3.11248254776001</v>
       </c>
       <c r="H244" t="n">
         <v>350856</v>
@@ -7503,7 +7503,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G246" t="n">
-        <v>3.09342098236084</v>
+        <v>3.09342050552368</v>
       </c>
       <c r="H246" t="n">
         <v>298347</v>
@@ -7532,7 +7532,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G247" t="n">
-        <v>3.16422080993652</v>
+        <v>3.16422057151794</v>
       </c>
       <c r="H247" t="n">
         <v>360292</v>
@@ -7561,7 +7561,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G248" t="n">
-        <v>3.18600535392761</v>
+        <v>3.18600559234619</v>
       </c>
       <c r="H248" t="n">
         <v>453538</v>
@@ -7590,7 +7590,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G249" t="n">
-        <v>3.23502135276794</v>
+        <v>3.23502063751221</v>
       </c>
       <c r="H249" t="n">
         <v>513814</v>
@@ -7648,7 +7648,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G251" t="n">
-        <v>3.18600535392761</v>
+        <v>3.18600559234619</v>
       </c>
       <c r="H251" t="n">
         <v>587417</v>
@@ -7706,7 +7706,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G253" t="n">
-        <v>3.20234394073486</v>
+        <v>3.20234441757202</v>
       </c>
       <c r="H253" t="n">
         <v>1032003</v>
@@ -7735,7 +7735,7 @@
         <v>5.5</v>
       </c>
       <c r="G254" t="n">
-        <v>3.2689106464386</v>
+        <v>3.26891136169434</v>
       </c>
       <c r="H254" t="n">
         <v>1331386</v>
@@ -7764,7 +7764,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G255" t="n">
-        <v>3.26296734809875</v>
+        <v>3.26296758651733</v>
       </c>
       <c r="H255" t="n">
         <v>491744</v>
@@ -7822,7 +7822,7 @@
         <v>5.5</v>
       </c>
       <c r="G257" t="n">
-        <v>3.2689106464386</v>
+        <v>3.26891136169434</v>
       </c>
       <c r="H257" t="n">
         <v>490521</v>
@@ -7851,7 +7851,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G258" t="n">
-        <v>3.24513745307922</v>
+        <v>3.24513697624207</v>
       </c>
       <c r="H258" t="n">
         <v>595648</v>
@@ -7880,7 +7880,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G259" t="n">
-        <v>3.21541953086853</v>
+        <v>3.21541976928711</v>
       </c>
       <c r="H259" t="n">
         <v>658405</v>
@@ -7909,7 +7909,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G260" t="n">
-        <v>3.1559853553772</v>
+        <v>3.15598487854004</v>
       </c>
       <c r="H260" t="n">
         <v>979931</v>
@@ -7938,7 +7938,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G261" t="n">
-        <v>3.20947670936584</v>
+        <v>3.20947623252869</v>
       </c>
       <c r="H261" t="n">
         <v>631640</v>
@@ -8025,7 +8025,7 @@
         <v>5.36499977111816</v>
       </c>
       <c r="G264" t="n">
-        <v>3.18867421150208</v>
+        <v>3.18867444992065</v>
       </c>
       <c r="H264" t="n">
         <v>221866</v>
@@ -8054,7 +8054,7 @@
         <v>5.25500011444092</v>
       </c>
       <c r="G265" t="n">
-        <v>3.12329626083374</v>
+        <v>3.12329578399658</v>
       </c>
       <c r="H265" t="n">
         <v>577217</v>
@@ -8112,7 +8112,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G267" t="n">
-        <v>3.13815474510193</v>
+        <v>3.13815450668335</v>
       </c>
       <c r="H267" t="n">
         <v>982246</v>
@@ -8141,7 +8141,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G268" t="n">
-        <v>3.06088948249817</v>
+        <v>3.06088972091675</v>
       </c>
       <c r="H268" t="n">
         <v>438786</v>
@@ -8170,7 +8170,7 @@
         <v>5.18499994277954</v>
       </c>
       <c r="G269" t="n">
-        <v>3.08169174194336</v>
+        <v>3.08169150352478</v>
       </c>
       <c r="H269" t="n">
         <v>231544</v>
@@ -8199,7 +8199,7 @@
         <v>5.25</v>
       </c>
       <c r="G270" t="n">
-        <v>3.12032413482666</v>
+        <v>3.12032437324524</v>
       </c>
       <c r="H270" t="n">
         <v>329941</v>
@@ -8228,7 +8228,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G271" t="n">
-        <v>3.13815474510193</v>
+        <v>3.13815450668335</v>
       </c>
       <c r="H271" t="n">
         <v>288840</v>
@@ -8257,7 +8257,7 @@
         <v>5.25500011444092</v>
       </c>
       <c r="G272" t="n">
-        <v>3.12329626083374</v>
+        <v>3.12329578399658</v>
       </c>
       <c r="H272" t="n">
         <v>328311</v>
@@ -8286,7 +8286,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G273" t="n">
-        <v>3.07871961593628</v>
+        <v>3.07872009277344</v>
       </c>
       <c r="H273" t="n">
         <v>369534</v>
@@ -8315,7 +8315,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G274" t="n">
-        <v>3.09655022621155</v>
+        <v>3.09655070304871</v>
       </c>
       <c r="H274" t="n">
         <v>417330</v>
@@ -8344,7 +8344,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G275" t="n">
-        <v>3.07277631759644</v>
+        <v>3.07277655601501</v>
       </c>
       <c r="H275" t="n">
         <v>698355</v>
@@ -8373,7 +8373,7 @@
         <v>5.02500009536743</v>
       </c>
       <c r="G276" t="n">
-        <v>2.98659586906433</v>
+        <v>2.98659634590149</v>
       </c>
       <c r="H276" t="n">
         <v>1166871</v>
@@ -8402,7 +8402,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G277" t="n">
-        <v>3.0073983669281</v>
+        <v>3.00739789009094</v>
       </c>
       <c r="H277" t="n">
         <v>576090</v>
@@ -8460,7 +8460,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G279" t="n">
-        <v>3.01928472518921</v>
+        <v>3.01928520202637</v>
       </c>
       <c r="H279" t="n">
         <v>636693</v>
@@ -8489,7 +8489,7 @@
         <v>4.96600008010864</v>
       </c>
       <c r="G280" t="n">
-        <v>2.95152997970581</v>
+        <v>2.95152974128723</v>
       </c>
       <c r="H280" t="n">
         <v>674444</v>
@@ -8576,7 +8576,7 @@
         <v>5.07499980926514</v>
       </c>
       <c r="G283" t="n">
-        <v>3.01631355285645</v>
+        <v>3.01631379127502</v>
       </c>
       <c r="H283" t="n">
         <v>226230</v>
@@ -8634,7 +8634,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G285" t="n">
-        <v>2.98362421989441</v>
+        <v>2.98362445831299</v>
       </c>
       <c r="H285" t="n">
         <v>352758</v>
@@ -8779,7 +8779,7 @@
         <v>5.07499980926514</v>
       </c>
       <c r="G290" t="n">
-        <v>3.01631355285645</v>
+        <v>3.01631379127502</v>
       </c>
       <c r="H290" t="n">
         <v>585591</v>
@@ -8808,7 +8808,7 @@
         <v>5.07499980926514</v>
       </c>
       <c r="G291" t="n">
-        <v>3.01631355285645</v>
+        <v>3.01631379127502</v>
       </c>
       <c r="H291" t="n">
         <v>697953</v>
@@ -8837,7 +8837,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G292" t="n">
-        <v>3.05791735649109</v>
+        <v>3.05791759490967</v>
       </c>
       <c r="H292" t="n">
         <v>416047</v>
@@ -8866,7 +8866,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G293" t="n">
-        <v>3.0906069278717</v>
+        <v>3.09060668945312</v>
       </c>
       <c r="H293" t="n">
         <v>267972</v>
@@ -8895,7 +8895,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G294" t="n">
-        <v>3.06683301925659</v>
+        <v>3.06683278083801</v>
       </c>
       <c r="H294" t="n">
         <v>263638</v>
@@ -8924,7 +8924,7 @@
         <v>5.11499977111816</v>
       </c>
       <c r="G295" t="n">
-        <v>3.04008769989014</v>
+        <v>3.0400869846344</v>
       </c>
       <c r="H295" t="n">
         <v>461713</v>
@@ -8982,7 +8982,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G297" t="n">
-        <v>3.03711581230164</v>
+        <v>3.03711605072021</v>
       </c>
       <c r="H297" t="n">
         <v>116870</v>
@@ -9011,7 +9011,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G298" t="n">
-        <v>3.06088948249817</v>
+        <v>3.06088972091675</v>
       </c>
       <c r="H298" t="n">
         <v>328764</v>
@@ -9040,7 +9040,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G299" t="n">
-        <v>3.11438083648682</v>
+        <v>3.11438059806824</v>
       </c>
       <c r="H299" t="n">
         <v>344162</v>
@@ -9069,7 +9069,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G300" t="n">
-        <v>3.0906069278717</v>
+        <v>3.09060668945312</v>
       </c>
       <c r="H300" t="n">
         <v>174295</v>
@@ -9127,7 +9127,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G302" t="n">
-        <v>3.13221120834351</v>
+        <v>3.13221144676208</v>
       </c>
       <c r="H302" t="n">
         <v>987196</v>
@@ -9156,7 +9156,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G303" t="n">
-        <v>3.1559853553772</v>
+        <v>3.15598487854004</v>
       </c>
       <c r="H303" t="n">
         <v>235545</v>
@@ -9214,7 +9214,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G305" t="n">
-        <v>3.14409780502319</v>
+        <v>3.14409804344177</v>
       </c>
       <c r="H305" t="n">
         <v>283594</v>
@@ -9243,7 +9243,7 @@
         <v>5.34499979019165</v>
       </c>
       <c r="G306" t="n">
-        <v>3.17678689956665</v>
+        <v>3.17678737640381</v>
       </c>
       <c r="H306" t="n">
         <v>272584</v>
@@ -9272,7 +9272,7 @@
         <v>5.13500022888184</v>
       </c>
       <c r="G307" t="n">
-        <v>3.05197429656982</v>
+        <v>3.05197405815125</v>
       </c>
       <c r="H307" t="n">
         <v>2197467</v>
@@ -9301,7 +9301,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G308" t="n">
-        <v>3.01928472518921</v>
+        <v>3.01928520202637</v>
       </c>
       <c r="H308" t="n">
         <v>172506</v>
@@ -9359,7 +9359,7 @@
         <v>4.95599985122681</v>
       </c>
       <c r="G310" t="n">
-        <v>2.94558572769165</v>
+        <v>2.94558620452881</v>
       </c>
       <c r="H310" t="n">
         <v>428973</v>
@@ -9388,7 +9388,7 @@
         <v>4.9539999961853</v>
       </c>
       <c r="G311" t="n">
-        <v>2.94439744949341</v>
+        <v>2.94439697265625</v>
       </c>
       <c r="H311" t="n">
         <v>179330</v>
@@ -9417,7 +9417,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G312" t="n">
-        <v>2.98362421989441</v>
+        <v>2.98362445831299</v>
       </c>
       <c r="H312" t="n">
         <v>142945</v>
@@ -9446,7 +9446,7 @@
         <v>5</v>
       </c>
       <c r="G313" t="n">
-        <v>2.97173762321472</v>
+        <v>2.97173738479614</v>
       </c>
       <c r="H313" t="n">
         <v>154813</v>
@@ -9475,7 +9475,7 @@
         <v>5.02500009536743</v>
       </c>
       <c r="G314" t="n">
-        <v>2.98659586906433</v>
+        <v>2.98659634590149</v>
       </c>
       <c r="H314" t="n">
         <v>109457</v>
@@ -9504,7 +9504,7 @@
         <v>4.93200016021729</v>
       </c>
       <c r="G315" t="n">
-        <v>2.93132209777832</v>
+        <v>2.93132185935974</v>
       </c>
       <c r="H315" t="n">
         <v>154692</v>
@@ -9533,7 +9533,7 @@
         <v>4.96199989318848</v>
       </c>
       <c r="G316" t="n">
-        <v>2.94915223121643</v>
+        <v>2.94915246963501</v>
       </c>
       <c r="H316" t="n">
         <v>227692</v>
@@ -9562,7 +9562,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G317" t="n">
-        <v>2.98956751823425</v>
+        <v>2.98956799507141</v>
       </c>
       <c r="H317" t="n">
         <v>166858</v>
@@ -9591,7 +9591,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G318" t="n">
-        <v>3.05791735649109</v>
+        <v>3.05791759490967</v>
       </c>
       <c r="H318" t="n">
         <v>170278</v>
@@ -9620,7 +9620,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G319" t="n">
-        <v>3.07277631759644</v>
+        <v>3.07277655601501</v>
       </c>
       <c r="H319" t="n">
         <v>153750</v>
@@ -9678,7 +9678,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G321" t="n">
-        <v>3.02522873878479</v>
+        <v>3.02522826194763</v>
       </c>
       <c r="H321" t="n">
         <v>173975</v>
@@ -9707,7 +9707,7 @@
         <v>5.13500022888184</v>
       </c>
       <c r="G322" t="n">
-        <v>3.05197429656982</v>
+        <v>3.05197405815125</v>
       </c>
       <c r="H322" t="n">
         <v>99798</v>
@@ -9736,7 +9736,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G323" t="n">
-        <v>3.06683301925659</v>
+        <v>3.06683278083801</v>
       </c>
       <c r="H323" t="n">
         <v>58760</v>
@@ -9765,7 +9765,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G324" t="n">
-        <v>3.13815474510193</v>
+        <v>3.13815450668335</v>
       </c>
       <c r="H324" t="n">
         <v>202372</v>
@@ -9794,7 +9794,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G325" t="n">
-        <v>3.12626791000366</v>
+        <v>3.12626767158508</v>
       </c>
       <c r="H325" t="n">
         <v>127239</v>
@@ -9823,7 +9823,7 @@
         <v>5.2350001335144</v>
       </c>
       <c r="G326" t="n">
-        <v>3.11140918731689</v>
+        <v>3.11140894889832</v>
       </c>
       <c r="H326" t="n">
         <v>76315</v>
@@ -9852,7 +9852,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G327" t="n">
-        <v>3.12626791000366</v>
+        <v>3.12626767158508</v>
       </c>
       <c r="H327" t="n">
         <v>103691</v>
@@ -9881,7 +9881,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G328" t="n">
-        <v>3.08466339111328</v>
+        <v>3.08466362953186</v>
       </c>
       <c r="H328" t="n">
         <v>66700</v>
@@ -9910,7 +9910,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G329" t="n">
-        <v>3.10843706130981</v>
+        <v>3.10843729972839</v>
       </c>
       <c r="H329" t="n">
         <v>163620</v>
@@ -9939,7 +9939,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G330" t="n">
-        <v>3.0906069278717</v>
+        <v>3.09060668945312</v>
       </c>
       <c r="H330" t="n">
         <v>128424</v>
@@ -9968,7 +9968,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G331" t="n">
-        <v>3.10843706130981</v>
+        <v>3.10843729972839</v>
       </c>
       <c r="H331" t="n">
         <v>113419</v>
@@ -10026,7 +10026,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G333" t="n">
-        <v>3.18570256233215</v>
+        <v>3.185702085495</v>
       </c>
       <c r="H333" t="n">
         <v>140475</v>
@@ -10055,7 +10055,7 @@
         <v>5.34499979019165</v>
       </c>
       <c r="G334" t="n">
-        <v>3.17678689956665</v>
+        <v>3.17678737640381</v>
       </c>
       <c r="H334" t="n">
         <v>99856</v>
@@ -10113,7 +10113,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G336" t="n">
-        <v>3.15004205703735</v>
+        <v>3.15004134178162</v>
       </c>
       <c r="H336" t="n">
         <v>364841</v>
@@ -10171,7 +10171,7 @@
         <v>5.17500019073486</v>
       </c>
       <c r="G338" t="n">
-        <v>3.07574844360352</v>
+        <v>3.07574796676636</v>
       </c>
       <c r="H338" t="n">
         <v>106130</v>
@@ -10200,7 +10200,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G339" t="n">
-        <v>3.18570256233215</v>
+        <v>3.185702085495</v>
       </c>
       <c r="H339" t="n">
         <v>115723</v>
@@ -10229,7 +10229,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G340" t="n">
-        <v>3.20947670936584</v>
+        <v>3.20947623252869</v>
       </c>
       <c r="H340" t="n">
         <v>1238146</v>
@@ -10316,7 +10316,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G343" t="n">
-        <v>3.16787171363831</v>
+        <v>3.16787195205688</v>
       </c>
       <c r="H343" t="n">
         <v>197982</v>
@@ -10345,7 +10345,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G344" t="n">
-        <v>3.16192889213562</v>
+        <v>3.16192865371704</v>
       </c>
       <c r="H344" t="n">
         <v>70903</v>
@@ -10403,7 +10403,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G346" t="n">
-        <v>3.0490026473999</v>
+        <v>3.04900288581848</v>
       </c>
       <c r="H346" t="n">
         <v>123014</v>
@@ -10432,7 +10432,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G347" t="n">
-        <v>3.05791735649109</v>
+        <v>3.05791759490967</v>
       </c>
       <c r="H347" t="n">
         <v>74239</v>
@@ -10461,7 +10461,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G348" t="n">
-        <v>3.08466339111328</v>
+        <v>3.08466362953186</v>
       </c>
       <c r="H348" t="n">
         <v>453065</v>
@@ -10490,7 +10490,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G349" t="n">
-        <v>3.06683301925659</v>
+        <v>3.06683278083801</v>
       </c>
       <c r="H349" t="n">
         <v>92763</v>
@@ -10548,7 +10548,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G351" t="n">
-        <v>3.06088948249817</v>
+        <v>3.06088972091675</v>
       </c>
       <c r="H351" t="n">
         <v>97494</v>
@@ -10577,7 +10577,7 @@
         <v>5.21500015258789</v>
       </c>
       <c r="G352" t="n">
-        <v>3.09952235221863</v>
+        <v>3.09952211380005</v>
       </c>
       <c r="H352" t="n">
         <v>118988</v>
@@ -10606,7 +10606,7 @@
         <v>5.17500019073486</v>
       </c>
       <c r="G353" t="n">
-        <v>3.07574844360352</v>
+        <v>3.07574796676636</v>
       </c>
       <c r="H353" t="n">
         <v>108557</v>
@@ -10635,7 +10635,7 @@
         <v>5.16499996185303</v>
       </c>
       <c r="G354" t="n">
-        <v>3.06980490684509</v>
+        <v>3.06980466842651</v>
       </c>
       <c r="H354" t="n">
         <v>82105</v>
@@ -10664,7 +10664,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G355" t="n">
-        <v>3.07277631759644</v>
+        <v>3.07277655601501</v>
       </c>
       <c r="H355" t="n">
         <v>230549</v>
@@ -10693,7 +10693,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G356" t="n">
-        <v>3.06088948249817</v>
+        <v>3.06088972091675</v>
       </c>
       <c r="H356" t="n">
         <v>91142</v>
@@ -10722,7 +10722,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G357" t="n">
-        <v>3.05791735649109</v>
+        <v>3.05791759490967</v>
       </c>
       <c r="H357" t="n">
         <v>28290</v>
@@ -10751,7 +10751,7 @@
         <v>5.125</v>
       </c>
       <c r="G358" t="n">
-        <v>3.04603052139282</v>
+        <v>3.0460307598114</v>
       </c>
       <c r="H358" t="n">
         <v>40886</v>
@@ -10780,7 +10780,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G359" t="n">
-        <v>3.07277631759644</v>
+        <v>3.07277655601501</v>
       </c>
       <c r="H359" t="n">
         <v>186054</v>
@@ -10809,7 +10809,7 @@
         <v>5.13500022888184</v>
       </c>
       <c r="G360" t="n">
-        <v>3.05197429656982</v>
+        <v>3.05197405815125</v>
       </c>
       <c r="H360" t="n">
         <v>90421</v>
@@ -10838,7 +10838,7 @@
         <v>5.13500022888184</v>
       </c>
       <c r="G361" t="n">
-        <v>3.05197429656982</v>
+        <v>3.05197405815125</v>
       </c>
       <c r="H361" t="n">
         <v>122930</v>
@@ -10867,7 +10867,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G362" t="n">
-        <v>3.06683301925659</v>
+        <v>3.06683278083801</v>
       </c>
       <c r="H362" t="n">
         <v>194545</v>
@@ -10925,7 +10925,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G364" t="n">
-        <v>3.05791735649109</v>
+        <v>3.05791759490967</v>
       </c>
       <c r="H364" t="n">
         <v>87130</v>
@@ -10954,7 +10954,7 @@
         <v>5.13500022888184</v>
       </c>
       <c r="G365" t="n">
-        <v>3.05197429656982</v>
+        <v>3.05197405815125</v>
       </c>
       <c r="H365" t="n">
         <v>61470</v>
@@ -11012,7 +11012,7 @@
         <v>5.125</v>
       </c>
       <c r="G367" t="n">
-        <v>3.04603052139282</v>
+        <v>3.0460307598114</v>
       </c>
       <c r="H367" t="n">
         <v>120227</v>
@@ -11041,7 +11041,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G368" t="n">
-        <v>3.06088948249817</v>
+        <v>3.06088972091675</v>
       </c>
       <c r="H368" t="n">
         <v>56278</v>
@@ -11070,7 +11070,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G369" t="n">
-        <v>3.0906069278717</v>
+        <v>3.09060668945312</v>
       </c>
       <c r="H369" t="n">
         <v>221869</v>
@@ -11099,7 +11099,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G370" t="n">
-        <v>3.11438083648682</v>
+        <v>3.11438059806824</v>
       </c>
       <c r="H370" t="n">
         <v>151879</v>
@@ -11128,7 +11128,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G371" t="n">
-        <v>3.1559853553772</v>
+        <v>3.15598487854004</v>
       </c>
       <c r="H371" t="n">
         <v>203445</v>
@@ -11157,7 +11157,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G372" t="n">
-        <v>3.09655022621155</v>
+        <v>3.09655070304871</v>
       </c>
       <c r="H372" t="n">
         <v>46233</v>
@@ -11186,7 +11186,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G373" t="n">
-        <v>3.07277631759644</v>
+        <v>3.07277655601501</v>
       </c>
       <c r="H373" t="n">
         <v>246726</v>
@@ -11215,7 +11215,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G374" t="n">
-        <v>3.09655022621155</v>
+        <v>3.09655070304871</v>
       </c>
       <c r="H374" t="n">
         <v>132834</v>
@@ -11244,7 +11244,7 @@
         <v>5.25500011444092</v>
       </c>
       <c r="G375" t="n">
-        <v>3.12329626083374</v>
+        <v>3.12329578399658</v>
       </c>
       <c r="H375" t="n">
         <v>154023</v>
@@ -11273,7 +11273,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G376" t="n">
-        <v>3.06683301925659</v>
+        <v>3.06683278083801</v>
       </c>
       <c r="H376" t="n">
         <v>286681</v>
@@ -11360,7 +11360,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G379" t="n">
-        <v>3.0490026473999</v>
+        <v>3.04900288581848</v>
       </c>
       <c r="H379" t="n">
         <v>177787</v>
@@ -11476,7 +11476,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G383" t="n">
-        <v>2.79937624931335</v>
+        <v>2.79937672615051</v>
       </c>
       <c r="H383" t="n">
         <v>488102</v>
@@ -11505,7 +11505,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G384" t="n">
-        <v>2.76965880393982</v>
+        <v>2.7696590423584</v>
       </c>
       <c r="H384" t="n">
         <v>576950</v>
@@ -11534,7 +11534,7 @@
         <v>4.71799993515015</v>
       </c>
       <c r="G385" t="n">
-        <v>2.80413150787354</v>
+        <v>2.80413103103638</v>
       </c>
       <c r="H385" t="n">
         <v>265565</v>
@@ -11563,7 +11563,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G386" t="n">
-        <v>2.78749012947083</v>
+        <v>2.78748989105225</v>
       </c>
       <c r="H386" t="n">
         <v>196107</v>
@@ -11592,7 +11592,7 @@
         <v>4.68400001525879</v>
       </c>
       <c r="G387" t="n">
-        <v>2.78392362594604</v>
+        <v>2.78392338752747</v>
       </c>
       <c r="H387" t="n">
         <v>169037</v>
@@ -11621,7 +11621,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G388" t="n">
-        <v>2.858811378479</v>
+        <v>2.85881161689758</v>
       </c>
       <c r="H388" t="n">
         <v>182848</v>
@@ -11650,7 +11650,7 @@
         <v>4.71400022506714</v>
       </c>
       <c r="G389" t="n">
-        <v>2.80175399780273</v>
+        <v>2.80175423622131</v>
       </c>
       <c r="H389" t="n">
         <v>271772</v>
@@ -11679,7 +11679,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G390" t="n">
-        <v>2.8053195476532</v>
+        <v>2.80531978607178</v>
       </c>
       <c r="H390" t="n">
         <v>91615</v>
@@ -11708,7 +11708,7 @@
         <v>4.59600019454956</v>
       </c>
       <c r="G391" t="n">
-        <v>2.7316210269928</v>
+        <v>2.73162126541138</v>
       </c>
       <c r="H391" t="n">
         <v>286266</v>
@@ -11737,7 +11737,7 @@
         <v>4.58199977874756</v>
       </c>
       <c r="G392" t="n">
-        <v>2.72329998016357</v>
+        <v>2.723299741745</v>
       </c>
       <c r="H392" t="n">
         <v>122845</v>
@@ -11766,7 +11766,7 @@
         <v>4.43400001525879</v>
       </c>
       <c r="G393" t="n">
-        <v>2.63533639907837</v>
+        <v>2.63533663749695</v>
       </c>
       <c r="H393" t="n">
         <v>176582</v>
@@ -11795,7 +11795,7 @@
         <v>4.33599996566772</v>
       </c>
       <c r="G394" t="n">
-        <v>2.57709050178528</v>
+        <v>2.57709074020386</v>
       </c>
       <c r="H394" t="n">
         <v>190947</v>
@@ -11882,7 +11882,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G397" t="n">
-        <v>2.63295936584473</v>
+        <v>2.63295912742615</v>
       </c>
       <c r="H397" t="n">
         <v>580470</v>
@@ -11940,7 +11940,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G399" t="n">
-        <v>2.70428085327148</v>
+        <v>2.70428109169006</v>
       </c>
       <c r="H399" t="n">
         <v>360794</v>
@@ -11969,7 +11969,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G400" t="n">
-        <v>2.70428085327148</v>
+        <v>2.70428109169006</v>
       </c>
       <c r="H400" t="n">
         <v>99931</v>
@@ -11998,7 +11998,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G401" t="n">
-        <v>2.71616816520691</v>
+        <v>2.71616792678833</v>
       </c>
       <c r="H401" t="n">
         <v>228006</v>
@@ -12027,7 +12027,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G402" t="n">
-        <v>2.71022439002991</v>
+        <v>2.71022391319275</v>
       </c>
       <c r="H402" t="n">
         <v>122945</v>
@@ -12056,7 +12056,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G403" t="n">
-        <v>2.68645071983337</v>
+        <v>2.68645095825195</v>
       </c>
       <c r="H403" t="n">
         <v>276905</v>
@@ -12085,7 +12085,7 @@
         <v>4.73600006103516</v>
       </c>
       <c r="G404" t="n">
-        <v>2.81482934951782</v>
+        <v>2.8148295879364</v>
       </c>
       <c r="H404" t="n">
         <v>608489</v>
@@ -12114,7 +12114,7 @@
         <v>4.61399984359741</v>
       </c>
       <c r="G405" t="n">
-        <v>2.74231886863708</v>
+        <v>2.74231934547424</v>
       </c>
       <c r="H405" t="n">
         <v>143504</v>
@@ -12201,7 +12201,7 @@
         <v>4.70599985122681</v>
       </c>
       <c r="G408" t="n">
-        <v>2.79699897766113</v>
+        <v>2.79699873924255</v>
       </c>
       <c r="H408" t="n">
         <v>161429</v>
@@ -12288,7 +12288,7 @@
         <v>4.51599979400635</v>
       </c>
       <c r="G411" t="n">
-        <v>2.68407273292542</v>
+        <v>2.68407297134399</v>
       </c>
       <c r="H411" t="n">
         <v>70296</v>
@@ -12317,7 +12317,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G412" t="n">
-        <v>2.71022439002991</v>
+        <v>2.71022391319275</v>
       </c>
       <c r="H412" t="n">
         <v>110897</v>
@@ -12375,7 +12375,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G414" t="n">
-        <v>2.70428085327148</v>
+        <v>2.70428109169006</v>
       </c>
       <c r="H414" t="n">
         <v>160385</v>
@@ -12404,7 +12404,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G415" t="n">
-        <v>2.71616816520691</v>
+        <v>2.71616792678833</v>
       </c>
       <c r="H415" t="n">
         <v>103050</v>
@@ -12462,7 +12462,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G417" t="n">
-        <v>2.79343318939209</v>
+        <v>2.79343295097351</v>
       </c>
       <c r="H417" t="n">
         <v>148154</v>
@@ -12491,7 +12491,7 @@
         <v>4.67199993133545</v>
       </c>
       <c r="G418" t="n">
-        <v>2.77679133415222</v>
+        <v>2.7767915725708</v>
       </c>
       <c r="H418" t="n">
         <v>157427</v>
@@ -12520,7 +12520,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G419" t="n">
-        <v>2.72805500030518</v>
+        <v>2.72805523872375</v>
       </c>
       <c r="H419" t="n">
         <v>217141</v>
@@ -12549,7 +12549,7 @@
         <v>4.59800004959106</v>
       </c>
       <c r="G420" t="n">
-        <v>2.73281002044678</v>
+        <v>2.73280930519104</v>
       </c>
       <c r="H420" t="n">
         <v>71919</v>
@@ -12578,7 +12578,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G421" t="n">
-        <v>2.74588537216187</v>
+        <v>2.74588513374329</v>
       </c>
       <c r="H421" t="n">
         <v>273873</v>
@@ -12607,7 +12607,7 @@
         <v>4.60400009155273</v>
       </c>
       <c r="G422" t="n">
-        <v>2.7363760471344</v>
+        <v>2.73637580871582</v>
       </c>
       <c r="H422" t="n">
         <v>268621</v>
@@ -12636,7 +12636,7 @@
         <v>4.6560001373291</v>
       </c>
       <c r="G423" t="n">
-        <v>2.76728200912476</v>
+        <v>2.76728177070618</v>
       </c>
       <c r="H423" t="n">
         <v>87837</v>
@@ -12665,7 +12665,7 @@
         <v>4.59800004959106</v>
       </c>
       <c r="G424" t="n">
-        <v>2.73281002044678</v>
+        <v>2.73280930519104</v>
       </c>
       <c r="H424" t="n">
         <v>54186</v>
@@ -12694,7 +12694,7 @@
         <v>4.53599977493286</v>
       </c>
       <c r="G425" t="n">
-        <v>2.69596004486084</v>
+        <v>2.69595980644226</v>
       </c>
       <c r="H425" t="n">
         <v>103550</v>
@@ -12723,7 +12723,7 @@
         <v>4.55600023269653</v>
       </c>
       <c r="G426" t="n">
-        <v>2.70784735679626</v>
+        <v>2.70784759521484</v>
       </c>
       <c r="H426" t="n">
         <v>83993</v>
@@ -12752,7 +12752,7 @@
         <v>4.50799989700317</v>
       </c>
       <c r="G427" t="n">
-        <v>2.67931818962097</v>
+        <v>2.67931842803955</v>
       </c>
       <c r="H427" t="n">
         <v>62972</v>
@@ -12781,7 +12781,7 @@
         <v>4.46199989318848</v>
       </c>
       <c r="G428" t="n">
-        <v>2.65197825431824</v>
+        <v>2.65197849273682</v>
       </c>
       <c r="H428" t="n">
         <v>105523</v>
@@ -12839,7 +12839,7 @@
         <v>4.61800003051758</v>
       </c>
       <c r="G430" t="n">
-        <v>2.74469661712646</v>
+        <v>2.74469637870789</v>
       </c>
       <c r="H430" t="n">
         <v>75304</v>
@@ -12868,7 +12868,7 @@
         <v>4.53399991989136</v>
       </c>
       <c r="G431" t="n">
-        <v>2.69477105140686</v>
+        <v>2.69477128982544</v>
       </c>
       <c r="H431" t="n">
         <v>67005</v>
@@ -12897,7 +12897,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G432" t="n">
-        <v>2.65673303604126</v>
+        <v>2.65673351287842</v>
       </c>
       <c r="H432" t="n">
         <v>91638</v>
@@ -12926,7 +12926,7 @@
         <v>4.48199987411499</v>
       </c>
       <c r="G433" t="n">
-        <v>2.66386532783508</v>
+        <v>2.6638650894165</v>
       </c>
       <c r="H433" t="n">
         <v>70856</v>
@@ -12984,7 +12984,7 @@
         <v>4.50400018692017</v>
       </c>
       <c r="G435" t="n">
-        <v>2.67694115638733</v>
+        <v>2.67694091796875</v>
       </c>
       <c r="H435" t="n">
         <v>90846</v>
@@ -13071,7 +13071,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G438" t="n">
-        <v>2.69833731651306</v>
+        <v>2.69833755493164</v>
       </c>
       <c r="H438" t="n">
         <v>49751</v>
@@ -13100,7 +13100,7 @@
         <v>4.57800006866455</v>
       </c>
       <c r="G439" t="n">
-        <v>2.72092294692993</v>
+        <v>2.72092270851135</v>
       </c>
       <c r="H439" t="n">
         <v>76196</v>
@@ -13158,7 +13158,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G441" t="n">
-        <v>2.86475467681885</v>
+        <v>2.86475515365601</v>
       </c>
       <c r="H441" t="n">
         <v>258995</v>
@@ -13187,7 +13187,7 @@
         <v>4.90199995040894</v>
       </c>
       <c r="G442" t="n">
-        <v>2.91349148750305</v>
+        <v>2.91349101066589</v>
       </c>
       <c r="H442" t="n">
         <v>262634</v>
@@ -13245,7 +13245,7 @@
         <v>4.85599994659424</v>
       </c>
       <c r="G444" t="n">
-        <v>2.88615131378174</v>
+        <v>2.88615107536316</v>
       </c>
       <c r="H444" t="n">
         <v>231839</v>
@@ -13506,7 +13506,7 @@
         <v>4.80399990081787</v>
       </c>
       <c r="G453" t="n">
-        <v>2.85524487495422</v>
+        <v>2.85524535179138</v>
       </c>
       <c r="H453" t="n">
         <v>129776</v>
@@ -13593,7 +13593,7 @@
         <v>4.92399978637695</v>
       </c>
       <c r="G456" t="n">
-        <v>2.92656707763672</v>
+        <v>2.92656660079956</v>
       </c>
       <c r="H456" t="n">
         <v>147514</v>
@@ -13622,7 +13622,7 @@
         <v>4.92600011825562</v>
       </c>
       <c r="G457" t="n">
-        <v>2.92775583267212</v>
+        <v>2.9277560710907</v>
       </c>
       <c r="H457" t="n">
         <v>149968</v>
@@ -13651,7 +13651,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G458" t="n">
-        <v>3.00145506858826</v>
+        <v>3.00145483016968</v>
       </c>
       <c r="H458" t="n">
         <v>653587</v>
@@ -13680,7 +13680,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G459" t="n">
-        <v>3.03711581230164</v>
+        <v>3.03711605072021</v>
       </c>
       <c r="H459" t="n">
         <v>507410</v>
@@ -13738,7 +13738,7 @@
         <v>5.02500009536743</v>
       </c>
       <c r="G461" t="n">
-        <v>2.98659586906433</v>
+        <v>2.98659634590149</v>
       </c>
       <c r="H461" t="n">
         <v>259088</v>
@@ -13796,7 +13796,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G463" t="n">
-        <v>3.0490026473999</v>
+        <v>3.04900288581848</v>
       </c>
       <c r="H463" t="n">
         <v>275636</v>
@@ -13854,7 +13854,7 @@
         <v>4.98600006103516</v>
       </c>
       <c r="G465" t="n">
-        <v>2.9634165763855</v>
+        <v>2.96341681480408</v>
       </c>
       <c r="H465" t="n">
         <v>365178</v>
@@ -13883,7 +13883,7 @@
         <v>5.11499977111816</v>
       </c>
       <c r="G466" t="n">
-        <v>3.04008769989014</v>
+        <v>3.0400869846344</v>
       </c>
       <c r="H466" t="n">
         <v>920387</v>
@@ -13941,7 +13941,7 @@
         <v>5.25</v>
       </c>
       <c r="G468" t="n">
-        <v>3.12032413482666</v>
+        <v>3.12032437324524</v>
       </c>
       <c r="H468" t="n">
         <v>599209</v>
@@ -13970,7 +13970,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G469" t="n">
-        <v>3.16787171363831</v>
+        <v>3.16787195205688</v>
       </c>
       <c r="H469" t="n">
         <v>981203</v>
@@ -13999,7 +13999,7 @@
         <v>5.25</v>
       </c>
       <c r="G470" t="n">
-        <v>3.12032413482666</v>
+        <v>3.12032437324524</v>
       </c>
       <c r="H470" t="n">
         <v>864726</v>
@@ -14028,7 +14028,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G471" t="n">
-        <v>3.16192889213562</v>
+        <v>3.16192865371704</v>
       </c>
       <c r="H471" t="n">
         <v>695141</v>
@@ -14057,7 +14057,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G472" t="n">
-        <v>3.21541953086853</v>
+        <v>3.21541976928711</v>
       </c>
       <c r="H472" t="n">
         <v>752076</v>
@@ -14086,7 +14086,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G473" t="n">
-        <v>3.16787171363831</v>
+        <v>3.16787195205688</v>
       </c>
       <c r="H473" t="n">
         <v>424757</v>
@@ -14115,7 +14115,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G474" t="n">
-        <v>3.16787171363831</v>
+        <v>3.16787195205688</v>
       </c>
       <c r="H474" t="n">
         <v>504964</v>
@@ -14144,7 +14144,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G475" t="n">
-        <v>3.15004205703735</v>
+        <v>3.15004134178162</v>
       </c>
       <c r="H475" t="n">
         <v>493758</v>
@@ -14202,7 +14202,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G477" t="n">
-        <v>3.15004205703735</v>
+        <v>3.15004134178162</v>
       </c>
       <c r="H477" t="n">
         <v>466486</v>
@@ -14231,7 +14231,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G478" t="n">
-        <v>3.0906069278717</v>
+        <v>3.09060668945312</v>
       </c>
       <c r="H478" t="n">
         <v>609117</v>
@@ -14260,7 +14260,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G479" t="n">
-        <v>3.07871961593628</v>
+        <v>3.07872009277344</v>
       </c>
       <c r="H479" t="n">
         <v>588665</v>
@@ -14318,7 +14318,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G481" t="n">
-        <v>3.14409780502319</v>
+        <v>3.14409804344177</v>
       </c>
       <c r="H481" t="n">
         <v>420743</v>
@@ -14347,7 +14347,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G482" t="n">
-        <v>3.15004205703735</v>
+        <v>3.15004134178162</v>
       </c>
       <c r="H482" t="n">
         <v>297729</v>
@@ -14434,7 +14434,7 @@
         <v>5.34499979019165</v>
       </c>
       <c r="G485" t="n">
-        <v>3.17678689956665</v>
+        <v>3.17678737640381</v>
       </c>
       <c r="H485" t="n">
         <v>257835</v>
@@ -14463,7 +14463,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G486" t="n">
-        <v>3.16787171363831</v>
+        <v>3.16787195205688</v>
       </c>
       <c r="H486" t="n">
         <v>302610</v>
@@ -14492,7 +14492,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G487" t="n">
-        <v>3.18570256233215</v>
+        <v>3.185702085495</v>
       </c>
       <c r="H487" t="n">
         <v>273552</v>
@@ -14521,7 +14521,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G488" t="n">
-        <v>3.19164609909058</v>
+        <v>3.191645860672</v>
       </c>
       <c r="H488" t="n">
         <v>323925</v>
@@ -14579,7 +14579,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G490" t="n">
-        <v>3.22730660438538</v>
+        <v>3.22730708122253</v>
       </c>
       <c r="H490" t="n">
         <v>437671</v>
@@ -14608,7 +14608,7 @@
         <v>5.49499988555908</v>
       </c>
       <c r="G491" t="n">
-        <v>3.26593923568726</v>
+        <v>3.2659387588501</v>
       </c>
       <c r="H491" t="n">
         <v>696421</v>
@@ -14637,7 +14637,7 @@
         <v>5.57499980926514</v>
       </c>
       <c r="G492" t="n">
-        <v>3.3134868144989</v>
+        <v>3.31348705291748</v>
       </c>
       <c r="H492" t="n">
         <v>414361</v>
@@ -14666,7 +14666,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G493" t="n">
-        <v>3.28079795837402</v>
+        <v>3.2807981967926</v>
       </c>
       <c r="H493" t="n">
         <v>427626</v>
@@ -14695,7 +14695,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G494" t="n">
-        <v>3.29862880706787</v>
+        <v>3.29862856864929</v>
       </c>
       <c r="H494" t="n">
         <v>486720</v>
@@ -14724,7 +14724,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G495" t="n">
-        <v>3.29862880706787</v>
+        <v>3.29862856864929</v>
       </c>
       <c r="H495" t="n">
         <v>335472</v>
@@ -14753,7 +14753,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G496" t="n">
-        <v>3.29268455505371</v>
+        <v>3.29268527030945</v>
       </c>
       <c r="H496" t="n">
         <v>426777</v>
@@ -14782,7 +14782,7 @@
         <v>5.5</v>
       </c>
       <c r="G497" t="n">
-        <v>3.2689106464386</v>
+        <v>3.26891136169434</v>
       </c>
       <c r="H497" t="n">
         <v>672154</v>
@@ -14811,7 +14811,7 @@
         <v>5.54500007629395</v>
       </c>
       <c r="G498" t="n">
-        <v>3.29565715789795</v>
+        <v>3.29565644264221</v>
       </c>
       <c r="H498" t="n">
         <v>524663</v>
@@ -14840,7 +14840,7 @@
         <v>5.625</v>
       </c>
       <c r="G499" t="n">
-        <v>3.34320473670959</v>
+        <v>3.34320425987244</v>
       </c>
       <c r="H499" t="n">
         <v>778967</v>
@@ -14869,7 +14869,7 @@
         <v>5.60500001907349</v>
       </c>
       <c r="G500" t="n">
-        <v>3.33131742477417</v>
+        <v>3.33131790161133</v>
       </c>
       <c r="H500" t="n">
         <v>652712</v>
@@ -14898,7 +14898,7 @@
         <v>5.42500019073486</v>
       </c>
       <c r="G501" t="n">
-        <v>3.22433543205261</v>
+        <v>3.22433471679688</v>
       </c>
       <c r="H501" t="n">
         <v>5303704</v>
@@ -14956,7 +14956,7 @@
         <v>4.96500015258789</v>
       </c>
       <c r="G503" t="n">
-        <v>3.2764687538147</v>
+        <v>3.27646851539612</v>
       </c>
       <c r="H503" t="n">
         <v>1438467</v>
@@ -15072,7 +15072,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G507" t="n">
-        <v>3.33256149291992</v>
+        <v>3.33256053924561</v>
       </c>
       <c r="H507" t="n">
         <v>310695</v>
@@ -15130,7 +15130,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G509" t="n">
-        <v>3.31936264038086</v>
+        <v>3.31936287879944</v>
       </c>
       <c r="H509" t="n">
         <v>378358</v>
@@ -15188,7 +15188,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G511" t="n">
-        <v>3.37215542793274</v>
+        <v>3.37215566635132</v>
       </c>
       <c r="H511" t="n">
         <v>270711</v>
@@ -15217,7 +15217,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G512" t="n">
-        <v>3.4051513671875</v>
+        <v>3.40515112876892</v>
       </c>
       <c r="H512" t="n">
         <v>346400</v>
@@ -15275,7 +15275,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G514" t="n">
-        <v>3.36555624008179</v>
+        <v>3.36555647850037</v>
       </c>
       <c r="H514" t="n">
         <v>602895</v>
@@ -15333,7 +15333,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G516" t="n">
-        <v>3.47114300727844</v>
+        <v>3.47114253044128</v>
       </c>
       <c r="H516" t="n">
         <v>419765</v>
@@ -15362,7 +15362,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G517" t="n">
-        <v>3.47114300727844</v>
+        <v>3.47114253044128</v>
       </c>
       <c r="H517" t="n">
         <v>482592</v>
@@ -15391,7 +15391,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G518" t="n">
-        <v>3.49093961715698</v>
+        <v>3.49093985557556</v>
       </c>
       <c r="H518" t="n">
         <v>195188</v>
@@ -15420,7 +15420,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G519" t="n">
-        <v>3.50413846969604</v>
+        <v>3.50413775444031</v>
       </c>
       <c r="H519" t="n">
         <v>436693</v>
@@ -15478,7 +15478,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G521" t="n">
-        <v>3.47114300727844</v>
+        <v>3.47114253044128</v>
       </c>
       <c r="H521" t="n">
         <v>297721</v>
@@ -15507,7 +15507,7 @@
         <v>5.25</v>
       </c>
       <c r="G522" t="n">
-        <v>3.46454381942749</v>
+        <v>3.46454334259033</v>
       </c>
       <c r="H522" t="n">
         <v>345412</v>
@@ -15536,7 +15536,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G523" t="n">
-        <v>3.43154788017273</v>
+        <v>3.43154811859131</v>
       </c>
       <c r="H523" t="n">
         <v>607512</v>
@@ -15565,7 +15565,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G524" t="n">
-        <v>3.39855217933655</v>
+        <v>3.39855241775513</v>
       </c>
       <c r="H524" t="n">
         <v>501174</v>
@@ -15623,7 +15623,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G526" t="n">
-        <v>3.35895752906799</v>
+        <v>3.35895776748657</v>
       </c>
       <c r="H526" t="n">
         <v>209893</v>
@@ -15652,7 +15652,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G527" t="n">
-        <v>3.33256149291992</v>
+        <v>3.33256053924561</v>
       </c>
       <c r="H527" t="n">
         <v>267715</v>
@@ -15681,7 +15681,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G528" t="n">
-        <v>3.31276345252991</v>
+        <v>3.31276297569275</v>
       </c>
       <c r="H528" t="n">
         <v>271659</v>
@@ -15710,7 +15710,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G529" t="n">
-        <v>3.27976775169373</v>
+        <v>3.27976727485657</v>
       </c>
       <c r="H529" t="n">
         <v>302738</v>
@@ -15797,7 +15797,7 @@
         <v>4.9850001335144</v>
       </c>
       <c r="G532" t="n">
-        <v>3.28966617584229</v>
+        <v>3.28966641426086</v>
       </c>
       <c r="H532" t="n">
         <v>183355</v>
@@ -15826,7 +15826,7 @@
         <v>4.9850001335144</v>
       </c>
       <c r="G533" t="n">
-        <v>3.28966617584229</v>
+        <v>3.28966641426086</v>
       </c>
       <c r="H533" t="n">
         <v>185408</v>
@@ -15855,7 +15855,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G534" t="n">
-        <v>3.27316904067993</v>
+        <v>3.27316880226135</v>
       </c>
       <c r="H534" t="n">
         <v>291730</v>
@@ -15884,7 +15884,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G535" t="n">
-        <v>3.30616474151611</v>
+        <v>3.30616497993469</v>
       </c>
       <c r="H535" t="n">
         <v>112782</v>
@@ -15942,7 +15942,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G537" t="n">
-        <v>3.14778518676758</v>
+        <v>3.14778542518616</v>
       </c>
       <c r="H537" t="n">
         <v>607886</v>
@@ -15971,7 +15971,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G538" t="n">
-        <v>3.19397926330566</v>
+        <v>3.19397902488708</v>
       </c>
       <c r="H538" t="n">
         <v>185948</v>
@@ -16000,7 +16000,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G539" t="n">
-        <v>3.22037601470947</v>
+        <v>3.22037553787231</v>
       </c>
       <c r="H539" t="n">
         <v>191125</v>
@@ -16029,7 +16029,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G540" t="n">
-        <v>3.20387816429138</v>
+        <v>3.20387768745422</v>
       </c>
       <c r="H540" t="n">
         <v>360189</v>
@@ -16058,7 +16058,7 @@
         <v>4.81500005722046</v>
       </c>
       <c r="G541" t="n">
-        <v>3.17748117446899</v>
+        <v>3.17748141288757</v>
       </c>
       <c r="H541" t="n">
         <v>159569</v>
@@ -16087,7 +16087,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G542" t="n">
-        <v>3.20387816429138</v>
+        <v>3.20387768745422</v>
       </c>
       <c r="H542" t="n">
         <v>307336</v>
@@ -16116,7 +16116,7 @@
         <v>4.77500009536743</v>
       </c>
       <c r="G543" t="n">
-        <v>3.15108466148376</v>
+        <v>3.15108489990234</v>
       </c>
       <c r="H543" t="n">
         <v>428166</v>
@@ -16145,7 +16145,7 @@
         <v>4.74499988555908</v>
       </c>
       <c r="G544" t="n">
-        <v>3.13128757476807</v>
+        <v>3.13128709793091</v>
       </c>
       <c r="H544" t="n">
         <v>338813</v>
@@ -16203,7 +16203,7 @@
         <v>4.9850001335144</v>
       </c>
       <c r="G546" t="n">
-        <v>3.28966617584229</v>
+        <v>3.28966641426086</v>
       </c>
       <c r="H546" t="n">
         <v>250598</v>
@@ -16232,7 +16232,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G547" t="n">
-        <v>3.31936264038086</v>
+        <v>3.31936287879944</v>
       </c>
       <c r="H547" t="n">
         <v>180843</v>
@@ -16290,7 +16290,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G549" t="n">
-        <v>3.28636693954468</v>
+        <v>3.28636717796326</v>
       </c>
       <c r="H549" t="n">
         <v>71591</v>
@@ -16348,7 +16348,7 @@
         <v>4.94500017166138</v>
       </c>
       <c r="G551" t="n">
-        <v>3.26327013969421</v>
+        <v>3.26327037811279</v>
       </c>
       <c r="H551" t="n">
         <v>121766</v>
@@ -16377,7 +16377,7 @@
         <v>4.96500015258789</v>
       </c>
       <c r="G552" t="n">
-        <v>3.2764687538147</v>
+        <v>3.27646851539612</v>
       </c>
       <c r="H552" t="n">
         <v>244304</v>
@@ -16406,7 +16406,7 @@
         <v>4.93499994277954</v>
       </c>
       <c r="G553" t="n">
-        <v>3.25667095184326</v>
+        <v>3.25667071342468</v>
       </c>
       <c r="H553" t="n">
         <v>159508</v>
@@ -16435,7 +16435,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G554" t="n">
-        <v>3.24017286300659</v>
+        <v>3.24017310142517</v>
       </c>
       <c r="H554" t="n">
         <v>201398</v>
@@ -16464,7 +16464,7 @@
         <v>4.94500017166138</v>
       </c>
       <c r="G555" t="n">
-        <v>3.26327013969421</v>
+        <v>3.26327037811279</v>
       </c>
       <c r="H555" t="n">
         <v>605541</v>
@@ -16522,7 +16522,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G557" t="n">
-        <v>3.31936264038086</v>
+        <v>3.31936287879944</v>
       </c>
       <c r="H557" t="n">
         <v>705472</v>
@@ -16609,7 +16609,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G560" t="n">
-        <v>3.22037601470947</v>
+        <v>3.22037553787231</v>
       </c>
       <c r="H560" t="n">
         <v>229037</v>
@@ -16638,7 +16638,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G561" t="n">
-        <v>3.20717740058899</v>
+        <v>3.20717763900757</v>
       </c>
       <c r="H561" t="n">
         <v>164491</v>
@@ -16667,7 +16667,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G562" t="n">
-        <v>3.21377635002136</v>
+        <v>3.21377611160278</v>
       </c>
       <c r="H562" t="n">
         <v>261298</v>
@@ -16696,7 +16696,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G563" t="n">
-        <v>3.2335741519928</v>
+        <v>3.23357391357422</v>
       </c>
       <c r="H563" t="n">
         <v>381715</v>
@@ -16754,7 +16754,7 @@
         <v>4.94500017166138</v>
       </c>
       <c r="G565" t="n">
-        <v>3.26327013969421</v>
+        <v>3.26327037811279</v>
       </c>
       <c r="H565" t="n">
         <v>267459</v>
@@ -16812,7 +16812,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G567" t="n">
-        <v>3.33256149291992</v>
+        <v>3.33256053924561</v>
       </c>
       <c r="H567" t="n">
         <v>658583</v>
@@ -16841,7 +16841,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G568" t="n">
-        <v>3.33916044235229</v>
+        <v>3.33915996551514</v>
       </c>
       <c r="H568" t="n">
         <v>424813</v>
@@ -16870,7 +16870,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G569" t="n">
-        <v>3.35235810279846</v>
+        <v>3.35235857963562</v>
       </c>
       <c r="H569" t="n">
         <v>293303</v>
@@ -16899,7 +16899,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G570" t="n">
-        <v>3.33256149291992</v>
+        <v>3.33256053924561</v>
       </c>
       <c r="H570" t="n">
         <v>189800</v>
@@ -16928,7 +16928,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G571" t="n">
-        <v>3.35895752906799</v>
+        <v>3.35895776748657</v>
       </c>
       <c r="H571" t="n">
         <v>455695</v>
@@ -16957,7 +16957,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G572" t="n">
-        <v>3.36555624008179</v>
+        <v>3.36555647850037</v>
       </c>
       <c r="H572" t="n">
         <v>211464</v>
@@ -17073,7 +17073,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G576" t="n">
-        <v>3.31936264038086</v>
+        <v>3.31936287879944</v>
       </c>
       <c r="H576" t="n">
         <v>553332</v>
@@ -17131,7 +17131,7 @@
         <v>4.92500019073486</v>
       </c>
       <c r="G578" t="n">
-        <v>3.25007176399231</v>
+        <v>3.25007200241089</v>
       </c>
       <c r="H578" t="n">
         <v>582874</v>
@@ -17160,7 +17160,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G579" t="n">
-        <v>3.24677205085754</v>
+        <v>3.24677228927612</v>
       </c>
       <c r="H579" t="n">
         <v>142859</v>
@@ -17189,7 +17189,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G580" t="n">
-        <v>3.2335741519928</v>
+        <v>3.23357391357422</v>
       </c>
       <c r="H580" t="n">
         <v>430468</v>
@@ -17218,7 +17218,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G581" t="n">
-        <v>3.22037601470947</v>
+        <v>3.22037553787231</v>
       </c>
       <c r="H581" t="n">
         <v>211872</v>
@@ -17247,7 +17247,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G582" t="n">
-        <v>3.24677205085754</v>
+        <v>3.24677228927612</v>
       </c>
       <c r="H582" t="n">
         <v>266759</v>
@@ -17305,7 +17305,7 @@
         <v>4.92500019073486</v>
       </c>
       <c r="G584" t="n">
-        <v>3.25007176399231</v>
+        <v>3.25007200241089</v>
       </c>
       <c r="H584" t="n">
         <v>253849</v>
@@ -17334,7 +17334,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G585" t="n">
-        <v>3.22697472572327</v>
+        <v>3.22697496414185</v>
       </c>
       <c r="H585" t="n">
         <v>392732</v>
@@ -17363,7 +17363,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G586" t="n">
-        <v>3.2335741519928</v>
+        <v>3.23357391357422</v>
       </c>
       <c r="H586" t="n">
         <v>232065</v>
@@ -17392,7 +17392,7 @@
         <v>4.96500015258789</v>
       </c>
       <c r="G587" t="n">
-        <v>3.2764687538147</v>
+        <v>3.27646851539612</v>
       </c>
       <c r="H587" t="n">
         <v>337593</v>
@@ -17450,7 +17450,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G589" t="n">
-        <v>3.20387816429138</v>
+        <v>3.20387768745422</v>
       </c>
       <c r="H589" t="n">
         <v>262105</v>
@@ -17479,7 +17479,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G590" t="n">
-        <v>3.27316904067993</v>
+        <v>3.27316880226135</v>
       </c>
       <c r="H590" t="n">
         <v>306419</v>
@@ -17508,7 +17508,7 @@
         <v>4.96500015258789</v>
       </c>
       <c r="G591" t="n">
-        <v>3.2764687538147</v>
+        <v>3.27646851539612</v>
       </c>
       <c r="H591" t="n">
         <v>197893</v>
@@ -17537,7 +17537,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G592" t="n">
-        <v>3.20717740058899</v>
+        <v>3.20717763900757</v>
       </c>
       <c r="H592" t="n">
         <v>433144</v>
@@ -17566,7 +17566,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G593" t="n">
-        <v>2.98610663414001</v>
+        <v>2.98610687255859</v>
       </c>
       <c r="H593" t="n">
         <v>1045262</v>
@@ -17595,7 +17595,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G594" t="n">
-        <v>2.93001437187195</v>
+        <v>2.93001389503479</v>
       </c>
       <c r="H594" t="n">
         <v>554636</v>
@@ -17624,7 +17624,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G595" t="n">
-        <v>3.0092031955719</v>
+        <v>3.00920343399048</v>
       </c>
       <c r="H595" t="n">
         <v>548032</v>
@@ -17653,7 +17653,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G596" t="n">
-        <v>2.94321227073669</v>
+        <v>2.94321203231812</v>
       </c>
       <c r="H596" t="n">
         <v>369522</v>
@@ -17682,7 +17682,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G597" t="n">
-        <v>3.03559970855713</v>
+        <v>3.03560018539429</v>
       </c>
       <c r="H597" t="n">
         <v>486651</v>
@@ -17711,7 +17711,7 @@
         <v>4.7350001335144</v>
       </c>
       <c r="G598" t="n">
-        <v>3.12468838691711</v>
+        <v>3.12468814849854</v>
       </c>
       <c r="H598" t="n">
         <v>362477</v>
@@ -17740,7 +17740,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G599" t="n">
-        <v>2.9993052482605</v>
+        <v>2.99930477142334</v>
       </c>
       <c r="H599" t="n">
         <v>459016</v>
@@ -17769,7 +17769,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G600" t="n">
-        <v>2.98940634727478</v>
+        <v>2.98940658569336</v>
       </c>
       <c r="H600" t="n">
         <v>483306</v>
@@ -17798,7 +17798,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G601" t="n">
-        <v>3.03559970855713</v>
+        <v>3.03560018539429</v>
       </c>
       <c r="H601" t="n">
         <v>278051</v>
@@ -17827,7 +17827,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G602" t="n">
-        <v>2.9993052482605</v>
+        <v>2.99930477142334</v>
       </c>
       <c r="H602" t="n">
         <v>294153</v>
@@ -17856,7 +17856,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G603" t="n">
-        <v>3.00260448455811</v>
+        <v>3.00260424613953</v>
       </c>
       <c r="H603" t="n">
         <v>113692</v>
@@ -18030,7 +18030,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G609" t="n">
-        <v>3.06859540939331</v>
+        <v>3.06859588623047</v>
       </c>
       <c r="H609" t="n">
         <v>181645</v>
@@ -18059,7 +18059,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G610" t="n">
-        <v>3.06859540939331</v>
+        <v>3.06859588623047</v>
       </c>
       <c r="H610" t="n">
         <v>433730</v>
@@ -18088,7 +18088,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G611" t="n">
-        <v>3.08839273452759</v>
+        <v>3.08839321136475</v>
       </c>
       <c r="H611" t="n">
         <v>391802</v>
@@ -18146,7 +18146,7 @@
         <v>4.75</v>
       </c>
       <c r="G613" t="n">
-        <v>3.13458681106567</v>
+        <v>3.13458728790283</v>
       </c>
       <c r="H613" t="n">
         <v>239817</v>
@@ -18175,7 +18175,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G614" t="n">
-        <v>3.17418146133423</v>
+        <v>3.17418169975281</v>
       </c>
       <c r="H614" t="n">
         <v>516589</v>
@@ -18204,7 +18204,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G615" t="n">
-        <v>3.17418146133423</v>
+        <v>3.17418169975281</v>
       </c>
       <c r="H615" t="n">
         <v>772590</v>
@@ -18262,7 +18262,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G617" t="n">
-        <v>3.20717740058899</v>
+        <v>3.20717763900757</v>
       </c>
       <c r="H617" t="n">
         <v>392932</v>
@@ -18291,7 +18291,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G618" t="n">
-        <v>3.18737983703613</v>
+        <v>3.18738031387329</v>
       </c>
       <c r="H618" t="n">
         <v>209724</v>
@@ -18349,7 +18349,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G620" t="n">
-        <v>3.18078064918518</v>
+        <v>3.18078088760376</v>
       </c>
       <c r="H620" t="n">
         <v>233302</v>
@@ -18378,7 +18378,7 @@
         <v>4.875</v>
       </c>
       <c r="G621" t="n">
-        <v>3.21707582473755</v>
+        <v>3.21707630157471</v>
       </c>
       <c r="H621" t="n">
         <v>150933</v>
@@ -18407,7 +18407,7 @@
         <v>4.81500005722046</v>
       </c>
       <c r="G622" t="n">
-        <v>3.17748117446899</v>
+        <v>3.17748141288757</v>
       </c>
       <c r="H622" t="n">
         <v>343744</v>
@@ -18436,7 +18436,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G623" t="n">
-        <v>3.16758322715759</v>
+        <v>3.16758275032043</v>
       </c>
       <c r="H623" t="n">
         <v>230869</v>
@@ -18465,7 +18465,7 @@
         <v>4.77500009536743</v>
       </c>
       <c r="G624" t="n">
-        <v>3.15108466148376</v>
+        <v>3.15108489990234</v>
       </c>
       <c r="H624" t="n">
         <v>214584</v>
@@ -18494,7 +18494,7 @@
         <v>4.74499988555908</v>
       </c>
       <c r="G625" t="n">
-        <v>3.13128757476807</v>
+        <v>3.13128709793091</v>
       </c>
       <c r="H625" t="n">
         <v>321351</v>
@@ -18552,7 +18552,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G627" t="n">
-        <v>3.17418146133423</v>
+        <v>3.17418169975281</v>
       </c>
       <c r="H627" t="n">
         <v>513181</v>
@@ -18610,7 +18610,7 @@
         <v>4.75500011444092</v>
       </c>
       <c r="G629" t="n">
-        <v>3.13788652420044</v>
+        <v>3.13788628578186</v>
       </c>
       <c r="H629" t="n">
         <v>196694</v>
@@ -18697,7 +18697,7 @@
         <v>4.75</v>
       </c>
       <c r="G632" t="n">
-        <v>3.13458681106567</v>
+        <v>3.13458728790283</v>
       </c>
       <c r="H632" t="n">
         <v>285250</v>
@@ -18726,7 +18726,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G633" t="n">
-        <v>3.16758322715759</v>
+        <v>3.16758275032043</v>
       </c>
       <c r="H633" t="n">
         <v>124776</v>
@@ -18755,7 +18755,7 @@
         <v>4.80499982833862</v>
       </c>
       <c r="G634" t="n">
-        <v>3.17088198661804</v>
+        <v>3.17088174819946</v>
       </c>
       <c r="H634" t="n">
         <v>318243</v>
@@ -18784,7 +18784,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G635" t="n">
-        <v>3.20057821273804</v>
+        <v>3.20057797431946</v>
       </c>
       <c r="H635" t="n">
         <v>355617</v>
@@ -18813,7 +18813,7 @@
         <v>4.88500022888184</v>
       </c>
       <c r="G636" t="n">
-        <v>3.22367548942566</v>
+        <v>3.22367525100708</v>
       </c>
       <c r="H636" t="n">
         <v>347918</v>
@@ -18871,7 +18871,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G638" t="n">
-        <v>3.31936264038086</v>
+        <v>3.31936287879944</v>
       </c>
       <c r="H638" t="n">
         <v>324782</v>
@@ -18900,7 +18900,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G639" t="n">
-        <v>3.35895752906799</v>
+        <v>3.35895776748657</v>
       </c>
       <c r="H639" t="n">
         <v>367299</v>
@@ -18929,7 +18929,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G640" t="n">
-        <v>3.33916044235229</v>
+        <v>3.33915996551514</v>
       </c>
       <c r="H640" t="n">
         <v>413174</v>
@@ -18958,7 +18958,7 @@
         <v>5.25</v>
       </c>
       <c r="G641" t="n">
-        <v>3.46454381942749</v>
+        <v>3.46454334259033</v>
       </c>
       <c r="H641" t="n">
         <v>1092587</v>
@@ -19045,7 +19045,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G644" t="n">
-        <v>3.55033183097839</v>
+        <v>3.55033230781555</v>
       </c>
       <c r="H644" t="n">
         <v>810423</v>
@@ -19074,7 +19074,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G645" t="n">
-        <v>3.5437331199646</v>
+        <v>3.54373264312744</v>
       </c>
       <c r="H645" t="n">
         <v>270515</v>
@@ -19103,7 +19103,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G646" t="n">
-        <v>3.53053498268127</v>
+        <v>3.5305347442627</v>
       </c>
       <c r="H646" t="n">
         <v>298286</v>
@@ -19132,7 +19132,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G647" t="n">
-        <v>3.55693101882935</v>
+        <v>3.5569314956665</v>
       </c>
       <c r="H647" t="n">
         <v>182303</v>
@@ -19219,7 +19219,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G650" t="n">
-        <v>3.58332800865173</v>
+        <v>3.58332753181458</v>
       </c>
       <c r="H650" t="n">
         <v>463002</v>
@@ -19248,7 +19248,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G651" t="n">
-        <v>3.58332800865173</v>
+        <v>3.58332753181458</v>
       </c>
       <c r="H651" t="n">
         <v>259823</v>
@@ -19364,7 +19364,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G655" t="n">
-        <v>3.56353044509888</v>
+        <v>3.5635302066803</v>
       </c>
       <c r="H655" t="n">
         <v>465278</v>
@@ -19393,7 +19393,7 @@
         <v>5.5</v>
       </c>
       <c r="G656" t="n">
-        <v>3.6295211315155</v>
+        <v>3.62952208518982</v>
       </c>
       <c r="H656" t="n">
         <v>522326</v>
@@ -19422,7 +19422,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G657" t="n">
-        <v>3.53053498268127</v>
+        <v>3.5305347442627</v>
       </c>
       <c r="H657" t="n">
         <v>819041</v>
@@ -19480,7 +19480,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G659" t="n">
-        <v>3.53053498268127</v>
+        <v>3.5305347442627</v>
       </c>
       <c r="H659" t="n">
         <v>882957</v>
@@ -19509,7 +19509,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G660" t="n">
-        <v>3.53053498268127</v>
+        <v>3.5305347442627</v>
       </c>
       <c r="H660" t="n">
         <v>685814</v>
@@ -19538,7 +19538,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G661" t="n">
-        <v>3.52393555641174</v>
+        <v>3.52393579483032</v>
       </c>
       <c r="H661" t="n">
         <v>322262</v>
@@ -19567,7 +19567,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G662" t="n">
-        <v>3.56353044509888</v>
+        <v>3.5635302066803</v>
       </c>
       <c r="H662" t="n">
         <v>423318</v>
@@ -19596,7 +19596,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G663" t="n">
-        <v>3.51733589172363</v>
+        <v>3.51733636856079</v>
       </c>
       <c r="H663" t="n">
         <v>264447</v>
@@ -19625,7 +19625,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G664" t="n">
-        <v>3.47114300727844</v>
+        <v>3.47114253044128</v>
       </c>
       <c r="H664" t="n">
         <v>357968</v>
@@ -19654,7 +19654,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G665" t="n">
-        <v>3.44474577903748</v>
+        <v>3.44474625587463</v>
       </c>
       <c r="H665" t="n">
         <v>534929</v>
@@ -19683,7 +19683,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G666" t="n">
-        <v>3.47114300727844</v>
+        <v>3.47114253044128</v>
       </c>
       <c r="H666" t="n">
         <v>307259</v>
@@ -19712,7 +19712,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G667" t="n">
-        <v>3.53053498268127</v>
+        <v>3.5305347442627</v>
       </c>
       <c r="H667" t="n">
         <v>427480</v>
@@ -19741,7 +19741,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G668" t="n">
-        <v>3.55693101882935</v>
+        <v>3.5569314956665</v>
       </c>
       <c r="H668" t="n">
         <v>462341</v>
@@ -19799,7 +19799,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G670" t="n">
-        <v>3.57672929763794</v>
+        <v>3.5767285823822</v>
       </c>
       <c r="H670" t="n">
         <v>1287483</v>
@@ -19857,7 +19857,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G672" t="n">
-        <v>3.60312533378601</v>
+        <v>3.60312509536743</v>
       </c>
       <c r="H672" t="n">
         <v>642386</v>
@@ -19886,7 +19886,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G673" t="n">
-        <v>3.5437331199646</v>
+        <v>3.54373264312744</v>
       </c>
       <c r="H673" t="n">
         <v>753716</v>
@@ -19915,7 +19915,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G674" t="n">
-        <v>3.53053498268127</v>
+        <v>3.5305347442627</v>
       </c>
       <c r="H674" t="n">
         <v>371452</v>
@@ -19973,7 +19973,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G676" t="n">
-        <v>3.55033183097839</v>
+        <v>3.55033230781555</v>
       </c>
       <c r="H676" t="n">
         <v>194556</v>
@@ -20031,7 +20031,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G678" t="n">
-        <v>3.51733589172363</v>
+        <v>3.51733636856079</v>
       </c>
       <c r="H678" t="n">
         <v>447708</v>
@@ -20060,7 +20060,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G679" t="n">
-        <v>3.49753928184509</v>
+        <v>3.49753975868225</v>
       </c>
       <c r="H679" t="n">
         <v>182643</v>
@@ -20089,7 +20089,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G680" t="n">
-        <v>3.5437331199646</v>
+        <v>3.54373264312744</v>
       </c>
       <c r="H680" t="n">
         <v>144245</v>
@@ -20118,7 +20118,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G681" t="n">
-        <v>3.53053498268127</v>
+        <v>3.5305347442627</v>
       </c>
       <c r="H681" t="n">
         <v>280241</v>
@@ -20176,7 +20176,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G683" t="n">
-        <v>3.49093961715698</v>
+        <v>3.49093985557556</v>
       </c>
       <c r="H683" t="n">
         <v>378018</v>
@@ -20205,7 +20205,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G684" t="n">
-        <v>3.50413846969604</v>
+        <v>3.50413775444031</v>
       </c>
       <c r="H684" t="n">
         <v>311667</v>
@@ -20234,7 +20234,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G685" t="n">
-        <v>3.55033183097839</v>
+        <v>3.55033230781555</v>
       </c>
       <c r="H685" t="n">
         <v>218627</v>
@@ -20263,7 +20263,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G686" t="n">
-        <v>3.53053498268127</v>
+        <v>3.5305347442627</v>
       </c>
       <c r="H686" t="n">
         <v>333103</v>
@@ -20292,7 +20292,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G687" t="n">
-        <v>3.51733589172363</v>
+        <v>3.51733636856079</v>
       </c>
       <c r="H687" t="n">
         <v>264164</v>
@@ -20321,7 +20321,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G688" t="n">
-        <v>3.49753928184509</v>
+        <v>3.49753975868225</v>
       </c>
       <c r="H688" t="n">
         <v>161714</v>
@@ -20350,7 +20350,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G689" t="n">
-        <v>3.47774171829224</v>
+        <v>3.47774195671082</v>
       </c>
       <c r="H689" t="n">
         <v>116557</v>
@@ -20379,7 +20379,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G690" t="n">
-        <v>3.52393555641174</v>
+        <v>3.52393579483032</v>
       </c>
       <c r="H690" t="n">
         <v>131707</v>
@@ -20408,7 +20408,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G691" t="n">
-        <v>3.5437331199646</v>
+        <v>3.54373264312744</v>
       </c>
       <c r="H691" t="n">
         <v>183512</v>
@@ -20437,7 +20437,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G692" t="n">
-        <v>3.50413846969604</v>
+        <v>3.50413775444031</v>
       </c>
       <c r="H692" t="n">
         <v>281512</v>
@@ -20466,7 +20466,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G693" t="n">
-        <v>3.49753928184509</v>
+        <v>3.49753975868225</v>
       </c>
       <c r="H693" t="n">
         <v>236744</v>
@@ -20495,7 +20495,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G694" t="n">
-        <v>3.53053498268127</v>
+        <v>3.5305347442627</v>
       </c>
       <c r="H694" t="n">
         <v>305166</v>
@@ -20553,7 +20553,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G696" t="n">
-        <v>3.55693101882935</v>
+        <v>3.5569314956665</v>
       </c>
       <c r="H696" t="n">
         <v>284871</v>
@@ -20582,7 +20582,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G697" t="n">
-        <v>3.53053498268127</v>
+        <v>3.5305347442627</v>
       </c>
       <c r="H697" t="n">
         <v>2007774</v>
@@ -20611,7 +20611,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G698" t="n">
-        <v>3.51733589172363</v>
+        <v>3.51733636856079</v>
       </c>
       <c r="H698" t="n">
         <v>584668</v>
@@ -20640,7 +20640,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G699" t="n">
-        <v>3.55693101882935</v>
+        <v>3.5569314956665</v>
       </c>
       <c r="H699" t="n">
         <v>963684</v>
@@ -20669,7 +20669,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G700" t="n">
-        <v>3.56353044509888</v>
+        <v>3.5635302066803</v>
       </c>
       <c r="H700" t="n">
         <v>462682</v>
@@ -20727,7 +20727,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G702" t="n">
-        <v>3.58992719650269</v>
+        <v>3.58992695808411</v>
       </c>
       <c r="H702" t="n">
         <v>385089</v>
@@ -20756,7 +20756,7 @@
         <v>5.5</v>
       </c>
       <c r="G703" t="n">
-        <v>3.6295211315155</v>
+        <v>3.62952208518982</v>
       </c>
       <c r="H703" t="n">
         <v>607552</v>
@@ -20785,7 +20785,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G704" t="n">
-        <v>3.70871162414551</v>
+        <v>3.70871090888977</v>
       </c>
       <c r="H704" t="n">
         <v>835923</v>
@@ -20814,7 +20814,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G705" t="n">
-        <v>3.72850894927979</v>
+        <v>3.72850847244263</v>
       </c>
       <c r="H705" t="n">
         <v>1055303</v>
@@ -20843,7 +20843,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G706" t="n">
-        <v>3.74170684814453</v>
+        <v>3.74170660972595</v>
       </c>
       <c r="H706" t="n">
         <v>599094</v>
@@ -20872,7 +20872,7 @@
         <v>5.75</v>
       </c>
       <c r="G707" t="n">
-        <v>3.79450011253357</v>
+        <v>3.79450035095215</v>
       </c>
       <c r="H707" t="n">
         <v>1836747</v>
@@ -20901,7 +20901,7 @@
         <v>5.75</v>
       </c>
       <c r="G708" t="n">
-        <v>3.79450011253357</v>
+        <v>3.79450035095215</v>
       </c>
       <c r="H708" t="n">
         <v>1115236</v>
@@ -20959,7 +20959,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G710" t="n">
-        <v>3.74830555915833</v>
+        <v>3.74830603599548</v>
       </c>
       <c r="H710" t="n">
         <v>838597</v>
@@ -20988,7 +20988,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G711" t="n">
-        <v>3.66251730918884</v>
+        <v>3.66251754760742</v>
       </c>
       <c r="H711" t="n">
         <v>543254</v>
@@ -21017,7 +21017,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G712" t="n">
-        <v>3.66251730918884</v>
+        <v>3.66251754760742</v>
       </c>
       <c r="H712" t="n">
         <v>667564</v>
@@ -21046,7 +21046,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G713" t="n">
-        <v>3.68891406059265</v>
+        <v>3.68891382217407</v>
       </c>
       <c r="H713" t="n">
         <v>447125</v>
@@ -21075,7 +21075,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G714" t="n">
-        <v>3.70871162414551</v>
+        <v>3.70871090888977</v>
       </c>
       <c r="H714" t="n">
         <v>295322</v>
@@ -21133,7 +21133,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G716" t="n">
-        <v>3.74830555915833</v>
+        <v>3.74830603599548</v>
       </c>
       <c r="H716" t="n">
         <v>696688</v>
@@ -21162,7 +21162,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G717" t="n">
-        <v>3.74830555915833</v>
+        <v>3.74830603599548</v>
       </c>
       <c r="H717" t="n">
         <v>330391</v>
@@ -21249,7 +21249,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G720" t="n">
-        <v>3.82749557495117</v>
+        <v>3.82749581336975</v>
       </c>
       <c r="H720" t="n">
         <v>1225246</v>
@@ -21278,7 +21278,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G721" t="n">
-        <v>3.82749557495117</v>
+        <v>3.82749581336975</v>
       </c>
       <c r="H721" t="n">
         <v>435487</v>
@@ -21307,7 +21307,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G722" t="n">
-        <v>3.8736891746521</v>
+        <v>3.87368941307068</v>
       </c>
       <c r="H722" t="n">
         <v>580517</v>
@@ -21394,7 +21394,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G725" t="n">
-        <v>4.03866767883301</v>
+        <v>4.03866815567017</v>
       </c>
       <c r="H725" t="n">
         <v>1308208</v>
@@ -21423,7 +21423,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G726" t="n">
-        <v>4.04526710510254</v>
+        <v>4.0452675819397</v>
       </c>
       <c r="H726" t="n">
         <v>598369</v>
@@ -21452,7 +21452,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G727" t="n">
-        <v>3.99247407913208</v>
+        <v>3.9924738407135</v>
       </c>
       <c r="H727" t="n">
         <v>872961</v>
@@ -21539,7 +21539,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G730" t="n">
-        <v>3.84729337692261</v>
+        <v>3.84729313850403</v>
       </c>
       <c r="H730" t="n">
         <v>878154</v>
@@ -21568,7 +21568,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G731" t="n">
-        <v>3.75490474700928</v>
+        <v>3.75490570068359</v>
       </c>
       <c r="H731" t="n">
         <v>972068</v>
@@ -21597,7 +21597,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G732" t="n">
-        <v>3.64931917190552</v>
+        <v>3.6493194103241</v>
       </c>
       <c r="H732" t="n">
         <v>1140649</v>
@@ -21655,7 +21655,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G734" t="n">
-        <v>3.55693101882935</v>
+        <v>3.5569314956665</v>
       </c>
       <c r="H734" t="n">
         <v>945739</v>
@@ -21713,7 +21713,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G736" t="n">
-        <v>3.47774171829224</v>
+        <v>3.47774195671082</v>
       </c>
       <c r="H736" t="n">
         <v>603387</v>
@@ -21771,7 +21771,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G738" t="n">
-        <v>3.06859540939331</v>
+        <v>3.06859588623047</v>
       </c>
       <c r="H738" t="n">
         <v>1138697</v>
@@ -21887,7 +21887,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G742" t="n">
-        <v>2.90361738204956</v>
+        <v>2.90361762046814</v>
       </c>
       <c r="H742" t="n">
         <v>1392043</v>
@@ -21916,7 +21916,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G743" t="n">
-        <v>2.76503539085388</v>
+        <v>2.76503586769104</v>
       </c>
       <c r="H743" t="n">
         <v>1314392</v>
@@ -21945,7 +21945,7 @@
         <v>4.14499998092651</v>
       </c>
       <c r="G744" t="n">
-        <v>2.73533964157104</v>
+        <v>2.73533940315247</v>
       </c>
       <c r="H744" t="n">
         <v>1016883</v>
@@ -21974,7 +21974,7 @@
         <v>4.07499980926514</v>
       </c>
       <c r="G745" t="n">
-        <v>2.68914532661438</v>
+        <v>2.68914556503296</v>
       </c>
       <c r="H745" t="n">
         <v>431233</v>
@@ -22061,7 +22061,7 @@
         <v>4.56500005722046</v>
       </c>
       <c r="G748" t="n">
-        <v>3.01250314712524</v>
+        <v>3.01250267028809</v>
       </c>
       <c r="H748" t="n">
         <v>779278</v>
@@ -22090,7 +22090,7 @@
         <v>4.75</v>
       </c>
       <c r="G749" t="n">
-        <v>3.13458681106567</v>
+        <v>3.13458728790283</v>
       </c>
       <c r="H749" t="n">
         <v>627016</v>
@@ -22119,7 +22119,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G750" t="n">
-        <v>3.06859540939331</v>
+        <v>3.06859588623047</v>
       </c>
       <c r="H750" t="n">
         <v>518902</v>
@@ -22177,7 +22177,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G752" t="n">
-        <v>3.16758322715759</v>
+        <v>3.16758275032043</v>
       </c>
       <c r="H752" t="n">
         <v>382070</v>
@@ -22206,7 +22206,7 @@
         <v>4.43499994277954</v>
       </c>
       <c r="G753" t="n">
-        <v>2.92671465873718</v>
+        <v>2.9267144203186</v>
       </c>
       <c r="H753" t="n">
         <v>370305</v>
@@ -22409,7 +22409,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G760" t="n">
-        <v>3.33916044235229</v>
+        <v>3.33915996551514</v>
       </c>
       <c r="H760" t="n">
         <v>280545</v>
@@ -22438,7 +22438,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G761" t="n">
-        <v>3.36555624008179</v>
+        <v>3.36555647850037</v>
       </c>
       <c r="H761" t="n">
         <v>237082</v>
@@ -22554,7 +22554,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G765" t="n">
-        <v>3.08839273452759</v>
+        <v>3.08839321136475</v>
       </c>
       <c r="H765" t="n">
         <v>200989</v>
@@ -22641,7 +22641,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G768" t="n">
-        <v>3.11478924751282</v>
+        <v>3.11478972434998</v>
       </c>
       <c r="H768" t="n">
         <v>157163</v>
@@ -22757,7 +22757,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G772" t="n">
-        <v>3.24017286300659</v>
+        <v>3.24017310142517</v>
       </c>
       <c r="H772" t="n">
         <v>273705</v>
@@ -22786,7 +22786,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G773" t="n">
-        <v>3.24017286300659</v>
+        <v>3.24017310142517</v>
       </c>
       <c r="H773" t="n">
         <v>440452</v>
@@ -22844,7 +22844,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G775" t="n">
-        <v>3.00260448455811</v>
+        <v>3.00260424613953</v>
       </c>
       <c r="H775" t="n">
         <v>200490</v>
@@ -22902,7 +22902,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G777" t="n">
-        <v>3.0619969367981</v>
+        <v>3.06199622154236</v>
       </c>
       <c r="H777" t="n">
         <v>234472</v>
@@ -22960,7 +22960,7 @@
         <v>4.82499980926514</v>
       </c>
       <c r="G779" t="n">
-        <v>3.18408036231995</v>
+        <v>3.18407988548279</v>
       </c>
       <c r="H779" t="n">
         <v>351158</v>
@@ -22989,7 +22989,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G780" t="n">
-        <v>3.17418146133423</v>
+        <v>3.17418169975281</v>
       </c>
       <c r="H780" t="n">
         <v>293195</v>
@@ -23018,7 +23018,7 @@
         <v>4.75</v>
       </c>
       <c r="G781" t="n">
-        <v>3.13458681106567</v>
+        <v>3.13458728790283</v>
       </c>
       <c r="H781" t="n">
         <v>191048</v>
@@ -23047,7 +23047,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G782" t="n">
-        <v>3.31276345252991</v>
+        <v>3.31276297569275</v>
       </c>
       <c r="H782" t="n">
         <v>1399782</v>
@@ -23105,7 +23105,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G784" t="n">
-        <v>3.22697472572327</v>
+        <v>3.22697496414185</v>
       </c>
       <c r="H784" t="n">
         <v>256228</v>
@@ -23134,7 +23134,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G785" t="n">
-        <v>3.37875437736511</v>
+        <v>3.37875461578369</v>
       </c>
       <c r="H785" t="n">
         <v>243429</v>
@@ -23163,7 +23163,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G786" t="n">
-        <v>3.36555624008179</v>
+        <v>3.36555647850037</v>
       </c>
       <c r="H786" t="n">
         <v>387278</v>
@@ -23221,7 +23221,7 @@
         <v>4.92500019073486</v>
       </c>
       <c r="G788" t="n">
-        <v>3.25007176399231</v>
+        <v>3.25007200241089</v>
       </c>
       <c r="H788" t="n">
         <v>231338</v>
@@ -23250,7 +23250,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G789" t="n">
-        <v>3.30616474151611</v>
+        <v>3.30616497993469</v>
       </c>
       <c r="H789" t="n">
         <v>459020</v>
@@ -23279,7 +23279,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G790" t="n">
-        <v>3.33256149291992</v>
+        <v>3.33256053924561</v>
       </c>
       <c r="H790" t="n">
         <v>113121</v>
@@ -23337,7 +23337,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G792" t="n">
-        <v>3.44474577903748</v>
+        <v>3.44474625587463</v>
       </c>
       <c r="H792" t="n">
         <v>514453</v>
@@ -23395,7 +23395,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G794" t="n">
-        <v>3.52393555641174</v>
+        <v>3.52393579483032</v>
       </c>
       <c r="H794" t="n">
         <v>1051283</v>
@@ -23424,7 +23424,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G795" t="n">
-        <v>3.52393555641174</v>
+        <v>3.52393579483032</v>
       </c>
       <c r="H795" t="n">
         <v>712372</v>
@@ -23453,7 +23453,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G796" t="n">
-        <v>3.35235810279846</v>
+        <v>3.35235857963562</v>
       </c>
       <c r="H796" t="n">
         <v>2450292</v>
@@ -23482,7 +23482,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G797" t="n">
-        <v>3.37215542793274</v>
+        <v>3.37215566635132</v>
       </c>
       <c r="H797" t="n">
         <v>923096</v>
@@ -23511,7 +23511,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G798" t="n">
-        <v>3.37875437736511</v>
+        <v>3.37875461578369</v>
       </c>
       <c r="H798" t="n">
         <v>708103</v>
@@ -23540,7 +23540,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G799" t="n">
-        <v>3.4051513671875</v>
+        <v>3.40515112876892</v>
       </c>
       <c r="H799" t="n">
         <v>1096765</v>
@@ -23569,7 +23569,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G800" t="n">
-        <v>3.37875437736511</v>
+        <v>3.37875461578369</v>
       </c>
       <c r="H800" t="n">
         <v>1043083</v>
@@ -23656,7 +23656,7 @@
         <v>4.79500007629395</v>
       </c>
       <c r="G803" t="n">
-        <v>3.16428327560425</v>
+        <v>3.16428303718567</v>
       </c>
       <c r="H803" t="n">
         <v>715825</v>
@@ -23743,7 +23743,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G806" t="n">
-        <v>3.16758322715759</v>
+        <v>3.16758275032043</v>
       </c>
       <c r="H806" t="n">
         <v>651462</v>
@@ -23772,7 +23772,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G807" t="n">
-        <v>3.18078064918518</v>
+        <v>3.18078088760376</v>
       </c>
       <c r="H807" t="n">
         <v>428355</v>
@@ -23801,7 +23801,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G808" t="n">
-        <v>3.19397926330566</v>
+        <v>3.19397902488708</v>
       </c>
       <c r="H808" t="n">
         <v>503537</v>
@@ -23830,7 +23830,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G809" t="n">
-        <v>3.19397926330566</v>
+        <v>3.19397902488708</v>
       </c>
       <c r="H809" t="n">
         <v>372300</v>
@@ -23859,7 +23859,7 @@
         <v>4.7649998664856</v>
       </c>
       <c r="G810" t="n">
-        <v>3.14448523521423</v>
+        <v>3.14448595046997</v>
       </c>
       <c r="H810" t="n">
         <v>226133</v>
@@ -23888,7 +23888,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G811" t="n">
-        <v>3.21377635002136</v>
+        <v>3.21377611160278</v>
       </c>
       <c r="H811" t="n">
         <v>468615</v>
@@ -23917,7 +23917,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G812" t="n">
-        <v>3.14118599891663</v>
+        <v>3.14118576049805</v>
       </c>
       <c r="H812" t="n">
         <v>381021</v>
@@ -23946,7 +23946,7 @@
         <v>4.7649998664856</v>
       </c>
       <c r="G813" t="n">
-        <v>3.14448523521423</v>
+        <v>3.14448595046997</v>
       </c>
       <c r="H813" t="n">
         <v>264508</v>
@@ -24033,7 +24033,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G816" t="n">
-        <v>3.33916044235229</v>
+        <v>3.33915996551514</v>
       </c>
       <c r="H816" t="n">
         <v>453513</v>
@@ -24062,7 +24062,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G817" t="n">
-        <v>3.33916044235229</v>
+        <v>3.33915996551514</v>
       </c>
       <c r="H817" t="n">
         <v>318896</v>
@@ -24149,7 +24149,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G820" t="n">
-        <v>3.39855217933655</v>
+        <v>3.39855241775513</v>
       </c>
       <c r="H820" t="n">
         <v>289895</v>
@@ -24178,7 +24178,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G821" t="n">
-        <v>3.36555624008179</v>
+        <v>3.36555647850037</v>
       </c>
       <c r="H821" t="n">
         <v>199410</v>
@@ -24265,7 +24265,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G824" t="n">
-        <v>3.39855217933655</v>
+        <v>3.39855241775513</v>
       </c>
       <c r="H824" t="n">
         <v>274315</v>
@@ -24294,7 +24294,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G825" t="n">
-        <v>3.31936264038086</v>
+        <v>3.31936287879944</v>
       </c>
       <c r="H825" t="n">
         <v>473756</v>
@@ -24323,7 +24323,7 @@
         <v>4.92500019073486</v>
       </c>
       <c r="G826" t="n">
-        <v>3.25007176399231</v>
+        <v>3.25007200241089</v>
       </c>
       <c r="H826" t="n">
         <v>412226</v>
@@ -24352,7 +24352,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G827" t="n">
-        <v>3.27976775169373</v>
+        <v>3.27976727485657</v>
       </c>
       <c r="H827" t="n">
         <v>264280</v>
@@ -24410,7 +24410,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G829" t="n">
-        <v>3.30616474151611</v>
+        <v>3.30616497993469</v>
       </c>
       <c r="H829" t="n">
         <v>225351</v>
@@ -24497,7 +24497,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G832" t="n">
-        <v>3.33916044235229</v>
+        <v>3.33915996551514</v>
       </c>
       <c r="H832" t="n">
         <v>393150</v>
@@ -24555,7 +24555,7 @@
         <v>4.91499996185303</v>
       </c>
       <c r="G834" t="n">
-        <v>3.24347257614136</v>
+        <v>3.2434720993042</v>
       </c>
       <c r="H834" t="n">
         <v>218245</v>
@@ -24584,7 +24584,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G835" t="n">
-        <v>3.22697472572327</v>
+        <v>3.22697496414185</v>
       </c>
       <c r="H835" t="n">
         <v>219258</v>
@@ -24613,7 +24613,7 @@
         <v>4.88500022888184</v>
       </c>
       <c r="G836" t="n">
-        <v>3.22367548942566</v>
+        <v>3.22367525100708</v>
       </c>
       <c r="H836" t="n">
         <v>288743</v>
@@ -24642,7 +24642,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G837" t="n">
-        <v>3.19397926330566</v>
+        <v>3.19397902488708</v>
       </c>
       <c r="H837" t="n">
         <v>421170</v>
@@ -24671,7 +24671,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G838" t="n">
-        <v>3.18078064918518</v>
+        <v>3.18078088760376</v>
       </c>
       <c r="H838" t="n">
         <v>1642514</v>
@@ -24700,7 +24700,7 @@
         <v>4.81500005722046</v>
       </c>
       <c r="G839" t="n">
-        <v>3.17748117446899</v>
+        <v>3.17748141288757</v>
       </c>
       <c r="H839" t="n">
         <v>213007</v>
@@ -24729,7 +24729,7 @@
         <v>4.80499982833862</v>
       </c>
       <c r="G840" t="n">
-        <v>3.17088198661804</v>
+        <v>3.17088174819946</v>
       </c>
       <c r="H840" t="n">
         <v>190395</v>
@@ -24787,7 +24787,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G842" t="n">
-        <v>3.2335741519928</v>
+        <v>3.23357391357422</v>
       </c>
       <c r="H842" t="n">
         <v>311804</v>
@@ -24816,7 +24816,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G843" t="n">
-        <v>3.16758322715759</v>
+        <v>3.16758275032043</v>
       </c>
       <c r="H843" t="n">
         <v>356628</v>
@@ -24845,7 +24845,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G844" t="n">
-        <v>3.16098356246948</v>
+        <v>3.1609833240509</v>
       </c>
       <c r="H844" t="n">
         <v>191279</v>
@@ -24874,7 +24874,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G845" t="n">
-        <v>3.16758322715759</v>
+        <v>3.16758275032043</v>
       </c>
       <c r="H845" t="n">
         <v>298505</v>
@@ -24903,7 +24903,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G846" t="n">
-        <v>3.14778518676758</v>
+        <v>3.14778542518616</v>
       </c>
       <c r="H846" t="n">
         <v>388358</v>
@@ -24932,7 +24932,7 @@
         <v>4.75500011444092</v>
       </c>
       <c r="G847" t="n">
-        <v>3.13788652420044</v>
+        <v>3.13788628578186</v>
       </c>
       <c r="H847" t="n">
         <v>208092</v>
@@ -24961,7 +24961,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G848" t="n">
-        <v>3.14778518676758</v>
+        <v>3.14778542518616</v>
       </c>
       <c r="H848" t="n">
         <v>542694</v>
@@ -24990,7 +24990,7 @@
         <v>4.75</v>
       </c>
       <c r="G849" t="n">
-        <v>3.13458681106567</v>
+        <v>3.13458728790283</v>
       </c>
       <c r="H849" t="n">
         <v>210000</v>
@@ -25048,7 +25048,7 @@
         <v>4.61499977111816</v>
       </c>
       <c r="G851" t="n">
-        <v>3.04549837112427</v>
+        <v>3.04549860954285</v>
       </c>
       <c r="H851" t="n">
         <v>522574</v>
@@ -25077,7 +25077,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G852" t="n">
-        <v>3.06859540939331</v>
+        <v>3.06859588623047</v>
       </c>
       <c r="H852" t="n">
         <v>323856</v>
@@ -25164,7 +25164,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G855" t="n">
-        <v>3.0619969367981</v>
+        <v>3.06199622154236</v>
       </c>
       <c r="H855" t="n">
         <v>280411</v>
@@ -25251,7 +25251,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G858" t="n">
-        <v>3.06859540939331</v>
+        <v>3.06859588623047</v>
       </c>
       <c r="H858" t="n">
         <v>269563</v>
@@ -25280,7 +25280,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G859" t="n">
-        <v>3.12798810005188</v>
+        <v>3.12798762321472</v>
       </c>
       <c r="H859" t="n">
         <v>676151</v>
@@ -25367,7 +25367,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G862" t="n">
-        <v>3.07519459724426</v>
+        <v>3.07519507408142</v>
       </c>
       <c r="H862" t="n">
         <v>323471</v>
@@ -25396,7 +25396,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G863" t="n">
-        <v>3.00590372085571</v>
+        <v>3.00590395927429</v>
       </c>
       <c r="H863" t="n">
         <v>399027</v>
@@ -25425,7 +25425,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G864" t="n">
-        <v>2.98610663414001</v>
+        <v>2.98610687255859</v>
       </c>
       <c r="H864" t="n">
         <v>312895</v>
@@ -25599,7 +25599,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G870" t="n">
-        <v>3.0619969367981</v>
+        <v>3.06199622154236</v>
       </c>
       <c r="H870" t="n">
         <v>228965</v>
@@ -25657,7 +25657,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G872" t="n">
-        <v>3.06859540939331</v>
+        <v>3.06859588623047</v>
       </c>
       <c r="H872" t="n">
         <v>182329</v>
@@ -25686,7 +25686,7 @@
         <v>4.7649998664856</v>
       </c>
       <c r="G873" t="n">
-        <v>3.14448523521423</v>
+        <v>3.14448595046997</v>
       </c>
       <c r="H873" t="n">
         <v>387190</v>
@@ -25715,7 +25715,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G874" t="n">
-        <v>3.18078064918518</v>
+        <v>3.18078088760376</v>
       </c>
       <c r="H874" t="n">
         <v>1195620</v>
@@ -25744,7 +25744,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G875" t="n">
-        <v>3.14118599891663</v>
+        <v>3.14118576049805</v>
       </c>
       <c r="H875" t="n">
         <v>855482</v>
@@ -25773,7 +25773,7 @@
         <v>4.75500011444092</v>
       </c>
       <c r="G876" t="n">
-        <v>3.13788652420044</v>
+        <v>3.13788628578186</v>
       </c>
       <c r="H876" t="n">
         <v>519622</v>
@@ -25802,7 +25802,7 @@
         <v>4.7649998664856</v>
       </c>
       <c r="G877" t="n">
-        <v>3.14448523521423</v>
+        <v>3.14448595046997</v>
       </c>
       <c r="H877" t="n">
         <v>391893</v>
@@ -25831,7 +25831,7 @@
         <v>4.7649998664856</v>
       </c>
       <c r="G878" t="n">
-        <v>3.14448523521423</v>
+        <v>3.14448595046997</v>
       </c>
       <c r="H878" t="n">
         <v>399152</v>
@@ -25860,7 +25860,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G879" t="n">
-        <v>3.16098356246948</v>
+        <v>3.1609833240509</v>
       </c>
       <c r="H879" t="n">
         <v>310145</v>
@@ -25918,7 +25918,7 @@
         <v>4.74499988555908</v>
       </c>
       <c r="G881" t="n">
-        <v>3.13128757476807</v>
+        <v>3.13128709793091</v>
       </c>
       <c r="H881" t="n">
         <v>154996</v>
@@ -25947,7 +25947,7 @@
         <v>4.80499982833862</v>
       </c>
       <c r="G882" t="n">
-        <v>3.17088198661804</v>
+        <v>3.17088174819946</v>
       </c>
       <c r="H882" t="n">
         <v>237202</v>
@@ -25976,7 +25976,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G883" t="n">
-        <v>3.16098356246948</v>
+        <v>3.1609833240509</v>
       </c>
       <c r="H883" t="n">
         <v>249770</v>
@@ -26005,7 +26005,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G884" t="n">
-        <v>3.20717740058899</v>
+        <v>3.20717763900757</v>
       </c>
       <c r="H884" t="n">
         <v>338216</v>
@@ -26034,7 +26034,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G885" t="n">
-        <v>3.22697472572327</v>
+        <v>3.22697496414185</v>
       </c>
       <c r="H885" t="n">
         <v>428907</v>
@@ -26063,7 +26063,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G886" t="n">
-        <v>3.33256149291992</v>
+        <v>3.33256053924561</v>
       </c>
       <c r="H886" t="n">
         <v>506092</v>
@@ -26092,7 +26092,7 @@
         <v>4.93499994277954</v>
       </c>
       <c r="G887" t="n">
-        <v>3.25667095184326</v>
+        <v>3.25667071342468</v>
       </c>
       <c r="H887" t="n">
         <v>648324</v>
@@ -26150,7 +26150,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G889" t="n">
-        <v>3.17418146133423</v>
+        <v>3.17418169975281</v>
       </c>
       <c r="H889" t="n">
         <v>237516</v>
@@ -26179,7 +26179,7 @@
         <v>4.81500005722046</v>
       </c>
       <c r="G890" t="n">
-        <v>3.17748117446899</v>
+        <v>3.17748141288757</v>
       </c>
       <c r="H890" t="n">
         <v>161863</v>
@@ -26208,7 +26208,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G891" t="n">
-        <v>3.08839273452759</v>
+        <v>3.08839321136475</v>
       </c>
       <c r="H891" t="n">
         <v>265471</v>
@@ -26266,7 +26266,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G893" t="n">
-        <v>2.94321227073669</v>
+        <v>2.94321203231812</v>
       </c>
       <c r="H893" t="n">
         <v>532914</v>
@@ -26295,7 +26295,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G894" t="n">
-        <v>2.94321227073669</v>
+        <v>2.94321203231812</v>
       </c>
       <c r="H894" t="n">
         <v>431208</v>
@@ -26353,7 +26353,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G896" t="n">
-        <v>2.90361738204956</v>
+        <v>2.90361762046814</v>
       </c>
       <c r="H896" t="n">
         <v>334866</v>
@@ -26411,7 +26411,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G898" t="n">
-        <v>2.84422516822815</v>
+        <v>2.84422492980957</v>
       </c>
       <c r="H898" t="n">
         <v>384540</v>
@@ -26498,7 +26498,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G901" t="n">
-        <v>2.75843620300293</v>
+        <v>2.75843644142151</v>
       </c>
       <c r="H901" t="n">
         <v>275017</v>
@@ -26556,7 +26556,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G903" t="n">
-        <v>2.61985492706299</v>
+        <v>2.61985468864441</v>
       </c>
       <c r="H903" t="n">
         <v>608301</v>
@@ -26585,7 +26585,7 @@
         <v>3.95499992370605</v>
       </c>
       <c r="G904" t="n">
-        <v>2.60995626449585</v>
+        <v>2.60995602607727</v>
       </c>
       <c r="H904" t="n">
         <v>489725</v>
@@ -26643,7 +26643,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G906" t="n">
-        <v>2.5736608505249</v>
+        <v>2.57366108894348</v>
       </c>
       <c r="H906" t="n">
         <v>687548</v>
@@ -26730,7 +26730,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G909" t="n">
-        <v>2.78483295440674</v>
+        <v>2.78483319282532</v>
       </c>
       <c r="H909" t="n">
         <v>513399</v>
@@ -26788,7 +26788,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G911" t="n">
-        <v>2.96300959587097</v>
+        <v>2.96300935745239</v>
       </c>
       <c r="H911" t="n">
         <v>897054</v>
@@ -26817,7 +26817,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G912" t="n">
-        <v>3.00260448455811</v>
+        <v>3.00260424613953</v>
       </c>
       <c r="H912" t="n">
         <v>731447</v>
@@ -26846,7 +26846,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G913" t="n">
-        <v>2.89041948318481</v>
+        <v>2.89041900634766</v>
       </c>
       <c r="H913" t="n">
         <v>474241</v>
@@ -26875,7 +26875,7 @@
         <v>4.36499977111816</v>
       </c>
       <c r="G914" t="n">
-        <v>2.88052010536194</v>
+        <v>2.8805205821991</v>
       </c>
       <c r="H914" t="n">
         <v>372350</v>
@@ -26933,7 +26933,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G916" t="n">
-        <v>3.00590372085571</v>
+        <v>3.00590395927429</v>
       </c>
       <c r="H916" t="n">
         <v>523382</v>
@@ -26991,7 +26991,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G918" t="n">
-        <v>3.00260448455811</v>
+        <v>3.00260424613953</v>
       </c>
       <c r="H918" t="n">
         <v>403577</v>
@@ -27078,7 +27078,7 @@
         <v>4.61499977111816</v>
       </c>
       <c r="G921" t="n">
-        <v>3.04549837112427</v>
+        <v>3.04549860954285</v>
       </c>
       <c r="H921" t="n">
         <v>474140</v>
@@ -27107,7 +27107,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G922" t="n">
-        <v>3.14778518676758</v>
+        <v>3.14778542518616</v>
       </c>
       <c r="H922" t="n">
         <v>776068</v>
@@ -27136,7 +27136,7 @@
         <v>4.7649998664856</v>
       </c>
       <c r="G923" t="n">
-        <v>3.14448523521423</v>
+        <v>3.14448595046997</v>
       </c>
       <c r="H923" t="n">
         <v>433661</v>
@@ -27194,7 +27194,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G925" t="n">
-        <v>3.03559970855713</v>
+        <v>3.03560018539429</v>
       </c>
       <c r="H925" t="n">
         <v>470951</v>
@@ -27252,7 +27252,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G927" t="n">
-        <v>2.98610663414001</v>
+        <v>2.98610687255859</v>
       </c>
       <c r="H927" t="n">
         <v>359622</v>
@@ -27281,7 +27281,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G928" t="n">
-        <v>2.97290802001953</v>
+        <v>2.97290825843811</v>
       </c>
       <c r="H928" t="n">
         <v>263796</v>
@@ -27310,7 +27310,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G929" t="n">
-        <v>3.00590372085571</v>
+        <v>3.00590395927429</v>
       </c>
       <c r="H929" t="n">
         <v>317790</v>
@@ -27339,7 +27339,7 @@
         <v>4.53499984741211</v>
       </c>
       <c r="G930" t="n">
-        <v>2.99270558357239</v>
+        <v>2.99270534515381</v>
       </c>
       <c r="H930" t="n">
         <v>287051</v>
@@ -27368,7 +27368,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G931" t="n">
-        <v>3.0092031955719</v>
+        <v>3.00920343399048</v>
       </c>
       <c r="H931" t="n">
         <v>282480</v>
@@ -27397,7 +27397,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G932" t="n">
-        <v>2.95971012115479</v>
+        <v>2.95970988273621</v>
       </c>
       <c r="H932" t="n">
         <v>575971</v>
@@ -27426,7 +27426,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G933" t="n">
-        <v>2.94981122016907</v>
+        <v>2.94981098175049</v>
       </c>
       <c r="H933" t="n">
         <v>313998</v>
@@ -27513,7 +27513,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G936" t="n">
-        <v>2.93001437187195</v>
+        <v>2.93001389503479</v>
       </c>
       <c r="H936" t="n">
         <v>999582</v>
@@ -27542,7 +27542,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G937" t="n">
-        <v>3.00590372085571</v>
+        <v>3.00590395927429</v>
       </c>
       <c r="H937" t="n">
         <v>1076257</v>
@@ -27571,7 +27571,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G938" t="n">
-        <v>3.0619969367981</v>
+        <v>3.06199622154236</v>
       </c>
       <c r="H938" t="n">
         <v>428241</v>
@@ -27658,7 +27658,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G941" t="n">
-        <v>2.98940634727478</v>
+        <v>2.98940658569336</v>
       </c>
       <c r="H941" t="n">
         <v>199870</v>
@@ -27687,7 +27687,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G942" t="n">
-        <v>3.03559970855713</v>
+        <v>3.03560018539429</v>
       </c>
       <c r="H942" t="n">
         <v>224093</v>
@@ -27745,7 +27745,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G944" t="n">
-        <v>3.20057821273804</v>
+        <v>3.20057797431946</v>
       </c>
       <c r="H944" t="n">
         <v>931314</v>
@@ -27803,7 +27803,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G946" t="n">
-        <v>3.16098356246948</v>
+        <v>3.1609833240509</v>
       </c>
       <c r="H946" t="n">
         <v>519133</v>
@@ -27861,7 +27861,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G948" t="n">
-        <v>3.14118599891663</v>
+        <v>3.14118576049805</v>
       </c>
       <c r="H948" t="n">
         <v>365815</v>
@@ -27890,7 +27890,7 @@
         <v>4.7350001335144</v>
       </c>
       <c r="G949" t="n">
-        <v>3.12468838691711</v>
+        <v>3.12468814849854</v>
       </c>
       <c r="H949" t="n">
         <v>383014</v>
@@ -27948,7 +27948,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G951" t="n">
-        <v>3.20387816429138</v>
+        <v>3.20387768745422</v>
       </c>
       <c r="H951" t="n">
         <v>693773</v>
@@ -27977,7 +27977,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G952" t="n">
-        <v>3.08839273452759</v>
+        <v>3.08839321136475</v>
       </c>
       <c r="H952" t="n">
         <v>747349</v>
@@ -28006,7 +28006,7 @@
         <v>4.70499992370605</v>
       </c>
       <c r="G953" t="n">
-        <v>3.10489058494568</v>
+        <v>3.10489106178284</v>
       </c>
       <c r="H953" t="n">
         <v>500759</v>
@@ -28093,7 +28093,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G956" t="n">
-        <v>3.08839273452759</v>
+        <v>3.08839321136475</v>
       </c>
       <c r="H956" t="n">
         <v>211957</v>
@@ -28122,7 +28122,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G957" t="n">
-        <v>3.08839273452759</v>
+        <v>3.08839321136475</v>
       </c>
       <c r="H957" t="n">
         <v>217582</v>
@@ -28151,7 +28151,7 @@
         <v>4.70499992370605</v>
       </c>
       <c r="G958" t="n">
-        <v>3.10489058494568</v>
+        <v>3.10489106178284</v>
       </c>
       <c r="H958" t="n">
         <v>415020</v>
@@ -28180,7 +28180,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G959" t="n">
-        <v>3.06859540939331</v>
+        <v>3.06859588623047</v>
       </c>
       <c r="H959" t="n">
         <v>215020</v>
@@ -28209,7 +28209,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G960" t="n">
-        <v>3.00260448455811</v>
+        <v>3.00260424613953</v>
       </c>
       <c r="H960" t="n">
         <v>980745</v>
@@ -28238,7 +28238,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G961" t="n">
-        <v>2.94981122016907</v>
+        <v>2.94981098175049</v>
       </c>
       <c r="H961" t="n">
         <v>660132</v>
@@ -28267,7 +28267,7 @@
         <v>4.60500001907349</v>
       </c>
       <c r="G962" t="n">
-        <v>3.03889942169189</v>
+        <v>3.03889966011047</v>
       </c>
       <c r="H962" t="n">
         <v>455979</v>
@@ -28325,7 +28325,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G964" t="n">
-        <v>2.98610663414001</v>
+        <v>2.98610687255859</v>
       </c>
       <c r="H964" t="n">
         <v>433796</v>
@@ -28354,7 +28354,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G965" t="n">
-        <v>2.9993052482605</v>
+        <v>2.99930477142334</v>
       </c>
       <c r="H965" t="n">
         <v>244958</v>
@@ -28383,7 +28383,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G966" t="n">
-        <v>3.03559970855713</v>
+        <v>3.03560018539429</v>
       </c>
       <c r="H966" t="n">
         <v>243903</v>
@@ -28412,7 +28412,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G967" t="n">
-        <v>3.03559970855713</v>
+        <v>3.03560018539429</v>
       </c>
       <c r="H967" t="n">
         <v>139634</v>
@@ -28441,7 +28441,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G968" t="n">
-        <v>3.11478924751282</v>
+        <v>3.11478972434998</v>
       </c>
       <c r="H968" t="n">
         <v>633821</v>
@@ -28470,7 +28470,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G969" t="n">
-        <v>3.20057821273804</v>
+        <v>3.20057797431946</v>
       </c>
       <c r="H969" t="n">
         <v>732691</v>
@@ -28528,7 +28528,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G971" t="n">
-        <v>3.2335741519928</v>
+        <v>3.23357391357422</v>
       </c>
       <c r="H971" t="n">
         <v>836015</v>
@@ -28557,7 +28557,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G972" t="n">
-        <v>3.25337076187134</v>
+        <v>3.25337100028992</v>
       </c>
       <c r="H972" t="n">
         <v>446877</v>
@@ -28586,7 +28586,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G973" t="n">
-        <v>3.43154788017273</v>
+        <v>3.43154811859131</v>
       </c>
       <c r="H973" t="n">
         <v>1763486</v>
@@ -28615,7 +28615,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G974" t="n">
-        <v>3.6955132484436</v>
+        <v>3.69551301002502</v>
       </c>
       <c r="H974" t="n">
         <v>4422675</v>
@@ -28644,7 +28644,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G975" t="n">
-        <v>3.74830555915833</v>
+        <v>3.74830603599548</v>
       </c>
       <c r="H975" t="n">
         <v>2499166</v>
@@ -28702,7 +28702,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G977" t="n">
-        <v>3.71531105041504</v>
+        <v>3.71531081199646</v>
       </c>
       <c r="H977" t="n">
         <v>728136</v>
@@ -28731,7 +28731,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G978" t="n">
-        <v>3.60312533378601</v>
+        <v>3.60312509536743</v>
       </c>
       <c r="H978" t="n">
         <v>844032</v>
@@ -28760,7 +28760,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G979" t="n">
-        <v>3.70211243629456</v>
+        <v>3.70211219787598</v>
       </c>
       <c r="H979" t="n">
         <v>913001</v>
@@ -28789,7 +28789,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G980" t="n">
-        <v>3.66251730918884</v>
+        <v>3.66251754760742</v>
       </c>
       <c r="H980" t="n">
         <v>720088</v>
@@ -28876,7 +28876,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G983" t="n">
-        <v>3.62292242050171</v>
+        <v>3.62292194366455</v>
       </c>
       <c r="H983" t="n">
         <v>318403</v>
@@ -28905,7 +28905,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G984" t="n">
-        <v>3.62292242050171</v>
+        <v>3.62292194366455</v>
       </c>
       <c r="H984" t="n">
         <v>496843</v>
@@ -28934,7 +28934,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G985" t="n">
-        <v>3.58992719650269</v>
+        <v>3.58992695808411</v>
       </c>
       <c r="H985" t="n">
         <v>863819</v>
@@ -28963,7 +28963,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G986" t="n">
-        <v>3.68231439590454</v>
+        <v>3.68231463432312</v>
       </c>
       <c r="H986" t="n">
         <v>494261</v>
@@ -28992,7 +28992,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G987" t="n">
-        <v>3.66911625862122</v>
+        <v>3.66911673545837</v>
       </c>
       <c r="H987" t="n">
         <v>285276</v>
@@ -29021,7 +29021,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G988" t="n">
-        <v>3.66911625862122</v>
+        <v>3.66911673545837</v>
       </c>
       <c r="H988" t="n">
         <v>407898</v>
@@ -29079,7 +29079,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G990" t="n">
-        <v>3.66911625862122</v>
+        <v>3.66911673545837</v>
       </c>
       <c r="H990" t="n">
         <v>585702</v>
@@ -29108,7 +29108,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G991" t="n">
-        <v>3.66251730918884</v>
+        <v>3.66251754760742</v>
       </c>
       <c r="H991" t="n">
         <v>260821</v>
@@ -29195,7 +29195,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G994" t="n">
-        <v>4.05186605453491</v>
+        <v>4.05186557769775</v>
       </c>
       <c r="H994" t="n">
         <v>989635</v>
@@ -29224,7 +29224,7 @@
         <v>6.30999994277954</v>
       </c>
       <c r="G995" t="n">
-        <v>4.16405153274536</v>
+        <v>4.1640510559082</v>
       </c>
       <c r="H995" t="n">
         <v>875121</v>
@@ -29398,7 +29398,7 @@
         <v>6.3899998664856</v>
       </c>
       <c r="G1001" t="n">
-        <v>4.21684408187866</v>
+        <v>4.21684455871582</v>
       </c>
       <c r="H1001" t="n">
         <v>233792</v>
@@ -29485,7 +29485,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G1004" t="n">
-        <v>4.27623605728149</v>
+        <v>4.27623653411865</v>
       </c>
       <c r="H1004" t="n">
         <v>357589</v>
@@ -29601,7 +29601,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G1008" t="n">
-        <v>4.14882135391235</v>
+        <v>4.14882183074951</v>
       </c>
       <c r="H1008" t="n">
         <v>609400</v>
@@ -29659,7 +29659,7 @@
         <v>6.52500009536743</v>
       </c>
       <c r="G1010" t="n">
-        <v>4.31755352020264</v>
+        <v>4.31755399703979</v>
       </c>
       <c r="H1010" t="n">
         <v>694149</v>
@@ -29717,7 +29717,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G1012" t="n">
-        <v>4.31424474716187</v>
+        <v>4.31424522399902</v>
       </c>
       <c r="H1012" t="n">
         <v>833502</v>
@@ -29746,7 +29746,7 @@
         <v>6.55499982833862</v>
       </c>
       <c r="G1013" t="n">
-        <v>4.33740472793579</v>
+        <v>4.33740425109863</v>
       </c>
       <c r="H1013" t="n">
         <v>353997</v>
@@ -29775,7 +29775,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G1014" t="n">
-        <v>4.3605637550354</v>
+        <v>4.36056423187256</v>
       </c>
       <c r="H1014" t="n">
         <v>300567</v>
@@ -29833,7 +29833,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G1016" t="n">
-        <v>4.51937055587769</v>
+        <v>4.51937007904053</v>
       </c>
       <c r="H1016" t="n">
         <v>522728</v>
@@ -29891,7 +29891,7 @@
         <v>7</v>
       </c>
       <c r="G1018" t="n">
-        <v>4.63185834884644</v>
+        <v>4.63185787200928</v>
       </c>
       <c r="H1018" t="n">
         <v>746089</v>
@@ -29978,7 +29978,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G1021" t="n">
-        <v>4.51937055587769</v>
+        <v>4.51937007904053</v>
       </c>
       <c r="H1021" t="n">
         <v>576196</v>
@@ -30007,7 +30007,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G1022" t="n">
-        <v>4.68479442596436</v>
+        <v>4.6847939491272</v>
       </c>
       <c r="H1022" t="n">
         <v>926752</v>
@@ -30036,7 +30036,7 @@
         <v>7.17500019073486</v>
       </c>
       <c r="G1023" t="n">
-        <v>4.7476544380188</v>
+        <v>4.74765491485596</v>
       </c>
       <c r="H1023" t="n">
         <v>993946</v>
@@ -30181,7 +30181,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G1028" t="n">
-        <v>4.92962026596069</v>
+        <v>4.92962074279785</v>
       </c>
       <c r="H1028" t="n">
         <v>950804</v>
@@ -30210,7 +30210,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G1029" t="n">
-        <v>4.92962026596069</v>
+        <v>4.92962074279785</v>
       </c>
       <c r="H1029" t="n">
         <v>522366</v>
@@ -30268,7 +30268,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G1031" t="n">
-        <v>4.91638708114624</v>
+        <v>4.91638660430908</v>
       </c>
       <c r="H1031" t="n">
         <v>537345</v>
@@ -30326,7 +30326,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1033" t="n">
-        <v>5.16121339797974</v>
+        <v>5.16121435165405</v>
       </c>
       <c r="H1033" t="n">
         <v>1489247</v>
@@ -30413,7 +30413,7 @@
         <v>7.30999994277954</v>
       </c>
       <c r="G1036" t="n">
-        <v>4.83698272705078</v>
+        <v>4.83698320388794</v>
       </c>
       <c r="H1036" t="n">
         <v>1386184</v>
@@ -30442,7 +30442,7 @@
         <v>7.61499977111816</v>
       </c>
       <c r="G1037" t="n">
-        <v>5.03879976272583</v>
+        <v>5.03880023956299</v>
       </c>
       <c r="H1037" t="n">
         <v>1088901</v>
@@ -30558,7 +30558,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G1041" t="n">
-        <v>5.0619592666626</v>
+        <v>5.06195974349976</v>
       </c>
       <c r="H1041" t="n">
         <v>411523</v>
@@ -30616,7 +30616,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1043" t="n">
-        <v>5.06857585906982</v>
+        <v>5.06857633590698</v>
       </c>
       <c r="H1043" t="n">
         <v>779852</v>
@@ -30645,7 +30645,7 @@
         <v>7.71500015258789</v>
       </c>
       <c r="G1044" t="n">
-        <v>5.1049690246582</v>
+        <v>5.10496950149536</v>
       </c>
       <c r="H1044" t="n">
         <v>471610</v>
@@ -30674,7 +30674,7 @@
         <v>7.625</v>
       </c>
       <c r="G1045" t="n">
-        <v>5.04541683197021</v>
+        <v>5.04541730880737</v>
       </c>
       <c r="H1045" t="n">
         <v>833832</v>
@@ -30732,7 +30732,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G1047" t="n">
-        <v>5.0619592666626</v>
+        <v>5.06195974349976</v>
       </c>
       <c r="H1047" t="n">
         <v>944084</v>
@@ -30761,7 +30761,7 @@
         <v>7.69500017166138</v>
       </c>
       <c r="G1048" t="n">
-        <v>5.09173583984375</v>
+        <v>5.09173631668091</v>
       </c>
       <c r="H1048" t="n">
         <v>427316</v>
@@ -30790,7 +30790,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G1049" t="n">
-        <v>5.08842754364014</v>
+        <v>5.08842706680298</v>
       </c>
       <c r="H1049" t="n">
         <v>484828</v>
@@ -30848,7 +30848,7 @@
         <v>8</v>
       </c>
       <c r="G1051" t="n">
-        <v>5.29355239868164</v>
+        <v>5.29355192184448</v>
       </c>
       <c r="H1051" t="n">
         <v>384872</v>
@@ -30877,7 +30877,7 @@
         <v>7.93499994277954</v>
       </c>
       <c r="G1052" t="n">
-        <v>5.25054168701172</v>
+        <v>5.25054264068604</v>
       </c>
       <c r="H1052" t="n">
         <v>575834</v>
@@ -30906,7 +30906,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1053" t="n">
-        <v>5.16121339797974</v>
+        <v>5.16121435165405</v>
       </c>
       <c r="H1053" t="n">
         <v>938379</v>
@@ -31022,7 +31022,7 @@
         <v>8.13000011444092</v>
       </c>
       <c r="G1057" t="n">
-        <v>5.37957191467285</v>
+        <v>5.37957239151001</v>
       </c>
       <c r="H1057" t="n">
         <v>987878</v>
@@ -31051,7 +31051,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1058" t="n">
-        <v>5.4655933380127</v>
+        <v>5.46559286117554</v>
       </c>
       <c r="H1058" t="n">
         <v>949718</v>
@@ -31080,7 +31080,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G1059" t="n">
-        <v>5.30678653717041</v>
+        <v>5.30678606033325</v>
       </c>
       <c r="H1059" t="n">
         <v>496247</v>
@@ -31254,7 +31254,7 @@
         <v>8.52999973297119</v>
       </c>
       <c r="G1065" t="n">
-        <v>5.64424991607666</v>
+        <v>5.64425039291382</v>
       </c>
       <c r="H1065" t="n">
         <v>480624</v>
@@ -31283,7 +31283,7 @@
         <v>8.51500034332275</v>
       </c>
       <c r="G1066" t="n">
-        <v>5.63432502746582</v>
+        <v>5.63432455062866</v>
       </c>
       <c r="H1066" t="n">
         <v>332436</v>
@@ -31341,7 +31341,7 @@
         <v>8.45499992370605</v>
       </c>
       <c r="G1068" t="n">
-        <v>5.59462308883667</v>
+        <v>5.59462356567383</v>
       </c>
       <c r="H1068" t="n">
         <v>250918</v>
@@ -31370,7 +31370,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G1069" t="n">
-        <v>5.54499578475952</v>
+        <v>5.54499626159668</v>
       </c>
       <c r="H1069" t="n">
         <v>404652</v>
@@ -31399,7 +31399,7 @@
         <v>8.51500034332275</v>
       </c>
       <c r="G1070" t="n">
-        <v>5.63432502746582</v>
+        <v>5.63432455062866</v>
       </c>
       <c r="H1070" t="n">
         <v>423036</v>
@@ -31428,7 +31428,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G1071" t="n">
-        <v>5.5913143157959</v>
+        <v>5.59131479263306</v>
       </c>
       <c r="H1071" t="n">
         <v>286074</v>
@@ -31457,7 +31457,7 @@
         <v>8.625</v>
       </c>
       <c r="G1072" t="n">
-        <v>5.70711088180542</v>
+        <v>5.70711135864258</v>
       </c>
       <c r="H1072" t="n">
         <v>375726</v>
@@ -31544,7 +31544,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G1075" t="n">
-        <v>5.57808113098145</v>
+        <v>5.57808065414429</v>
       </c>
       <c r="H1075" t="n">
         <v>389826</v>
@@ -31573,7 +31573,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G1076" t="n">
-        <v>5.52514505386353</v>
+        <v>5.52514553070068</v>
       </c>
       <c r="H1076" t="n">
         <v>527736</v>
@@ -31602,7 +31602,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1077" t="n">
-        <v>5.50529432296753</v>
+        <v>5.50529384613037</v>
       </c>
       <c r="H1077" t="n">
         <v>619248</v>
@@ -31631,7 +31631,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G1078" t="n">
-        <v>5.6508674621582</v>
+        <v>5.65086698532104</v>
       </c>
       <c r="H1078" t="n">
         <v>262421</v>
@@ -31660,7 +31660,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1079" t="n">
-        <v>5.55822944641113</v>
+        <v>5.55822992324829</v>
       </c>
       <c r="H1079" t="n">
         <v>609659</v>
@@ -31689,7 +31689,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G1080" t="n">
-        <v>5.57808113098145</v>
+        <v>5.57808065414429</v>
       </c>
       <c r="H1080" t="n">
         <v>330939</v>
@@ -31718,7 +31718,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1081" t="n">
-        <v>5.65748453140259</v>
+        <v>5.65748405456543</v>
       </c>
       <c r="H1081" t="n">
         <v>299157</v>
@@ -31776,7 +31776,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1083" t="n">
-        <v>5.42589092254639</v>
+        <v>5.42589044570923</v>
       </c>
       <c r="H1083" t="n">
         <v>416896</v>
@@ -31805,7 +31805,7 @@
         <v>7.95499992370605</v>
       </c>
       <c r="G1084" t="n">
-        <v>5.26377630233765</v>
+        <v>5.26377582550049</v>
       </c>
       <c r="H1084" t="n">
         <v>622275</v>
@@ -31834,7 +31834,7 @@
         <v>8.07499980926514</v>
       </c>
       <c r="G1085" t="n">
-        <v>5.34317922592163</v>
+        <v>5.34317874908447</v>
       </c>
       <c r="H1085" t="n">
         <v>537425</v>
@@ -31892,7 +31892,7 @@
         <v>8.49499988555908</v>
       </c>
       <c r="G1087" t="n">
-        <v>5.62109136581421</v>
+        <v>5.62109041213989</v>
       </c>
       <c r="H1087" t="n">
         <v>830197</v>
@@ -31921,7 +31921,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G1088" t="n">
-        <v>5.70380306243896</v>
+        <v>5.70380258560181</v>
       </c>
       <c r="H1088" t="n">
         <v>369279</v>
@@ -31950,7 +31950,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G1089" t="n">
-        <v>5.8162899017334</v>
+        <v>5.81629085540771</v>
       </c>
       <c r="H1089" t="n">
         <v>541031</v>
@@ -32037,7 +32037,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1092" t="n">
-        <v>5.88907623291016</v>
+        <v>5.88907670974731</v>
       </c>
       <c r="H1092" t="n">
         <v>242107</v>
@@ -32066,7 +32066,7 @@
         <v>8.8100004196167</v>
       </c>
       <c r="G1093" t="n">
-        <v>5.82952451705933</v>
+        <v>5.82952499389648</v>
       </c>
       <c r="H1093" t="n">
         <v>264946</v>
@@ -32095,7 +32095,7 @@
         <v>8.86999988555908</v>
       </c>
       <c r="G1094" t="n">
-        <v>5.86922645568848</v>
+        <v>5.86922597885132</v>
       </c>
       <c r="H1094" t="n">
         <v>310467</v>
@@ -32153,7 +32153,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G1096" t="n">
-        <v>5.83614110946655</v>
+        <v>5.83614158630371</v>
       </c>
       <c r="H1096" t="n">
         <v>326978</v>
@@ -32182,7 +32182,7 @@
         <v>8.86999988555908</v>
       </c>
       <c r="G1097" t="n">
-        <v>5.86922645568848</v>
+        <v>5.86922597885132</v>
       </c>
       <c r="H1097" t="n">
         <v>404572</v>
@@ -32298,7 +32298,7 @@
         <v>7.78499984741211</v>
       </c>
       <c r="G1101" t="n">
-        <v>5.15128803253174</v>
+        <v>5.15128755569458</v>
       </c>
       <c r="H1101" t="n">
         <v>1483673</v>
@@ -32327,7 +32327,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G1102" t="n">
-        <v>5.1942982673645</v>
+        <v>5.19429731369019</v>
       </c>
       <c r="H1102" t="n">
         <v>1084000</v>
@@ -32356,7 +32356,7 @@
         <v>7.7649998664856</v>
       </c>
       <c r="G1103" t="n">
-        <v>5.13805389404297</v>
+        <v>5.13805437088013</v>
       </c>
       <c r="H1103" t="n">
         <v>779171</v>
@@ -32414,7 +32414,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G1105" t="n">
-        <v>5.0619592666626</v>
+        <v>5.06195974349976</v>
       </c>
       <c r="H1105" t="n">
         <v>261213</v>
@@ -32472,7 +32472,7 @@
         <v>7.71500015258789</v>
       </c>
       <c r="G1107" t="n">
-        <v>5.1049690246582</v>
+        <v>5.10496950149536</v>
       </c>
       <c r="H1107" t="n">
         <v>374750</v>
@@ -32530,7 +32530,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G1109" t="n">
-        <v>5.23400020599365</v>
+        <v>5.23399972915649</v>
       </c>
       <c r="H1109" t="n">
         <v>436719</v>
@@ -32588,7 +32588,7 @@
         <v>8</v>
       </c>
       <c r="G1111" t="n">
-        <v>5.29355239868164</v>
+        <v>5.29355192184448</v>
       </c>
       <c r="H1111" t="n">
         <v>398454</v>
@@ -32617,7 +32617,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1112" t="n">
-        <v>5.22738313674927</v>
+        <v>5.22738265991211</v>
       </c>
       <c r="H1112" t="n">
         <v>405945</v>
@@ -32704,7 +32704,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G1115" t="n">
-        <v>5.12151145935059</v>
+        <v>5.12151193618774</v>
       </c>
       <c r="H1115" t="n">
         <v>775169</v>
@@ -32733,7 +32733,7 @@
         <v>7.7649998664856</v>
       </c>
       <c r="G1116" t="n">
-        <v>5.13805389404297</v>
+        <v>5.13805437088013</v>
       </c>
       <c r="H1116" t="n">
         <v>322553</v>
@@ -32820,7 +32820,7 @@
         <v>8.01500034332275</v>
       </c>
       <c r="G1119" t="n">
-        <v>5.3034782409668</v>
+        <v>5.30347776412964</v>
       </c>
       <c r="H1119" t="n">
         <v>896226</v>
@@ -32878,7 +32878,7 @@
         <v>8</v>
       </c>
       <c r="G1121" t="n">
-        <v>5.29355239868164</v>
+        <v>5.29355192184448</v>
       </c>
       <c r="H1121" t="n">
         <v>677107</v>
@@ -32965,7 +32965,7 @@
         <v>8.01000022888184</v>
       </c>
       <c r="G1124" t="n">
-        <v>5.30016994476318</v>
+        <v>5.30016946792603</v>
       </c>
       <c r="H1124" t="n">
         <v>1015645</v>
@@ -33052,7 +33052,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G1127" t="n">
-        <v>5.3464879989624</v>
+        <v>5.34648752212524</v>
       </c>
       <c r="H1127" t="n">
         <v>474334</v>
@@ -33081,7 +33081,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G1128" t="n">
-        <v>5.3464879989624</v>
+        <v>5.34648752212524</v>
       </c>
       <c r="H1128" t="n">
         <v>753182</v>
@@ -33110,7 +33110,7 @@
         <v>7.95499992370605</v>
       </c>
       <c r="G1129" t="n">
-        <v>5.26377630233765</v>
+        <v>5.26377582550049</v>
       </c>
       <c r="H1129" t="n">
         <v>561915</v>
@@ -33139,7 +33139,7 @@
         <v>8.0649995803833</v>
       </c>
       <c r="G1130" t="n">
-        <v>5.3365626335144</v>
+        <v>5.33656167984009</v>
       </c>
       <c r="H1130" t="n">
         <v>418262</v>
@@ -33168,7 +33168,7 @@
         <v>8.15499973297119</v>
       </c>
       <c r="G1131" t="n">
-        <v>5.39611434936523</v>
+        <v>5.39611482620239</v>
       </c>
       <c r="H1131" t="n">
         <v>427051</v>
@@ -33197,7 +33197,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G1132" t="n">
-        <v>5.419273853302</v>
+        <v>5.41927433013916</v>
       </c>
       <c r="H1132" t="n">
         <v>375323</v>
@@ -33226,7 +33226,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1133" t="n">
-        <v>5.41265773773193</v>
+        <v>5.41265726089478</v>
       </c>
       <c r="H1133" t="n">
         <v>339462</v>
@@ -33342,7 +33342,7 @@
         <v>8.39500045776367</v>
       </c>
       <c r="G1137" t="n">
-        <v>5.55492162704468</v>
+        <v>5.55492210388184</v>
       </c>
       <c r="H1137" t="n">
         <v>1125508</v>
@@ -33371,7 +33371,7 @@
         <v>8.57499980926514</v>
       </c>
       <c r="G1138" t="n">
-        <v>5.67402648925781</v>
+        <v>5.67402601242065</v>
       </c>
       <c r="H1138" t="n">
         <v>989908</v>
@@ -33400,7 +33400,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1139" t="n">
-        <v>5.45235824584961</v>
+        <v>5.45235872268677</v>
       </c>
       <c r="H1139" t="n">
         <v>1384647</v>
@@ -33429,7 +33429,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G1140" t="n">
-        <v>5.44574117660522</v>
+        <v>5.44574165344238</v>
       </c>
       <c r="H1140" t="n">
         <v>913516</v>
@@ -33458,7 +33458,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1141" t="n">
-        <v>5.41265773773193</v>
+        <v>5.41265726089478</v>
       </c>
       <c r="H1141" t="n">
         <v>928250</v>
@@ -33516,7 +33516,7 @@
         <v>8.17500019073486</v>
       </c>
       <c r="G1143" t="n">
-        <v>5.409348487854</v>
+        <v>5.40934896469116</v>
       </c>
       <c r="H1143" t="n">
         <v>1350278</v>
@@ -33545,7 +33545,7 @@
         <v>7.05499982833862</v>
       </c>
       <c r="G1144" t="n">
-        <v>5.24187612533569</v>
+        <v>5.24187660217285</v>
       </c>
       <c r="H1144" t="n">
         <v>3230287</v>
@@ -33661,7 +33661,7 @@
         <v>7.5</v>
       </c>
       <c r="G1148" t="n">
-        <v>5.57251262664795</v>
+        <v>5.57251214981079</v>
       </c>
       <c r="H1148" t="n">
         <v>725174</v>
@@ -33690,7 +33690,7 @@
         <v>7.7350001335144</v>
       </c>
       <c r="G1149" t="n">
-        <v>5.74711751937866</v>
+        <v>5.7471170425415</v>
       </c>
       <c r="H1149" t="n">
         <v>823147</v>
@@ -33748,7 +33748,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1151" t="n">
-        <v>5.79541254043579</v>
+        <v>5.79541301727295</v>
       </c>
       <c r="H1151" t="n">
         <v>630578</v>
@@ -33777,7 +33777,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G1152" t="n">
-        <v>5.78798246383667</v>
+        <v>5.78798198699951</v>
       </c>
       <c r="H1152" t="n">
         <v>529762</v>
@@ -33835,7 +33835,7 @@
         <v>7.86999988555908</v>
       </c>
       <c r="G1154" t="n">
-        <v>5.84742259979248</v>
+        <v>5.84742212295532</v>
       </c>
       <c r="H1154" t="n">
         <v>952654</v>
@@ -33922,7 +33922,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G1157" t="n">
-        <v>5.74340200424194</v>
+        <v>5.74340152740479</v>
       </c>
       <c r="H1157" t="n">
         <v>310425</v>
@@ -33951,7 +33951,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G1158" t="n">
-        <v>5.75083208084106</v>
+        <v>5.75083255767822</v>
       </c>
       <c r="H1158" t="n">
         <v>337031</v>
@@ -34038,7 +34038,7 @@
         <v>7.42500019073486</v>
       </c>
       <c r="G1161" t="n">
-        <v>5.51678657531738</v>
+        <v>5.51678705215454</v>
       </c>
       <c r="H1161" t="n">
         <v>830344</v>
@@ -34067,7 +34067,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1162" t="n">
-        <v>5.4982123374939</v>
+        <v>5.49821186065674</v>
       </c>
       <c r="H1162" t="n">
         <v>2125447</v>
@@ -34183,7 +34183,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G1166" t="n">
-        <v>5.34218120574951</v>
+        <v>5.34218168258667</v>
       </c>
       <c r="H1166" t="n">
         <v>865639</v>
@@ -34241,7 +34241,7 @@
         <v>7.42500019073486</v>
       </c>
       <c r="G1168" t="n">
-        <v>5.51678657531738</v>
+        <v>5.51678705215454</v>
       </c>
       <c r="H1168" t="n">
         <v>377537</v>
@@ -34270,7 +34270,7 @@
         <v>7.40999984741211</v>
       </c>
       <c r="G1169" t="n">
-        <v>5.5056414604187</v>
+        <v>5.50564193725586</v>
       </c>
       <c r="H1169" t="n">
         <v>356240</v>
@@ -34299,7 +34299,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G1170" t="n">
-        <v>5.41648197174072</v>
+        <v>5.41648149490356</v>
       </c>
       <c r="H1170" t="n">
         <v>365012</v>
@@ -34386,7 +34386,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G1173" t="n">
-        <v>5.16386079788208</v>
+        <v>5.16386127471924</v>
       </c>
       <c r="H1173" t="n">
         <v>600099</v>
@@ -34473,7 +34473,7 @@
         <v>6.82499980926514</v>
       </c>
       <c r="G1176" t="n">
-        <v>5.07098579406738</v>
+        <v>5.07098531723022</v>
       </c>
       <c r="H1176" t="n">
         <v>409920</v>
@@ -34502,7 +34502,7 @@
         <v>6.91499996185303</v>
       </c>
       <c r="G1177" t="n">
-        <v>5.13785648345947</v>
+        <v>5.13785552978516</v>
       </c>
       <c r="H1177" t="n">
         <v>182140</v>
@@ -34531,7 +34531,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G1178" t="n">
-        <v>4.92610025405884</v>
+        <v>4.92610120773315</v>
       </c>
       <c r="H1178" t="n">
         <v>787105</v>
@@ -34560,7 +34560,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1179" t="n">
-        <v>4.79979038238525</v>
+        <v>4.7997899055481</v>
       </c>
       <c r="H1179" t="n">
         <v>1034930</v>
@@ -34618,7 +34618,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1181" t="n">
-        <v>5.05241060256958</v>
+        <v>5.05241107940674</v>
       </c>
       <c r="H1181" t="n">
         <v>350530</v>
@@ -34705,7 +34705,7 @@
         <v>6.63500022888184</v>
       </c>
       <c r="G1184" t="n">
-        <v>4.9298152923584</v>
+        <v>4.92981624603271</v>
       </c>
       <c r="H1184" t="n">
         <v>315675</v>
@@ -34763,7 +34763,7 @@
         <v>6.57000017166138</v>
       </c>
       <c r="G1186" t="n">
-        <v>4.88152122497559</v>
+        <v>4.88152074813843</v>
       </c>
       <c r="H1186" t="n">
         <v>247408</v>
@@ -34792,7 +34792,7 @@
         <v>6.70499992370605</v>
       </c>
       <c r="G1187" t="n">
-        <v>4.98182582855225</v>
+        <v>4.9818263053894</v>
       </c>
       <c r="H1187" t="n">
         <v>905876</v>
@@ -34879,7 +34879,7 @@
         <v>6.66499996185303</v>
       </c>
       <c r="G1190" t="n">
-        <v>4.95210599899292</v>
+        <v>4.95210552215576</v>
       </c>
       <c r="H1190" t="n">
         <v>373430</v>
@@ -34937,7 +34937,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G1192" t="n">
-        <v>5.08956098556519</v>
+        <v>5.08956050872803</v>
       </c>
       <c r="H1192" t="n">
         <v>481573</v>
@@ -34995,7 +34995,7 @@
         <v>6.7350001335144</v>
       </c>
       <c r="G1194" t="n">
-        <v>5.00411605834961</v>
+        <v>5.00411558151245</v>
       </c>
       <c r="H1194" t="n">
         <v>250517</v>
@@ -35111,7 +35111,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G1198" t="n">
-        <v>5.22330141067505</v>
+        <v>5.22330093383789</v>
       </c>
       <c r="H1198" t="n">
         <v>151999</v>
@@ -35140,7 +35140,7 @@
         <v>7.11499977111816</v>
       </c>
       <c r="G1199" t="n">
-        <v>5.28645610809326</v>
+        <v>5.28645658493042</v>
       </c>
       <c r="H1199" t="n">
         <v>207221</v>
@@ -35169,7 +35169,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1200" t="n">
-        <v>5.27531099319458</v>
+        <v>5.2753119468689</v>
       </c>
       <c r="H1200" t="n">
         <v>154414</v>
@@ -35227,7 +35227,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1202" t="n">
-        <v>5.34961080551147</v>
+        <v>5.34961128234863</v>
       </c>
       <c r="H1202" t="n">
         <v>307369</v>
@@ -35285,7 +35285,7 @@
         <v>7.17500019073486</v>
       </c>
       <c r="G1204" t="n">
-        <v>5.33103609085083</v>
+        <v>5.33103656768799</v>
       </c>
       <c r="H1204" t="n">
         <v>404955</v>
@@ -35314,7 +35314,7 @@
         <v>7.14499998092651</v>
       </c>
       <c r="G1205" t="n">
-        <v>5.30874586105347</v>
+        <v>5.30874681472778</v>
       </c>
       <c r="H1205" t="n">
         <v>369898</v>
@@ -35343,7 +35343,7 @@
         <v>7.21500015258789</v>
       </c>
       <c r="G1206" t="n">
-        <v>5.36075639724731</v>
+        <v>5.36075687408447</v>
       </c>
       <c r="H1206" t="n">
         <v>254866</v>
@@ -35401,7 +35401,7 @@
         <v>7.21500015258789</v>
       </c>
       <c r="G1208" t="n">
-        <v>5.36075639724731</v>
+        <v>5.36075687408447</v>
       </c>
       <c r="H1208" t="n">
         <v>285788</v>
@@ -35430,7 +35430,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1209" t="n">
-        <v>5.27531099319458</v>
+        <v>5.2753119468689</v>
       </c>
       <c r="H1209" t="n">
         <v>331176</v>
@@ -35459,7 +35459,7 @@
         <v>7.05499982833862</v>
       </c>
       <c r="G1210" t="n">
-        <v>5.24187612533569</v>
+        <v>5.24187660217285</v>
       </c>
       <c r="H1210" t="n">
         <v>188040</v>
@@ -35488,7 +35488,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G1211" t="n">
-        <v>5.2455906867981</v>
+        <v>5.24559116363525</v>
       </c>
       <c r="H1211" t="n">
         <v>185931</v>
@@ -35546,7 +35546,7 @@
         <v>6.94500017166138</v>
       </c>
       <c r="G1213" t="n">
-        <v>5.16014671325684</v>
+        <v>5.16014623641968</v>
       </c>
       <c r="H1213" t="n">
         <v>399759</v>
@@ -35575,7 +35575,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G1214" t="n">
-        <v>5.22330141067505</v>
+        <v>5.22330093383789</v>
       </c>
       <c r="H1214" t="n">
         <v>278021</v>
@@ -35633,7 +35633,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G1216" t="n">
-        <v>5.12671136856079</v>
+        <v>5.12671089172363</v>
       </c>
       <c r="H1216" t="n">
         <v>217888</v>
@@ -35691,7 +35691,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G1218" t="n">
-        <v>4.92610025405884</v>
+        <v>4.92610120773315</v>
       </c>
       <c r="H1218" t="n">
         <v>536678</v>
@@ -35749,7 +35749,7 @@
         <v>6.82499980926514</v>
       </c>
       <c r="G1220" t="n">
-        <v>5.07098579406738</v>
+        <v>5.07098531723022</v>
       </c>
       <c r="H1220" t="n">
         <v>345082</v>
@@ -35778,7 +35778,7 @@
         <v>6.81500005722046</v>
       </c>
       <c r="G1221" t="n">
-        <v>5.06355571746826</v>
+        <v>5.06355619430542</v>
       </c>
       <c r="H1221" t="n">
         <v>322552</v>
@@ -35836,7 +35836,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G1223" t="n">
-        <v>5.17872142791748</v>
+        <v>5.17872047424316</v>
       </c>
       <c r="H1223" t="n">
         <v>363502</v>
@@ -35894,7 +35894,7 @@
         <v>6.80499982833862</v>
       </c>
       <c r="G1225" t="n">
-        <v>5.0561261177063</v>
+        <v>5.05612564086914</v>
       </c>
       <c r="H1225" t="n">
         <v>495232</v>
@@ -35952,7 +35952,7 @@
         <v>6.76999998092651</v>
       </c>
       <c r="G1227" t="n">
-        <v>5.03012084960938</v>
+        <v>5.03012132644653</v>
       </c>
       <c r="H1227" t="n">
         <v>311808</v>
@@ -35981,7 +35981,7 @@
         <v>6.80499982833862</v>
       </c>
       <c r="G1228" t="n">
-        <v>5.0561261177063</v>
+        <v>5.05612564086914</v>
       </c>
       <c r="H1228" t="n">
         <v>481192</v>
@@ -36068,7 +36068,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G1231" t="n">
-        <v>5.7062520980835</v>
+        <v>5.70625257492065</v>
       </c>
       <c r="H1231" t="n">
         <v>1441593</v>
@@ -36184,7 +36184,7 @@
         <v>7.375</v>
       </c>
       <c r="G1235" t="n">
-        <v>5.47963714599609</v>
+        <v>5.47963666915894</v>
       </c>
       <c r="H1235" t="n">
         <v>514007</v>
@@ -36242,7 +36242,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G1237" t="n">
-        <v>5.34218120574951</v>
+        <v>5.34218168258667</v>
       </c>
       <c r="H1237" t="n">
         <v>603372</v>
@@ -36329,7 +36329,7 @@
         <v>6.53000020980835</v>
       </c>
       <c r="G1240" t="n">
-        <v>4.85180044174194</v>
+        <v>4.8518009185791</v>
       </c>
       <c r="H1240" t="n">
         <v>1581067</v>
@@ -36561,7 +36561,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G1248" t="n">
-        <v>4.53973960876465</v>
+        <v>4.53974008560181</v>
       </c>
       <c r="H1248" t="n">
         <v>1277935</v>
@@ -36590,7 +36590,7 @@
         <v>6.25</v>
       </c>
       <c r="G1249" t="n">
-        <v>4.64376068115234</v>
+        <v>4.64375972747803</v>
       </c>
       <c r="H1249" t="n">
         <v>3209768</v>
@@ -36619,7 +36619,7 @@
         <v>6.06500005722046</v>
       </c>
       <c r="G1250" t="n">
-        <v>4.5063042640686</v>
+        <v>4.50630474090576</v>
       </c>
       <c r="H1250" t="n">
         <v>1013000</v>
@@ -36648,7 +36648,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G1251" t="n">
-        <v>4.53231000900269</v>
+        <v>4.53230953216553</v>
       </c>
       <c r="H1251" t="n">
         <v>894445</v>
@@ -36822,7 +36822,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1257" t="n">
-        <v>4.79979038238525</v>
+        <v>4.7997899055481</v>
       </c>
       <c r="H1257" t="n">
         <v>754597</v>
@@ -36909,7 +36909,7 @@
         <v>6.67000007629395</v>
       </c>
       <c r="G1260" t="n">
-        <v>4.95582103729248</v>
+        <v>4.95582056045532</v>
       </c>
       <c r="H1260" t="n">
         <v>944806</v>
@@ -36996,7 +36996,7 @@
         <v>6.82499980926514</v>
       </c>
       <c r="G1263" t="n">
-        <v>5.07098579406738</v>
+        <v>5.07098531723022</v>
       </c>
       <c r="H1263" t="n">
         <v>1002577</v>
@@ -37025,7 +37025,7 @@
         <v>6.82499980926514</v>
       </c>
       <c r="G1264" t="n">
-        <v>5.07098579406738</v>
+        <v>5.07098531723022</v>
       </c>
       <c r="H1264" t="n">
         <v>588306</v>
@@ -37054,7 +37054,7 @@
         <v>6.7350001335144</v>
       </c>
       <c r="G1265" t="n">
-        <v>5.00411605834961</v>
+        <v>5.00411558151245</v>
       </c>
       <c r="H1265" t="n">
         <v>721014</v>
@@ -37141,7 +37141,7 @@
         <v>7.00500011444092</v>
       </c>
       <c r="G1268" t="n">
-        <v>5.20472574234009</v>
+        <v>5.20472621917725</v>
       </c>
       <c r="H1268" t="n">
         <v>1084901</v>
@@ -37199,7 +37199,7 @@
         <v>6.80499982833862</v>
       </c>
       <c r="G1270" t="n">
-        <v>5.0561261177063</v>
+        <v>5.05612564086914</v>
       </c>
       <c r="H1270" t="n">
         <v>924463</v>
@@ -37228,7 +37228,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G1271" t="n">
-        <v>5.16386079788208</v>
+        <v>5.16386127471924</v>
       </c>
       <c r="H1271" t="n">
         <v>645323</v>
@@ -37257,7 +37257,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G1272" t="n">
-        <v>5.15643072128296</v>
+        <v>5.15643119812012</v>
       </c>
       <c r="H1272" t="n">
         <v>982597</v>
@@ -37315,7 +37315,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G1274" t="n">
-        <v>5.11185121536255</v>
+        <v>5.11185073852539</v>
       </c>
       <c r="H1274" t="n">
         <v>1020585</v>
@@ -37373,7 +37373,7 @@
         <v>6.15500020980835</v>
       </c>
       <c r="G1276" t="n">
-        <v>5.07072877883911</v>
+        <v>5.07072830200195</v>
       </c>
       <c r="H1276" t="n">
         <v>2083546</v>
@@ -37460,7 +37460,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G1279" t="n">
-        <v>4.98422574996948</v>
+        <v>4.98422527313232</v>
       </c>
       <c r="H1279" t="n">
         <v>706800</v>
@@ -37576,7 +37576,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G1283" t="n">
-        <v>4.91831827163696</v>
+        <v>4.9183177947998</v>
       </c>
       <c r="H1283" t="n">
         <v>584822</v>
@@ -37605,7 +37605,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G1284" t="n">
-        <v>4.90184116363525</v>
+        <v>4.90184164047241</v>
       </c>
       <c r="H1284" t="n">
         <v>1058391</v>
@@ -37634,7 +37634,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G1285" t="n">
-        <v>4.95127201080322</v>
+        <v>4.95127248764038</v>
       </c>
       <c r="H1285" t="n">
         <v>1145853</v>
@@ -37663,7 +37663,7 @@
         <v>6.22499990463257</v>
       </c>
       <c r="G1286" t="n">
-        <v>5.12839698791504</v>
+        <v>5.1283974647522</v>
       </c>
       <c r="H1286" t="n">
         <v>1536642</v>
@@ -37779,7 +37779,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G1290" t="n">
-        <v>5.06660938262939</v>
+        <v>5.06660890579224</v>
       </c>
       <c r="H1290" t="n">
         <v>640613</v>
@@ -37808,7 +37808,7 @@
         <v>6.30499982833862</v>
       </c>
       <c r="G1291" t="n">
-        <v>5.19430446624756</v>
+        <v>5.1943039894104</v>
       </c>
       <c r="H1291" t="n">
         <v>899123</v>
@@ -37895,7 +37895,7 @@
         <v>6.71500015258789</v>
       </c>
       <c r="G1294" t="n">
-        <v>5.53207874298096</v>
+        <v>5.5320782661438</v>
       </c>
       <c r="H1294" t="n">
         <v>1703942</v>
@@ -38011,7 +38011,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G1298" t="n">
-        <v>5.82454109191895</v>
+        <v>5.8245415687561</v>
       </c>
       <c r="H1298" t="n">
         <v>729162</v>
@@ -38040,7 +38040,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G1299" t="n">
-        <v>5.98930835723877</v>
+        <v>5.98930883407593</v>
       </c>
       <c r="H1299" t="n">
         <v>1579602</v>
@@ -38098,7 +38098,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G1301" t="n">
-        <v>5.98930835723877</v>
+        <v>5.98930883407593</v>
       </c>
       <c r="H1301" t="n">
         <v>683265</v>
@@ -38214,7 +38214,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G1305" t="n">
-        <v>6.11288452148438</v>
+        <v>6.11288499832153</v>
       </c>
       <c r="H1305" t="n">
         <v>723894</v>
@@ -38243,7 +38243,7 @@
         <v>7.25</v>
       </c>
       <c r="G1306" t="n">
-        <v>5.97283172607422</v>
+        <v>5.97283220291138</v>
       </c>
       <c r="H1306" t="n">
         <v>849175</v>
@@ -38272,7 +38272,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G1307" t="n">
-        <v>6.00578594207764</v>
+        <v>6.00578546524048</v>
       </c>
       <c r="H1307" t="n">
         <v>464920</v>
@@ -38562,7 +38562,7 @@
         <v>6.86499977111816</v>
       </c>
       <c r="G1317" t="n">
-        <v>5.6556544303894</v>
+        <v>5.65565395355225</v>
       </c>
       <c r="H1317" t="n">
         <v>519132</v>
@@ -38707,7 +38707,7 @@
         <v>6.48999977111816</v>
       </c>
       <c r="G1322" t="n">
-        <v>5.34671449661255</v>
+        <v>5.34671401977539</v>
       </c>
       <c r="H1322" t="n">
         <v>475353</v>
@@ -38736,7 +38736,7 @@
         <v>6.5149998664856</v>
       </c>
       <c r="G1323" t="n">
-        <v>5.36731052398682</v>
+        <v>5.36731004714966</v>
       </c>
       <c r="H1323" t="n">
         <v>581058</v>
@@ -38765,7 +38765,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G1324" t="n">
-        <v>5.5032434463501</v>
+        <v>5.50324392318726</v>
       </c>
       <c r="H1324" t="n">
         <v>619799</v>
@@ -38794,7 +38794,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G1325" t="n">
-        <v>5.5032434463501</v>
+        <v>5.50324392318726</v>
       </c>
       <c r="H1325" t="n">
         <v>464277</v>
@@ -38852,7 +38852,7 @@
         <v>6.63500022888184</v>
       </c>
       <c r="G1327" t="n">
-        <v>5.46617126464844</v>
+        <v>5.4661717414856</v>
       </c>
       <c r="H1327" t="n">
         <v>342171</v>
@@ -38997,7 +38997,7 @@
         <v>6.30999994277954</v>
       </c>
       <c r="G1332" t="n">
-        <v>5.19842338562012</v>
+        <v>5.19842290878296</v>
       </c>
       <c r="H1332" t="n">
         <v>302909</v>
@@ -39026,7 +39026,7 @@
         <v>6.43499994277954</v>
       </c>
       <c r="G1333" t="n">
-        <v>5.3014030456543</v>
+        <v>5.30140352249146</v>
       </c>
       <c r="H1333" t="n">
         <v>364660</v>
@@ -39055,7 +39055,7 @@
         <v>6.57000017166138</v>
       </c>
       <c r="G1334" t="n">
-        <v>5.41262197494507</v>
+        <v>5.41262245178223</v>
       </c>
       <c r="H1334" t="n">
         <v>455465</v>
@@ -39084,7 +39084,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G1335" t="n">
-        <v>5.33023691177368</v>
+        <v>5.33023738861084</v>
       </c>
       <c r="H1335" t="n">
         <v>362879</v>
@@ -39113,7 +39113,7 @@
         <v>6.55499982833862</v>
       </c>
       <c r="G1336" t="n">
-        <v>5.40026378631592</v>
+        <v>5.40026426315308</v>
       </c>
       <c r="H1336" t="n">
         <v>311331</v>
@@ -39142,7 +39142,7 @@
         <v>6.44500017166138</v>
       </c>
       <c r="G1337" t="n">
-        <v>5.30964231491089</v>
+        <v>5.30964183807373</v>
       </c>
       <c r="H1337" t="n">
         <v>327664</v>
@@ -39403,7 +39403,7 @@
         <v>6.63500022888184</v>
       </c>
       <c r="G1346" t="n">
-        <v>5.46617126464844</v>
+        <v>5.4661717414856</v>
       </c>
       <c r="H1346" t="n">
         <v>301137</v>
@@ -39432,7 +39432,7 @@
         <v>6.67000007629395</v>
       </c>
       <c r="G1347" t="n">
-        <v>5.49500608444214</v>
+        <v>5.49500560760498</v>
       </c>
       <c r="H1347" t="n">
         <v>330416</v>
@@ -39490,7 +39490,7 @@
         <v>6.85500001907349</v>
       </c>
       <c r="G1349" t="n">
-        <v>5.64741611480713</v>
+        <v>5.64741563796997</v>
       </c>
       <c r="H1349" t="n">
         <v>421301</v>
@@ -39519,7 +39519,7 @@
         <v>6.86499977111816</v>
       </c>
       <c r="G1350" t="n">
-        <v>5.6556544303894</v>
+        <v>5.65565395355225</v>
       </c>
       <c r="H1350" t="n">
         <v>463464</v>
@@ -39693,7 +39693,7 @@
         <v>6.86499977111816</v>
       </c>
       <c r="G1356" t="n">
-        <v>5.6556544303894</v>
+        <v>5.65565395355225</v>
       </c>
       <c r="H1356" t="n">
         <v>779460</v>
@@ -39722,7 +39722,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G1357" t="n">
-        <v>5.68448877334595</v>
+        <v>5.68448829650879</v>
       </c>
       <c r="H1357" t="n">
         <v>382672</v>
@@ -39751,7 +39751,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G1358" t="n">
-        <v>5.72568035125732</v>
+        <v>5.72567987442017</v>
       </c>
       <c r="H1358" t="n">
         <v>286476</v>
@@ -39780,7 +39780,7 @@
         <v>7.0149998664856</v>
       </c>
       <c r="G1359" t="n">
-        <v>5.77923011779785</v>
+        <v>5.77922964096069</v>
       </c>
       <c r="H1359" t="n">
         <v>307914</v>
@@ -39809,7 +39809,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1360" t="n">
-        <v>5.84925556182861</v>
+        <v>5.84925603866577</v>
       </c>
       <c r="H1360" t="n">
         <v>390352</v>
@@ -39896,7 +39896,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G1363" t="n">
-        <v>5.67624998092651</v>
+        <v>5.67625045776367</v>
       </c>
       <c r="H1363" t="n">
         <v>820183</v>
@@ -70584,6 +70584,35 @@
         <v>2175619</v>
       </c>
       <c r="I2421" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2422">
+      <c r="A2422" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2422" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C2422" t="n">
+        <v>2.07200002670288</v>
+      </c>
+      <c r="D2422" t="n">
+        <v>2.15799999237061</v>
+      </c>
+      <c r="E2422" t="n">
+        <v>2.06599998474121</v>
+      </c>
+      <c r="F2422" t="n">
+        <v>2.09999990463257</v>
+      </c>
+      <c r="G2422" t="n">
+        <v>2.09999990463257</v>
+      </c>
+      <c r="H2422" t="n">
+        <v>2438707</v>
+      </c>
+      <c r="I2422" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BFF.MI.xlsx
+++ b/data/BFF.MI.xlsx
@@ -427,7 +427,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G2" t="n">
-        <v>2.25471162796021</v>
+        <v>2.25471138954163</v>
       </c>
       <c r="H2" t="n">
         <v>14210256</v>
@@ -485,7 +485,7 @@
         <v>4.25</v>
       </c>
       <c r="G4" t="n">
-        <v>2.31461954116821</v>
+        <v>2.31461977958679</v>
       </c>
       <c r="H4" t="n">
         <v>1265581</v>
@@ -514,7 +514,7 @@
         <v>4.29400014877319</v>
       </c>
       <c r="G5" t="n">
-        <v>2.33858299255371</v>
+        <v>2.33858251571655</v>
       </c>
       <c r="H5" t="n">
         <v>392814</v>
@@ -572,7 +572,7 @@
         <v>4.06599998474121</v>
       </c>
       <c r="G7" t="n">
-        <v>2.21440982818604</v>
+        <v>2.21441006660461</v>
       </c>
       <c r="H7" t="n">
         <v>485751</v>
@@ -601,7 +601,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G8" t="n">
-        <v>2.22203493118286</v>
+        <v>2.22203469276428</v>
       </c>
       <c r="H8" t="n">
         <v>362054</v>
@@ -659,7 +659,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G10" t="n">
-        <v>2.22748112678528</v>
+        <v>2.2274808883667</v>
       </c>
       <c r="H10" t="n">
         <v>428382</v>
@@ -746,7 +746,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G13" t="n">
-        <v>2.34185028076172</v>
+        <v>2.3418505191803</v>
       </c>
       <c r="H13" t="n">
         <v>345195</v>
@@ -775,7 +775,7 @@
         <v>4.2979998588562</v>
       </c>
       <c r="G14" t="n">
-        <v>2.3407609462738</v>
+        <v>2.34076070785522</v>
       </c>
       <c r="H14" t="n">
         <v>134855</v>
@@ -833,7 +833,7 @@
         <v>4.36199998855591</v>
       </c>
       <c r="G16" t="n">
-        <v>2.37561655044556</v>
+        <v>2.37561631202698</v>
       </c>
       <c r="H16" t="n">
         <v>470779</v>
@@ -862,7 +862,7 @@
         <v>4.44600009918213</v>
       </c>
       <c r="G17" t="n">
-        <v>2.42136406898499</v>
+        <v>2.42136430740356</v>
       </c>
       <c r="H17" t="n">
         <v>136910</v>
@@ -978,7 +978,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G21" t="n">
-        <v>2.54335832595825</v>
+        <v>2.54335856437683</v>
       </c>
       <c r="H21" t="n">
         <v>983059</v>
@@ -1007,7 +1007,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G22" t="n">
-        <v>2.5596969127655</v>
+        <v>2.55969667434692</v>
       </c>
       <c r="H22" t="n">
         <v>1178689</v>
@@ -1065,7 +1065,7 @@
         <v>4.85400009155273</v>
       </c>
       <c r="G24" t="n">
-        <v>2.64356827735901</v>
+        <v>2.64356780052185</v>
       </c>
       <c r="H24" t="n">
         <v>436457</v>
@@ -1094,7 +1094,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G25" t="n">
-        <v>2.5596969127655</v>
+        <v>2.55969667434692</v>
       </c>
       <c r="H25" t="n">
         <v>657690</v>
@@ -1123,7 +1123,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G26" t="n">
-        <v>2.63049650192261</v>
+        <v>2.63049697875977</v>
       </c>
       <c r="H26" t="n">
         <v>546498</v>
@@ -1152,7 +1152,7 @@
         <v>4.73799991607666</v>
       </c>
       <c r="G27" t="n">
-        <v>2.58039236068726</v>
+        <v>2.58039212226868</v>
       </c>
       <c r="H27" t="n">
         <v>737177</v>
@@ -1181,7 +1181,7 @@
         <v>4.64200019836426</v>
       </c>
       <c r="G28" t="n">
-        <v>2.5281093120575</v>
+        <v>2.52810907363892</v>
       </c>
       <c r="H28" t="n">
         <v>712797</v>
@@ -1210,7 +1210,7 @@
         <v>4.73199987411499</v>
       </c>
       <c r="G29" t="n">
-        <v>2.57712459564209</v>
+        <v>2.57712483406067</v>
       </c>
       <c r="H29" t="n">
         <v>243474</v>
@@ -1239,7 +1239,7 @@
         <v>4.74200010299683</v>
       </c>
       <c r="G30" t="n">
-        <v>2.58257102966309</v>
+        <v>2.58257055282593</v>
       </c>
       <c r="H30" t="n">
         <v>138384</v>
@@ -1268,7 +1268,7 @@
         <v>4.83799982070923</v>
       </c>
       <c r="G31" t="n">
-        <v>2.63485336303711</v>
+        <v>2.63485383987427</v>
       </c>
       <c r="H31" t="n">
         <v>253749</v>
@@ -1297,7 +1297,7 @@
         <v>4.77600002288818</v>
       </c>
       <c r="G32" t="n">
-        <v>2.60108757019043</v>
+        <v>2.60108780860901</v>
       </c>
       <c r="H32" t="n">
         <v>224481</v>
@@ -1326,7 +1326,7 @@
         <v>4.92399978637695</v>
       </c>
       <c r="G33" t="n">
-        <v>2.68169045448303</v>
+        <v>2.68169069290161</v>
       </c>
       <c r="H33" t="n">
         <v>289211</v>
@@ -1355,7 +1355,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G34" t="n">
-        <v>2.66317391395569</v>
+        <v>2.66317367553711</v>
       </c>
       <c r="H34" t="n">
         <v>156895</v>
@@ -1384,7 +1384,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G35" t="n">
-        <v>2.68495869636536</v>
+        <v>2.68495845794678</v>
       </c>
       <c r="H35" t="n">
         <v>134645</v>
@@ -1442,7 +1442,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G37" t="n">
-        <v>2.68495869636536</v>
+        <v>2.68495845794678</v>
       </c>
       <c r="H37" t="n">
         <v>213166</v>
@@ -1500,7 +1500,7 @@
         <v>4.92199993133545</v>
       </c>
       <c r="G39" t="n">
-        <v>2.68060159683228</v>
+        <v>2.68060183525085</v>
       </c>
       <c r="H39" t="n">
         <v>31918</v>
@@ -1529,7 +1529,7 @@
         <v>4.86800003051758</v>
       </c>
       <c r="G40" t="n">
-        <v>2.6511926651001</v>
+        <v>2.65119218826294</v>
       </c>
       <c r="H40" t="n">
         <v>98755</v>
@@ -1558,7 +1558,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G41" t="n">
-        <v>2.64138889312744</v>
+        <v>2.6413893699646</v>
       </c>
       <c r="H41" t="n">
         <v>200735</v>
@@ -1616,7 +1616,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G43" t="n">
-        <v>2.66862034797668</v>
+        <v>2.66861987113953</v>
       </c>
       <c r="H43" t="n">
         <v>427562</v>
@@ -1645,7 +1645,7 @@
         <v>4.87599992752075</v>
       </c>
       <c r="G44" t="n">
-        <v>2.6555495262146</v>
+        <v>2.65554881095886</v>
       </c>
       <c r="H44" t="n">
         <v>74237</v>
@@ -1674,7 +1674,7 @@
         <v>4.84600019454956</v>
       </c>
       <c r="G45" t="n">
-        <v>2.63921093940735</v>
+        <v>2.63921117782593</v>
       </c>
       <c r="H45" t="n">
         <v>152647</v>
@@ -1703,7 +1703,7 @@
         <v>4.89599990844727</v>
       </c>
       <c r="G46" t="n">
-        <v>2.66644144058228</v>
+        <v>2.66644167900085</v>
       </c>
       <c r="H46" t="n">
         <v>263706</v>
@@ -1732,7 +1732,7 @@
         <v>5.06500005722046</v>
       </c>
       <c r="G47" t="n">
-        <v>2.7584822177887</v>
+        <v>2.75848197937012</v>
       </c>
       <c r="H47" t="n">
         <v>666612</v>
@@ -1848,7 +1848,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G51" t="n">
-        <v>2.81022024154663</v>
+        <v>2.81022047996521</v>
       </c>
       <c r="H51" t="n">
         <v>347203</v>
@@ -1877,7 +1877,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G52" t="n">
-        <v>2.82111263275146</v>
+        <v>2.82111287117004</v>
       </c>
       <c r="H52" t="n">
         <v>326242</v>
@@ -1906,7 +1906,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G53" t="n">
-        <v>2.80749750137329</v>
+        <v>2.80749726295471</v>
       </c>
       <c r="H53" t="n">
         <v>204010</v>
@@ -1935,7 +1935,7 @@
         <v>5</v>
       </c>
       <c r="G54" t="n">
-        <v>2.7230818271637</v>
+        <v>2.72308206558228</v>
       </c>
       <c r="H54" t="n">
         <v>408160</v>
@@ -1964,7 +1964,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G55" t="n">
-        <v>2.76120471954346</v>
+        <v>2.76120519638062</v>
       </c>
       <c r="H55" t="n">
         <v>232368</v>
@@ -1993,7 +1993,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G56" t="n">
-        <v>2.81566667556763</v>
+        <v>2.81566643714905</v>
       </c>
       <c r="H56" t="n">
         <v>196453</v>
@@ -2051,7 +2051,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G58" t="n">
-        <v>2.81022024154663</v>
+        <v>2.81022047996521</v>
       </c>
       <c r="H58" t="n">
         <v>260985</v>
@@ -2080,7 +2080,7 @@
         <v>5</v>
       </c>
       <c r="G59" t="n">
-        <v>2.7230818271637</v>
+        <v>2.72308206558228</v>
       </c>
       <c r="H59" t="n">
         <v>282562</v>
@@ -2109,7 +2109,7 @@
         <v>5.09499979019165</v>
       </c>
       <c r="G60" t="n">
-        <v>2.77482008934021</v>
+        <v>2.77482032775879</v>
       </c>
       <c r="H60" t="n">
         <v>176285</v>
@@ -2138,7 +2138,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G61" t="n">
-        <v>2.79932808876038</v>
+        <v>2.7993278503418</v>
       </c>
       <c r="H61" t="n">
         <v>158805</v>
@@ -2167,7 +2167,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G62" t="n">
-        <v>2.78298997879028</v>
+        <v>2.78298950195312</v>
       </c>
       <c r="H62" t="n">
         <v>49073</v>
@@ -2196,7 +2196,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G63" t="n">
-        <v>2.79932808876038</v>
+        <v>2.7993278503418</v>
       </c>
       <c r="H63" t="n">
         <v>150641</v>
@@ -2254,7 +2254,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G65" t="n">
-        <v>2.79388213157654</v>
+        <v>2.79388189315796</v>
       </c>
       <c r="H65" t="n">
         <v>62383</v>
@@ -2341,7 +2341,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G68" t="n">
-        <v>2.81566667556763</v>
+        <v>2.81566643714905</v>
       </c>
       <c r="H68" t="n">
         <v>161371</v>
@@ -2399,7 +2399,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G70" t="n">
-        <v>2.80477452278137</v>
+        <v>2.80477404594421</v>
       </c>
       <c r="H70" t="n">
         <v>110557</v>
@@ -2457,7 +2457,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G72" t="n">
-        <v>2.78026652336121</v>
+        <v>2.78026604652405</v>
       </c>
       <c r="H72" t="n">
         <v>78741</v>
@@ -2486,7 +2486,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G73" t="n">
-        <v>2.78026652336121</v>
+        <v>2.78026604652405</v>
       </c>
       <c r="H73" t="n">
         <v>162459</v>
@@ -2544,7 +2544,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G75" t="n">
-        <v>2.80477452278137</v>
+        <v>2.80477404594421</v>
       </c>
       <c r="H75" t="n">
         <v>69294</v>
@@ -2602,7 +2602,7 @@
         <v>5.17500019073486</v>
       </c>
       <c r="G77" t="n">
-        <v>2.81838917732239</v>
+        <v>2.81838989257812</v>
       </c>
       <c r="H77" t="n">
         <v>63737</v>
@@ -2689,7 +2689,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G80" t="n">
-        <v>2.82111263275146</v>
+        <v>2.82111287117004</v>
       </c>
       <c r="H80" t="n">
         <v>96649</v>
@@ -2718,7 +2718,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G81" t="n">
-        <v>2.80477452278137</v>
+        <v>2.80477404594421</v>
       </c>
       <c r="H81" t="n">
         <v>169020</v>
@@ -2747,7 +2747,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G82" t="n">
-        <v>2.80477452278137</v>
+        <v>2.80477404594421</v>
       </c>
       <c r="H82" t="n">
         <v>173934</v>
@@ -2776,7 +2776,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G83" t="n">
-        <v>2.80477452278137</v>
+        <v>2.80477404594421</v>
       </c>
       <c r="H83" t="n">
         <v>134385</v>
@@ -2805,7 +2805,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G84" t="n">
-        <v>2.79932808876038</v>
+        <v>2.7993278503418</v>
       </c>
       <c r="H84" t="n">
         <v>92528</v>
@@ -2834,7 +2834,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G85" t="n">
-        <v>2.80749750137329</v>
+        <v>2.80749726295471</v>
       </c>
       <c r="H85" t="n">
         <v>646041</v>
@@ -2863,7 +2863,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G86" t="n">
-        <v>2.80477452278137</v>
+        <v>2.80477404594421</v>
       </c>
       <c r="H86" t="n">
         <v>338706</v>
@@ -2892,7 +2892,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G87" t="n">
-        <v>2.79388213157654</v>
+        <v>2.79388189315796</v>
       </c>
       <c r="H87" t="n">
         <v>216904</v>
@@ -2979,7 +2979,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G90" t="n">
-        <v>2.81566667556763</v>
+        <v>2.81566643714905</v>
       </c>
       <c r="H90" t="n">
         <v>67984</v>
@@ -3008,7 +3008,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G91" t="n">
-        <v>2.83745169639587</v>
+        <v>2.83745145797729</v>
       </c>
       <c r="H91" t="n">
         <v>178885</v>
@@ -3037,7 +3037,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G92" t="n">
-        <v>2.81566667556763</v>
+        <v>2.81566643714905</v>
       </c>
       <c r="H92" t="n">
         <v>121885</v>
@@ -3066,7 +3066,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G93" t="n">
-        <v>2.80749750137329</v>
+        <v>2.80749726295471</v>
       </c>
       <c r="H93" t="n">
         <v>91566</v>
@@ -3095,7 +3095,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G94" t="n">
-        <v>2.80749750137329</v>
+        <v>2.80749726295471</v>
       </c>
       <c r="H94" t="n">
         <v>86354</v>
@@ -3124,7 +3124,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G95" t="n">
-        <v>2.79932808876038</v>
+        <v>2.7993278503418</v>
       </c>
       <c r="H95" t="n">
         <v>110787</v>
@@ -3182,7 +3182,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G97" t="n">
-        <v>2.81566667556763</v>
+        <v>2.81566643714905</v>
       </c>
       <c r="H97" t="n">
         <v>249991</v>
@@ -3211,7 +3211,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G98" t="n">
-        <v>2.79932808876038</v>
+        <v>2.7993278503418</v>
       </c>
       <c r="H98" t="n">
         <v>73538</v>
@@ -3240,7 +3240,7 @@
         <v>5.11499977111816</v>
       </c>
       <c r="G99" t="n">
-        <v>2.78571224212646</v>
+        <v>2.78571271896362</v>
       </c>
       <c r="H99" t="n">
         <v>76893</v>
@@ -3269,7 +3269,7 @@
         <v>4.9520001411438</v>
       </c>
       <c r="G100" t="n">
-        <v>2.69694042205811</v>
+        <v>2.69694066047668</v>
       </c>
       <c r="H100" t="n">
         <v>430990</v>
@@ -3298,7 +3298,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G101" t="n">
-        <v>2.69585061073303</v>
+        <v>2.69585108757019</v>
       </c>
       <c r="H101" t="n">
         <v>151734</v>
@@ -3327,7 +3327,7 @@
         <v>4.99200010299683</v>
       </c>
       <c r="G102" t="n">
-        <v>2.71872520446777</v>
+        <v>2.71872496604919</v>
       </c>
       <c r="H102" t="n">
         <v>128275</v>
@@ -3356,7 +3356,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G103" t="n">
-        <v>2.73942041397095</v>
+        <v>2.73942017555237</v>
       </c>
       <c r="H103" t="n">
         <v>67808</v>
@@ -3385,7 +3385,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G104" t="n">
-        <v>2.81022024154663</v>
+        <v>2.81022047996521</v>
       </c>
       <c r="H104" t="n">
         <v>322247</v>
@@ -3443,7 +3443,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G106" t="n">
-        <v>2.78026652336121</v>
+        <v>2.78026604652405</v>
       </c>
       <c r="H106" t="n">
         <v>70314</v>
@@ -3646,7 +3646,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G113" t="n">
-        <v>2.86468195915222</v>
+        <v>2.86468172073364</v>
       </c>
       <c r="H113" t="n">
         <v>458239</v>
@@ -3675,7 +3675,7 @@
         <v>5.50500011444092</v>
       </c>
       <c r="G114" t="n">
-        <v>2.99811315536499</v>
+        <v>2.99811291694641</v>
       </c>
       <c r="H114" t="n">
         <v>826293</v>
@@ -3704,7 +3704,7 @@
         <v>5.49499988555908</v>
       </c>
       <c r="G115" t="n">
-        <v>2.99266695976257</v>
+        <v>2.99266719818115</v>
       </c>
       <c r="H115" t="n">
         <v>356186</v>
@@ -3733,7 +3733,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G116" t="n">
-        <v>3.02806735038757</v>
+        <v>3.02806711196899</v>
       </c>
       <c r="H116" t="n">
         <v>223092</v>
@@ -3820,7 +3820,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G119" t="n">
-        <v>3.08797478675842</v>
+        <v>3.087975025177</v>
       </c>
       <c r="H119" t="n">
         <v>355437</v>
@@ -3907,7 +3907,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G122" t="n">
-        <v>3.21323657035828</v>
+        <v>3.21323680877686</v>
       </c>
       <c r="H122" t="n">
         <v>312872</v>
@@ -3936,7 +3936,7 @@
         <v>5.75</v>
       </c>
       <c r="G123" t="n">
-        <v>3.1315438747406</v>
+        <v>3.13154411315918</v>
       </c>
       <c r="H123" t="n">
         <v>633225</v>
@@ -3965,7 +3965,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G124" t="n">
-        <v>3.1968982219696</v>
+        <v>3.19689798355103</v>
       </c>
       <c r="H124" t="n">
         <v>236136</v>
@@ -3994,7 +3994,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G125" t="n">
-        <v>3.12609791755676</v>
+        <v>3.12609767913818</v>
       </c>
       <c r="H125" t="n">
         <v>258170</v>
@@ -4052,7 +4052,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G127" t="n">
-        <v>3.14243650436401</v>
+        <v>3.14243674278259</v>
       </c>
       <c r="H127" t="n">
         <v>218228</v>
@@ -4081,7 +4081,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G128" t="n">
-        <v>3.10431313514709</v>
+        <v>3.10431361198425</v>
       </c>
       <c r="H128" t="n">
         <v>185479</v>
@@ -4139,7 +4139,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G130" t="n">
-        <v>3.15877509117126</v>
+        <v>3.15877461433411</v>
       </c>
       <c r="H130" t="n">
         <v>217232</v>
@@ -4168,7 +4168,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G131" t="n">
-        <v>3.20234441757202</v>
+        <v>3.20234417915344</v>
       </c>
       <c r="H131" t="n">
         <v>262047</v>
@@ -4226,7 +4226,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G133" t="n">
-        <v>3.32215929031372</v>
+        <v>3.32215976715088</v>
       </c>
       <c r="H133" t="n">
         <v>490719</v>
@@ -4255,7 +4255,7 @@
         <v>6.125</v>
       </c>
       <c r="G134" t="n">
-        <v>3.33577513694763</v>
+        <v>3.33577561378479</v>
       </c>
       <c r="H134" t="n">
         <v>653279</v>
@@ -4284,7 +4284,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G135" t="n">
-        <v>3.30582165718079</v>
+        <v>3.30582118034363</v>
       </c>
       <c r="H135" t="n">
         <v>362617</v>
@@ -4313,7 +4313,7 @@
         <v>6.11499977111816</v>
       </c>
       <c r="G136" t="n">
-        <v>3.33032846450806</v>
+        <v>3.33032894134521</v>
       </c>
       <c r="H136" t="n">
         <v>223437</v>
@@ -4342,7 +4342,7 @@
         <v>6.04500007629395</v>
       </c>
       <c r="G137" t="n">
-        <v>3.29220581054688</v>
+        <v>3.2922055721283</v>
       </c>
       <c r="H137" t="n">
         <v>375661</v>
@@ -4371,7 +4371,7 @@
         <v>6</v>
       </c>
       <c r="G138" t="n">
-        <v>3.26769804954529</v>
+        <v>3.26769828796387</v>
       </c>
       <c r="H138" t="n">
         <v>214993</v>
@@ -4400,7 +4400,7 @@
         <v>6.11499977111816</v>
       </c>
       <c r="G139" t="n">
-        <v>3.33032846450806</v>
+        <v>3.33032894134521</v>
       </c>
       <c r="H139" t="n">
         <v>151537</v>
@@ -4458,7 +4458,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G141" t="n">
-        <v>3.32215929031372</v>
+        <v>3.32215976715088</v>
       </c>
       <c r="H141" t="n">
         <v>185465</v>
@@ -4487,7 +4487,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G142" t="n">
-        <v>3.34939050674438</v>
+        <v>3.34939098358154</v>
       </c>
       <c r="H142" t="n">
         <v>178387</v>
@@ -4545,7 +4545,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G144" t="n">
-        <v>3.3875138759613</v>
+        <v>3.38751363754272</v>
       </c>
       <c r="H144" t="n">
         <v>271554</v>
@@ -4574,7 +4574,7 @@
         <v>6.25</v>
       </c>
       <c r="G145" t="n">
-        <v>3.40385222434998</v>
+        <v>3.40385270118713</v>
       </c>
       <c r="H145" t="n">
         <v>169413</v>
@@ -4603,7 +4603,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G146" t="n">
-        <v>3.38206768035889</v>
+        <v>3.38206744194031</v>
       </c>
       <c r="H146" t="n">
         <v>189558</v>
@@ -4632,7 +4632,7 @@
         <v>6.11499977111816</v>
       </c>
       <c r="G147" t="n">
-        <v>3.33032846450806</v>
+        <v>3.33032894134521</v>
       </c>
       <c r="H147" t="n">
         <v>211124</v>
@@ -4661,7 +4661,7 @@
         <v>6.02500009536743</v>
       </c>
       <c r="G148" t="n">
-        <v>3.28131365776062</v>
+        <v>3.28131341934204</v>
       </c>
       <c r="H148" t="n">
         <v>424488</v>
@@ -4690,7 +4690,7 @@
         <v>6.00500011444092</v>
       </c>
       <c r="G149" t="n">
-        <v>3.27042198181152</v>
+        <v>3.27042150497437</v>
       </c>
       <c r="H149" t="n">
         <v>352526</v>
@@ -4748,7 +4748,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G151" t="n">
-        <v>3.28403687477112</v>
+        <v>3.28403639793396</v>
       </c>
       <c r="H151" t="n">
         <v>1050651</v>
@@ -4806,7 +4806,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G153" t="n">
-        <v>3.24591326713562</v>
+        <v>3.24591374397278</v>
       </c>
       <c r="H153" t="n">
         <v>259079</v>
@@ -4864,7 +4864,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G155" t="n">
-        <v>3.21323657035828</v>
+        <v>3.21323680877686</v>
       </c>
       <c r="H155" t="n">
         <v>247331</v>
@@ -4893,7 +4893,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G156" t="n">
-        <v>3.27314448356628</v>
+        <v>3.27314424514771</v>
       </c>
       <c r="H156" t="n">
         <v>248030</v>
@@ -4922,7 +4922,7 @@
         <v>6</v>
       </c>
       <c r="G157" t="n">
-        <v>3.26769804954529</v>
+        <v>3.26769828796387</v>
       </c>
       <c r="H157" t="n">
         <v>312140</v>
@@ -4951,7 +4951,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G158" t="n">
-        <v>3.32760620117188</v>
+        <v>3.3276059627533</v>
       </c>
       <c r="H158" t="n">
         <v>187242</v>
@@ -4980,7 +4980,7 @@
         <v>6.125</v>
       </c>
       <c r="G159" t="n">
-        <v>3.33577513694763</v>
+        <v>3.33577561378479</v>
       </c>
       <c r="H159" t="n">
         <v>172302</v>
@@ -5009,7 +5009,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G160" t="n">
-        <v>3.36028289794922</v>
+        <v>3.3602831363678</v>
       </c>
       <c r="H160" t="n">
         <v>149678</v>
@@ -5038,7 +5038,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G161" t="n">
-        <v>3.38206768035889</v>
+        <v>3.38206744194031</v>
       </c>
       <c r="H161" t="n">
         <v>102667</v>
@@ -5067,7 +5067,7 @@
         <v>6.40999984741211</v>
       </c>
       <c r="G162" t="n">
-        <v>3.49099087715149</v>
+        <v>3.49099111557007</v>
       </c>
       <c r="H162" t="n">
         <v>474666</v>
@@ -5154,7 +5154,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G165" t="n">
-        <v>3.45831394195557</v>
+        <v>3.45831346511841</v>
       </c>
       <c r="H165" t="n">
         <v>177233</v>
@@ -5183,7 +5183,7 @@
         <v>6.41499996185303</v>
       </c>
       <c r="G166" t="n">
-        <v>3.49371337890625</v>
+        <v>3.49371361732483</v>
       </c>
       <c r="H166" t="n">
         <v>319302</v>
@@ -5212,7 +5212,7 @@
         <v>6.45499992370605</v>
       </c>
       <c r="G167" t="n">
-        <v>3.51549863815308</v>
+        <v>3.5154983997345</v>
       </c>
       <c r="H167" t="n">
         <v>1366720</v>
@@ -5328,7 +5328,7 @@
         <v>6.40999984741211</v>
       </c>
       <c r="G171" t="n">
-        <v>3.49099087715149</v>
+        <v>3.49099111557007</v>
       </c>
       <c r="H171" t="n">
         <v>199264</v>
@@ -5415,7 +5415,7 @@
         <v>6.58500003814697</v>
       </c>
       <c r="G174" t="n">
-        <v>3.58629894256592</v>
+        <v>3.58629870414734</v>
       </c>
       <c r="H174" t="n">
         <v>218569</v>
@@ -5444,7 +5444,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G175" t="n">
-        <v>3.59446787834167</v>
+        <v>3.5944676399231</v>
       </c>
       <c r="H175" t="n">
         <v>269404</v>
@@ -5473,7 +5473,7 @@
         <v>6.53000020980835</v>
       </c>
       <c r="G176" t="n">
-        <v>3.55634498596191</v>
+        <v>3.55634522438049</v>
       </c>
       <c r="H176" t="n">
         <v>106003</v>
@@ -5531,7 +5531,7 @@
         <v>6.53499984741211</v>
       </c>
       <c r="G178" t="n">
-        <v>3.5590672492981</v>
+        <v>3.55906772613525</v>
       </c>
       <c r="H178" t="n">
         <v>1769120</v>
@@ -5560,7 +5560,7 @@
         <v>6.5149998664856</v>
       </c>
       <c r="G179" t="n">
-        <v>3.54817533493042</v>
+        <v>3.548175573349</v>
       </c>
       <c r="H179" t="n">
         <v>157084</v>
@@ -5589,7 +5589,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G180" t="n">
-        <v>3.61080598831177</v>
+        <v>3.61080646514893</v>
       </c>
       <c r="H180" t="n">
         <v>190579</v>
@@ -5618,7 +5618,7 @@
         <v>6.375</v>
       </c>
       <c r="G181" t="n">
-        <v>3.47192883491516</v>
+        <v>3.47192978858948</v>
       </c>
       <c r="H181" t="n">
         <v>417337</v>
@@ -5676,7 +5676,7 @@
         <v>6.25</v>
       </c>
       <c r="G183" t="n">
-        <v>3.40385222434998</v>
+        <v>3.40385270118713</v>
       </c>
       <c r="H183" t="n">
         <v>163948</v>
@@ -5705,7 +5705,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G184" t="n">
-        <v>3.44742107391357</v>
+        <v>3.44742155075073</v>
       </c>
       <c r="H184" t="n">
         <v>187122</v>
@@ -5734,7 +5734,7 @@
         <v>6.38500022888184</v>
       </c>
       <c r="G185" t="n">
-        <v>3.47737503051758</v>
+        <v>3.47737574577332</v>
       </c>
       <c r="H185" t="n">
         <v>256687</v>
@@ -5763,7 +5763,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G186" t="n">
-        <v>3.48554468154907</v>
+        <v>3.48554444313049</v>
       </c>
       <c r="H186" t="n">
         <v>124137</v>
@@ -5792,7 +5792,7 @@
         <v>6.41499996185303</v>
       </c>
       <c r="G187" t="n">
-        <v>3.49371337890625</v>
+        <v>3.49371361732483</v>
       </c>
       <c r="H187" t="n">
         <v>155738</v>
@@ -5821,7 +5821,7 @@
         <v>6.53499984741211</v>
       </c>
       <c r="G188" t="n">
-        <v>3.5590672492981</v>
+        <v>3.55906772613525</v>
       </c>
       <c r="H188" t="n">
         <v>188172</v>
@@ -5850,7 +5850,7 @@
         <v>6.5</v>
       </c>
       <c r="G189" t="n">
-        <v>3.54000663757324</v>
+        <v>3.54000639915466</v>
       </c>
       <c r="H189" t="n">
         <v>147545</v>
@@ -5879,7 +5879,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G190" t="n">
-        <v>3.54545283317566</v>
+        <v>3.54545259475708</v>
       </c>
       <c r="H190" t="n">
         <v>100540</v>
@@ -5908,7 +5908,7 @@
         <v>6.5</v>
       </c>
       <c r="G191" t="n">
-        <v>3.54000663757324</v>
+        <v>3.54000639915466</v>
       </c>
       <c r="H191" t="n">
         <v>187692</v>
@@ -5937,7 +5937,7 @@
         <v>6.43499994277954</v>
       </c>
       <c r="G192" t="n">
-        <v>3.50460624694824</v>
+        <v>3.50460648536682</v>
       </c>
       <c r="H192" t="n">
         <v>350852</v>
@@ -6024,7 +6024,7 @@
         <v>6.46500015258789</v>
       </c>
       <c r="G195" t="n">
-        <v>3.52094483375549</v>
+        <v>3.52094459533691</v>
       </c>
       <c r="H195" t="n">
         <v>418341</v>
@@ -6053,7 +6053,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G196" t="n">
-        <v>3.52911424636841</v>
+        <v>3.52911376953125</v>
       </c>
       <c r="H196" t="n">
         <v>260163</v>
@@ -6082,7 +6082,7 @@
         <v>6.5</v>
       </c>
       <c r="G197" t="n">
-        <v>3.54000663757324</v>
+        <v>3.54000639915466</v>
       </c>
       <c r="H197" t="n">
         <v>305887</v>
@@ -6111,7 +6111,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G198" t="n">
-        <v>3.54545283317566</v>
+        <v>3.54545259475708</v>
       </c>
       <c r="H198" t="n">
         <v>218115</v>
@@ -6140,7 +6140,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G199" t="n">
-        <v>3.54545283317566</v>
+        <v>3.54545259475708</v>
       </c>
       <c r="H199" t="n">
         <v>236976</v>
@@ -6169,7 +6169,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G200" t="n">
-        <v>3.54545283317566</v>
+        <v>3.54545259475708</v>
       </c>
       <c r="H200" t="n">
         <v>242488</v>
@@ -6198,7 +6198,7 @@
         <v>6.57499980926514</v>
       </c>
       <c r="G201" t="n">
-        <v>3.58085250854492</v>
+        <v>3.5808527469635</v>
       </c>
       <c r="H201" t="n">
         <v>324190</v>
@@ -6256,7 +6256,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G203" t="n">
-        <v>3.59446787834167</v>
+        <v>3.5944676399231</v>
       </c>
       <c r="H203" t="n">
         <v>289318</v>
@@ -6285,7 +6285,7 @@
         <v>6.53000020980835</v>
       </c>
       <c r="G204" t="n">
-        <v>3.55634498596191</v>
+        <v>3.55634522438049</v>
       </c>
       <c r="H204" t="n">
         <v>263917</v>
@@ -6314,7 +6314,7 @@
         <v>6.59499979019165</v>
       </c>
       <c r="G205" t="n">
-        <v>3.59174489974976</v>
+        <v>3.59174466133118</v>
       </c>
       <c r="H205" t="n">
         <v>305878</v>
@@ -6343,7 +6343,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G206" t="n">
-        <v>3.59991407394409</v>
+        <v>3.59991383552551</v>
       </c>
       <c r="H206" t="n">
         <v>182453</v>
@@ -6372,7 +6372,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G207" t="n">
-        <v>3.54545283317566</v>
+        <v>3.54545259475708</v>
       </c>
       <c r="H207" t="n">
         <v>240046</v>
@@ -6401,7 +6401,7 @@
         <v>6.4850001335144</v>
       </c>
       <c r="G208" t="n">
-        <v>3.53183674812317</v>
+        <v>3.53183722496033</v>
       </c>
       <c r="H208" t="n">
         <v>191731</v>
@@ -6430,7 +6430,7 @@
         <v>6.41499996185303</v>
       </c>
       <c r="G209" t="n">
-        <v>3.49371337890625</v>
+        <v>3.49371361732483</v>
       </c>
       <c r="H209" t="n">
         <v>424467</v>
@@ -6459,7 +6459,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G210" t="n">
-        <v>3.29492902755737</v>
+        <v>3.29492926597595</v>
       </c>
       <c r="H210" t="n">
         <v>1379424</v>
@@ -6488,7 +6488,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G211" t="n">
-        <v>3.28403687477112</v>
+        <v>3.28403639793396</v>
       </c>
       <c r="H211" t="n">
         <v>569842</v>
@@ -6517,7 +6517,7 @@
         <v>5.91499996185303</v>
       </c>
       <c r="G212" t="n">
-        <v>3.22140526771545</v>
+        <v>3.22140598297119</v>
       </c>
       <c r="H212" t="n">
         <v>551509</v>
@@ -6546,7 +6546,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G213" t="n">
-        <v>3.2785906791687</v>
+        <v>3.27859044075012</v>
       </c>
       <c r="H213" t="n">
         <v>502251</v>
@@ -6575,7 +6575,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G214" t="n">
-        <v>3.12065172195435</v>
+        <v>3.12065148353577</v>
       </c>
       <c r="H214" t="n">
         <v>491862</v>
@@ -6662,7 +6662,7 @@
         <v>5.81500005722046</v>
       </c>
       <c r="G217" t="n">
-        <v>3.1669442653656</v>
+        <v>3.16694402694702</v>
       </c>
       <c r="H217" t="n">
         <v>376884</v>
@@ -6691,7 +6691,7 @@
         <v>5.93499994277954</v>
       </c>
       <c r="G218" t="n">
-        <v>3.23229813575745</v>
+        <v>3.23229765892029</v>
       </c>
       <c r="H218" t="n">
         <v>202608</v>
@@ -6720,7 +6720,7 @@
         <v>6</v>
       </c>
       <c r="G219" t="n">
-        <v>3.26769804954529</v>
+        <v>3.26769828796387</v>
       </c>
       <c r="H219" t="n">
         <v>193373</v>
@@ -6749,7 +6749,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G220" t="n">
-        <v>3.38206768035889</v>
+        <v>3.38206744194031</v>
       </c>
       <c r="H220" t="n">
         <v>329166</v>
@@ -6778,7 +6778,7 @@
         <v>6.14499998092651</v>
       </c>
       <c r="G221" t="n">
-        <v>3.34666728973389</v>
+        <v>3.34666752815247</v>
       </c>
       <c r="H221" t="n">
         <v>229142</v>
@@ -6807,7 +6807,7 @@
         <v>6.16499996185303</v>
       </c>
       <c r="G222" t="n">
-        <v>3.3575599193573</v>
+        <v>3.35755968093872</v>
       </c>
       <c r="H222" t="n">
         <v>146326</v>
@@ -6836,7 +6836,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G223" t="n">
-        <v>3.21323657035828</v>
+        <v>3.21323680877686</v>
       </c>
       <c r="H223" t="n">
         <v>6562008</v>
@@ -6865,7 +6865,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G224" t="n">
-        <v>3.18055939674377</v>
+        <v>3.18055963516235</v>
       </c>
       <c r="H224" t="n">
         <v>610892</v>
@@ -6952,7 +6952,7 @@
         <v>5.81500005722046</v>
       </c>
       <c r="G227" t="n">
-        <v>3.1669442653656</v>
+        <v>3.16694402694702</v>
       </c>
       <c r="H227" t="n">
         <v>613256</v>
@@ -6981,7 +6981,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G228" t="n">
-        <v>3.18600559234619</v>
+        <v>3.18600535392761</v>
       </c>
       <c r="H228" t="n">
         <v>292988</v>
@@ -7010,7 +7010,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G229" t="n">
-        <v>3.18600559234619</v>
+        <v>3.18600535392761</v>
       </c>
       <c r="H229" t="n">
         <v>343071</v>
@@ -7039,7 +7039,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G230" t="n">
-        <v>3.17511296272278</v>
+        <v>3.17511391639709</v>
       </c>
       <c r="H230" t="n">
         <v>422499</v>
@@ -7068,7 +7068,7 @@
         <v>5.78499984741211</v>
       </c>
       <c r="G231" t="n">
-        <v>3.15060567855835</v>
+        <v>3.15060544013977</v>
       </c>
       <c r="H231" t="n">
         <v>350773</v>
@@ -7097,7 +7097,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G232" t="n">
-        <v>3.15877509117126</v>
+        <v>3.15877461433411</v>
       </c>
       <c r="H232" t="n">
         <v>351826</v>
@@ -7155,7 +7155,7 @@
         <v>5.88500022888184</v>
       </c>
       <c r="G234" t="n">
-        <v>3.20506691932678</v>
+        <v>3.20506715774536</v>
       </c>
       <c r="H234" t="n">
         <v>425600</v>
@@ -7213,7 +7213,7 @@
         <v>6.04500007629395</v>
       </c>
       <c r="G236" t="n">
-        <v>3.29220581054688</v>
+        <v>3.2922055721283</v>
       </c>
       <c r="H236" t="n">
         <v>640079</v>
@@ -7300,7 +7300,7 @@
         <v>5.88500022888184</v>
       </c>
       <c r="G239" t="n">
-        <v>3.20506691932678</v>
+        <v>3.20506715774536</v>
       </c>
       <c r="H239" t="n">
         <v>420138</v>
@@ -7329,7 +7329,7 @@
         <v>5.91499996185303</v>
       </c>
       <c r="G240" t="n">
-        <v>3.22140526771545</v>
+        <v>3.22140598297119</v>
       </c>
       <c r="H240" t="n">
         <v>647032</v>
@@ -7358,7 +7358,7 @@
         <v>5.88500022888184</v>
       </c>
       <c r="G241" t="n">
-        <v>3.20506691932678</v>
+        <v>3.20506715774536</v>
       </c>
       <c r="H241" t="n">
         <v>352034</v>
@@ -7387,7 +7387,7 @@
         <v>5.75</v>
       </c>
       <c r="G242" t="n">
-        <v>3.1315438747406</v>
+        <v>3.13154411315918</v>
       </c>
       <c r="H242" t="n">
         <v>1209727</v>
@@ -7416,7 +7416,7 @@
         <v>5.7350001335144</v>
       </c>
       <c r="G243" t="n">
-        <v>3.12337470054626</v>
+        <v>3.12337446212769</v>
       </c>
       <c r="H243" t="n">
         <v>509155</v>
@@ -7445,7 +7445,7 @@
         <v>5.71500015258789</v>
       </c>
       <c r="G244" t="n">
-        <v>3.11248254776001</v>
+        <v>3.11248278617859</v>
       </c>
       <c r="H244" t="n">
         <v>350856</v>
@@ -7474,7 +7474,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G245" t="n">
-        <v>3.08797478675842</v>
+        <v>3.087975025177</v>
       </c>
       <c r="H245" t="n">
         <v>494103</v>
@@ -7503,7 +7503,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G246" t="n">
-        <v>3.09342050552368</v>
+        <v>3.09342074394226</v>
       </c>
       <c r="H246" t="n">
         <v>298347</v>
@@ -7532,7 +7532,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G247" t="n">
-        <v>3.16422057151794</v>
+        <v>3.16422080993652</v>
       </c>
       <c r="H247" t="n">
         <v>360292</v>
@@ -7561,7 +7561,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G248" t="n">
-        <v>3.18600559234619</v>
+        <v>3.18600535392761</v>
       </c>
       <c r="H248" t="n">
         <v>453538</v>
@@ -7590,7 +7590,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G249" t="n">
-        <v>3.23502063751221</v>
+        <v>3.23502111434937</v>
       </c>
       <c r="H249" t="n">
         <v>513814</v>
@@ -7619,7 +7619,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G250" t="n">
-        <v>3.21323657035828</v>
+        <v>3.21323680877686</v>
       </c>
       <c r="H250" t="n">
         <v>872993</v>
@@ -7648,7 +7648,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G251" t="n">
-        <v>3.18600559234619</v>
+        <v>3.18600535392761</v>
       </c>
       <c r="H251" t="n">
         <v>587417</v>
@@ -7677,7 +7677,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G252" t="n">
-        <v>3.20779037475586</v>
+        <v>3.20779013633728</v>
       </c>
       <c r="H252" t="n">
         <v>1027562</v>
@@ -7706,7 +7706,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G253" t="n">
-        <v>3.20234441757202</v>
+        <v>3.20234417915344</v>
       </c>
       <c r="H253" t="n">
         <v>1032003</v>
@@ -7735,7 +7735,7 @@
         <v>5.5</v>
       </c>
       <c r="G254" t="n">
-        <v>3.26891136169434</v>
+        <v>3.26891112327576</v>
       </c>
       <c r="H254" t="n">
         <v>1331386</v>
@@ -7764,7 +7764,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G255" t="n">
-        <v>3.26296758651733</v>
+        <v>3.26296782493591</v>
       </c>
       <c r="H255" t="n">
         <v>491744</v>
@@ -7793,7 +7793,7 @@
         <v>5.32499980926514</v>
       </c>
       <c r="G256" t="n">
-        <v>3.16490030288696</v>
+        <v>3.16490054130554</v>
       </c>
       <c r="H256" t="n">
         <v>461820</v>
@@ -7822,7 +7822,7 @@
         <v>5.5</v>
       </c>
       <c r="G257" t="n">
-        <v>3.26891136169434</v>
+        <v>3.26891112327576</v>
       </c>
       <c r="H257" t="n">
         <v>490521</v>
@@ -7880,7 +7880,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G259" t="n">
-        <v>3.21541976928711</v>
+        <v>3.21542000770569</v>
       </c>
       <c r="H259" t="n">
         <v>658405</v>
@@ -7909,7 +7909,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G260" t="n">
-        <v>3.15598487854004</v>
+        <v>3.1559853553772</v>
       </c>
       <c r="H260" t="n">
         <v>979931</v>
@@ -7967,7 +7967,7 @@
         <v>5.41499996185303</v>
       </c>
       <c r="G262" t="n">
-        <v>3.21839165687561</v>
+        <v>3.21839141845703</v>
       </c>
       <c r="H262" t="n">
         <v>292368</v>
@@ -7996,7 +7996,7 @@
         <v>5.35500001907349</v>
       </c>
       <c r="G263" t="n">
-        <v>3.18273091316223</v>
+        <v>3.18273067474365</v>
       </c>
       <c r="H263" t="n">
         <v>387880</v>
@@ -8025,7 +8025,7 @@
         <v>5.36499977111816</v>
       </c>
       <c r="G264" t="n">
-        <v>3.18867444992065</v>
+        <v>3.1886739730835</v>
       </c>
       <c r="H264" t="n">
         <v>221866</v>
@@ -8054,7 +8054,7 @@
         <v>5.25500011444092</v>
       </c>
       <c r="G265" t="n">
-        <v>3.12329578399658</v>
+        <v>3.12329602241516</v>
       </c>
       <c r="H265" t="n">
         <v>577217</v>
@@ -8083,7 +8083,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G266" t="n">
-        <v>3.06386137008667</v>
+        <v>3.06386113166809</v>
       </c>
       <c r="H266" t="n">
         <v>347362</v>
@@ -8112,7 +8112,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G267" t="n">
-        <v>3.13815450668335</v>
+        <v>3.13815498352051</v>
       </c>
       <c r="H267" t="n">
         <v>982246</v>
@@ -8141,7 +8141,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G268" t="n">
-        <v>3.06088972091675</v>
+        <v>3.06088948249817</v>
       </c>
       <c r="H268" t="n">
         <v>438786</v>
@@ -8199,7 +8199,7 @@
         <v>5.25</v>
       </c>
       <c r="G270" t="n">
-        <v>3.12032437324524</v>
+        <v>3.12032413482666</v>
       </c>
       <c r="H270" t="n">
         <v>329941</v>
@@ -8228,7 +8228,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G271" t="n">
-        <v>3.13815450668335</v>
+        <v>3.13815498352051</v>
       </c>
       <c r="H271" t="n">
         <v>288840</v>
@@ -8257,7 +8257,7 @@
         <v>5.25500011444092</v>
       </c>
       <c r="G272" t="n">
-        <v>3.12329578399658</v>
+        <v>3.12329602241516</v>
       </c>
       <c r="H272" t="n">
         <v>328311</v>
@@ -8315,7 +8315,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G274" t="n">
-        <v>3.09655070304871</v>
+        <v>3.09655046463013</v>
       </c>
       <c r="H274" t="n">
         <v>417330</v>
@@ -8344,7 +8344,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G275" t="n">
-        <v>3.07277655601501</v>
+        <v>3.07277631759644</v>
       </c>
       <c r="H275" t="n">
         <v>698355</v>
@@ -8373,7 +8373,7 @@
         <v>5.02500009536743</v>
       </c>
       <c r="G276" t="n">
-        <v>2.98659634590149</v>
+        <v>2.98659563064575</v>
       </c>
       <c r="H276" t="n">
         <v>1166871</v>
@@ -8402,7 +8402,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G277" t="n">
-        <v>3.00739789009094</v>
+        <v>3.00739812850952</v>
       </c>
       <c r="H277" t="n">
         <v>576090</v>
@@ -8460,7 +8460,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G279" t="n">
-        <v>3.01928520202637</v>
+        <v>3.01928496360779</v>
       </c>
       <c r="H279" t="n">
         <v>636693</v>
@@ -8489,7 +8489,7 @@
         <v>4.96600008010864</v>
       </c>
       <c r="G280" t="n">
-        <v>2.95152974128723</v>
+        <v>2.95152950286865</v>
       </c>
       <c r="H280" t="n">
         <v>674444</v>
@@ -8547,7 +8547,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G282" t="n">
-        <v>3.05494594573975</v>
+        <v>3.05494570732117</v>
       </c>
       <c r="H282" t="n">
         <v>828859</v>
@@ -8576,7 +8576,7 @@
         <v>5.07499980926514</v>
       </c>
       <c r="G283" t="n">
-        <v>3.01631379127502</v>
+        <v>3.01631355285645</v>
       </c>
       <c r="H283" t="n">
         <v>226230</v>
@@ -8605,7 +8605,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G284" t="n">
-        <v>3.03414392471313</v>
+        <v>3.03414344787598</v>
       </c>
       <c r="H284" t="n">
         <v>446617</v>
@@ -8634,7 +8634,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G285" t="n">
-        <v>2.98362445831299</v>
+        <v>2.98362398147583</v>
       </c>
       <c r="H285" t="n">
         <v>352758</v>
@@ -8663,7 +8663,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G286" t="n">
-        <v>3.03117227554321</v>
+        <v>3.03117179870605</v>
       </c>
       <c r="H286" t="n">
         <v>247206</v>
@@ -8692,7 +8692,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G287" t="n">
-        <v>3.06386137008667</v>
+        <v>3.06386113166809</v>
       </c>
       <c r="H287" t="n">
         <v>682895</v>
@@ -8721,7 +8721,7 @@
         <v>5.04500007629395</v>
       </c>
       <c r="G288" t="n">
-        <v>2.99848318099976</v>
+        <v>2.99848341941833</v>
       </c>
       <c r="H288" t="n">
         <v>534293</v>
@@ -8750,7 +8750,7 @@
         <v>4.89200019836426</v>
       </c>
       <c r="G289" t="n">
-        <v>2.90754818916321</v>
+        <v>2.90754771232605</v>
       </c>
       <c r="H289" t="n">
         <v>537893</v>
@@ -8779,7 +8779,7 @@
         <v>5.07499980926514</v>
       </c>
       <c r="G290" t="n">
-        <v>3.01631379127502</v>
+        <v>3.01631355285645</v>
       </c>
       <c r="H290" t="n">
         <v>585591</v>
@@ -8808,7 +8808,7 @@
         <v>5.07499980926514</v>
       </c>
       <c r="G291" t="n">
-        <v>3.01631379127502</v>
+        <v>3.01631355285645</v>
       </c>
       <c r="H291" t="n">
         <v>697953</v>
@@ -8837,7 +8837,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G292" t="n">
-        <v>3.05791759490967</v>
+        <v>3.05791735649109</v>
       </c>
       <c r="H292" t="n">
         <v>416047</v>
@@ -8866,7 +8866,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G293" t="n">
-        <v>3.09060668945312</v>
+        <v>3.0906069278717</v>
       </c>
       <c r="H293" t="n">
         <v>267972</v>
@@ -8895,7 +8895,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G294" t="n">
-        <v>3.06683278083801</v>
+        <v>3.06683301925659</v>
       </c>
       <c r="H294" t="n">
         <v>263638</v>
@@ -8924,7 +8924,7 @@
         <v>5.11499977111816</v>
       </c>
       <c r="G295" t="n">
-        <v>3.0400869846344</v>
+        <v>3.04008722305298</v>
       </c>
       <c r="H295" t="n">
         <v>461713</v>
@@ -8982,7 +8982,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G297" t="n">
-        <v>3.03711605072021</v>
+        <v>3.03711557388306</v>
       </c>
       <c r="H297" t="n">
         <v>116870</v>
@@ -9011,7 +9011,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G298" t="n">
-        <v>3.06088972091675</v>
+        <v>3.06088948249817</v>
       </c>
       <c r="H298" t="n">
         <v>328764</v>
@@ -9069,7 +9069,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G300" t="n">
-        <v>3.09060668945312</v>
+        <v>3.0906069278717</v>
       </c>
       <c r="H300" t="n">
         <v>174295</v>
@@ -9098,7 +9098,7 @@
         <v>5.29500007629395</v>
       </c>
       <c r="G301" t="n">
-        <v>3.14706993103027</v>
+        <v>3.14707016944885</v>
       </c>
       <c r="H301" t="n">
         <v>597621</v>
@@ -9127,7 +9127,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G302" t="n">
-        <v>3.13221144676208</v>
+        <v>3.13221096992493</v>
       </c>
       <c r="H302" t="n">
         <v>987196</v>
@@ -9156,7 +9156,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G303" t="n">
-        <v>3.15598487854004</v>
+        <v>3.1559853553772</v>
       </c>
       <c r="H303" t="n">
         <v>235545</v>
@@ -9243,7 +9243,7 @@
         <v>5.34499979019165</v>
       </c>
       <c r="G306" t="n">
-        <v>3.17678737640381</v>
+        <v>3.17678713798523</v>
       </c>
       <c r="H306" t="n">
         <v>272584</v>
@@ -9272,7 +9272,7 @@
         <v>5.13500022888184</v>
       </c>
       <c r="G307" t="n">
-        <v>3.05197405815125</v>
+        <v>3.0519745349884</v>
       </c>
       <c r="H307" t="n">
         <v>2197467</v>
@@ -9301,7 +9301,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G308" t="n">
-        <v>3.01928520202637</v>
+        <v>3.01928496360779</v>
       </c>
       <c r="H308" t="n">
         <v>172506</v>
@@ -9330,7 +9330,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G309" t="n">
-        <v>3.01334142684937</v>
+        <v>3.01334190368652</v>
       </c>
       <c r="H309" t="n">
         <v>403149</v>
@@ -9359,7 +9359,7 @@
         <v>4.95599985122681</v>
       </c>
       <c r="G310" t="n">
-        <v>2.94558620452881</v>
+        <v>2.94558596611023</v>
       </c>
       <c r="H310" t="n">
         <v>428973</v>
@@ -9388,7 +9388,7 @@
         <v>4.9539999961853</v>
       </c>
       <c r="G311" t="n">
-        <v>2.94439697265625</v>
+        <v>2.94439721107483</v>
       </c>
       <c r="H311" t="n">
         <v>179330</v>
@@ -9417,7 +9417,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G312" t="n">
-        <v>2.98362445831299</v>
+        <v>2.98362398147583</v>
       </c>
       <c r="H312" t="n">
         <v>142945</v>
@@ -9475,7 +9475,7 @@
         <v>5.02500009536743</v>
       </c>
       <c r="G314" t="n">
-        <v>2.98659634590149</v>
+        <v>2.98659563064575</v>
       </c>
       <c r="H314" t="n">
         <v>109457</v>
@@ -9504,7 +9504,7 @@
         <v>4.93200016021729</v>
       </c>
       <c r="G315" t="n">
-        <v>2.93132185935974</v>
+        <v>2.93132209777832</v>
       </c>
       <c r="H315" t="n">
         <v>154692</v>
@@ -9533,7 +9533,7 @@
         <v>4.96199989318848</v>
       </c>
       <c r="G316" t="n">
-        <v>2.94915246963501</v>
+        <v>2.94915199279785</v>
       </c>
       <c r="H316" t="n">
         <v>227692</v>
@@ -9562,7 +9562,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G317" t="n">
-        <v>2.98956799507141</v>
+        <v>2.98956751823425</v>
       </c>
       <c r="H317" t="n">
         <v>166858</v>
@@ -9591,7 +9591,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G318" t="n">
-        <v>3.05791759490967</v>
+        <v>3.05791735649109</v>
       </c>
       <c r="H318" t="n">
         <v>170278</v>
@@ -9620,7 +9620,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G319" t="n">
-        <v>3.07277655601501</v>
+        <v>3.07277631759644</v>
       </c>
       <c r="H319" t="n">
         <v>153750</v>
@@ -9678,7 +9678,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G321" t="n">
-        <v>3.02522826194763</v>
+        <v>3.02522873878479</v>
       </c>
       <c r="H321" t="n">
         <v>173975</v>
@@ -9707,7 +9707,7 @@
         <v>5.13500022888184</v>
       </c>
       <c r="G322" t="n">
-        <v>3.05197405815125</v>
+        <v>3.0519745349884</v>
       </c>
       <c r="H322" t="n">
         <v>99798</v>
@@ -9736,7 +9736,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G323" t="n">
-        <v>3.06683278083801</v>
+        <v>3.06683301925659</v>
       </c>
       <c r="H323" t="n">
         <v>58760</v>
@@ -9765,7 +9765,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G324" t="n">
-        <v>3.13815450668335</v>
+        <v>3.13815498352051</v>
       </c>
       <c r="H324" t="n">
         <v>202372</v>
@@ -9794,7 +9794,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G325" t="n">
-        <v>3.12626767158508</v>
+        <v>3.1262674331665</v>
       </c>
       <c r="H325" t="n">
         <v>127239</v>
@@ -9823,7 +9823,7 @@
         <v>5.2350001335144</v>
       </c>
       <c r="G326" t="n">
-        <v>3.11140894889832</v>
+        <v>3.11140847206116</v>
       </c>
       <c r="H326" t="n">
         <v>76315</v>
@@ -9852,7 +9852,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G327" t="n">
-        <v>3.12626767158508</v>
+        <v>3.1262674331665</v>
       </c>
       <c r="H327" t="n">
         <v>103691</v>
@@ -9881,7 +9881,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G328" t="n">
-        <v>3.08466362953186</v>
+        <v>3.08466339111328</v>
       </c>
       <c r="H328" t="n">
         <v>66700</v>
@@ -9910,7 +9910,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G329" t="n">
-        <v>3.10843729972839</v>
+        <v>3.10843753814697</v>
       </c>
       <c r="H329" t="n">
         <v>163620</v>
@@ -9939,7 +9939,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G330" t="n">
-        <v>3.09060668945312</v>
+        <v>3.0906069278717</v>
       </c>
       <c r="H330" t="n">
         <v>128424</v>
@@ -9968,7 +9968,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G331" t="n">
-        <v>3.10843729972839</v>
+        <v>3.10843753814697</v>
       </c>
       <c r="H331" t="n">
         <v>113419</v>
@@ -9997,7 +9997,7 @@
         <v>5.29500007629395</v>
       </c>
       <c r="G332" t="n">
-        <v>3.14706993103027</v>
+        <v>3.14707016944885</v>
       </c>
       <c r="H332" t="n">
         <v>90503</v>
@@ -10026,7 +10026,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G333" t="n">
-        <v>3.185702085495</v>
+        <v>3.18570280075073</v>
       </c>
       <c r="H333" t="n">
         <v>140475</v>
@@ -10055,7 +10055,7 @@
         <v>5.34499979019165</v>
       </c>
       <c r="G334" t="n">
-        <v>3.17678737640381</v>
+        <v>3.17678713798523</v>
       </c>
       <c r="H334" t="n">
         <v>99856</v>
@@ -10113,7 +10113,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G336" t="n">
-        <v>3.15004134178162</v>
+        <v>3.1500415802002</v>
       </c>
       <c r="H336" t="n">
         <v>364841</v>
@@ -10142,7 +10142,7 @@
         <v>5.28499984741211</v>
       </c>
       <c r="G337" t="n">
-        <v>3.14112663269043</v>
+        <v>3.14112639427185</v>
       </c>
       <c r="H337" t="n">
         <v>146417</v>
@@ -10171,7 +10171,7 @@
         <v>5.17500019073486</v>
       </c>
       <c r="G338" t="n">
-        <v>3.07574796676636</v>
+        <v>3.07574844360352</v>
       </c>
       <c r="H338" t="n">
         <v>106130</v>
@@ -10200,7 +10200,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G339" t="n">
-        <v>3.185702085495</v>
+        <v>3.18570280075073</v>
       </c>
       <c r="H339" t="n">
         <v>115723</v>
@@ -10287,7 +10287,7 @@
         <v>5.35500001907349</v>
       </c>
       <c r="G342" t="n">
-        <v>3.18273091316223</v>
+        <v>3.18273067474365</v>
       </c>
       <c r="H342" t="n">
         <v>130806</v>
@@ -10345,7 +10345,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G344" t="n">
-        <v>3.16192865371704</v>
+        <v>3.16192889213562</v>
       </c>
       <c r="H344" t="n">
         <v>70903</v>
@@ -10374,7 +10374,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G345" t="n">
-        <v>3.10249376296997</v>
+        <v>3.10249352455139</v>
       </c>
       <c r="H345" t="n">
         <v>223546</v>
@@ -10403,7 +10403,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G346" t="n">
-        <v>3.04900288581848</v>
+        <v>3.0490026473999</v>
       </c>
       <c r="H346" t="n">
         <v>123014</v>
@@ -10432,7 +10432,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G347" t="n">
-        <v>3.05791759490967</v>
+        <v>3.05791735649109</v>
       </c>
       <c r="H347" t="n">
         <v>74239</v>
@@ -10461,7 +10461,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G348" t="n">
-        <v>3.08466362953186</v>
+        <v>3.08466339111328</v>
       </c>
       <c r="H348" t="n">
         <v>453065</v>
@@ -10490,7 +10490,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G349" t="n">
-        <v>3.06683278083801</v>
+        <v>3.06683301925659</v>
       </c>
       <c r="H349" t="n">
         <v>92763</v>
@@ -10519,7 +10519,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G350" t="n">
-        <v>3.05494594573975</v>
+        <v>3.05494570732117</v>
       </c>
       <c r="H350" t="n">
         <v>106495</v>
@@ -10548,7 +10548,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G351" t="n">
-        <v>3.06088972091675</v>
+        <v>3.06088948249817</v>
       </c>
       <c r="H351" t="n">
         <v>97494</v>
@@ -10577,7 +10577,7 @@
         <v>5.21500015258789</v>
       </c>
       <c r="G352" t="n">
-        <v>3.09952211380005</v>
+        <v>3.09952235221863</v>
       </c>
       <c r="H352" t="n">
         <v>118988</v>
@@ -10606,7 +10606,7 @@
         <v>5.17500019073486</v>
       </c>
       <c r="G353" t="n">
-        <v>3.07574796676636</v>
+        <v>3.07574844360352</v>
       </c>
       <c r="H353" t="n">
         <v>108557</v>
@@ -10635,7 +10635,7 @@
         <v>5.16499996185303</v>
       </c>
       <c r="G354" t="n">
-        <v>3.06980466842651</v>
+        <v>3.06980490684509</v>
       </c>
       <c r="H354" t="n">
         <v>82105</v>
@@ -10664,7 +10664,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G355" t="n">
-        <v>3.07277655601501</v>
+        <v>3.07277631759644</v>
       </c>
       <c r="H355" t="n">
         <v>230549</v>
@@ -10693,7 +10693,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G356" t="n">
-        <v>3.06088972091675</v>
+        <v>3.06088948249817</v>
       </c>
       <c r="H356" t="n">
         <v>91142</v>
@@ -10722,7 +10722,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G357" t="n">
-        <v>3.05791759490967</v>
+        <v>3.05791735649109</v>
       </c>
       <c r="H357" t="n">
         <v>28290</v>
@@ -10751,7 +10751,7 @@
         <v>5.125</v>
       </c>
       <c r="G358" t="n">
-        <v>3.0460307598114</v>
+        <v>3.04603052139282</v>
       </c>
       <c r="H358" t="n">
         <v>40886</v>
@@ -10780,7 +10780,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G359" t="n">
-        <v>3.07277655601501</v>
+        <v>3.07277631759644</v>
       </c>
       <c r="H359" t="n">
         <v>186054</v>
@@ -10809,7 +10809,7 @@
         <v>5.13500022888184</v>
       </c>
       <c r="G360" t="n">
-        <v>3.05197405815125</v>
+        <v>3.0519745349884</v>
       </c>
       <c r="H360" t="n">
         <v>90421</v>
@@ -10838,7 +10838,7 @@
         <v>5.13500022888184</v>
       </c>
       <c r="G361" t="n">
-        <v>3.05197405815125</v>
+        <v>3.0519745349884</v>
       </c>
       <c r="H361" t="n">
         <v>122930</v>
@@ -10867,7 +10867,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G362" t="n">
-        <v>3.06683278083801</v>
+        <v>3.06683301925659</v>
       </c>
       <c r="H362" t="n">
         <v>194545</v>
@@ -10896,7 +10896,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G363" t="n">
-        <v>3.05494594573975</v>
+        <v>3.05494570732117</v>
       </c>
       <c r="H363" t="n">
         <v>74473</v>
@@ -10925,7 +10925,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G364" t="n">
-        <v>3.05791759490967</v>
+        <v>3.05791735649109</v>
       </c>
       <c r="H364" t="n">
         <v>87130</v>
@@ -10954,7 +10954,7 @@
         <v>5.13500022888184</v>
       </c>
       <c r="G365" t="n">
-        <v>3.05197405815125</v>
+        <v>3.0519745349884</v>
       </c>
       <c r="H365" t="n">
         <v>61470</v>
@@ -10983,7 +10983,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G366" t="n">
-        <v>3.05494594573975</v>
+        <v>3.05494570732117</v>
       </c>
       <c r="H366" t="n">
         <v>46236</v>
@@ -11012,7 +11012,7 @@
         <v>5.125</v>
       </c>
       <c r="G367" t="n">
-        <v>3.0460307598114</v>
+        <v>3.04603052139282</v>
       </c>
       <c r="H367" t="n">
         <v>120227</v>
@@ -11041,7 +11041,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G368" t="n">
-        <v>3.06088972091675</v>
+        <v>3.06088948249817</v>
       </c>
       <c r="H368" t="n">
         <v>56278</v>
@@ -11070,7 +11070,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G369" t="n">
-        <v>3.09060668945312</v>
+        <v>3.0906069278717</v>
       </c>
       <c r="H369" t="n">
         <v>221869</v>
@@ -11128,7 +11128,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G371" t="n">
-        <v>3.15598487854004</v>
+        <v>3.1559853553772</v>
       </c>
       <c r="H371" t="n">
         <v>203445</v>
@@ -11157,7 +11157,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G372" t="n">
-        <v>3.09655070304871</v>
+        <v>3.09655046463013</v>
       </c>
       <c r="H372" t="n">
         <v>46233</v>
@@ -11186,7 +11186,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G373" t="n">
-        <v>3.07277655601501</v>
+        <v>3.07277631759644</v>
       </c>
       <c r="H373" t="n">
         <v>246726</v>
@@ -11215,7 +11215,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G374" t="n">
-        <v>3.09655070304871</v>
+        <v>3.09655046463013</v>
       </c>
       <c r="H374" t="n">
         <v>132834</v>
@@ -11244,7 +11244,7 @@
         <v>5.25500011444092</v>
       </c>
       <c r="G375" t="n">
-        <v>3.12329578399658</v>
+        <v>3.12329602241516</v>
       </c>
       <c r="H375" t="n">
         <v>154023</v>
@@ -11273,7 +11273,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G376" t="n">
-        <v>3.06683278083801</v>
+        <v>3.06683301925659</v>
       </c>
       <c r="H376" t="n">
         <v>286681</v>
@@ -11302,7 +11302,7 @@
         <v>5.09499979019165</v>
       </c>
       <c r="G377" t="n">
-        <v>3.02820014953613</v>
+        <v>3.02820038795471</v>
       </c>
       <c r="H377" t="n">
         <v>251588</v>
@@ -11331,7 +11331,7 @@
         <v>5.09499979019165</v>
       </c>
       <c r="G378" t="n">
-        <v>3.02820014953613</v>
+        <v>3.02820038795471</v>
       </c>
       <c r="H378" t="n">
         <v>168308</v>
@@ -11360,7 +11360,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G379" t="n">
-        <v>3.04900288581848</v>
+        <v>3.0490026473999</v>
       </c>
       <c r="H379" t="n">
         <v>177787</v>
@@ -11447,7 +11447,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G382" t="n">
-        <v>2.8172070980072</v>
+        <v>2.81720662117004</v>
       </c>
       <c r="H382" t="n">
         <v>320617</v>
@@ -11476,7 +11476,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G383" t="n">
-        <v>2.79937672615051</v>
+        <v>2.79937696456909</v>
       </c>
       <c r="H383" t="n">
         <v>488102</v>
@@ -11505,7 +11505,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G384" t="n">
-        <v>2.7696590423584</v>
+        <v>2.76965951919556</v>
       </c>
       <c r="H384" t="n">
         <v>576950</v>
@@ -11534,7 +11534,7 @@
         <v>4.71799993515015</v>
       </c>
       <c r="G385" t="n">
-        <v>2.80413103103638</v>
+        <v>2.80413150787354</v>
       </c>
       <c r="H385" t="n">
         <v>265565</v>
@@ -11563,7 +11563,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G386" t="n">
-        <v>2.78748989105225</v>
+        <v>2.78748965263367</v>
       </c>
       <c r="H386" t="n">
         <v>196107</v>
@@ -11592,7 +11592,7 @@
         <v>4.68400001525879</v>
       </c>
       <c r="G387" t="n">
-        <v>2.78392338752747</v>
+        <v>2.78392386436462</v>
       </c>
       <c r="H387" t="n">
         <v>169037</v>
@@ -11621,7 +11621,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G388" t="n">
-        <v>2.85881161689758</v>
+        <v>2.85881114006042</v>
       </c>
       <c r="H388" t="n">
         <v>182848</v>
@@ -11650,7 +11650,7 @@
         <v>4.71400022506714</v>
       </c>
       <c r="G389" t="n">
-        <v>2.80175423622131</v>
+        <v>2.80175399780273</v>
       </c>
       <c r="H389" t="n">
         <v>271772</v>
@@ -11766,7 +11766,7 @@
         <v>4.43400001525879</v>
       </c>
       <c r="G393" t="n">
-        <v>2.63533663749695</v>
+        <v>2.63533687591553</v>
       </c>
       <c r="H393" t="n">
         <v>176582</v>
@@ -11795,7 +11795,7 @@
         <v>4.33599996566772</v>
       </c>
       <c r="G394" t="n">
-        <v>2.57709074020386</v>
+        <v>2.57709050178528</v>
       </c>
       <c r="H394" t="n">
         <v>190947</v>
@@ -11853,7 +11853,7 @@
         <v>4.30600023269653</v>
       </c>
       <c r="G396" t="n">
-        <v>2.55926036834717</v>
+        <v>2.55926012992859</v>
       </c>
       <c r="H396" t="n">
         <v>285753</v>
@@ -11911,7 +11911,7 @@
         <v>4.49599981307983</v>
       </c>
       <c r="G398" t="n">
-        <v>2.67218613624573</v>
+        <v>2.67218589782715</v>
       </c>
       <c r="H398" t="n">
         <v>359368</v>
@@ -12027,7 +12027,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G402" t="n">
-        <v>2.71022391319275</v>
+        <v>2.71022462844849</v>
       </c>
       <c r="H402" t="n">
         <v>122945</v>
@@ -12056,7 +12056,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G403" t="n">
-        <v>2.68645095825195</v>
+        <v>2.68645048141479</v>
       </c>
       <c r="H403" t="n">
         <v>276905</v>
@@ -12085,7 +12085,7 @@
         <v>4.73600006103516</v>
       </c>
       <c r="G404" t="n">
-        <v>2.8148295879364</v>
+        <v>2.81482934951782</v>
       </c>
       <c r="H404" t="n">
         <v>608489</v>
@@ -12114,7 +12114,7 @@
         <v>4.61399984359741</v>
       </c>
       <c r="G405" t="n">
-        <v>2.74231934547424</v>
+        <v>2.74231910705566</v>
       </c>
       <c r="H405" t="n">
         <v>143504</v>
@@ -12172,7 +12172,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G407" t="n">
-        <v>2.73994183540344</v>
+        <v>2.73994159698486</v>
       </c>
       <c r="H407" t="n">
         <v>174008</v>
@@ -12230,7 +12230,7 @@
         <v>4.57600021362305</v>
       </c>
       <c r="G409" t="n">
-        <v>2.71973419189453</v>
+        <v>2.71973395347595</v>
       </c>
       <c r="H409" t="n">
         <v>65945</v>
@@ -12259,7 +12259,7 @@
         <v>4.57600021362305</v>
       </c>
       <c r="G410" t="n">
-        <v>2.71973419189453</v>
+        <v>2.71973395347595</v>
       </c>
       <c r="H410" t="n">
         <v>83746</v>
@@ -12288,7 +12288,7 @@
         <v>4.51599979400635</v>
       </c>
       <c r="G411" t="n">
-        <v>2.68407297134399</v>
+        <v>2.68407320976257</v>
       </c>
       <c r="H411" t="n">
         <v>70296</v>
@@ -12317,7 +12317,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G412" t="n">
-        <v>2.71022391319275</v>
+        <v>2.71022462844849</v>
       </c>
       <c r="H412" t="n">
         <v>110897</v>
@@ -12346,7 +12346,7 @@
         <v>4.48799991607666</v>
       </c>
       <c r="G413" t="n">
-        <v>2.66743135452271</v>
+        <v>2.66743111610413</v>
       </c>
       <c r="H413" t="n">
         <v>168191</v>
@@ -12491,7 +12491,7 @@
         <v>4.67199993133545</v>
       </c>
       <c r="G418" t="n">
-        <v>2.7767915725708</v>
+        <v>2.77679133415222</v>
       </c>
       <c r="H418" t="n">
         <v>157427</v>
@@ -12520,7 +12520,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G419" t="n">
-        <v>2.72805523872375</v>
+        <v>2.72805500030518</v>
       </c>
       <c r="H419" t="n">
         <v>217141</v>
@@ -12549,7 +12549,7 @@
         <v>4.59800004959106</v>
       </c>
       <c r="G420" t="n">
-        <v>2.73280930519104</v>
+        <v>2.73280954360962</v>
       </c>
       <c r="H420" t="n">
         <v>71919</v>
@@ -12578,7 +12578,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G421" t="n">
-        <v>2.74588513374329</v>
+        <v>2.74588537216187</v>
       </c>
       <c r="H421" t="n">
         <v>273873</v>
@@ -12636,7 +12636,7 @@
         <v>4.6560001373291</v>
       </c>
       <c r="G423" t="n">
-        <v>2.76728177070618</v>
+        <v>2.76728224754333</v>
       </c>
       <c r="H423" t="n">
         <v>87837</v>
@@ -12665,7 +12665,7 @@
         <v>4.59800004959106</v>
       </c>
       <c r="G424" t="n">
-        <v>2.73280930519104</v>
+        <v>2.73280954360962</v>
       </c>
       <c r="H424" t="n">
         <v>54186</v>
@@ -12723,7 +12723,7 @@
         <v>4.55600023269653</v>
       </c>
       <c r="G426" t="n">
-        <v>2.70784759521484</v>
+        <v>2.70784735679626</v>
       </c>
       <c r="H426" t="n">
         <v>83993</v>
@@ -12752,7 +12752,7 @@
         <v>4.50799989700317</v>
       </c>
       <c r="G427" t="n">
-        <v>2.67931842803955</v>
+        <v>2.67931795120239</v>
       </c>
       <c r="H427" t="n">
         <v>62972</v>
@@ -12781,7 +12781,7 @@
         <v>4.46199989318848</v>
       </c>
       <c r="G428" t="n">
-        <v>2.65197849273682</v>
+        <v>2.65197825431824</v>
       </c>
       <c r="H428" t="n">
         <v>105523</v>
@@ -12810,7 +12810,7 @@
         <v>4.57399988174438</v>
       </c>
       <c r="G429" t="n">
-        <v>2.71854543685913</v>
+        <v>2.71854496002197</v>
       </c>
       <c r="H429" t="n">
         <v>164053</v>
@@ -12897,7 +12897,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G432" t="n">
-        <v>2.65673351287842</v>
+        <v>2.65673303604126</v>
       </c>
       <c r="H432" t="n">
         <v>91638</v>
@@ -12926,7 +12926,7 @@
         <v>4.48199987411499</v>
       </c>
       <c r="G433" t="n">
-        <v>2.6638650894165</v>
+        <v>2.66386532783508</v>
       </c>
       <c r="H433" t="n">
         <v>70856</v>
@@ -12955,7 +12955,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G434" t="n">
-        <v>2.6923942565918</v>
+        <v>2.69239401817322</v>
       </c>
       <c r="H434" t="n">
         <v>80551</v>
@@ -13013,7 +13013,7 @@
         <v>4.49599981307983</v>
       </c>
       <c r="G436" t="n">
-        <v>2.67218613624573</v>
+        <v>2.67218589782715</v>
       </c>
       <c r="H436" t="n">
         <v>248723</v>
@@ -13100,7 +13100,7 @@
         <v>4.57800006866455</v>
       </c>
       <c r="G439" t="n">
-        <v>2.72092270851135</v>
+        <v>2.72092247009277</v>
       </c>
       <c r="H439" t="n">
         <v>76196</v>
@@ -13158,7 +13158,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G441" t="n">
-        <v>2.86475515365601</v>
+        <v>2.86475467681885</v>
       </c>
       <c r="H441" t="n">
         <v>258995</v>
@@ -13187,7 +13187,7 @@
         <v>4.90199995040894</v>
       </c>
       <c r="G442" t="n">
-        <v>2.91349101066589</v>
+        <v>2.91349124908447</v>
       </c>
       <c r="H442" t="n">
         <v>262634</v>
@@ -13216,7 +13216,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G443" t="n">
-        <v>2.95390653610229</v>
+        <v>2.95390677452087</v>
       </c>
       <c r="H443" t="n">
         <v>243923</v>
@@ -13245,7 +13245,7 @@
         <v>4.85599994659424</v>
       </c>
       <c r="G444" t="n">
-        <v>2.88615107536316</v>
+        <v>2.88615155220032</v>
       </c>
       <c r="H444" t="n">
         <v>231839</v>
@@ -13332,7 +13332,7 @@
         <v>4.73199987411499</v>
       </c>
       <c r="G447" t="n">
-        <v>2.8124520778656</v>
+        <v>2.81245255470276</v>
       </c>
       <c r="H447" t="n">
         <v>98851</v>
@@ -13361,7 +13361,7 @@
         <v>4.76800012588501</v>
       </c>
       <c r="G448" t="n">
-        <v>2.83384895324707</v>
+        <v>2.83384847640991</v>
       </c>
       <c r="H448" t="n">
         <v>101568</v>
@@ -13390,7 +13390,7 @@
         <v>4.81199979782104</v>
       </c>
       <c r="G449" t="n">
-        <v>2.85999989509583</v>
+        <v>2.85999965667725</v>
       </c>
       <c r="H449" t="n">
         <v>101062</v>
@@ -13419,7 +13419,7 @@
         <v>4.77400016784668</v>
       </c>
       <c r="G450" t="n">
-        <v>2.83741521835327</v>
+        <v>2.83741497993469</v>
       </c>
       <c r="H450" t="n">
         <v>115804</v>
@@ -13448,7 +13448,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G451" t="n">
-        <v>2.89447212219238</v>
+        <v>2.89447236061096</v>
       </c>
       <c r="H451" t="n">
         <v>157644</v>
@@ -13477,7 +13477,7 @@
         <v>4.84600019454956</v>
       </c>
       <c r="G452" t="n">
-        <v>2.88020801544189</v>
+        <v>2.88020825386047</v>
       </c>
       <c r="H452" t="n">
         <v>128912</v>
@@ -13564,7 +13564,7 @@
         <v>4.87799978256226</v>
       </c>
       <c r="G455" t="n">
-        <v>2.89922666549683</v>
+        <v>2.89922714233398</v>
       </c>
       <c r="H455" t="n">
         <v>105734</v>
@@ -13593,7 +13593,7 @@
         <v>4.92399978637695</v>
       </c>
       <c r="G456" t="n">
-        <v>2.92656660079956</v>
+        <v>2.92656683921814</v>
       </c>
       <c r="H456" t="n">
         <v>147514</v>
@@ -13651,7 +13651,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G458" t="n">
-        <v>3.00145483016968</v>
+        <v>3.00145506858826</v>
       </c>
       <c r="H458" t="n">
         <v>653587</v>
@@ -13680,7 +13680,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G459" t="n">
-        <v>3.03711605072021</v>
+        <v>3.03711557388306</v>
       </c>
       <c r="H459" t="n">
         <v>507410</v>
@@ -13738,7 +13738,7 @@
         <v>5.02500009536743</v>
       </c>
       <c r="G461" t="n">
-        <v>2.98659634590149</v>
+        <v>2.98659563064575</v>
       </c>
       <c r="H461" t="n">
         <v>259088</v>
@@ -13767,7 +13767,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G462" t="n">
-        <v>3.01334142684937</v>
+        <v>3.01334190368652</v>
       </c>
       <c r="H462" t="n">
         <v>189433</v>
@@ -13796,7 +13796,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G463" t="n">
-        <v>3.04900288581848</v>
+        <v>3.0490026473999</v>
       </c>
       <c r="H463" t="n">
         <v>275636</v>
@@ -13854,7 +13854,7 @@
         <v>4.98600006103516</v>
       </c>
       <c r="G465" t="n">
-        <v>2.96341681480408</v>
+        <v>2.96341633796692</v>
       </c>
       <c r="H465" t="n">
         <v>365178</v>
@@ -13883,7 +13883,7 @@
         <v>5.11499977111816</v>
       </c>
       <c r="G466" t="n">
-        <v>3.0400869846344</v>
+        <v>3.04008722305298</v>
       </c>
       <c r="H466" t="n">
         <v>920387</v>
@@ -13912,7 +13912,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G467" t="n">
-        <v>3.05494594573975</v>
+        <v>3.05494570732117</v>
       </c>
       <c r="H467" t="n">
         <v>1080876</v>
@@ -13941,7 +13941,7 @@
         <v>5.25</v>
       </c>
       <c r="G468" t="n">
-        <v>3.12032437324524</v>
+        <v>3.12032413482666</v>
       </c>
       <c r="H468" t="n">
         <v>599209</v>
@@ -13999,7 +13999,7 @@
         <v>5.25</v>
       </c>
       <c r="G470" t="n">
-        <v>3.12032437324524</v>
+        <v>3.12032413482666</v>
       </c>
       <c r="H470" t="n">
         <v>864726</v>
@@ -14028,7 +14028,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G471" t="n">
-        <v>3.16192865371704</v>
+        <v>3.16192889213562</v>
       </c>
       <c r="H471" t="n">
         <v>695141</v>
@@ -14057,7 +14057,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G472" t="n">
-        <v>3.21541976928711</v>
+        <v>3.21542000770569</v>
       </c>
       <c r="H472" t="n">
         <v>752076</v>
@@ -14144,7 +14144,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G475" t="n">
-        <v>3.15004134178162</v>
+        <v>3.1500415802002</v>
       </c>
       <c r="H475" t="n">
         <v>493758</v>
@@ -14202,7 +14202,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G477" t="n">
-        <v>3.15004134178162</v>
+        <v>3.1500415802002</v>
       </c>
       <c r="H477" t="n">
         <v>466486</v>
@@ -14231,7 +14231,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G478" t="n">
-        <v>3.09060668945312</v>
+        <v>3.0906069278717</v>
       </c>
       <c r="H478" t="n">
         <v>609117</v>
@@ -14289,7 +14289,7 @@
         <v>5.24499988555908</v>
       </c>
       <c r="G480" t="n">
-        <v>3.11735248565674</v>
+        <v>3.1173529624939</v>
       </c>
       <c r="H480" t="n">
         <v>774521</v>
@@ -14347,7 +14347,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G482" t="n">
-        <v>3.15004134178162</v>
+        <v>3.1500415802002</v>
       </c>
       <c r="H482" t="n">
         <v>297729</v>
@@ -14376,7 +14376,7 @@
         <v>5.30499982833862</v>
       </c>
       <c r="G483" t="n">
-        <v>3.15301299095154</v>
+        <v>3.15301322937012</v>
       </c>
       <c r="H483" t="n">
         <v>452499</v>
@@ -14405,7 +14405,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G484" t="n">
-        <v>3.17381548881531</v>
+        <v>3.17381596565247</v>
       </c>
       <c r="H484" t="n">
         <v>513873</v>
@@ -14434,7 +14434,7 @@
         <v>5.34499979019165</v>
       </c>
       <c r="G485" t="n">
-        <v>3.17678737640381</v>
+        <v>3.17678713798523</v>
       </c>
       <c r="H485" t="n">
         <v>257835</v>
@@ -14492,7 +14492,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G487" t="n">
-        <v>3.185702085495</v>
+        <v>3.18570280075073</v>
       </c>
       <c r="H487" t="n">
         <v>273552</v>
@@ -14550,7 +14550,7 @@
         <v>5.35500001907349</v>
       </c>
       <c r="G489" t="n">
-        <v>3.18273091316223</v>
+        <v>3.18273067474365</v>
       </c>
       <c r="H489" t="n">
         <v>247576</v>
@@ -14579,7 +14579,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G490" t="n">
-        <v>3.22730708122253</v>
+        <v>3.22730684280396</v>
       </c>
       <c r="H490" t="n">
         <v>437671</v>
@@ -14608,7 +14608,7 @@
         <v>5.49499988555908</v>
       </c>
       <c r="G491" t="n">
-        <v>3.2659387588501</v>
+        <v>3.26593923568726</v>
       </c>
       <c r="H491" t="n">
         <v>696421</v>
@@ -14637,7 +14637,7 @@
         <v>5.57499980926514</v>
       </c>
       <c r="G492" t="n">
-        <v>3.31348705291748</v>
+        <v>3.3134868144989</v>
       </c>
       <c r="H492" t="n">
         <v>414361</v>
@@ -14695,7 +14695,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G494" t="n">
-        <v>3.29862856864929</v>
+        <v>3.29862833023071</v>
       </c>
       <c r="H494" t="n">
         <v>486720</v>
@@ -14724,7 +14724,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G495" t="n">
-        <v>3.29862856864929</v>
+        <v>3.29862833023071</v>
       </c>
       <c r="H495" t="n">
         <v>335472</v>
@@ -14782,7 +14782,7 @@
         <v>5.5</v>
       </c>
       <c r="G497" t="n">
-        <v>3.26891136169434</v>
+        <v>3.26891112327576</v>
       </c>
       <c r="H497" t="n">
         <v>672154</v>
@@ -14811,7 +14811,7 @@
         <v>5.54500007629395</v>
       </c>
       <c r="G498" t="n">
-        <v>3.29565644264221</v>
+        <v>3.29565668106079</v>
       </c>
       <c r="H498" t="n">
         <v>524663</v>
@@ -14840,7 +14840,7 @@
         <v>5.625</v>
       </c>
       <c r="G499" t="n">
-        <v>3.34320425987244</v>
+        <v>3.34320473670959</v>
       </c>
       <c r="H499" t="n">
         <v>778967</v>
@@ -14869,7 +14869,7 @@
         <v>5.60500001907349</v>
       </c>
       <c r="G500" t="n">
-        <v>3.33131790161133</v>
+        <v>3.33131766319275</v>
       </c>
       <c r="H500" t="n">
         <v>652712</v>
@@ -14898,7 +14898,7 @@
         <v>5.42500019073486</v>
       </c>
       <c r="G501" t="n">
-        <v>3.22433471679688</v>
+        <v>3.22433519363403</v>
       </c>
       <c r="H501" t="n">
         <v>5303704</v>
@@ -14956,7 +14956,7 @@
         <v>4.96500015258789</v>
       </c>
       <c r="G503" t="n">
-        <v>3.27646851539612</v>
+        <v>3.27646827697754</v>
       </c>
       <c r="H503" t="n">
         <v>1438467</v>
@@ -14985,7 +14985,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G504" t="n">
-        <v>3.28306746482849</v>
+        <v>3.28306722640991</v>
       </c>
       <c r="H504" t="n">
         <v>920785</v>
@@ -15014,7 +15014,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G505" t="n">
-        <v>3.29296588897705</v>
+        <v>3.29296612739563</v>
       </c>
       <c r="H505" t="n">
         <v>579212</v>
@@ -15072,7 +15072,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G507" t="n">
-        <v>3.33256053924561</v>
+        <v>3.33256125450134</v>
       </c>
       <c r="H507" t="n">
         <v>310695</v>
@@ -15130,7 +15130,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G509" t="n">
-        <v>3.31936287879944</v>
+        <v>3.31936240196228</v>
       </c>
       <c r="H509" t="n">
         <v>378358</v>
@@ -15217,7 +15217,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G512" t="n">
-        <v>3.40515112876892</v>
+        <v>3.4051513671875</v>
       </c>
       <c r="H512" t="n">
         <v>346400</v>
@@ -15246,7 +15246,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G513" t="n">
-        <v>3.3919529914856</v>
+        <v>3.39195275306702</v>
       </c>
       <c r="H513" t="n">
         <v>270878</v>
@@ -15275,7 +15275,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G514" t="n">
-        <v>3.36555647850037</v>
+        <v>3.36555624008179</v>
       </c>
       <c r="H514" t="n">
         <v>602895</v>
@@ -15304,7 +15304,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G515" t="n">
-        <v>3.41175055503845</v>
+        <v>3.41175031661987</v>
       </c>
       <c r="H515" t="n">
         <v>430306</v>
@@ -15333,7 +15333,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G516" t="n">
-        <v>3.47114253044128</v>
+        <v>3.47114229202271</v>
       </c>
       <c r="H516" t="n">
         <v>419765</v>
@@ -15362,7 +15362,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G517" t="n">
-        <v>3.47114253044128</v>
+        <v>3.47114229202271</v>
       </c>
       <c r="H517" t="n">
         <v>482592</v>
@@ -15420,7 +15420,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G519" t="n">
-        <v>3.50413775444031</v>
+        <v>3.50413846969604</v>
       </c>
       <c r="H519" t="n">
         <v>436693</v>
@@ -15478,7 +15478,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G521" t="n">
-        <v>3.47114253044128</v>
+        <v>3.47114229202271</v>
       </c>
       <c r="H521" t="n">
         <v>297721</v>
@@ -15536,7 +15536,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G523" t="n">
-        <v>3.43154811859131</v>
+        <v>3.43154788017273</v>
       </c>
       <c r="H523" t="n">
         <v>607512</v>
@@ -15565,7 +15565,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G524" t="n">
-        <v>3.39855241775513</v>
+        <v>3.39855217933655</v>
       </c>
       <c r="H524" t="n">
         <v>501174</v>
@@ -15623,7 +15623,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G526" t="n">
-        <v>3.35895776748657</v>
+        <v>3.35895752906799</v>
       </c>
       <c r="H526" t="n">
         <v>209893</v>
@@ -15652,7 +15652,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G527" t="n">
-        <v>3.33256053924561</v>
+        <v>3.33256125450134</v>
       </c>
       <c r="H527" t="n">
         <v>267715</v>
@@ -15681,7 +15681,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G528" t="n">
-        <v>3.31276297569275</v>
+        <v>3.31276321411133</v>
       </c>
       <c r="H528" t="n">
         <v>271659</v>
@@ -15710,7 +15710,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G529" t="n">
-        <v>3.27976727485657</v>
+        <v>3.27976775169373</v>
       </c>
       <c r="H529" t="n">
         <v>302738</v>
@@ -15739,7 +15739,7 @@
         <v>5</v>
       </c>
       <c r="G530" t="n">
-        <v>3.299565076828</v>
+        <v>3.29956531524658</v>
       </c>
       <c r="H530" t="n">
         <v>168461</v>
@@ -15768,7 +15768,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G531" t="n">
-        <v>3.28306746482849</v>
+        <v>3.28306722640991</v>
       </c>
       <c r="H531" t="n">
         <v>132601</v>
@@ -15797,7 +15797,7 @@
         <v>4.9850001335144</v>
       </c>
       <c r="G532" t="n">
-        <v>3.28966641426086</v>
+        <v>3.28966665267944</v>
       </c>
       <c r="H532" t="n">
         <v>183355</v>
@@ -15826,7 +15826,7 @@
         <v>4.9850001335144</v>
       </c>
       <c r="G533" t="n">
-        <v>3.28966641426086</v>
+        <v>3.28966665267944</v>
       </c>
       <c r="H533" t="n">
         <v>185408</v>
@@ -15855,7 +15855,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G534" t="n">
-        <v>3.27316880226135</v>
+        <v>3.27316904067993</v>
       </c>
       <c r="H534" t="n">
         <v>291730</v>
@@ -15884,7 +15884,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G535" t="n">
-        <v>3.30616497993469</v>
+        <v>3.30616402626038</v>
       </c>
       <c r="H535" t="n">
         <v>112782</v>
@@ -15942,7 +15942,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G537" t="n">
-        <v>3.14778542518616</v>
+        <v>3.147784948349</v>
       </c>
       <c r="H537" t="n">
         <v>607886</v>
@@ -15971,7 +15971,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G538" t="n">
-        <v>3.19397902488708</v>
+        <v>3.19397926330566</v>
       </c>
       <c r="H538" t="n">
         <v>185948</v>
@@ -16174,7 +16174,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G545" t="n">
-        <v>3.29296588897705</v>
+        <v>3.29296612739563</v>
       </c>
       <c r="H545" t="n">
         <v>324729</v>
@@ -16203,7 +16203,7 @@
         <v>4.9850001335144</v>
       </c>
       <c r="G546" t="n">
-        <v>3.28966641426086</v>
+        <v>3.28966665267944</v>
       </c>
       <c r="H546" t="n">
         <v>250598</v>
@@ -16232,7 +16232,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G547" t="n">
-        <v>3.31936287879944</v>
+        <v>3.31936240196228</v>
       </c>
       <c r="H547" t="n">
         <v>180843</v>
@@ -16290,7 +16290,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G549" t="n">
-        <v>3.28636717796326</v>
+        <v>3.28636693954468</v>
       </c>
       <c r="H549" t="n">
         <v>71591</v>
@@ -16319,7 +16319,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G550" t="n">
-        <v>3.28306746482849</v>
+        <v>3.28306722640991</v>
       </c>
       <c r="H550" t="n">
         <v>448492</v>
@@ -16348,7 +16348,7 @@
         <v>4.94500017166138</v>
       </c>
       <c r="G551" t="n">
-        <v>3.26327037811279</v>
+        <v>3.26326966285706</v>
       </c>
       <c r="H551" t="n">
         <v>121766</v>
@@ -16377,7 +16377,7 @@
         <v>4.96500015258789</v>
       </c>
       <c r="G552" t="n">
-        <v>3.27646851539612</v>
+        <v>3.27646827697754</v>
       </c>
       <c r="H552" t="n">
         <v>244304</v>
@@ -16406,7 +16406,7 @@
         <v>4.93499994277954</v>
       </c>
       <c r="G553" t="n">
-        <v>3.25667071342468</v>
+        <v>3.25667095184326</v>
       </c>
       <c r="H553" t="n">
         <v>159508</v>
@@ -16435,7 +16435,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G554" t="n">
-        <v>3.24017310142517</v>
+        <v>3.24017333984375</v>
       </c>
       <c r="H554" t="n">
         <v>201398</v>
@@ -16464,7 +16464,7 @@
         <v>4.94500017166138</v>
       </c>
       <c r="G555" t="n">
-        <v>3.26327037811279</v>
+        <v>3.26326966285706</v>
       </c>
       <c r="H555" t="n">
         <v>605541</v>
@@ -16493,7 +16493,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G556" t="n">
-        <v>3.29296588897705</v>
+        <v>3.29296612739563</v>
       </c>
       <c r="H556" t="n">
         <v>732921</v>
@@ -16522,7 +16522,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G557" t="n">
-        <v>3.31936287879944</v>
+        <v>3.31936240196228</v>
       </c>
       <c r="H557" t="n">
         <v>705472</v>
@@ -16551,7 +16551,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G558" t="n">
-        <v>3.28306746482849</v>
+        <v>3.28306722640991</v>
       </c>
       <c r="H558" t="n">
         <v>1567251</v>
@@ -16580,7 +16580,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G559" t="n">
-        <v>3.28306746482849</v>
+        <v>3.28306722640991</v>
       </c>
       <c r="H559" t="n">
         <v>159980</v>
@@ -16638,7 +16638,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G561" t="n">
-        <v>3.20717763900757</v>
+        <v>3.20717716217041</v>
       </c>
       <c r="H561" t="n">
         <v>164491</v>
@@ -16667,7 +16667,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G562" t="n">
-        <v>3.21377611160278</v>
+        <v>3.21377658843994</v>
       </c>
       <c r="H562" t="n">
         <v>261298</v>
@@ -16696,7 +16696,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G563" t="n">
-        <v>3.23357391357422</v>
+        <v>3.23357343673706</v>
       </c>
       <c r="H563" t="n">
         <v>381715</v>
@@ -16725,7 +16725,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G564" t="n">
-        <v>3.25997042655945</v>
+        <v>3.25997090339661</v>
       </c>
       <c r="H564" t="n">
         <v>339536</v>
@@ -16754,7 +16754,7 @@
         <v>4.94500017166138</v>
       </c>
       <c r="G565" t="n">
-        <v>3.26327037811279</v>
+        <v>3.26326966285706</v>
       </c>
       <c r="H565" t="n">
         <v>267459</v>
@@ -16783,7 +16783,7 @@
         <v>5</v>
       </c>
       <c r="G566" t="n">
-        <v>3.299565076828</v>
+        <v>3.29956531524658</v>
       </c>
       <c r="H566" t="n">
         <v>528276</v>
@@ -16812,7 +16812,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G567" t="n">
-        <v>3.33256053924561</v>
+        <v>3.33256125450134</v>
       </c>
       <c r="H567" t="n">
         <v>658583</v>
@@ -16870,7 +16870,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G569" t="n">
-        <v>3.35235857963562</v>
+        <v>3.35235810279846</v>
       </c>
       <c r="H569" t="n">
         <v>293303</v>
@@ -16899,7 +16899,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G570" t="n">
-        <v>3.33256053924561</v>
+        <v>3.33256125450134</v>
       </c>
       <c r="H570" t="n">
         <v>189800</v>
@@ -16928,7 +16928,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G571" t="n">
-        <v>3.35895776748657</v>
+        <v>3.35895752906799</v>
       </c>
       <c r="H571" t="n">
         <v>455695</v>
@@ -16957,7 +16957,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G572" t="n">
-        <v>3.36555647850037</v>
+        <v>3.36555624008179</v>
       </c>
       <c r="H572" t="n">
         <v>211464</v>
@@ -17073,7 +17073,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G576" t="n">
-        <v>3.31936287879944</v>
+        <v>3.31936240196228</v>
       </c>
       <c r="H576" t="n">
         <v>553332</v>
@@ -17189,7 +17189,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G580" t="n">
-        <v>3.23357391357422</v>
+        <v>3.23357343673706</v>
       </c>
       <c r="H580" t="n">
         <v>430468</v>
@@ -17276,7 +17276,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G583" t="n">
-        <v>3.28306746482849</v>
+        <v>3.28306722640991</v>
       </c>
       <c r="H583" t="n">
         <v>211563</v>
@@ -17334,7 +17334,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G585" t="n">
-        <v>3.22697496414185</v>
+        <v>3.22697472572327</v>
       </c>
       <c r="H585" t="n">
         <v>392732</v>
@@ -17363,7 +17363,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G586" t="n">
-        <v>3.23357391357422</v>
+        <v>3.23357343673706</v>
       </c>
       <c r="H586" t="n">
         <v>232065</v>
@@ -17392,7 +17392,7 @@
         <v>4.96500015258789</v>
       </c>
       <c r="G587" t="n">
-        <v>3.27646851539612</v>
+        <v>3.27646827697754</v>
       </c>
       <c r="H587" t="n">
         <v>337593</v>
@@ -17421,7 +17421,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G588" t="n">
-        <v>3.23027467727661</v>
+        <v>3.23027443885803</v>
       </c>
       <c r="H588" t="n">
         <v>169004</v>
@@ -17479,7 +17479,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G590" t="n">
-        <v>3.27316880226135</v>
+        <v>3.27316904067993</v>
       </c>
       <c r="H590" t="n">
         <v>306419</v>
@@ -17508,7 +17508,7 @@
         <v>4.96500015258789</v>
       </c>
       <c r="G591" t="n">
-        <v>3.27646851539612</v>
+        <v>3.27646827697754</v>
       </c>
       <c r="H591" t="n">
         <v>197893</v>
@@ -17537,7 +17537,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G592" t="n">
-        <v>3.20717763900757</v>
+        <v>3.20717716217041</v>
       </c>
       <c r="H592" t="n">
         <v>433144</v>
@@ -17566,7 +17566,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G593" t="n">
-        <v>2.98610687255859</v>
+        <v>2.98610663414001</v>
       </c>
       <c r="H593" t="n">
         <v>1045262</v>
@@ -17595,7 +17595,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G594" t="n">
-        <v>2.93001389503479</v>
+        <v>2.93001365661621</v>
       </c>
       <c r="H594" t="n">
         <v>554636</v>
@@ -17624,7 +17624,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G595" t="n">
-        <v>3.00920343399048</v>
+        <v>3.00920367240906</v>
       </c>
       <c r="H595" t="n">
         <v>548032</v>
@@ -17653,7 +17653,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G596" t="n">
-        <v>2.94321203231812</v>
+        <v>2.94321227073669</v>
       </c>
       <c r="H596" t="n">
         <v>369522</v>
@@ -17682,7 +17682,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G597" t="n">
-        <v>3.03560018539429</v>
+        <v>3.03559994697571</v>
       </c>
       <c r="H597" t="n">
         <v>486651</v>
@@ -17769,7 +17769,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G600" t="n">
-        <v>2.98940658569336</v>
+        <v>2.9894061088562</v>
       </c>
       <c r="H600" t="n">
         <v>483306</v>
@@ -17798,7 +17798,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G601" t="n">
-        <v>3.03560018539429</v>
+        <v>3.03559994697571</v>
       </c>
       <c r="H601" t="n">
         <v>278051</v>
@@ -17856,7 +17856,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G603" t="n">
-        <v>3.00260424613953</v>
+        <v>3.00260448455811</v>
       </c>
       <c r="H603" t="n">
         <v>113692</v>
@@ -17885,7 +17885,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G604" t="n">
-        <v>3.02240180969238</v>
+        <v>3.02240204811096</v>
       </c>
       <c r="H604" t="n">
         <v>315725</v>
@@ -17972,7 +17972,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G607" t="n">
-        <v>3.04219913482666</v>
+        <v>3.04219889640808</v>
       </c>
       <c r="H607" t="n">
         <v>231932</v>
@@ -18001,7 +18001,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G608" t="n">
-        <v>3.05539751052856</v>
+        <v>3.05539703369141</v>
       </c>
       <c r="H608" t="n">
         <v>214042</v>
@@ -18030,7 +18030,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G609" t="n">
-        <v>3.06859588623047</v>
+        <v>3.06859540939331</v>
       </c>
       <c r="H609" t="n">
         <v>181645</v>
@@ -18059,7 +18059,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G610" t="n">
-        <v>3.06859588623047</v>
+        <v>3.06859540939331</v>
       </c>
       <c r="H610" t="n">
         <v>433730</v>
@@ -18088,7 +18088,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G611" t="n">
-        <v>3.08839321136475</v>
+        <v>3.08839273452759</v>
       </c>
       <c r="H611" t="n">
         <v>391802</v>
@@ -18146,7 +18146,7 @@
         <v>4.75</v>
       </c>
       <c r="G613" t="n">
-        <v>3.13458728790283</v>
+        <v>3.13458704948425</v>
       </c>
       <c r="H613" t="n">
         <v>239817</v>
@@ -18175,7 +18175,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G614" t="n">
-        <v>3.17418169975281</v>
+        <v>3.17418146133423</v>
       </c>
       <c r="H614" t="n">
         <v>516589</v>
@@ -18204,7 +18204,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G615" t="n">
-        <v>3.17418169975281</v>
+        <v>3.17418146133423</v>
       </c>
       <c r="H615" t="n">
         <v>772590</v>
@@ -18262,7 +18262,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G617" t="n">
-        <v>3.20717763900757</v>
+        <v>3.20717716217041</v>
       </c>
       <c r="H617" t="n">
         <v>392932</v>
@@ -18291,7 +18291,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G618" t="n">
-        <v>3.18738031387329</v>
+        <v>3.18737983703613</v>
       </c>
       <c r="H618" t="n">
         <v>209724</v>
@@ -18320,7 +18320,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G619" t="n">
-        <v>3.15438437461853</v>
+        <v>3.15438461303711</v>
       </c>
       <c r="H619" t="n">
         <v>220794</v>
@@ -18349,7 +18349,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G620" t="n">
-        <v>3.18078088760376</v>
+        <v>3.18078064918518</v>
       </c>
       <c r="H620" t="n">
         <v>233302</v>
@@ -18378,7 +18378,7 @@
         <v>4.875</v>
       </c>
       <c r="G621" t="n">
-        <v>3.21707630157471</v>
+        <v>3.21707582473755</v>
       </c>
       <c r="H621" t="n">
         <v>150933</v>
@@ -18552,7 +18552,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G627" t="n">
-        <v>3.17418169975281</v>
+        <v>3.17418146133423</v>
       </c>
       <c r="H627" t="n">
         <v>513181</v>
@@ -18610,7 +18610,7 @@
         <v>4.75500011444092</v>
       </c>
       <c r="G629" t="n">
-        <v>3.13788628578186</v>
+        <v>3.13788652420044</v>
       </c>
       <c r="H629" t="n">
         <v>196694</v>
@@ -18639,7 +18639,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G630" t="n">
-        <v>3.10159134864807</v>
+        <v>3.10159111022949</v>
       </c>
       <c r="H630" t="n">
         <v>399107</v>
@@ -18668,7 +18668,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G631" t="n">
-        <v>3.10819029808044</v>
+        <v>3.1081907749176</v>
       </c>
       <c r="H631" t="n">
         <v>267135</v>
@@ -18697,7 +18697,7 @@
         <v>4.75</v>
       </c>
       <c r="G632" t="n">
-        <v>3.13458728790283</v>
+        <v>3.13458704948425</v>
       </c>
       <c r="H632" t="n">
         <v>285250</v>
@@ -18755,7 +18755,7 @@
         <v>4.80499982833862</v>
       </c>
       <c r="G634" t="n">
-        <v>3.17088174819946</v>
+        <v>3.17088222503662</v>
       </c>
       <c r="H634" t="n">
         <v>318243</v>
@@ -18784,7 +18784,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G635" t="n">
-        <v>3.20057797431946</v>
+        <v>3.20057821273804</v>
       </c>
       <c r="H635" t="n">
         <v>355617</v>
@@ -18842,7 +18842,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G637" t="n">
-        <v>3.28306746482849</v>
+        <v>3.28306722640991</v>
       </c>
       <c r="H637" t="n">
         <v>517201</v>
@@ -18871,7 +18871,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G638" t="n">
-        <v>3.31936287879944</v>
+        <v>3.31936240196228</v>
       </c>
       <c r="H638" t="n">
         <v>324782</v>
@@ -18900,7 +18900,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G639" t="n">
-        <v>3.35895776748657</v>
+        <v>3.35895752906799</v>
       </c>
       <c r="H639" t="n">
         <v>367299</v>
@@ -19016,7 +19016,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G643" t="n">
-        <v>3.48434090614319</v>
+        <v>3.48434114456177</v>
       </c>
       <c r="H643" t="n">
         <v>989076</v>
@@ -19045,7 +19045,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G644" t="n">
-        <v>3.55033230781555</v>
+        <v>3.55033206939697</v>
       </c>
       <c r="H644" t="n">
         <v>810423</v>
@@ -19074,7 +19074,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G645" t="n">
-        <v>3.54373264312744</v>
+        <v>3.54373288154602</v>
       </c>
       <c r="H645" t="n">
         <v>270515</v>
@@ -19132,7 +19132,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G647" t="n">
-        <v>3.5569314956665</v>
+        <v>3.55693125724792</v>
       </c>
       <c r="H647" t="n">
         <v>182303</v>
@@ -19190,7 +19190,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G649" t="n">
-        <v>3.61632370948792</v>
+        <v>3.61632323265076</v>
       </c>
       <c r="H649" t="n">
         <v>682311</v>
@@ -19219,7 +19219,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G650" t="n">
-        <v>3.58332753181458</v>
+        <v>3.58332800865173</v>
       </c>
       <c r="H650" t="n">
         <v>463002</v>
@@ -19248,7 +19248,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G651" t="n">
-        <v>3.58332753181458</v>
+        <v>3.58332800865173</v>
       </c>
       <c r="H651" t="n">
         <v>259823</v>
@@ -19393,7 +19393,7 @@
         <v>5.5</v>
       </c>
       <c r="G656" t="n">
-        <v>3.62952208518982</v>
+        <v>3.62952184677124</v>
       </c>
       <c r="H656" t="n">
         <v>522326</v>
@@ -19451,7 +19451,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G658" t="n">
-        <v>3.48434090614319</v>
+        <v>3.48434114456177</v>
       </c>
       <c r="H658" t="n">
         <v>676372</v>
@@ -19538,7 +19538,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G661" t="n">
-        <v>3.52393579483032</v>
+        <v>3.5239360332489</v>
       </c>
       <c r="H661" t="n">
         <v>322262</v>
@@ -19625,7 +19625,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G664" t="n">
-        <v>3.47114253044128</v>
+        <v>3.47114229202271</v>
       </c>
       <c r="H664" t="n">
         <v>357968</v>
@@ -19654,7 +19654,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G665" t="n">
-        <v>3.44474625587463</v>
+        <v>3.44474577903748</v>
       </c>
       <c r="H665" t="n">
         <v>534929</v>
@@ -19683,7 +19683,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G666" t="n">
-        <v>3.47114253044128</v>
+        <v>3.47114229202271</v>
       </c>
       <c r="H666" t="n">
         <v>307259</v>
@@ -19741,7 +19741,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G668" t="n">
-        <v>3.5569314956665</v>
+        <v>3.55693125724792</v>
       </c>
       <c r="H668" t="n">
         <v>462341</v>
@@ -19799,7 +19799,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G670" t="n">
-        <v>3.5767285823822</v>
+        <v>3.57672834396362</v>
       </c>
       <c r="H670" t="n">
         <v>1287483</v>
@@ -19857,7 +19857,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G672" t="n">
-        <v>3.60312509536743</v>
+        <v>3.60312485694885</v>
       </c>
       <c r="H672" t="n">
         <v>642386</v>
@@ -19886,7 +19886,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G673" t="n">
-        <v>3.54373264312744</v>
+        <v>3.54373288154602</v>
       </c>
       <c r="H673" t="n">
         <v>753716</v>
@@ -19944,7 +19944,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G675" t="n">
-        <v>3.53713393211365</v>
+        <v>3.53713417053223</v>
       </c>
       <c r="H675" t="n">
         <v>179341</v>
@@ -19973,7 +19973,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G676" t="n">
-        <v>3.55033230781555</v>
+        <v>3.55033206939697</v>
       </c>
       <c r="H676" t="n">
         <v>194556</v>
@@ -20060,7 +20060,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G679" t="n">
-        <v>3.49753975868225</v>
+        <v>3.49753904342651</v>
       </c>
       <c r="H679" t="n">
         <v>182643</v>
@@ -20089,7 +20089,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G680" t="n">
-        <v>3.54373264312744</v>
+        <v>3.54373288154602</v>
       </c>
       <c r="H680" t="n">
         <v>144245</v>
@@ -20205,7 +20205,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G684" t="n">
-        <v>3.50413775444031</v>
+        <v>3.50413846969604</v>
       </c>
       <c r="H684" t="n">
         <v>311667</v>
@@ -20234,7 +20234,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G685" t="n">
-        <v>3.55033230781555</v>
+        <v>3.55033206939697</v>
       </c>
       <c r="H685" t="n">
         <v>218627</v>
@@ -20321,7 +20321,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G688" t="n">
-        <v>3.49753975868225</v>
+        <v>3.49753904342651</v>
       </c>
       <c r="H688" t="n">
         <v>161714</v>
@@ -20350,7 +20350,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G689" t="n">
-        <v>3.47774195671082</v>
+        <v>3.47774147987366</v>
       </c>
       <c r="H689" t="n">
         <v>116557</v>
@@ -20379,7 +20379,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G690" t="n">
-        <v>3.52393579483032</v>
+        <v>3.5239360332489</v>
       </c>
       <c r="H690" t="n">
         <v>131707</v>
@@ -20408,7 +20408,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G691" t="n">
-        <v>3.54373264312744</v>
+        <v>3.54373288154602</v>
       </c>
       <c r="H691" t="n">
         <v>183512</v>
@@ -20437,7 +20437,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G692" t="n">
-        <v>3.50413775444031</v>
+        <v>3.50413846969604</v>
       </c>
       <c r="H692" t="n">
         <v>281512</v>
@@ -20466,7 +20466,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G693" t="n">
-        <v>3.49753975868225</v>
+        <v>3.49753904342651</v>
       </c>
       <c r="H693" t="n">
         <v>236744</v>
@@ -20524,7 +20524,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G695" t="n">
-        <v>3.53713393211365</v>
+        <v>3.53713417053223</v>
       </c>
       <c r="H695" t="n">
         <v>235432</v>
@@ -20553,7 +20553,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G696" t="n">
-        <v>3.5569314956665</v>
+        <v>3.55693125724792</v>
       </c>
       <c r="H696" t="n">
         <v>284871</v>
@@ -20640,7 +20640,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G699" t="n">
-        <v>3.5569314956665</v>
+        <v>3.55693125724792</v>
       </c>
       <c r="H699" t="n">
         <v>963684</v>
@@ -20698,7 +20698,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G701" t="n">
-        <v>3.53713393211365</v>
+        <v>3.53713417053223</v>
       </c>
       <c r="H701" t="n">
         <v>340867</v>
@@ -20727,7 +20727,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G702" t="n">
-        <v>3.58992695808411</v>
+        <v>3.58992719650269</v>
       </c>
       <c r="H702" t="n">
         <v>385089</v>
@@ -20756,7 +20756,7 @@
         <v>5.5</v>
       </c>
       <c r="G703" t="n">
-        <v>3.62952208518982</v>
+        <v>3.62952184677124</v>
       </c>
       <c r="H703" t="n">
         <v>607552</v>
@@ -20785,7 +20785,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G704" t="n">
-        <v>3.70871090888977</v>
+        <v>3.70871138572693</v>
       </c>
       <c r="H704" t="n">
         <v>835923</v>
@@ -20814,7 +20814,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G705" t="n">
-        <v>3.72850847244263</v>
+        <v>3.72850871086121</v>
       </c>
       <c r="H705" t="n">
         <v>1055303</v>
@@ -20843,7 +20843,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G706" t="n">
-        <v>3.74170660972595</v>
+        <v>3.74170708656311</v>
       </c>
       <c r="H706" t="n">
         <v>599094</v>
@@ -20872,7 +20872,7 @@
         <v>5.75</v>
       </c>
       <c r="G707" t="n">
-        <v>3.79450035095215</v>
+        <v>3.79450011253357</v>
       </c>
       <c r="H707" t="n">
         <v>1836747</v>
@@ -20901,7 +20901,7 @@
         <v>5.75</v>
       </c>
       <c r="G708" t="n">
-        <v>3.79450035095215</v>
+        <v>3.79450011253357</v>
       </c>
       <c r="H708" t="n">
         <v>1115236</v>
@@ -20959,7 +20959,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G710" t="n">
-        <v>3.74830603599548</v>
+        <v>3.7483057975769</v>
       </c>
       <c r="H710" t="n">
         <v>838597</v>
@@ -20988,7 +20988,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G711" t="n">
-        <v>3.66251754760742</v>
+        <v>3.66251730918884</v>
       </c>
       <c r="H711" t="n">
         <v>543254</v>
@@ -21017,7 +21017,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G712" t="n">
-        <v>3.66251754760742</v>
+        <v>3.66251730918884</v>
       </c>
       <c r="H712" t="n">
         <v>667564</v>
@@ -21046,7 +21046,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G713" t="n">
-        <v>3.68891382217407</v>
+        <v>3.68891406059265</v>
       </c>
       <c r="H713" t="n">
         <v>447125</v>
@@ -21075,7 +21075,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G714" t="n">
-        <v>3.70871090888977</v>
+        <v>3.70871138572693</v>
       </c>
       <c r="H714" t="n">
         <v>295322</v>
@@ -21133,7 +21133,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G716" t="n">
-        <v>3.74830603599548</v>
+        <v>3.7483057975769</v>
       </c>
       <c r="H716" t="n">
         <v>696688</v>
@@ -21162,7 +21162,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G717" t="n">
-        <v>3.74830603599548</v>
+        <v>3.7483057975769</v>
       </c>
       <c r="H717" t="n">
         <v>330391</v>
@@ -21191,7 +21191,7 @@
         <v>5.73999977111816</v>
       </c>
 